--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋143湖光月色</t>
+  </si>
+  <si>
+    <t>#先锋144无尽王国</t>
   </si>
   <si>
     <t>Center</t>
@@ -1257,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12420,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>14401</v>
+      </c>
+      <c r="D657" s="3">
+        <v>144</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20415</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>14402</v>
+      </c>
+      <c r="D658" s="3">
+        <v>144</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20416</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>14403</v>
+      </c>
+      <c r="D659" s="3">
+        <v>144</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>14404</v>
+      </c>
+      <c r="D660" s="3">
+        <v>144</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20418</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>14405</v>
+      </c>
+      <c r="D661" s="3">
+        <v>144</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>14406</v>
+      </c>
+      <c r="D662" s="3">
+        <v>144</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>14407</v>
+      </c>
+      <c r="D663" s="3">
+        <v>144</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>14408</v>
+      </c>
+      <c r="D664" s="3">
+        <v>144</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>14409</v>
+      </c>
+      <c r="D665" s="3">
+        <v>144</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>14410</v>
+      </c>
+      <c r="D666" s="3">
+        <v>144</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>14411</v>
+      </c>
+      <c r="D667" s="3">
+        <v>144</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>14412</v>
+      </c>
+      <c r="D668" s="3">
+        <v>144</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>14413</v>
+      </c>
+      <c r="D669" s="3">
+        <v>144</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>14414</v>
+      </c>
+      <c r="D670" s="3">
+        <v>144</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>14415</v>
+      </c>
+      <c r="D671" s="3">
+        <v>144</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>14416</v>
+      </c>
+      <c r="D672" s="3">
+        <v>144</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>14417</v>
+      </c>
+      <c r="D673" s="3">
+        <v>144</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>14418</v>
+      </c>
+      <c r="D674" s="3">
+        <v>144</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>14419</v>
+      </c>
+      <c r="D675" s="3">
+        <v>144</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>14420</v>
+      </c>
+      <c r="D676" s="3">
+        <v>144</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>14421</v>
+      </c>
+      <c r="D677" s="3">
+        <v>144</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>14422</v>
+      </c>
+      <c r="D678" s="3">
+        <v>144</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>14423</v>
+      </c>
+      <c r="D679" s="3">
+        <v>144</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>14424</v>
+      </c>
+      <c r="D680" s="3">
+        <v>144</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>14425</v>
+      </c>
+      <c r="D681" s="3">
+        <v>144</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12540,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12558,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12576,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12594,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12614,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12712,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋144无尽王国</t>
+  </si>
+  <si>
+    <t>#先锋145</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>14501</v>
+      </c>
+      <c r="D683" s="3">
+        <v>145</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20375</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>14502</v>
+      </c>
+      <c r="D684" s="3">
+        <v>145</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20376</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>14503</v>
+      </c>
+      <c r="D685" s="3">
+        <v>145</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20377</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>14504</v>
+      </c>
+      <c r="D686" s="3">
+        <v>145</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20378</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>14505</v>
+      </c>
+      <c r="D687" s="3">
+        <v>145</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>14506</v>
+      </c>
+      <c r="D688" s="3">
+        <v>145</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>14507</v>
+      </c>
+      <c r="D689" s="3">
+        <v>145</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>14508</v>
+      </c>
+      <c r="D690" s="3">
+        <v>145</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>14509</v>
+      </c>
+      <c r="D691" s="3">
+        <v>145</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>14510</v>
+      </c>
+      <c r="D692" s="3">
+        <v>145</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>14511</v>
+      </c>
+      <c r="D693" s="3">
+        <v>145</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>14512</v>
+      </c>
+      <c r="D694" s="3">
+        <v>145</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>14513</v>
+      </c>
+      <c r="D695" s="3">
+        <v>145</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>14514</v>
+      </c>
+      <c r="D696" s="3">
+        <v>145</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>14515</v>
+      </c>
+      <c r="D697" s="3">
+        <v>145</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>14516</v>
+      </c>
+      <c r="D698" s="3">
+        <v>145</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>14517</v>
+      </c>
+      <c r="D699" s="3">
+        <v>145</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>14518</v>
+      </c>
+      <c r="D700" s="3">
+        <v>145</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>14519</v>
+      </c>
+      <c r="D701" s="3">
+        <v>145</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>14520</v>
+      </c>
+      <c r="D702" s="3">
+        <v>145</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>14521</v>
+      </c>
+      <c r="D703" s="3">
+        <v>145</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>14522</v>
+      </c>
+      <c r="D704" s="3">
+        <v>145</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>14523</v>
+      </c>
+      <c r="D705" s="3">
+        <v>145</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>14524</v>
+      </c>
+      <c r="D706" s="3">
+        <v>145</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>14525</v>
+      </c>
+      <c r="D707" s="3">
+        <v>145</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -235,7 +235,10 @@
     <t>#先锋144无尽王国</t>
   </si>
   <si>
-    <t>#先锋145</t>
+    <t>#先锋145一统山河</t>
+  </si>
+  <si>
+    <t>#先锋146</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>14601</v>
+      </c>
+      <c r="D709" s="3">
+        <v>146</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>14602</v>
+      </c>
+      <c r="D710" s="3">
+        <v>146</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="711" spans="3:8">
+      <c r="C711" s="6">
+        <v>14603</v>
+      </c>
+      <c r="D711" s="3">
+        <v>146</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="712" spans="3:8">
+      <c r="C712" s="6">
+        <v>14604</v>
+      </c>
+      <c r="D712" s="3">
+        <v>146</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="713" spans="3:7">
+      <c r="C713" s="6">
+        <v>14605</v>
+      </c>
+      <c r="D713" s="3">
+        <v>146</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="3:7">
+      <c r="C714" s="6">
+        <v>14606</v>
+      </c>
+      <c r="D714" s="3">
+        <v>146</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="3:7">
+      <c r="C715" s="6">
+        <v>14607</v>
+      </c>
+      <c r="D715" s="3">
+        <v>146</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="3:7">
+      <c r="C716" s="6">
+        <v>14608</v>
+      </c>
+      <c r="D716" s="3">
+        <v>146</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="3:7">
+      <c r="C717" s="6">
+        <v>14609</v>
+      </c>
+      <c r="D717" s="3">
+        <v>146</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="3:7">
+      <c r="C718" s="6">
+        <v>14610</v>
+      </c>
+      <c r="D718" s="3">
+        <v>146</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="3:7">
+      <c r="C719" s="6">
+        <v>14611</v>
+      </c>
+      <c r="D719" s="3">
+        <v>146</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="3:7">
+      <c r="C720" s="6">
+        <v>14612</v>
+      </c>
+      <c r="D720" s="3">
+        <v>146</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>14613</v>
+      </c>
+      <c r="D721" s="3">
+        <v>146</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>14614</v>
+      </c>
+      <c r="D722" s="3">
+        <v>146</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>14615</v>
+      </c>
+      <c r="D723" s="3">
+        <v>146</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>14616</v>
+      </c>
+      <c r="D724" s="3">
+        <v>146</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>14617</v>
+      </c>
+      <c r="D725" s="3">
+        <v>146</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>14618</v>
+      </c>
+      <c r="D726" s="3">
+        <v>146</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>14619</v>
+      </c>
+      <c r="D727" s="3">
+        <v>146</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>14620</v>
+      </c>
+      <c r="D728" s="3">
+        <v>146</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>14621</v>
+      </c>
+      <c r="D729" s="3">
+        <v>146</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>14622</v>
+      </c>
+      <c r="D730" s="3">
+        <v>146</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>14623</v>
+      </c>
+      <c r="D731" s="3">
+        <v>146</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>14624</v>
+      </c>
+      <c r="D732" s="3">
+        <v>146</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>14625</v>
+      </c>
+      <c r="D733" s="3">
+        <v>146</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -238,7 +238,7 @@
     <t>#先锋145一统山河</t>
   </si>
   <si>
-    <t>#先锋146</t>
+    <t>#先锋146星辰坠落</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋146星辰坠落</t>
+  </si>
+  <si>
+    <t>#先锋147紫禁之巅</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>14701</v>
+      </c>
+      <c r="D735" s="3">
+        <v>147</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20495</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>14702</v>
+      </c>
+      <c r="D736" s="3">
+        <v>147</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20496</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>14703</v>
+      </c>
+      <c r="D737" s="3">
+        <v>147</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20497</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>14704</v>
+      </c>
+      <c r="D738" s="3">
+        <v>147</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20498</v>
+      </c>
+    </row>
+    <row r="739" spans="3:7">
+      <c r="C739" s="6">
+        <v>14705</v>
+      </c>
+      <c r="D739" s="3">
+        <v>147</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:7">
+      <c r="C740" s="6">
+        <v>14706</v>
+      </c>
+      <c r="D740" s="3">
+        <v>147</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:7">
+      <c r="C741" s="6">
+        <v>14707</v>
+      </c>
+      <c r="D741" s="3">
+        <v>147</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:7">
+      <c r="C742" s="6">
+        <v>14708</v>
+      </c>
+      <c r="D742" s="3">
+        <v>147</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:7">
+      <c r="C743" s="6">
+        <v>14709</v>
+      </c>
+      <c r="D743" s="3">
+        <v>147</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:7">
+      <c r="C744" s="6">
+        <v>14710</v>
+      </c>
+      <c r="D744" s="3">
+        <v>147</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:7">
+      <c r="C745" s="6">
+        <v>14711</v>
+      </c>
+      <c r="D745" s="3">
+        <v>147</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:7">
+      <c r="C746" s="6">
+        <v>14712</v>
+      </c>
+      <c r="D746" s="3">
+        <v>147</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:7">
+      <c r="C747" s="6">
+        <v>14713</v>
+      </c>
+      <c r="D747" s="3">
+        <v>147</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:7">
+      <c r="C748" s="6">
+        <v>14714</v>
+      </c>
+      <c r="D748" s="3">
+        <v>147</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:7">
+      <c r="C749" s="6">
+        <v>14715</v>
+      </c>
+      <c r="D749" s="3">
+        <v>147</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:7">
+      <c r="C750" s="6">
+        <v>14716</v>
+      </c>
+      <c r="D750" s="3">
+        <v>147</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:7">
+      <c r="C751" s="6">
+        <v>14717</v>
+      </c>
+      <c r="D751" s="3">
+        <v>147</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:7">
+      <c r="C752" s="6">
+        <v>14718</v>
+      </c>
+      <c r="D752" s="3">
+        <v>147</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>14719</v>
+      </c>
+      <c r="D753" s="3">
+        <v>147</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>14720</v>
+      </c>
+      <c r="D754" s="3">
+        <v>147</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>14721</v>
+      </c>
+      <c r="D755" s="3">
+        <v>147</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>14722</v>
+      </c>
+      <c r="D756" s="3">
+        <v>147</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>14723</v>
+      </c>
+      <c r="D757" s="3">
+        <v>147</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>14724</v>
+      </c>
+      <c r="D758" s="3">
+        <v>147</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>14725</v>
+      </c>
+      <c r="D759" s="3">
+        <v>147</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>#先锋147紫禁之巅</t>
+  </si>
+  <si>
+    <t>#先锋148</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O785"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14200,6 +14203,448 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C761" s="6">
+        <v>14801</v>
+      </c>
+      <c r="D761" s="3">
+        <v>148</v>
+      </c>
+      <c r="E761" s="5">
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H761" s="3">
+        <v>20585</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="6">
+        <v>14802</v>
+      </c>
+      <c r="D762" s="3">
+        <v>148</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20586</v>
+      </c>
+    </row>
+    <row r="763" spans="3:8">
+      <c r="C763" s="6">
+        <v>14803</v>
+      </c>
+      <c r="D763" s="3">
+        <v>148</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20587</v>
+      </c>
+    </row>
+    <row r="764" spans="3:8">
+      <c r="C764" s="6">
+        <v>14804</v>
+      </c>
+      <c r="D764" s="3">
+        <v>148</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20588</v>
+      </c>
+    </row>
+    <row r="765" spans="3:7">
+      <c r="C765" s="6">
+        <v>14805</v>
+      </c>
+      <c r="D765" s="3">
+        <v>148</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="3:7">
+      <c r="C766" s="6">
+        <v>14806</v>
+      </c>
+      <c r="D766" s="3">
+        <v>148</v>
+      </c>
+      <c r="E766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="767" spans="3:7">
+      <c r="C767" s="6">
+        <v>14807</v>
+      </c>
+      <c r="D767" s="3">
+        <v>148</v>
+      </c>
+      <c r="E767" s="5">
+        <v>1</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="3:7">
+      <c r="C768" s="6">
+        <v>14808</v>
+      </c>
+      <c r="D768" s="3">
+        <v>148</v>
+      </c>
+      <c r="E768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>14809</v>
+      </c>
+      <c r="D769" s="3">
+        <v>148</v>
+      </c>
+      <c r="E769" s="3">
+        <v>1</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>14810</v>
+      </c>
+      <c r="D770" s="3">
+        <v>148</v>
+      </c>
+      <c r="E770" s="5">
+        <v>1</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>14811</v>
+      </c>
+      <c r="D771" s="3">
+        <v>148</v>
+      </c>
+      <c r="E771" s="5">
+        <v>1</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>14812</v>
+      </c>
+      <c r="D772" s="3">
+        <v>148</v>
+      </c>
+      <c r="E772" s="5">
+        <v>1</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>14813</v>
+      </c>
+      <c r="D773" s="3">
+        <v>148</v>
+      </c>
+      <c r="E773" s="3">
+        <v>1</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>14814</v>
+      </c>
+      <c r="D774" s="3">
+        <v>148</v>
+      </c>
+      <c r="E774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>14815</v>
+      </c>
+      <c r="D775" s="3">
+        <v>148</v>
+      </c>
+      <c r="E775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>14816</v>
+      </c>
+      <c r="D776" s="3">
+        <v>148</v>
+      </c>
+      <c r="E776" s="5">
+        <v>1</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>14817</v>
+      </c>
+      <c r="D777" s="3">
+        <v>148</v>
+      </c>
+      <c r="E777" s="3">
+        <v>1</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>14818</v>
+      </c>
+      <c r="D778" s="3">
+        <v>148</v>
+      </c>
+      <c r="E778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>14819</v>
+      </c>
+      <c r="D779" s="3">
+        <v>148</v>
+      </c>
+      <c r="E779" s="5">
+        <v>1</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>14820</v>
+      </c>
+      <c r="D780" s="3">
+        <v>148</v>
+      </c>
+      <c r="E780" s="5">
+        <v>1</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>14821</v>
+      </c>
+      <c r="D781" s="3">
+        <v>148</v>
+      </c>
+      <c r="E781" s="3">
+        <v>1</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>14822</v>
+      </c>
+      <c r="D782" s="3">
+        <v>148</v>
+      </c>
+      <c r="E782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>14823</v>
+      </c>
+      <c r="D783" s="3">
+        <v>148</v>
+      </c>
+      <c r="E783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>14824</v>
+      </c>
+      <c r="D784" s="3">
+        <v>148</v>
+      </c>
+      <c r="E784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>14825</v>
+      </c>
+      <c r="D785" s="3">
+        <v>148</v>
+      </c>
+      <c r="E785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +14765,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +14783,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +14801,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +14819,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +14839,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14937,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -214,19 +214,10 @@
     <t>#先锋135永恒之境</t>
   </si>
   <si>
-    <t>#先锋137千山万水</t>
-  </si>
-  <si>
     <t>#先锋139吉祥如意</t>
   </si>
   <si>
-    <t>#先锋140新年快乐</t>
-  </si>
-  <si>
     <t>#先锋141恭喜发财</t>
-  </si>
-  <si>
-    <t>#先锋142元宵佳节</t>
   </si>
   <si>
     <t>#先锋143湖光月色</t>
@@ -244,7 +235,7 @@
     <t>#先锋147紫禁之巅</t>
   </si>
   <si>
-    <t>#先锋148</t>
+    <t>#先锋148威震天下</t>
   </si>
   <si>
     <t>Center</t>
@@ -1272,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O785"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -9791,10 +9782,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>13701</v>
+        <v>13901</v>
       </c>
       <c r="D501" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9806,17 +9797,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20445</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>13702</v>
+        <v>13902</v>
       </c>
       <c r="D502" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9828,15 +9819,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20446</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>13703</v>
+        <v>13903</v>
       </c>
       <c r="D503" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9848,15 +9839,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20447</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>13704</v>
+        <v>13904</v>
       </c>
       <c r="D504" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9868,15 +9859,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20448</v>
+        <v>20478</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>13705</v>
+        <v>13905</v>
       </c>
       <c r="D505" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9890,10 +9881,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>13706</v>
+        <v>13906</v>
       </c>
       <c r="D506" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9907,10 +9898,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>13707</v>
+        <v>13907</v>
       </c>
       <c r="D507" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9924,10 +9915,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>13708</v>
+        <v>13908</v>
       </c>
       <c r="D508" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9941,10 +9932,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>13709</v>
+        <v>13909</v>
       </c>
       <c r="D509" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9958,10 +9949,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>13710</v>
+        <v>13910</v>
       </c>
       <c r="D510" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9975,10 +9966,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>13711</v>
+        <v>13911</v>
       </c>
       <c r="D511" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9992,10 +9983,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>13712</v>
+        <v>13912</v>
       </c>
       <c r="D512" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10009,10 +10000,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>13713</v>
+        <v>13913</v>
       </c>
       <c r="D513" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10026,10 +10017,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>13714</v>
+        <v>13914</v>
       </c>
       <c r="D514" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10043,10 +10034,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>13715</v>
+        <v>13915</v>
       </c>
       <c r="D515" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10060,10 +10051,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>13716</v>
+        <v>13916</v>
       </c>
       <c r="D516" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10077,10 +10068,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>13717</v>
+        <v>13917</v>
       </c>
       <c r="D517" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10094,10 +10085,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>13718</v>
+        <v>13918</v>
       </c>
       <c r="D518" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10111,10 +10102,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>13719</v>
+        <v>13919</v>
       </c>
       <c r="D519" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10128,10 +10119,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>13720</v>
+        <v>13920</v>
       </c>
       <c r="D520" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10145,10 +10136,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>13721</v>
+        <v>13921</v>
       </c>
       <c r="D521" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10162,10 +10153,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>13722</v>
+        <v>13922</v>
       </c>
       <c r="D522" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10179,10 +10170,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>13723</v>
+        <v>13923</v>
       </c>
       <c r="D523" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10196,10 +10187,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>13724</v>
+        <v>13924</v>
       </c>
       <c r="D524" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10213,10 +10204,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>13725</v>
+        <v>13925</v>
       </c>
       <c r="D525" s="3">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10233,10 +10224,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>13901</v>
+        <v>14101</v>
       </c>
       <c r="D527" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10248,17 +10239,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20475</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>13902</v>
+        <v>14102</v>
       </c>
       <c r="D528" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10270,15 +10261,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20476</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>13903</v>
+        <v>14103</v>
       </c>
       <c r="D529" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10290,15 +10281,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20477</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>13904</v>
+        <v>14104</v>
       </c>
       <c r="D530" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10310,15 +10301,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20478</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>13905</v>
+        <v>14105</v>
       </c>
       <c r="D531" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10332,10 +10323,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>13906</v>
+        <v>14106</v>
       </c>
       <c r="D532" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10349,10 +10340,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>13907</v>
+        <v>14107</v>
       </c>
       <c r="D533" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10366,10 +10357,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>13908</v>
+        <v>14108</v>
       </c>
       <c r="D534" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10383,10 +10374,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>13909</v>
+        <v>14109</v>
       </c>
       <c r="D535" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10400,10 +10391,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>13910</v>
+        <v>14110</v>
       </c>
       <c r="D536" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10417,10 +10408,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>13911</v>
+        <v>14111</v>
       </c>
       <c r="D537" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10434,10 +10425,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>13912</v>
+        <v>14112</v>
       </c>
       <c r="D538" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10451,10 +10442,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>13913</v>
+        <v>14113</v>
       </c>
       <c r="D539" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10468,10 +10459,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>13914</v>
+        <v>14114</v>
       </c>
       <c r="D540" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10485,10 +10476,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>13915</v>
+        <v>14115</v>
       </c>
       <c r="D541" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10502,10 +10493,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>13916</v>
+        <v>14116</v>
       </c>
       <c r="D542" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10519,10 +10510,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>13917</v>
+        <v>14117</v>
       </c>
       <c r="D543" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10536,10 +10527,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>13918</v>
+        <v>14118</v>
       </c>
       <c r="D544" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10553,10 +10544,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>13919</v>
+        <v>14119</v>
       </c>
       <c r="D545" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10570,10 +10561,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>13920</v>
+        <v>14120</v>
       </c>
       <c r="D546" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10587,10 +10578,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>13921</v>
+        <v>14121</v>
       </c>
       <c r="D547" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10604,10 +10595,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>13922</v>
+        <v>14122</v>
       </c>
       <c r="D548" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10621,10 +10612,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>13923</v>
+        <v>14123</v>
       </c>
       <c r="D549" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10638,10 +10629,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>13924</v>
+        <v>14124</v>
       </c>
       <c r="D550" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10655,10 +10646,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>13925</v>
+        <v>14125</v>
       </c>
       <c r="D551" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10675,10 +10666,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>14001</v>
+        <v>14301</v>
       </c>
       <c r="D553" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10690,17 +10681,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20505</v>
+        <v>20575</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>14002</v>
+        <v>14302</v>
       </c>
       <c r="D554" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10712,15 +10703,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20506</v>
+        <v>20576</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>14003</v>
+        <v>14303</v>
       </c>
       <c r="D555" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10732,15 +10723,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20507</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>14004</v>
+        <v>14304</v>
       </c>
       <c r="D556" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10752,15 +10743,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20508</v>
+        <v>20578</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>14005</v>
+        <v>14305</v>
       </c>
       <c r="D557" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10774,10 +10765,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>14006</v>
+        <v>14306</v>
       </c>
       <c r="D558" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10791,10 +10782,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>14007</v>
+        <v>14307</v>
       </c>
       <c r="D559" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10808,10 +10799,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>14008</v>
+        <v>14308</v>
       </c>
       <c r="D560" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10825,10 +10816,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>14009</v>
+        <v>14309</v>
       </c>
       <c r="D561" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10842,10 +10833,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>14010</v>
+        <v>14310</v>
       </c>
       <c r="D562" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10859,10 +10850,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>14011</v>
+        <v>14311</v>
       </c>
       <c r="D563" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10876,10 +10867,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>14012</v>
+        <v>14312</v>
       </c>
       <c r="D564" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10893,10 +10884,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>14013</v>
+        <v>14313</v>
       </c>
       <c r="D565" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10910,10 +10901,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>14014</v>
+        <v>14314</v>
       </c>
       <c r="D566" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10927,10 +10918,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>14015</v>
+        <v>14315</v>
       </c>
       <c r="D567" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10944,10 +10935,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>14016</v>
+        <v>14316</v>
       </c>
       <c r="D568" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10961,10 +10952,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>14017</v>
+        <v>14317</v>
       </c>
       <c r="D569" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10978,10 +10969,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>14018</v>
+        <v>14318</v>
       </c>
       <c r="D570" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10995,10 +10986,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>14019</v>
+        <v>14319</v>
       </c>
       <c r="D571" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11012,10 +11003,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>14020</v>
+        <v>14320</v>
       </c>
       <c r="D572" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11029,10 +11020,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>14021</v>
+        <v>14321</v>
       </c>
       <c r="D573" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11046,10 +11037,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>14022</v>
+        <v>14322</v>
       </c>
       <c r="D574" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11063,10 +11054,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>14023</v>
+        <v>14323</v>
       </c>
       <c r="D575" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11080,10 +11071,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>14024</v>
+        <v>14324</v>
       </c>
       <c r="D576" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11097,10 +11088,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>14025</v>
+        <v>14325</v>
       </c>
       <c r="D577" s="3">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11117,10 +11108,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>14101</v>
+        <v>14401</v>
       </c>
       <c r="D579" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11132,17 +11123,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20525</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>14102</v>
+        <v>14402</v>
       </c>
       <c r="D580" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11154,15 +11145,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20526</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>14103</v>
+        <v>14403</v>
       </c>
       <c r="D581" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11174,15 +11165,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20527</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>14104</v>
+        <v>14404</v>
       </c>
       <c r="D582" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11194,15 +11185,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20528</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>14105</v>
+        <v>14405</v>
       </c>
       <c r="D583" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11216,10 +11207,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>14106</v>
+        <v>14406</v>
       </c>
       <c r="D584" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11233,10 +11224,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>14107</v>
+        <v>14407</v>
       </c>
       <c r="D585" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11250,10 +11241,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>14108</v>
+        <v>14408</v>
       </c>
       <c r="D586" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11267,10 +11258,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>14109</v>
+        <v>14409</v>
       </c>
       <c r="D587" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11284,10 +11275,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>14110</v>
+        <v>14410</v>
       </c>
       <c r="D588" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11301,10 +11292,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>14111</v>
+        <v>14411</v>
       </c>
       <c r="D589" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11318,10 +11309,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>14112</v>
+        <v>14412</v>
       </c>
       <c r="D590" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11335,10 +11326,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>14113</v>
+        <v>14413</v>
       </c>
       <c r="D591" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11352,10 +11343,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>14114</v>
+        <v>14414</v>
       </c>
       <c r="D592" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11369,10 +11360,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>14115</v>
+        <v>14415</v>
       </c>
       <c r="D593" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11386,10 +11377,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>14116</v>
+        <v>14416</v>
       </c>
       <c r="D594" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11403,10 +11394,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>14117</v>
+        <v>14417</v>
       </c>
       <c r="D595" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11420,10 +11411,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>14118</v>
+        <v>14418</v>
       </c>
       <c r="D596" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11437,10 +11428,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>14119</v>
+        <v>14419</v>
       </c>
       <c r="D597" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11454,10 +11445,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>14120</v>
+        <v>14420</v>
       </c>
       <c r="D598" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11471,10 +11462,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>14121</v>
+        <v>14421</v>
       </c>
       <c r="D599" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11488,10 +11479,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>14122</v>
+        <v>14422</v>
       </c>
       <c r="D600" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11505,10 +11496,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>14123</v>
+        <v>14423</v>
       </c>
       <c r="D601" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11522,10 +11513,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>14124</v>
+        <v>14424</v>
       </c>
       <c r="D602" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11539,10 +11530,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>14125</v>
+        <v>14425</v>
       </c>
       <c r="D603" s="3">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11559,10 +11550,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>14201</v>
+        <v>14501</v>
       </c>
       <c r="D605" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11574,17 +11565,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20565</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>14202</v>
+        <v>14502</v>
       </c>
       <c r="D606" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11596,15 +11587,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20566</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>14203</v>
+        <v>14503</v>
       </c>
       <c r="D607" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11616,15 +11607,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20567</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>14204</v>
+        <v>14504</v>
       </c>
       <c r="D608" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11636,15 +11627,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20568</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>14205</v>
+        <v>14505</v>
       </c>
       <c r="D609" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11658,10 +11649,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>14206</v>
+        <v>14506</v>
       </c>
       <c r="D610" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11675,10 +11666,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>14207</v>
+        <v>14507</v>
       </c>
       <c r="D611" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11692,10 +11683,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>14208</v>
+        <v>14508</v>
       </c>
       <c r="D612" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11709,10 +11700,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>14209</v>
+        <v>14509</v>
       </c>
       <c r="D613" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11726,10 +11717,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>14210</v>
+        <v>14510</v>
       </c>
       <c r="D614" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11743,10 +11734,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>14211</v>
+        <v>14511</v>
       </c>
       <c r="D615" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11760,10 +11751,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>14212</v>
+        <v>14512</v>
       </c>
       <c r="D616" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11777,10 +11768,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>14213</v>
+        <v>14513</v>
       </c>
       <c r="D617" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11794,10 +11785,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>14214</v>
+        <v>14514</v>
       </c>
       <c r="D618" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11811,10 +11802,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>14215</v>
+        <v>14515</v>
       </c>
       <c r="D619" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11828,10 +11819,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>14216</v>
+        <v>14516</v>
       </c>
       <c r="D620" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11845,10 +11836,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>14217</v>
+        <v>14517</v>
       </c>
       <c r="D621" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11862,10 +11853,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>14218</v>
+        <v>14518</v>
       </c>
       <c r="D622" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11879,10 +11870,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>14219</v>
+        <v>14519</v>
       </c>
       <c r="D623" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11896,10 +11887,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>14220</v>
+        <v>14520</v>
       </c>
       <c r="D624" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11913,10 +11904,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>14221</v>
+        <v>14521</v>
       </c>
       <c r="D625" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11930,10 +11921,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>14222</v>
+        <v>14522</v>
       </c>
       <c r="D626" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11947,10 +11938,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>14223</v>
+        <v>14523</v>
       </c>
       <c r="D627" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11964,10 +11955,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>14224</v>
+        <v>14524</v>
       </c>
       <c r="D628" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11981,10 +11972,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>14225</v>
+        <v>14525</v>
       </c>
       <c r="D629" s="3">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -12001,10 +11992,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>14301</v>
+        <v>14601</v>
       </c>
       <c r="D631" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12016,17 +12007,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20575</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>14302</v>
+        <v>14602</v>
       </c>
       <c r="D632" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12038,15 +12029,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20576</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>14303</v>
+        <v>14603</v>
       </c>
       <c r="D633" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12058,15 +12049,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20577</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>14304</v>
+        <v>14604</v>
       </c>
       <c r="D634" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12078,15 +12069,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20578</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>14305</v>
+        <v>14605</v>
       </c>
       <c r="D635" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12100,10 +12091,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>14306</v>
+        <v>14606</v>
       </c>
       <c r="D636" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12117,10 +12108,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>14307</v>
+        <v>14607</v>
       </c>
       <c r="D637" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12134,10 +12125,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>14308</v>
+        <v>14608</v>
       </c>
       <c r="D638" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12151,10 +12142,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>14309</v>
+        <v>14609</v>
       </c>
       <c r="D639" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12168,10 +12159,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>14310</v>
+        <v>14610</v>
       </c>
       <c r="D640" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12185,10 +12176,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>14311</v>
+        <v>14611</v>
       </c>
       <c r="D641" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12202,10 +12193,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>14312</v>
+        <v>14612</v>
       </c>
       <c r="D642" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12219,10 +12210,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>14313</v>
+        <v>14613</v>
       </c>
       <c r="D643" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12236,10 +12227,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>14314</v>
+        <v>14614</v>
       </c>
       <c r="D644" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12253,10 +12244,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>14315</v>
+        <v>14615</v>
       </c>
       <c r="D645" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12270,10 +12261,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>14316</v>
+        <v>14616</v>
       </c>
       <c r="D646" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12287,10 +12278,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>14317</v>
+        <v>14617</v>
       </c>
       <c r="D647" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12304,10 +12295,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>14318</v>
+        <v>14618</v>
       </c>
       <c r="D648" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12321,10 +12312,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>14319</v>
+        <v>14619</v>
       </c>
       <c r="D649" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12338,10 +12329,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>14320</v>
+        <v>14620</v>
       </c>
       <c r="D650" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12355,10 +12346,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>14321</v>
+        <v>14621</v>
       </c>
       <c r="D651" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12372,10 +12363,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>14322</v>
+        <v>14622</v>
       </c>
       <c r="D652" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12389,10 +12380,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>14323</v>
+        <v>14623</v>
       </c>
       <c r="D653" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12406,10 +12397,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>14324</v>
+        <v>14624</v>
       </c>
       <c r="D654" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12423,10 +12414,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>14325</v>
+        <v>14625</v>
       </c>
       <c r="D655" s="3">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12443,10 +12434,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>14401</v>
+        <v>14701</v>
       </c>
       <c r="D657" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12458,17 +12449,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20415</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>14402</v>
+        <v>14702</v>
       </c>
       <c r="D658" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12480,15 +12471,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20416</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="659" spans="3:8">
       <c r="C659" s="6">
-        <v>14403</v>
+        <v>14703</v>
       </c>
       <c r="D659" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12500,15 +12491,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20417</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="660" spans="3:8">
       <c r="C660" s="6">
-        <v>14404</v>
+        <v>14704</v>
       </c>
       <c r="D660" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12520,15 +12511,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20418</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="661" spans="3:7">
       <c r="C661" s="6">
-        <v>14405</v>
+        <v>14705</v>
       </c>
       <c r="D661" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12542,10 +12533,10 @@
     </row>
     <row r="662" spans="3:7">
       <c r="C662" s="6">
-        <v>14406</v>
+        <v>14706</v>
       </c>
       <c r="D662" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12559,10 +12550,10 @@
     </row>
     <row r="663" spans="3:7">
       <c r="C663" s="6">
-        <v>14407</v>
+        <v>14707</v>
       </c>
       <c r="D663" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12576,10 +12567,10 @@
     </row>
     <row r="664" spans="3:7">
       <c r="C664" s="6">
-        <v>14408</v>
+        <v>14708</v>
       </c>
       <c r="D664" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12593,10 +12584,10 @@
     </row>
     <row r="665" spans="3:7">
       <c r="C665" s="6">
-        <v>14409</v>
+        <v>14709</v>
       </c>
       <c r="D665" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12610,10 +12601,10 @@
     </row>
     <row r="666" spans="3:7">
       <c r="C666" s="6">
-        <v>14410</v>
+        <v>14710</v>
       </c>
       <c r="D666" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12627,10 +12618,10 @@
     </row>
     <row r="667" spans="3:7">
       <c r="C667" s="6">
-        <v>14411</v>
+        <v>14711</v>
       </c>
       <c r="D667" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12644,10 +12635,10 @@
     </row>
     <row r="668" spans="3:7">
       <c r="C668" s="6">
-        <v>14412</v>
+        <v>14712</v>
       </c>
       <c r="D668" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12661,10 +12652,10 @@
     </row>
     <row r="669" spans="3:7">
       <c r="C669" s="6">
-        <v>14413</v>
+        <v>14713</v>
       </c>
       <c r="D669" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12678,10 +12669,10 @@
     </row>
     <row r="670" spans="3:7">
       <c r="C670" s="6">
-        <v>14414</v>
+        <v>14714</v>
       </c>
       <c r="D670" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12695,10 +12686,10 @@
     </row>
     <row r="671" spans="3:7">
       <c r="C671" s="6">
-        <v>14415</v>
+        <v>14715</v>
       </c>
       <c r="D671" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12712,10 +12703,10 @@
     </row>
     <row r="672" spans="3:7">
       <c r="C672" s="6">
-        <v>14416</v>
+        <v>14716</v>
       </c>
       <c r="D672" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12729,10 +12720,10 @@
     </row>
     <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>14417</v>
+        <v>14717</v>
       </c>
       <c r="D673" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12746,10 +12737,10 @@
     </row>
     <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>14418</v>
+        <v>14718</v>
       </c>
       <c r="D674" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12763,10 +12754,10 @@
     </row>
     <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>14419</v>
+        <v>14719</v>
       </c>
       <c r="D675" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12780,10 +12771,10 @@
     </row>
     <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>14420</v>
+        <v>14720</v>
       </c>
       <c r="D676" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12797,10 +12788,10 @@
     </row>
     <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>14421</v>
+        <v>14721</v>
       </c>
       <c r="D677" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12814,10 +12805,10 @@
     </row>
     <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>14422</v>
+        <v>14722</v>
       </c>
       <c r="D678" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12831,10 +12822,10 @@
     </row>
     <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>14423</v>
+        <v>14723</v>
       </c>
       <c r="D679" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12848,10 +12839,10 @@
     </row>
     <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>14424</v>
+        <v>14724</v>
       </c>
       <c r="D680" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12865,10 +12856,10 @@
     </row>
     <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>14425</v>
+        <v>14725</v>
       </c>
       <c r="D681" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12885,10 +12876,10 @@
         <v>68</v>
       </c>
       <c r="C683" s="6">
-        <v>14501</v>
+        <v>14801</v>
       </c>
       <c r="D683" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E683" s="5">
         <v>1</v>
@@ -12900,17 +12891,17 @@
         <v>15</v>
       </c>
       <c r="H683" s="3">
-        <v>20375</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="684" spans="1:8">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="6">
-        <v>14502</v>
+        <v>14802</v>
       </c>
       <c r="D684" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E684" s="5">
         <v>1</v>
@@ -12922,15 +12913,15 @@
         <v>16</v>
       </c>
       <c r="H684" s="3">
-        <v>20376</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="685" spans="3:8">
       <c r="C685" s="6">
-        <v>14503</v>
+        <v>14803</v>
       </c>
       <c r="D685" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E685" s="5">
         <v>1</v>
@@ -12942,15 +12933,15 @@
         <v>18</v>
       </c>
       <c r="H685" s="3">
-        <v>20377</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="686" spans="3:8">
       <c r="C686" s="6">
-        <v>14504</v>
+        <v>14804</v>
       </c>
       <c r="D686" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E686" s="5">
         <v>1</v>
@@ -12962,15 +12953,15 @@
         <v>19</v>
       </c>
       <c r="H686" s="3">
-        <v>20378</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="687" spans="3:7">
       <c r="C687" s="6">
-        <v>14505</v>
+        <v>14805</v>
       </c>
       <c r="D687" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E687" s="3">
         <v>1</v>
@@ -12984,10 +12975,10 @@
     </row>
     <row r="688" spans="3:7">
       <c r="C688" s="6">
-        <v>14506</v>
+        <v>14806</v>
       </c>
       <c r="D688" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E688" s="5">
         <v>1</v>
@@ -13001,10 +12992,10 @@
     </row>
     <row r="689" spans="3:7">
       <c r="C689" s="6">
-        <v>14507</v>
+        <v>14807</v>
       </c>
       <c r="D689" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E689" s="5">
         <v>1</v>
@@ -13018,10 +13009,10 @@
     </row>
     <row r="690" spans="3:7">
       <c r="C690" s="6">
-        <v>14508</v>
+        <v>14808</v>
       </c>
       <c r="D690" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E690" s="5">
         <v>1</v>
@@ -13035,10 +13026,10 @@
     </row>
     <row r="691" spans="3:7">
       <c r="C691" s="6">
-        <v>14509</v>
+        <v>14809</v>
       </c>
       <c r="D691" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E691" s="3">
         <v>1</v>
@@ -13052,10 +13043,10 @@
     </row>
     <row r="692" spans="3:7">
       <c r="C692" s="6">
-        <v>14510</v>
+        <v>14810</v>
       </c>
       <c r="D692" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E692" s="5">
         <v>1</v>
@@ -13069,10 +13060,10 @@
     </row>
     <row r="693" spans="3:7">
       <c r="C693" s="6">
-        <v>14511</v>
+        <v>14811</v>
       </c>
       <c r="D693" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E693" s="5">
         <v>1</v>
@@ -13086,10 +13077,10 @@
     </row>
     <row r="694" spans="3:7">
       <c r="C694" s="6">
-        <v>14512</v>
+        <v>14812</v>
       </c>
       <c r="D694" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E694" s="5">
         <v>1</v>
@@ -13103,10 +13094,10 @@
     </row>
     <row r="695" spans="3:7">
       <c r="C695" s="6">
-        <v>14513</v>
+        <v>14813</v>
       </c>
       <c r="D695" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E695" s="3">
         <v>1</v>
@@ -13120,10 +13111,10 @@
     </row>
     <row r="696" spans="3:7">
       <c r="C696" s="6">
-        <v>14514</v>
+        <v>14814</v>
       </c>
       <c r="D696" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E696" s="5">
         <v>1</v>
@@ -13137,10 +13128,10 @@
     </row>
     <row r="697" spans="3:7">
       <c r="C697" s="6">
-        <v>14515</v>
+        <v>14815</v>
       </c>
       <c r="D697" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E697" s="5">
         <v>1</v>
@@ -13154,10 +13145,10 @@
     </row>
     <row r="698" spans="3:7">
       <c r="C698" s="6">
-        <v>14516</v>
+        <v>14816</v>
       </c>
       <c r="D698" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E698" s="5">
         <v>1</v>
@@ -13171,10 +13162,10 @@
     </row>
     <row r="699" spans="3:7">
       <c r="C699" s="6">
-        <v>14517</v>
+        <v>14817</v>
       </c>
       <c r="D699" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E699" s="3">
         <v>1</v>
@@ -13188,10 +13179,10 @@
     </row>
     <row r="700" spans="3:7">
       <c r="C700" s="6">
-        <v>14518</v>
+        <v>14818</v>
       </c>
       <c r="D700" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E700" s="5">
         <v>1</v>
@@ -13205,10 +13196,10 @@
     </row>
     <row r="701" spans="3:7">
       <c r="C701" s="6">
-        <v>14519</v>
+        <v>14819</v>
       </c>
       <c r="D701" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E701" s="5">
         <v>1</v>
@@ -13222,10 +13213,10 @@
     </row>
     <row r="702" spans="3:7">
       <c r="C702" s="6">
-        <v>14520</v>
+        <v>14820</v>
       </c>
       <c r="D702" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E702" s="5">
         <v>1</v>
@@ -13239,10 +13230,10 @@
     </row>
     <row r="703" spans="3:7">
       <c r="C703" s="6">
-        <v>14521</v>
+        <v>14821</v>
       </c>
       <c r="D703" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E703" s="3">
         <v>1</v>
@@ -13256,10 +13247,10 @@
     </row>
     <row r="704" spans="3:7">
       <c r="C704" s="6">
-        <v>14522</v>
+        <v>14822</v>
       </c>
       <c r="D704" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E704" s="5">
         <v>1</v>
@@ -13273,10 +13264,10 @@
     </row>
     <row r="705" spans="3:7">
       <c r="C705" s="6">
-        <v>14523</v>
+        <v>14823</v>
       </c>
       <c r="D705" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E705" s="5">
         <v>1</v>
@@ -13290,10 +13281,10 @@
     </row>
     <row r="706" spans="3:7">
       <c r="C706" s="6">
-        <v>14524</v>
+        <v>14824</v>
       </c>
       <c r="D706" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E706" s="5">
         <v>1</v>
@@ -13307,10 +13298,10 @@
     </row>
     <row r="707" spans="3:7">
       <c r="C707" s="6">
-        <v>14525</v>
+        <v>14825</v>
       </c>
       <c r="D707" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E707" s="3">
         <v>1</v>
@@ -13319,1332 +13310,6 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>14601</v>
-      </c>
-      <c r="D709" s="3">
-        <v>146</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20455</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>14602</v>
-      </c>
-      <c r="D710" s="3">
-        <v>146</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20456</v>
-      </c>
-    </row>
-    <row r="711" spans="3:8">
-      <c r="C711" s="6">
-        <v>14603</v>
-      </c>
-      <c r="D711" s="3">
-        <v>146</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20457</v>
-      </c>
-    </row>
-    <row r="712" spans="3:8">
-      <c r="C712" s="6">
-        <v>14604</v>
-      </c>
-      <c r="D712" s="3">
-        <v>146</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20458</v>
-      </c>
-    </row>
-    <row r="713" spans="3:7">
-      <c r="C713" s="6">
-        <v>14605</v>
-      </c>
-      <c r="D713" s="3">
-        <v>146</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="3:7">
-      <c r="C714" s="6">
-        <v>14606</v>
-      </c>
-      <c r="D714" s="3">
-        <v>146</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="3:7">
-      <c r="C715" s="6">
-        <v>14607</v>
-      </c>
-      <c r="D715" s="3">
-        <v>146</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="3:7">
-      <c r="C716" s="6">
-        <v>14608</v>
-      </c>
-      <c r="D716" s="3">
-        <v>146</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="3:7">
-      <c r="C717" s="6">
-        <v>14609</v>
-      </c>
-      <c r="D717" s="3">
-        <v>146</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="3:7">
-      <c r="C718" s="6">
-        <v>14610</v>
-      </c>
-      <c r="D718" s="3">
-        <v>146</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="3:7">
-      <c r="C719" s="6">
-        <v>14611</v>
-      </c>
-      <c r="D719" s="3">
-        <v>146</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="3:7">
-      <c r="C720" s="6">
-        <v>14612</v>
-      </c>
-      <c r="D720" s="3">
-        <v>146</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="3:7">
-      <c r="C721" s="6">
-        <v>14613</v>
-      </c>
-      <c r="D721" s="3">
-        <v>146</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="3:7">
-      <c r="C722" s="6">
-        <v>14614</v>
-      </c>
-      <c r="D722" s="3">
-        <v>146</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="3:7">
-      <c r="C723" s="6">
-        <v>14615</v>
-      </c>
-      <c r="D723" s="3">
-        <v>146</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="3:7">
-      <c r="C724" s="6">
-        <v>14616</v>
-      </c>
-      <c r="D724" s="3">
-        <v>146</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="3:7">
-      <c r="C725" s="6">
-        <v>14617</v>
-      </c>
-      <c r="D725" s="3">
-        <v>146</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="3:7">
-      <c r="C726" s="6">
-        <v>14618</v>
-      </c>
-      <c r="D726" s="3">
-        <v>146</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="3:7">
-      <c r="C727" s="6">
-        <v>14619</v>
-      </c>
-      <c r="D727" s="3">
-        <v>146</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="3:7">
-      <c r="C728" s="6">
-        <v>14620</v>
-      </c>
-      <c r="D728" s="3">
-        <v>146</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="3:7">
-      <c r="C729" s="6">
-        <v>14621</v>
-      </c>
-      <c r="D729" s="3">
-        <v>146</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="3:7">
-      <c r="C730" s="6">
-        <v>14622</v>
-      </c>
-      <c r="D730" s="3">
-        <v>146</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="3:7">
-      <c r="C731" s="6">
-        <v>14623</v>
-      </c>
-      <c r="D731" s="3">
-        <v>146</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="3:7">
-      <c r="C732" s="6">
-        <v>14624</v>
-      </c>
-      <c r="D732" s="3">
-        <v>146</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="3:7">
-      <c r="C733" s="6">
-        <v>14625</v>
-      </c>
-      <c r="D733" s="3">
-        <v>146</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>14701</v>
-      </c>
-      <c r="D735" s="3">
-        <v>147</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20495</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>14702</v>
-      </c>
-      <c r="D736" s="3">
-        <v>147</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20496</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>14703</v>
-      </c>
-      <c r="D737" s="3">
-        <v>147</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20497</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>14704</v>
-      </c>
-      <c r="D738" s="3">
-        <v>147</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20498</v>
-      </c>
-    </row>
-    <row r="739" spans="3:7">
-      <c r="C739" s="6">
-        <v>14705</v>
-      </c>
-      <c r="D739" s="3">
-        <v>147</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:7">
-      <c r="C740" s="6">
-        <v>14706</v>
-      </c>
-      <c r="D740" s="3">
-        <v>147</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:7">
-      <c r="C741" s="6">
-        <v>14707</v>
-      </c>
-      <c r="D741" s="3">
-        <v>147</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:7">
-      <c r="C742" s="6">
-        <v>14708</v>
-      </c>
-      <c r="D742" s="3">
-        <v>147</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:7">
-      <c r="C743" s="6">
-        <v>14709</v>
-      </c>
-      <c r="D743" s="3">
-        <v>147</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:7">
-      <c r="C744" s="6">
-        <v>14710</v>
-      </c>
-      <c r="D744" s="3">
-        <v>147</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:7">
-      <c r="C745" s="6">
-        <v>14711</v>
-      </c>
-      <c r="D745" s="3">
-        <v>147</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:7">
-      <c r="C746" s="6">
-        <v>14712</v>
-      </c>
-      <c r="D746" s="3">
-        <v>147</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:7">
-      <c r="C747" s="6">
-        <v>14713</v>
-      </c>
-      <c r="D747" s="3">
-        <v>147</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:7">
-      <c r="C748" s="6">
-        <v>14714</v>
-      </c>
-      <c r="D748" s="3">
-        <v>147</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:7">
-      <c r="C749" s="6">
-        <v>14715</v>
-      </c>
-      <c r="D749" s="3">
-        <v>147</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:7">
-      <c r="C750" s="6">
-        <v>14716</v>
-      </c>
-      <c r="D750" s="3">
-        <v>147</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:7">
-      <c r="C751" s="6">
-        <v>14717</v>
-      </c>
-      <c r="D751" s="3">
-        <v>147</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:7">
-      <c r="C752" s="6">
-        <v>14718</v>
-      </c>
-      <c r="D752" s="3">
-        <v>147</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="3:7">
-      <c r="C753" s="6">
-        <v>14719</v>
-      </c>
-      <c r="D753" s="3">
-        <v>147</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="3:7">
-      <c r="C754" s="6">
-        <v>14720</v>
-      </c>
-      <c r="D754" s="3">
-        <v>147</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="3:7">
-      <c r="C755" s="6">
-        <v>14721</v>
-      </c>
-      <c r="D755" s="3">
-        <v>147</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="3:7">
-      <c r="C756" s="6">
-        <v>14722</v>
-      </c>
-      <c r="D756" s="3">
-        <v>147</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="3:7">
-      <c r="C757" s="6">
-        <v>14723</v>
-      </c>
-      <c r="D757" s="3">
-        <v>147</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="3:7">
-      <c r="C758" s="6">
-        <v>14724</v>
-      </c>
-      <c r="D758" s="3">
-        <v>147</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="3:7">
-      <c r="C759" s="6">
-        <v>14725</v>
-      </c>
-      <c r="D759" s="3">
-        <v>147</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="761" spans="1:8">
-      <c r="A761" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C761" s="6">
-        <v>14801</v>
-      </c>
-      <c r="D761" s="3">
-        <v>148</v>
-      </c>
-      <c r="E761" s="5">
-        <v>1</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H761" s="3">
-        <v>20585</v>
-      </c>
-    </row>
-    <row r="762" spans="1:8">
-      <c r="A762" s="1"/>
-      <c r="B762" s="1"/>
-      <c r="C762" s="6">
-        <v>14802</v>
-      </c>
-      <c r="D762" s="3">
-        <v>148</v>
-      </c>
-      <c r="E762" s="5">
-        <v>1</v>
-      </c>
-      <c r="F762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H762" s="3">
-        <v>20586</v>
-      </c>
-    </row>
-    <row r="763" spans="3:8">
-      <c r="C763" s="6">
-        <v>14803</v>
-      </c>
-      <c r="D763" s="3">
-        <v>148</v>
-      </c>
-      <c r="E763" s="5">
-        <v>1</v>
-      </c>
-      <c r="F763" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G763" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H763" s="3">
-        <v>20587</v>
-      </c>
-    </row>
-    <row r="764" spans="3:8">
-      <c r="C764" s="6">
-        <v>14804</v>
-      </c>
-      <c r="D764" s="3">
-        <v>148</v>
-      </c>
-      <c r="E764" s="5">
-        <v>1</v>
-      </c>
-      <c r="F764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H764" s="3">
-        <v>20588</v>
-      </c>
-    </row>
-    <row r="765" spans="3:7">
-      <c r="C765" s="6">
-        <v>14805</v>
-      </c>
-      <c r="D765" s="3">
-        <v>148</v>
-      </c>
-      <c r="E765" s="3">
-        <v>1</v>
-      </c>
-      <c r="F765" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G765" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="766" spans="3:7">
-      <c r="C766" s="6">
-        <v>14806</v>
-      </c>
-      <c r="D766" s="3">
-        <v>148</v>
-      </c>
-      <c r="E766" s="5">
-        <v>1</v>
-      </c>
-      <c r="F766" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G766" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="767" spans="3:7">
-      <c r="C767" s="6">
-        <v>14807</v>
-      </c>
-      <c r="D767" s="3">
-        <v>148</v>
-      </c>
-      <c r="E767" s="5">
-        <v>1</v>
-      </c>
-      <c r="F767" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G767" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="768" spans="3:7">
-      <c r="C768" s="6">
-        <v>14808</v>
-      </c>
-      <c r="D768" s="3">
-        <v>148</v>
-      </c>
-      <c r="E768" s="5">
-        <v>1</v>
-      </c>
-      <c r="F768" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G768" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="769" spans="3:7">
-      <c r="C769" s="6">
-        <v>14809</v>
-      </c>
-      <c r="D769" s="3">
-        <v>148</v>
-      </c>
-      <c r="E769" s="3">
-        <v>1</v>
-      </c>
-      <c r="F769" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G769" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="770" spans="3:7">
-      <c r="C770" s="6">
-        <v>14810</v>
-      </c>
-      <c r="D770" s="3">
-        <v>148</v>
-      </c>
-      <c r="E770" s="5">
-        <v>1</v>
-      </c>
-      <c r="F770" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G770" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="771" spans="3:7">
-      <c r="C771" s="6">
-        <v>14811</v>
-      </c>
-      <c r="D771" s="3">
-        <v>148</v>
-      </c>
-      <c r="E771" s="5">
-        <v>1</v>
-      </c>
-      <c r="F771" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G771" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="772" spans="3:7">
-      <c r="C772" s="6">
-        <v>14812</v>
-      </c>
-      <c r="D772" s="3">
-        <v>148</v>
-      </c>
-      <c r="E772" s="5">
-        <v>1</v>
-      </c>
-      <c r="F772" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G772" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="773" spans="3:7">
-      <c r="C773" s="6">
-        <v>14813</v>
-      </c>
-      <c r="D773" s="3">
-        <v>148</v>
-      </c>
-      <c r="E773" s="3">
-        <v>1</v>
-      </c>
-      <c r="F773" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G773" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="774" spans="3:7">
-      <c r="C774" s="6">
-        <v>14814</v>
-      </c>
-      <c r="D774" s="3">
-        <v>148</v>
-      </c>
-      <c r="E774" s="5">
-        <v>1</v>
-      </c>
-      <c r="F774" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G774" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="775" spans="3:7">
-      <c r="C775" s="6">
-        <v>14815</v>
-      </c>
-      <c r="D775" s="3">
-        <v>148</v>
-      </c>
-      <c r="E775" s="5">
-        <v>1</v>
-      </c>
-      <c r="F775" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G775" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="776" spans="3:7">
-      <c r="C776" s="6">
-        <v>14816</v>
-      </c>
-      <c r="D776" s="3">
-        <v>148</v>
-      </c>
-      <c r="E776" s="5">
-        <v>1</v>
-      </c>
-      <c r="F776" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G776" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="777" spans="3:7">
-      <c r="C777" s="6">
-        <v>14817</v>
-      </c>
-      <c r="D777" s="3">
-        <v>148</v>
-      </c>
-      <c r="E777" s="3">
-        <v>1</v>
-      </c>
-      <c r="F777" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G777" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="778" spans="3:7">
-      <c r="C778" s="6">
-        <v>14818</v>
-      </c>
-      <c r="D778" s="3">
-        <v>148</v>
-      </c>
-      <c r="E778" s="5">
-        <v>1</v>
-      </c>
-      <c r="F778" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G778" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="779" spans="3:7">
-      <c r="C779" s="6">
-        <v>14819</v>
-      </c>
-      <c r="D779" s="3">
-        <v>148</v>
-      </c>
-      <c r="E779" s="5">
-        <v>1</v>
-      </c>
-      <c r="F779" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G779" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="780" spans="3:7">
-      <c r="C780" s="6">
-        <v>14820</v>
-      </c>
-      <c r="D780" s="3">
-        <v>148</v>
-      </c>
-      <c r="E780" s="5">
-        <v>1</v>
-      </c>
-      <c r="F780" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G780" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="781" spans="3:7">
-      <c r="C781" s="6">
-        <v>14821</v>
-      </c>
-      <c r="D781" s="3">
-        <v>148</v>
-      </c>
-      <c r="E781" s="3">
-        <v>1</v>
-      </c>
-      <c r="F781" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G781" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="782" spans="3:7">
-      <c r="C782" s="6">
-        <v>14822</v>
-      </c>
-      <c r="D782" s="3">
-        <v>148</v>
-      </c>
-      <c r="E782" s="5">
-        <v>1</v>
-      </c>
-      <c r="F782" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G782" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="783" spans="3:7">
-      <c r="C783" s="6">
-        <v>14823</v>
-      </c>
-      <c r="D783" s="3">
-        <v>148</v>
-      </c>
-      <c r="E783" s="5">
-        <v>1</v>
-      </c>
-      <c r="F783" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G783" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="784" spans="3:7">
-      <c r="C784" s="6">
-        <v>14824</v>
-      </c>
-      <c r="D784" s="3">
-        <v>148</v>
-      </c>
-      <c r="E784" s="5">
-        <v>1</v>
-      </c>
-      <c r="F784" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G784" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="785" spans="3:7">
-      <c r="C785" s="6">
-        <v>14825</v>
-      </c>
-      <c r="D785" s="3">
-        <v>148</v>
-      </c>
-      <c r="E785" s="3">
-        <v>1</v>
-      </c>
-      <c r="F785" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14765,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14783,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14801,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14819,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14839,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -14937,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋148威震天下</t>
+  </si>
+  <si>
+    <t>#先锋149春暖花开</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>14901</v>
+      </c>
+      <c r="D709" s="3">
+        <v>149</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20445</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>14902</v>
+      </c>
+      <c r="D710" s="3">
+        <v>149</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="711" spans="3:8">
+      <c r="C711" s="6">
+        <v>14903</v>
+      </c>
+      <c r="D711" s="3">
+        <v>149</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20447</v>
+      </c>
+    </row>
+    <row r="712" spans="3:8">
+      <c r="C712" s="6">
+        <v>14904</v>
+      </c>
+      <c r="D712" s="3">
+        <v>149</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20448</v>
+      </c>
+    </row>
+    <row r="713" spans="3:7">
+      <c r="C713" s="6">
+        <v>14905</v>
+      </c>
+      <c r="D713" s="3">
+        <v>149</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="3:7">
+      <c r="C714" s="6">
+        <v>14906</v>
+      </c>
+      <c r="D714" s="3">
+        <v>149</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="3:7">
+      <c r="C715" s="6">
+        <v>14907</v>
+      </c>
+      <c r="D715" s="3">
+        <v>149</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="3:7">
+      <c r="C716" s="6">
+        <v>14908</v>
+      </c>
+      <c r="D716" s="3">
+        <v>149</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="3:7">
+      <c r="C717" s="6">
+        <v>14909</v>
+      </c>
+      <c r="D717" s="3">
+        <v>149</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="3:7">
+      <c r="C718" s="6">
+        <v>14910</v>
+      </c>
+      <c r="D718" s="3">
+        <v>149</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="3:7">
+      <c r="C719" s="6">
+        <v>14911</v>
+      </c>
+      <c r="D719" s="3">
+        <v>149</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="3:7">
+      <c r="C720" s="6">
+        <v>14912</v>
+      </c>
+      <c r="D720" s="3">
+        <v>149</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>14913</v>
+      </c>
+      <c r="D721" s="3">
+        <v>149</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>14914</v>
+      </c>
+      <c r="D722" s="3">
+        <v>149</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>14915</v>
+      </c>
+      <c r="D723" s="3">
+        <v>149</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>14916</v>
+      </c>
+      <c r="D724" s="3">
+        <v>149</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>14917</v>
+      </c>
+      <c r="D725" s="3">
+        <v>149</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>14918</v>
+      </c>
+      <c r="D726" s="3">
+        <v>149</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>14919</v>
+      </c>
+      <c r="D727" s="3">
+        <v>149</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>14920</v>
+      </c>
+      <c r="D728" s="3">
+        <v>149</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>14921</v>
+      </c>
+      <c r="D729" s="3">
+        <v>149</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>14922</v>
+      </c>
+      <c r="D730" s="3">
+        <v>149</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>14923</v>
+      </c>
+      <c r="D731" s="3">
+        <v>149</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>14924</v>
+      </c>
+      <c r="D732" s="3">
+        <v>149</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>14925</v>
+      </c>
+      <c r="D733" s="3">
+        <v>149</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -202,9 +202,6 @@
     <t>#先锋121区太平盛世</t>
   </si>
   <si>
-    <t>#先锋125断桥残雪</t>
-  </si>
-  <si>
     <t>#先锋128主播专服</t>
   </si>
   <si>
@@ -223,13 +220,7 @@
     <t>#先锋143湖光月色</t>
   </si>
   <si>
-    <t>#先锋144无尽王国</t>
-  </si>
-  <si>
     <t>#先锋145一统山河</t>
-  </si>
-  <si>
-    <t>#先锋146星辰坠落</t>
   </si>
   <si>
     <t>#先锋147紫禁之巅</t>
@@ -239,6 +230,9 @@
   </si>
   <si>
     <t>#先锋149春暖花开</t>
+  </si>
+  <si>
+    <t>#先锋150破晓之战</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -8017,10 +8011,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>12501</v>
+        <v>12801</v>
       </c>
       <c r="D397" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8032,17 +8026,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20605</v>
+        <v>20425</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>12502</v>
+        <v>12802</v>
       </c>
       <c r="D398" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8054,15 +8048,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20606</v>
+        <v>20426</v>
       </c>
     </row>
     <row r="399" spans="3:8">
       <c r="C399" s="6">
-        <v>12503</v>
+        <v>12803</v>
       </c>
       <c r="D399" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8074,15 +8068,15 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20607</v>
+        <v>20427</v>
       </c>
     </row>
     <row r="400" spans="3:8">
       <c r="C400" s="6">
-        <v>12504</v>
+        <v>12804</v>
       </c>
       <c r="D400" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E400" s="3">
         <v>1</v>
@@ -8094,15 +8088,15 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20608</v>
+        <v>20428</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>12505</v>
+        <v>12805</v>
       </c>
       <c r="D401" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E401" s="5">
         <v>1</v>
@@ -8116,10 +8110,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>12506</v>
+        <v>12806</v>
       </c>
       <c r="D402" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8133,10 +8127,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>12507</v>
+        <v>12807</v>
       </c>
       <c r="D403" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8150,10 +8144,10 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>12508</v>
+        <v>12808</v>
       </c>
       <c r="D404" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E404" s="3">
         <v>1</v>
@@ -8167,10 +8161,10 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>12509</v>
+        <v>12809</v>
       </c>
       <c r="D405" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E405" s="5">
         <v>1</v>
@@ -8184,10 +8178,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>12510</v>
+        <v>12810</v>
       </c>
       <c r="D406" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8201,10 +8195,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>12511</v>
+        <v>12811</v>
       </c>
       <c r="D407" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8218,10 +8212,10 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>12512</v>
+        <v>12812</v>
       </c>
       <c r="D408" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E408" s="3">
         <v>1</v>
@@ -8235,10 +8229,10 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>12513</v>
+        <v>12813</v>
       </c>
       <c r="D409" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E409" s="5">
         <v>1</v>
@@ -8252,10 +8246,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>12514</v>
+        <v>12814</v>
       </c>
       <c r="D410" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8269,10 +8263,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>12515</v>
+        <v>12815</v>
       </c>
       <c r="D411" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8286,10 +8280,10 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>12516</v>
+        <v>12816</v>
       </c>
       <c r="D412" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E412" s="3">
         <v>1</v>
@@ -8303,10 +8297,10 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>12517</v>
+        <v>12817</v>
       </c>
       <c r="D413" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E413" s="5">
         <v>1</v>
@@ -8320,10 +8314,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>12518</v>
+        <v>12818</v>
       </c>
       <c r="D414" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8337,10 +8331,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>12519</v>
+        <v>12819</v>
       </c>
       <c r="D415" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8354,10 +8348,10 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>12520</v>
+        <v>12820</v>
       </c>
       <c r="D416" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E416" s="3">
         <v>1</v>
@@ -8371,10 +8365,10 @@
     </row>
     <row r="417" spans="3:7">
       <c r="C417" s="6">
-        <v>12521</v>
+        <v>12821</v>
       </c>
       <c r="D417" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E417" s="5">
         <v>1</v>
@@ -8388,10 +8382,10 @@
     </row>
     <row r="418" spans="3:7">
       <c r="C418" s="6">
-        <v>12522</v>
+        <v>12822</v>
       </c>
       <c r="D418" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8405,10 +8399,10 @@
     </row>
     <row r="419" spans="3:7">
       <c r="C419" s="6">
-        <v>12523</v>
+        <v>12823</v>
       </c>
       <c r="D419" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8422,10 +8416,10 @@
     </row>
     <row r="420" spans="3:7">
       <c r="C420" s="6">
-        <v>12524</v>
+        <v>12824</v>
       </c>
       <c r="D420" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E420" s="3">
         <v>1</v>
@@ -8439,10 +8433,10 @@
     </row>
     <row r="421" spans="3:7">
       <c r="C421" s="6">
-        <v>12525</v>
+        <v>12825</v>
       </c>
       <c r="D421" s="3">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E421" s="5">
         <v>1</v>
@@ -8459,10 +8453,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>12801</v>
+        <v>13101</v>
       </c>
       <c r="D423" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8474,17 +8468,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20425</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>12802</v>
+        <v>13102</v>
       </c>
       <c r="D424" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8496,15 +8490,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20426</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>12803</v>
+        <v>13103</v>
       </c>
       <c r="D425" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8516,17 +8510,17 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20427</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>12804</v>
+        <v>13104</v>
       </c>
       <c r="D426" s="3">
-        <v>128</v>
-      </c>
-      <c r="E426" s="3">
+        <v>131</v>
+      </c>
+      <c r="E426" s="5">
         <v>1</v>
       </c>
       <c r="F426" s="3" t="s">
@@ -8536,17 +8530,17 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20428</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>12805</v>
+        <v>13105</v>
       </c>
       <c r="D427" s="3">
-        <v>128</v>
-      </c>
-      <c r="E427" s="5">
+        <v>131</v>
+      </c>
+      <c r="E427" s="3">
         <v>1</v>
       </c>
       <c r="F427" s="3" t="s">
@@ -8558,10 +8552,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>12806</v>
+        <v>13106</v>
       </c>
       <c r="D428" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8575,10 +8569,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>12807</v>
+        <v>13107</v>
       </c>
       <c r="D429" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8592,12 +8586,12 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>12808</v>
+        <v>13108</v>
       </c>
       <c r="D430" s="3">
-        <v>128</v>
-      </c>
-      <c r="E430" s="3">
+        <v>131</v>
+      </c>
+      <c r="E430" s="5">
         <v>1</v>
       </c>
       <c r="F430" s="3" t="s">
@@ -8609,12 +8603,12 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>12809</v>
+        <v>13109</v>
       </c>
       <c r="D431" s="3">
-        <v>128</v>
-      </c>
-      <c r="E431" s="5">
+        <v>131</v>
+      </c>
+      <c r="E431" s="3">
         <v>1</v>
       </c>
       <c r="F431" s="3" t="s">
@@ -8626,10 +8620,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>12810</v>
+        <v>13110</v>
       </c>
       <c r="D432" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8643,10 +8637,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>12811</v>
+        <v>13111</v>
       </c>
       <c r="D433" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8660,12 +8654,12 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>12812</v>
+        <v>13112</v>
       </c>
       <c r="D434" s="3">
-        <v>128</v>
-      </c>
-      <c r="E434" s="3">
+        <v>131</v>
+      </c>
+      <c r="E434" s="5">
         <v>1</v>
       </c>
       <c r="F434" s="3" t="s">
@@ -8677,12 +8671,12 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>12813</v>
+        <v>13113</v>
       </c>
       <c r="D435" s="3">
-        <v>128</v>
-      </c>
-      <c r="E435" s="5">
+        <v>131</v>
+      </c>
+      <c r="E435" s="3">
         <v>1</v>
       </c>
       <c r="F435" s="3" t="s">
@@ -8694,10 +8688,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>12814</v>
+        <v>13114</v>
       </c>
       <c r="D436" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8711,10 +8705,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>12815</v>
+        <v>13115</v>
       </c>
       <c r="D437" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8728,12 +8722,12 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>12816</v>
+        <v>13116</v>
       </c>
       <c r="D438" s="3">
-        <v>128</v>
-      </c>
-      <c r="E438" s="3">
+        <v>131</v>
+      </c>
+      <c r="E438" s="5">
         <v>1</v>
       </c>
       <c r="F438" s="3" t="s">
@@ -8745,12 +8739,12 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>12817</v>
+        <v>13117</v>
       </c>
       <c r="D439" s="3">
-        <v>128</v>
-      </c>
-      <c r="E439" s="5">
+        <v>131</v>
+      </c>
+      <c r="E439" s="3">
         <v>1</v>
       </c>
       <c r="F439" s="3" t="s">
@@ -8762,10 +8756,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>12818</v>
+        <v>13118</v>
       </c>
       <c r="D440" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8779,10 +8773,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>12819</v>
+        <v>13119</v>
       </c>
       <c r="D441" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8796,12 +8790,12 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>12820</v>
+        <v>13120</v>
       </c>
       <c r="D442" s="3">
-        <v>128</v>
-      </c>
-      <c r="E442" s="3">
+        <v>131</v>
+      </c>
+      <c r="E442" s="5">
         <v>1</v>
       </c>
       <c r="F442" s="3" t="s">
@@ -8813,12 +8807,12 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>12821</v>
+        <v>13121</v>
       </c>
       <c r="D443" s="3">
-        <v>128</v>
-      </c>
-      <c r="E443" s="5">
+        <v>131</v>
+      </c>
+      <c r="E443" s="3">
         <v>1</v>
       </c>
       <c r="F443" s="3" t="s">
@@ -8830,10 +8824,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>12822</v>
+        <v>13122</v>
       </c>
       <c r="D444" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8847,10 +8841,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>12823</v>
+        <v>13123</v>
       </c>
       <c r="D445" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8864,12 +8858,12 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>12824</v>
+        <v>13124</v>
       </c>
       <c r="D446" s="3">
-        <v>128</v>
-      </c>
-      <c r="E446" s="3">
+        <v>131</v>
+      </c>
+      <c r="E446" s="5">
         <v>1</v>
       </c>
       <c r="F446" s="3" t="s">
@@ -8881,12 +8875,12 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>12825</v>
+        <v>13125</v>
       </c>
       <c r="D447" s="3">
-        <v>128</v>
-      </c>
-      <c r="E447" s="5">
+        <v>131</v>
+      </c>
+      <c r="E447" s="3">
         <v>1</v>
       </c>
       <c r="F447" s="3" t="s">
@@ -8901,10 +8895,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>13101</v>
+        <v>13501</v>
       </c>
       <c r="D449" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8916,17 +8910,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20515</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>13102</v>
+        <v>13502</v>
       </c>
       <c r="D450" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8938,15 +8932,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20516</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>13103</v>
+        <v>13503</v>
       </c>
       <c r="D451" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8958,15 +8952,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20517</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>13104</v>
+        <v>13504</v>
       </c>
       <c r="D452" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8978,15 +8972,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20518</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>13105</v>
+        <v>13505</v>
       </c>
       <c r="D453" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9000,10 +8994,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>13106</v>
+        <v>13506</v>
       </c>
       <c r="D454" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9017,10 +9011,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>13107</v>
+        <v>13507</v>
       </c>
       <c r="D455" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9034,10 +9028,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>13108</v>
+        <v>13508</v>
       </c>
       <c r="D456" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9051,10 +9045,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>13109</v>
+        <v>13509</v>
       </c>
       <c r="D457" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9068,10 +9062,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>13110</v>
+        <v>13510</v>
       </c>
       <c r="D458" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9085,10 +9079,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>13111</v>
+        <v>13511</v>
       </c>
       <c r="D459" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9102,10 +9096,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>13112</v>
+        <v>13512</v>
       </c>
       <c r="D460" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9119,10 +9113,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>13113</v>
+        <v>13513</v>
       </c>
       <c r="D461" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9136,10 +9130,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>13114</v>
+        <v>13514</v>
       </c>
       <c r="D462" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9153,10 +9147,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>13115</v>
+        <v>13515</v>
       </c>
       <c r="D463" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9170,10 +9164,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>13116</v>
+        <v>13516</v>
       </c>
       <c r="D464" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9187,10 +9181,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>13117</v>
+        <v>13517</v>
       </c>
       <c r="D465" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9204,10 +9198,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>13118</v>
+        <v>13518</v>
       </c>
       <c r="D466" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9221,10 +9215,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>13119</v>
+        <v>13519</v>
       </c>
       <c r="D467" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9238,10 +9232,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>13120</v>
+        <v>13520</v>
       </c>
       <c r="D468" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9255,10 +9249,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>13121</v>
+        <v>13521</v>
       </c>
       <c r="D469" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9272,10 +9266,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>13122</v>
+        <v>13522</v>
       </c>
       <c r="D470" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9289,10 +9283,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>13123</v>
+        <v>13523</v>
       </c>
       <c r="D471" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9306,10 +9300,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>13124</v>
+        <v>13524</v>
       </c>
       <c r="D472" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9323,10 +9317,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>13125</v>
+        <v>13525</v>
       </c>
       <c r="D473" s="3">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9343,10 +9337,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>13501</v>
+        <v>13901</v>
       </c>
       <c r="D475" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9358,17 +9352,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20405</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>13502</v>
+        <v>13902</v>
       </c>
       <c r="D476" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9380,15 +9374,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20406</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>13503</v>
+        <v>13903</v>
       </c>
       <c r="D477" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9400,15 +9394,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20407</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>13504</v>
+        <v>13904</v>
       </c>
       <c r="D478" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9420,15 +9414,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20408</v>
+        <v>20478</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>13505</v>
+        <v>13905</v>
       </c>
       <c r="D479" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9442,10 +9436,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>13506</v>
+        <v>13906</v>
       </c>
       <c r="D480" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9459,10 +9453,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>13507</v>
+        <v>13907</v>
       </c>
       <c r="D481" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9476,10 +9470,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>13508</v>
+        <v>13908</v>
       </c>
       <c r="D482" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9493,10 +9487,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>13509</v>
+        <v>13909</v>
       </c>
       <c r="D483" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9510,10 +9504,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>13510</v>
+        <v>13910</v>
       </c>
       <c r="D484" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9527,10 +9521,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>13511</v>
+        <v>13911</v>
       </c>
       <c r="D485" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9544,10 +9538,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>13512</v>
+        <v>13912</v>
       </c>
       <c r="D486" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9561,10 +9555,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>13513</v>
+        <v>13913</v>
       </c>
       <c r="D487" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9578,10 +9572,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>13514</v>
+        <v>13914</v>
       </c>
       <c r="D488" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9595,10 +9589,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>13515</v>
+        <v>13915</v>
       </c>
       <c r="D489" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9612,10 +9606,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>13516</v>
+        <v>13916</v>
       </c>
       <c r="D490" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9629,10 +9623,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>13517</v>
+        <v>13917</v>
       </c>
       <c r="D491" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9646,10 +9640,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>13518</v>
+        <v>13918</v>
       </c>
       <c r="D492" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9663,10 +9657,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>13519</v>
+        <v>13919</v>
       </c>
       <c r="D493" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9680,10 +9674,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>13520</v>
+        <v>13920</v>
       </c>
       <c r="D494" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9697,10 +9691,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>13521</v>
+        <v>13921</v>
       </c>
       <c r="D495" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9714,10 +9708,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>13522</v>
+        <v>13922</v>
       </c>
       <c r="D496" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9731,10 +9725,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>13523</v>
+        <v>13923</v>
       </c>
       <c r="D497" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9748,10 +9742,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>13524</v>
+        <v>13924</v>
       </c>
       <c r="D498" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9765,10 +9759,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>13525</v>
+        <v>13925</v>
       </c>
       <c r="D499" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9785,10 +9779,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>13901</v>
+        <v>14101</v>
       </c>
       <c r="D501" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9800,17 +9794,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20475</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>13902</v>
+        <v>14102</v>
       </c>
       <c r="D502" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9822,15 +9816,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20476</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>13903</v>
+        <v>14103</v>
       </c>
       <c r="D503" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9842,15 +9836,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20477</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>13904</v>
+        <v>14104</v>
       </c>
       <c r="D504" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9862,15 +9856,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20478</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>13905</v>
+        <v>14105</v>
       </c>
       <c r="D505" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9884,10 +9878,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>13906</v>
+        <v>14106</v>
       </c>
       <c r="D506" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9901,10 +9895,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>13907</v>
+        <v>14107</v>
       </c>
       <c r="D507" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9918,10 +9912,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>13908</v>
+        <v>14108</v>
       </c>
       <c r="D508" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9935,10 +9929,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>13909</v>
+        <v>14109</v>
       </c>
       <c r="D509" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9952,10 +9946,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>13910</v>
+        <v>14110</v>
       </c>
       <c r="D510" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9969,10 +9963,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>13911</v>
+        <v>14111</v>
       </c>
       <c r="D511" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9986,10 +9980,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>13912</v>
+        <v>14112</v>
       </c>
       <c r="D512" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10003,10 +9997,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>13913</v>
+        <v>14113</v>
       </c>
       <c r="D513" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10020,10 +10014,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>13914</v>
+        <v>14114</v>
       </c>
       <c r="D514" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10037,10 +10031,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>13915</v>
+        <v>14115</v>
       </c>
       <c r="D515" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10054,10 +10048,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>13916</v>
+        <v>14116</v>
       </c>
       <c r="D516" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10071,10 +10065,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>13917</v>
+        <v>14117</v>
       </c>
       <c r="D517" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10088,10 +10082,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>13918</v>
+        <v>14118</v>
       </c>
       <c r="D518" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10105,10 +10099,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>13919</v>
+        <v>14119</v>
       </c>
       <c r="D519" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10122,10 +10116,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>13920</v>
+        <v>14120</v>
       </c>
       <c r="D520" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10139,10 +10133,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>13921</v>
+        <v>14121</v>
       </c>
       <c r="D521" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10156,10 +10150,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>13922</v>
+        <v>14122</v>
       </c>
       <c r="D522" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10173,10 +10167,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>13923</v>
+        <v>14123</v>
       </c>
       <c r="D523" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10190,10 +10184,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>13924</v>
+        <v>14124</v>
       </c>
       <c r="D524" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10207,10 +10201,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>13925</v>
+        <v>14125</v>
       </c>
       <c r="D525" s="3">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10227,10 +10221,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>14101</v>
+        <v>14301</v>
       </c>
       <c r="D527" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10242,17 +10236,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20525</v>
+        <v>20575</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>14102</v>
+        <v>14302</v>
       </c>
       <c r="D528" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10264,15 +10258,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20526</v>
+        <v>20576</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>14103</v>
+        <v>14303</v>
       </c>
       <c r="D529" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10284,15 +10278,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20527</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>14104</v>
+        <v>14304</v>
       </c>
       <c r="D530" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10304,15 +10298,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20528</v>
+        <v>20578</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>14105</v>
+        <v>14305</v>
       </c>
       <c r="D531" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10326,10 +10320,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>14106</v>
+        <v>14306</v>
       </c>
       <c r="D532" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10343,10 +10337,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>14107</v>
+        <v>14307</v>
       </c>
       <c r="D533" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10360,10 +10354,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>14108</v>
+        <v>14308</v>
       </c>
       <c r="D534" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10377,10 +10371,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>14109</v>
+        <v>14309</v>
       </c>
       <c r="D535" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10394,10 +10388,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>14110</v>
+        <v>14310</v>
       </c>
       <c r="D536" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10411,10 +10405,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>14111</v>
+        <v>14311</v>
       </c>
       <c r="D537" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10428,10 +10422,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>14112</v>
+        <v>14312</v>
       </c>
       <c r="D538" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10445,10 +10439,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>14113</v>
+        <v>14313</v>
       </c>
       <c r="D539" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10462,10 +10456,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>14114</v>
+        <v>14314</v>
       </c>
       <c r="D540" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10479,10 +10473,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>14115</v>
+        <v>14315</v>
       </c>
       <c r="D541" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10496,10 +10490,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>14116</v>
+        <v>14316</v>
       </c>
       <c r="D542" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10513,10 +10507,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>14117</v>
+        <v>14317</v>
       </c>
       <c r="D543" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10530,10 +10524,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>14118</v>
+        <v>14318</v>
       </c>
       <c r="D544" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10547,10 +10541,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>14119</v>
+        <v>14319</v>
       </c>
       <c r="D545" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10564,10 +10558,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>14120</v>
+        <v>14320</v>
       </c>
       <c r="D546" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10581,10 +10575,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>14121</v>
+        <v>14321</v>
       </c>
       <c r="D547" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10598,10 +10592,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>14122</v>
+        <v>14322</v>
       </c>
       <c r="D548" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10615,10 +10609,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>14123</v>
+        <v>14323</v>
       </c>
       <c r="D549" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10632,10 +10626,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>14124</v>
+        <v>14324</v>
       </c>
       <c r="D550" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10649,10 +10643,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>14125</v>
+        <v>14325</v>
       </c>
       <c r="D551" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10669,10 +10663,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>14301</v>
+        <v>14501</v>
       </c>
       <c r="D553" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10684,17 +10678,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20575</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>14302</v>
+        <v>14502</v>
       </c>
       <c r="D554" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10706,15 +10700,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20576</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>14303</v>
+        <v>14503</v>
       </c>
       <c r="D555" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10726,15 +10720,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20577</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>14304</v>
+        <v>14504</v>
       </c>
       <c r="D556" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10746,15 +10740,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20578</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>14305</v>
+        <v>14505</v>
       </c>
       <c r="D557" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10768,10 +10762,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>14306</v>
+        <v>14506</v>
       </c>
       <c r="D558" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10785,10 +10779,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>14307</v>
+        <v>14507</v>
       </c>
       <c r="D559" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10802,10 +10796,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>14308</v>
+        <v>14508</v>
       </c>
       <c r="D560" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10819,10 +10813,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>14309</v>
+        <v>14509</v>
       </c>
       <c r="D561" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10836,10 +10830,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>14310</v>
+        <v>14510</v>
       </c>
       <c r="D562" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10853,10 +10847,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>14311</v>
+        <v>14511</v>
       </c>
       <c r="D563" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10870,10 +10864,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>14312</v>
+        <v>14512</v>
       </c>
       <c r="D564" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10887,10 +10881,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>14313</v>
+        <v>14513</v>
       </c>
       <c r="D565" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10904,10 +10898,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>14314</v>
+        <v>14514</v>
       </c>
       <c r="D566" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10921,10 +10915,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>14315</v>
+        <v>14515</v>
       </c>
       <c r="D567" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10938,10 +10932,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>14316</v>
+        <v>14516</v>
       </c>
       <c r="D568" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10955,10 +10949,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>14317</v>
+        <v>14517</v>
       </c>
       <c r="D569" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10972,10 +10966,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>14318</v>
+        <v>14518</v>
       </c>
       <c r="D570" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10989,10 +10983,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>14319</v>
+        <v>14519</v>
       </c>
       <c r="D571" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11006,10 +11000,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>14320</v>
+        <v>14520</v>
       </c>
       <c r="D572" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11023,10 +11017,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>14321</v>
+        <v>14521</v>
       </c>
       <c r="D573" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11040,10 +11034,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>14322</v>
+        <v>14522</v>
       </c>
       <c r="D574" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11057,10 +11051,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>14323</v>
+        <v>14523</v>
       </c>
       <c r="D575" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11074,10 +11068,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>14324</v>
+        <v>14524</v>
       </c>
       <c r="D576" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11091,10 +11085,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>14325</v>
+        <v>14525</v>
       </c>
       <c r="D577" s="3">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11111,10 +11105,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>14401</v>
+        <v>14701</v>
       </c>
       <c r="D579" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11126,17 +11120,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20415</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>14402</v>
+        <v>14702</v>
       </c>
       <c r="D580" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11148,15 +11142,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20416</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>14403</v>
+        <v>14703</v>
       </c>
       <c r="D581" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11168,15 +11162,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20417</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>14404</v>
+        <v>14704</v>
       </c>
       <c r="D582" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11188,15 +11182,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20418</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>14405</v>
+        <v>14705</v>
       </c>
       <c r="D583" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11210,10 +11204,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>14406</v>
+        <v>14706</v>
       </c>
       <c r="D584" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11227,10 +11221,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>14407</v>
+        <v>14707</v>
       </c>
       <c r="D585" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11244,10 +11238,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>14408</v>
+        <v>14708</v>
       </c>
       <c r="D586" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11261,10 +11255,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>14409</v>
+        <v>14709</v>
       </c>
       <c r="D587" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11278,10 +11272,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>14410</v>
+        <v>14710</v>
       </c>
       <c r="D588" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11295,10 +11289,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>14411</v>
+        <v>14711</v>
       </c>
       <c r="D589" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11312,10 +11306,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>14412</v>
+        <v>14712</v>
       </c>
       <c r="D590" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11329,10 +11323,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>14413</v>
+        <v>14713</v>
       </c>
       <c r="D591" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11346,10 +11340,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>14414</v>
+        <v>14714</v>
       </c>
       <c r="D592" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11363,10 +11357,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>14415</v>
+        <v>14715</v>
       </c>
       <c r="D593" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11380,10 +11374,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>14416</v>
+        <v>14716</v>
       </c>
       <c r="D594" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11397,10 +11391,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>14417</v>
+        <v>14717</v>
       </c>
       <c r="D595" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11414,10 +11408,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>14418</v>
+        <v>14718</v>
       </c>
       <c r="D596" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11431,10 +11425,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>14419</v>
+        <v>14719</v>
       </c>
       <c r="D597" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11448,10 +11442,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>14420</v>
+        <v>14720</v>
       </c>
       <c r="D598" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11465,10 +11459,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>14421</v>
+        <v>14721</v>
       </c>
       <c r="D599" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11482,10 +11476,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>14422</v>
+        <v>14722</v>
       </c>
       <c r="D600" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11499,10 +11493,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>14423</v>
+        <v>14723</v>
       </c>
       <c r="D601" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11516,10 +11510,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>14424</v>
+        <v>14724</v>
       </c>
       <c r="D602" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11533,10 +11527,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>14425</v>
+        <v>14725</v>
       </c>
       <c r="D603" s="3">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11553,10 +11547,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>14501</v>
+        <v>14801</v>
       </c>
       <c r="D605" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11568,17 +11562,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20375</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>14502</v>
+        <v>14802</v>
       </c>
       <c r="D606" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11590,15 +11584,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20376</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>14503</v>
+        <v>14803</v>
       </c>
       <c r="D607" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11610,15 +11604,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20377</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>14504</v>
+        <v>14804</v>
       </c>
       <c r="D608" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11630,15 +11624,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20378</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>14505</v>
+        <v>14805</v>
       </c>
       <c r="D609" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11652,10 +11646,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>14506</v>
+        <v>14806</v>
       </c>
       <c r="D610" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11669,10 +11663,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>14507</v>
+        <v>14807</v>
       </c>
       <c r="D611" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11686,10 +11680,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>14508</v>
+        <v>14808</v>
       </c>
       <c r="D612" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11703,10 +11697,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>14509</v>
+        <v>14809</v>
       </c>
       <c r="D613" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11720,10 +11714,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>14510</v>
+        <v>14810</v>
       </c>
       <c r="D614" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11737,10 +11731,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>14511</v>
+        <v>14811</v>
       </c>
       <c r="D615" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11754,10 +11748,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>14512</v>
+        <v>14812</v>
       </c>
       <c r="D616" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11771,10 +11765,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>14513</v>
+        <v>14813</v>
       </c>
       <c r="D617" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11788,10 +11782,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>14514</v>
+        <v>14814</v>
       </c>
       <c r="D618" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11805,10 +11799,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>14515</v>
+        <v>14815</v>
       </c>
       <c r="D619" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11822,10 +11816,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>14516</v>
+        <v>14816</v>
       </c>
       <c r="D620" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11839,10 +11833,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>14517</v>
+        <v>14817</v>
       </c>
       <c r="D621" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11856,10 +11850,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>14518</v>
+        <v>14818</v>
       </c>
       <c r="D622" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11873,10 +11867,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>14519</v>
+        <v>14819</v>
       </c>
       <c r="D623" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11890,10 +11884,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>14520</v>
+        <v>14820</v>
       </c>
       <c r="D624" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11907,10 +11901,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>14521</v>
+        <v>14821</v>
       </c>
       <c r="D625" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11924,10 +11918,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>14522</v>
+        <v>14822</v>
       </c>
       <c r="D626" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11941,10 +11935,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>14523</v>
+        <v>14823</v>
       </c>
       <c r="D627" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11958,10 +11952,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>14524</v>
+        <v>14824</v>
       </c>
       <c r="D628" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11975,10 +11969,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>14525</v>
+        <v>14825</v>
       </c>
       <c r="D629" s="3">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11995,10 +11989,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>14601</v>
+        <v>14901</v>
       </c>
       <c r="D631" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12010,17 +12004,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20455</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>14602</v>
+        <v>14902</v>
       </c>
       <c r="D632" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12032,15 +12026,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20456</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>14603</v>
+        <v>14903</v>
       </c>
       <c r="D633" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12052,15 +12046,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20457</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>14604</v>
+        <v>14904</v>
       </c>
       <c r="D634" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12072,15 +12066,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20458</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>14605</v>
+        <v>14905</v>
       </c>
       <c r="D635" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12094,10 +12088,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>14606</v>
+        <v>14906</v>
       </c>
       <c r="D636" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12111,10 +12105,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>14607</v>
+        <v>14907</v>
       </c>
       <c r="D637" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12128,10 +12122,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>14608</v>
+        <v>14908</v>
       </c>
       <c r="D638" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12145,10 +12139,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>14609</v>
+        <v>14909</v>
       </c>
       <c r="D639" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12162,10 +12156,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>14610</v>
+        <v>14910</v>
       </c>
       <c r="D640" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12179,10 +12173,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>14611</v>
+        <v>14911</v>
       </c>
       <c r="D641" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12196,10 +12190,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>14612</v>
+        <v>14912</v>
       </c>
       <c r="D642" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12213,10 +12207,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>14613</v>
+        <v>14913</v>
       </c>
       <c r="D643" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12230,10 +12224,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>14614</v>
+        <v>14914</v>
       </c>
       <c r="D644" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12247,10 +12241,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>14615</v>
+        <v>14915</v>
       </c>
       <c r="D645" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12264,10 +12258,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>14616</v>
+        <v>14916</v>
       </c>
       <c r="D646" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12281,10 +12275,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>14617</v>
+        <v>14917</v>
       </c>
       <c r="D647" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12298,10 +12292,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>14618</v>
+        <v>14918</v>
       </c>
       <c r="D648" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12315,10 +12309,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>14619</v>
+        <v>14919</v>
       </c>
       <c r="D649" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12332,10 +12326,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>14620</v>
+        <v>14920</v>
       </c>
       <c r="D650" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12349,10 +12343,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>14621</v>
+        <v>14921</v>
       </c>
       <c r="D651" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12366,10 +12360,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>14622</v>
+        <v>14922</v>
       </c>
       <c r="D652" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12383,10 +12377,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>14623</v>
+        <v>14923</v>
       </c>
       <c r="D653" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12400,10 +12394,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>14624</v>
+        <v>14924</v>
       </c>
       <c r="D654" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12417,10 +12411,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>14625</v>
+        <v>14925</v>
       </c>
       <c r="D655" s="3">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12437,10 +12431,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>14701</v>
+        <v>15001</v>
       </c>
       <c r="D657" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12452,17 +12446,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20495</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>14702</v>
+        <v>15002</v>
       </c>
       <c r="D658" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12474,15 +12468,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20496</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="659" spans="3:8">
       <c r="C659" s="6">
-        <v>14703</v>
+        <v>15003</v>
       </c>
       <c r="D659" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12494,15 +12488,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20497</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="660" spans="3:8">
       <c r="C660" s="6">
-        <v>14704</v>
+        <v>15004</v>
       </c>
       <c r="D660" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12514,15 +12508,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20498</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="661" spans="3:7">
       <c r="C661" s="6">
-        <v>14705</v>
+        <v>15005</v>
       </c>
       <c r="D661" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12536,10 +12530,10 @@
     </row>
     <row r="662" spans="3:7">
       <c r="C662" s="6">
-        <v>14706</v>
+        <v>15006</v>
       </c>
       <c r="D662" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12553,10 +12547,10 @@
     </row>
     <row r="663" spans="3:7">
       <c r="C663" s="6">
-        <v>14707</v>
+        <v>15007</v>
       </c>
       <c r="D663" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12570,10 +12564,10 @@
     </row>
     <row r="664" spans="3:7">
       <c r="C664" s="6">
-        <v>14708</v>
+        <v>15008</v>
       </c>
       <c r="D664" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12587,10 +12581,10 @@
     </row>
     <row r="665" spans="3:7">
       <c r="C665" s="6">
-        <v>14709</v>
+        <v>15009</v>
       </c>
       <c r="D665" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12604,10 +12598,10 @@
     </row>
     <row r="666" spans="3:7">
       <c r="C666" s="6">
-        <v>14710</v>
+        <v>15010</v>
       </c>
       <c r="D666" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12621,10 +12615,10 @@
     </row>
     <row r="667" spans="3:7">
       <c r="C667" s="6">
-        <v>14711</v>
+        <v>15011</v>
       </c>
       <c r="D667" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12638,10 +12632,10 @@
     </row>
     <row r="668" spans="3:7">
       <c r="C668" s="6">
-        <v>14712</v>
+        <v>15012</v>
       </c>
       <c r="D668" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12655,10 +12649,10 @@
     </row>
     <row r="669" spans="3:7">
       <c r="C669" s="6">
-        <v>14713</v>
+        <v>15013</v>
       </c>
       <c r="D669" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12672,10 +12666,10 @@
     </row>
     <row r="670" spans="3:7">
       <c r="C670" s="6">
-        <v>14714</v>
+        <v>15014</v>
       </c>
       <c r="D670" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12689,10 +12683,10 @@
     </row>
     <row r="671" spans="3:7">
       <c r="C671" s="6">
-        <v>14715</v>
+        <v>15015</v>
       </c>
       <c r="D671" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12706,10 +12700,10 @@
     </row>
     <row r="672" spans="3:7">
       <c r="C672" s="6">
-        <v>14716</v>
+        <v>15016</v>
       </c>
       <c r="D672" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12723,10 +12717,10 @@
     </row>
     <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>14717</v>
+        <v>15017</v>
       </c>
       <c r="D673" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12740,10 +12734,10 @@
     </row>
     <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>14718</v>
+        <v>15018</v>
       </c>
       <c r="D674" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12757,10 +12751,10 @@
     </row>
     <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>14719</v>
+        <v>15019</v>
       </c>
       <c r="D675" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12774,10 +12768,10 @@
     </row>
     <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>14720</v>
+        <v>15020</v>
       </c>
       <c r="D676" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12791,10 +12785,10 @@
     </row>
     <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>14721</v>
+        <v>15021</v>
       </c>
       <c r="D677" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12808,10 +12802,10 @@
     </row>
     <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>14722</v>
+        <v>15022</v>
       </c>
       <c r="D678" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12825,10 +12819,10 @@
     </row>
     <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>14723</v>
+        <v>15023</v>
       </c>
       <c r="D679" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12842,10 +12836,10 @@
     </row>
     <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>14724</v>
+        <v>15024</v>
       </c>
       <c r="D680" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12859,10 +12853,10 @@
     </row>
     <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>14725</v>
+        <v>15025</v>
       </c>
       <c r="D681" s="3">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12871,890 +12865,6 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>14801</v>
-      </c>
-      <c r="D683" s="3">
-        <v>148</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20585</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>14802</v>
-      </c>
-      <c r="D684" s="3">
-        <v>148</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20586</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>14803</v>
-      </c>
-      <c r="D685" s="3">
-        <v>148</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20587</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>14804</v>
-      </c>
-      <c r="D686" s="3">
-        <v>148</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20588</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>14805</v>
-      </c>
-      <c r="D687" s="3">
-        <v>148</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>14806</v>
-      </c>
-      <c r="D688" s="3">
-        <v>148</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>14807</v>
-      </c>
-      <c r="D689" s="3">
-        <v>148</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>14808</v>
-      </c>
-      <c r="D690" s="3">
-        <v>148</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>14809</v>
-      </c>
-      <c r="D691" s="3">
-        <v>148</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>14810</v>
-      </c>
-      <c r="D692" s="3">
-        <v>148</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>14811</v>
-      </c>
-      <c r="D693" s="3">
-        <v>148</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>14812</v>
-      </c>
-      <c r="D694" s="3">
-        <v>148</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>14813</v>
-      </c>
-      <c r="D695" s="3">
-        <v>148</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>14814</v>
-      </c>
-      <c r="D696" s="3">
-        <v>148</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>14815</v>
-      </c>
-      <c r="D697" s="3">
-        <v>148</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>14816</v>
-      </c>
-      <c r="D698" s="3">
-        <v>148</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>14817</v>
-      </c>
-      <c r="D699" s="3">
-        <v>148</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>14818</v>
-      </c>
-      <c r="D700" s="3">
-        <v>148</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>14819</v>
-      </c>
-      <c r="D701" s="3">
-        <v>148</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>14820</v>
-      </c>
-      <c r="D702" s="3">
-        <v>148</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>14821</v>
-      </c>
-      <c r="D703" s="3">
-        <v>148</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>14822</v>
-      </c>
-      <c r="D704" s="3">
-        <v>148</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>14823</v>
-      </c>
-      <c r="D705" s="3">
-        <v>148</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>14824</v>
-      </c>
-      <c r="D706" s="3">
-        <v>148</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>14825</v>
-      </c>
-      <c r="D707" s="3">
-        <v>148</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>14901</v>
-      </c>
-      <c r="D709" s="3">
-        <v>149</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20445</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>14902</v>
-      </c>
-      <c r="D710" s="3">
-        <v>149</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20446</v>
-      </c>
-    </row>
-    <row r="711" spans="3:8">
-      <c r="C711" s="6">
-        <v>14903</v>
-      </c>
-      <c r="D711" s="3">
-        <v>149</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20447</v>
-      </c>
-    </row>
-    <row r="712" spans="3:8">
-      <c r="C712" s="6">
-        <v>14904</v>
-      </c>
-      <c r="D712" s="3">
-        <v>149</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20448</v>
-      </c>
-    </row>
-    <row r="713" spans="3:7">
-      <c r="C713" s="6">
-        <v>14905</v>
-      </c>
-      <c r="D713" s="3">
-        <v>149</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="3:7">
-      <c r="C714" s="6">
-        <v>14906</v>
-      </c>
-      <c r="D714" s="3">
-        <v>149</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="3:7">
-      <c r="C715" s="6">
-        <v>14907</v>
-      </c>
-      <c r="D715" s="3">
-        <v>149</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="3:7">
-      <c r="C716" s="6">
-        <v>14908</v>
-      </c>
-      <c r="D716" s="3">
-        <v>149</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="3:7">
-      <c r="C717" s="6">
-        <v>14909</v>
-      </c>
-      <c r="D717" s="3">
-        <v>149</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="3:7">
-      <c r="C718" s="6">
-        <v>14910</v>
-      </c>
-      <c r="D718" s="3">
-        <v>149</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="3:7">
-      <c r="C719" s="6">
-        <v>14911</v>
-      </c>
-      <c r="D719" s="3">
-        <v>149</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="3:7">
-      <c r="C720" s="6">
-        <v>14912</v>
-      </c>
-      <c r="D720" s="3">
-        <v>149</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="3:7">
-      <c r="C721" s="6">
-        <v>14913</v>
-      </c>
-      <c r="D721" s="3">
-        <v>149</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="3:7">
-      <c r="C722" s="6">
-        <v>14914</v>
-      </c>
-      <c r="D722" s="3">
-        <v>149</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="3:7">
-      <c r="C723" s="6">
-        <v>14915</v>
-      </c>
-      <c r="D723" s="3">
-        <v>149</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="3:7">
-      <c r="C724" s="6">
-        <v>14916</v>
-      </c>
-      <c r="D724" s="3">
-        <v>149</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="3:7">
-      <c r="C725" s="6">
-        <v>14917</v>
-      </c>
-      <c r="D725" s="3">
-        <v>149</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="3:7">
-      <c r="C726" s="6">
-        <v>14918</v>
-      </c>
-      <c r="D726" s="3">
-        <v>149</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="3:7">
-      <c r="C727" s="6">
-        <v>14919</v>
-      </c>
-      <c r="D727" s="3">
-        <v>149</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="3:7">
-      <c r="C728" s="6">
-        <v>14920</v>
-      </c>
-      <c r="D728" s="3">
-        <v>149</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="3:7">
-      <c r="C729" s="6">
-        <v>14921</v>
-      </c>
-      <c r="D729" s="3">
-        <v>149</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="3:7">
-      <c r="C730" s="6">
-        <v>14922</v>
-      </c>
-      <c r="D730" s="3">
-        <v>149</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="3:7">
-      <c r="C731" s="6">
-        <v>14923</v>
-      </c>
-      <c r="D731" s="3">
-        <v>149</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="3:7">
-      <c r="C732" s="6">
-        <v>14924</v>
-      </c>
-      <c r="D732" s="3">
-        <v>149</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="3:7">
-      <c r="C733" s="6">
-        <v>14925</v>
-      </c>
-      <c r="D733" s="3">
-        <v>149</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋150破晓之战</t>
+  </si>
+  <si>
+    <t>#先锋151龙裔国度</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>15101</v>
+      </c>
+      <c r="D683" s="3">
+        <v>151</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20415</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>15102</v>
+      </c>
+      <c r="D684" s="3">
+        <v>151</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20416</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>15103</v>
+      </c>
+      <c r="D685" s="3">
+        <v>151</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>15104</v>
+      </c>
+      <c r="D686" s="3">
+        <v>151</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20418</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>15105</v>
+      </c>
+      <c r="D687" s="3">
+        <v>151</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>15106</v>
+      </c>
+      <c r="D688" s="3">
+        <v>151</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>15107</v>
+      </c>
+      <c r="D689" s="3">
+        <v>151</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>15108</v>
+      </c>
+      <c r="D690" s="3">
+        <v>151</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>15109</v>
+      </c>
+      <c r="D691" s="3">
+        <v>151</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>15110</v>
+      </c>
+      <c r="D692" s="3">
+        <v>151</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>15111</v>
+      </c>
+      <c r="D693" s="3">
+        <v>151</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>15112</v>
+      </c>
+      <c r="D694" s="3">
+        <v>151</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>15113</v>
+      </c>
+      <c r="D695" s="3">
+        <v>151</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>15114</v>
+      </c>
+      <c r="D696" s="3">
+        <v>151</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>15115</v>
+      </c>
+      <c r="D697" s="3">
+        <v>151</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>15116</v>
+      </c>
+      <c r="D698" s="3">
+        <v>151</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>15117</v>
+      </c>
+      <c r="D699" s="3">
+        <v>151</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>15118</v>
+      </c>
+      <c r="D700" s="3">
+        <v>151</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>15119</v>
+      </c>
+      <c r="D701" s="3">
+        <v>151</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>15120</v>
+      </c>
+      <c r="D702" s="3">
+        <v>151</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>15121</v>
+      </c>
+      <c r="D703" s="3">
+        <v>151</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>15122</v>
+      </c>
+      <c r="D704" s="3">
+        <v>151</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>15123</v>
+      </c>
+      <c r="D705" s="3">
+        <v>151</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>15124</v>
+      </c>
+      <c r="D706" s="3">
+        <v>151</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>15125</v>
+      </c>
+      <c r="D707" s="3">
+        <v>151</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋151龙裔国度</t>
+  </si>
+  <si>
+    <t>#先锋152秘境森林</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>15201</v>
+      </c>
+      <c r="D709" s="3">
+        <v>152</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>15202</v>
+      </c>
+      <c r="D710" s="3">
+        <v>152</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="711" spans="3:8">
+      <c r="C711" s="6">
+        <v>15203</v>
+      </c>
+      <c r="D711" s="3">
+        <v>152</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="712" spans="3:8">
+      <c r="C712" s="6">
+        <v>15204</v>
+      </c>
+      <c r="D712" s="3">
+        <v>152</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="713" spans="3:7">
+      <c r="C713" s="6">
+        <v>15205</v>
+      </c>
+      <c r="D713" s="3">
+        <v>152</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="3:7">
+      <c r="C714" s="6">
+        <v>15206</v>
+      </c>
+      <c r="D714" s="3">
+        <v>152</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="3:7">
+      <c r="C715" s="6">
+        <v>15207</v>
+      </c>
+      <c r="D715" s="3">
+        <v>152</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="3:7">
+      <c r="C716" s="6">
+        <v>15208</v>
+      </c>
+      <c r="D716" s="3">
+        <v>152</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="3:7">
+      <c r="C717" s="6">
+        <v>15209</v>
+      </c>
+      <c r="D717" s="3">
+        <v>152</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="3:7">
+      <c r="C718" s="6">
+        <v>15210</v>
+      </c>
+      <c r="D718" s="3">
+        <v>152</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="3:7">
+      <c r="C719" s="6">
+        <v>15211</v>
+      </c>
+      <c r="D719" s="3">
+        <v>152</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="3:7">
+      <c r="C720" s="6">
+        <v>15212</v>
+      </c>
+      <c r="D720" s="3">
+        <v>152</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>15213</v>
+      </c>
+      <c r="D721" s="3">
+        <v>152</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>15214</v>
+      </c>
+      <c r="D722" s="3">
+        <v>152</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>15215</v>
+      </c>
+      <c r="D723" s="3">
+        <v>152</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>15216</v>
+      </c>
+      <c r="D724" s="3">
+        <v>152</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>15217</v>
+      </c>
+      <c r="D725" s="3">
+        <v>152</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>15218</v>
+      </c>
+      <c r="D726" s="3">
+        <v>152</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>15219</v>
+      </c>
+      <c r="D727" s="3">
+        <v>152</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>15220</v>
+      </c>
+      <c r="D728" s="3">
+        <v>152</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>15221</v>
+      </c>
+      <c r="D729" s="3">
+        <v>152</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>15222</v>
+      </c>
+      <c r="D730" s="3">
+        <v>152</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>15223</v>
+      </c>
+      <c r="D731" s="3">
+        <v>152</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>15224</v>
+      </c>
+      <c r="D732" s="3">
+        <v>152</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>15225</v>
+      </c>
+      <c r="D733" s="3">
+        <v>152</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋152秘境森林</t>
+  </si>
+  <si>
+    <t>#先锋153荣耀之路</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>15301</v>
+      </c>
+      <c r="D735" s="3">
+        <v>153</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20565</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>15302</v>
+      </c>
+      <c r="D736" s="3">
+        <v>153</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20566</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>15303</v>
+      </c>
+      <c r="D737" s="3">
+        <v>153</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20567</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>15304</v>
+      </c>
+      <c r="D738" s="3">
+        <v>153</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20568</v>
+      </c>
+    </row>
+    <row r="739" spans="3:7">
+      <c r="C739" s="6">
+        <v>15305</v>
+      </c>
+      <c r="D739" s="3">
+        <v>153</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:7">
+      <c r="C740" s="6">
+        <v>15306</v>
+      </c>
+      <c r="D740" s="3">
+        <v>153</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:7">
+      <c r="C741" s="6">
+        <v>15307</v>
+      </c>
+      <c r="D741" s="3">
+        <v>153</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:7">
+      <c r="C742" s="6">
+        <v>15308</v>
+      </c>
+      <c r="D742" s="3">
+        <v>153</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:7">
+      <c r="C743" s="6">
+        <v>15309</v>
+      </c>
+      <c r="D743" s="3">
+        <v>153</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:7">
+      <c r="C744" s="6">
+        <v>15310</v>
+      </c>
+      <c r="D744" s="3">
+        <v>153</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:7">
+      <c r="C745" s="6">
+        <v>15311</v>
+      </c>
+      <c r="D745" s="3">
+        <v>153</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:7">
+      <c r="C746" s="6">
+        <v>15312</v>
+      </c>
+      <c r="D746" s="3">
+        <v>153</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:7">
+      <c r="C747" s="6">
+        <v>15313</v>
+      </c>
+      <c r="D747" s="3">
+        <v>153</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:7">
+      <c r="C748" s="6">
+        <v>15314</v>
+      </c>
+      <c r="D748" s="3">
+        <v>153</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:7">
+      <c r="C749" s="6">
+        <v>15315</v>
+      </c>
+      <c r="D749" s="3">
+        <v>153</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:7">
+      <c r="C750" s="6">
+        <v>15316</v>
+      </c>
+      <c r="D750" s="3">
+        <v>153</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:7">
+      <c r="C751" s="6">
+        <v>15317</v>
+      </c>
+      <c r="D751" s="3">
+        <v>153</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:7">
+      <c r="C752" s="6">
+        <v>15318</v>
+      </c>
+      <c r="D752" s="3">
+        <v>153</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>15319</v>
+      </c>
+      <c r="D753" s="3">
+        <v>153</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>15320</v>
+      </c>
+      <c r="D754" s="3">
+        <v>153</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>15321</v>
+      </c>
+      <c r="D755" s="3">
+        <v>153</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>15322</v>
+      </c>
+      <c r="D756" s="3">
+        <v>153</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>15323</v>
+      </c>
+      <c r="D757" s="3">
+        <v>153</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>15324</v>
+      </c>
+      <c r="D758" s="3">
+        <v>153</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>15325</v>
+      </c>
+      <c r="D759" s="3">
+        <v>153</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>#先锋153荣耀之路</t>
+  </si>
+  <si>
+    <t>#先锋154荣耀之路</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O785"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14200,6 +14203,448 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C761" s="6">
+        <v>15401</v>
+      </c>
+      <c r="D761" s="3">
+        <v>154</v>
+      </c>
+      <c r="E761" s="5">
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H761" s="3">
+        <v>20595</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="6">
+        <v>15402</v>
+      </c>
+      <c r="D762" s="3">
+        <v>154</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20596</v>
+      </c>
+    </row>
+    <row r="763" spans="3:8">
+      <c r="C763" s="6">
+        <v>15403</v>
+      </c>
+      <c r="D763" s="3">
+        <v>154</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20597</v>
+      </c>
+    </row>
+    <row r="764" spans="3:8">
+      <c r="C764" s="6">
+        <v>15404</v>
+      </c>
+      <c r="D764" s="3">
+        <v>154</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20598</v>
+      </c>
+    </row>
+    <row r="765" spans="3:7">
+      <c r="C765" s="6">
+        <v>15405</v>
+      </c>
+      <c r="D765" s="3">
+        <v>154</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="3:7">
+      <c r="C766" s="6">
+        <v>15406</v>
+      </c>
+      <c r="D766" s="3">
+        <v>154</v>
+      </c>
+      <c r="E766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="767" spans="3:7">
+      <c r="C767" s="6">
+        <v>15407</v>
+      </c>
+      <c r="D767" s="3">
+        <v>154</v>
+      </c>
+      <c r="E767" s="5">
+        <v>1</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="3:7">
+      <c r="C768" s="6">
+        <v>15408</v>
+      </c>
+      <c r="D768" s="3">
+        <v>154</v>
+      </c>
+      <c r="E768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>15409</v>
+      </c>
+      <c r="D769" s="3">
+        <v>154</v>
+      </c>
+      <c r="E769" s="3">
+        <v>1</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>15410</v>
+      </c>
+      <c r="D770" s="3">
+        <v>154</v>
+      </c>
+      <c r="E770" s="5">
+        <v>1</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>15411</v>
+      </c>
+      <c r="D771" s="3">
+        <v>154</v>
+      </c>
+      <c r="E771" s="5">
+        <v>1</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>15412</v>
+      </c>
+      <c r="D772" s="3">
+        <v>154</v>
+      </c>
+      <c r="E772" s="5">
+        <v>1</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>15413</v>
+      </c>
+      <c r="D773" s="3">
+        <v>154</v>
+      </c>
+      <c r="E773" s="3">
+        <v>1</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>15414</v>
+      </c>
+      <c r="D774" s="3">
+        <v>154</v>
+      </c>
+      <c r="E774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>15415</v>
+      </c>
+      <c r="D775" s="3">
+        <v>154</v>
+      </c>
+      <c r="E775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>15416</v>
+      </c>
+      <c r="D776" s="3">
+        <v>154</v>
+      </c>
+      <c r="E776" s="5">
+        <v>1</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>15417</v>
+      </c>
+      <c r="D777" s="3">
+        <v>154</v>
+      </c>
+      <c r="E777" s="3">
+        <v>1</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>15418</v>
+      </c>
+      <c r="D778" s="3">
+        <v>154</v>
+      </c>
+      <c r="E778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>15419</v>
+      </c>
+      <c r="D779" s="3">
+        <v>154</v>
+      </c>
+      <c r="E779" s="5">
+        <v>1</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>15420</v>
+      </c>
+      <c r="D780" s="3">
+        <v>154</v>
+      </c>
+      <c r="E780" s="5">
+        <v>1</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>15421</v>
+      </c>
+      <c r="D781" s="3">
+        <v>154</v>
+      </c>
+      <c r="E781" s="3">
+        <v>1</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>15422</v>
+      </c>
+      <c r="D782" s="3">
+        <v>154</v>
+      </c>
+      <c r="E782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>15423</v>
+      </c>
+      <c r="D783" s="3">
+        <v>154</v>
+      </c>
+      <c r="E783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>15424</v>
+      </c>
+      <c r="D784" s="3">
+        <v>154</v>
+      </c>
+      <c r="E784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>15425</v>
+      </c>
+      <c r="D785" s="3">
+        <v>154</v>
+      </c>
+      <c r="E785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +14765,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +14783,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +14801,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +14819,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +14839,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14937,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>#先锋154荣耀之路</t>
+  </si>
+  <si>
+    <t>#先锋155雷霆万钧</t>
   </si>
   <si>
     <t>Center</t>
@@ -1272,7 +1275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O785"/>
+  <dimension ref="A3:O811"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14645,6 +14648,448 @@
         <v>42</v>
       </c>
       <c r="G785" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8">
+      <c r="A787" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C787" s="6">
+        <v>15501</v>
+      </c>
+      <c r="D787" s="3">
+        <v>155</v>
+      </c>
+      <c r="E787" s="5">
+        <v>1</v>
+      </c>
+      <c r="F787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H787" s="3">
+        <v>20605</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8">
+      <c r="A788" s="1"/>
+      <c r="B788" s="1"/>
+      <c r="C788" s="6">
+        <v>15502</v>
+      </c>
+      <c r="D788" s="3">
+        <v>155</v>
+      </c>
+      <c r="E788" s="5">
+        <v>1</v>
+      </c>
+      <c r="F788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H788" s="3">
+        <v>20606</v>
+      </c>
+    </row>
+    <row r="789" spans="3:8">
+      <c r="C789" s="6">
+        <v>15503</v>
+      </c>
+      <c r="D789" s="3">
+        <v>155</v>
+      </c>
+      <c r="E789" s="5">
+        <v>1</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H789" s="3">
+        <v>20607</v>
+      </c>
+    </row>
+    <row r="790" spans="3:8">
+      <c r="C790" s="6">
+        <v>15504</v>
+      </c>
+      <c r="D790" s="3">
+        <v>155</v>
+      </c>
+      <c r="E790" s="5">
+        <v>1</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H790" s="3">
+        <v>20608</v>
+      </c>
+    </row>
+    <row r="791" spans="3:7">
+      <c r="C791" s="6">
+        <v>15505</v>
+      </c>
+      <c r="D791" s="3">
+        <v>155</v>
+      </c>
+      <c r="E791" s="3">
+        <v>1</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="3:7">
+      <c r="C792" s="6">
+        <v>15506</v>
+      </c>
+      <c r="D792" s="3">
+        <v>155</v>
+      </c>
+      <c r="E792" s="5">
+        <v>1</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="793" spans="3:7">
+      <c r="C793" s="6">
+        <v>15507</v>
+      </c>
+      <c r="D793" s="3">
+        <v>155</v>
+      </c>
+      <c r="E793" s="5">
+        <v>1</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="794" spans="3:7">
+      <c r="C794" s="6">
+        <v>15508</v>
+      </c>
+      <c r="D794" s="3">
+        <v>155</v>
+      </c>
+      <c r="E794" s="5">
+        <v>1</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="795" spans="3:7">
+      <c r="C795" s="6">
+        <v>15509</v>
+      </c>
+      <c r="D795" s="3">
+        <v>155</v>
+      </c>
+      <c r="E795" s="3">
+        <v>1</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="796" spans="3:7">
+      <c r="C796" s="6">
+        <v>15510</v>
+      </c>
+      <c r="D796" s="3">
+        <v>155</v>
+      </c>
+      <c r="E796" s="5">
+        <v>1</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="797" spans="3:7">
+      <c r="C797" s="6">
+        <v>15511</v>
+      </c>
+      <c r="D797" s="3">
+        <v>155</v>
+      </c>
+      <c r="E797" s="5">
+        <v>1</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="798" spans="3:7">
+      <c r="C798" s="6">
+        <v>15512</v>
+      </c>
+      <c r="D798" s="3">
+        <v>155</v>
+      </c>
+      <c r="E798" s="5">
+        <v>1</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="799" spans="3:7">
+      <c r="C799" s="6">
+        <v>15513</v>
+      </c>
+      <c r="D799" s="3">
+        <v>155</v>
+      </c>
+      <c r="E799" s="3">
+        <v>1</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="800" spans="3:7">
+      <c r="C800" s="6">
+        <v>15514</v>
+      </c>
+      <c r="D800" s="3">
+        <v>155</v>
+      </c>
+      <c r="E800" s="5">
+        <v>1</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="801" spans="3:7">
+      <c r="C801" s="6">
+        <v>15515</v>
+      </c>
+      <c r="D801" s="3">
+        <v>155</v>
+      </c>
+      <c r="E801" s="5">
+        <v>1</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="802" spans="3:7">
+      <c r="C802" s="6">
+        <v>15516</v>
+      </c>
+      <c r="D802" s="3">
+        <v>155</v>
+      </c>
+      <c r="E802" s="5">
+        <v>1</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="803" spans="3:7">
+      <c r="C803" s="6">
+        <v>15517</v>
+      </c>
+      <c r="D803" s="3">
+        <v>155</v>
+      </c>
+      <c r="E803" s="3">
+        <v>1</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="804" spans="3:7">
+      <c r="C804" s="6">
+        <v>15518</v>
+      </c>
+      <c r="D804" s="3">
+        <v>155</v>
+      </c>
+      <c r="E804" s="5">
+        <v>1</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="805" spans="3:7">
+      <c r="C805" s="6">
+        <v>15519</v>
+      </c>
+      <c r="D805" s="3">
+        <v>155</v>
+      </c>
+      <c r="E805" s="5">
+        <v>1</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="806" spans="3:7">
+      <c r="C806" s="6">
+        <v>15520</v>
+      </c>
+      <c r="D806" s="3">
+        <v>155</v>
+      </c>
+      <c r="E806" s="5">
+        <v>1</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="807" spans="3:7">
+      <c r="C807" s="6">
+        <v>15521</v>
+      </c>
+      <c r="D807" s="3">
+        <v>155</v>
+      </c>
+      <c r="E807" s="3">
+        <v>1</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="808" spans="3:7">
+      <c r="C808" s="6">
+        <v>15522</v>
+      </c>
+      <c r="D808" s="3">
+        <v>155</v>
+      </c>
+      <c r="E808" s="5">
+        <v>1</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="809" spans="3:7">
+      <c r="C809" s="6">
+        <v>15523</v>
+      </c>
+      <c r="D809" s="3">
+        <v>155</v>
+      </c>
+      <c r="E809" s="5">
+        <v>1</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="810" spans="3:7">
+      <c r="C810" s="6">
+        <v>15524</v>
+      </c>
+      <c r="D810" s="3">
+        <v>155</v>
+      </c>
+      <c r="E810" s="5">
+        <v>1</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="811" spans="3:7">
+      <c r="C811" s="6">
+        <v>15525</v>
+      </c>
+      <c r="D811" s="3">
+        <v>155</v>
+      </c>
+      <c r="E811" s="3">
+        <v>1</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G811" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14765,10 +15210,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14783,10 +15228,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14801,10 +15246,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14819,10 +15264,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14839,10 +15284,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14937,10 +15382,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>#先锋155雷霆万钧</t>
+  </si>
+  <si>
+    <t>#先锋156龙翔九天</t>
   </si>
   <si>
     <t>Center</t>
@@ -1275,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O811"/>
+  <dimension ref="A3:O837"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -15090,6 +15093,448 @@
         <v>42</v>
       </c>
       <c r="G811" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="813" spans="1:8">
+      <c r="A813" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C813" s="6">
+        <v>15601</v>
+      </c>
+      <c r="D813" s="3">
+        <v>156</v>
+      </c>
+      <c r="E813" s="5">
+        <v>1</v>
+      </c>
+      <c r="F813" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G813" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H813" s="3">
+        <v>20615</v>
+      </c>
+    </row>
+    <row r="814" spans="1:8">
+      <c r="A814" s="1"/>
+      <c r="B814" s="1"/>
+      <c r="C814" s="6">
+        <v>15602</v>
+      </c>
+      <c r="D814" s="3">
+        <v>156</v>
+      </c>
+      <c r="E814" s="5">
+        <v>1</v>
+      </c>
+      <c r="F814" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G814" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H814" s="3">
+        <v>20616</v>
+      </c>
+    </row>
+    <row r="815" spans="3:8">
+      <c r="C815" s="6">
+        <v>15603</v>
+      </c>
+      <c r="D815" s="3">
+        <v>156</v>
+      </c>
+      <c r="E815" s="5">
+        <v>1</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H815" s="3">
+        <v>20617</v>
+      </c>
+    </row>
+    <row r="816" spans="3:8">
+      <c r="C816" s="6">
+        <v>15604</v>
+      </c>
+      <c r="D816" s="3">
+        <v>156</v>
+      </c>
+      <c r="E816" s="5">
+        <v>1</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G816" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H816" s="3">
+        <v>20618</v>
+      </c>
+    </row>
+    <row r="817" spans="3:7">
+      <c r="C817" s="6">
+        <v>15605</v>
+      </c>
+      <c r="D817" s="3">
+        <v>156</v>
+      </c>
+      <c r="E817" s="3">
+        <v>1</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G817" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="818" spans="3:7">
+      <c r="C818" s="6">
+        <v>15606</v>
+      </c>
+      <c r="D818" s="3">
+        <v>156</v>
+      </c>
+      <c r="E818" s="5">
+        <v>1</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="819" spans="3:7">
+      <c r="C819" s="6">
+        <v>15607</v>
+      </c>
+      <c r="D819" s="3">
+        <v>156</v>
+      </c>
+      <c r="E819" s="5">
+        <v>1</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="820" spans="3:7">
+      <c r="C820" s="6">
+        <v>15608</v>
+      </c>
+      <c r="D820" s="3">
+        <v>156</v>
+      </c>
+      <c r="E820" s="5">
+        <v>1</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="821" spans="3:7">
+      <c r="C821" s="6">
+        <v>15609</v>
+      </c>
+      <c r="D821" s="3">
+        <v>156</v>
+      </c>
+      <c r="E821" s="3">
+        <v>1</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="822" spans="3:7">
+      <c r="C822" s="6">
+        <v>15610</v>
+      </c>
+      <c r="D822" s="3">
+        <v>156</v>
+      </c>
+      <c r="E822" s="5">
+        <v>1</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="823" spans="3:7">
+      <c r="C823" s="6">
+        <v>15611</v>
+      </c>
+      <c r="D823" s="3">
+        <v>156</v>
+      </c>
+      <c r="E823" s="5">
+        <v>1</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="824" spans="3:7">
+      <c r="C824" s="6">
+        <v>15612</v>
+      </c>
+      <c r="D824" s="3">
+        <v>156</v>
+      </c>
+      <c r="E824" s="5">
+        <v>1</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="825" spans="3:7">
+      <c r="C825" s="6">
+        <v>15613</v>
+      </c>
+      <c r="D825" s="3">
+        <v>156</v>
+      </c>
+      <c r="E825" s="3">
+        <v>1</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="826" spans="3:7">
+      <c r="C826" s="6">
+        <v>15614</v>
+      </c>
+      <c r="D826" s="3">
+        <v>156</v>
+      </c>
+      <c r="E826" s="5">
+        <v>1</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G826" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="827" spans="3:7">
+      <c r="C827" s="6">
+        <v>15615</v>
+      </c>
+      <c r="D827" s="3">
+        <v>156</v>
+      </c>
+      <c r="E827" s="5">
+        <v>1</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="828" spans="3:7">
+      <c r="C828" s="6">
+        <v>15616</v>
+      </c>
+      <c r="D828" s="3">
+        <v>156</v>
+      </c>
+      <c r="E828" s="5">
+        <v>1</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="829" spans="3:7">
+      <c r="C829" s="6">
+        <v>15617</v>
+      </c>
+      <c r="D829" s="3">
+        <v>156</v>
+      </c>
+      <c r="E829" s="3">
+        <v>1</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="830" spans="3:7">
+      <c r="C830" s="6">
+        <v>15618</v>
+      </c>
+      <c r="D830" s="3">
+        <v>156</v>
+      </c>
+      <c r="E830" s="5">
+        <v>1</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G830" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="831" spans="3:7">
+      <c r="C831" s="6">
+        <v>15619</v>
+      </c>
+      <c r="D831" s="3">
+        <v>156</v>
+      </c>
+      <c r="E831" s="5">
+        <v>1</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="832" spans="3:7">
+      <c r="C832" s="6">
+        <v>15620</v>
+      </c>
+      <c r="D832" s="3">
+        <v>156</v>
+      </c>
+      <c r="E832" s="5">
+        <v>1</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G832" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="833" spans="3:7">
+      <c r="C833" s="6">
+        <v>15621</v>
+      </c>
+      <c r="D833" s="3">
+        <v>156</v>
+      </c>
+      <c r="E833" s="3">
+        <v>1</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="834" spans="3:7">
+      <c r="C834" s="6">
+        <v>15622</v>
+      </c>
+      <c r="D834" s="3">
+        <v>156</v>
+      </c>
+      <c r="E834" s="5">
+        <v>1</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G834" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="835" spans="3:7">
+      <c r="C835" s="6">
+        <v>15623</v>
+      </c>
+      <c r="D835" s="3">
+        <v>156</v>
+      </c>
+      <c r="E835" s="5">
+        <v>1</v>
+      </c>
+      <c r="F835" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="836" spans="3:7">
+      <c r="C836" s="6">
+        <v>15624</v>
+      </c>
+      <c r="D836" s="3">
+        <v>156</v>
+      </c>
+      <c r="E836" s="5">
+        <v>1</v>
+      </c>
+      <c r="F836" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G836" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="837" spans="3:7">
+      <c r="C837" s="6">
+        <v>15625</v>
+      </c>
+      <c r="D837" s="3">
+        <v>156</v>
+      </c>
+      <c r="E837" s="3">
+        <v>1</v>
+      </c>
+      <c r="F837" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G837" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15210,10 +15655,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -15228,10 +15673,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -15246,10 +15691,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -15264,10 +15709,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -15284,10 +15729,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -15382,10 +15827,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -214,25 +214,13 @@
     <t>#先锋139吉祥如意</t>
   </si>
   <si>
-    <t>#先锋141恭喜发财</t>
-  </si>
-  <si>
     <t>#先锋143湖光月色</t>
-  </si>
-  <si>
-    <t>#先锋145一统山河</t>
   </si>
   <si>
     <t>#先锋147紫禁之巅</t>
   </si>
   <si>
-    <t>#先锋148威震天下</t>
-  </si>
-  <si>
     <t>#先锋149春暖花开</t>
-  </si>
-  <si>
-    <t>#先锋150破晓之战</t>
   </si>
   <si>
     <t>#先锋151龙裔国度</t>
@@ -251,6 +239,9 @@
   </si>
   <si>
     <t>#先锋156龙翔九天</t>
+  </si>
+  <si>
+    <t>#先锋157神谕森林</t>
   </si>
   <si>
     <t>Center</t>
@@ -1278,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O837"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -9797,10 +9788,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>14101</v>
+        <v>14301</v>
       </c>
       <c r="D501" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9812,17 +9803,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20525</v>
+        <v>20575</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>14102</v>
+        <v>14302</v>
       </c>
       <c r="D502" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9834,15 +9825,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20526</v>
+        <v>20576</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>14103</v>
+        <v>14303</v>
       </c>
       <c r="D503" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9854,15 +9845,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20527</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>14104</v>
+        <v>14304</v>
       </c>
       <c r="D504" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9874,15 +9865,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20528</v>
+        <v>20578</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>14105</v>
+        <v>14305</v>
       </c>
       <c r="D505" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9896,10 +9887,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>14106</v>
+        <v>14306</v>
       </c>
       <c r="D506" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9913,10 +9904,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>14107</v>
+        <v>14307</v>
       </c>
       <c r="D507" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9930,10 +9921,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>14108</v>
+        <v>14308</v>
       </c>
       <c r="D508" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9947,10 +9938,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>14109</v>
+        <v>14309</v>
       </c>
       <c r="D509" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9964,10 +9955,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>14110</v>
+        <v>14310</v>
       </c>
       <c r="D510" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9981,10 +9972,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>14111</v>
+        <v>14311</v>
       </c>
       <c r="D511" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9998,10 +9989,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>14112</v>
+        <v>14312</v>
       </c>
       <c r="D512" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10015,10 +10006,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>14113</v>
+        <v>14313</v>
       </c>
       <c r="D513" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10032,10 +10023,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>14114</v>
+        <v>14314</v>
       </c>
       <c r="D514" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10049,10 +10040,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>14115</v>
+        <v>14315</v>
       </c>
       <c r="D515" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10066,10 +10057,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>14116</v>
+        <v>14316</v>
       </c>
       <c r="D516" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10083,10 +10074,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>14117</v>
+        <v>14317</v>
       </c>
       <c r="D517" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10100,10 +10091,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>14118</v>
+        <v>14318</v>
       </c>
       <c r="D518" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10117,10 +10108,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>14119</v>
+        <v>14319</v>
       </c>
       <c r="D519" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10134,10 +10125,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>14120</v>
+        <v>14320</v>
       </c>
       <c r="D520" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10151,10 +10142,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>14121</v>
+        <v>14321</v>
       </c>
       <c r="D521" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10168,10 +10159,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>14122</v>
+        <v>14322</v>
       </c>
       <c r="D522" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10185,10 +10176,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>14123</v>
+        <v>14323</v>
       </c>
       <c r="D523" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10202,10 +10193,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>14124</v>
+        <v>14324</v>
       </c>
       <c r="D524" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10219,10 +10210,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>14125</v>
+        <v>14325</v>
       </c>
       <c r="D525" s="3">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10239,10 +10230,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>14301</v>
+        <v>14701</v>
       </c>
       <c r="D527" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10254,17 +10245,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20575</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>14302</v>
+        <v>14702</v>
       </c>
       <c r="D528" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10276,15 +10267,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20576</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>14303</v>
+        <v>14703</v>
       </c>
       <c r="D529" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10296,15 +10287,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20577</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>14304</v>
+        <v>14704</v>
       </c>
       <c r="D530" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10316,15 +10307,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20578</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>14305</v>
+        <v>14705</v>
       </c>
       <c r="D531" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10338,10 +10329,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>14306</v>
+        <v>14706</v>
       </c>
       <c r="D532" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10355,10 +10346,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>14307</v>
+        <v>14707</v>
       </c>
       <c r="D533" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10372,10 +10363,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>14308</v>
+        <v>14708</v>
       </c>
       <c r="D534" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10389,10 +10380,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>14309</v>
+        <v>14709</v>
       </c>
       <c r="D535" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10406,10 +10397,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>14310</v>
+        <v>14710</v>
       </c>
       <c r="D536" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10423,10 +10414,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>14311</v>
+        <v>14711</v>
       </c>
       <c r="D537" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10440,10 +10431,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>14312</v>
+        <v>14712</v>
       </c>
       <c r="D538" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10457,10 +10448,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>14313</v>
+        <v>14713</v>
       </c>
       <c r="D539" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10474,10 +10465,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>14314</v>
+        <v>14714</v>
       </c>
       <c r="D540" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10491,10 +10482,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>14315</v>
+        <v>14715</v>
       </c>
       <c r="D541" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10508,10 +10499,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>14316</v>
+        <v>14716</v>
       </c>
       <c r="D542" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10525,10 +10516,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>14317</v>
+        <v>14717</v>
       </c>
       <c r="D543" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10542,10 +10533,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>14318</v>
+        <v>14718</v>
       </c>
       <c r="D544" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10559,10 +10550,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>14319</v>
+        <v>14719</v>
       </c>
       <c r="D545" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10576,10 +10567,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>14320</v>
+        <v>14720</v>
       </c>
       <c r="D546" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10593,10 +10584,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>14321</v>
+        <v>14721</v>
       </c>
       <c r="D547" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10610,10 +10601,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>14322</v>
+        <v>14722</v>
       </c>
       <c r="D548" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10627,10 +10618,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>14323</v>
+        <v>14723</v>
       </c>
       <c r="D549" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10644,10 +10635,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>14324</v>
+        <v>14724</v>
       </c>
       <c r="D550" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10661,10 +10652,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>14325</v>
+        <v>14725</v>
       </c>
       <c r="D551" s="3">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10681,10 +10672,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>14501</v>
+        <v>14901</v>
       </c>
       <c r="D553" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10696,17 +10687,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20375</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>14502</v>
+        <v>14902</v>
       </c>
       <c r="D554" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10718,15 +10709,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20376</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>14503</v>
+        <v>14903</v>
       </c>
       <c r="D555" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10738,15 +10729,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20377</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>14504</v>
+        <v>14904</v>
       </c>
       <c r="D556" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10758,15 +10749,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20378</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>14505</v>
+        <v>14905</v>
       </c>
       <c r="D557" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10780,10 +10771,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>14506</v>
+        <v>14906</v>
       </c>
       <c r="D558" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10797,10 +10788,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>14507</v>
+        <v>14907</v>
       </c>
       <c r="D559" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10814,10 +10805,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>14508</v>
+        <v>14908</v>
       </c>
       <c r="D560" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10831,10 +10822,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>14509</v>
+        <v>14909</v>
       </c>
       <c r="D561" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10848,10 +10839,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>14510</v>
+        <v>14910</v>
       </c>
       <c r="D562" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10865,10 +10856,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>14511</v>
+        <v>14911</v>
       </c>
       <c r="D563" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10882,10 +10873,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>14512</v>
+        <v>14912</v>
       </c>
       <c r="D564" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10899,10 +10890,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>14513</v>
+        <v>14913</v>
       </c>
       <c r="D565" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10916,10 +10907,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>14514</v>
+        <v>14914</v>
       </c>
       <c r="D566" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10933,10 +10924,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>14515</v>
+        <v>14915</v>
       </c>
       <c r="D567" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10950,10 +10941,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>14516</v>
+        <v>14916</v>
       </c>
       <c r="D568" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10967,10 +10958,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>14517</v>
+        <v>14917</v>
       </c>
       <c r="D569" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10984,10 +10975,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>14518</v>
+        <v>14918</v>
       </c>
       <c r="D570" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -11001,10 +10992,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>14519</v>
+        <v>14919</v>
       </c>
       <c r="D571" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11018,10 +11009,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>14520</v>
+        <v>14920</v>
       </c>
       <c r="D572" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11035,10 +11026,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>14521</v>
+        <v>14921</v>
       </c>
       <c r="D573" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11052,10 +11043,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>14522</v>
+        <v>14922</v>
       </c>
       <c r="D574" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11069,10 +11060,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>14523</v>
+        <v>14923</v>
       </c>
       <c r="D575" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11086,10 +11077,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>14524</v>
+        <v>14924</v>
       </c>
       <c r="D576" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11103,10 +11094,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>14525</v>
+        <v>14925</v>
       </c>
       <c r="D577" s="3">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11123,10 +11114,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>14701</v>
+        <v>15101</v>
       </c>
       <c r="D579" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11138,17 +11129,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20495</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>14702</v>
+        <v>15102</v>
       </c>
       <c r="D580" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11160,15 +11151,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20496</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>14703</v>
+        <v>15103</v>
       </c>
       <c r="D581" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11180,15 +11171,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20497</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>14704</v>
+        <v>15104</v>
       </c>
       <c r="D582" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11200,15 +11191,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20498</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>14705</v>
+        <v>15105</v>
       </c>
       <c r="D583" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11222,10 +11213,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>14706</v>
+        <v>15106</v>
       </c>
       <c r="D584" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11239,10 +11230,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>14707</v>
+        <v>15107</v>
       </c>
       <c r="D585" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11256,10 +11247,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>14708</v>
+        <v>15108</v>
       </c>
       <c r="D586" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11273,10 +11264,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>14709</v>
+        <v>15109</v>
       </c>
       <c r="D587" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11290,10 +11281,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>14710</v>
+        <v>15110</v>
       </c>
       <c r="D588" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11307,10 +11298,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>14711</v>
+        <v>15111</v>
       </c>
       <c r="D589" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11324,10 +11315,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>14712</v>
+        <v>15112</v>
       </c>
       <c r="D590" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11341,10 +11332,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>14713</v>
+        <v>15113</v>
       </c>
       <c r="D591" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11358,10 +11349,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>14714</v>
+        <v>15114</v>
       </c>
       <c r="D592" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11375,10 +11366,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>14715</v>
+        <v>15115</v>
       </c>
       <c r="D593" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11392,10 +11383,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>14716</v>
+        <v>15116</v>
       </c>
       <c r="D594" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11409,10 +11400,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>14717</v>
+        <v>15117</v>
       </c>
       <c r="D595" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11426,10 +11417,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>14718</v>
+        <v>15118</v>
       </c>
       <c r="D596" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11443,10 +11434,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>14719</v>
+        <v>15119</v>
       </c>
       <c r="D597" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11460,10 +11451,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>14720</v>
+        <v>15120</v>
       </c>
       <c r="D598" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11477,10 +11468,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>14721</v>
+        <v>15121</v>
       </c>
       <c r="D599" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11494,10 +11485,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>14722</v>
+        <v>15122</v>
       </c>
       <c r="D600" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11511,10 +11502,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>14723</v>
+        <v>15123</v>
       </c>
       <c r="D601" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11528,10 +11519,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>14724</v>
+        <v>15124</v>
       </c>
       <c r="D602" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11545,10 +11536,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>14725</v>
+        <v>15125</v>
       </c>
       <c r="D603" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11565,10 +11556,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>14801</v>
+        <v>15201</v>
       </c>
       <c r="D605" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11580,17 +11571,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20585</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>14802</v>
+        <v>15202</v>
       </c>
       <c r="D606" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11602,15 +11593,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20586</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>14803</v>
+        <v>15203</v>
       </c>
       <c r="D607" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11622,15 +11613,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20587</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>14804</v>
+        <v>15204</v>
       </c>
       <c r="D608" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11642,15 +11633,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20588</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>14805</v>
+        <v>15205</v>
       </c>
       <c r="D609" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11664,10 +11655,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>14806</v>
+        <v>15206</v>
       </c>
       <c r="D610" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11681,10 +11672,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>14807</v>
+        <v>15207</v>
       </c>
       <c r="D611" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11698,10 +11689,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>14808</v>
+        <v>15208</v>
       </c>
       <c r="D612" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11715,10 +11706,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>14809</v>
+        <v>15209</v>
       </c>
       <c r="D613" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11732,10 +11723,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>14810</v>
+        <v>15210</v>
       </c>
       <c r="D614" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11749,10 +11740,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>14811</v>
+        <v>15211</v>
       </c>
       <c r="D615" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11766,10 +11757,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>14812</v>
+        <v>15212</v>
       </c>
       <c r="D616" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11783,10 +11774,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>14813</v>
+        <v>15213</v>
       </c>
       <c r="D617" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11800,10 +11791,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>14814</v>
+        <v>15214</v>
       </c>
       <c r="D618" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11817,10 +11808,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>14815</v>
+        <v>15215</v>
       </c>
       <c r="D619" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11834,10 +11825,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>14816</v>
+        <v>15216</v>
       </c>
       <c r="D620" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11851,10 +11842,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>14817</v>
+        <v>15217</v>
       </c>
       <c r="D621" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11868,10 +11859,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>14818</v>
+        <v>15218</v>
       </c>
       <c r="D622" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11885,10 +11876,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>14819</v>
+        <v>15219</v>
       </c>
       <c r="D623" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11902,10 +11893,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>14820</v>
+        <v>15220</v>
       </c>
       <c r="D624" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11919,10 +11910,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>14821</v>
+        <v>15221</v>
       </c>
       <c r="D625" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11936,10 +11927,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>14822</v>
+        <v>15222</v>
       </c>
       <c r="D626" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11953,10 +11944,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>14823</v>
+        <v>15223</v>
       </c>
       <c r="D627" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11970,10 +11961,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>14824</v>
+        <v>15224</v>
       </c>
       <c r="D628" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11987,10 +11978,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>14825</v>
+        <v>15225</v>
       </c>
       <c r="D629" s="3">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -12007,10 +11998,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>14901</v>
+        <v>15301</v>
       </c>
       <c r="D631" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12022,17 +12013,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20445</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>14902</v>
+        <v>15302</v>
       </c>
       <c r="D632" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12044,15 +12035,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20446</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>14903</v>
+        <v>15303</v>
       </c>
       <c r="D633" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12064,15 +12055,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20447</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>14904</v>
+        <v>15304</v>
       </c>
       <c r="D634" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12084,15 +12075,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20448</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>14905</v>
+        <v>15305</v>
       </c>
       <c r="D635" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12106,10 +12097,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>14906</v>
+        <v>15306</v>
       </c>
       <c r="D636" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12123,10 +12114,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>14907</v>
+        <v>15307</v>
       </c>
       <c r="D637" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12140,10 +12131,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>14908</v>
+        <v>15308</v>
       </c>
       <c r="D638" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12157,10 +12148,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>14909</v>
+        <v>15309</v>
       </c>
       <c r="D639" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12174,10 +12165,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>14910</v>
+        <v>15310</v>
       </c>
       <c r="D640" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12191,10 +12182,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>14911</v>
+        <v>15311</v>
       </c>
       <c r="D641" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12208,10 +12199,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>14912</v>
+        <v>15312</v>
       </c>
       <c r="D642" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12225,10 +12216,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>14913</v>
+        <v>15313</v>
       </c>
       <c r="D643" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12242,10 +12233,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>14914</v>
+        <v>15314</v>
       </c>
       <c r="D644" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12259,10 +12250,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>14915</v>
+        <v>15315</v>
       </c>
       <c r="D645" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12276,10 +12267,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>14916</v>
+        <v>15316</v>
       </c>
       <c r="D646" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12293,10 +12284,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>14917</v>
+        <v>15317</v>
       </c>
       <c r="D647" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12310,10 +12301,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>14918</v>
+        <v>15318</v>
       </c>
       <c r="D648" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12327,10 +12318,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>14919</v>
+        <v>15319</v>
       </c>
       <c r="D649" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12344,10 +12335,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>14920</v>
+        <v>15320</v>
       </c>
       <c r="D650" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12361,10 +12352,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>14921</v>
+        <v>15321</v>
       </c>
       <c r="D651" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12378,10 +12369,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>14922</v>
+        <v>15322</v>
       </c>
       <c r="D652" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12395,10 +12386,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>14923</v>
+        <v>15323</v>
       </c>
       <c r="D653" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12412,10 +12403,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>14924</v>
+        <v>15324</v>
       </c>
       <c r="D654" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12429,10 +12420,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>14925</v>
+        <v>15325</v>
       </c>
       <c r="D655" s="3">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12449,10 +12440,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>15001</v>
+        <v>15401</v>
       </c>
       <c r="D657" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12464,17 +12455,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20505</v>
+        <v>20595</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>15002</v>
+        <v>15402</v>
       </c>
       <c r="D658" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12486,15 +12477,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20506</v>
+        <v>20596</v>
       </c>
     </row>
     <row r="659" spans="3:8">
       <c r="C659" s="6">
-        <v>15003</v>
+        <v>15403</v>
       </c>
       <c r="D659" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12506,15 +12497,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20507</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="660" spans="3:8">
       <c r="C660" s="6">
-        <v>15004</v>
+        <v>15404</v>
       </c>
       <c r="D660" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12526,15 +12517,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20508</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="661" spans="3:7">
       <c r="C661" s="6">
-        <v>15005</v>
+        <v>15405</v>
       </c>
       <c r="D661" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12548,10 +12539,10 @@
     </row>
     <row r="662" spans="3:7">
       <c r="C662" s="6">
-        <v>15006</v>
+        <v>15406</v>
       </c>
       <c r="D662" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12565,10 +12556,10 @@
     </row>
     <row r="663" spans="3:7">
       <c r="C663" s="6">
-        <v>15007</v>
+        <v>15407</v>
       </c>
       <c r="D663" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12582,10 +12573,10 @@
     </row>
     <row r="664" spans="3:7">
       <c r="C664" s="6">
-        <v>15008</v>
+        <v>15408</v>
       </c>
       <c r="D664" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12599,10 +12590,10 @@
     </row>
     <row r="665" spans="3:7">
       <c r="C665" s="6">
-        <v>15009</v>
+        <v>15409</v>
       </c>
       <c r="D665" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12616,10 +12607,10 @@
     </row>
     <row r="666" spans="3:7">
       <c r="C666" s="6">
-        <v>15010</v>
+        <v>15410</v>
       </c>
       <c r="D666" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12633,10 +12624,10 @@
     </row>
     <row r="667" spans="3:7">
       <c r="C667" s="6">
-        <v>15011</v>
+        <v>15411</v>
       </c>
       <c r="D667" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12650,10 +12641,10 @@
     </row>
     <row r="668" spans="3:7">
       <c r="C668" s="6">
-        <v>15012</v>
+        <v>15412</v>
       </c>
       <c r="D668" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12667,10 +12658,10 @@
     </row>
     <row r="669" spans="3:7">
       <c r="C669" s="6">
-        <v>15013</v>
+        <v>15413</v>
       </c>
       <c r="D669" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12684,10 +12675,10 @@
     </row>
     <row r="670" spans="3:7">
       <c r="C670" s="6">
-        <v>15014</v>
+        <v>15414</v>
       </c>
       <c r="D670" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12701,10 +12692,10 @@
     </row>
     <row r="671" spans="3:7">
       <c r="C671" s="6">
-        <v>15015</v>
+        <v>15415</v>
       </c>
       <c r="D671" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12718,10 +12709,10 @@
     </row>
     <row r="672" spans="3:7">
       <c r="C672" s="6">
-        <v>15016</v>
+        <v>15416</v>
       </c>
       <c r="D672" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12735,10 +12726,10 @@
     </row>
     <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>15017</v>
+        <v>15417</v>
       </c>
       <c r="D673" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12752,10 +12743,10 @@
     </row>
     <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>15018</v>
+        <v>15418</v>
       </c>
       <c r="D674" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12769,10 +12760,10 @@
     </row>
     <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>15019</v>
+        <v>15419</v>
       </c>
       <c r="D675" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12786,10 +12777,10 @@
     </row>
     <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>15020</v>
+        <v>15420</v>
       </c>
       <c r="D676" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12803,10 +12794,10 @@
     </row>
     <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>15021</v>
+        <v>15421</v>
       </c>
       <c r="D677" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12820,10 +12811,10 @@
     </row>
     <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>15022</v>
+        <v>15422</v>
       </c>
       <c r="D678" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12837,10 +12828,10 @@
     </row>
     <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>15023</v>
+        <v>15423</v>
       </c>
       <c r="D679" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12854,10 +12845,10 @@
     </row>
     <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>15024</v>
+        <v>15424</v>
       </c>
       <c r="D680" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12871,10 +12862,10 @@
     </row>
     <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>15025</v>
+        <v>15425</v>
       </c>
       <c r="D681" s="3">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12891,10 +12882,10 @@
         <v>68</v>
       </c>
       <c r="C683" s="6">
-        <v>15101</v>
+        <v>15501</v>
       </c>
       <c r="D683" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E683" s="5">
         <v>1</v>
@@ -12906,17 +12897,17 @@
         <v>15</v>
       </c>
       <c r="H683" s="3">
-        <v>20415</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="684" spans="1:8">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="6">
-        <v>15102</v>
+        <v>15502</v>
       </c>
       <c r="D684" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E684" s="5">
         <v>1</v>
@@ -12928,15 +12919,15 @@
         <v>16</v>
       </c>
       <c r="H684" s="3">
-        <v>20416</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="685" spans="3:8">
       <c r="C685" s="6">
-        <v>15103</v>
+        <v>15503</v>
       </c>
       <c r="D685" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E685" s="5">
         <v>1</v>
@@ -12948,15 +12939,15 @@
         <v>18</v>
       </c>
       <c r="H685" s="3">
-        <v>20417</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="686" spans="3:8">
       <c r="C686" s="6">
-        <v>15104</v>
+        <v>15504</v>
       </c>
       <c r="D686" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E686" s="5">
         <v>1</v>
@@ -12968,15 +12959,15 @@
         <v>19</v>
       </c>
       <c r="H686" s="3">
-        <v>20418</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="687" spans="3:7">
       <c r="C687" s="6">
-        <v>15105</v>
+        <v>15505</v>
       </c>
       <c r="D687" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E687" s="3">
         <v>1</v>
@@ -12990,10 +12981,10 @@
     </row>
     <row r="688" spans="3:7">
       <c r="C688" s="6">
-        <v>15106</v>
+        <v>15506</v>
       </c>
       <c r="D688" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E688" s="5">
         <v>1</v>
@@ -13007,10 +12998,10 @@
     </row>
     <row r="689" spans="3:7">
       <c r="C689" s="6">
-        <v>15107</v>
+        <v>15507</v>
       </c>
       <c r="D689" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E689" s="5">
         <v>1</v>
@@ -13024,10 +13015,10 @@
     </row>
     <row r="690" spans="3:7">
       <c r="C690" s="6">
-        <v>15108</v>
+        <v>15508</v>
       </c>
       <c r="D690" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E690" s="5">
         <v>1</v>
@@ -13041,10 +13032,10 @@
     </row>
     <row r="691" spans="3:7">
       <c r="C691" s="6">
-        <v>15109</v>
+        <v>15509</v>
       </c>
       <c r="D691" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E691" s="3">
         <v>1</v>
@@ -13058,10 +13049,10 @@
     </row>
     <row r="692" spans="3:7">
       <c r="C692" s="6">
-        <v>15110</v>
+        <v>15510</v>
       </c>
       <c r="D692" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E692" s="5">
         <v>1</v>
@@ -13075,10 +13066,10 @@
     </row>
     <row r="693" spans="3:7">
       <c r="C693" s="6">
-        <v>15111</v>
+        <v>15511</v>
       </c>
       <c r="D693" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E693" s="5">
         <v>1</v>
@@ -13092,10 +13083,10 @@
     </row>
     <row r="694" spans="3:7">
       <c r="C694" s="6">
-        <v>15112</v>
+        <v>15512</v>
       </c>
       <c r="D694" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E694" s="5">
         <v>1</v>
@@ -13109,10 +13100,10 @@
     </row>
     <row r="695" spans="3:7">
       <c r="C695" s="6">
-        <v>15113</v>
+        <v>15513</v>
       </c>
       <c r="D695" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E695" s="3">
         <v>1</v>
@@ -13126,10 +13117,10 @@
     </row>
     <row r="696" spans="3:7">
       <c r="C696" s="6">
-        <v>15114</v>
+        <v>15514</v>
       </c>
       <c r="D696" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E696" s="5">
         <v>1</v>
@@ -13143,10 +13134,10 @@
     </row>
     <row r="697" spans="3:7">
       <c r="C697" s="6">
-        <v>15115</v>
+        <v>15515</v>
       </c>
       <c r="D697" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E697" s="5">
         <v>1</v>
@@ -13160,10 +13151,10 @@
     </row>
     <row r="698" spans="3:7">
       <c r="C698" s="6">
-        <v>15116</v>
+        <v>15516</v>
       </c>
       <c r="D698" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E698" s="5">
         <v>1</v>
@@ -13177,10 +13168,10 @@
     </row>
     <row r="699" spans="3:7">
       <c r="C699" s="6">
-        <v>15117</v>
+        <v>15517</v>
       </c>
       <c r="D699" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E699" s="3">
         <v>1</v>
@@ -13194,10 +13185,10 @@
     </row>
     <row r="700" spans="3:7">
       <c r="C700" s="6">
-        <v>15118</v>
+        <v>15518</v>
       </c>
       <c r="D700" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E700" s="5">
         <v>1</v>
@@ -13211,10 +13202,10 @@
     </row>
     <row r="701" spans="3:7">
       <c r="C701" s="6">
-        <v>15119</v>
+        <v>15519</v>
       </c>
       <c r="D701" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E701" s="5">
         <v>1</v>
@@ -13228,10 +13219,10 @@
     </row>
     <row r="702" spans="3:7">
       <c r="C702" s="6">
-        <v>15120</v>
+        <v>15520</v>
       </c>
       <c r="D702" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E702" s="5">
         <v>1</v>
@@ -13245,10 +13236,10 @@
     </row>
     <row r="703" spans="3:7">
       <c r="C703" s="6">
-        <v>15121</v>
+        <v>15521</v>
       </c>
       <c r="D703" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E703" s="3">
         <v>1</v>
@@ -13262,10 +13253,10 @@
     </row>
     <row r="704" spans="3:7">
       <c r="C704" s="6">
-        <v>15122</v>
+        <v>15522</v>
       </c>
       <c r="D704" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E704" s="5">
         <v>1</v>
@@ -13279,10 +13270,10 @@
     </row>
     <row r="705" spans="3:7">
       <c r="C705" s="6">
-        <v>15123</v>
+        <v>15523</v>
       </c>
       <c r="D705" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E705" s="5">
         <v>1</v>
@@ -13296,10 +13287,10 @@
     </row>
     <row r="706" spans="3:7">
       <c r="C706" s="6">
-        <v>15124</v>
+        <v>15524</v>
       </c>
       <c r="D706" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E706" s="5">
         <v>1</v>
@@ -13313,10 +13304,10 @@
     </row>
     <row r="707" spans="3:7">
       <c r="C707" s="6">
-        <v>15125</v>
+        <v>15525</v>
       </c>
       <c r="D707" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E707" s="3">
         <v>1</v>
@@ -13333,10 +13324,10 @@
         <v>69</v>
       </c>
       <c r="C709" s="6">
-        <v>15201</v>
+        <v>15601</v>
       </c>
       <c r="D709" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E709" s="5">
         <v>1</v>
@@ -13348,17 +13339,17 @@
         <v>15</v>
       </c>
       <c r="H709" s="3">
-        <v>20455</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="710" spans="1:8">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="6">
-        <v>15202</v>
+        <v>15602</v>
       </c>
       <c r="D710" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E710" s="5">
         <v>1</v>
@@ -13370,15 +13361,15 @@
         <v>16</v>
       </c>
       <c r="H710" s="3">
-        <v>20456</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="711" spans="3:8">
       <c r="C711" s="6">
-        <v>15203</v>
+        <v>15603</v>
       </c>
       <c r="D711" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E711" s="5">
         <v>1</v>
@@ -13390,15 +13381,15 @@
         <v>18</v>
       </c>
       <c r="H711" s="3">
-        <v>20457</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="712" spans="3:8">
       <c r="C712" s="6">
-        <v>15204</v>
+        <v>15604</v>
       </c>
       <c r="D712" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E712" s="5">
         <v>1</v>
@@ -13410,15 +13401,15 @@
         <v>19</v>
       </c>
       <c r="H712" s="3">
-        <v>20458</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="713" spans="3:7">
       <c r="C713" s="6">
-        <v>15205</v>
+        <v>15605</v>
       </c>
       <c r="D713" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E713" s="3">
         <v>1</v>
@@ -13432,10 +13423,10 @@
     </row>
     <row r="714" spans="3:7">
       <c r="C714" s="6">
-        <v>15206</v>
+        <v>15606</v>
       </c>
       <c r="D714" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E714" s="5">
         <v>1</v>
@@ -13449,10 +13440,10 @@
     </row>
     <row r="715" spans="3:7">
       <c r="C715" s="6">
-        <v>15207</v>
+        <v>15607</v>
       </c>
       <c r="D715" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E715" s="5">
         <v>1</v>
@@ -13466,10 +13457,10 @@
     </row>
     <row r="716" spans="3:7">
       <c r="C716" s="6">
-        <v>15208</v>
+        <v>15608</v>
       </c>
       <c r="D716" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E716" s="5">
         <v>1</v>
@@ -13483,10 +13474,10 @@
     </row>
     <row r="717" spans="3:7">
       <c r="C717" s="6">
-        <v>15209</v>
+        <v>15609</v>
       </c>
       <c r="D717" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E717" s="3">
         <v>1</v>
@@ -13500,10 +13491,10 @@
     </row>
     <row r="718" spans="3:7">
       <c r="C718" s="6">
-        <v>15210</v>
+        <v>15610</v>
       </c>
       <c r="D718" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E718" s="5">
         <v>1</v>
@@ -13517,10 +13508,10 @@
     </row>
     <row r="719" spans="3:7">
       <c r="C719" s="6">
-        <v>15211</v>
+        <v>15611</v>
       </c>
       <c r="D719" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E719" s="5">
         <v>1</v>
@@ -13534,10 +13525,10 @@
     </row>
     <row r="720" spans="3:7">
       <c r="C720" s="6">
-        <v>15212</v>
+        <v>15612</v>
       </c>
       <c r="D720" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E720" s="5">
         <v>1</v>
@@ -13551,10 +13542,10 @@
     </row>
     <row r="721" spans="3:7">
       <c r="C721" s="6">
-        <v>15213</v>
+        <v>15613</v>
       </c>
       <c r="D721" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E721" s="3">
         <v>1</v>
@@ -13568,10 +13559,10 @@
     </row>
     <row r="722" spans="3:7">
       <c r="C722" s="6">
-        <v>15214</v>
+        <v>15614</v>
       </c>
       <c r="D722" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E722" s="5">
         <v>1</v>
@@ -13585,10 +13576,10 @@
     </row>
     <row r="723" spans="3:7">
       <c r="C723" s="6">
-        <v>15215</v>
+        <v>15615</v>
       </c>
       <c r="D723" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E723" s="5">
         <v>1</v>
@@ -13602,10 +13593,10 @@
     </row>
     <row r="724" spans="3:7">
       <c r="C724" s="6">
-        <v>15216</v>
+        <v>15616</v>
       </c>
       <c r="D724" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E724" s="5">
         <v>1</v>
@@ -13619,10 +13610,10 @@
     </row>
     <row r="725" spans="3:7">
       <c r="C725" s="6">
-        <v>15217</v>
+        <v>15617</v>
       </c>
       <c r="D725" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E725" s="3">
         <v>1</v>
@@ -13636,10 +13627,10 @@
     </row>
     <row r="726" spans="3:7">
       <c r="C726" s="6">
-        <v>15218</v>
+        <v>15618</v>
       </c>
       <c r="D726" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E726" s="5">
         <v>1</v>
@@ -13653,10 +13644,10 @@
     </row>
     <row r="727" spans="3:7">
       <c r="C727" s="6">
-        <v>15219</v>
+        <v>15619</v>
       </c>
       <c r="D727" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E727" s="5">
         <v>1</v>
@@ -13670,10 +13661,10 @@
     </row>
     <row r="728" spans="3:7">
       <c r="C728" s="6">
-        <v>15220</v>
+        <v>15620</v>
       </c>
       <c r="D728" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E728" s="5">
         <v>1</v>
@@ -13687,10 +13678,10 @@
     </row>
     <row r="729" spans="3:7">
       <c r="C729" s="6">
-        <v>15221</v>
+        <v>15621</v>
       </c>
       <c r="D729" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E729" s="3">
         <v>1</v>
@@ -13704,10 +13695,10 @@
     </row>
     <row r="730" spans="3:7">
       <c r="C730" s="6">
-        <v>15222</v>
+        <v>15622</v>
       </c>
       <c r="D730" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E730" s="5">
         <v>1</v>
@@ -13721,10 +13712,10 @@
     </row>
     <row r="731" spans="3:7">
       <c r="C731" s="6">
-        <v>15223</v>
+        <v>15623</v>
       </c>
       <c r="D731" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E731" s="5">
         <v>1</v>
@@ -13738,10 +13729,10 @@
     </row>
     <row r="732" spans="3:7">
       <c r="C732" s="6">
-        <v>15224</v>
+        <v>15624</v>
       </c>
       <c r="D732" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E732" s="5">
         <v>1</v>
@@ -13755,10 +13746,10 @@
     </row>
     <row r="733" spans="3:7">
       <c r="C733" s="6">
-        <v>15225</v>
+        <v>15625</v>
       </c>
       <c r="D733" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E733" s="3">
         <v>1</v>
@@ -13775,10 +13766,10 @@
         <v>70</v>
       </c>
       <c r="C735" s="6">
-        <v>15301</v>
+        <v>15701</v>
       </c>
       <c r="D735" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E735" s="5">
         <v>1</v>
@@ -13790,17 +13781,17 @@
         <v>15</v>
       </c>
       <c r="H735" s="3">
-        <v>20565</v>
+        <v>20645</v>
       </c>
     </row>
     <row r="736" spans="1:8">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="6">
-        <v>15302</v>
+        <v>15702</v>
       </c>
       <c r="D736" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E736" s="5">
         <v>1</v>
@@ -13812,15 +13803,15 @@
         <v>16</v>
       </c>
       <c r="H736" s="3">
-        <v>20566</v>
+        <v>20646</v>
       </c>
     </row>
     <row r="737" spans="3:8">
       <c r="C737" s="6">
-        <v>15303</v>
+        <v>15703</v>
       </c>
       <c r="D737" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E737" s="5">
         <v>1</v>
@@ -13832,15 +13823,15 @@
         <v>18</v>
       </c>
       <c r="H737" s="3">
-        <v>20567</v>
+        <v>20647</v>
       </c>
     </row>
     <row r="738" spans="3:8">
       <c r="C738" s="6">
-        <v>15304</v>
+        <v>15704</v>
       </c>
       <c r="D738" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E738" s="5">
         <v>1</v>
@@ -13852,15 +13843,15 @@
         <v>19</v>
       </c>
       <c r="H738" s="3">
-        <v>20568</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="739" spans="3:7">
       <c r="C739" s="6">
-        <v>15305</v>
+        <v>15705</v>
       </c>
       <c r="D739" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E739" s="3">
         <v>1</v>
@@ -13874,10 +13865,10 @@
     </row>
     <row r="740" spans="3:7">
       <c r="C740" s="6">
-        <v>15306</v>
+        <v>15706</v>
       </c>
       <c r="D740" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E740" s="5">
         <v>1</v>
@@ -13891,10 +13882,10 @@
     </row>
     <row r="741" spans="3:7">
       <c r="C741" s="6">
-        <v>15307</v>
+        <v>15707</v>
       </c>
       <c r="D741" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E741" s="5">
         <v>1</v>
@@ -13908,10 +13899,10 @@
     </row>
     <row r="742" spans="3:7">
       <c r="C742" s="6">
-        <v>15308</v>
+        <v>15708</v>
       </c>
       <c r="D742" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E742" s="5">
         <v>1</v>
@@ -13925,10 +13916,10 @@
     </row>
     <row r="743" spans="3:7">
       <c r="C743" s="6">
-        <v>15309</v>
+        <v>15709</v>
       </c>
       <c r="D743" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E743" s="3">
         <v>1</v>
@@ -13942,10 +13933,10 @@
     </row>
     <row r="744" spans="3:7">
       <c r="C744" s="6">
-        <v>15310</v>
+        <v>15710</v>
       </c>
       <c r="D744" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E744" s="5">
         <v>1</v>
@@ -13959,10 +13950,10 @@
     </row>
     <row r="745" spans="3:7">
       <c r="C745" s="6">
-        <v>15311</v>
+        <v>15711</v>
       </c>
       <c r="D745" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E745" s="5">
         <v>1</v>
@@ -13976,10 +13967,10 @@
     </row>
     <row r="746" spans="3:7">
       <c r="C746" s="6">
-        <v>15312</v>
+        <v>15712</v>
       </c>
       <c r="D746" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E746" s="5">
         <v>1</v>
@@ -13993,10 +13984,10 @@
     </row>
     <row r="747" spans="3:7">
       <c r="C747" s="6">
-        <v>15313</v>
+        <v>15713</v>
       </c>
       <c r="D747" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E747" s="3">
         <v>1</v>
@@ -14010,10 +14001,10 @@
     </row>
     <row r="748" spans="3:7">
       <c r="C748" s="6">
-        <v>15314</v>
+        <v>15714</v>
       </c>
       <c r="D748" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E748" s="5">
         <v>1</v>
@@ -14027,10 +14018,10 @@
     </row>
     <row r="749" spans="3:7">
       <c r="C749" s="6">
-        <v>15315</v>
+        <v>15715</v>
       </c>
       <c r="D749" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E749" s="5">
         <v>1</v>
@@ -14044,10 +14035,10 @@
     </row>
     <row r="750" spans="3:7">
       <c r="C750" s="6">
-        <v>15316</v>
+        <v>15716</v>
       </c>
       <c r="D750" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E750" s="5">
         <v>1</v>
@@ -14061,10 +14052,10 @@
     </row>
     <row r="751" spans="3:7">
       <c r="C751" s="6">
-        <v>15317</v>
+        <v>15717</v>
       </c>
       <c r="D751" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E751" s="3">
         <v>1</v>
@@ -14078,10 +14069,10 @@
     </row>
     <row r="752" spans="3:7">
       <c r="C752" s="6">
-        <v>15318</v>
+        <v>15718</v>
       </c>
       <c r="D752" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E752" s="5">
         <v>1</v>
@@ -14095,10 +14086,10 @@
     </row>
     <row r="753" spans="3:7">
       <c r="C753" s="6">
-        <v>15319</v>
+        <v>15719</v>
       </c>
       <c r="D753" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E753" s="5">
         <v>1</v>
@@ -14112,10 +14103,10 @@
     </row>
     <row r="754" spans="3:7">
       <c r="C754" s="6">
-        <v>15320</v>
+        <v>15720</v>
       </c>
       <c r="D754" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E754" s="5">
         <v>1</v>
@@ -14129,10 +14120,10 @@
     </row>
     <row r="755" spans="3:7">
       <c r="C755" s="6">
-        <v>15321</v>
+        <v>15721</v>
       </c>
       <c r="D755" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E755" s="3">
         <v>1</v>
@@ -14146,10 +14137,10 @@
     </row>
     <row r="756" spans="3:7">
       <c r="C756" s="6">
-        <v>15322</v>
+        <v>15722</v>
       </c>
       <c r="D756" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E756" s="5">
         <v>1</v>
@@ -14163,10 +14154,10 @@
     </row>
     <row r="757" spans="3:7">
       <c r="C757" s="6">
-        <v>15323</v>
+        <v>15723</v>
       </c>
       <c r="D757" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E757" s="5">
         <v>1</v>
@@ -14180,10 +14171,10 @@
     </row>
     <row r="758" spans="3:7">
       <c r="C758" s="6">
-        <v>15324</v>
+        <v>15724</v>
       </c>
       <c r="D758" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E758" s="5">
         <v>1</v>
@@ -14197,10 +14188,10 @@
     </row>
     <row r="759" spans="3:7">
       <c r="C759" s="6">
-        <v>15325</v>
+        <v>15725</v>
       </c>
       <c r="D759" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E759" s="3">
         <v>1</v>
@@ -14209,1332 +14200,6 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="761" spans="1:8">
-      <c r="A761" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C761" s="6">
-        <v>15401</v>
-      </c>
-      <c r="D761" s="3">
-        <v>154</v>
-      </c>
-      <c r="E761" s="5">
-        <v>1</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H761" s="3">
-        <v>20595</v>
-      </c>
-    </row>
-    <row r="762" spans="1:8">
-      <c r="A762" s="1"/>
-      <c r="B762" s="1"/>
-      <c r="C762" s="6">
-        <v>15402</v>
-      </c>
-      <c r="D762" s="3">
-        <v>154</v>
-      </c>
-      <c r="E762" s="5">
-        <v>1</v>
-      </c>
-      <c r="F762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H762" s="3">
-        <v>20596</v>
-      </c>
-    </row>
-    <row r="763" spans="3:8">
-      <c r="C763" s="6">
-        <v>15403</v>
-      </c>
-      <c r="D763" s="3">
-        <v>154</v>
-      </c>
-      <c r="E763" s="5">
-        <v>1</v>
-      </c>
-      <c r="F763" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G763" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H763" s="3">
-        <v>20597</v>
-      </c>
-    </row>
-    <row r="764" spans="3:8">
-      <c r="C764" s="6">
-        <v>15404</v>
-      </c>
-      <c r="D764" s="3">
-        <v>154</v>
-      </c>
-      <c r="E764" s="5">
-        <v>1</v>
-      </c>
-      <c r="F764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H764" s="3">
-        <v>20598</v>
-      </c>
-    </row>
-    <row r="765" spans="3:7">
-      <c r="C765" s="6">
-        <v>15405</v>
-      </c>
-      <c r="D765" s="3">
-        <v>154</v>
-      </c>
-      <c r="E765" s="3">
-        <v>1</v>
-      </c>
-      <c r="F765" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G765" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="766" spans="3:7">
-      <c r="C766" s="6">
-        <v>15406</v>
-      </c>
-      <c r="D766" s="3">
-        <v>154</v>
-      </c>
-      <c r="E766" s="5">
-        <v>1</v>
-      </c>
-      <c r="F766" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G766" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="767" spans="3:7">
-      <c r="C767" s="6">
-        <v>15407</v>
-      </c>
-      <c r="D767" s="3">
-        <v>154</v>
-      </c>
-      <c r="E767" s="5">
-        <v>1</v>
-      </c>
-      <c r="F767" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G767" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="768" spans="3:7">
-      <c r="C768" s="6">
-        <v>15408</v>
-      </c>
-      <c r="D768" s="3">
-        <v>154</v>
-      </c>
-      <c r="E768" s="5">
-        <v>1</v>
-      </c>
-      <c r="F768" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G768" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="769" spans="3:7">
-      <c r="C769" s="6">
-        <v>15409</v>
-      </c>
-      <c r="D769" s="3">
-        <v>154</v>
-      </c>
-      <c r="E769" s="3">
-        <v>1</v>
-      </c>
-      <c r="F769" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G769" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="770" spans="3:7">
-      <c r="C770" s="6">
-        <v>15410</v>
-      </c>
-      <c r="D770" s="3">
-        <v>154</v>
-      </c>
-      <c r="E770" s="5">
-        <v>1</v>
-      </c>
-      <c r="F770" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G770" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="771" spans="3:7">
-      <c r="C771" s="6">
-        <v>15411</v>
-      </c>
-      <c r="D771" s="3">
-        <v>154</v>
-      </c>
-      <c r="E771" s="5">
-        <v>1</v>
-      </c>
-      <c r="F771" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G771" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="772" spans="3:7">
-      <c r="C772" s="6">
-        <v>15412</v>
-      </c>
-      <c r="D772" s="3">
-        <v>154</v>
-      </c>
-      <c r="E772" s="5">
-        <v>1</v>
-      </c>
-      <c r="F772" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G772" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="773" spans="3:7">
-      <c r="C773" s="6">
-        <v>15413</v>
-      </c>
-      <c r="D773" s="3">
-        <v>154</v>
-      </c>
-      <c r="E773" s="3">
-        <v>1</v>
-      </c>
-      <c r="F773" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G773" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="774" spans="3:7">
-      <c r="C774" s="6">
-        <v>15414</v>
-      </c>
-      <c r="D774" s="3">
-        <v>154</v>
-      </c>
-      <c r="E774" s="5">
-        <v>1</v>
-      </c>
-      <c r="F774" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G774" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="775" spans="3:7">
-      <c r="C775" s="6">
-        <v>15415</v>
-      </c>
-      <c r="D775" s="3">
-        <v>154</v>
-      </c>
-      <c r="E775" s="5">
-        <v>1</v>
-      </c>
-      <c r="F775" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G775" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="776" spans="3:7">
-      <c r="C776" s="6">
-        <v>15416</v>
-      </c>
-      <c r="D776" s="3">
-        <v>154</v>
-      </c>
-      <c r="E776" s="5">
-        <v>1</v>
-      </c>
-      <c r="F776" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G776" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="777" spans="3:7">
-      <c r="C777" s="6">
-        <v>15417</v>
-      </c>
-      <c r="D777" s="3">
-        <v>154</v>
-      </c>
-      <c r="E777" s="3">
-        <v>1</v>
-      </c>
-      <c r="F777" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G777" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="778" spans="3:7">
-      <c r="C778" s="6">
-        <v>15418</v>
-      </c>
-      <c r="D778" s="3">
-        <v>154</v>
-      </c>
-      <c r="E778" s="5">
-        <v>1</v>
-      </c>
-      <c r="F778" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G778" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="779" spans="3:7">
-      <c r="C779" s="6">
-        <v>15419</v>
-      </c>
-      <c r="D779" s="3">
-        <v>154</v>
-      </c>
-      <c r="E779" s="5">
-        <v>1</v>
-      </c>
-      <c r="F779" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G779" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="780" spans="3:7">
-      <c r="C780" s="6">
-        <v>15420</v>
-      </c>
-      <c r="D780" s="3">
-        <v>154</v>
-      </c>
-      <c r="E780" s="5">
-        <v>1</v>
-      </c>
-      <c r="F780" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G780" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="781" spans="3:7">
-      <c r="C781" s="6">
-        <v>15421</v>
-      </c>
-      <c r="D781" s="3">
-        <v>154</v>
-      </c>
-      <c r="E781" s="3">
-        <v>1</v>
-      </c>
-      <c r="F781" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G781" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="782" spans="3:7">
-      <c r="C782" s="6">
-        <v>15422</v>
-      </c>
-      <c r="D782" s="3">
-        <v>154</v>
-      </c>
-      <c r="E782" s="5">
-        <v>1</v>
-      </c>
-      <c r="F782" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G782" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="783" spans="3:7">
-      <c r="C783" s="6">
-        <v>15423</v>
-      </c>
-      <c r="D783" s="3">
-        <v>154</v>
-      </c>
-      <c r="E783" s="5">
-        <v>1</v>
-      </c>
-      <c r="F783" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G783" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="784" spans="3:7">
-      <c r="C784" s="6">
-        <v>15424</v>
-      </c>
-      <c r="D784" s="3">
-        <v>154</v>
-      </c>
-      <c r="E784" s="5">
-        <v>1</v>
-      </c>
-      <c r="F784" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G784" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="785" spans="3:7">
-      <c r="C785" s="6">
-        <v>15425</v>
-      </c>
-      <c r="D785" s="3">
-        <v>154</v>
-      </c>
-      <c r="E785" s="3">
-        <v>1</v>
-      </c>
-      <c r="F785" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G785" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="787" spans="1:8">
-      <c r="A787" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C787" s="6">
-        <v>15501</v>
-      </c>
-      <c r="D787" s="3">
-        <v>155</v>
-      </c>
-      <c r="E787" s="5">
-        <v>1</v>
-      </c>
-      <c r="F787" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G787" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H787" s="3">
-        <v>20605</v>
-      </c>
-    </row>
-    <row r="788" spans="1:8">
-      <c r="A788" s="1"/>
-      <c r="B788" s="1"/>
-      <c r="C788" s="6">
-        <v>15502</v>
-      </c>
-      <c r="D788" s="3">
-        <v>155</v>
-      </c>
-      <c r="E788" s="5">
-        <v>1</v>
-      </c>
-      <c r="F788" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G788" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H788" s="3">
-        <v>20606</v>
-      </c>
-    </row>
-    <row r="789" spans="3:8">
-      <c r="C789" s="6">
-        <v>15503</v>
-      </c>
-      <c r="D789" s="3">
-        <v>155</v>
-      </c>
-      <c r="E789" s="5">
-        <v>1</v>
-      </c>
-      <c r="F789" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G789" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H789" s="3">
-        <v>20607</v>
-      </c>
-    </row>
-    <row r="790" spans="3:8">
-      <c r="C790" s="6">
-        <v>15504</v>
-      </c>
-      <c r="D790" s="3">
-        <v>155</v>
-      </c>
-      <c r="E790" s="5">
-        <v>1</v>
-      </c>
-      <c r="F790" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G790" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H790" s="3">
-        <v>20608</v>
-      </c>
-    </row>
-    <row r="791" spans="3:7">
-      <c r="C791" s="6">
-        <v>15505</v>
-      </c>
-      <c r="D791" s="3">
-        <v>155</v>
-      </c>
-      <c r="E791" s="3">
-        <v>1</v>
-      </c>
-      <c r="F791" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G791" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="792" spans="3:7">
-      <c r="C792" s="6">
-        <v>15506</v>
-      </c>
-      <c r="D792" s="3">
-        <v>155</v>
-      </c>
-      <c r="E792" s="5">
-        <v>1</v>
-      </c>
-      <c r="F792" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G792" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="793" spans="3:7">
-      <c r="C793" s="6">
-        <v>15507</v>
-      </c>
-      <c r="D793" s="3">
-        <v>155</v>
-      </c>
-      <c r="E793" s="5">
-        <v>1</v>
-      </c>
-      <c r="F793" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G793" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="794" spans="3:7">
-      <c r="C794" s="6">
-        <v>15508</v>
-      </c>
-      <c r="D794" s="3">
-        <v>155</v>
-      </c>
-      <c r="E794" s="5">
-        <v>1</v>
-      </c>
-      <c r="F794" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G794" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="795" spans="3:7">
-      <c r="C795" s="6">
-        <v>15509</v>
-      </c>
-      <c r="D795" s="3">
-        <v>155</v>
-      </c>
-      <c r="E795" s="3">
-        <v>1</v>
-      </c>
-      <c r="F795" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G795" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="796" spans="3:7">
-      <c r="C796" s="6">
-        <v>15510</v>
-      </c>
-      <c r="D796" s="3">
-        <v>155</v>
-      </c>
-      <c r="E796" s="5">
-        <v>1</v>
-      </c>
-      <c r="F796" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G796" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="797" spans="3:7">
-      <c r="C797" s="6">
-        <v>15511</v>
-      </c>
-      <c r="D797" s="3">
-        <v>155</v>
-      </c>
-      <c r="E797" s="5">
-        <v>1</v>
-      </c>
-      <c r="F797" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G797" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="798" spans="3:7">
-      <c r="C798" s="6">
-        <v>15512</v>
-      </c>
-      <c r="D798" s="3">
-        <v>155</v>
-      </c>
-      <c r="E798" s="5">
-        <v>1</v>
-      </c>
-      <c r="F798" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G798" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="799" spans="3:7">
-      <c r="C799" s="6">
-        <v>15513</v>
-      </c>
-      <c r="D799" s="3">
-        <v>155</v>
-      </c>
-      <c r="E799" s="3">
-        <v>1</v>
-      </c>
-      <c r="F799" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G799" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="800" spans="3:7">
-      <c r="C800" s="6">
-        <v>15514</v>
-      </c>
-      <c r="D800" s="3">
-        <v>155</v>
-      </c>
-      <c r="E800" s="5">
-        <v>1</v>
-      </c>
-      <c r="F800" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G800" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="801" spans="3:7">
-      <c r="C801" s="6">
-        <v>15515</v>
-      </c>
-      <c r="D801" s="3">
-        <v>155</v>
-      </c>
-      <c r="E801" s="5">
-        <v>1</v>
-      </c>
-      <c r="F801" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G801" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="802" spans="3:7">
-      <c r="C802" s="6">
-        <v>15516</v>
-      </c>
-      <c r="D802" s="3">
-        <v>155</v>
-      </c>
-      <c r="E802" s="5">
-        <v>1</v>
-      </c>
-      <c r="F802" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G802" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="803" spans="3:7">
-      <c r="C803" s="6">
-        <v>15517</v>
-      </c>
-      <c r="D803" s="3">
-        <v>155</v>
-      </c>
-      <c r="E803" s="3">
-        <v>1</v>
-      </c>
-      <c r="F803" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G803" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="804" spans="3:7">
-      <c r="C804" s="6">
-        <v>15518</v>
-      </c>
-      <c r="D804" s="3">
-        <v>155</v>
-      </c>
-      <c r="E804" s="5">
-        <v>1</v>
-      </c>
-      <c r="F804" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G804" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="805" spans="3:7">
-      <c r="C805" s="6">
-        <v>15519</v>
-      </c>
-      <c r="D805" s="3">
-        <v>155</v>
-      </c>
-      <c r="E805" s="5">
-        <v>1</v>
-      </c>
-      <c r="F805" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G805" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="806" spans="3:7">
-      <c r="C806" s="6">
-        <v>15520</v>
-      </c>
-      <c r="D806" s="3">
-        <v>155</v>
-      </c>
-      <c r="E806" s="5">
-        <v>1</v>
-      </c>
-      <c r="F806" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G806" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="807" spans="3:7">
-      <c r="C807" s="6">
-        <v>15521</v>
-      </c>
-      <c r="D807" s="3">
-        <v>155</v>
-      </c>
-      <c r="E807" s="3">
-        <v>1</v>
-      </c>
-      <c r="F807" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G807" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="808" spans="3:7">
-      <c r="C808" s="6">
-        <v>15522</v>
-      </c>
-      <c r="D808" s="3">
-        <v>155</v>
-      </c>
-      <c r="E808" s="5">
-        <v>1</v>
-      </c>
-      <c r="F808" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G808" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="809" spans="3:7">
-      <c r="C809" s="6">
-        <v>15523</v>
-      </c>
-      <c r="D809" s="3">
-        <v>155</v>
-      </c>
-      <c r="E809" s="5">
-        <v>1</v>
-      </c>
-      <c r="F809" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G809" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="810" spans="3:7">
-      <c r="C810" s="6">
-        <v>15524</v>
-      </c>
-      <c r="D810" s="3">
-        <v>155</v>
-      </c>
-      <c r="E810" s="5">
-        <v>1</v>
-      </c>
-      <c r="F810" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G810" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="811" spans="3:7">
-      <c r="C811" s="6">
-        <v>15525</v>
-      </c>
-      <c r="D811" s="3">
-        <v>155</v>
-      </c>
-      <c r="E811" s="3">
-        <v>1</v>
-      </c>
-      <c r="F811" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G811" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="813" spans="1:8">
-      <c r="A813" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C813" s="6">
-        <v>15601</v>
-      </c>
-      <c r="D813" s="3">
-        <v>156</v>
-      </c>
-      <c r="E813" s="5">
-        <v>1</v>
-      </c>
-      <c r="F813" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G813" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H813" s="3">
-        <v>20615</v>
-      </c>
-    </row>
-    <row r="814" spans="1:8">
-      <c r="A814" s="1"/>
-      <c r="B814" s="1"/>
-      <c r="C814" s="6">
-        <v>15602</v>
-      </c>
-      <c r="D814" s="3">
-        <v>156</v>
-      </c>
-      <c r="E814" s="5">
-        <v>1</v>
-      </c>
-      <c r="F814" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G814" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H814" s="3">
-        <v>20616</v>
-      </c>
-    </row>
-    <row r="815" spans="3:8">
-      <c r="C815" s="6">
-        <v>15603</v>
-      </c>
-      <c r="D815" s="3">
-        <v>156</v>
-      </c>
-      <c r="E815" s="5">
-        <v>1</v>
-      </c>
-      <c r="F815" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G815" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H815" s="3">
-        <v>20617</v>
-      </c>
-    </row>
-    <row r="816" spans="3:8">
-      <c r="C816" s="6">
-        <v>15604</v>
-      </c>
-      <c r="D816" s="3">
-        <v>156</v>
-      </c>
-      <c r="E816" s="5">
-        <v>1</v>
-      </c>
-      <c r="F816" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G816" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H816" s="3">
-        <v>20618</v>
-      </c>
-    </row>
-    <row r="817" spans="3:7">
-      <c r="C817" s="6">
-        <v>15605</v>
-      </c>
-      <c r="D817" s="3">
-        <v>156</v>
-      </c>
-      <c r="E817" s="3">
-        <v>1</v>
-      </c>
-      <c r="F817" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G817" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="818" spans="3:7">
-      <c r="C818" s="6">
-        <v>15606</v>
-      </c>
-      <c r="D818" s="3">
-        <v>156</v>
-      </c>
-      <c r="E818" s="5">
-        <v>1</v>
-      </c>
-      <c r="F818" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G818" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="819" spans="3:7">
-      <c r="C819" s="6">
-        <v>15607</v>
-      </c>
-      <c r="D819" s="3">
-        <v>156</v>
-      </c>
-      <c r="E819" s="5">
-        <v>1</v>
-      </c>
-      <c r="F819" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G819" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="820" spans="3:7">
-      <c r="C820" s="6">
-        <v>15608</v>
-      </c>
-      <c r="D820" s="3">
-        <v>156</v>
-      </c>
-      <c r="E820" s="5">
-        <v>1</v>
-      </c>
-      <c r="F820" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G820" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="821" spans="3:7">
-      <c r="C821" s="6">
-        <v>15609</v>
-      </c>
-      <c r="D821" s="3">
-        <v>156</v>
-      </c>
-      <c r="E821" s="3">
-        <v>1</v>
-      </c>
-      <c r="F821" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G821" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="822" spans="3:7">
-      <c r="C822" s="6">
-        <v>15610</v>
-      </c>
-      <c r="D822" s="3">
-        <v>156</v>
-      </c>
-      <c r="E822" s="5">
-        <v>1</v>
-      </c>
-      <c r="F822" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G822" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="823" spans="3:7">
-      <c r="C823" s="6">
-        <v>15611</v>
-      </c>
-      <c r="D823" s="3">
-        <v>156</v>
-      </c>
-      <c r="E823" s="5">
-        <v>1</v>
-      </c>
-      <c r="F823" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G823" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="824" spans="3:7">
-      <c r="C824" s="6">
-        <v>15612</v>
-      </c>
-      <c r="D824" s="3">
-        <v>156</v>
-      </c>
-      <c r="E824" s="5">
-        <v>1</v>
-      </c>
-      <c r="F824" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G824" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="825" spans="3:7">
-      <c r="C825" s="6">
-        <v>15613</v>
-      </c>
-      <c r="D825" s="3">
-        <v>156</v>
-      </c>
-      <c r="E825" s="3">
-        <v>1</v>
-      </c>
-      <c r="F825" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G825" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="826" spans="3:7">
-      <c r="C826" s="6">
-        <v>15614</v>
-      </c>
-      <c r="D826" s="3">
-        <v>156</v>
-      </c>
-      <c r="E826" s="5">
-        <v>1</v>
-      </c>
-      <c r="F826" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G826" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="827" spans="3:7">
-      <c r="C827" s="6">
-        <v>15615</v>
-      </c>
-      <c r="D827" s="3">
-        <v>156</v>
-      </c>
-      <c r="E827" s="5">
-        <v>1</v>
-      </c>
-      <c r="F827" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G827" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="828" spans="3:7">
-      <c r="C828" s="6">
-        <v>15616</v>
-      </c>
-      <c r="D828" s="3">
-        <v>156</v>
-      </c>
-      <c r="E828" s="5">
-        <v>1</v>
-      </c>
-      <c r="F828" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G828" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="829" spans="3:7">
-      <c r="C829" s="6">
-        <v>15617</v>
-      </c>
-      <c r="D829" s="3">
-        <v>156</v>
-      </c>
-      <c r="E829" s="3">
-        <v>1</v>
-      </c>
-      <c r="F829" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G829" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="830" spans="3:7">
-      <c r="C830" s="6">
-        <v>15618</v>
-      </c>
-      <c r="D830" s="3">
-        <v>156</v>
-      </c>
-      <c r="E830" s="5">
-        <v>1</v>
-      </c>
-      <c r="F830" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G830" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="831" spans="3:7">
-      <c r="C831" s="6">
-        <v>15619</v>
-      </c>
-      <c r="D831" s="3">
-        <v>156</v>
-      </c>
-      <c r="E831" s="5">
-        <v>1</v>
-      </c>
-      <c r="F831" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G831" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="832" spans="3:7">
-      <c r="C832" s="6">
-        <v>15620</v>
-      </c>
-      <c r="D832" s="3">
-        <v>156</v>
-      </c>
-      <c r="E832" s="5">
-        <v>1</v>
-      </c>
-      <c r="F832" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G832" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="833" spans="3:7">
-      <c r="C833" s="6">
-        <v>15621</v>
-      </c>
-      <c r="D833" s="3">
-        <v>156</v>
-      </c>
-      <c r="E833" s="3">
-        <v>1</v>
-      </c>
-      <c r="F833" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G833" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="834" spans="3:7">
-      <c r="C834" s="6">
-        <v>15622</v>
-      </c>
-      <c r="D834" s="3">
-        <v>156</v>
-      </c>
-      <c r="E834" s="5">
-        <v>1</v>
-      </c>
-      <c r="F834" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G834" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="835" spans="3:7">
-      <c r="C835" s="6">
-        <v>15623</v>
-      </c>
-      <c r="D835" s="3">
-        <v>156</v>
-      </c>
-      <c r="E835" s="5">
-        <v>1</v>
-      </c>
-      <c r="F835" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G835" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="836" spans="3:7">
-      <c r="C836" s="6">
-        <v>15624</v>
-      </c>
-      <c r="D836" s="3">
-        <v>156</v>
-      </c>
-      <c r="E836" s="5">
-        <v>1</v>
-      </c>
-      <c r="F836" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G836" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="837" spans="3:7">
-      <c r="C837" s="6">
-        <v>15625</v>
-      </c>
-      <c r="D837" s="3">
-        <v>156</v>
-      </c>
-      <c r="E837" s="3">
-        <v>1</v>
-      </c>
-      <c r="F837" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G837" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15655,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -15673,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -15691,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -15709,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -15729,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -15827,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -190,13 +190,7 @@
     <t>#先锋89区诗情画意</t>
   </si>
   <si>
-    <t>#先锋97区萤火森林</t>
-  </si>
-  <si>
     <t>#先锋105区锦绣山河</t>
-  </si>
-  <si>
-    <t>#先锋113区纵横驰骋</t>
   </si>
   <si>
     <t>#先锋121区太平盛世</t>
@@ -206,9 +200,6 @@
   </si>
   <si>
     <t>#先锋131花满楼</t>
-  </si>
-  <si>
-    <t>#先锋135永恒之境</t>
   </si>
   <si>
     <t>#先锋139吉祥如意</t>
@@ -226,9 +217,6 @@
     <t>#先锋151龙裔国度</t>
   </si>
   <si>
-    <t>#先锋152秘境森林</t>
-  </si>
-  <si>
     <t>#先锋153荣耀之路</t>
   </si>
   <si>
@@ -242,6 +230,9 @@
   </si>
   <si>
     <t>#先锋157神谕森林</t>
+  </si>
+  <si>
+    <t>#先锋158泰坦神殿</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -6252,10 +6243,10 @@
         <v>53</v>
       </c>
       <c r="C293" s="6">
-        <v>9701</v>
+        <v>10501</v>
       </c>
       <c r="D293" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E293" s="5">
         <v>1</v>
@@ -6267,17 +6258,17 @@
         <v>15</v>
       </c>
       <c r="H293" s="3">
-        <v>20555</v>
+        <v>20395</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="6">
-        <v>9702</v>
+        <v>10502</v>
       </c>
       <c r="D294" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E294" s="5">
         <v>1</v>
@@ -6289,15 +6280,15 @@
         <v>16</v>
       </c>
       <c r="H294" s="3">
-        <v>20556</v>
+        <v>20396</v>
       </c>
     </row>
     <row r="295" spans="3:8">
       <c r="C295" s="6">
-        <v>9703</v>
+        <v>10503</v>
       </c>
       <c r="D295" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E295" s="5">
         <v>1</v>
@@ -6309,15 +6300,15 @@
         <v>18</v>
       </c>
       <c r="H295" s="3">
-        <v>20557</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="296" spans="3:8">
       <c r="C296" s="6">
-        <v>9704</v>
+        <v>10504</v>
       </c>
       <c r="D296" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E296" s="3">
         <v>1</v>
@@ -6329,15 +6320,15 @@
         <v>19</v>
       </c>
       <c r="H296" s="3">
-        <v>20558</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="297" spans="3:7">
       <c r="C297" s="6">
-        <v>9705</v>
+        <v>10505</v>
       </c>
       <c r="D297" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E297" s="5">
         <v>1</v>
@@ -6351,10 +6342,10 @@
     </row>
     <row r="298" spans="3:7">
       <c r="C298" s="6">
-        <v>9706</v>
+        <v>10506</v>
       </c>
       <c r="D298" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E298" s="5">
         <v>1</v>
@@ -6368,10 +6359,10 @@
     </row>
     <row r="299" spans="3:7">
       <c r="C299" s="6">
-        <v>9707</v>
+        <v>10507</v>
       </c>
       <c r="D299" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E299" s="5">
         <v>1</v>
@@ -6385,10 +6376,10 @@
     </row>
     <row r="300" spans="3:7">
       <c r="C300" s="6">
-        <v>9708</v>
+        <v>10508</v>
       </c>
       <c r="D300" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E300" s="3">
         <v>1</v>
@@ -6402,10 +6393,10 @@
     </row>
     <row r="301" spans="3:7">
       <c r="C301" s="6">
-        <v>9709</v>
+        <v>10509</v>
       </c>
       <c r="D301" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E301" s="5">
         <v>1</v>
@@ -6419,10 +6410,10 @@
     </row>
     <row r="302" spans="3:7">
       <c r="C302" s="6">
-        <v>9710</v>
+        <v>10510</v>
       </c>
       <c r="D302" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E302" s="5">
         <v>1</v>
@@ -6436,10 +6427,10 @@
     </row>
     <row r="303" spans="3:7">
       <c r="C303" s="6">
-        <v>9711</v>
+        <v>10511</v>
       </c>
       <c r="D303" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E303" s="5">
         <v>1</v>
@@ -6453,10 +6444,10 @@
     </row>
     <row r="304" spans="3:7">
       <c r="C304" s="6">
-        <v>9712</v>
+        <v>10512</v>
       </c>
       <c r="D304" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E304" s="3">
         <v>1</v>
@@ -6470,10 +6461,10 @@
     </row>
     <row r="305" spans="3:7">
       <c r="C305" s="6">
-        <v>9713</v>
+        <v>10513</v>
       </c>
       <c r="D305" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E305" s="5">
         <v>1</v>
@@ -6487,10 +6478,10 @@
     </row>
     <row r="306" spans="3:7">
       <c r="C306" s="6">
-        <v>9714</v>
+        <v>10514</v>
       </c>
       <c r="D306" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E306" s="5">
         <v>1</v>
@@ -6504,10 +6495,10 @@
     </row>
     <row r="307" spans="3:7">
       <c r="C307" s="6">
-        <v>9715</v>
+        <v>10515</v>
       </c>
       <c r="D307" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E307" s="5">
         <v>1</v>
@@ -6521,10 +6512,10 @@
     </row>
     <row r="308" spans="3:7">
       <c r="C308" s="6">
-        <v>9716</v>
+        <v>10516</v>
       </c>
       <c r="D308" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E308" s="3">
         <v>1</v>
@@ -6538,10 +6529,10 @@
     </row>
     <row r="309" spans="3:7">
       <c r="C309" s="6">
-        <v>9717</v>
+        <v>10517</v>
       </c>
       <c r="D309" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E309" s="5">
         <v>1</v>
@@ -6555,10 +6546,10 @@
     </row>
     <row r="310" spans="3:7">
       <c r="C310" s="6">
-        <v>9718</v>
+        <v>10518</v>
       </c>
       <c r="D310" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E310" s="5">
         <v>1</v>
@@ -6572,10 +6563,10 @@
     </row>
     <row r="311" spans="3:7">
       <c r="C311" s="6">
-        <v>9719</v>
+        <v>10519</v>
       </c>
       <c r="D311" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E311" s="5">
         <v>1</v>
@@ -6589,10 +6580,10 @@
     </row>
     <row r="312" spans="3:7">
       <c r="C312" s="6">
-        <v>9720</v>
+        <v>10520</v>
       </c>
       <c r="D312" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E312" s="3">
         <v>1</v>
@@ -6606,10 +6597,10 @@
     </row>
     <row r="313" spans="3:7">
       <c r="C313" s="6">
-        <v>9721</v>
+        <v>10521</v>
       </c>
       <c r="D313" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E313" s="5">
         <v>1</v>
@@ -6623,10 +6614,10 @@
     </row>
     <row r="314" spans="3:7">
       <c r="C314" s="6">
-        <v>9722</v>
+        <v>10522</v>
       </c>
       <c r="D314" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E314" s="5">
         <v>1</v>
@@ -6640,10 +6631,10 @@
     </row>
     <row r="315" spans="3:7">
       <c r="C315" s="6">
-        <v>9723</v>
+        <v>10523</v>
       </c>
       <c r="D315" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E315" s="5">
         <v>1</v>
@@ -6657,10 +6648,10 @@
     </row>
     <row r="316" spans="3:7">
       <c r="C316" s="6">
-        <v>9724</v>
+        <v>10524</v>
       </c>
       <c r="D316" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E316" s="3">
         <v>1</v>
@@ -6674,10 +6665,10 @@
     </row>
     <row r="317" spans="3:7">
       <c r="C317" s="6">
-        <v>9725</v>
+        <v>10525</v>
       </c>
       <c r="D317" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="E317" s="5">
         <v>1</v>
@@ -6694,10 +6685,10 @@
         <v>54</v>
       </c>
       <c r="C319" s="6">
-        <v>10501</v>
+        <v>12101</v>
       </c>
       <c r="D319" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E319" s="5">
         <v>1</v>
@@ -6709,17 +6700,17 @@
         <v>15</v>
       </c>
       <c r="H319" s="3">
-        <v>20395</v>
+        <v>20465</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="6">
-        <v>10502</v>
+        <v>12102</v>
       </c>
       <c r="D320" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E320" s="5">
         <v>1</v>
@@ -6731,15 +6722,15 @@
         <v>16</v>
       </c>
       <c r="H320" s="3">
-        <v>20396</v>
+        <v>20466</v>
       </c>
     </row>
     <row r="321" spans="3:8">
       <c r="C321" s="6">
-        <v>10503</v>
+        <v>12103</v>
       </c>
       <c r="D321" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E321" s="5">
         <v>1</v>
@@ -6751,15 +6742,15 @@
         <v>18</v>
       </c>
       <c r="H321" s="3">
-        <v>20397</v>
+        <v>20467</v>
       </c>
     </row>
     <row r="322" spans="3:8">
       <c r="C322" s="6">
-        <v>10504</v>
+        <v>12104</v>
       </c>
       <c r="D322" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E322" s="3">
         <v>1</v>
@@ -6771,15 +6762,15 @@
         <v>19</v>
       </c>
       <c r="H322" s="3">
-        <v>20398</v>
+        <v>20468</v>
       </c>
     </row>
     <row r="323" spans="3:7">
       <c r="C323" s="6">
-        <v>10505</v>
+        <v>12105</v>
       </c>
       <c r="D323" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E323" s="5">
         <v>1</v>
@@ -6793,10 +6784,10 @@
     </row>
     <row r="324" spans="3:7">
       <c r="C324" s="6">
-        <v>10506</v>
+        <v>12106</v>
       </c>
       <c r="D324" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E324" s="5">
         <v>1</v>
@@ -6810,10 +6801,10 @@
     </row>
     <row r="325" spans="3:7">
       <c r="C325" s="6">
-        <v>10507</v>
+        <v>12107</v>
       </c>
       <c r="D325" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E325" s="5">
         <v>1</v>
@@ -6827,10 +6818,10 @@
     </row>
     <row r="326" spans="3:7">
       <c r="C326" s="6">
-        <v>10508</v>
+        <v>12108</v>
       </c>
       <c r="D326" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E326" s="3">
         <v>1</v>
@@ -6844,10 +6835,10 @@
     </row>
     <row r="327" spans="3:7">
       <c r="C327" s="6">
-        <v>10509</v>
+        <v>12109</v>
       </c>
       <c r="D327" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E327" s="5">
         <v>1</v>
@@ -6861,10 +6852,10 @@
     </row>
     <row r="328" spans="3:7">
       <c r="C328" s="6">
-        <v>10510</v>
+        <v>12110</v>
       </c>
       <c r="D328" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E328" s="5">
         <v>1</v>
@@ -6878,10 +6869,10 @@
     </row>
     <row r="329" spans="3:7">
       <c r="C329" s="6">
-        <v>10511</v>
+        <v>12111</v>
       </c>
       <c r="D329" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E329" s="5">
         <v>1</v>
@@ -6895,10 +6886,10 @@
     </row>
     <row r="330" spans="3:7">
       <c r="C330" s="6">
-        <v>10512</v>
+        <v>12112</v>
       </c>
       <c r="D330" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E330" s="3">
         <v>1</v>
@@ -6912,10 +6903,10 @@
     </row>
     <row r="331" spans="3:7">
       <c r="C331" s="6">
-        <v>10513</v>
+        <v>12113</v>
       </c>
       <c r="D331" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E331" s="5">
         <v>1</v>
@@ -6929,10 +6920,10 @@
     </row>
     <row r="332" spans="3:7">
       <c r="C332" s="6">
-        <v>10514</v>
+        <v>12114</v>
       </c>
       <c r="D332" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E332" s="5">
         <v>1</v>
@@ -6946,10 +6937,10 @@
     </row>
     <row r="333" spans="3:7">
       <c r="C333" s="6">
-        <v>10515</v>
+        <v>12115</v>
       </c>
       <c r="D333" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E333" s="5">
         <v>1</v>
@@ -6963,10 +6954,10 @@
     </row>
     <row r="334" spans="3:7">
       <c r="C334" s="6">
-        <v>10516</v>
+        <v>12116</v>
       </c>
       <c r="D334" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E334" s="3">
         <v>1</v>
@@ -6980,10 +6971,10 @@
     </row>
     <row r="335" spans="3:7">
       <c r="C335" s="6">
-        <v>10517</v>
+        <v>12117</v>
       </c>
       <c r="D335" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E335" s="5">
         <v>1</v>
@@ -6997,10 +6988,10 @@
     </row>
     <row r="336" spans="3:7">
       <c r="C336" s="6">
-        <v>10518</v>
+        <v>12118</v>
       </c>
       <c r="D336" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E336" s="5">
         <v>1</v>
@@ -7014,10 +7005,10 @@
     </row>
     <row r="337" spans="3:7">
       <c r="C337" s="6">
-        <v>10519</v>
+        <v>12119</v>
       </c>
       <c r="D337" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E337" s="5">
         <v>1</v>
@@ -7031,10 +7022,10 @@
     </row>
     <row r="338" spans="3:7">
       <c r="C338" s="6">
-        <v>10520</v>
+        <v>12120</v>
       </c>
       <c r="D338" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E338" s="3">
         <v>1</v>
@@ -7048,10 +7039,10 @@
     </row>
     <row r="339" spans="3:7">
       <c r="C339" s="6">
-        <v>10521</v>
+        <v>12121</v>
       </c>
       <c r="D339" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E339" s="5">
         <v>1</v>
@@ -7065,10 +7056,10 @@
     </row>
     <row r="340" spans="3:7">
       <c r="C340" s="6">
-        <v>10522</v>
+        <v>12122</v>
       </c>
       <c r="D340" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E340" s="5">
         <v>1</v>
@@ -7082,10 +7073,10 @@
     </row>
     <row r="341" spans="3:7">
       <c r="C341" s="6">
-        <v>10523</v>
+        <v>12123</v>
       </c>
       <c r="D341" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E341" s="5">
         <v>1</v>
@@ -7099,10 +7090,10 @@
     </row>
     <row r="342" spans="3:7">
       <c r="C342" s="6">
-        <v>10524</v>
+        <v>12124</v>
       </c>
       <c r="D342" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E342" s="3">
         <v>1</v>
@@ -7116,10 +7107,10 @@
     </row>
     <row r="343" spans="3:7">
       <c r="C343" s="6">
-        <v>10525</v>
+        <v>12125</v>
       </c>
       <c r="D343" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E343" s="5">
         <v>1</v>
@@ -7136,10 +7127,10 @@
         <v>55</v>
       </c>
       <c r="C345" s="6">
-        <v>11301</v>
+        <v>12801</v>
       </c>
       <c r="D345" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E345" s="5">
         <v>1</v>
@@ -7151,17 +7142,17 @@
         <v>15</v>
       </c>
       <c r="H345" s="3">
-        <v>20545</v>
+        <v>20425</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="6">
-        <v>11302</v>
+        <v>12802</v>
       </c>
       <c r="D346" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E346" s="5">
         <v>1</v>
@@ -7173,15 +7164,15 @@
         <v>16</v>
       </c>
       <c r="H346" s="3">
-        <v>20546</v>
+        <v>20426</v>
       </c>
     </row>
     <row r="347" spans="3:8">
       <c r="C347" s="6">
-        <v>11303</v>
+        <v>12803</v>
       </c>
       <c r="D347" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E347" s="5">
         <v>1</v>
@@ -7193,15 +7184,15 @@
         <v>18</v>
       </c>
       <c r="H347" s="3">
-        <v>20547</v>
+        <v>20427</v>
       </c>
     </row>
     <row r="348" spans="3:8">
       <c r="C348" s="6">
-        <v>11304</v>
+        <v>12804</v>
       </c>
       <c r="D348" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E348" s="3">
         <v>1</v>
@@ -7213,15 +7204,15 @@
         <v>19</v>
       </c>
       <c r="H348" s="3">
-        <v>20548</v>
+        <v>20428</v>
       </c>
     </row>
     <row r="349" spans="3:7">
       <c r="C349" s="6">
-        <v>11305</v>
+        <v>12805</v>
       </c>
       <c r="D349" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E349" s="5">
         <v>1</v>
@@ -7235,10 +7226,10 @@
     </row>
     <row r="350" spans="3:7">
       <c r="C350" s="6">
-        <v>11306</v>
+        <v>12806</v>
       </c>
       <c r="D350" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E350" s="5">
         <v>1</v>
@@ -7252,10 +7243,10 @@
     </row>
     <row r="351" spans="3:7">
       <c r="C351" s="6">
-        <v>11307</v>
+        <v>12807</v>
       </c>
       <c r="D351" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E351" s="5">
         <v>1</v>
@@ -7269,10 +7260,10 @@
     </row>
     <row r="352" spans="3:7">
       <c r="C352" s="6">
-        <v>11308</v>
+        <v>12808</v>
       </c>
       <c r="D352" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E352" s="3">
         <v>1</v>
@@ -7286,10 +7277,10 @@
     </row>
     <row r="353" spans="3:7">
       <c r="C353" s="6">
-        <v>11309</v>
+        <v>12809</v>
       </c>
       <c r="D353" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E353" s="5">
         <v>1</v>
@@ -7303,10 +7294,10 @@
     </row>
     <row r="354" spans="3:7">
       <c r="C354" s="6">
-        <v>11310</v>
+        <v>12810</v>
       </c>
       <c r="D354" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E354" s="5">
         <v>1</v>
@@ -7320,10 +7311,10 @@
     </row>
     <row r="355" spans="3:7">
       <c r="C355" s="6">
-        <v>11311</v>
+        <v>12811</v>
       </c>
       <c r="D355" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E355" s="5">
         <v>1</v>
@@ -7337,10 +7328,10 @@
     </row>
     <row r="356" spans="3:7">
       <c r="C356" s="6">
-        <v>11312</v>
+        <v>12812</v>
       </c>
       <c r="D356" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E356" s="3">
         <v>1</v>
@@ -7354,10 +7345,10 @@
     </row>
     <row r="357" spans="3:7">
       <c r="C357" s="6">
-        <v>11313</v>
+        <v>12813</v>
       </c>
       <c r="D357" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E357" s="5">
         <v>1</v>
@@ -7371,10 +7362,10 @@
     </row>
     <row r="358" spans="3:7">
       <c r="C358" s="6">
-        <v>11314</v>
+        <v>12814</v>
       </c>
       <c r="D358" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E358" s="5">
         <v>1</v>
@@ -7388,10 +7379,10 @@
     </row>
     <row r="359" spans="3:7">
       <c r="C359" s="6">
-        <v>11315</v>
+        <v>12815</v>
       </c>
       <c r="D359" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E359" s="5">
         <v>1</v>
@@ -7405,10 +7396,10 @@
     </row>
     <row r="360" spans="3:7">
       <c r="C360" s="6">
-        <v>11316</v>
+        <v>12816</v>
       </c>
       <c r="D360" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E360" s="3">
         <v>1</v>
@@ -7422,10 +7413,10 @@
     </row>
     <row r="361" spans="3:7">
       <c r="C361" s="6">
-        <v>11317</v>
+        <v>12817</v>
       </c>
       <c r="D361" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E361" s="5">
         <v>1</v>
@@ -7439,10 +7430,10 @@
     </row>
     <row r="362" spans="3:7">
       <c r="C362" s="6">
-        <v>11318</v>
+        <v>12818</v>
       </c>
       <c r="D362" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E362" s="5">
         <v>1</v>
@@ -7456,10 +7447,10 @@
     </row>
     <row r="363" spans="3:7">
       <c r="C363" s="6">
-        <v>11319</v>
+        <v>12819</v>
       </c>
       <c r="D363" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E363" s="5">
         <v>1</v>
@@ -7473,10 +7464,10 @@
     </row>
     <row r="364" spans="3:7">
       <c r="C364" s="6">
-        <v>11320</v>
+        <v>12820</v>
       </c>
       <c r="D364" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E364" s="3">
         <v>1</v>
@@ -7490,10 +7481,10 @@
     </row>
     <row r="365" spans="3:7">
       <c r="C365" s="6">
-        <v>11321</v>
+        <v>12821</v>
       </c>
       <c r="D365" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E365" s="5">
         <v>1</v>
@@ -7507,10 +7498,10 @@
     </row>
     <row r="366" spans="3:7">
       <c r="C366" s="6">
-        <v>11322</v>
+        <v>12822</v>
       </c>
       <c r="D366" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E366" s="5">
         <v>1</v>
@@ -7524,10 +7515,10 @@
     </row>
     <row r="367" spans="3:7">
       <c r="C367" s="6">
-        <v>11323</v>
+        <v>12823</v>
       </c>
       <c r="D367" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E367" s="5">
         <v>1</v>
@@ -7541,10 +7532,10 @@
     </row>
     <row r="368" spans="3:7">
       <c r="C368" s="6">
-        <v>11324</v>
+        <v>12824</v>
       </c>
       <c r="D368" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E368" s="3">
         <v>1</v>
@@ -7558,10 +7549,10 @@
     </row>
     <row r="369" spans="3:7">
       <c r="C369" s="6">
-        <v>11325</v>
+        <v>12825</v>
       </c>
       <c r="D369" s="3">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="E369" s="5">
         <v>1</v>
@@ -7578,10 +7569,10 @@
         <v>56</v>
       </c>
       <c r="C371" s="6">
-        <v>12101</v>
+        <v>13101</v>
       </c>
       <c r="D371" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E371" s="5">
         <v>1</v>
@@ -7593,17 +7584,17 @@
         <v>15</v>
       </c>
       <c r="H371" s="3">
-        <v>20465</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="6">
-        <v>12102</v>
+        <v>13102</v>
       </c>
       <c r="D372" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E372" s="5">
         <v>1</v>
@@ -7615,15 +7606,15 @@
         <v>16</v>
       </c>
       <c r="H372" s="3">
-        <v>20466</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="373" spans="3:8">
       <c r="C373" s="6">
-        <v>12103</v>
+        <v>13103</v>
       </c>
       <c r="D373" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E373" s="5">
         <v>1</v>
@@ -7635,17 +7626,17 @@
         <v>18</v>
       </c>
       <c r="H373" s="3">
-        <v>20467</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="374" spans="3:8">
       <c r="C374" s="6">
-        <v>12104</v>
+        <v>13104</v>
       </c>
       <c r="D374" s="3">
-        <v>121</v>
-      </c>
-      <c r="E374" s="3">
+        <v>131</v>
+      </c>
+      <c r="E374" s="5">
         <v>1</v>
       </c>
       <c r="F374" s="3" t="s">
@@ -7655,17 +7646,17 @@
         <v>19</v>
       </c>
       <c r="H374" s="3">
-        <v>20468</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="375" spans="3:7">
       <c r="C375" s="6">
-        <v>12105</v>
+        <v>13105</v>
       </c>
       <c r="D375" s="3">
-        <v>121</v>
-      </c>
-      <c r="E375" s="5">
+        <v>131</v>
+      </c>
+      <c r="E375" s="3">
         <v>1</v>
       </c>
       <c r="F375" s="3" t="s">
@@ -7677,10 +7668,10 @@
     </row>
     <row r="376" spans="3:7">
       <c r="C376" s="6">
-        <v>12106</v>
+        <v>13106</v>
       </c>
       <c r="D376" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E376" s="5">
         <v>1</v>
@@ -7694,10 +7685,10 @@
     </row>
     <row r="377" spans="3:7">
       <c r="C377" s="6">
-        <v>12107</v>
+        <v>13107</v>
       </c>
       <c r="D377" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E377" s="5">
         <v>1</v>
@@ -7711,12 +7702,12 @@
     </row>
     <row r="378" spans="3:7">
       <c r="C378" s="6">
-        <v>12108</v>
+        <v>13108</v>
       </c>
       <c r="D378" s="3">
-        <v>121</v>
-      </c>
-      <c r="E378" s="3">
+        <v>131</v>
+      </c>
+      <c r="E378" s="5">
         <v>1</v>
       </c>
       <c r="F378" s="3" t="s">
@@ -7728,12 +7719,12 @@
     </row>
     <row r="379" spans="3:7">
       <c r="C379" s="6">
-        <v>12109</v>
+        <v>13109</v>
       </c>
       <c r="D379" s="3">
-        <v>121</v>
-      </c>
-      <c r="E379" s="5">
+        <v>131</v>
+      </c>
+      <c r="E379" s="3">
         <v>1</v>
       </c>
       <c r="F379" s="3" t="s">
@@ -7745,10 +7736,10 @@
     </row>
     <row r="380" spans="3:7">
       <c r="C380" s="6">
-        <v>12110</v>
+        <v>13110</v>
       </c>
       <c r="D380" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E380" s="5">
         <v>1</v>
@@ -7762,10 +7753,10 @@
     </row>
     <row r="381" spans="3:7">
       <c r="C381" s="6">
-        <v>12111</v>
+        <v>13111</v>
       </c>
       <c r="D381" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E381" s="5">
         <v>1</v>
@@ -7779,12 +7770,12 @@
     </row>
     <row r="382" spans="3:7">
       <c r="C382" s="6">
-        <v>12112</v>
+        <v>13112</v>
       </c>
       <c r="D382" s="3">
-        <v>121</v>
-      </c>
-      <c r="E382" s="3">
+        <v>131</v>
+      </c>
+      <c r="E382" s="5">
         <v>1</v>
       </c>
       <c r="F382" s="3" t="s">
@@ -7796,12 +7787,12 @@
     </row>
     <row r="383" spans="3:7">
       <c r="C383" s="6">
-        <v>12113</v>
+        <v>13113</v>
       </c>
       <c r="D383" s="3">
-        <v>121</v>
-      </c>
-      <c r="E383" s="5">
+        <v>131</v>
+      </c>
+      <c r="E383" s="3">
         <v>1</v>
       </c>
       <c r="F383" s="3" t="s">
@@ -7813,10 +7804,10 @@
     </row>
     <row r="384" spans="3:7">
       <c r="C384" s="6">
-        <v>12114</v>
+        <v>13114</v>
       </c>
       <c r="D384" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E384" s="5">
         <v>1</v>
@@ -7830,10 +7821,10 @@
     </row>
     <row r="385" spans="3:7">
       <c r="C385" s="6">
-        <v>12115</v>
+        <v>13115</v>
       </c>
       <c r="D385" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E385" s="5">
         <v>1</v>
@@ -7847,12 +7838,12 @@
     </row>
     <row r="386" spans="3:7">
       <c r="C386" s="6">
-        <v>12116</v>
+        <v>13116</v>
       </c>
       <c r="D386" s="3">
-        <v>121</v>
-      </c>
-      <c r="E386" s="3">
+        <v>131</v>
+      </c>
+      <c r="E386" s="5">
         <v>1</v>
       </c>
       <c r="F386" s="3" t="s">
@@ -7864,12 +7855,12 @@
     </row>
     <row r="387" spans="3:7">
       <c r="C387" s="6">
-        <v>12117</v>
+        <v>13117</v>
       </c>
       <c r="D387" s="3">
-        <v>121</v>
-      </c>
-      <c r="E387" s="5">
+        <v>131</v>
+      </c>
+      <c r="E387" s="3">
         <v>1</v>
       </c>
       <c r="F387" s="3" t="s">
@@ -7881,10 +7872,10 @@
     </row>
     <row r="388" spans="3:7">
       <c r="C388" s="6">
-        <v>12118</v>
+        <v>13118</v>
       </c>
       <c r="D388" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E388" s="5">
         <v>1</v>
@@ -7898,10 +7889,10 @@
     </row>
     <row r="389" spans="3:7">
       <c r="C389" s="6">
-        <v>12119</v>
+        <v>13119</v>
       </c>
       <c r="D389" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E389" s="5">
         <v>1</v>
@@ -7915,12 +7906,12 @@
     </row>
     <row r="390" spans="3:7">
       <c r="C390" s="6">
-        <v>12120</v>
+        <v>13120</v>
       </c>
       <c r="D390" s="3">
-        <v>121</v>
-      </c>
-      <c r="E390" s="3">
+        <v>131</v>
+      </c>
+      <c r="E390" s="5">
         <v>1</v>
       </c>
       <c r="F390" s="3" t="s">
@@ -7932,12 +7923,12 @@
     </row>
     <row r="391" spans="3:7">
       <c r="C391" s="6">
-        <v>12121</v>
+        <v>13121</v>
       </c>
       <c r="D391" s="3">
-        <v>121</v>
-      </c>
-      <c r="E391" s="5">
+        <v>131</v>
+      </c>
+      <c r="E391" s="3">
         <v>1</v>
       </c>
       <c r="F391" s="3" t="s">
@@ -7949,10 +7940,10 @@
     </row>
     <row r="392" spans="3:7">
       <c r="C392" s="6">
-        <v>12122</v>
+        <v>13122</v>
       </c>
       <c r="D392" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E392" s="5">
         <v>1</v>
@@ -7966,10 +7957,10 @@
     </row>
     <row r="393" spans="3:7">
       <c r="C393" s="6">
-        <v>12123</v>
+        <v>13123</v>
       </c>
       <c r="D393" s="3">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E393" s="5">
         <v>1</v>
@@ -7983,12 +7974,12 @@
     </row>
     <row r="394" spans="3:7">
       <c r="C394" s="6">
-        <v>12124</v>
+        <v>13124</v>
       </c>
       <c r="D394" s="3">
-        <v>121</v>
-      </c>
-      <c r="E394" s="3">
+        <v>131</v>
+      </c>
+      <c r="E394" s="5">
         <v>1</v>
       </c>
       <c r="F394" s="3" t="s">
@@ -8000,12 +7991,12 @@
     </row>
     <row r="395" spans="3:7">
       <c r="C395" s="6">
-        <v>12125</v>
+        <v>13125</v>
       </c>
       <c r="D395" s="3">
-        <v>121</v>
-      </c>
-      <c r="E395" s="5">
+        <v>131</v>
+      </c>
+      <c r="E395" s="3">
         <v>1</v>
       </c>
       <c r="F395" s="3" t="s">
@@ -8020,10 +8011,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>12801</v>
+        <v>13901</v>
       </c>
       <c r="D397" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8035,17 +8026,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20425</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>12802</v>
+        <v>13902</v>
       </c>
       <c r="D398" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8057,15 +8048,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20426</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="399" spans="3:8">
       <c r="C399" s="6">
-        <v>12803</v>
+        <v>13903</v>
       </c>
       <c r="D399" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8077,17 +8068,17 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20427</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="400" spans="3:8">
       <c r="C400" s="6">
-        <v>12804</v>
+        <v>13904</v>
       </c>
       <c r="D400" s="3">
-        <v>128</v>
-      </c>
-      <c r="E400" s="3">
+        <v>139</v>
+      </c>
+      <c r="E400" s="5">
         <v>1</v>
       </c>
       <c r="F400" s="3" t="s">
@@ -8097,17 +8088,17 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20428</v>
+        <v>20478</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>12805</v>
+        <v>13905</v>
       </c>
       <c r="D401" s="3">
-        <v>128</v>
-      </c>
-      <c r="E401" s="5">
+        <v>139</v>
+      </c>
+      <c r="E401" s="3">
         <v>1</v>
       </c>
       <c r="F401" s="3" t="s">
@@ -8119,10 +8110,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>12806</v>
+        <v>13906</v>
       </c>
       <c r="D402" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8136,10 +8127,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>12807</v>
+        <v>13907</v>
       </c>
       <c r="D403" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8153,12 +8144,12 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>12808</v>
+        <v>13908</v>
       </c>
       <c r="D404" s="3">
-        <v>128</v>
-      </c>
-      <c r="E404" s="3">
+        <v>139</v>
+      </c>
+      <c r="E404" s="5">
         <v>1</v>
       </c>
       <c r="F404" s="3" t="s">
@@ -8170,12 +8161,12 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>12809</v>
+        <v>13909</v>
       </c>
       <c r="D405" s="3">
-        <v>128</v>
-      </c>
-      <c r="E405" s="5">
+        <v>139</v>
+      </c>
+      <c r="E405" s="3">
         <v>1</v>
       </c>
       <c r="F405" s="3" t="s">
@@ -8187,10 +8178,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>12810</v>
+        <v>13910</v>
       </c>
       <c r="D406" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8204,10 +8195,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>12811</v>
+        <v>13911</v>
       </c>
       <c r="D407" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8221,12 +8212,12 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>12812</v>
+        <v>13912</v>
       </c>
       <c r="D408" s="3">
-        <v>128</v>
-      </c>
-      <c r="E408" s="3">
+        <v>139</v>
+      </c>
+      <c r="E408" s="5">
         <v>1</v>
       </c>
       <c r="F408" s="3" t="s">
@@ -8238,12 +8229,12 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>12813</v>
+        <v>13913</v>
       </c>
       <c r="D409" s="3">
-        <v>128</v>
-      </c>
-      <c r="E409" s="5">
+        <v>139</v>
+      </c>
+      <c r="E409" s="3">
         <v>1</v>
       </c>
       <c r="F409" s="3" t="s">
@@ -8255,10 +8246,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>12814</v>
+        <v>13914</v>
       </c>
       <c r="D410" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8272,10 +8263,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>12815</v>
+        <v>13915</v>
       </c>
       <c r="D411" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8289,12 +8280,12 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>12816</v>
+        <v>13916</v>
       </c>
       <c r="D412" s="3">
-        <v>128</v>
-      </c>
-      <c r="E412" s="3">
+        <v>139</v>
+      </c>
+      <c r="E412" s="5">
         <v>1</v>
       </c>
       <c r="F412" s="3" t="s">
@@ -8306,12 +8297,12 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>12817</v>
+        <v>13917</v>
       </c>
       <c r="D413" s="3">
-        <v>128</v>
-      </c>
-      <c r="E413" s="5">
+        <v>139</v>
+      </c>
+      <c r="E413" s="3">
         <v>1</v>
       </c>
       <c r="F413" s="3" t="s">
@@ -8323,10 +8314,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>12818</v>
+        <v>13918</v>
       </c>
       <c r="D414" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8340,10 +8331,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>12819</v>
+        <v>13919</v>
       </c>
       <c r="D415" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8357,12 +8348,12 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>12820</v>
+        <v>13920</v>
       </c>
       <c r="D416" s="3">
-        <v>128</v>
-      </c>
-      <c r="E416" s="3">
+        <v>139</v>
+      </c>
+      <c r="E416" s="5">
         <v>1</v>
       </c>
       <c r="F416" s="3" t="s">
@@ -8374,12 +8365,12 @@
     </row>
     <row r="417" spans="3:7">
       <c r="C417" s="6">
-        <v>12821</v>
+        <v>13921</v>
       </c>
       <c r="D417" s="3">
-        <v>128</v>
-      </c>
-      <c r="E417" s="5">
+        <v>139</v>
+      </c>
+      <c r="E417" s="3">
         <v>1</v>
       </c>
       <c r="F417" s="3" t="s">
@@ -8391,10 +8382,10 @@
     </row>
     <row r="418" spans="3:7">
       <c r="C418" s="6">
-        <v>12822</v>
+        <v>13922</v>
       </c>
       <c r="D418" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8408,10 +8399,10 @@
     </row>
     <row r="419" spans="3:7">
       <c r="C419" s="6">
-        <v>12823</v>
+        <v>13923</v>
       </c>
       <c r="D419" s="3">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8425,12 +8416,12 @@
     </row>
     <row r="420" spans="3:7">
       <c r="C420" s="6">
-        <v>12824</v>
+        <v>13924</v>
       </c>
       <c r="D420" s="3">
-        <v>128</v>
-      </c>
-      <c r="E420" s="3">
+        <v>139</v>
+      </c>
+      <c r="E420" s="5">
         <v>1</v>
       </c>
       <c r="F420" s="3" t="s">
@@ -8442,12 +8433,12 @@
     </row>
     <row r="421" spans="3:7">
       <c r="C421" s="6">
-        <v>12825</v>
+        <v>13925</v>
       </c>
       <c r="D421" s="3">
-        <v>128</v>
-      </c>
-      <c r="E421" s="5">
+        <v>139</v>
+      </c>
+      <c r="E421" s="3">
         <v>1</v>
       </c>
       <c r="F421" s="3" t="s">
@@ -8462,10 +8453,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>13101</v>
+        <v>14301</v>
       </c>
       <c r="D423" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8477,17 +8468,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20515</v>
+        <v>20575</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>13102</v>
+        <v>14302</v>
       </c>
       <c r="D424" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8499,15 +8490,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20516</v>
+        <v>20576</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>13103</v>
+        <v>14303</v>
       </c>
       <c r="D425" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8519,15 +8510,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20517</v>
+        <v>20577</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>13104</v>
+        <v>14304</v>
       </c>
       <c r="D426" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8539,15 +8530,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20518</v>
+        <v>20578</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>13105</v>
+        <v>14305</v>
       </c>
       <c r="D427" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8561,10 +8552,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>13106</v>
+        <v>14306</v>
       </c>
       <c r="D428" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8578,10 +8569,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>13107</v>
+        <v>14307</v>
       </c>
       <c r="D429" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8595,10 +8586,10 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>13108</v>
+        <v>14308</v>
       </c>
       <c r="D430" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8612,10 +8603,10 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>13109</v>
+        <v>14309</v>
       </c>
       <c r="D431" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8629,10 +8620,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>13110</v>
+        <v>14310</v>
       </c>
       <c r="D432" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8646,10 +8637,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>13111</v>
+        <v>14311</v>
       </c>
       <c r="D433" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8663,10 +8654,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>13112</v>
+        <v>14312</v>
       </c>
       <c r="D434" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8680,10 +8671,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>13113</v>
+        <v>14313</v>
       </c>
       <c r="D435" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8697,10 +8688,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>13114</v>
+        <v>14314</v>
       </c>
       <c r="D436" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8714,10 +8705,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>13115</v>
+        <v>14315</v>
       </c>
       <c r="D437" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8731,10 +8722,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>13116</v>
+        <v>14316</v>
       </c>
       <c r="D438" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8748,10 +8739,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>13117</v>
+        <v>14317</v>
       </c>
       <c r="D439" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8765,10 +8756,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>13118</v>
+        <v>14318</v>
       </c>
       <c r="D440" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8782,10 +8773,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>13119</v>
+        <v>14319</v>
       </c>
       <c r="D441" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8799,10 +8790,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>13120</v>
+        <v>14320</v>
       </c>
       <c r="D442" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8816,10 +8807,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>13121</v>
+        <v>14321</v>
       </c>
       <c r="D443" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8833,10 +8824,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>13122</v>
+        <v>14322</v>
       </c>
       <c r="D444" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8850,10 +8841,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>13123</v>
+        <v>14323</v>
       </c>
       <c r="D445" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8867,10 +8858,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>13124</v>
+        <v>14324</v>
       </c>
       <c r="D446" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8884,10 +8875,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>13125</v>
+        <v>14325</v>
       </c>
       <c r="D447" s="3">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8904,10 +8895,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>13501</v>
+        <v>14701</v>
       </c>
       <c r="D449" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8919,17 +8910,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20405</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>13502</v>
+        <v>14702</v>
       </c>
       <c r="D450" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8941,15 +8932,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20406</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>13503</v>
+        <v>14703</v>
       </c>
       <c r="D451" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8961,15 +8952,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20407</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>13504</v>
+        <v>14704</v>
       </c>
       <c r="D452" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8981,15 +8972,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20408</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>13505</v>
+        <v>14705</v>
       </c>
       <c r="D453" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9003,10 +8994,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>13506</v>
+        <v>14706</v>
       </c>
       <c r="D454" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9020,10 +9011,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>13507</v>
+        <v>14707</v>
       </c>
       <c r="D455" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9037,10 +9028,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>13508</v>
+        <v>14708</v>
       </c>
       <c r="D456" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9054,10 +9045,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>13509</v>
+        <v>14709</v>
       </c>
       <c r="D457" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9071,10 +9062,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>13510</v>
+        <v>14710</v>
       </c>
       <c r="D458" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9088,10 +9079,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>13511</v>
+        <v>14711</v>
       </c>
       <c r="D459" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9105,10 +9096,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>13512</v>
+        <v>14712</v>
       </c>
       <c r="D460" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9122,10 +9113,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>13513</v>
+        <v>14713</v>
       </c>
       <c r="D461" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9139,10 +9130,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>13514</v>
+        <v>14714</v>
       </c>
       <c r="D462" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9156,10 +9147,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>13515</v>
+        <v>14715</v>
       </c>
       <c r="D463" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9173,10 +9164,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>13516</v>
+        <v>14716</v>
       </c>
       <c r="D464" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9190,10 +9181,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>13517</v>
+        <v>14717</v>
       </c>
       <c r="D465" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9207,10 +9198,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>13518</v>
+        <v>14718</v>
       </c>
       <c r="D466" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9224,10 +9215,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>13519</v>
+        <v>14719</v>
       </c>
       <c r="D467" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9241,10 +9232,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>13520</v>
+        <v>14720</v>
       </c>
       <c r="D468" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9258,10 +9249,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>13521</v>
+        <v>14721</v>
       </c>
       <c r="D469" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9275,10 +9266,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>13522</v>
+        <v>14722</v>
       </c>
       <c r="D470" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9292,10 +9283,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>13523</v>
+        <v>14723</v>
       </c>
       <c r="D471" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9309,10 +9300,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>13524</v>
+        <v>14724</v>
       </c>
       <c r="D472" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9326,10 +9317,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>13525</v>
+        <v>14725</v>
       </c>
       <c r="D473" s="3">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9346,10 +9337,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>13901</v>
+        <v>14901</v>
       </c>
       <c r="D475" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9361,17 +9352,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20475</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>13902</v>
+        <v>14902</v>
       </c>
       <c r="D476" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9383,15 +9374,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20476</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>13903</v>
+        <v>14903</v>
       </c>
       <c r="D477" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9403,15 +9394,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20477</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>13904</v>
+        <v>14904</v>
       </c>
       <c r="D478" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9423,15 +9414,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20478</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>13905</v>
+        <v>14905</v>
       </c>
       <c r="D479" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9445,10 +9436,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>13906</v>
+        <v>14906</v>
       </c>
       <c r="D480" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9462,10 +9453,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>13907</v>
+        <v>14907</v>
       </c>
       <c r="D481" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9479,10 +9470,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>13908</v>
+        <v>14908</v>
       </c>
       <c r="D482" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9496,10 +9487,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>13909</v>
+        <v>14909</v>
       </c>
       <c r="D483" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9513,10 +9504,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>13910</v>
+        <v>14910</v>
       </c>
       <c r="D484" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9530,10 +9521,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>13911</v>
+        <v>14911</v>
       </c>
       <c r="D485" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9547,10 +9538,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>13912</v>
+        <v>14912</v>
       </c>
       <c r="D486" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9564,10 +9555,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>13913</v>
+        <v>14913</v>
       </c>
       <c r="D487" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9581,10 +9572,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>13914</v>
+        <v>14914</v>
       </c>
       <c r="D488" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9598,10 +9589,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>13915</v>
+        <v>14915</v>
       </c>
       <c r="D489" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9615,10 +9606,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>13916</v>
+        <v>14916</v>
       </c>
       <c r="D490" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9632,10 +9623,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>13917</v>
+        <v>14917</v>
       </c>
       <c r="D491" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9649,10 +9640,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>13918</v>
+        <v>14918</v>
       </c>
       <c r="D492" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9666,10 +9657,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>13919</v>
+        <v>14919</v>
       </c>
       <c r="D493" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9683,10 +9674,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>13920</v>
+        <v>14920</v>
       </c>
       <c r="D494" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9700,10 +9691,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>13921</v>
+        <v>14921</v>
       </c>
       <c r="D495" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9717,10 +9708,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>13922</v>
+        <v>14922</v>
       </c>
       <c r="D496" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9734,10 +9725,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>13923</v>
+        <v>14923</v>
       </c>
       <c r="D497" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9751,10 +9742,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>13924</v>
+        <v>14924</v>
       </c>
       <c r="D498" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9768,10 +9759,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>13925</v>
+        <v>14925</v>
       </c>
       <c r="D499" s="3">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9788,10 +9779,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>14301</v>
+        <v>15101</v>
       </c>
       <c r="D501" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9803,17 +9794,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20575</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>14302</v>
+        <v>15102</v>
       </c>
       <c r="D502" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9825,15 +9816,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20576</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>14303</v>
+        <v>15103</v>
       </c>
       <c r="D503" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9845,15 +9836,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20577</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>14304</v>
+        <v>15104</v>
       </c>
       <c r="D504" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9865,15 +9856,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20578</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>14305</v>
+        <v>15105</v>
       </c>
       <c r="D505" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9887,10 +9878,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>14306</v>
+        <v>15106</v>
       </c>
       <c r="D506" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9904,10 +9895,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>14307</v>
+        <v>15107</v>
       </c>
       <c r="D507" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9921,10 +9912,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>14308</v>
+        <v>15108</v>
       </c>
       <c r="D508" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9938,10 +9929,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>14309</v>
+        <v>15109</v>
       </c>
       <c r="D509" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9955,10 +9946,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>14310</v>
+        <v>15110</v>
       </c>
       <c r="D510" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9972,10 +9963,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>14311</v>
+        <v>15111</v>
       </c>
       <c r="D511" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9989,10 +9980,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>14312</v>
+        <v>15112</v>
       </c>
       <c r="D512" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10006,10 +9997,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>14313</v>
+        <v>15113</v>
       </c>
       <c r="D513" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10023,10 +10014,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>14314</v>
+        <v>15114</v>
       </c>
       <c r="D514" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10040,10 +10031,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>14315</v>
+        <v>15115</v>
       </c>
       <c r="D515" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10057,10 +10048,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>14316</v>
+        <v>15116</v>
       </c>
       <c r="D516" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10074,10 +10065,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>14317</v>
+        <v>15117</v>
       </c>
       <c r="D517" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10091,10 +10082,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>14318</v>
+        <v>15118</v>
       </c>
       <c r="D518" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10108,10 +10099,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>14319</v>
+        <v>15119</v>
       </c>
       <c r="D519" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10125,10 +10116,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>14320</v>
+        <v>15120</v>
       </c>
       <c r="D520" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10142,10 +10133,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>14321</v>
+        <v>15121</v>
       </c>
       <c r="D521" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10159,10 +10150,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>14322</v>
+        <v>15122</v>
       </c>
       <c r="D522" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10176,10 +10167,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>14323</v>
+        <v>15123</v>
       </c>
       <c r="D523" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10193,10 +10184,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>14324</v>
+        <v>15124</v>
       </c>
       <c r="D524" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10210,10 +10201,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>14325</v>
+        <v>15125</v>
       </c>
       <c r="D525" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10230,10 +10221,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>14701</v>
+        <v>15301</v>
       </c>
       <c r="D527" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10245,17 +10236,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20495</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>14702</v>
+        <v>15302</v>
       </c>
       <c r="D528" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10267,15 +10258,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20496</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>14703</v>
+        <v>15303</v>
       </c>
       <c r="D529" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10287,15 +10278,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20497</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>14704</v>
+        <v>15304</v>
       </c>
       <c r="D530" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10307,15 +10298,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20498</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>14705</v>
+        <v>15305</v>
       </c>
       <c r="D531" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10329,10 +10320,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>14706</v>
+        <v>15306</v>
       </c>
       <c r="D532" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10346,10 +10337,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>14707</v>
+        <v>15307</v>
       </c>
       <c r="D533" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10363,10 +10354,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>14708</v>
+        <v>15308</v>
       </c>
       <c r="D534" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10380,10 +10371,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>14709</v>
+        <v>15309</v>
       </c>
       <c r="D535" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10397,10 +10388,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>14710</v>
+        <v>15310</v>
       </c>
       <c r="D536" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10414,10 +10405,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>14711</v>
+        <v>15311</v>
       </c>
       <c r="D537" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10431,10 +10422,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>14712</v>
+        <v>15312</v>
       </c>
       <c r="D538" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10448,10 +10439,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>14713</v>
+        <v>15313</v>
       </c>
       <c r="D539" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10465,10 +10456,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>14714</v>
+        <v>15314</v>
       </c>
       <c r="D540" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10482,10 +10473,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>14715</v>
+        <v>15315</v>
       </c>
       <c r="D541" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10499,10 +10490,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>14716</v>
+        <v>15316</v>
       </c>
       <c r="D542" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10516,10 +10507,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>14717</v>
+        <v>15317</v>
       </c>
       <c r="D543" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10533,10 +10524,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>14718</v>
+        <v>15318</v>
       </c>
       <c r="D544" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10550,10 +10541,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>14719</v>
+        <v>15319</v>
       </c>
       <c r="D545" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10567,10 +10558,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>14720</v>
+        <v>15320</v>
       </c>
       <c r="D546" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10584,10 +10575,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>14721</v>
+        <v>15321</v>
       </c>
       <c r="D547" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10601,10 +10592,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>14722</v>
+        <v>15322</v>
       </c>
       <c r="D548" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10618,10 +10609,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>14723</v>
+        <v>15323</v>
       </c>
       <c r="D549" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10635,10 +10626,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>14724</v>
+        <v>15324</v>
       </c>
       <c r="D550" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10652,10 +10643,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>14725</v>
+        <v>15325</v>
       </c>
       <c r="D551" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10672,10 +10663,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>14901</v>
+        <v>15401</v>
       </c>
       <c r="D553" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10687,17 +10678,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20445</v>
+        <v>20595</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>14902</v>
+        <v>15402</v>
       </c>
       <c r="D554" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10709,15 +10700,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20446</v>
+        <v>20596</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>14903</v>
+        <v>15403</v>
       </c>
       <c r="D555" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10729,15 +10720,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20447</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>14904</v>
+        <v>15404</v>
       </c>
       <c r="D556" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10749,15 +10740,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20448</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>14905</v>
+        <v>15405</v>
       </c>
       <c r="D557" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10771,10 +10762,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>14906</v>
+        <v>15406</v>
       </c>
       <c r="D558" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10788,10 +10779,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>14907</v>
+        <v>15407</v>
       </c>
       <c r="D559" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10805,10 +10796,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>14908</v>
+        <v>15408</v>
       </c>
       <c r="D560" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10822,10 +10813,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>14909</v>
+        <v>15409</v>
       </c>
       <c r="D561" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10839,10 +10830,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>14910</v>
+        <v>15410</v>
       </c>
       <c r="D562" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10856,10 +10847,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>14911</v>
+        <v>15411</v>
       </c>
       <c r="D563" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10873,10 +10864,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>14912</v>
+        <v>15412</v>
       </c>
       <c r="D564" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10890,10 +10881,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>14913</v>
+        <v>15413</v>
       </c>
       <c r="D565" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10907,10 +10898,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>14914</v>
+        <v>15414</v>
       </c>
       <c r="D566" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10924,10 +10915,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>14915</v>
+        <v>15415</v>
       </c>
       <c r="D567" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10941,10 +10932,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>14916</v>
+        <v>15416</v>
       </c>
       <c r="D568" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10958,10 +10949,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>14917</v>
+        <v>15417</v>
       </c>
       <c r="D569" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10975,10 +10966,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>14918</v>
+        <v>15418</v>
       </c>
       <c r="D570" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10992,10 +10983,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>14919</v>
+        <v>15419</v>
       </c>
       <c r="D571" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11009,10 +11000,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>14920</v>
+        <v>15420</v>
       </c>
       <c r="D572" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11026,10 +11017,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>14921</v>
+        <v>15421</v>
       </c>
       <c r="D573" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11043,10 +11034,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>14922</v>
+        <v>15422</v>
       </c>
       <c r="D574" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11060,10 +11051,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>14923</v>
+        <v>15423</v>
       </c>
       <c r="D575" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11077,10 +11068,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>14924</v>
+        <v>15424</v>
       </c>
       <c r="D576" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11094,10 +11085,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>14925</v>
+        <v>15425</v>
       </c>
       <c r="D577" s="3">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11114,10 +11105,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>15101</v>
+        <v>15501</v>
       </c>
       <c r="D579" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11129,17 +11120,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20415</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>15102</v>
+        <v>15502</v>
       </c>
       <c r="D580" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11151,15 +11142,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20416</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>15103</v>
+        <v>15503</v>
       </c>
       <c r="D581" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11171,15 +11162,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20417</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>15104</v>
+        <v>15504</v>
       </c>
       <c r="D582" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11191,15 +11182,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20418</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>15105</v>
+        <v>15505</v>
       </c>
       <c r="D583" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11213,10 +11204,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>15106</v>
+        <v>15506</v>
       </c>
       <c r="D584" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11230,10 +11221,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>15107</v>
+        <v>15507</v>
       </c>
       <c r="D585" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11247,10 +11238,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>15108</v>
+        <v>15508</v>
       </c>
       <c r="D586" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11264,10 +11255,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>15109</v>
+        <v>15509</v>
       </c>
       <c r="D587" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11281,10 +11272,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>15110</v>
+        <v>15510</v>
       </c>
       <c r="D588" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11298,10 +11289,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>15111</v>
+        <v>15511</v>
       </c>
       <c r="D589" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11315,10 +11306,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>15112</v>
+        <v>15512</v>
       </c>
       <c r="D590" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11332,10 +11323,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>15113</v>
+        <v>15513</v>
       </c>
       <c r="D591" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11349,10 +11340,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>15114</v>
+        <v>15514</v>
       </c>
       <c r="D592" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11366,10 +11357,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>15115</v>
+        <v>15515</v>
       </c>
       <c r="D593" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11383,10 +11374,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>15116</v>
+        <v>15516</v>
       </c>
       <c r="D594" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11400,10 +11391,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>15117</v>
+        <v>15517</v>
       </c>
       <c r="D595" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11417,10 +11408,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>15118</v>
+        <v>15518</v>
       </c>
       <c r="D596" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11434,10 +11425,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>15119</v>
+        <v>15519</v>
       </c>
       <c r="D597" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11451,10 +11442,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>15120</v>
+        <v>15520</v>
       </c>
       <c r="D598" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11468,10 +11459,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>15121</v>
+        <v>15521</v>
       </c>
       <c r="D599" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11485,10 +11476,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>15122</v>
+        <v>15522</v>
       </c>
       <c r="D600" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11502,10 +11493,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>15123</v>
+        <v>15523</v>
       </c>
       <c r="D601" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11519,10 +11510,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>15124</v>
+        <v>15524</v>
       </c>
       <c r="D602" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11536,10 +11527,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>15125</v>
+        <v>15525</v>
       </c>
       <c r="D603" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11556,10 +11547,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>15201</v>
+        <v>15601</v>
       </c>
       <c r="D605" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11571,17 +11562,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20455</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>15202</v>
+        <v>15602</v>
       </c>
       <c r="D606" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11593,15 +11584,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20456</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>15203</v>
+        <v>15603</v>
       </c>
       <c r="D607" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11613,15 +11604,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20457</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>15204</v>
+        <v>15604</v>
       </c>
       <c r="D608" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11633,15 +11624,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20458</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>15205</v>
+        <v>15605</v>
       </c>
       <c r="D609" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11655,10 +11646,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>15206</v>
+        <v>15606</v>
       </c>
       <c r="D610" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11672,10 +11663,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>15207</v>
+        <v>15607</v>
       </c>
       <c r="D611" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11689,10 +11680,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>15208</v>
+        <v>15608</v>
       </c>
       <c r="D612" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11706,10 +11697,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>15209</v>
+        <v>15609</v>
       </c>
       <c r="D613" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11723,10 +11714,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>15210</v>
+        <v>15610</v>
       </c>
       <c r="D614" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11740,10 +11731,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>15211</v>
+        <v>15611</v>
       </c>
       <c r="D615" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11757,10 +11748,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>15212</v>
+        <v>15612</v>
       </c>
       <c r="D616" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11774,10 +11765,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>15213</v>
+        <v>15613</v>
       </c>
       <c r="D617" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11791,10 +11782,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>15214</v>
+        <v>15614</v>
       </c>
       <c r="D618" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11808,10 +11799,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>15215</v>
+        <v>15615</v>
       </c>
       <c r="D619" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11825,10 +11816,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>15216</v>
+        <v>15616</v>
       </c>
       <c r="D620" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11842,10 +11833,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>15217</v>
+        <v>15617</v>
       </c>
       <c r="D621" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11859,10 +11850,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>15218</v>
+        <v>15618</v>
       </c>
       <c r="D622" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11876,10 +11867,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>15219</v>
+        <v>15619</v>
       </c>
       <c r="D623" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11893,10 +11884,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>15220</v>
+        <v>15620</v>
       </c>
       <c r="D624" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11910,10 +11901,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>15221</v>
+        <v>15621</v>
       </c>
       <c r="D625" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11927,10 +11918,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>15222</v>
+        <v>15622</v>
       </c>
       <c r="D626" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11944,10 +11935,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>15223</v>
+        <v>15623</v>
       </c>
       <c r="D627" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11961,10 +11952,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>15224</v>
+        <v>15624</v>
       </c>
       <c r="D628" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11978,10 +11969,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>15225</v>
+        <v>15625</v>
       </c>
       <c r="D629" s="3">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11998,10 +11989,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>15301</v>
+        <v>15701</v>
       </c>
       <c r="D631" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12013,17 +12004,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20565</v>
+        <v>20645</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>15302</v>
+        <v>15702</v>
       </c>
       <c r="D632" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12035,15 +12026,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20566</v>
+        <v>20646</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>15303</v>
+        <v>15703</v>
       </c>
       <c r="D633" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12055,15 +12046,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20567</v>
+        <v>20647</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>15304</v>
+        <v>15704</v>
       </c>
       <c r="D634" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12075,15 +12066,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20568</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>15305</v>
+        <v>15705</v>
       </c>
       <c r="D635" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12097,10 +12088,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>15306</v>
+        <v>15706</v>
       </c>
       <c r="D636" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12114,10 +12105,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>15307</v>
+        <v>15707</v>
       </c>
       <c r="D637" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12131,10 +12122,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>15308</v>
+        <v>15708</v>
       </c>
       <c r="D638" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12148,10 +12139,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>15309</v>
+        <v>15709</v>
       </c>
       <c r="D639" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12165,10 +12156,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>15310</v>
+        <v>15710</v>
       </c>
       <c r="D640" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12182,10 +12173,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>15311</v>
+        <v>15711</v>
       </c>
       <c r="D641" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12199,10 +12190,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>15312</v>
+        <v>15712</v>
       </c>
       <c r="D642" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12216,10 +12207,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>15313</v>
+        <v>15713</v>
       </c>
       <c r="D643" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12233,10 +12224,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>15314</v>
+        <v>15714</v>
       </c>
       <c r="D644" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12250,10 +12241,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>15315</v>
+        <v>15715</v>
       </c>
       <c r="D645" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12267,10 +12258,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>15316</v>
+        <v>15716</v>
       </c>
       <c r="D646" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12284,10 +12275,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>15317</v>
+        <v>15717</v>
       </c>
       <c r="D647" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12301,10 +12292,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>15318</v>
+        <v>15718</v>
       </c>
       <c r="D648" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12318,10 +12309,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>15319</v>
+        <v>15719</v>
       </c>
       <c r="D649" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12335,10 +12326,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>15320</v>
+        <v>15720</v>
       </c>
       <c r="D650" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12352,10 +12343,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>15321</v>
+        <v>15721</v>
       </c>
       <c r="D651" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>15322</v>
+        <v>15722</v>
       </c>
       <c r="D652" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12386,10 +12377,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>15323</v>
+        <v>15723</v>
       </c>
       <c r="D653" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12403,10 +12394,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>15324</v>
+        <v>15724</v>
       </c>
       <c r="D654" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12420,10 +12411,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>15325</v>
+        <v>15725</v>
       </c>
       <c r="D655" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12440,10 +12431,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>15401</v>
+        <v>15801</v>
       </c>
       <c r="D657" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12455,17 +12446,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20595</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>15402</v>
+        <v>15802</v>
       </c>
       <c r="D658" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12477,15 +12468,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20596</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="659" spans="3:8">
       <c r="C659" s="6">
-        <v>15403</v>
+        <v>15803</v>
       </c>
       <c r="D659" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12497,15 +12488,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20597</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="660" spans="3:8">
       <c r="C660" s="6">
-        <v>15404</v>
+        <v>15804</v>
       </c>
       <c r="D660" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12517,15 +12508,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20598</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="661" spans="3:7">
       <c r="C661" s="6">
-        <v>15405</v>
+        <v>15805</v>
       </c>
       <c r="D661" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12539,10 +12530,10 @@
     </row>
     <row r="662" spans="3:7">
       <c r="C662" s="6">
-        <v>15406</v>
+        <v>15806</v>
       </c>
       <c r="D662" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12556,10 +12547,10 @@
     </row>
     <row r="663" spans="3:7">
       <c r="C663" s="6">
-        <v>15407</v>
+        <v>15807</v>
       </c>
       <c r="D663" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12573,10 +12564,10 @@
     </row>
     <row r="664" spans="3:7">
       <c r="C664" s="6">
-        <v>15408</v>
+        <v>15808</v>
       </c>
       <c r="D664" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12590,10 +12581,10 @@
     </row>
     <row r="665" spans="3:7">
       <c r="C665" s="6">
-        <v>15409</v>
+        <v>15809</v>
       </c>
       <c r="D665" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12607,10 +12598,10 @@
     </row>
     <row r="666" spans="3:7">
       <c r="C666" s="6">
-        <v>15410</v>
+        <v>15810</v>
       </c>
       <c r="D666" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12624,10 +12615,10 @@
     </row>
     <row r="667" spans="3:7">
       <c r="C667" s="6">
-        <v>15411</v>
+        <v>15811</v>
       </c>
       <c r="D667" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12641,10 +12632,10 @@
     </row>
     <row r="668" spans="3:7">
       <c r="C668" s="6">
-        <v>15412</v>
+        <v>15812</v>
       </c>
       <c r="D668" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12658,10 +12649,10 @@
     </row>
     <row r="669" spans="3:7">
       <c r="C669" s="6">
-        <v>15413</v>
+        <v>15813</v>
       </c>
       <c r="D669" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12675,10 +12666,10 @@
     </row>
     <row r="670" spans="3:7">
       <c r="C670" s="6">
-        <v>15414</v>
+        <v>15814</v>
       </c>
       <c r="D670" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12692,10 +12683,10 @@
     </row>
     <row r="671" spans="3:7">
       <c r="C671" s="6">
-        <v>15415</v>
+        <v>15815</v>
       </c>
       <c r="D671" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12709,10 +12700,10 @@
     </row>
     <row r="672" spans="3:7">
       <c r="C672" s="6">
-        <v>15416</v>
+        <v>15816</v>
       </c>
       <c r="D672" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12726,10 +12717,10 @@
     </row>
     <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>15417</v>
+        <v>15817</v>
       </c>
       <c r="D673" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12743,10 +12734,10 @@
     </row>
     <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>15418</v>
+        <v>15818</v>
       </c>
       <c r="D674" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12760,10 +12751,10 @@
     </row>
     <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>15419</v>
+        <v>15819</v>
       </c>
       <c r="D675" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12777,10 +12768,10 @@
     </row>
     <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>15420</v>
+        <v>15820</v>
       </c>
       <c r="D676" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12794,10 +12785,10 @@
     </row>
     <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>15421</v>
+        <v>15821</v>
       </c>
       <c r="D677" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12811,10 +12802,10 @@
     </row>
     <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>15422</v>
+        <v>15822</v>
       </c>
       <c r="D678" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12828,10 +12819,10 @@
     </row>
     <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>15423</v>
+        <v>15823</v>
       </c>
       <c r="D679" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12845,10 +12836,10 @@
     </row>
     <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>15424</v>
+        <v>15824</v>
       </c>
       <c r="D680" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12862,10 +12853,10 @@
     </row>
     <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>15425</v>
+        <v>15825</v>
       </c>
       <c r="D681" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12874,1332 +12865,6 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>15501</v>
-      </c>
-      <c r="D683" s="3">
-        <v>155</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20605</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>15502</v>
-      </c>
-      <c r="D684" s="3">
-        <v>155</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20606</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>15503</v>
-      </c>
-      <c r="D685" s="3">
-        <v>155</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20607</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>15504</v>
-      </c>
-      <c r="D686" s="3">
-        <v>155</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20608</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>15505</v>
-      </c>
-      <c r="D687" s="3">
-        <v>155</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>15506</v>
-      </c>
-      <c r="D688" s="3">
-        <v>155</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>15507</v>
-      </c>
-      <c r="D689" s="3">
-        <v>155</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>15508</v>
-      </c>
-      <c r="D690" s="3">
-        <v>155</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>15509</v>
-      </c>
-      <c r="D691" s="3">
-        <v>155</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>15510</v>
-      </c>
-      <c r="D692" s="3">
-        <v>155</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>15511</v>
-      </c>
-      <c r="D693" s="3">
-        <v>155</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>15512</v>
-      </c>
-      <c r="D694" s="3">
-        <v>155</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>15513</v>
-      </c>
-      <c r="D695" s="3">
-        <v>155</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>15514</v>
-      </c>
-      <c r="D696" s="3">
-        <v>155</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>15515</v>
-      </c>
-      <c r="D697" s="3">
-        <v>155</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>15516</v>
-      </c>
-      <c r="D698" s="3">
-        <v>155</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>15517</v>
-      </c>
-      <c r="D699" s="3">
-        <v>155</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>15518</v>
-      </c>
-      <c r="D700" s="3">
-        <v>155</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>15519</v>
-      </c>
-      <c r="D701" s="3">
-        <v>155</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>15520</v>
-      </c>
-      <c r="D702" s="3">
-        <v>155</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>15521</v>
-      </c>
-      <c r="D703" s="3">
-        <v>155</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>15522</v>
-      </c>
-      <c r="D704" s="3">
-        <v>155</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>15523</v>
-      </c>
-      <c r="D705" s="3">
-        <v>155</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>15524</v>
-      </c>
-      <c r="D706" s="3">
-        <v>155</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>15525</v>
-      </c>
-      <c r="D707" s="3">
-        <v>155</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>15601</v>
-      </c>
-      <c r="D709" s="3">
-        <v>156</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20615</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>15602</v>
-      </c>
-      <c r="D710" s="3">
-        <v>156</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20616</v>
-      </c>
-    </row>
-    <row r="711" spans="3:8">
-      <c r="C711" s="6">
-        <v>15603</v>
-      </c>
-      <c r="D711" s="3">
-        <v>156</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20617</v>
-      </c>
-    </row>
-    <row r="712" spans="3:8">
-      <c r="C712" s="6">
-        <v>15604</v>
-      </c>
-      <c r="D712" s="3">
-        <v>156</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20618</v>
-      </c>
-    </row>
-    <row r="713" spans="3:7">
-      <c r="C713" s="6">
-        <v>15605</v>
-      </c>
-      <c r="D713" s="3">
-        <v>156</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="3:7">
-      <c r="C714" s="6">
-        <v>15606</v>
-      </c>
-      <c r="D714" s="3">
-        <v>156</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="3:7">
-      <c r="C715" s="6">
-        <v>15607</v>
-      </c>
-      <c r="D715" s="3">
-        <v>156</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="3:7">
-      <c r="C716" s="6">
-        <v>15608</v>
-      </c>
-      <c r="D716" s="3">
-        <v>156</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="3:7">
-      <c r="C717" s="6">
-        <v>15609</v>
-      </c>
-      <c r="D717" s="3">
-        <v>156</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="3:7">
-      <c r="C718" s="6">
-        <v>15610</v>
-      </c>
-      <c r="D718" s="3">
-        <v>156</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="3:7">
-      <c r="C719" s="6">
-        <v>15611</v>
-      </c>
-      <c r="D719" s="3">
-        <v>156</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="3:7">
-      <c r="C720" s="6">
-        <v>15612</v>
-      </c>
-      <c r="D720" s="3">
-        <v>156</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="3:7">
-      <c r="C721" s="6">
-        <v>15613</v>
-      </c>
-      <c r="D721" s="3">
-        <v>156</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="3:7">
-      <c r="C722" s="6">
-        <v>15614</v>
-      </c>
-      <c r="D722" s="3">
-        <v>156</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="3:7">
-      <c r="C723" s="6">
-        <v>15615</v>
-      </c>
-      <c r="D723" s="3">
-        <v>156</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="3:7">
-      <c r="C724" s="6">
-        <v>15616</v>
-      </c>
-      <c r="D724" s="3">
-        <v>156</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="3:7">
-      <c r="C725" s="6">
-        <v>15617</v>
-      </c>
-      <c r="D725" s="3">
-        <v>156</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="3:7">
-      <c r="C726" s="6">
-        <v>15618</v>
-      </c>
-      <c r="D726" s="3">
-        <v>156</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="3:7">
-      <c r="C727" s="6">
-        <v>15619</v>
-      </c>
-      <c r="D727" s="3">
-        <v>156</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="3:7">
-      <c r="C728" s="6">
-        <v>15620</v>
-      </c>
-      <c r="D728" s="3">
-        <v>156</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="3:7">
-      <c r="C729" s="6">
-        <v>15621</v>
-      </c>
-      <c r="D729" s="3">
-        <v>156</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="3:7">
-      <c r="C730" s="6">
-        <v>15622</v>
-      </c>
-      <c r="D730" s="3">
-        <v>156</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="3:7">
-      <c r="C731" s="6">
-        <v>15623</v>
-      </c>
-      <c r="D731" s="3">
-        <v>156</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="3:7">
-      <c r="C732" s="6">
-        <v>15624</v>
-      </c>
-      <c r="D732" s="3">
-        <v>156</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="3:7">
-      <c r="C733" s="6">
-        <v>15625</v>
-      </c>
-      <c r="D733" s="3">
-        <v>156</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>15701</v>
-      </c>
-      <c r="D735" s="3">
-        <v>157</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20645</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>15702</v>
-      </c>
-      <c r="D736" s="3">
-        <v>157</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20646</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>15703</v>
-      </c>
-      <c r="D737" s="3">
-        <v>157</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20647</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>15704</v>
-      </c>
-      <c r="D738" s="3">
-        <v>157</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20648</v>
-      </c>
-    </row>
-    <row r="739" spans="3:7">
-      <c r="C739" s="6">
-        <v>15705</v>
-      </c>
-      <c r="D739" s="3">
-        <v>157</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:7">
-      <c r="C740" s="6">
-        <v>15706</v>
-      </c>
-      <c r="D740" s="3">
-        <v>157</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:7">
-      <c r="C741" s="6">
-        <v>15707</v>
-      </c>
-      <c r="D741" s="3">
-        <v>157</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:7">
-      <c r="C742" s="6">
-        <v>15708</v>
-      </c>
-      <c r="D742" s="3">
-        <v>157</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:7">
-      <c r="C743" s="6">
-        <v>15709</v>
-      </c>
-      <c r="D743" s="3">
-        <v>157</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:7">
-      <c r="C744" s="6">
-        <v>15710</v>
-      </c>
-      <c r="D744" s="3">
-        <v>157</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:7">
-      <c r="C745" s="6">
-        <v>15711</v>
-      </c>
-      <c r="D745" s="3">
-        <v>157</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:7">
-      <c r="C746" s="6">
-        <v>15712</v>
-      </c>
-      <c r="D746" s="3">
-        <v>157</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:7">
-      <c r="C747" s="6">
-        <v>15713</v>
-      </c>
-      <c r="D747" s="3">
-        <v>157</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:7">
-      <c r="C748" s="6">
-        <v>15714</v>
-      </c>
-      <c r="D748" s="3">
-        <v>157</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:7">
-      <c r="C749" s="6">
-        <v>15715</v>
-      </c>
-      <c r="D749" s="3">
-        <v>157</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:7">
-      <c r="C750" s="6">
-        <v>15716</v>
-      </c>
-      <c r="D750" s="3">
-        <v>157</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:7">
-      <c r="C751" s="6">
-        <v>15717</v>
-      </c>
-      <c r="D751" s="3">
-        <v>157</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:7">
-      <c r="C752" s="6">
-        <v>15718</v>
-      </c>
-      <c r="D752" s="3">
-        <v>157</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="3:7">
-      <c r="C753" s="6">
-        <v>15719</v>
-      </c>
-      <c r="D753" s="3">
-        <v>157</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="3:7">
-      <c r="C754" s="6">
-        <v>15720</v>
-      </c>
-      <c r="D754" s="3">
-        <v>157</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="3:7">
-      <c r="C755" s="6">
-        <v>15721</v>
-      </c>
-      <c r="D755" s="3">
-        <v>157</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="3:7">
-      <c r="C756" s="6">
-        <v>15722</v>
-      </c>
-      <c r="D756" s="3">
-        <v>157</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="3:7">
-      <c r="C757" s="6">
-        <v>15723</v>
-      </c>
-      <c r="D757" s="3">
-        <v>157</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="3:7">
-      <c r="C758" s="6">
-        <v>15724</v>
-      </c>
-      <c r="D758" s="3">
-        <v>157</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="3:7">
-      <c r="C759" s="6">
-        <v>15725</v>
-      </c>
-      <c r="D759" s="3">
-        <v>157</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋158泰坦神殿</t>
+  </si>
+  <si>
+    <t>#先锋159</t>
   </si>
   <si>
     <t>Center</t>
@@ -973,6 +976,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
@@ -1260,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12875,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>15901</v>
+      </c>
+      <c r="D683" s="3">
+        <v>159</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20405</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>15902</v>
+      </c>
+      <c r="D684" s="3">
+        <v>159</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20406</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>15903</v>
+      </c>
+      <c r="D685" s="3">
+        <v>159</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20407</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>15904</v>
+      </c>
+      <c r="D686" s="3">
+        <v>159</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20408</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>15905</v>
+      </c>
+      <c r="D687" s="3">
+        <v>159</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>15906</v>
+      </c>
+      <c r="D688" s="3">
+        <v>159</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>15907</v>
+      </c>
+      <c r="D689" s="3">
+        <v>159</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>15908</v>
+      </c>
+      <c r="D690" s="3">
+        <v>159</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>15909</v>
+      </c>
+      <c r="D691" s="3">
+        <v>159</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>15910</v>
+      </c>
+      <c r="D692" s="3">
+        <v>159</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>15911</v>
+      </c>
+      <c r="D693" s="3">
+        <v>159</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>15912</v>
+      </c>
+      <c r="D694" s="3">
+        <v>159</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>15913</v>
+      </c>
+      <c r="D695" s="3">
+        <v>159</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>15914</v>
+      </c>
+      <c r="D696" s="3">
+        <v>159</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>15915</v>
+      </c>
+      <c r="D697" s="3">
+        <v>159</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>15916</v>
+      </c>
+      <c r="D698" s="3">
+        <v>159</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>15917</v>
+      </c>
+      <c r="D699" s="3">
+        <v>159</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>15918</v>
+      </c>
+      <c r="D700" s="3">
+        <v>159</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>15919</v>
+      </c>
+      <c r="D701" s="3">
+        <v>159</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>15920</v>
+      </c>
+      <c r="D702" s="3">
+        <v>159</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>15921</v>
+      </c>
+      <c r="D703" s="3">
+        <v>159</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>15922</v>
+      </c>
+      <c r="D704" s="3">
+        <v>159</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>15923</v>
+      </c>
+      <c r="D705" s="3">
+        <v>159</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>15924</v>
+      </c>
+      <c r="D706" s="3">
+        <v>159</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>15925</v>
+      </c>
+      <c r="D707" s="3">
+        <v>159</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13437,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13455,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13473,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13491,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13511,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13609,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -184,9 +184,6 @@
     <t>#先锋84区龙的传人</t>
   </si>
   <si>
-    <t>#先锋85区春意阑珊</t>
-  </si>
-  <si>
     <t>#先锋89区诗情画意</t>
   </si>
   <si>
@@ -205,22 +202,13 @@
     <t>#先锋139吉祥如意</t>
   </si>
   <si>
-    <t>#先锋143湖光月色</t>
-  </si>
-  <si>
     <t>#先锋147紫禁之巅</t>
-  </si>
-  <si>
-    <t>#先锋149春暖花开</t>
   </si>
   <si>
     <t>#先锋151龙裔国度</t>
   </si>
   <si>
     <t>#先锋153荣耀之路</t>
-  </si>
-  <si>
-    <t>#先锋154荣耀之路</t>
   </si>
   <si>
     <t>#先锋155雷霆万钧</t>
@@ -235,7 +223,10 @@
     <t>#先锋158泰坦神殿</t>
   </si>
   <si>
-    <t>#先锋159</t>
+    <t>#先锋159星辰之巅</t>
+  </si>
+  <si>
+    <t>#先锋160微风草原</t>
   </si>
   <si>
     <t>Center</t>
@@ -1270,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O629"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -5369,10 +5360,10 @@
         <v>51</v>
       </c>
       <c r="C241" s="6">
-        <v>8501</v>
+        <v>8901</v>
       </c>
       <c r="D241" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E241" s="5">
         <v>1</v>
@@ -5384,17 +5375,17 @@
         <v>15</v>
       </c>
       <c r="H241" s="3">
-        <v>20635</v>
+        <v>20435</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="6">
-        <v>8502</v>
+        <v>8902</v>
       </c>
       <c r="D242" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E242" s="5">
         <v>1</v>
@@ -5406,15 +5397,15 @@
         <v>16</v>
       </c>
       <c r="H242" s="3">
-        <v>20636</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="243" spans="3:8">
       <c r="C243" s="6">
-        <v>8503</v>
+        <v>8903</v>
       </c>
       <c r="D243" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E243" s="5">
         <v>1</v>
@@ -5426,15 +5417,15 @@
         <v>18</v>
       </c>
       <c r="H243" s="3">
-        <v>20637</v>
+        <v>20437</v>
       </c>
     </row>
     <row r="244" spans="3:8">
       <c r="C244" s="6">
-        <v>8504</v>
+        <v>8904</v>
       </c>
       <c r="D244" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E244" s="3">
         <v>1</v>
@@ -5446,15 +5437,15 @@
         <v>19</v>
       </c>
       <c r="H244" s="3">
-        <v>20638</v>
+        <v>20438</v>
       </c>
     </row>
     <row r="245" spans="3:7">
       <c r="C245" s="6">
-        <v>8505</v>
+        <v>8905</v>
       </c>
       <c r="D245" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E245" s="5">
         <v>1</v>
@@ -5468,10 +5459,10 @@
     </row>
     <row r="246" spans="3:7">
       <c r="C246" s="6">
-        <v>8506</v>
+        <v>8906</v>
       </c>
       <c r="D246" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E246" s="5">
         <v>1</v>
@@ -5485,10 +5476,10 @@
     </row>
     <row r="247" spans="3:7">
       <c r="C247" s="6">
-        <v>8507</v>
+        <v>8907</v>
       </c>
       <c r="D247" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E247" s="5">
         <v>1</v>
@@ -5502,10 +5493,10 @@
     </row>
     <row r="248" spans="3:7">
       <c r="C248" s="6">
-        <v>8508</v>
+        <v>8908</v>
       </c>
       <c r="D248" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E248" s="3">
         <v>1</v>
@@ -5519,10 +5510,10 @@
     </row>
     <row r="249" spans="3:7">
       <c r="C249" s="6">
-        <v>8509</v>
+        <v>8909</v>
       </c>
       <c r="D249" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E249" s="5">
         <v>1</v>
@@ -5536,10 +5527,10 @@
     </row>
     <row r="250" spans="3:7">
       <c r="C250" s="6">
-        <v>8510</v>
+        <v>8910</v>
       </c>
       <c r="D250" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E250" s="5">
         <v>1</v>
@@ -5553,10 +5544,10 @@
     </row>
     <row r="251" spans="3:7">
       <c r="C251" s="6">
-        <v>8511</v>
+        <v>8911</v>
       </c>
       <c r="D251" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E251" s="5">
         <v>1</v>
@@ -5570,10 +5561,10 @@
     </row>
     <row r="252" spans="3:7">
       <c r="C252" s="6">
-        <v>8512</v>
+        <v>8912</v>
       </c>
       <c r="D252" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E252" s="3">
         <v>1</v>
@@ -5587,10 +5578,10 @@
     </row>
     <row r="253" spans="3:7">
       <c r="C253" s="6">
-        <v>8513</v>
+        <v>8913</v>
       </c>
       <c r="D253" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E253" s="5">
         <v>1</v>
@@ -5604,10 +5595,10 @@
     </row>
     <row r="254" spans="3:7">
       <c r="C254" s="6">
-        <v>8514</v>
+        <v>8914</v>
       </c>
       <c r="D254" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E254" s="5">
         <v>1</v>
@@ -5621,10 +5612,10 @@
     </row>
     <row r="255" spans="3:7">
       <c r="C255" s="6">
-        <v>8515</v>
+        <v>8915</v>
       </c>
       <c r="D255" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E255" s="5">
         <v>1</v>
@@ -5638,10 +5629,10 @@
     </row>
     <row r="256" spans="3:7">
       <c r="C256" s="6">
-        <v>8516</v>
+        <v>8916</v>
       </c>
       <c r="D256" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E256" s="3">
         <v>1</v>
@@ -5655,10 +5646,10 @@
     </row>
     <row r="257" spans="3:7">
       <c r="C257" s="6">
-        <v>8517</v>
+        <v>8917</v>
       </c>
       <c r="D257" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E257" s="5">
         <v>1</v>
@@ -5672,10 +5663,10 @@
     </row>
     <row r="258" spans="3:7">
       <c r="C258" s="6">
-        <v>8518</v>
+        <v>8918</v>
       </c>
       <c r="D258" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E258" s="5">
         <v>1</v>
@@ -5689,10 +5680,10 @@
     </row>
     <row r="259" spans="3:7">
       <c r="C259" s="6">
-        <v>8519</v>
+        <v>8919</v>
       </c>
       <c r="D259" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E259" s="5">
         <v>1</v>
@@ -5706,10 +5697,10 @@
     </row>
     <row r="260" spans="3:7">
       <c r="C260" s="6">
-        <v>8520</v>
+        <v>8920</v>
       </c>
       <c r="D260" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E260" s="3">
         <v>1</v>
@@ -5723,10 +5714,10 @@
     </row>
     <row r="261" spans="3:7">
       <c r="C261" s="6">
-        <v>8521</v>
+        <v>8921</v>
       </c>
       <c r="D261" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E261" s="5">
         <v>1</v>
@@ -5740,10 +5731,10 @@
     </row>
     <row r="262" spans="3:7">
       <c r="C262" s="6">
-        <v>8522</v>
+        <v>8922</v>
       </c>
       <c r="D262" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E262" s="5">
         <v>1</v>
@@ -5757,10 +5748,10 @@
     </row>
     <row r="263" spans="3:7">
       <c r="C263" s="6">
-        <v>8523</v>
+        <v>8923</v>
       </c>
       <c r="D263" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E263" s="5">
         <v>1</v>
@@ -5774,10 +5765,10 @@
     </row>
     <row r="264" spans="3:7">
       <c r="C264" s="6">
-        <v>8524</v>
+        <v>8924</v>
       </c>
       <c r="D264" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E264" s="3">
         <v>1</v>
@@ -5791,10 +5782,10 @@
     </row>
     <row r="265" spans="3:7">
       <c r="C265" s="6">
-        <v>8525</v>
+        <v>8925</v>
       </c>
       <c r="D265" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E265" s="5">
         <v>1</v>
@@ -5811,10 +5802,10 @@
         <v>52</v>
       </c>
       <c r="C267" s="6">
-        <v>8901</v>
+        <v>10501</v>
       </c>
       <c r="D267" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E267" s="5">
         <v>1</v>
@@ -5826,17 +5817,17 @@
         <v>15</v>
       </c>
       <c r="H267" s="3">
-        <v>20435</v>
+        <v>20395</v>
       </c>
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="6">
-        <v>8902</v>
+        <v>10502</v>
       </c>
       <c r="D268" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E268" s="5">
         <v>1</v>
@@ -5848,15 +5839,15 @@
         <v>16</v>
       </c>
       <c r="H268" s="3">
-        <v>20436</v>
+        <v>20396</v>
       </c>
     </row>
     <row r="269" spans="3:8">
       <c r="C269" s="6">
-        <v>8903</v>
+        <v>10503</v>
       </c>
       <c r="D269" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E269" s="5">
         <v>1</v>
@@ -5868,15 +5859,15 @@
         <v>18</v>
       </c>
       <c r="H269" s="3">
-        <v>20437</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="270" spans="3:8">
       <c r="C270" s="6">
-        <v>8904</v>
+        <v>10504</v>
       </c>
       <c r="D270" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E270" s="3">
         <v>1</v>
@@ -5888,15 +5879,15 @@
         <v>19</v>
       </c>
       <c r="H270" s="3">
-        <v>20438</v>
+        <v>20398</v>
       </c>
     </row>
     <row r="271" spans="3:7">
       <c r="C271" s="6">
-        <v>8905</v>
+        <v>10505</v>
       </c>
       <c r="D271" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E271" s="5">
         <v>1</v>
@@ -5910,10 +5901,10 @@
     </row>
     <row r="272" spans="3:7">
       <c r="C272" s="6">
-        <v>8906</v>
+        <v>10506</v>
       </c>
       <c r="D272" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E272" s="5">
         <v>1</v>
@@ -5927,10 +5918,10 @@
     </row>
     <row r="273" spans="3:7">
       <c r="C273" s="6">
-        <v>8907</v>
+        <v>10507</v>
       </c>
       <c r="D273" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E273" s="5">
         <v>1</v>
@@ -5944,10 +5935,10 @@
     </row>
     <row r="274" spans="3:7">
       <c r="C274" s="6">
-        <v>8908</v>
+        <v>10508</v>
       </c>
       <c r="D274" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E274" s="3">
         <v>1</v>
@@ -5961,10 +5952,10 @@
     </row>
     <row r="275" spans="3:7">
       <c r="C275" s="6">
-        <v>8909</v>
+        <v>10509</v>
       </c>
       <c r="D275" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E275" s="5">
         <v>1</v>
@@ -5978,10 +5969,10 @@
     </row>
     <row r="276" spans="3:7">
       <c r="C276" s="6">
-        <v>8910</v>
+        <v>10510</v>
       </c>
       <c r="D276" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E276" s="5">
         <v>1</v>
@@ -5995,10 +5986,10 @@
     </row>
     <row r="277" spans="3:7">
       <c r="C277" s="6">
-        <v>8911</v>
+        <v>10511</v>
       </c>
       <c r="D277" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E277" s="5">
         <v>1</v>
@@ -6012,10 +6003,10 @@
     </row>
     <row r="278" spans="3:7">
       <c r="C278" s="6">
-        <v>8912</v>
+        <v>10512</v>
       </c>
       <c r="D278" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E278" s="3">
         <v>1</v>
@@ -6029,10 +6020,10 @@
     </row>
     <row r="279" spans="3:7">
       <c r="C279" s="6">
-        <v>8913</v>
+        <v>10513</v>
       </c>
       <c r="D279" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E279" s="5">
         <v>1</v>
@@ -6046,10 +6037,10 @@
     </row>
     <row r="280" spans="3:7">
       <c r="C280" s="6">
-        <v>8914</v>
+        <v>10514</v>
       </c>
       <c r="D280" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E280" s="5">
         <v>1</v>
@@ -6063,10 +6054,10 @@
     </row>
     <row r="281" spans="3:7">
       <c r="C281" s="6">
-        <v>8915</v>
+        <v>10515</v>
       </c>
       <c r="D281" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E281" s="5">
         <v>1</v>
@@ -6080,10 +6071,10 @@
     </row>
     <row r="282" spans="3:7">
       <c r="C282" s="6">
-        <v>8916</v>
+        <v>10516</v>
       </c>
       <c r="D282" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E282" s="3">
         <v>1</v>
@@ -6097,10 +6088,10 @@
     </row>
     <row r="283" spans="3:7">
       <c r="C283" s="6">
-        <v>8917</v>
+        <v>10517</v>
       </c>
       <c r="D283" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E283" s="5">
         <v>1</v>
@@ -6114,10 +6105,10 @@
     </row>
     <row r="284" spans="3:7">
       <c r="C284" s="6">
-        <v>8918</v>
+        <v>10518</v>
       </c>
       <c r="D284" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E284" s="5">
         <v>1</v>
@@ -6131,10 +6122,10 @@
     </row>
     <row r="285" spans="3:7">
       <c r="C285" s="6">
-        <v>8919</v>
+        <v>10519</v>
       </c>
       <c r="D285" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E285" s="5">
         <v>1</v>
@@ -6148,10 +6139,10 @@
     </row>
     <row r="286" spans="3:7">
       <c r="C286" s="6">
-        <v>8920</v>
+        <v>10520</v>
       </c>
       <c r="D286" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E286" s="3">
         <v>1</v>
@@ -6165,10 +6156,10 @@
     </row>
     <row r="287" spans="3:7">
       <c r="C287" s="6">
-        <v>8921</v>
+        <v>10521</v>
       </c>
       <c r="D287" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E287" s="5">
         <v>1</v>
@@ -6182,10 +6173,10 @@
     </row>
     <row r="288" spans="3:7">
       <c r="C288" s="6">
-        <v>8922</v>
+        <v>10522</v>
       </c>
       <c r="D288" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E288" s="5">
         <v>1</v>
@@ -6199,10 +6190,10 @@
     </row>
     <row r="289" spans="3:7">
       <c r="C289" s="6">
-        <v>8923</v>
+        <v>10523</v>
       </c>
       <c r="D289" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E289" s="5">
         <v>1</v>
@@ -6216,10 +6207,10 @@
     </row>
     <row r="290" spans="3:7">
       <c r="C290" s="6">
-        <v>8924</v>
+        <v>10524</v>
       </c>
       <c r="D290" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E290" s="3">
         <v>1</v>
@@ -6233,10 +6224,10 @@
     </row>
     <row r="291" spans="3:7">
       <c r="C291" s="6">
-        <v>8925</v>
+        <v>10525</v>
       </c>
       <c r="D291" s="3">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E291" s="5">
         <v>1</v>
@@ -6253,10 +6244,10 @@
         <v>53</v>
       </c>
       <c r="C293" s="6">
-        <v>10501</v>
+        <v>12101</v>
       </c>
       <c r="D293" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E293" s="5">
         <v>1</v>
@@ -6268,17 +6259,17 @@
         <v>15</v>
       </c>
       <c r="H293" s="3">
-        <v>20395</v>
+        <v>20465</v>
       </c>
     </row>
     <row r="294" spans="1:8">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="6">
-        <v>10502</v>
+        <v>12102</v>
       </c>
       <c r="D294" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E294" s="5">
         <v>1</v>
@@ -6290,15 +6281,15 @@
         <v>16</v>
       </c>
       <c r="H294" s="3">
-        <v>20396</v>
+        <v>20466</v>
       </c>
     </row>
     <row r="295" spans="3:8">
       <c r="C295" s="6">
-        <v>10503</v>
+        <v>12103</v>
       </c>
       <c r="D295" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E295" s="5">
         <v>1</v>
@@ -6310,15 +6301,15 @@
         <v>18</v>
       </c>
       <c r="H295" s="3">
-        <v>20397</v>
+        <v>20467</v>
       </c>
     </row>
     <row r="296" spans="3:8">
       <c r="C296" s="6">
-        <v>10504</v>
+        <v>12104</v>
       </c>
       <c r="D296" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E296" s="3">
         <v>1</v>
@@ -6330,15 +6321,15 @@
         <v>19</v>
       </c>
       <c r="H296" s="3">
-        <v>20398</v>
+        <v>20468</v>
       </c>
     </row>
     <row r="297" spans="3:7">
       <c r="C297" s="6">
-        <v>10505</v>
+        <v>12105</v>
       </c>
       <c r="D297" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E297" s="5">
         <v>1</v>
@@ -6352,10 +6343,10 @@
     </row>
     <row r="298" spans="3:7">
       <c r="C298" s="6">
-        <v>10506</v>
+        <v>12106</v>
       </c>
       <c r="D298" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E298" s="5">
         <v>1</v>
@@ -6369,10 +6360,10 @@
     </row>
     <row r="299" spans="3:7">
       <c r="C299" s="6">
-        <v>10507</v>
+        <v>12107</v>
       </c>
       <c r="D299" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E299" s="5">
         <v>1</v>
@@ -6386,10 +6377,10 @@
     </row>
     <row r="300" spans="3:7">
       <c r="C300" s="6">
-        <v>10508</v>
+        <v>12108</v>
       </c>
       <c r="D300" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E300" s="3">
         <v>1</v>
@@ -6403,10 +6394,10 @@
     </row>
     <row r="301" spans="3:7">
       <c r="C301" s="6">
-        <v>10509</v>
+        <v>12109</v>
       </c>
       <c r="D301" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E301" s="5">
         <v>1</v>
@@ -6420,10 +6411,10 @@
     </row>
     <row r="302" spans="3:7">
       <c r="C302" s="6">
-        <v>10510</v>
+        <v>12110</v>
       </c>
       <c r="D302" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E302" s="5">
         <v>1</v>
@@ -6437,10 +6428,10 @@
     </row>
     <row r="303" spans="3:7">
       <c r="C303" s="6">
-        <v>10511</v>
+        <v>12111</v>
       </c>
       <c r="D303" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E303" s="5">
         <v>1</v>
@@ -6454,10 +6445,10 @@
     </row>
     <row r="304" spans="3:7">
       <c r="C304" s="6">
-        <v>10512</v>
+        <v>12112</v>
       </c>
       <c r="D304" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E304" s="3">
         <v>1</v>
@@ -6471,10 +6462,10 @@
     </row>
     <row r="305" spans="3:7">
       <c r="C305" s="6">
-        <v>10513</v>
+        <v>12113</v>
       </c>
       <c r="D305" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E305" s="5">
         <v>1</v>
@@ -6488,10 +6479,10 @@
     </row>
     <row r="306" spans="3:7">
       <c r="C306" s="6">
-        <v>10514</v>
+        <v>12114</v>
       </c>
       <c r="D306" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E306" s="5">
         <v>1</v>
@@ -6505,10 +6496,10 @@
     </row>
     <row r="307" spans="3:7">
       <c r="C307" s="6">
-        <v>10515</v>
+        <v>12115</v>
       </c>
       <c r="D307" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E307" s="5">
         <v>1</v>
@@ -6522,10 +6513,10 @@
     </row>
     <row r="308" spans="3:7">
       <c r="C308" s="6">
-        <v>10516</v>
+        <v>12116</v>
       </c>
       <c r="D308" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E308" s="3">
         <v>1</v>
@@ -6539,10 +6530,10 @@
     </row>
     <row r="309" spans="3:7">
       <c r="C309" s="6">
-        <v>10517</v>
+        <v>12117</v>
       </c>
       <c r="D309" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E309" s="5">
         <v>1</v>
@@ -6556,10 +6547,10 @@
     </row>
     <row r="310" spans="3:7">
       <c r="C310" s="6">
-        <v>10518</v>
+        <v>12118</v>
       </c>
       <c r="D310" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E310" s="5">
         <v>1</v>
@@ -6573,10 +6564,10 @@
     </row>
     <row r="311" spans="3:7">
       <c r="C311" s="6">
-        <v>10519</v>
+        <v>12119</v>
       </c>
       <c r="D311" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E311" s="5">
         <v>1</v>
@@ -6590,10 +6581,10 @@
     </row>
     <row r="312" spans="3:7">
       <c r="C312" s="6">
-        <v>10520</v>
+        <v>12120</v>
       </c>
       <c r="D312" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E312" s="3">
         <v>1</v>
@@ -6607,10 +6598,10 @@
     </row>
     <row r="313" spans="3:7">
       <c r="C313" s="6">
-        <v>10521</v>
+        <v>12121</v>
       </c>
       <c r="D313" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E313" s="5">
         <v>1</v>
@@ -6624,10 +6615,10 @@
     </row>
     <row r="314" spans="3:7">
       <c r="C314" s="6">
-        <v>10522</v>
+        <v>12122</v>
       </c>
       <c r="D314" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E314" s="5">
         <v>1</v>
@@ -6641,10 +6632,10 @@
     </row>
     <row r="315" spans="3:7">
       <c r="C315" s="6">
-        <v>10523</v>
+        <v>12123</v>
       </c>
       <c r="D315" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E315" s="5">
         <v>1</v>
@@ -6658,10 +6649,10 @@
     </row>
     <row r="316" spans="3:7">
       <c r="C316" s="6">
-        <v>10524</v>
+        <v>12124</v>
       </c>
       <c r="D316" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E316" s="3">
         <v>1</v>
@@ -6675,10 +6666,10 @@
     </row>
     <row r="317" spans="3:7">
       <c r="C317" s="6">
-        <v>10525</v>
+        <v>12125</v>
       </c>
       <c r="D317" s="3">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E317" s="5">
         <v>1</v>
@@ -6695,10 +6686,10 @@
         <v>54</v>
       </c>
       <c r="C319" s="6">
-        <v>12101</v>
+        <v>12801</v>
       </c>
       <c r="D319" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E319" s="5">
         <v>1</v>
@@ -6710,17 +6701,17 @@
         <v>15</v>
       </c>
       <c r="H319" s="3">
-        <v>20465</v>
+        <v>20425</v>
       </c>
     </row>
     <row r="320" spans="1:8">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="6">
-        <v>12102</v>
+        <v>12802</v>
       </c>
       <c r="D320" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E320" s="5">
         <v>1</v>
@@ -6732,15 +6723,15 @@
         <v>16</v>
       </c>
       <c r="H320" s="3">
-        <v>20466</v>
+        <v>20426</v>
       </c>
     </row>
     <row r="321" spans="3:8">
       <c r="C321" s="6">
-        <v>12103</v>
+        <v>12803</v>
       </c>
       <c r="D321" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E321" s="5">
         <v>1</v>
@@ -6752,15 +6743,15 @@
         <v>18</v>
       </c>
       <c r="H321" s="3">
-        <v>20467</v>
+        <v>20427</v>
       </c>
     </row>
     <row r="322" spans="3:8">
       <c r="C322" s="6">
-        <v>12104</v>
+        <v>12804</v>
       </c>
       <c r="D322" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E322" s="3">
         <v>1</v>
@@ -6772,15 +6763,15 @@
         <v>19</v>
       </c>
       <c r="H322" s="3">
-        <v>20468</v>
+        <v>20428</v>
       </c>
     </row>
     <row r="323" spans="3:7">
       <c r="C323" s="6">
-        <v>12105</v>
+        <v>12805</v>
       </c>
       <c r="D323" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E323" s="5">
         <v>1</v>
@@ -6794,10 +6785,10 @@
     </row>
     <row r="324" spans="3:7">
       <c r="C324" s="6">
-        <v>12106</v>
+        <v>12806</v>
       </c>
       <c r="D324" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E324" s="5">
         <v>1</v>
@@ -6811,10 +6802,10 @@
     </row>
     <row r="325" spans="3:7">
       <c r="C325" s="6">
-        <v>12107</v>
+        <v>12807</v>
       </c>
       <c r="D325" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E325" s="5">
         <v>1</v>
@@ -6828,10 +6819,10 @@
     </row>
     <row r="326" spans="3:7">
       <c r="C326" s="6">
-        <v>12108</v>
+        <v>12808</v>
       </c>
       <c r="D326" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E326" s="3">
         <v>1</v>
@@ -6845,10 +6836,10 @@
     </row>
     <row r="327" spans="3:7">
       <c r="C327" s="6">
-        <v>12109</v>
+        <v>12809</v>
       </c>
       <c r="D327" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E327" s="5">
         <v>1</v>
@@ -6862,10 +6853,10 @@
     </row>
     <row r="328" spans="3:7">
       <c r="C328" s="6">
-        <v>12110</v>
+        <v>12810</v>
       </c>
       <c r="D328" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E328" s="5">
         <v>1</v>
@@ -6879,10 +6870,10 @@
     </row>
     <row r="329" spans="3:7">
       <c r="C329" s="6">
-        <v>12111</v>
+        <v>12811</v>
       </c>
       <c r="D329" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E329" s="5">
         <v>1</v>
@@ -6896,10 +6887,10 @@
     </row>
     <row r="330" spans="3:7">
       <c r="C330" s="6">
-        <v>12112</v>
+        <v>12812</v>
       </c>
       <c r="D330" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E330" s="3">
         <v>1</v>
@@ -6913,10 +6904,10 @@
     </row>
     <row r="331" spans="3:7">
       <c r="C331" s="6">
-        <v>12113</v>
+        <v>12813</v>
       </c>
       <c r="D331" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E331" s="5">
         <v>1</v>
@@ -6930,10 +6921,10 @@
     </row>
     <row r="332" spans="3:7">
       <c r="C332" s="6">
-        <v>12114</v>
+        <v>12814</v>
       </c>
       <c r="D332" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E332" s="5">
         <v>1</v>
@@ -6947,10 +6938,10 @@
     </row>
     <row r="333" spans="3:7">
       <c r="C333" s="6">
-        <v>12115</v>
+        <v>12815</v>
       </c>
       <c r="D333" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E333" s="5">
         <v>1</v>
@@ -6964,10 +6955,10 @@
     </row>
     <row r="334" spans="3:7">
       <c r="C334" s="6">
-        <v>12116</v>
+        <v>12816</v>
       </c>
       <c r="D334" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E334" s="3">
         <v>1</v>
@@ -6981,10 +6972,10 @@
     </row>
     <row r="335" spans="3:7">
       <c r="C335" s="6">
-        <v>12117</v>
+        <v>12817</v>
       </c>
       <c r="D335" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E335" s="5">
         <v>1</v>
@@ -6998,10 +6989,10 @@
     </row>
     <row r="336" spans="3:7">
       <c r="C336" s="6">
-        <v>12118</v>
+        <v>12818</v>
       </c>
       <c r="D336" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E336" s="5">
         <v>1</v>
@@ -7015,10 +7006,10 @@
     </row>
     <row r="337" spans="3:7">
       <c r="C337" s="6">
-        <v>12119</v>
+        <v>12819</v>
       </c>
       <c r="D337" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E337" s="5">
         <v>1</v>
@@ -7032,10 +7023,10 @@
     </row>
     <row r="338" spans="3:7">
       <c r="C338" s="6">
-        <v>12120</v>
+        <v>12820</v>
       </c>
       <c r="D338" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E338" s="3">
         <v>1</v>
@@ -7049,10 +7040,10 @@
     </row>
     <row r="339" spans="3:7">
       <c r="C339" s="6">
-        <v>12121</v>
+        <v>12821</v>
       </c>
       <c r="D339" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E339" s="5">
         <v>1</v>
@@ -7066,10 +7057,10 @@
     </row>
     <row r="340" spans="3:7">
       <c r="C340" s="6">
-        <v>12122</v>
+        <v>12822</v>
       </c>
       <c r="D340" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E340" s="5">
         <v>1</v>
@@ -7083,10 +7074,10 @@
     </row>
     <row r="341" spans="3:7">
       <c r="C341" s="6">
-        <v>12123</v>
+        <v>12823</v>
       </c>
       <c r="D341" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E341" s="5">
         <v>1</v>
@@ -7100,10 +7091,10 @@
     </row>
     <row r="342" spans="3:7">
       <c r="C342" s="6">
-        <v>12124</v>
+        <v>12824</v>
       </c>
       <c r="D342" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E342" s="3">
         <v>1</v>
@@ -7117,10 +7108,10 @@
     </row>
     <row r="343" spans="3:7">
       <c r="C343" s="6">
-        <v>12125</v>
+        <v>12825</v>
       </c>
       <c r="D343" s="3">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E343" s="5">
         <v>1</v>
@@ -7137,10 +7128,10 @@
         <v>55</v>
       </c>
       <c r="C345" s="6">
-        <v>12801</v>
+        <v>13101</v>
       </c>
       <c r="D345" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E345" s="5">
         <v>1</v>
@@ -7152,17 +7143,17 @@
         <v>15</v>
       </c>
       <c r="H345" s="3">
-        <v>20425</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="6">
-        <v>12802</v>
+        <v>13102</v>
       </c>
       <c r="D346" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E346" s="5">
         <v>1</v>
@@ -7174,15 +7165,15 @@
         <v>16</v>
       </c>
       <c r="H346" s="3">
-        <v>20426</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="347" spans="3:8">
       <c r="C347" s="6">
-        <v>12803</v>
+        <v>13103</v>
       </c>
       <c r="D347" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E347" s="5">
         <v>1</v>
@@ -7194,17 +7185,17 @@
         <v>18</v>
       </c>
       <c r="H347" s="3">
-        <v>20427</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="348" spans="3:8">
       <c r="C348" s="6">
-        <v>12804</v>
+        <v>13104</v>
       </c>
       <c r="D348" s="3">
-        <v>128</v>
-      </c>
-      <c r="E348" s="3">
+        <v>131</v>
+      </c>
+      <c r="E348" s="5">
         <v>1</v>
       </c>
       <c r="F348" s="3" t="s">
@@ -7214,17 +7205,17 @@
         <v>19</v>
       </c>
       <c r="H348" s="3">
-        <v>20428</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="349" spans="3:7">
       <c r="C349" s="6">
-        <v>12805</v>
+        <v>13105</v>
       </c>
       <c r="D349" s="3">
-        <v>128</v>
-      </c>
-      <c r="E349" s="5">
+        <v>131</v>
+      </c>
+      <c r="E349" s="3">
         <v>1</v>
       </c>
       <c r="F349" s="3" t="s">
@@ -7236,10 +7227,10 @@
     </row>
     <row r="350" spans="3:7">
       <c r="C350" s="6">
-        <v>12806</v>
+        <v>13106</v>
       </c>
       <c r="D350" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E350" s="5">
         <v>1</v>
@@ -7253,10 +7244,10 @@
     </row>
     <row r="351" spans="3:7">
       <c r="C351" s="6">
-        <v>12807</v>
+        <v>13107</v>
       </c>
       <c r="D351" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E351" s="5">
         <v>1</v>
@@ -7270,12 +7261,12 @@
     </row>
     <row r="352" spans="3:7">
       <c r="C352" s="6">
-        <v>12808</v>
+        <v>13108</v>
       </c>
       <c r="D352" s="3">
-        <v>128</v>
-      </c>
-      <c r="E352" s="3">
+        <v>131</v>
+      </c>
+      <c r="E352" s="5">
         <v>1</v>
       </c>
       <c r="F352" s="3" t="s">
@@ -7287,12 +7278,12 @@
     </row>
     <row r="353" spans="3:7">
       <c r="C353" s="6">
-        <v>12809</v>
+        <v>13109</v>
       </c>
       <c r="D353" s="3">
-        <v>128</v>
-      </c>
-      <c r="E353" s="5">
+        <v>131</v>
+      </c>
+      <c r="E353" s="3">
         <v>1</v>
       </c>
       <c r="F353" s="3" t="s">
@@ -7304,10 +7295,10 @@
     </row>
     <row r="354" spans="3:7">
       <c r="C354" s="6">
-        <v>12810</v>
+        <v>13110</v>
       </c>
       <c r="D354" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E354" s="5">
         <v>1</v>
@@ -7321,10 +7312,10 @@
     </row>
     <row r="355" spans="3:7">
       <c r="C355" s="6">
-        <v>12811</v>
+        <v>13111</v>
       </c>
       <c r="D355" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E355" s="5">
         <v>1</v>
@@ -7338,12 +7329,12 @@
     </row>
     <row r="356" spans="3:7">
       <c r="C356" s="6">
-        <v>12812</v>
+        <v>13112</v>
       </c>
       <c r="D356" s="3">
-        <v>128</v>
-      </c>
-      <c r="E356" s="3">
+        <v>131</v>
+      </c>
+      <c r="E356" s="5">
         <v>1</v>
       </c>
       <c r="F356" s="3" t="s">
@@ -7355,12 +7346,12 @@
     </row>
     <row r="357" spans="3:7">
       <c r="C357" s="6">
-        <v>12813</v>
+        <v>13113</v>
       </c>
       <c r="D357" s="3">
-        <v>128</v>
-      </c>
-      <c r="E357" s="5">
+        <v>131</v>
+      </c>
+      <c r="E357" s="3">
         <v>1</v>
       </c>
       <c r="F357" s="3" t="s">
@@ -7372,10 +7363,10 @@
     </row>
     <row r="358" spans="3:7">
       <c r="C358" s="6">
-        <v>12814</v>
+        <v>13114</v>
       </c>
       <c r="D358" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E358" s="5">
         <v>1</v>
@@ -7389,10 +7380,10 @@
     </row>
     <row r="359" spans="3:7">
       <c r="C359" s="6">
-        <v>12815</v>
+        <v>13115</v>
       </c>
       <c r="D359" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E359" s="5">
         <v>1</v>
@@ -7406,12 +7397,12 @@
     </row>
     <row r="360" spans="3:7">
       <c r="C360" s="6">
-        <v>12816</v>
+        <v>13116</v>
       </c>
       <c r="D360" s="3">
-        <v>128</v>
-      </c>
-      <c r="E360" s="3">
+        <v>131</v>
+      </c>
+      <c r="E360" s="5">
         <v>1</v>
       </c>
       <c r="F360" s="3" t="s">
@@ -7423,12 +7414,12 @@
     </row>
     <row r="361" spans="3:7">
       <c r="C361" s="6">
-        <v>12817</v>
+        <v>13117</v>
       </c>
       <c r="D361" s="3">
-        <v>128</v>
-      </c>
-      <c r="E361" s="5">
+        <v>131</v>
+      </c>
+      <c r="E361" s="3">
         <v>1</v>
       </c>
       <c r="F361" s="3" t="s">
@@ -7440,10 +7431,10 @@
     </row>
     <row r="362" spans="3:7">
       <c r="C362" s="6">
-        <v>12818</v>
+        <v>13118</v>
       </c>
       <c r="D362" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E362" s="5">
         <v>1</v>
@@ -7457,10 +7448,10 @@
     </row>
     <row r="363" spans="3:7">
       <c r="C363" s="6">
-        <v>12819</v>
+        <v>13119</v>
       </c>
       <c r="D363" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E363" s="5">
         <v>1</v>
@@ -7474,12 +7465,12 @@
     </row>
     <row r="364" spans="3:7">
       <c r="C364" s="6">
-        <v>12820</v>
+        <v>13120</v>
       </c>
       <c r="D364" s="3">
-        <v>128</v>
-      </c>
-      <c r="E364" s="3">
+        <v>131</v>
+      </c>
+      <c r="E364" s="5">
         <v>1</v>
       </c>
       <c r="F364" s="3" t="s">
@@ -7491,12 +7482,12 @@
     </row>
     <row r="365" spans="3:7">
       <c r="C365" s="6">
-        <v>12821</v>
+        <v>13121</v>
       </c>
       <c r="D365" s="3">
-        <v>128</v>
-      </c>
-      <c r="E365" s="5">
+        <v>131</v>
+      </c>
+      <c r="E365" s="3">
         <v>1</v>
       </c>
       <c r="F365" s="3" t="s">
@@ -7508,10 +7499,10 @@
     </row>
     <row r="366" spans="3:7">
       <c r="C366" s="6">
-        <v>12822</v>
+        <v>13122</v>
       </c>
       <c r="D366" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E366" s="5">
         <v>1</v>
@@ -7525,10 +7516,10 @@
     </row>
     <row r="367" spans="3:7">
       <c r="C367" s="6">
-        <v>12823</v>
+        <v>13123</v>
       </c>
       <c r="D367" s="3">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E367" s="5">
         <v>1</v>
@@ -7542,12 +7533,12 @@
     </row>
     <row r="368" spans="3:7">
       <c r="C368" s="6">
-        <v>12824</v>
+        <v>13124</v>
       </c>
       <c r="D368" s="3">
-        <v>128</v>
-      </c>
-      <c r="E368" s="3">
+        <v>131</v>
+      </c>
+      <c r="E368" s="5">
         <v>1</v>
       </c>
       <c r="F368" s="3" t="s">
@@ -7559,12 +7550,12 @@
     </row>
     <row r="369" spans="3:7">
       <c r="C369" s="6">
-        <v>12825</v>
+        <v>13125</v>
       </c>
       <c r="D369" s="3">
-        <v>128</v>
-      </c>
-      <c r="E369" s="5">
+        <v>131</v>
+      </c>
+      <c r="E369" s="3">
         <v>1</v>
       </c>
       <c r="F369" s="3" t="s">
@@ -7579,10 +7570,10 @@
         <v>56</v>
       </c>
       <c r="C371" s="6">
-        <v>13101</v>
+        <v>13901</v>
       </c>
       <c r="D371" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E371" s="5">
         <v>1</v>
@@ -7594,17 +7585,17 @@
         <v>15</v>
       </c>
       <c r="H371" s="3">
-        <v>20515</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="6">
-        <v>13102</v>
+        <v>13902</v>
       </c>
       <c r="D372" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E372" s="5">
         <v>1</v>
@@ -7616,15 +7607,15 @@
         <v>16</v>
       </c>
       <c r="H372" s="3">
-        <v>20516</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="373" spans="3:8">
       <c r="C373" s="6">
-        <v>13103</v>
+        <v>13903</v>
       </c>
       <c r="D373" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E373" s="5">
         <v>1</v>
@@ -7636,15 +7627,15 @@
         <v>18</v>
       </c>
       <c r="H373" s="3">
-        <v>20517</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="374" spans="3:8">
       <c r="C374" s="6">
-        <v>13104</v>
+        <v>13904</v>
       </c>
       <c r="D374" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E374" s="5">
         <v>1</v>
@@ -7656,15 +7647,15 @@
         <v>19</v>
       </c>
       <c r="H374" s="3">
-        <v>20518</v>
+        <v>20478</v>
       </c>
     </row>
     <row r="375" spans="3:7">
       <c r="C375" s="6">
-        <v>13105</v>
+        <v>13905</v>
       </c>
       <c r="D375" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E375" s="3">
         <v>1</v>
@@ -7678,10 +7669,10 @@
     </row>
     <row r="376" spans="3:7">
       <c r="C376" s="6">
-        <v>13106</v>
+        <v>13906</v>
       </c>
       <c r="D376" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E376" s="5">
         <v>1</v>
@@ -7695,10 +7686,10 @@
     </row>
     <row r="377" spans="3:7">
       <c r="C377" s="6">
-        <v>13107</v>
+        <v>13907</v>
       </c>
       <c r="D377" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E377" s="5">
         <v>1</v>
@@ -7712,10 +7703,10 @@
     </row>
     <row r="378" spans="3:7">
       <c r="C378" s="6">
-        <v>13108</v>
+        <v>13908</v>
       </c>
       <c r="D378" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E378" s="5">
         <v>1</v>
@@ -7729,10 +7720,10 @@
     </row>
     <row r="379" spans="3:7">
       <c r="C379" s="6">
-        <v>13109</v>
+        <v>13909</v>
       </c>
       <c r="D379" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E379" s="3">
         <v>1</v>
@@ -7746,10 +7737,10 @@
     </row>
     <row r="380" spans="3:7">
       <c r="C380" s="6">
-        <v>13110</v>
+        <v>13910</v>
       </c>
       <c r="D380" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E380" s="5">
         <v>1</v>
@@ -7763,10 +7754,10 @@
     </row>
     <row r="381" spans="3:7">
       <c r="C381" s="6">
-        <v>13111</v>
+        <v>13911</v>
       </c>
       <c r="D381" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E381" s="5">
         <v>1</v>
@@ -7780,10 +7771,10 @@
     </row>
     <row r="382" spans="3:7">
       <c r="C382" s="6">
-        <v>13112</v>
+        <v>13912</v>
       </c>
       <c r="D382" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E382" s="5">
         <v>1</v>
@@ -7797,10 +7788,10 @@
     </row>
     <row r="383" spans="3:7">
       <c r="C383" s="6">
-        <v>13113</v>
+        <v>13913</v>
       </c>
       <c r="D383" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E383" s="3">
         <v>1</v>
@@ -7814,10 +7805,10 @@
     </row>
     <row r="384" spans="3:7">
       <c r="C384" s="6">
-        <v>13114</v>
+        <v>13914</v>
       </c>
       <c r="D384" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E384" s="5">
         <v>1</v>
@@ -7831,10 +7822,10 @@
     </row>
     <row r="385" spans="3:7">
       <c r="C385" s="6">
-        <v>13115</v>
+        <v>13915</v>
       </c>
       <c r="D385" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E385" s="5">
         <v>1</v>
@@ -7848,10 +7839,10 @@
     </row>
     <row r="386" spans="3:7">
       <c r="C386" s="6">
-        <v>13116</v>
+        <v>13916</v>
       </c>
       <c r="D386" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E386" s="5">
         <v>1</v>
@@ -7865,10 +7856,10 @@
     </row>
     <row r="387" spans="3:7">
       <c r="C387" s="6">
-        <v>13117</v>
+        <v>13917</v>
       </c>
       <c r="D387" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E387" s="3">
         <v>1</v>
@@ -7882,10 +7873,10 @@
     </row>
     <row r="388" spans="3:7">
       <c r="C388" s="6">
-        <v>13118</v>
+        <v>13918</v>
       </c>
       <c r="D388" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E388" s="5">
         <v>1</v>
@@ -7899,10 +7890,10 @@
     </row>
     <row r="389" spans="3:7">
       <c r="C389" s="6">
-        <v>13119</v>
+        <v>13919</v>
       </c>
       <c r="D389" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E389" s="5">
         <v>1</v>
@@ -7916,10 +7907,10 @@
     </row>
     <row r="390" spans="3:7">
       <c r="C390" s="6">
-        <v>13120</v>
+        <v>13920</v>
       </c>
       <c r="D390" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E390" s="5">
         <v>1</v>
@@ -7933,10 +7924,10 @@
     </row>
     <row r="391" spans="3:7">
       <c r="C391" s="6">
-        <v>13121</v>
+        <v>13921</v>
       </c>
       <c r="D391" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E391" s="3">
         <v>1</v>
@@ -7950,10 +7941,10 @@
     </row>
     <row r="392" spans="3:7">
       <c r="C392" s="6">
-        <v>13122</v>
+        <v>13922</v>
       </c>
       <c r="D392" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E392" s="5">
         <v>1</v>
@@ -7967,10 +7958,10 @@
     </row>
     <row r="393" spans="3:7">
       <c r="C393" s="6">
-        <v>13123</v>
+        <v>13923</v>
       </c>
       <c r="D393" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E393" s="5">
         <v>1</v>
@@ -7984,10 +7975,10 @@
     </row>
     <row r="394" spans="3:7">
       <c r="C394" s="6">
-        <v>13124</v>
+        <v>13924</v>
       </c>
       <c r="D394" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E394" s="5">
         <v>1</v>
@@ -8001,10 +7992,10 @@
     </row>
     <row r="395" spans="3:7">
       <c r="C395" s="6">
-        <v>13125</v>
+        <v>13925</v>
       </c>
       <c r="D395" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E395" s="3">
         <v>1</v>
@@ -8021,10 +8012,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>13901</v>
+        <v>14701</v>
       </c>
       <c r="D397" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8036,17 +8027,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20475</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>13902</v>
+        <v>14702</v>
       </c>
       <c r="D398" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8058,15 +8049,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20476</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="399" spans="3:8">
       <c r="C399" s="6">
-        <v>13903</v>
+        <v>14703</v>
       </c>
       <c r="D399" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8078,15 +8069,15 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20477</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="400" spans="3:8">
       <c r="C400" s="6">
-        <v>13904</v>
+        <v>14704</v>
       </c>
       <c r="D400" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E400" s="5">
         <v>1</v>
@@ -8098,15 +8089,15 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20478</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>13905</v>
+        <v>14705</v>
       </c>
       <c r="D401" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E401" s="3">
         <v>1</v>
@@ -8120,10 +8111,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>13906</v>
+        <v>14706</v>
       </c>
       <c r="D402" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8137,10 +8128,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>13907</v>
+        <v>14707</v>
       </c>
       <c r="D403" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8154,10 +8145,10 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>13908</v>
+        <v>14708</v>
       </c>
       <c r="D404" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E404" s="5">
         <v>1</v>
@@ -8171,10 +8162,10 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>13909</v>
+        <v>14709</v>
       </c>
       <c r="D405" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E405" s="3">
         <v>1</v>
@@ -8188,10 +8179,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>13910</v>
+        <v>14710</v>
       </c>
       <c r="D406" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8205,10 +8196,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>13911</v>
+        <v>14711</v>
       </c>
       <c r="D407" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8222,10 +8213,10 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>13912</v>
+        <v>14712</v>
       </c>
       <c r="D408" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E408" s="5">
         <v>1</v>
@@ -8239,10 +8230,10 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>13913</v>
+        <v>14713</v>
       </c>
       <c r="D409" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E409" s="3">
         <v>1</v>
@@ -8256,10 +8247,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>13914</v>
+        <v>14714</v>
       </c>
       <c r="D410" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8273,10 +8264,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>13915</v>
+        <v>14715</v>
       </c>
       <c r="D411" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8290,10 +8281,10 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>13916</v>
+        <v>14716</v>
       </c>
       <c r="D412" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E412" s="5">
         <v>1</v>
@@ -8307,10 +8298,10 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>13917</v>
+        <v>14717</v>
       </c>
       <c r="D413" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E413" s="3">
         <v>1</v>
@@ -8324,10 +8315,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>13918</v>
+        <v>14718</v>
       </c>
       <c r="D414" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8341,10 +8332,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>13919</v>
+        <v>14719</v>
       </c>
       <c r="D415" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8358,10 +8349,10 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>13920</v>
+        <v>14720</v>
       </c>
       <c r="D416" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E416" s="5">
         <v>1</v>
@@ -8375,10 +8366,10 @@
     </row>
     <row r="417" spans="3:7">
       <c r="C417" s="6">
-        <v>13921</v>
+        <v>14721</v>
       </c>
       <c r="D417" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E417" s="3">
         <v>1</v>
@@ -8392,10 +8383,10 @@
     </row>
     <row r="418" spans="3:7">
       <c r="C418" s="6">
-        <v>13922</v>
+        <v>14722</v>
       </c>
       <c r="D418" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8409,10 +8400,10 @@
     </row>
     <row r="419" spans="3:7">
       <c r="C419" s="6">
-        <v>13923</v>
+        <v>14723</v>
       </c>
       <c r="D419" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8426,10 +8417,10 @@
     </row>
     <row r="420" spans="3:7">
       <c r="C420" s="6">
-        <v>13924</v>
+        <v>14724</v>
       </c>
       <c r="D420" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E420" s="5">
         <v>1</v>
@@ -8443,10 +8434,10 @@
     </row>
     <row r="421" spans="3:7">
       <c r="C421" s="6">
-        <v>13925</v>
+        <v>14725</v>
       </c>
       <c r="D421" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E421" s="3">
         <v>1</v>
@@ -8463,10 +8454,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>14301</v>
+        <v>15101</v>
       </c>
       <c r="D423" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8478,17 +8469,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20575</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>14302</v>
+        <v>15102</v>
       </c>
       <c r="D424" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8500,15 +8491,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20576</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>14303</v>
+        <v>15103</v>
       </c>
       <c r="D425" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8520,15 +8511,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20577</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>14304</v>
+        <v>15104</v>
       </c>
       <c r="D426" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8540,15 +8531,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20578</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>14305</v>
+        <v>15105</v>
       </c>
       <c r="D427" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8562,10 +8553,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>14306</v>
+        <v>15106</v>
       </c>
       <c r="D428" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8579,10 +8570,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>14307</v>
+        <v>15107</v>
       </c>
       <c r="D429" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8596,10 +8587,10 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>14308</v>
+        <v>15108</v>
       </c>
       <c r="D430" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8613,10 +8604,10 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>14309</v>
+        <v>15109</v>
       </c>
       <c r="D431" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8630,10 +8621,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>14310</v>
+        <v>15110</v>
       </c>
       <c r="D432" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8647,10 +8638,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>14311</v>
+        <v>15111</v>
       </c>
       <c r="D433" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8664,10 +8655,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>14312</v>
+        <v>15112</v>
       </c>
       <c r="D434" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8681,10 +8672,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>14313</v>
+        <v>15113</v>
       </c>
       <c r="D435" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8698,10 +8689,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>14314</v>
+        <v>15114</v>
       </c>
       <c r="D436" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8715,10 +8706,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>14315</v>
+        <v>15115</v>
       </c>
       <c r="D437" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8732,10 +8723,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>14316</v>
+        <v>15116</v>
       </c>
       <c r="D438" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8749,10 +8740,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>14317</v>
+        <v>15117</v>
       </c>
       <c r="D439" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8766,10 +8757,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>14318</v>
+        <v>15118</v>
       </c>
       <c r="D440" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8783,10 +8774,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>14319</v>
+        <v>15119</v>
       </c>
       <c r="D441" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8800,10 +8791,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>14320</v>
+        <v>15120</v>
       </c>
       <c r="D442" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8817,10 +8808,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>14321</v>
+        <v>15121</v>
       </c>
       <c r="D443" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8834,10 +8825,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>14322</v>
+        <v>15122</v>
       </c>
       <c r="D444" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8851,10 +8842,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>14323</v>
+        <v>15123</v>
       </c>
       <c r="D445" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8868,10 +8859,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>14324</v>
+        <v>15124</v>
       </c>
       <c r="D446" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8885,10 +8876,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>14325</v>
+        <v>15125</v>
       </c>
       <c r="D447" s="3">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8905,10 +8896,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>14701</v>
+        <v>15301</v>
       </c>
       <c r="D449" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8920,17 +8911,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20495</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>14702</v>
+        <v>15302</v>
       </c>
       <c r="D450" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8942,15 +8933,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20496</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>14703</v>
+        <v>15303</v>
       </c>
       <c r="D451" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8962,15 +8953,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20497</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>14704</v>
+        <v>15304</v>
       </c>
       <c r="D452" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8982,15 +8973,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20498</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>14705</v>
+        <v>15305</v>
       </c>
       <c r="D453" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9004,10 +8995,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>14706</v>
+        <v>15306</v>
       </c>
       <c r="D454" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9021,10 +9012,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>14707</v>
+        <v>15307</v>
       </c>
       <c r="D455" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9038,10 +9029,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>14708</v>
+        <v>15308</v>
       </c>
       <c r="D456" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9055,10 +9046,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>14709</v>
+        <v>15309</v>
       </c>
       <c r="D457" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9072,10 +9063,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>14710</v>
+        <v>15310</v>
       </c>
       <c r="D458" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9089,10 +9080,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>14711</v>
+        <v>15311</v>
       </c>
       <c r="D459" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9106,10 +9097,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>14712</v>
+        <v>15312</v>
       </c>
       <c r="D460" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9123,10 +9114,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>14713</v>
+        <v>15313</v>
       </c>
       <c r="D461" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9140,10 +9131,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>14714</v>
+        <v>15314</v>
       </c>
       <c r="D462" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9157,10 +9148,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>14715</v>
+        <v>15315</v>
       </c>
       <c r="D463" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9174,10 +9165,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>14716</v>
+        <v>15316</v>
       </c>
       <c r="D464" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9191,10 +9182,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>14717</v>
+        <v>15317</v>
       </c>
       <c r="D465" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9208,10 +9199,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>14718</v>
+        <v>15318</v>
       </c>
       <c r="D466" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9225,10 +9216,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>14719</v>
+        <v>15319</v>
       </c>
       <c r="D467" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9242,10 +9233,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>14720</v>
+        <v>15320</v>
       </c>
       <c r="D468" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9259,10 +9250,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>14721</v>
+        <v>15321</v>
       </c>
       <c r="D469" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9276,10 +9267,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>14722</v>
+        <v>15322</v>
       </c>
       <c r="D470" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9293,10 +9284,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>14723</v>
+        <v>15323</v>
       </c>
       <c r="D471" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9310,10 +9301,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>14724</v>
+        <v>15324</v>
       </c>
       <c r="D472" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9327,10 +9318,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>14725</v>
+        <v>15325</v>
       </c>
       <c r="D473" s="3">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9347,10 +9338,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>14901</v>
+        <v>15501</v>
       </c>
       <c r="D475" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9362,17 +9353,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20445</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>14902</v>
+        <v>15502</v>
       </c>
       <c r="D476" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9384,15 +9375,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20446</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>14903</v>
+        <v>15503</v>
       </c>
       <c r="D477" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9404,15 +9395,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20447</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>14904</v>
+        <v>15504</v>
       </c>
       <c r="D478" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9424,15 +9415,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20448</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>14905</v>
+        <v>15505</v>
       </c>
       <c r="D479" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9446,10 +9437,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>14906</v>
+        <v>15506</v>
       </c>
       <c r="D480" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9463,10 +9454,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>14907</v>
+        <v>15507</v>
       </c>
       <c r="D481" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9480,10 +9471,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>14908</v>
+        <v>15508</v>
       </c>
       <c r="D482" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9497,10 +9488,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>14909</v>
+        <v>15509</v>
       </c>
       <c r="D483" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9514,10 +9505,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>14910</v>
+        <v>15510</v>
       </c>
       <c r="D484" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9531,10 +9522,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>14911</v>
+        <v>15511</v>
       </c>
       <c r="D485" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9548,10 +9539,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>14912</v>
+        <v>15512</v>
       </c>
       <c r="D486" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9565,10 +9556,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>14913</v>
+        <v>15513</v>
       </c>
       <c r="D487" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9582,10 +9573,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>14914</v>
+        <v>15514</v>
       </c>
       <c r="D488" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9599,10 +9590,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>14915</v>
+        <v>15515</v>
       </c>
       <c r="D489" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9616,10 +9607,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>14916</v>
+        <v>15516</v>
       </c>
       <c r="D490" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9633,10 +9624,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>14917</v>
+        <v>15517</v>
       </c>
       <c r="D491" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9650,10 +9641,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>14918</v>
+        <v>15518</v>
       </c>
       <c r="D492" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9667,10 +9658,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>14919</v>
+        <v>15519</v>
       </c>
       <c r="D493" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9684,10 +9675,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>14920</v>
+        <v>15520</v>
       </c>
       <c r="D494" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9701,10 +9692,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>14921</v>
+        <v>15521</v>
       </c>
       <c r="D495" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9718,10 +9709,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>14922</v>
+        <v>15522</v>
       </c>
       <c r="D496" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9735,10 +9726,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>14923</v>
+        <v>15523</v>
       </c>
       <c r="D497" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9752,10 +9743,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>14924</v>
+        <v>15524</v>
       </c>
       <c r="D498" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9769,10 +9760,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>14925</v>
+        <v>15525</v>
       </c>
       <c r="D499" s="3">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9789,10 +9780,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>15101</v>
+        <v>15601</v>
       </c>
       <c r="D501" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9804,17 +9795,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20415</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>15102</v>
+        <v>15602</v>
       </c>
       <c r="D502" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9826,15 +9817,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20416</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>15103</v>
+        <v>15603</v>
       </c>
       <c r="D503" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9846,15 +9837,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20417</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>15104</v>
+        <v>15604</v>
       </c>
       <c r="D504" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9866,15 +9857,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20418</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>15105</v>
+        <v>15605</v>
       </c>
       <c r="D505" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9888,10 +9879,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>15106</v>
+        <v>15606</v>
       </c>
       <c r="D506" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9905,10 +9896,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>15107</v>
+        <v>15607</v>
       </c>
       <c r="D507" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9922,10 +9913,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>15108</v>
+        <v>15608</v>
       </c>
       <c r="D508" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9939,10 +9930,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>15109</v>
+        <v>15609</v>
       </c>
       <c r="D509" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9956,10 +9947,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>15110</v>
+        <v>15610</v>
       </c>
       <c r="D510" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9973,10 +9964,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>15111</v>
+        <v>15611</v>
       </c>
       <c r="D511" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9990,10 +9981,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>15112</v>
+        <v>15612</v>
       </c>
       <c r="D512" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10007,10 +9998,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>15113</v>
+        <v>15613</v>
       </c>
       <c r="D513" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10024,10 +10015,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>15114</v>
+        <v>15614</v>
       </c>
       <c r="D514" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10041,10 +10032,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>15115</v>
+        <v>15615</v>
       </c>
       <c r="D515" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10058,10 +10049,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>15116</v>
+        <v>15616</v>
       </c>
       <c r="D516" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10075,10 +10066,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>15117</v>
+        <v>15617</v>
       </c>
       <c r="D517" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10092,10 +10083,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>15118</v>
+        <v>15618</v>
       </c>
       <c r="D518" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10109,10 +10100,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>15119</v>
+        <v>15619</v>
       </c>
       <c r="D519" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10126,10 +10117,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>15120</v>
+        <v>15620</v>
       </c>
       <c r="D520" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10143,10 +10134,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>15121</v>
+        <v>15621</v>
       </c>
       <c r="D521" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10160,10 +10151,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>15122</v>
+        <v>15622</v>
       </c>
       <c r="D522" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10177,10 +10168,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>15123</v>
+        <v>15623</v>
       </c>
       <c r="D523" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10194,10 +10185,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>15124</v>
+        <v>15624</v>
       </c>
       <c r="D524" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10211,10 +10202,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>15125</v>
+        <v>15625</v>
       </c>
       <c r="D525" s="3">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10231,10 +10222,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>15301</v>
+        <v>15701</v>
       </c>
       <c r="D527" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10246,17 +10237,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20565</v>
+        <v>20645</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>15302</v>
+        <v>15702</v>
       </c>
       <c r="D528" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10268,15 +10259,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20566</v>
+        <v>20646</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>15303</v>
+        <v>15703</v>
       </c>
       <c r="D529" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10288,15 +10279,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20567</v>
+        <v>20647</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>15304</v>
+        <v>15704</v>
       </c>
       <c r="D530" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10308,15 +10299,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20568</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>15305</v>
+        <v>15705</v>
       </c>
       <c r="D531" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10330,10 +10321,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>15306</v>
+        <v>15706</v>
       </c>
       <c r="D532" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10347,10 +10338,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>15307</v>
+        <v>15707</v>
       </c>
       <c r="D533" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10364,10 +10355,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>15308</v>
+        <v>15708</v>
       </c>
       <c r="D534" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10381,10 +10372,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>15309</v>
+        <v>15709</v>
       </c>
       <c r="D535" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10398,10 +10389,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>15310</v>
+        <v>15710</v>
       </c>
       <c r="D536" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10415,10 +10406,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>15311</v>
+        <v>15711</v>
       </c>
       <c r="D537" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10432,10 +10423,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>15312</v>
+        <v>15712</v>
       </c>
       <c r="D538" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10449,10 +10440,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>15313</v>
+        <v>15713</v>
       </c>
       <c r="D539" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10466,10 +10457,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>15314</v>
+        <v>15714</v>
       </c>
       <c r="D540" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10483,10 +10474,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>15315</v>
+        <v>15715</v>
       </c>
       <c r="D541" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10500,10 +10491,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>15316</v>
+        <v>15716</v>
       </c>
       <c r="D542" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10517,10 +10508,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>15317</v>
+        <v>15717</v>
       </c>
       <c r="D543" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10534,10 +10525,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>15318</v>
+        <v>15718</v>
       </c>
       <c r="D544" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10551,10 +10542,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>15319</v>
+        <v>15719</v>
       </c>
       <c r="D545" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10568,10 +10559,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>15320</v>
+        <v>15720</v>
       </c>
       <c r="D546" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10585,10 +10576,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>15321</v>
+        <v>15721</v>
       </c>
       <c r="D547" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10602,10 +10593,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>15322</v>
+        <v>15722</v>
       </c>
       <c r="D548" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10619,10 +10610,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>15323</v>
+        <v>15723</v>
       </c>
       <c r="D549" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10636,10 +10627,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>15324</v>
+        <v>15724</v>
       </c>
       <c r="D550" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10653,10 +10644,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>15325</v>
+        <v>15725</v>
       </c>
       <c r="D551" s="3">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10673,10 +10664,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>15401</v>
+        <v>15801</v>
       </c>
       <c r="D553" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10688,17 +10679,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20595</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>15402</v>
+        <v>15802</v>
       </c>
       <c r="D554" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10710,15 +10701,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20596</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>15403</v>
+        <v>15803</v>
       </c>
       <c r="D555" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10730,15 +10721,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20597</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>15404</v>
+        <v>15804</v>
       </c>
       <c r="D556" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10750,15 +10741,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20598</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>15405</v>
+        <v>15805</v>
       </c>
       <c r="D557" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10772,10 +10763,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>15406</v>
+        <v>15806</v>
       </c>
       <c r="D558" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10789,10 +10780,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>15407</v>
+        <v>15807</v>
       </c>
       <c r="D559" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10806,10 +10797,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>15408</v>
+        <v>15808</v>
       </c>
       <c r="D560" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10823,10 +10814,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>15409</v>
+        <v>15809</v>
       </c>
       <c r="D561" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10840,10 +10831,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>15410</v>
+        <v>15810</v>
       </c>
       <c r="D562" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10857,10 +10848,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>15411</v>
+        <v>15811</v>
       </c>
       <c r="D563" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10874,10 +10865,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>15412</v>
+        <v>15812</v>
       </c>
       <c r="D564" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10891,10 +10882,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>15413</v>
+        <v>15813</v>
       </c>
       <c r="D565" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10908,10 +10899,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>15414</v>
+        <v>15814</v>
       </c>
       <c r="D566" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10925,10 +10916,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>15415</v>
+        <v>15815</v>
       </c>
       <c r="D567" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10942,10 +10933,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>15416</v>
+        <v>15816</v>
       </c>
       <c r="D568" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10959,10 +10950,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>15417</v>
+        <v>15817</v>
       </c>
       <c r="D569" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10976,10 +10967,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>15418</v>
+        <v>15818</v>
       </c>
       <c r="D570" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10993,10 +10984,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>15419</v>
+        <v>15819</v>
       </c>
       <c r="D571" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11010,10 +11001,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>15420</v>
+        <v>15820</v>
       </c>
       <c r="D572" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11027,10 +11018,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>15421</v>
+        <v>15821</v>
       </c>
       <c r="D573" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11044,10 +11035,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>15422</v>
+        <v>15822</v>
       </c>
       <c r="D574" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11061,10 +11052,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>15423</v>
+        <v>15823</v>
       </c>
       <c r="D575" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11078,10 +11069,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>15424</v>
+        <v>15824</v>
       </c>
       <c r="D576" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11095,10 +11086,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>15425</v>
+        <v>15825</v>
       </c>
       <c r="D577" s="3">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11115,10 +11106,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>15501</v>
+        <v>15901</v>
       </c>
       <c r="D579" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11130,17 +11121,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20605</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>15502</v>
+        <v>15902</v>
       </c>
       <c r="D580" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11152,15 +11143,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20606</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>15503</v>
+        <v>15903</v>
       </c>
       <c r="D581" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11172,15 +11163,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20607</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>15504</v>
+        <v>15904</v>
       </c>
       <c r="D582" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11192,15 +11183,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20608</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>15505</v>
+        <v>15905</v>
       </c>
       <c r="D583" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11214,10 +11205,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>15506</v>
+        <v>15906</v>
       </c>
       <c r="D584" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11231,10 +11222,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>15507</v>
+        <v>15907</v>
       </c>
       <c r="D585" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11248,10 +11239,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>15508</v>
+        <v>15908</v>
       </c>
       <c r="D586" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11265,10 +11256,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>15509</v>
+        <v>15909</v>
       </c>
       <c r="D587" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11282,10 +11273,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>15510</v>
+        <v>15910</v>
       </c>
       <c r="D588" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11299,10 +11290,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>15511</v>
+        <v>15911</v>
       </c>
       <c r="D589" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11316,10 +11307,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>15512</v>
+        <v>15912</v>
       </c>
       <c r="D590" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11333,10 +11324,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>15513</v>
+        <v>15913</v>
       </c>
       <c r="D591" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11350,10 +11341,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>15514</v>
+        <v>15914</v>
       </c>
       <c r="D592" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11367,10 +11358,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>15515</v>
+        <v>15915</v>
       </c>
       <c r="D593" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11384,10 +11375,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>15516</v>
+        <v>15916</v>
       </c>
       <c r="D594" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11401,10 +11392,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>15517</v>
+        <v>15917</v>
       </c>
       <c r="D595" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11418,10 +11409,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>15518</v>
+        <v>15918</v>
       </c>
       <c r="D596" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11435,10 +11426,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>15519</v>
+        <v>15919</v>
       </c>
       <c r="D597" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11452,10 +11443,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>15520</v>
+        <v>15920</v>
       </c>
       <c r="D598" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11469,10 +11460,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>15521</v>
+        <v>15921</v>
       </c>
       <c r="D599" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11486,10 +11477,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>15522</v>
+        <v>15922</v>
       </c>
       <c r="D600" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11503,10 +11494,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>15523</v>
+        <v>15923</v>
       </c>
       <c r="D601" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11520,10 +11511,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>15524</v>
+        <v>15924</v>
       </c>
       <c r="D602" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11537,10 +11528,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>15525</v>
+        <v>15925</v>
       </c>
       <c r="D603" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11557,10 +11548,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>15601</v>
+        <v>16001</v>
       </c>
       <c r="D605" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11572,17 +11563,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20615</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>15602</v>
+        <v>16002</v>
       </c>
       <c r="D606" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11594,15 +11585,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20616</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>15603</v>
+        <v>16003</v>
       </c>
       <c r="D607" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11614,15 +11605,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20617</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>15604</v>
+        <v>16004</v>
       </c>
       <c r="D608" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11634,15 +11625,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20618</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>15605</v>
+        <v>16005</v>
       </c>
       <c r="D609" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11656,10 +11647,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>15606</v>
+        <v>16006</v>
       </c>
       <c r="D610" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11673,10 +11664,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>15607</v>
+        <v>16007</v>
       </c>
       <c r="D611" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11690,10 +11681,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>15608</v>
+        <v>16008</v>
       </c>
       <c r="D612" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11707,10 +11698,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>15609</v>
+        <v>16009</v>
       </c>
       <c r="D613" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11724,10 +11715,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>15610</v>
+        <v>16010</v>
       </c>
       <c r="D614" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11741,10 +11732,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>15611</v>
+        <v>16011</v>
       </c>
       <c r="D615" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11758,10 +11749,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>15612</v>
+        <v>16012</v>
       </c>
       <c r="D616" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11775,10 +11766,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>15613</v>
+        <v>16013</v>
       </c>
       <c r="D617" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11792,10 +11783,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>15614</v>
+        <v>16014</v>
       </c>
       <c r="D618" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11809,10 +11800,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>15615</v>
+        <v>16015</v>
       </c>
       <c r="D619" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11826,10 +11817,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>15616</v>
+        <v>16016</v>
       </c>
       <c r="D620" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11843,10 +11834,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>15617</v>
+        <v>16017</v>
       </c>
       <c r="D621" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11860,10 +11851,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>15618</v>
+        <v>16018</v>
       </c>
       <c r="D622" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11877,10 +11868,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>15619</v>
+        <v>16019</v>
       </c>
       <c r="D623" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11894,10 +11885,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>15620</v>
+        <v>16020</v>
       </c>
       <c r="D624" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11911,10 +11902,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>15621</v>
+        <v>16021</v>
       </c>
       <c r="D625" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11928,10 +11919,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>15622</v>
+        <v>16022</v>
       </c>
       <c r="D626" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11945,10 +11936,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>15623</v>
+        <v>16023</v>
       </c>
       <c r="D627" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11962,10 +11953,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>15624</v>
+        <v>16024</v>
       </c>
       <c r="D628" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11979,10 +11970,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>15625</v>
+        <v>16025</v>
       </c>
       <c r="D629" s="3">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11991,1332 +11982,6 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8">
-      <c r="A631" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C631" s="6">
-        <v>15701</v>
-      </c>
-      <c r="D631" s="3">
-        <v>157</v>
-      </c>
-      <c r="E631" s="5">
-        <v>1</v>
-      </c>
-      <c r="F631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H631" s="3">
-        <v>20645</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8">
-      <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
-      <c r="C632" s="6">
-        <v>15702</v>
-      </c>
-      <c r="D632" s="3">
-        <v>157</v>
-      </c>
-      <c r="E632" s="5">
-        <v>1</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H632" s="3">
-        <v>20646</v>
-      </c>
-    </row>
-    <row r="633" spans="3:8">
-      <c r="C633" s="6">
-        <v>15703</v>
-      </c>
-      <c r="D633" s="3">
-        <v>157</v>
-      </c>
-      <c r="E633" s="5">
-        <v>1</v>
-      </c>
-      <c r="F633" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G633" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H633" s="3">
-        <v>20647</v>
-      </c>
-    </row>
-    <row r="634" spans="3:8">
-      <c r="C634" s="6">
-        <v>15704</v>
-      </c>
-      <c r="D634" s="3">
-        <v>157</v>
-      </c>
-      <c r="E634" s="5">
-        <v>1</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H634" s="3">
-        <v>20648</v>
-      </c>
-    </row>
-    <row r="635" spans="3:7">
-      <c r="C635" s="6">
-        <v>15705</v>
-      </c>
-      <c r="D635" s="3">
-        <v>157</v>
-      </c>
-      <c r="E635" s="3">
-        <v>1</v>
-      </c>
-      <c r="F635" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G635" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="636" spans="3:7">
-      <c r="C636" s="6">
-        <v>15706</v>
-      </c>
-      <c r="D636" s="3">
-        <v>157</v>
-      </c>
-      <c r="E636" s="5">
-        <v>1</v>
-      </c>
-      <c r="F636" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G636" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="637" spans="3:7">
-      <c r="C637" s="6">
-        <v>15707</v>
-      </c>
-      <c r="D637" s="3">
-        <v>157</v>
-      </c>
-      <c r="E637" s="5">
-        <v>1</v>
-      </c>
-      <c r="F637" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G637" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="638" spans="3:7">
-      <c r="C638" s="6">
-        <v>15708</v>
-      </c>
-      <c r="D638" s="3">
-        <v>157</v>
-      </c>
-      <c r="E638" s="5">
-        <v>1</v>
-      </c>
-      <c r="F638" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G638" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="639" spans="3:7">
-      <c r="C639" s="6">
-        <v>15709</v>
-      </c>
-      <c r="D639" s="3">
-        <v>157</v>
-      </c>
-      <c r="E639" s="3">
-        <v>1</v>
-      </c>
-      <c r="F639" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G639" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="640" spans="3:7">
-      <c r="C640" s="6">
-        <v>15710</v>
-      </c>
-      <c r="D640" s="3">
-        <v>157</v>
-      </c>
-      <c r="E640" s="5">
-        <v>1</v>
-      </c>
-      <c r="F640" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G640" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="641" spans="3:7">
-      <c r="C641" s="6">
-        <v>15711</v>
-      </c>
-      <c r="D641" s="3">
-        <v>157</v>
-      </c>
-      <c r="E641" s="5">
-        <v>1</v>
-      </c>
-      <c r="F641" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G641" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="642" spans="3:7">
-      <c r="C642" s="6">
-        <v>15712</v>
-      </c>
-      <c r="D642" s="3">
-        <v>157</v>
-      </c>
-      <c r="E642" s="5">
-        <v>1</v>
-      </c>
-      <c r="F642" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G642" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="643" spans="3:7">
-      <c r="C643" s="6">
-        <v>15713</v>
-      </c>
-      <c r="D643" s="3">
-        <v>157</v>
-      </c>
-      <c r="E643" s="3">
-        <v>1</v>
-      </c>
-      <c r="F643" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G643" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="644" spans="3:7">
-      <c r="C644" s="6">
-        <v>15714</v>
-      </c>
-      <c r="D644" s="3">
-        <v>157</v>
-      </c>
-      <c r="E644" s="5">
-        <v>1</v>
-      </c>
-      <c r="F644" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G644" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="645" spans="3:7">
-      <c r="C645" s="6">
-        <v>15715</v>
-      </c>
-      <c r="D645" s="3">
-        <v>157</v>
-      </c>
-      <c r="E645" s="5">
-        <v>1</v>
-      </c>
-      <c r="F645" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G645" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="646" spans="3:7">
-      <c r="C646" s="6">
-        <v>15716</v>
-      </c>
-      <c r="D646" s="3">
-        <v>157</v>
-      </c>
-      <c r="E646" s="5">
-        <v>1</v>
-      </c>
-      <c r="F646" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G646" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="647" spans="3:7">
-      <c r="C647" s="6">
-        <v>15717</v>
-      </c>
-      <c r="D647" s="3">
-        <v>157</v>
-      </c>
-      <c r="E647" s="3">
-        <v>1</v>
-      </c>
-      <c r="F647" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G647" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="648" spans="3:7">
-      <c r="C648" s="6">
-        <v>15718</v>
-      </c>
-      <c r="D648" s="3">
-        <v>157</v>
-      </c>
-      <c r="E648" s="5">
-        <v>1</v>
-      </c>
-      <c r="F648" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G648" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="649" spans="3:7">
-      <c r="C649" s="6">
-        <v>15719</v>
-      </c>
-      <c r="D649" s="3">
-        <v>157</v>
-      </c>
-      <c r="E649" s="5">
-        <v>1</v>
-      </c>
-      <c r="F649" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G649" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="650" spans="3:7">
-      <c r="C650" s="6">
-        <v>15720</v>
-      </c>
-      <c r="D650" s="3">
-        <v>157</v>
-      </c>
-      <c r="E650" s="5">
-        <v>1</v>
-      </c>
-      <c r="F650" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G650" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="651" spans="3:7">
-      <c r="C651" s="6">
-        <v>15721</v>
-      </c>
-      <c r="D651" s="3">
-        <v>157</v>
-      </c>
-      <c r="E651" s="3">
-        <v>1</v>
-      </c>
-      <c r="F651" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G651" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="652" spans="3:7">
-      <c r="C652" s="6">
-        <v>15722</v>
-      </c>
-      <c r="D652" s="3">
-        <v>157</v>
-      </c>
-      <c r="E652" s="5">
-        <v>1</v>
-      </c>
-      <c r="F652" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G652" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="653" spans="3:7">
-      <c r="C653" s="6">
-        <v>15723</v>
-      </c>
-      <c r="D653" s="3">
-        <v>157</v>
-      </c>
-      <c r="E653" s="5">
-        <v>1</v>
-      </c>
-      <c r="F653" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G653" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="654" spans="3:7">
-      <c r="C654" s="6">
-        <v>15724</v>
-      </c>
-      <c r="D654" s="3">
-        <v>157</v>
-      </c>
-      <c r="E654" s="5">
-        <v>1</v>
-      </c>
-      <c r="F654" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G654" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="655" spans="3:7">
-      <c r="C655" s="6">
-        <v>15725</v>
-      </c>
-      <c r="D655" s="3">
-        <v>157</v>
-      </c>
-      <c r="E655" s="3">
-        <v>1</v>
-      </c>
-      <c r="F655" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G655" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="657" spans="1:8">
-      <c r="A657" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C657" s="6">
-        <v>15801</v>
-      </c>
-      <c r="D657" s="3">
-        <v>158</v>
-      </c>
-      <c r="E657" s="5">
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H657" s="3">
-        <v>20375</v>
-      </c>
-    </row>
-    <row r="658" spans="1:8">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-      <c r="C658" s="6">
-        <v>15802</v>
-      </c>
-      <c r="D658" s="3">
-        <v>158</v>
-      </c>
-      <c r="E658" s="5">
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H658" s="3">
-        <v>20376</v>
-      </c>
-    </row>
-    <row r="659" spans="3:8">
-      <c r="C659" s="6">
-        <v>15803</v>
-      </c>
-      <c r="D659" s="3">
-        <v>158</v>
-      </c>
-      <c r="E659" s="5">
-        <v>1</v>
-      </c>
-      <c r="F659" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G659" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H659" s="3">
-        <v>20377</v>
-      </c>
-    </row>
-    <row r="660" spans="3:8">
-      <c r="C660" s="6">
-        <v>15804</v>
-      </c>
-      <c r="D660" s="3">
-        <v>158</v>
-      </c>
-      <c r="E660" s="5">
-        <v>1</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H660" s="3">
-        <v>20378</v>
-      </c>
-    </row>
-    <row r="661" spans="3:7">
-      <c r="C661" s="6">
-        <v>15805</v>
-      </c>
-      <c r="D661" s="3">
-        <v>158</v>
-      </c>
-      <c r="E661" s="3">
-        <v>1</v>
-      </c>
-      <c r="F661" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G661" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="662" spans="3:7">
-      <c r="C662" s="6">
-        <v>15806</v>
-      </c>
-      <c r="D662" s="3">
-        <v>158</v>
-      </c>
-      <c r="E662" s="5">
-        <v>1</v>
-      </c>
-      <c r="F662" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G662" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="663" spans="3:7">
-      <c r="C663" s="6">
-        <v>15807</v>
-      </c>
-      <c r="D663" s="3">
-        <v>158</v>
-      </c>
-      <c r="E663" s="5">
-        <v>1</v>
-      </c>
-      <c r="F663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G663" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="664" spans="3:7">
-      <c r="C664" s="6">
-        <v>15808</v>
-      </c>
-      <c r="D664" s="3">
-        <v>158</v>
-      </c>
-      <c r="E664" s="5">
-        <v>1</v>
-      </c>
-      <c r="F664" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G664" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="665" spans="3:7">
-      <c r="C665" s="6">
-        <v>15809</v>
-      </c>
-      <c r="D665" s="3">
-        <v>158</v>
-      </c>
-      <c r="E665" s="3">
-        <v>1</v>
-      </c>
-      <c r="F665" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G665" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="666" spans="3:7">
-      <c r="C666" s="6">
-        <v>15810</v>
-      </c>
-      <c r="D666" s="3">
-        <v>158</v>
-      </c>
-      <c r="E666" s="5">
-        <v>1</v>
-      </c>
-      <c r="F666" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G666" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="667" spans="3:7">
-      <c r="C667" s="6">
-        <v>15811</v>
-      </c>
-      <c r="D667" s="3">
-        <v>158</v>
-      </c>
-      <c r="E667" s="5">
-        <v>1</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G667" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="668" spans="3:7">
-      <c r="C668" s="6">
-        <v>15812</v>
-      </c>
-      <c r="D668" s="3">
-        <v>158</v>
-      </c>
-      <c r="E668" s="5">
-        <v>1</v>
-      </c>
-      <c r="F668" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G668" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="669" spans="3:7">
-      <c r="C669" s="6">
-        <v>15813</v>
-      </c>
-      <c r="D669" s="3">
-        <v>158</v>
-      </c>
-      <c r="E669" s="3">
-        <v>1</v>
-      </c>
-      <c r="F669" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G669" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="670" spans="3:7">
-      <c r="C670" s="6">
-        <v>15814</v>
-      </c>
-      <c r="D670" s="3">
-        <v>158</v>
-      </c>
-      <c r="E670" s="5">
-        <v>1</v>
-      </c>
-      <c r="F670" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G670" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="671" spans="3:7">
-      <c r="C671" s="6">
-        <v>15815</v>
-      </c>
-      <c r="D671" s="3">
-        <v>158</v>
-      </c>
-      <c r="E671" s="5">
-        <v>1</v>
-      </c>
-      <c r="F671" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G671" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="672" spans="3:7">
-      <c r="C672" s="6">
-        <v>15816</v>
-      </c>
-      <c r="D672" s="3">
-        <v>158</v>
-      </c>
-      <c r="E672" s="5">
-        <v>1</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G672" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="673" spans="3:7">
-      <c r="C673" s="6">
-        <v>15817</v>
-      </c>
-      <c r="D673" s="3">
-        <v>158</v>
-      </c>
-      <c r="E673" s="3">
-        <v>1</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G673" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="674" spans="3:7">
-      <c r="C674" s="6">
-        <v>15818</v>
-      </c>
-      <c r="D674" s="3">
-        <v>158</v>
-      </c>
-      <c r="E674" s="5">
-        <v>1</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G674" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="675" spans="3:7">
-      <c r="C675" s="6">
-        <v>15819</v>
-      </c>
-      <c r="D675" s="3">
-        <v>158</v>
-      </c>
-      <c r="E675" s="5">
-        <v>1</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G675" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="676" spans="3:7">
-      <c r="C676" s="6">
-        <v>15820</v>
-      </c>
-      <c r="D676" s="3">
-        <v>158</v>
-      </c>
-      <c r="E676" s="5">
-        <v>1</v>
-      </c>
-      <c r="F676" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G676" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="677" spans="3:7">
-      <c r="C677" s="6">
-        <v>15821</v>
-      </c>
-      <c r="D677" s="3">
-        <v>158</v>
-      </c>
-      <c r="E677" s="3">
-        <v>1</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G677" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="678" spans="3:7">
-      <c r="C678" s="6">
-        <v>15822</v>
-      </c>
-      <c r="D678" s="3">
-        <v>158</v>
-      </c>
-      <c r="E678" s="5">
-        <v>1</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G678" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="679" spans="3:7">
-      <c r="C679" s="6">
-        <v>15823</v>
-      </c>
-      <c r="D679" s="3">
-        <v>158</v>
-      </c>
-      <c r="E679" s="5">
-        <v>1</v>
-      </c>
-      <c r="F679" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G679" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="680" spans="3:7">
-      <c r="C680" s="6">
-        <v>15824</v>
-      </c>
-      <c r="D680" s="3">
-        <v>158</v>
-      </c>
-      <c r="E680" s="5">
-        <v>1</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G680" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="681" spans="3:7">
-      <c r="C681" s="6">
-        <v>15825</v>
-      </c>
-      <c r="D681" s="3">
-        <v>158</v>
-      </c>
-      <c r="E681" s="3">
-        <v>1</v>
-      </c>
-      <c r="F681" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>15901</v>
-      </c>
-      <c r="D683" s="3">
-        <v>159</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20405</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>15902</v>
-      </c>
-      <c r="D684" s="3">
-        <v>159</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20406</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>15903</v>
-      </c>
-      <c r="D685" s="3">
-        <v>159</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20407</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>15904</v>
-      </c>
-      <c r="D686" s="3">
-        <v>159</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20408</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>15905</v>
-      </c>
-      <c r="D687" s="3">
-        <v>159</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>15906</v>
-      </c>
-      <c r="D688" s="3">
-        <v>159</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>15907</v>
-      </c>
-      <c r="D689" s="3">
-        <v>159</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>15908</v>
-      </c>
-      <c r="D690" s="3">
-        <v>159</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>15909</v>
-      </c>
-      <c r="D691" s="3">
-        <v>159</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>15910</v>
-      </c>
-      <c r="D692" s="3">
-        <v>159</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>15911</v>
-      </c>
-      <c r="D693" s="3">
-        <v>159</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>15912</v>
-      </c>
-      <c r="D694" s="3">
-        <v>159</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>15913</v>
-      </c>
-      <c r="D695" s="3">
-        <v>159</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>15914</v>
-      </c>
-      <c r="D696" s="3">
-        <v>159</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>15915</v>
-      </c>
-      <c r="D697" s="3">
-        <v>159</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>15916</v>
-      </c>
-      <c r="D698" s="3">
-        <v>159</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>15917</v>
-      </c>
-      <c r="D699" s="3">
-        <v>159</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>15918</v>
-      </c>
-      <c r="D700" s="3">
-        <v>159</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>15919</v>
-      </c>
-      <c r="D701" s="3">
-        <v>159</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>15920</v>
-      </c>
-      <c r="D702" s="3">
-        <v>159</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>15921</v>
-      </c>
-      <c r="D703" s="3">
-        <v>159</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>15922</v>
-      </c>
-      <c r="D704" s="3">
-        <v>159</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>15923</v>
-      </c>
-      <c r="D705" s="3">
-        <v>159</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>15924</v>
-      </c>
-      <c r="D706" s="3">
-        <v>159</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>15925</v>
-      </c>
-      <c r="D707" s="3">
-        <v>159</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13437,10 +12102,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13455,10 +12120,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13473,10 +12138,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13491,10 +12156,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13511,10 +12176,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -13609,10 +12274,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>#先锋160微风草原</t>
+  </si>
+  <si>
+    <t>#先锋161时光镇</t>
   </si>
   <si>
     <t>Center</t>
@@ -1261,7 +1264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O629"/>
+  <dimension ref="A3:O655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -11982,6 +11985,448 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C631" s="6">
+        <v>16101</v>
+      </c>
+      <c r="D631" s="3">
+        <v>161</v>
+      </c>
+      <c r="E631" s="5">
+        <v>1</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H631" s="3">
+        <v>20445</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="6">
+        <v>16102</v>
+      </c>
+      <c r="D632" s="3">
+        <v>161</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H632" s="3">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="633" spans="3:8">
+      <c r="C633" s="6">
+        <v>16103</v>
+      </c>
+      <c r="D633" s="3">
+        <v>161</v>
+      </c>
+      <c r="E633" s="5">
+        <v>1</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H633" s="3">
+        <v>20447</v>
+      </c>
+    </row>
+    <row r="634" spans="3:8">
+      <c r="C634" s="6">
+        <v>16104</v>
+      </c>
+      <c r="D634" s="3">
+        <v>161</v>
+      </c>
+      <c r="E634" s="5">
+        <v>1</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H634" s="3">
+        <v>20448</v>
+      </c>
+    </row>
+    <row r="635" spans="3:7">
+      <c r="C635" s="6">
+        <v>16105</v>
+      </c>
+      <c r="D635" s="3">
+        <v>161</v>
+      </c>
+      <c r="E635" s="3">
+        <v>1</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G635" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="636" spans="3:7">
+      <c r="C636" s="6">
+        <v>16106</v>
+      </c>
+      <c r="D636" s="3">
+        <v>161</v>
+      </c>
+      <c r="E636" s="5">
+        <v>1</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="637" spans="3:7">
+      <c r="C637" s="6">
+        <v>16107</v>
+      </c>
+      <c r="D637" s="3">
+        <v>161</v>
+      </c>
+      <c r="E637" s="5">
+        <v>1</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="638" spans="3:7">
+      <c r="C638" s="6">
+        <v>16108</v>
+      </c>
+      <c r="D638" s="3">
+        <v>161</v>
+      </c>
+      <c r="E638" s="5">
+        <v>1</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="639" spans="3:7">
+      <c r="C639" s="6">
+        <v>16109</v>
+      </c>
+      <c r="D639" s="3">
+        <v>161</v>
+      </c>
+      <c r="E639" s="3">
+        <v>1</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="640" spans="3:7">
+      <c r="C640" s="6">
+        <v>16110</v>
+      </c>
+      <c r="D640" s="3">
+        <v>161</v>
+      </c>
+      <c r="E640" s="5">
+        <v>1</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="3:7">
+      <c r="C641" s="6">
+        <v>16111</v>
+      </c>
+      <c r="D641" s="3">
+        <v>161</v>
+      </c>
+      <c r="E641" s="5">
+        <v>1</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="642" spans="3:7">
+      <c r="C642" s="6">
+        <v>16112</v>
+      </c>
+      <c r="D642" s="3">
+        <v>161</v>
+      </c>
+      <c r="E642" s="5">
+        <v>1</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="643" spans="3:7">
+      <c r="C643" s="6">
+        <v>16113</v>
+      </c>
+      <c r="D643" s="3">
+        <v>161</v>
+      </c>
+      <c r="E643" s="3">
+        <v>1</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="644" spans="3:7">
+      <c r="C644" s="6">
+        <v>16114</v>
+      </c>
+      <c r="D644" s="3">
+        <v>161</v>
+      </c>
+      <c r="E644" s="5">
+        <v>1</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G644" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="645" spans="3:7">
+      <c r="C645" s="6">
+        <v>16115</v>
+      </c>
+      <c r="D645" s="3">
+        <v>161</v>
+      </c>
+      <c r="E645" s="5">
+        <v>1</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="646" spans="3:7">
+      <c r="C646" s="6">
+        <v>16116</v>
+      </c>
+      <c r="D646" s="3">
+        <v>161</v>
+      </c>
+      <c r="E646" s="5">
+        <v>1</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="647" spans="3:7">
+      <c r="C647" s="6">
+        <v>16117</v>
+      </c>
+      <c r="D647" s="3">
+        <v>161</v>
+      </c>
+      <c r="E647" s="3">
+        <v>1</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="648" spans="3:7">
+      <c r="C648" s="6">
+        <v>16118</v>
+      </c>
+      <c r="D648" s="3">
+        <v>161</v>
+      </c>
+      <c r="E648" s="5">
+        <v>1</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="649" spans="3:7">
+      <c r="C649" s="6">
+        <v>16119</v>
+      </c>
+      <c r="D649" s="3">
+        <v>161</v>
+      </c>
+      <c r="E649" s="5">
+        <v>1</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="650" spans="3:7">
+      <c r="C650" s="6">
+        <v>16120</v>
+      </c>
+      <c r="D650" s="3">
+        <v>161</v>
+      </c>
+      <c r="E650" s="5">
+        <v>1</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="651" spans="3:7">
+      <c r="C651" s="6">
+        <v>16121</v>
+      </c>
+      <c r="D651" s="3">
+        <v>161</v>
+      </c>
+      <c r="E651" s="3">
+        <v>1</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="652" spans="3:7">
+      <c r="C652" s="6">
+        <v>16122</v>
+      </c>
+      <c r="D652" s="3">
+        <v>161</v>
+      </c>
+      <c r="E652" s="5">
+        <v>1</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="653" spans="3:7">
+      <c r="C653" s="6">
+        <v>16123</v>
+      </c>
+      <c r="D653" s="3">
+        <v>161</v>
+      </c>
+      <c r="E653" s="5">
+        <v>1</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="654" spans="3:7">
+      <c r="C654" s="6">
+        <v>16124</v>
+      </c>
+      <c r="D654" s="3">
+        <v>161</v>
+      </c>
+      <c r="E654" s="5">
+        <v>1</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="655" spans="3:7">
+      <c r="C655" s="6">
+        <v>16125</v>
+      </c>
+      <c r="D655" s="3">
+        <v>161</v>
+      </c>
+      <c r="E655" s="3">
+        <v>1</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G655" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12102,10 +12547,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12120,10 +12565,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12138,10 +12583,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12156,10 +12601,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12176,10 +12621,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12274,10 +12719,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋161时光镇</t>
+  </si>
+  <si>
+    <t>#先锋162棉花糖</t>
   </si>
   <si>
     <t>Center</t>
@@ -970,13 +973,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
@@ -1264,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12427,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>16201</v>
+      </c>
+      <c r="D657" s="3">
+        <v>162</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20505</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>16202</v>
+      </c>
+      <c r="D658" s="3">
+        <v>162</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20506</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>16203</v>
+      </c>
+      <c r="D659" s="3">
+        <v>162</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20507</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>16204</v>
+      </c>
+      <c r="D660" s="3">
+        <v>162</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20508</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>16205</v>
+      </c>
+      <c r="D661" s="3">
+        <v>162</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>16206</v>
+      </c>
+      <c r="D662" s="3">
+        <v>162</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>16207</v>
+      </c>
+      <c r="D663" s="3">
+        <v>162</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>16208</v>
+      </c>
+      <c r="D664" s="3">
+        <v>162</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>16209</v>
+      </c>
+      <c r="D665" s="3">
+        <v>162</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>16210</v>
+      </c>
+      <c r="D666" s="3">
+        <v>162</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>16211</v>
+      </c>
+      <c r="D667" s="3">
+        <v>162</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>16212</v>
+      </c>
+      <c r="D668" s="3">
+        <v>162</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>16213</v>
+      </c>
+      <c r="D669" s="3">
+        <v>162</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>16214</v>
+      </c>
+      <c r="D670" s="3">
+        <v>162</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>16215</v>
+      </c>
+      <c r="D671" s="3">
+        <v>162</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>16216</v>
+      </c>
+      <c r="D672" s="3">
+        <v>162</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>16217</v>
+      </c>
+      <c r="D673" s="3">
+        <v>162</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>16218</v>
+      </c>
+      <c r="D674" s="3">
+        <v>162</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>16219</v>
+      </c>
+      <c r="D675" s="3">
+        <v>162</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>16220</v>
+      </c>
+      <c r="D676" s="3">
+        <v>162</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>16221</v>
+      </c>
+      <c r="D677" s="3">
+        <v>162</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>16222</v>
+      </c>
+      <c r="D678" s="3">
+        <v>162</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>16223</v>
+      </c>
+      <c r="D679" s="3">
+        <v>162</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>16224</v>
+      </c>
+      <c r="D680" s="3">
+        <v>162</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>16225</v>
+      </c>
+      <c r="D681" s="3">
+        <v>162</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12547,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12565,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12583,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12601,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12621,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12719,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋162棉花糖</t>
+  </si>
+  <si>
+    <t>#先锋163</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>16301</v>
+      </c>
+      <c r="D683" s="3">
+        <v>163</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20525</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>16302</v>
+      </c>
+      <c r="D684" s="3">
+        <v>163</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20526</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>16303</v>
+      </c>
+      <c r="D685" s="3">
+        <v>163</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20527</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>16304</v>
+      </c>
+      <c r="D686" s="3">
+        <v>163</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20528</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>16305</v>
+      </c>
+      <c r="D687" s="3">
+        <v>163</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>16306</v>
+      </c>
+      <c r="D688" s="3">
+        <v>163</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>16307</v>
+      </c>
+      <c r="D689" s="3">
+        <v>163</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>16308</v>
+      </c>
+      <c r="D690" s="3">
+        <v>163</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>16309</v>
+      </c>
+      <c r="D691" s="3">
+        <v>163</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>16310</v>
+      </c>
+      <c r="D692" s="3">
+        <v>163</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>16311</v>
+      </c>
+      <c r="D693" s="3">
+        <v>163</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>16312</v>
+      </c>
+      <c r="D694" s="3">
+        <v>163</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>16313</v>
+      </c>
+      <c r="D695" s="3">
+        <v>163</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>16314</v>
+      </c>
+      <c r="D696" s="3">
+        <v>163</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>16315</v>
+      </c>
+      <c r="D697" s="3">
+        <v>163</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>16316</v>
+      </c>
+      <c r="D698" s="3">
+        <v>163</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>16317</v>
+      </c>
+      <c r="D699" s="3">
+        <v>163</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>16318</v>
+      </c>
+      <c r="D700" s="3">
+        <v>163</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>16319</v>
+      </c>
+      <c r="D701" s="3">
+        <v>163</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>16320</v>
+      </c>
+      <c r="D702" s="3">
+        <v>163</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>16321</v>
+      </c>
+      <c r="D703" s="3">
+        <v>163</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>16322</v>
+      </c>
+      <c r="D704" s="3">
+        <v>163</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>16323</v>
+      </c>
+      <c r="D705" s="3">
+        <v>163</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>16324</v>
+      </c>
+      <c r="D706" s="3">
+        <v>163</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>16325</v>
+      </c>
+      <c r="D707" s="3">
+        <v>163</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -235,7 +235,7 @@
     <t>#先锋162棉花糖</t>
   </si>
   <si>
-    <t>#先锋163</t>
+    <t>#先锋163破晓战歌</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -208,25 +208,13 @@
     <t>#先锋151龙裔国度</t>
   </si>
   <si>
-    <t>#先锋153荣耀之路</t>
-  </si>
-  <si>
     <t>#先锋155雷霆万钧</t>
-  </si>
-  <si>
-    <t>#先锋156龙翔九天</t>
   </si>
   <si>
     <t>#先锋157神谕森林</t>
   </si>
   <si>
-    <t>#先锋158泰坦神殿</t>
-  </si>
-  <si>
     <t>#先锋159星辰之巅</t>
-  </si>
-  <si>
-    <t>#先锋160微风草原</t>
   </si>
   <si>
     <t>#先锋161时光镇</t>
@@ -236,6 +224,9 @@
   </si>
   <si>
     <t>#先锋163破晓战歌</t>
+  </si>
+  <si>
+    <t>#先锋164翡翠仙境</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1254,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O629"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -8898,10 +8889,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>15301</v>
+        <v>15501</v>
       </c>
       <c r="D449" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8913,17 +8904,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20565</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>15302</v>
+        <v>15502</v>
       </c>
       <c r="D450" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8935,15 +8926,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20566</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>15303</v>
+        <v>15503</v>
       </c>
       <c r="D451" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8955,15 +8946,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20567</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>15304</v>
+        <v>15504</v>
       </c>
       <c r="D452" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8975,15 +8966,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20568</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>15305</v>
+        <v>15505</v>
       </c>
       <c r="D453" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -8997,10 +8988,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>15306</v>
+        <v>15506</v>
       </c>
       <c r="D454" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9014,10 +9005,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>15307</v>
+        <v>15507</v>
       </c>
       <c r="D455" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9031,10 +9022,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>15308</v>
+        <v>15508</v>
       </c>
       <c r="D456" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9048,10 +9039,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>15309</v>
+        <v>15509</v>
       </c>
       <c r="D457" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9065,10 +9056,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>15310</v>
+        <v>15510</v>
       </c>
       <c r="D458" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9082,10 +9073,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>15311</v>
+        <v>15511</v>
       </c>
       <c r="D459" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9099,10 +9090,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>15312</v>
+        <v>15512</v>
       </c>
       <c r="D460" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9116,10 +9107,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>15313</v>
+        <v>15513</v>
       </c>
       <c r="D461" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9133,10 +9124,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>15314</v>
+        <v>15514</v>
       </c>
       <c r="D462" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9150,10 +9141,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>15315</v>
+        <v>15515</v>
       </c>
       <c r="D463" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9167,10 +9158,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>15316</v>
+        <v>15516</v>
       </c>
       <c r="D464" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9184,10 +9175,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>15317</v>
+        <v>15517</v>
       </c>
       <c r="D465" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9201,10 +9192,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>15318</v>
+        <v>15518</v>
       </c>
       <c r="D466" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9218,10 +9209,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>15319</v>
+        <v>15519</v>
       </c>
       <c r="D467" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9235,10 +9226,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>15320</v>
+        <v>15520</v>
       </c>
       <c r="D468" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9252,10 +9243,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>15321</v>
+        <v>15521</v>
       </c>
       <c r="D469" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9269,10 +9260,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>15322</v>
+        <v>15522</v>
       </c>
       <c r="D470" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9286,10 +9277,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>15323</v>
+        <v>15523</v>
       </c>
       <c r="D471" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9303,10 +9294,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>15324</v>
+        <v>15524</v>
       </c>
       <c r="D472" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9320,10 +9311,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>15325</v>
+        <v>15525</v>
       </c>
       <c r="D473" s="3">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9340,10 +9331,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>15501</v>
+        <v>15701</v>
       </c>
       <c r="D475" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9355,17 +9346,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20605</v>
+        <v>20645</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>15502</v>
+        <v>15702</v>
       </c>
       <c r="D476" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9377,15 +9368,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20606</v>
+        <v>20646</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>15503</v>
+        <v>15703</v>
       </c>
       <c r="D477" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9397,15 +9388,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20607</v>
+        <v>20647</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>15504</v>
+        <v>15704</v>
       </c>
       <c r="D478" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9417,15 +9408,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20608</v>
+        <v>20648</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>15505</v>
+        <v>15705</v>
       </c>
       <c r="D479" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9439,10 +9430,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>15506</v>
+        <v>15706</v>
       </c>
       <c r="D480" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9456,10 +9447,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>15507</v>
+        <v>15707</v>
       </c>
       <c r="D481" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9473,10 +9464,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>15508</v>
+        <v>15708</v>
       </c>
       <c r="D482" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9490,10 +9481,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>15509</v>
+        <v>15709</v>
       </c>
       <c r="D483" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9507,10 +9498,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>15510</v>
+        <v>15710</v>
       </c>
       <c r="D484" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9524,10 +9515,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>15511</v>
+        <v>15711</v>
       </c>
       <c r="D485" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9541,10 +9532,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>15512</v>
+        <v>15712</v>
       </c>
       <c r="D486" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9558,10 +9549,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>15513</v>
+        <v>15713</v>
       </c>
       <c r="D487" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9575,10 +9566,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>15514</v>
+        <v>15714</v>
       </c>
       <c r="D488" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9592,10 +9583,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>15515</v>
+        <v>15715</v>
       </c>
       <c r="D489" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9609,10 +9600,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>15516</v>
+        <v>15716</v>
       </c>
       <c r="D490" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9626,10 +9617,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>15517</v>
+        <v>15717</v>
       </c>
       <c r="D491" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9643,10 +9634,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>15518</v>
+        <v>15718</v>
       </c>
       <c r="D492" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9660,10 +9651,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>15519</v>
+        <v>15719</v>
       </c>
       <c r="D493" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9677,10 +9668,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>15520</v>
+        <v>15720</v>
       </c>
       <c r="D494" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9694,10 +9685,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>15521</v>
+        <v>15721</v>
       </c>
       <c r="D495" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9711,10 +9702,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>15522</v>
+        <v>15722</v>
       </c>
       <c r="D496" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9728,10 +9719,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>15523</v>
+        <v>15723</v>
       </c>
       <c r="D497" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9745,10 +9736,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>15524</v>
+        <v>15724</v>
       </c>
       <c r="D498" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9762,10 +9753,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>15525</v>
+        <v>15725</v>
       </c>
       <c r="D499" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9782,10 +9773,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>15601</v>
+        <v>15901</v>
       </c>
       <c r="D501" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9797,17 +9788,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20615</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>15602</v>
+        <v>15902</v>
       </c>
       <c r="D502" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9819,15 +9810,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20616</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>15603</v>
+        <v>15903</v>
       </c>
       <c r="D503" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9839,15 +9830,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20617</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>15604</v>
+        <v>15904</v>
       </c>
       <c r="D504" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9859,15 +9850,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20618</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>15605</v>
+        <v>15905</v>
       </c>
       <c r="D505" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9881,10 +9872,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>15606</v>
+        <v>15906</v>
       </c>
       <c r="D506" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9898,10 +9889,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>15607</v>
+        <v>15907</v>
       </c>
       <c r="D507" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9915,10 +9906,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>15608</v>
+        <v>15908</v>
       </c>
       <c r="D508" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9932,10 +9923,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>15609</v>
+        <v>15909</v>
       </c>
       <c r="D509" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9949,10 +9940,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>15610</v>
+        <v>15910</v>
       </c>
       <c r="D510" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9966,10 +9957,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>15611</v>
+        <v>15911</v>
       </c>
       <c r="D511" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9983,10 +9974,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>15612</v>
+        <v>15912</v>
       </c>
       <c r="D512" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10000,10 +9991,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>15613</v>
+        <v>15913</v>
       </c>
       <c r="D513" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10017,10 +10008,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>15614</v>
+        <v>15914</v>
       </c>
       <c r="D514" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10034,10 +10025,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>15615</v>
+        <v>15915</v>
       </c>
       <c r="D515" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10051,10 +10042,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>15616</v>
+        <v>15916</v>
       </c>
       <c r="D516" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10068,10 +10059,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>15617</v>
+        <v>15917</v>
       </c>
       <c r="D517" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10085,10 +10076,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>15618</v>
+        <v>15918</v>
       </c>
       <c r="D518" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10102,10 +10093,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>15619</v>
+        <v>15919</v>
       </c>
       <c r="D519" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10119,10 +10110,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>15620</v>
+        <v>15920</v>
       </c>
       <c r="D520" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10136,10 +10127,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>15621</v>
+        <v>15921</v>
       </c>
       <c r="D521" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10153,10 +10144,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>15622</v>
+        <v>15922</v>
       </c>
       <c r="D522" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10170,10 +10161,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>15623</v>
+        <v>15923</v>
       </c>
       <c r="D523" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10187,10 +10178,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>15624</v>
+        <v>15924</v>
       </c>
       <c r="D524" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10204,10 +10195,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>15625</v>
+        <v>15925</v>
       </c>
       <c r="D525" s="3">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10224,10 +10215,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>15701</v>
+        <v>16101</v>
       </c>
       <c r="D527" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10239,17 +10230,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20645</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>15702</v>
+        <v>16102</v>
       </c>
       <c r="D528" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10261,15 +10252,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20646</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>15703</v>
+        <v>16103</v>
       </c>
       <c r="D529" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10281,15 +10272,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20647</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>15704</v>
+        <v>16104</v>
       </c>
       <c r="D530" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10301,15 +10292,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20648</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>15705</v>
+        <v>16105</v>
       </c>
       <c r="D531" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10323,10 +10314,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>15706</v>
+        <v>16106</v>
       </c>
       <c r="D532" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10340,10 +10331,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>15707</v>
+        <v>16107</v>
       </c>
       <c r="D533" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10357,10 +10348,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>15708</v>
+        <v>16108</v>
       </c>
       <c r="D534" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10374,10 +10365,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>15709</v>
+        <v>16109</v>
       </c>
       <c r="D535" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10391,10 +10382,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>15710</v>
+        <v>16110</v>
       </c>
       <c r="D536" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10408,10 +10399,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>15711</v>
+        <v>16111</v>
       </c>
       <c r="D537" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10425,10 +10416,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>15712</v>
+        <v>16112</v>
       </c>
       <c r="D538" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10442,10 +10433,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>15713</v>
+        <v>16113</v>
       </c>
       <c r="D539" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10459,10 +10450,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>15714</v>
+        <v>16114</v>
       </c>
       <c r="D540" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10476,10 +10467,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>15715</v>
+        <v>16115</v>
       </c>
       <c r="D541" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10493,10 +10484,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>15716</v>
+        <v>16116</v>
       </c>
       <c r="D542" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10510,10 +10501,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>15717</v>
+        <v>16117</v>
       </c>
       <c r="D543" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10527,10 +10518,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>15718</v>
+        <v>16118</v>
       </c>
       <c r="D544" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10544,10 +10535,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>15719</v>
+        <v>16119</v>
       </c>
       <c r="D545" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10561,10 +10552,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>15720</v>
+        <v>16120</v>
       </c>
       <c r="D546" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10578,10 +10569,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>15721</v>
+        <v>16121</v>
       </c>
       <c r="D547" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10595,10 +10586,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>15722</v>
+        <v>16122</v>
       </c>
       <c r="D548" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10612,10 +10603,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>15723</v>
+        <v>16123</v>
       </c>
       <c r="D549" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10629,10 +10620,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>15724</v>
+        <v>16124</v>
       </c>
       <c r="D550" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10646,10 +10637,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>15725</v>
+        <v>16125</v>
       </c>
       <c r="D551" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10666,10 +10657,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>15801</v>
+        <v>16201</v>
       </c>
       <c r="D553" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10681,17 +10672,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20375</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>15802</v>
+        <v>16202</v>
       </c>
       <c r="D554" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10703,15 +10694,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20376</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>15803</v>
+        <v>16203</v>
       </c>
       <c r="D555" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10723,15 +10714,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20377</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>15804</v>
+        <v>16204</v>
       </c>
       <c r="D556" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10743,15 +10734,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20378</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>15805</v>
+        <v>16205</v>
       </c>
       <c r="D557" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10765,10 +10756,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>15806</v>
+        <v>16206</v>
       </c>
       <c r="D558" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10782,10 +10773,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>15807</v>
+        <v>16207</v>
       </c>
       <c r="D559" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10799,10 +10790,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>15808</v>
+        <v>16208</v>
       </c>
       <c r="D560" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10816,10 +10807,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>15809</v>
+        <v>16209</v>
       </c>
       <c r="D561" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10833,10 +10824,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>15810</v>
+        <v>16210</v>
       </c>
       <c r="D562" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10850,10 +10841,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>15811</v>
+        <v>16211</v>
       </c>
       <c r="D563" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10867,10 +10858,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>15812</v>
+        <v>16212</v>
       </c>
       <c r="D564" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10884,10 +10875,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>15813</v>
+        <v>16213</v>
       </c>
       <c r="D565" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10901,10 +10892,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>15814</v>
+        <v>16214</v>
       </c>
       <c r="D566" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10918,10 +10909,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>15815</v>
+        <v>16215</v>
       </c>
       <c r="D567" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10935,10 +10926,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>15816</v>
+        <v>16216</v>
       </c>
       <c r="D568" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10952,10 +10943,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>15817</v>
+        <v>16217</v>
       </c>
       <c r="D569" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10969,10 +10960,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>15818</v>
+        <v>16218</v>
       </c>
       <c r="D570" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10986,10 +10977,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>15819</v>
+        <v>16219</v>
       </c>
       <c r="D571" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11003,10 +10994,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>15820</v>
+        <v>16220</v>
       </c>
       <c r="D572" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11020,10 +11011,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>15821</v>
+        <v>16221</v>
       </c>
       <c r="D573" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11037,10 +11028,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>15822</v>
+        <v>16222</v>
       </c>
       <c r="D574" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11054,10 +11045,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>15823</v>
+        <v>16223</v>
       </c>
       <c r="D575" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11071,10 +11062,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>15824</v>
+        <v>16224</v>
       </c>
       <c r="D576" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11088,10 +11079,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>15825</v>
+        <v>16225</v>
       </c>
       <c r="D577" s="3">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11108,10 +11099,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>15901</v>
+        <v>16301</v>
       </c>
       <c r="D579" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11123,17 +11114,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20405</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>15902</v>
+        <v>16302</v>
       </c>
       <c r="D580" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11145,15 +11136,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20406</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>15903</v>
+        <v>16303</v>
       </c>
       <c r="D581" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11165,15 +11156,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20407</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>15904</v>
+        <v>16304</v>
       </c>
       <c r="D582" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11185,15 +11176,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20408</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>15905</v>
+        <v>16305</v>
       </c>
       <c r="D583" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11207,10 +11198,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>15906</v>
+        <v>16306</v>
       </c>
       <c r="D584" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11224,10 +11215,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>15907</v>
+        <v>16307</v>
       </c>
       <c r="D585" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11241,10 +11232,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>15908</v>
+        <v>16308</v>
       </c>
       <c r="D586" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11258,10 +11249,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>15909</v>
+        <v>16309</v>
       </c>
       <c r="D587" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11275,10 +11266,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>15910</v>
+        <v>16310</v>
       </c>
       <c r="D588" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11292,10 +11283,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>15911</v>
+        <v>16311</v>
       </c>
       <c r="D589" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11309,10 +11300,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>15912</v>
+        <v>16312</v>
       </c>
       <c r="D590" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11326,10 +11317,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>15913</v>
+        <v>16313</v>
       </c>
       <c r="D591" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11343,10 +11334,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>15914</v>
+        <v>16314</v>
       </c>
       <c r="D592" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11360,10 +11351,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>15915</v>
+        <v>16315</v>
       </c>
       <c r="D593" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11377,10 +11368,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>15916</v>
+        <v>16316</v>
       </c>
       <c r="D594" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11394,10 +11385,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>15917</v>
+        <v>16317</v>
       </c>
       <c r="D595" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11411,10 +11402,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>15918</v>
+        <v>16318</v>
       </c>
       <c r="D596" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11428,10 +11419,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>15919</v>
+        <v>16319</v>
       </c>
       <c r="D597" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11445,10 +11436,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>15920</v>
+        <v>16320</v>
       </c>
       <c r="D598" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11462,10 +11453,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>15921</v>
+        <v>16321</v>
       </c>
       <c r="D599" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11479,10 +11470,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>15922</v>
+        <v>16322</v>
       </c>
       <c r="D600" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11496,10 +11487,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>15923</v>
+        <v>16323</v>
       </c>
       <c r="D601" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11513,10 +11504,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>15924</v>
+        <v>16324</v>
       </c>
       <c r="D602" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11530,10 +11521,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>15925</v>
+        <v>16325</v>
       </c>
       <c r="D603" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11550,10 +11541,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>16001</v>
+        <v>16401</v>
       </c>
       <c r="D605" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11565,17 +11556,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20455</v>
+        <v>20545</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>16002</v>
+        <v>16402</v>
       </c>
       <c r="D606" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11587,15 +11578,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20456</v>
+        <v>20546</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>16003</v>
+        <v>16403</v>
       </c>
       <c r="D607" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11607,15 +11598,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20457</v>
+        <v>20547</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>16004</v>
+        <v>16404</v>
       </c>
       <c r="D608" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11627,15 +11618,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20458</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>16005</v>
+        <v>16405</v>
       </c>
       <c r="D609" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11649,10 +11640,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>16006</v>
+        <v>16406</v>
       </c>
       <c r="D610" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11666,10 +11657,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>16007</v>
+        <v>16407</v>
       </c>
       <c r="D611" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11683,10 +11674,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>16008</v>
+        <v>16408</v>
       </c>
       <c r="D612" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11700,10 +11691,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>16009</v>
+        <v>16409</v>
       </c>
       <c r="D613" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11717,10 +11708,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>16010</v>
+        <v>16410</v>
       </c>
       <c r="D614" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11734,10 +11725,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>16011</v>
+        <v>16411</v>
       </c>
       <c r="D615" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11751,10 +11742,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>16012</v>
+        <v>16412</v>
       </c>
       <c r="D616" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11768,10 +11759,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>16013</v>
+        <v>16413</v>
       </c>
       <c r="D617" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11785,10 +11776,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>16014</v>
+        <v>16414</v>
       </c>
       <c r="D618" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11802,10 +11793,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>16015</v>
+        <v>16415</v>
       </c>
       <c r="D619" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11819,10 +11810,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>16016</v>
+        <v>16416</v>
       </c>
       <c r="D620" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11836,10 +11827,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>16017</v>
+        <v>16417</v>
       </c>
       <c r="D621" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11853,10 +11844,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>16018</v>
+        <v>16418</v>
       </c>
       <c r="D622" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11870,10 +11861,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>16019</v>
+        <v>16419</v>
       </c>
       <c r="D623" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11887,10 +11878,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>16020</v>
+        <v>16420</v>
       </c>
       <c r="D624" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11904,10 +11895,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>16021</v>
+        <v>16421</v>
       </c>
       <c r="D625" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11921,10 +11912,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>16022</v>
+        <v>16422</v>
       </c>
       <c r="D626" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11938,10 +11929,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>16023</v>
+        <v>16423</v>
       </c>
       <c r="D627" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11955,10 +11946,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>16024</v>
+        <v>16424</v>
       </c>
       <c r="D628" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11972,10 +11963,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>16025</v>
+        <v>16425</v>
       </c>
       <c r="D629" s="3">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11984,1332 +11975,6 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8">
-      <c r="A631" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C631" s="6">
-        <v>16101</v>
-      </c>
-      <c r="D631" s="3">
-        <v>161</v>
-      </c>
-      <c r="E631" s="5">
-        <v>1</v>
-      </c>
-      <c r="F631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H631" s="3">
-        <v>20445</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8">
-      <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
-      <c r="C632" s="6">
-        <v>16102</v>
-      </c>
-      <c r="D632" s="3">
-        <v>161</v>
-      </c>
-      <c r="E632" s="5">
-        <v>1</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H632" s="3">
-        <v>20446</v>
-      </c>
-    </row>
-    <row r="633" spans="3:8">
-      <c r="C633" s="6">
-        <v>16103</v>
-      </c>
-      <c r="D633" s="3">
-        <v>161</v>
-      </c>
-      <c r="E633" s="5">
-        <v>1</v>
-      </c>
-      <c r="F633" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G633" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H633" s="3">
-        <v>20447</v>
-      </c>
-    </row>
-    <row r="634" spans="3:8">
-      <c r="C634" s="6">
-        <v>16104</v>
-      </c>
-      <c r="D634" s="3">
-        <v>161</v>
-      </c>
-      <c r="E634" s="5">
-        <v>1</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H634" s="3">
-        <v>20448</v>
-      </c>
-    </row>
-    <row r="635" spans="3:7">
-      <c r="C635" s="6">
-        <v>16105</v>
-      </c>
-      <c r="D635" s="3">
-        <v>161</v>
-      </c>
-      <c r="E635" s="3">
-        <v>1</v>
-      </c>
-      <c r="F635" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G635" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="636" spans="3:7">
-      <c r="C636" s="6">
-        <v>16106</v>
-      </c>
-      <c r="D636" s="3">
-        <v>161</v>
-      </c>
-      <c r="E636" s="5">
-        <v>1</v>
-      </c>
-      <c r="F636" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G636" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="637" spans="3:7">
-      <c r="C637" s="6">
-        <v>16107</v>
-      </c>
-      <c r="D637" s="3">
-        <v>161</v>
-      </c>
-      <c r="E637" s="5">
-        <v>1</v>
-      </c>
-      <c r="F637" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G637" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="638" spans="3:7">
-      <c r="C638" s="6">
-        <v>16108</v>
-      </c>
-      <c r="D638" s="3">
-        <v>161</v>
-      </c>
-      <c r="E638" s="5">
-        <v>1</v>
-      </c>
-      <c r="F638" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G638" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="639" spans="3:7">
-      <c r="C639" s="6">
-        <v>16109</v>
-      </c>
-      <c r="D639" s="3">
-        <v>161</v>
-      </c>
-      <c r="E639" s="3">
-        <v>1</v>
-      </c>
-      <c r="F639" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G639" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="640" spans="3:7">
-      <c r="C640" s="6">
-        <v>16110</v>
-      </c>
-      <c r="D640" s="3">
-        <v>161</v>
-      </c>
-      <c r="E640" s="5">
-        <v>1</v>
-      </c>
-      <c r="F640" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G640" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="641" spans="3:7">
-      <c r="C641" s="6">
-        <v>16111</v>
-      </c>
-      <c r="D641" s="3">
-        <v>161</v>
-      </c>
-      <c r="E641" s="5">
-        <v>1</v>
-      </c>
-      <c r="F641" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G641" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="642" spans="3:7">
-      <c r="C642" s="6">
-        <v>16112</v>
-      </c>
-      <c r="D642" s="3">
-        <v>161</v>
-      </c>
-      <c r="E642" s="5">
-        <v>1</v>
-      </c>
-      <c r="F642" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G642" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="643" spans="3:7">
-      <c r="C643" s="6">
-        <v>16113</v>
-      </c>
-      <c r="D643" s="3">
-        <v>161</v>
-      </c>
-      <c r="E643" s="3">
-        <v>1</v>
-      </c>
-      <c r="F643" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G643" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="644" spans="3:7">
-      <c r="C644" s="6">
-        <v>16114</v>
-      </c>
-      <c r="D644" s="3">
-        <v>161</v>
-      </c>
-      <c r="E644" s="5">
-        <v>1</v>
-      </c>
-      <c r="F644" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G644" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="645" spans="3:7">
-      <c r="C645" s="6">
-        <v>16115</v>
-      </c>
-      <c r="D645" s="3">
-        <v>161</v>
-      </c>
-      <c r="E645" s="5">
-        <v>1</v>
-      </c>
-      <c r="F645" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G645" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="646" spans="3:7">
-      <c r="C646" s="6">
-        <v>16116</v>
-      </c>
-      <c r="D646" s="3">
-        <v>161</v>
-      </c>
-      <c r="E646" s="5">
-        <v>1</v>
-      </c>
-      <c r="F646" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G646" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="647" spans="3:7">
-      <c r="C647" s="6">
-        <v>16117</v>
-      </c>
-      <c r="D647" s="3">
-        <v>161</v>
-      </c>
-      <c r="E647" s="3">
-        <v>1</v>
-      </c>
-      <c r="F647" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G647" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="648" spans="3:7">
-      <c r="C648" s="6">
-        <v>16118</v>
-      </c>
-      <c r="D648" s="3">
-        <v>161</v>
-      </c>
-      <c r="E648" s="5">
-        <v>1</v>
-      </c>
-      <c r="F648" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G648" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="649" spans="3:7">
-      <c r="C649" s="6">
-        <v>16119</v>
-      </c>
-      <c r="D649" s="3">
-        <v>161</v>
-      </c>
-      <c r="E649" s="5">
-        <v>1</v>
-      </c>
-      <c r="F649" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G649" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="650" spans="3:7">
-      <c r="C650" s="6">
-        <v>16120</v>
-      </c>
-      <c r="D650" s="3">
-        <v>161</v>
-      </c>
-      <c r="E650" s="5">
-        <v>1</v>
-      </c>
-      <c r="F650" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G650" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="651" spans="3:7">
-      <c r="C651" s="6">
-        <v>16121</v>
-      </c>
-      <c r="D651" s="3">
-        <v>161</v>
-      </c>
-      <c r="E651" s="3">
-        <v>1</v>
-      </c>
-      <c r="F651" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G651" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="652" spans="3:7">
-      <c r="C652" s="6">
-        <v>16122</v>
-      </c>
-      <c r="D652" s="3">
-        <v>161</v>
-      </c>
-      <c r="E652" s="5">
-        <v>1</v>
-      </c>
-      <c r="F652" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G652" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="653" spans="3:7">
-      <c r="C653" s="6">
-        <v>16123</v>
-      </c>
-      <c r="D653" s="3">
-        <v>161</v>
-      </c>
-      <c r="E653" s="5">
-        <v>1</v>
-      </c>
-      <c r="F653" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G653" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="654" spans="3:7">
-      <c r="C654" s="6">
-        <v>16124</v>
-      </c>
-      <c r="D654" s="3">
-        <v>161</v>
-      </c>
-      <c r="E654" s="5">
-        <v>1</v>
-      </c>
-      <c r="F654" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G654" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="655" spans="3:7">
-      <c r="C655" s="6">
-        <v>16125</v>
-      </c>
-      <c r="D655" s="3">
-        <v>161</v>
-      </c>
-      <c r="E655" s="3">
-        <v>1</v>
-      </c>
-      <c r="F655" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G655" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="657" spans="1:8">
-      <c r="A657" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C657" s="6">
-        <v>16201</v>
-      </c>
-      <c r="D657" s="3">
-        <v>162</v>
-      </c>
-      <c r="E657" s="5">
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H657" s="3">
-        <v>20505</v>
-      </c>
-    </row>
-    <row r="658" spans="1:8">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-      <c r="C658" s="6">
-        <v>16202</v>
-      </c>
-      <c r="D658" s="3">
-        <v>162</v>
-      </c>
-      <c r="E658" s="5">
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H658" s="3">
-        <v>20506</v>
-      </c>
-    </row>
-    <row r="659" spans="3:8">
-      <c r="C659" s="6">
-        <v>16203</v>
-      </c>
-      <c r="D659" s="3">
-        <v>162</v>
-      </c>
-      <c r="E659" s="5">
-        <v>1</v>
-      </c>
-      <c r="F659" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G659" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H659" s="3">
-        <v>20507</v>
-      </c>
-    </row>
-    <row r="660" spans="3:8">
-      <c r="C660" s="6">
-        <v>16204</v>
-      </c>
-      <c r="D660" s="3">
-        <v>162</v>
-      </c>
-      <c r="E660" s="5">
-        <v>1</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H660" s="3">
-        <v>20508</v>
-      </c>
-    </row>
-    <row r="661" spans="3:7">
-      <c r="C661" s="6">
-        <v>16205</v>
-      </c>
-      <c r="D661" s="3">
-        <v>162</v>
-      </c>
-      <c r="E661" s="3">
-        <v>1</v>
-      </c>
-      <c r="F661" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G661" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="662" spans="3:7">
-      <c r="C662" s="6">
-        <v>16206</v>
-      </c>
-      <c r="D662" s="3">
-        <v>162</v>
-      </c>
-      <c r="E662" s="5">
-        <v>1</v>
-      </c>
-      <c r="F662" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G662" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="663" spans="3:7">
-      <c r="C663" s="6">
-        <v>16207</v>
-      </c>
-      <c r="D663" s="3">
-        <v>162</v>
-      </c>
-      <c r="E663" s="5">
-        <v>1</v>
-      </c>
-      <c r="F663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G663" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="664" spans="3:7">
-      <c r="C664" s="6">
-        <v>16208</v>
-      </c>
-      <c r="D664" s="3">
-        <v>162</v>
-      </c>
-      <c r="E664" s="5">
-        <v>1</v>
-      </c>
-      <c r="F664" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G664" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="665" spans="3:7">
-      <c r="C665" s="6">
-        <v>16209</v>
-      </c>
-      <c r="D665" s="3">
-        <v>162</v>
-      </c>
-      <c r="E665" s="3">
-        <v>1</v>
-      </c>
-      <c r="F665" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G665" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="666" spans="3:7">
-      <c r="C666" s="6">
-        <v>16210</v>
-      </c>
-      <c r="D666" s="3">
-        <v>162</v>
-      </c>
-      <c r="E666" s="5">
-        <v>1</v>
-      </c>
-      <c r="F666" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G666" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="667" spans="3:7">
-      <c r="C667" s="6">
-        <v>16211</v>
-      </c>
-      <c r="D667" s="3">
-        <v>162</v>
-      </c>
-      <c r="E667" s="5">
-        <v>1</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G667" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="668" spans="3:7">
-      <c r="C668" s="6">
-        <v>16212</v>
-      </c>
-      <c r="D668" s="3">
-        <v>162</v>
-      </c>
-      <c r="E668" s="5">
-        <v>1</v>
-      </c>
-      <c r="F668" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G668" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="669" spans="3:7">
-      <c r="C669" s="6">
-        <v>16213</v>
-      </c>
-      <c r="D669" s="3">
-        <v>162</v>
-      </c>
-      <c r="E669" s="3">
-        <v>1</v>
-      </c>
-      <c r="F669" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G669" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="670" spans="3:7">
-      <c r="C670" s="6">
-        <v>16214</v>
-      </c>
-      <c r="D670" s="3">
-        <v>162</v>
-      </c>
-      <c r="E670" s="5">
-        <v>1</v>
-      </c>
-      <c r="F670" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G670" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="671" spans="3:7">
-      <c r="C671" s="6">
-        <v>16215</v>
-      </c>
-      <c r="D671" s="3">
-        <v>162</v>
-      </c>
-      <c r="E671" s="5">
-        <v>1</v>
-      </c>
-      <c r="F671" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G671" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="672" spans="3:7">
-      <c r="C672" s="6">
-        <v>16216</v>
-      </c>
-      <c r="D672" s="3">
-        <v>162</v>
-      </c>
-      <c r="E672" s="5">
-        <v>1</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G672" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="673" spans="3:7">
-      <c r="C673" s="6">
-        <v>16217</v>
-      </c>
-      <c r="D673" s="3">
-        <v>162</v>
-      </c>
-      <c r="E673" s="3">
-        <v>1</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G673" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="674" spans="3:7">
-      <c r="C674" s="6">
-        <v>16218</v>
-      </c>
-      <c r="D674" s="3">
-        <v>162</v>
-      </c>
-      <c r="E674" s="5">
-        <v>1</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G674" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="675" spans="3:7">
-      <c r="C675" s="6">
-        <v>16219</v>
-      </c>
-      <c r="D675" s="3">
-        <v>162</v>
-      </c>
-      <c r="E675" s="5">
-        <v>1</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G675" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="676" spans="3:7">
-      <c r="C676" s="6">
-        <v>16220</v>
-      </c>
-      <c r="D676" s="3">
-        <v>162</v>
-      </c>
-      <c r="E676" s="5">
-        <v>1</v>
-      </c>
-      <c r="F676" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G676" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="677" spans="3:7">
-      <c r="C677" s="6">
-        <v>16221</v>
-      </c>
-      <c r="D677" s="3">
-        <v>162</v>
-      </c>
-      <c r="E677" s="3">
-        <v>1</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G677" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="678" spans="3:7">
-      <c r="C678" s="6">
-        <v>16222</v>
-      </c>
-      <c r="D678" s="3">
-        <v>162</v>
-      </c>
-      <c r="E678" s="5">
-        <v>1</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G678" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="679" spans="3:7">
-      <c r="C679" s="6">
-        <v>16223</v>
-      </c>
-      <c r="D679" s="3">
-        <v>162</v>
-      </c>
-      <c r="E679" s="5">
-        <v>1</v>
-      </c>
-      <c r="F679" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G679" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="680" spans="3:7">
-      <c r="C680" s="6">
-        <v>16224</v>
-      </c>
-      <c r="D680" s="3">
-        <v>162</v>
-      </c>
-      <c r="E680" s="5">
-        <v>1</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G680" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="681" spans="3:7">
-      <c r="C681" s="6">
-        <v>16225</v>
-      </c>
-      <c r="D681" s="3">
-        <v>162</v>
-      </c>
-      <c r="E681" s="3">
-        <v>1</v>
-      </c>
-      <c r="F681" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>16301</v>
-      </c>
-      <c r="D683" s="3">
-        <v>163</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20525</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>16302</v>
-      </c>
-      <c r="D684" s="3">
-        <v>163</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20526</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>16303</v>
-      </c>
-      <c r="D685" s="3">
-        <v>163</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20527</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>16304</v>
-      </c>
-      <c r="D686" s="3">
-        <v>163</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20528</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>16305</v>
-      </c>
-      <c r="D687" s="3">
-        <v>163</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>16306</v>
-      </c>
-      <c r="D688" s="3">
-        <v>163</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>16307</v>
-      </c>
-      <c r="D689" s="3">
-        <v>163</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>16308</v>
-      </c>
-      <c r="D690" s="3">
-        <v>163</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>16309</v>
-      </c>
-      <c r="D691" s="3">
-        <v>163</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>16310</v>
-      </c>
-      <c r="D692" s="3">
-        <v>163</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>16311</v>
-      </c>
-      <c r="D693" s="3">
-        <v>163</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>16312</v>
-      </c>
-      <c r="D694" s="3">
-        <v>163</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>16313</v>
-      </c>
-      <c r="D695" s="3">
-        <v>163</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>16314</v>
-      </c>
-      <c r="D696" s="3">
-        <v>163</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>16315</v>
-      </c>
-      <c r="D697" s="3">
-        <v>163</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>16316</v>
-      </c>
-      <c r="D698" s="3">
-        <v>163</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>16317</v>
-      </c>
-      <c r="D699" s="3">
-        <v>163</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>16318</v>
-      </c>
-      <c r="D700" s="3">
-        <v>163</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>16319</v>
-      </c>
-      <c r="D701" s="3">
-        <v>163</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>16320</v>
-      </c>
-      <c r="D702" s="3">
-        <v>163</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>16321</v>
-      </c>
-      <c r="D703" s="3">
-        <v>163</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>16322</v>
-      </c>
-      <c r="D704" s="3">
-        <v>163</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>16323</v>
-      </c>
-      <c r="D705" s="3">
-        <v>163</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>16324</v>
-      </c>
-      <c r="D706" s="3">
-        <v>163</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>16325</v>
-      </c>
-      <c r="D707" s="3">
-        <v>163</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +12095,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +12113,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +12131,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +12149,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +12169,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +12267,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>#先锋164翡翠仙境</t>
+  </si>
+  <si>
+    <t>#先锋165繁花谷</t>
   </si>
   <si>
     <t>Center</t>
@@ -1254,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O629"/>
+  <dimension ref="A3:O655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -11975,6 +11978,448 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C631" s="6">
+        <v>16501</v>
+      </c>
+      <c r="D631" s="3">
+        <v>165</v>
+      </c>
+      <c r="E631" s="5">
+        <v>1</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H631" s="3">
+        <v>20375</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="6">
+        <v>16502</v>
+      </c>
+      <c r="D632" s="3">
+        <v>165</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H632" s="3">
+        <v>20376</v>
+      </c>
+    </row>
+    <row r="633" spans="3:8">
+      <c r="C633" s="6">
+        <v>16503</v>
+      </c>
+      <c r="D633" s="3">
+        <v>165</v>
+      </c>
+      <c r="E633" s="5">
+        <v>1</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H633" s="3">
+        <v>20377</v>
+      </c>
+    </row>
+    <row r="634" spans="3:8">
+      <c r="C634" s="6">
+        <v>16504</v>
+      </c>
+      <c r="D634" s="3">
+        <v>165</v>
+      </c>
+      <c r="E634" s="5">
+        <v>1</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H634" s="3">
+        <v>20378</v>
+      </c>
+    </row>
+    <row r="635" spans="3:7">
+      <c r="C635" s="6">
+        <v>16505</v>
+      </c>
+      <c r="D635" s="3">
+        <v>165</v>
+      </c>
+      <c r="E635" s="3">
+        <v>1</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G635" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="636" spans="3:7">
+      <c r="C636" s="6">
+        <v>16506</v>
+      </c>
+      <c r="D636" s="3">
+        <v>165</v>
+      </c>
+      <c r="E636" s="5">
+        <v>1</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="637" spans="3:7">
+      <c r="C637" s="6">
+        <v>16507</v>
+      </c>
+      <c r="D637" s="3">
+        <v>165</v>
+      </c>
+      <c r="E637" s="5">
+        <v>1</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="638" spans="3:7">
+      <c r="C638" s="6">
+        <v>16508</v>
+      </c>
+      <c r="D638" s="3">
+        <v>165</v>
+      </c>
+      <c r="E638" s="5">
+        <v>1</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="639" spans="3:7">
+      <c r="C639" s="6">
+        <v>16509</v>
+      </c>
+      <c r="D639" s="3">
+        <v>165</v>
+      </c>
+      <c r="E639" s="3">
+        <v>1</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="640" spans="3:7">
+      <c r="C640" s="6">
+        <v>16510</v>
+      </c>
+      <c r="D640" s="3">
+        <v>165</v>
+      </c>
+      <c r="E640" s="5">
+        <v>1</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="3:7">
+      <c r="C641" s="6">
+        <v>16511</v>
+      </c>
+      <c r="D641" s="3">
+        <v>165</v>
+      </c>
+      <c r="E641" s="5">
+        <v>1</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="642" spans="3:7">
+      <c r="C642" s="6">
+        <v>16512</v>
+      </c>
+      <c r="D642" s="3">
+        <v>165</v>
+      </c>
+      <c r="E642" s="5">
+        <v>1</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="643" spans="3:7">
+      <c r="C643" s="6">
+        <v>16513</v>
+      </c>
+      <c r="D643" s="3">
+        <v>165</v>
+      </c>
+      <c r="E643" s="3">
+        <v>1</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="644" spans="3:7">
+      <c r="C644" s="6">
+        <v>16514</v>
+      </c>
+      <c r="D644" s="3">
+        <v>165</v>
+      </c>
+      <c r="E644" s="5">
+        <v>1</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G644" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="645" spans="3:7">
+      <c r="C645" s="6">
+        <v>16515</v>
+      </c>
+      <c r="D645" s="3">
+        <v>165</v>
+      </c>
+      <c r="E645" s="5">
+        <v>1</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="646" spans="3:7">
+      <c r="C646" s="6">
+        <v>16516</v>
+      </c>
+      <c r="D646" s="3">
+        <v>165</v>
+      </c>
+      <c r="E646" s="5">
+        <v>1</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="647" spans="3:7">
+      <c r="C647" s="6">
+        <v>16517</v>
+      </c>
+      <c r="D647" s="3">
+        <v>165</v>
+      </c>
+      <c r="E647" s="3">
+        <v>1</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="648" spans="3:7">
+      <c r="C648" s="6">
+        <v>16518</v>
+      </c>
+      <c r="D648" s="3">
+        <v>165</v>
+      </c>
+      <c r="E648" s="5">
+        <v>1</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="649" spans="3:7">
+      <c r="C649" s="6">
+        <v>16519</v>
+      </c>
+      <c r="D649" s="3">
+        <v>165</v>
+      </c>
+      <c r="E649" s="5">
+        <v>1</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="650" spans="3:7">
+      <c r="C650" s="6">
+        <v>16520</v>
+      </c>
+      <c r="D650" s="3">
+        <v>165</v>
+      </c>
+      <c r="E650" s="5">
+        <v>1</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="651" spans="3:7">
+      <c r="C651" s="6">
+        <v>16521</v>
+      </c>
+      <c r="D651" s="3">
+        <v>165</v>
+      </c>
+      <c r="E651" s="3">
+        <v>1</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="652" spans="3:7">
+      <c r="C652" s="6">
+        <v>16522</v>
+      </c>
+      <c r="D652" s="3">
+        <v>165</v>
+      </c>
+      <c r="E652" s="5">
+        <v>1</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="653" spans="3:7">
+      <c r="C653" s="6">
+        <v>16523</v>
+      </c>
+      <c r="D653" s="3">
+        <v>165</v>
+      </c>
+      <c r="E653" s="5">
+        <v>1</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="654" spans="3:7">
+      <c r="C654" s="6">
+        <v>16524</v>
+      </c>
+      <c r="D654" s="3">
+        <v>165</v>
+      </c>
+      <c r="E654" s="5">
+        <v>1</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="655" spans="3:7">
+      <c r="C655" s="6">
+        <v>16525</v>
+      </c>
+      <c r="D655" s="3">
+        <v>165</v>
+      </c>
+      <c r="E655" s="3">
+        <v>1</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G655" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12095,10 +12540,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12113,10 +12558,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12131,10 +12576,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12149,10 +12594,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12169,10 +12614,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12267,10 +12712,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋165繁花谷</t>
+  </si>
+  <si>
+    <t>#先锋166萤火森林</t>
   </si>
   <si>
     <t>Center</t>
@@ -1257,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12420,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>16601</v>
+      </c>
+      <c r="D657" s="3">
+        <v>166</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>16602</v>
+      </c>
+      <c r="D658" s="3">
+        <v>166</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>16603</v>
+      </c>
+      <c r="D659" s="3">
+        <v>166</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>16604</v>
+      </c>
+      <c r="D660" s="3">
+        <v>166</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>16605</v>
+      </c>
+      <c r="D661" s="3">
+        <v>166</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>16606</v>
+      </c>
+      <c r="D662" s="3">
+        <v>166</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>16607</v>
+      </c>
+      <c r="D663" s="3">
+        <v>166</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>16608</v>
+      </c>
+      <c r="D664" s="3">
+        <v>166</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>16609</v>
+      </c>
+      <c r="D665" s="3">
+        <v>166</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>16610</v>
+      </c>
+      <c r="D666" s="3">
+        <v>166</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>16611</v>
+      </c>
+      <c r="D667" s="3">
+        <v>166</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>16612</v>
+      </c>
+      <c r="D668" s="3">
+        <v>166</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>16613</v>
+      </c>
+      <c r="D669" s="3">
+        <v>166</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>16614</v>
+      </c>
+      <c r="D670" s="3">
+        <v>166</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>16615</v>
+      </c>
+      <c r="D671" s="3">
+        <v>166</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>16616</v>
+      </c>
+      <c r="D672" s="3">
+        <v>166</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>16617</v>
+      </c>
+      <c r="D673" s="3">
+        <v>166</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>16618</v>
+      </c>
+      <c r="D674" s="3">
+        <v>166</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>16619</v>
+      </c>
+      <c r="D675" s="3">
+        <v>166</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>16620</v>
+      </c>
+      <c r="D676" s="3">
+        <v>166</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>16621</v>
+      </c>
+      <c r="D677" s="3">
+        <v>166</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>16622</v>
+      </c>
+      <c r="D678" s="3">
+        <v>166</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>16623</v>
+      </c>
+      <c r="D679" s="3">
+        <v>166</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>16624</v>
+      </c>
+      <c r="D680" s="3">
+        <v>166</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>16625</v>
+      </c>
+      <c r="D681" s="3">
+        <v>166</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12540,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12558,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12576,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12594,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12614,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12712,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -196,9 +196,6 @@
     <t>#先锋128主播专服</t>
   </si>
   <si>
-    <t>#先锋131花满楼</t>
-  </si>
-  <si>
     <t>#先锋139吉祥如意</t>
   </si>
   <si>
@@ -211,16 +208,10 @@
     <t>#先锋155雷霆万钧</t>
   </si>
   <si>
-    <t>#先锋157神谕森林</t>
-  </si>
-  <si>
     <t>#先锋159星辰之巅</t>
   </si>
   <si>
     <t>#先锋161时光镇</t>
-  </si>
-  <si>
-    <t>#先锋162棉花糖</t>
   </si>
   <si>
     <t>#先锋163破晓战歌</t>
@@ -233,6 +224,9 @@
   </si>
   <si>
     <t>#先锋166萤火森林</t>
+  </si>
+  <si>
+    <t>#先锋167青云之巅</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1254,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O629"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -7127,10 +7121,10 @@
         <v>55</v>
       </c>
       <c r="C345" s="6">
-        <v>13101</v>
+        <v>13901</v>
       </c>
       <c r="D345" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E345" s="5">
         <v>1</v>
@@ -7142,17 +7136,17 @@
         <v>15</v>
       </c>
       <c r="H345" s="3">
-        <v>20515</v>
+        <v>20475</v>
       </c>
     </row>
     <row r="346" spans="1:8">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="6">
-        <v>13102</v>
+        <v>13902</v>
       </c>
       <c r="D346" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E346" s="5">
         <v>1</v>
@@ -7164,15 +7158,15 @@
         <v>16</v>
       </c>
       <c r="H346" s="3">
-        <v>20516</v>
+        <v>20476</v>
       </c>
     </row>
     <row r="347" spans="3:8">
       <c r="C347" s="6">
-        <v>13103</v>
+        <v>13903</v>
       </c>
       <c r="D347" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E347" s="5">
         <v>1</v>
@@ -7184,15 +7178,15 @@
         <v>18</v>
       </c>
       <c r="H347" s="3">
-        <v>20517</v>
+        <v>20477</v>
       </c>
     </row>
     <row r="348" spans="3:8">
       <c r="C348" s="6">
-        <v>13104</v>
+        <v>13904</v>
       </c>
       <c r="D348" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E348" s="5">
         <v>1</v>
@@ -7204,15 +7198,15 @@
         <v>19</v>
       </c>
       <c r="H348" s="3">
-        <v>20518</v>
+        <v>20478</v>
       </c>
     </row>
     <row r="349" spans="3:7">
       <c r="C349" s="6">
-        <v>13105</v>
+        <v>13905</v>
       </c>
       <c r="D349" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E349" s="3">
         <v>1</v>
@@ -7226,10 +7220,10 @@
     </row>
     <row r="350" spans="3:7">
       <c r="C350" s="6">
-        <v>13106</v>
+        <v>13906</v>
       </c>
       <c r="D350" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E350" s="5">
         <v>1</v>
@@ -7243,10 +7237,10 @@
     </row>
     <row r="351" spans="3:7">
       <c r="C351" s="6">
-        <v>13107</v>
+        <v>13907</v>
       </c>
       <c r="D351" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E351" s="5">
         <v>1</v>
@@ -7260,10 +7254,10 @@
     </row>
     <row r="352" spans="3:7">
       <c r="C352" s="6">
-        <v>13108</v>
+        <v>13908</v>
       </c>
       <c r="D352" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E352" s="5">
         <v>1</v>
@@ -7277,10 +7271,10 @@
     </row>
     <row r="353" spans="3:7">
       <c r="C353" s="6">
-        <v>13109</v>
+        <v>13909</v>
       </c>
       <c r="D353" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E353" s="3">
         <v>1</v>
@@ -7294,10 +7288,10 @@
     </row>
     <row r="354" spans="3:7">
       <c r="C354" s="6">
-        <v>13110</v>
+        <v>13910</v>
       </c>
       <c r="D354" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E354" s="5">
         <v>1</v>
@@ -7311,10 +7305,10 @@
     </row>
     <row r="355" spans="3:7">
       <c r="C355" s="6">
-        <v>13111</v>
+        <v>13911</v>
       </c>
       <c r="D355" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E355" s="5">
         <v>1</v>
@@ -7328,10 +7322,10 @@
     </row>
     <row r="356" spans="3:7">
       <c r="C356" s="6">
-        <v>13112</v>
+        <v>13912</v>
       </c>
       <c r="D356" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E356" s="5">
         <v>1</v>
@@ -7345,10 +7339,10 @@
     </row>
     <row r="357" spans="3:7">
       <c r="C357" s="6">
-        <v>13113</v>
+        <v>13913</v>
       </c>
       <c r="D357" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E357" s="3">
         <v>1</v>
@@ -7362,10 +7356,10 @@
     </row>
     <row r="358" spans="3:7">
       <c r="C358" s="6">
-        <v>13114</v>
+        <v>13914</v>
       </c>
       <c r="D358" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E358" s="5">
         <v>1</v>
@@ -7379,10 +7373,10 @@
     </row>
     <row r="359" spans="3:7">
       <c r="C359" s="6">
-        <v>13115</v>
+        <v>13915</v>
       </c>
       <c r="D359" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E359" s="5">
         <v>1</v>
@@ -7396,10 +7390,10 @@
     </row>
     <row r="360" spans="3:7">
       <c r="C360" s="6">
-        <v>13116</v>
+        <v>13916</v>
       </c>
       <c r="D360" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E360" s="5">
         <v>1</v>
@@ -7413,10 +7407,10 @@
     </row>
     <row r="361" spans="3:7">
       <c r="C361" s="6">
-        <v>13117</v>
+        <v>13917</v>
       </c>
       <c r="D361" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E361" s="3">
         <v>1</v>
@@ -7430,10 +7424,10 @@
     </row>
     <row r="362" spans="3:7">
       <c r="C362" s="6">
-        <v>13118</v>
+        <v>13918</v>
       </c>
       <c r="D362" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E362" s="5">
         <v>1</v>
@@ -7447,10 +7441,10 @@
     </row>
     <row r="363" spans="3:7">
       <c r="C363" s="6">
-        <v>13119</v>
+        <v>13919</v>
       </c>
       <c r="D363" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E363" s="5">
         <v>1</v>
@@ -7464,10 +7458,10 @@
     </row>
     <row r="364" spans="3:7">
       <c r="C364" s="6">
-        <v>13120</v>
+        <v>13920</v>
       </c>
       <c r="D364" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E364" s="5">
         <v>1</v>
@@ -7481,10 +7475,10 @@
     </row>
     <row r="365" spans="3:7">
       <c r="C365" s="6">
-        <v>13121</v>
+        <v>13921</v>
       </c>
       <c r="D365" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E365" s="3">
         <v>1</v>
@@ -7498,10 +7492,10 @@
     </row>
     <row r="366" spans="3:7">
       <c r="C366" s="6">
-        <v>13122</v>
+        <v>13922</v>
       </c>
       <c r="D366" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E366" s="5">
         <v>1</v>
@@ -7515,10 +7509,10 @@
     </row>
     <row r="367" spans="3:7">
       <c r="C367" s="6">
-        <v>13123</v>
+        <v>13923</v>
       </c>
       <c r="D367" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E367" s="5">
         <v>1</v>
@@ -7532,10 +7526,10 @@
     </row>
     <row r="368" spans="3:7">
       <c r="C368" s="6">
-        <v>13124</v>
+        <v>13924</v>
       </c>
       <c r="D368" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E368" s="5">
         <v>1</v>
@@ -7549,10 +7543,10 @@
     </row>
     <row r="369" spans="3:7">
       <c r="C369" s="6">
-        <v>13125</v>
+        <v>13925</v>
       </c>
       <c r="D369" s="3">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E369" s="3">
         <v>1</v>
@@ -7569,10 +7563,10 @@
         <v>56</v>
       </c>
       <c r="C371" s="6">
-        <v>13901</v>
+        <v>14701</v>
       </c>
       <c r="D371" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E371" s="5">
         <v>1</v>
@@ -7584,17 +7578,17 @@
         <v>15</v>
       </c>
       <c r="H371" s="3">
-        <v>20475</v>
+        <v>20495</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="6">
-        <v>13902</v>
+        <v>14702</v>
       </c>
       <c r="D372" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E372" s="5">
         <v>1</v>
@@ -7606,15 +7600,15 @@
         <v>16</v>
       </c>
       <c r="H372" s="3">
-        <v>20476</v>
+        <v>20496</v>
       </c>
     </row>
     <row r="373" spans="3:8">
       <c r="C373" s="6">
-        <v>13903</v>
+        <v>14703</v>
       </c>
       <c r="D373" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E373" s="5">
         <v>1</v>
@@ -7626,15 +7620,15 @@
         <v>18</v>
       </c>
       <c r="H373" s="3">
-        <v>20477</v>
+        <v>20497</v>
       </c>
     </row>
     <row r="374" spans="3:8">
       <c r="C374" s="6">
-        <v>13904</v>
+        <v>14704</v>
       </c>
       <c r="D374" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E374" s="5">
         <v>1</v>
@@ -7646,15 +7640,15 @@
         <v>19</v>
       </c>
       <c r="H374" s="3">
-        <v>20478</v>
+        <v>20498</v>
       </c>
     </row>
     <row r="375" spans="3:7">
       <c r="C375" s="6">
-        <v>13905</v>
+        <v>14705</v>
       </c>
       <c r="D375" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E375" s="3">
         <v>1</v>
@@ -7668,10 +7662,10 @@
     </row>
     <row r="376" spans="3:7">
       <c r="C376" s="6">
-        <v>13906</v>
+        <v>14706</v>
       </c>
       <c r="D376" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E376" s="5">
         <v>1</v>
@@ -7685,10 +7679,10 @@
     </row>
     <row r="377" spans="3:7">
       <c r="C377" s="6">
-        <v>13907</v>
+        <v>14707</v>
       </c>
       <c r="D377" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E377" s="5">
         <v>1</v>
@@ -7702,10 +7696,10 @@
     </row>
     <row r="378" spans="3:7">
       <c r="C378" s="6">
-        <v>13908</v>
+        <v>14708</v>
       </c>
       <c r="D378" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E378" s="5">
         <v>1</v>
@@ -7719,10 +7713,10 @@
     </row>
     <row r="379" spans="3:7">
       <c r="C379" s="6">
-        <v>13909</v>
+        <v>14709</v>
       </c>
       <c r="D379" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E379" s="3">
         <v>1</v>
@@ -7736,10 +7730,10 @@
     </row>
     <row r="380" spans="3:7">
       <c r="C380" s="6">
-        <v>13910</v>
+        <v>14710</v>
       </c>
       <c r="D380" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E380" s="5">
         <v>1</v>
@@ -7753,10 +7747,10 @@
     </row>
     <row r="381" spans="3:7">
       <c r="C381" s="6">
-        <v>13911</v>
+        <v>14711</v>
       </c>
       <c r="D381" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E381" s="5">
         <v>1</v>
@@ -7770,10 +7764,10 @@
     </row>
     <row r="382" spans="3:7">
       <c r="C382" s="6">
-        <v>13912</v>
+        <v>14712</v>
       </c>
       <c r="D382" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E382" s="5">
         <v>1</v>
@@ -7787,10 +7781,10 @@
     </row>
     <row r="383" spans="3:7">
       <c r="C383" s="6">
-        <v>13913</v>
+        <v>14713</v>
       </c>
       <c r="D383" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E383" s="3">
         <v>1</v>
@@ -7804,10 +7798,10 @@
     </row>
     <row r="384" spans="3:7">
       <c r="C384" s="6">
-        <v>13914</v>
+        <v>14714</v>
       </c>
       <c r="D384" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E384" s="5">
         <v>1</v>
@@ -7821,10 +7815,10 @@
     </row>
     <row r="385" spans="3:7">
       <c r="C385" s="6">
-        <v>13915</v>
+        <v>14715</v>
       </c>
       <c r="D385" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E385" s="5">
         <v>1</v>
@@ -7838,10 +7832,10 @@
     </row>
     <row r="386" spans="3:7">
       <c r="C386" s="6">
-        <v>13916</v>
+        <v>14716</v>
       </c>
       <c r="D386" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E386" s="5">
         <v>1</v>
@@ -7855,10 +7849,10 @@
     </row>
     <row r="387" spans="3:7">
       <c r="C387" s="6">
-        <v>13917</v>
+        <v>14717</v>
       </c>
       <c r="D387" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E387" s="3">
         <v>1</v>
@@ -7872,10 +7866,10 @@
     </row>
     <row r="388" spans="3:7">
       <c r="C388" s="6">
-        <v>13918</v>
+        <v>14718</v>
       </c>
       <c r="D388" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E388" s="5">
         <v>1</v>
@@ -7889,10 +7883,10 @@
     </row>
     <row r="389" spans="3:7">
       <c r="C389" s="6">
-        <v>13919</v>
+        <v>14719</v>
       </c>
       <c r="D389" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E389" s="5">
         <v>1</v>
@@ -7906,10 +7900,10 @@
     </row>
     <row r="390" spans="3:7">
       <c r="C390" s="6">
-        <v>13920</v>
+        <v>14720</v>
       </c>
       <c r="D390" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E390" s="5">
         <v>1</v>
@@ -7923,10 +7917,10 @@
     </row>
     <row r="391" spans="3:7">
       <c r="C391" s="6">
-        <v>13921</v>
+        <v>14721</v>
       </c>
       <c r="D391" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E391" s="3">
         <v>1</v>
@@ -7940,10 +7934,10 @@
     </row>
     <row r="392" spans="3:7">
       <c r="C392" s="6">
-        <v>13922</v>
+        <v>14722</v>
       </c>
       <c r="D392" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E392" s="5">
         <v>1</v>
@@ -7957,10 +7951,10 @@
     </row>
     <row r="393" spans="3:7">
       <c r="C393" s="6">
-        <v>13923</v>
+        <v>14723</v>
       </c>
       <c r="D393" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E393" s="5">
         <v>1</v>
@@ -7974,10 +7968,10 @@
     </row>
     <row r="394" spans="3:7">
       <c r="C394" s="6">
-        <v>13924</v>
+        <v>14724</v>
       </c>
       <c r="D394" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E394" s="5">
         <v>1</v>
@@ -7991,10 +7985,10 @@
     </row>
     <row r="395" spans="3:7">
       <c r="C395" s="6">
-        <v>13925</v>
+        <v>14725</v>
       </c>
       <c r="D395" s="3">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E395" s="3">
         <v>1</v>
@@ -8011,10 +8005,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>14701</v>
+        <v>15101</v>
       </c>
       <c r="D397" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8026,17 +8020,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20495</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>14702</v>
+        <v>15102</v>
       </c>
       <c r="D398" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8048,15 +8042,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20496</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="399" spans="3:8">
       <c r="C399" s="6">
-        <v>14703</v>
+        <v>15103</v>
       </c>
       <c r="D399" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8068,15 +8062,15 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20497</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="400" spans="3:8">
       <c r="C400" s="6">
-        <v>14704</v>
+        <v>15104</v>
       </c>
       <c r="D400" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E400" s="5">
         <v>1</v>
@@ -8088,15 +8082,15 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20498</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>14705</v>
+        <v>15105</v>
       </c>
       <c r="D401" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E401" s="3">
         <v>1</v>
@@ -8110,10 +8104,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>14706</v>
+        <v>15106</v>
       </c>
       <c r="D402" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8127,10 +8121,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>14707</v>
+        <v>15107</v>
       </c>
       <c r="D403" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8144,10 +8138,10 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>14708</v>
+        <v>15108</v>
       </c>
       <c r="D404" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E404" s="5">
         <v>1</v>
@@ -8161,10 +8155,10 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>14709</v>
+        <v>15109</v>
       </c>
       <c r="D405" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E405" s="3">
         <v>1</v>
@@ -8178,10 +8172,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>14710</v>
+        <v>15110</v>
       </c>
       <c r="D406" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8195,10 +8189,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>14711</v>
+        <v>15111</v>
       </c>
       <c r="D407" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8212,10 +8206,10 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>14712</v>
+        <v>15112</v>
       </c>
       <c r="D408" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E408" s="5">
         <v>1</v>
@@ -8229,10 +8223,10 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>14713</v>
+        <v>15113</v>
       </c>
       <c r="D409" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E409" s="3">
         <v>1</v>
@@ -8246,10 +8240,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>14714</v>
+        <v>15114</v>
       </c>
       <c r="D410" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8263,10 +8257,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>14715</v>
+        <v>15115</v>
       </c>
       <c r="D411" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8280,10 +8274,10 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>14716</v>
+        <v>15116</v>
       </c>
       <c r="D412" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E412" s="5">
         <v>1</v>
@@ -8297,10 +8291,10 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>14717</v>
+        <v>15117</v>
       </c>
       <c r="D413" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E413" s="3">
         <v>1</v>
@@ -8314,10 +8308,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>14718</v>
+        <v>15118</v>
       </c>
       <c r="D414" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8331,10 +8325,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>14719</v>
+        <v>15119</v>
       </c>
       <c r="D415" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8348,10 +8342,10 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>14720</v>
+        <v>15120</v>
       </c>
       <c r="D416" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E416" s="5">
         <v>1</v>
@@ -8365,10 +8359,10 @@
     </row>
     <row r="417" spans="3:7">
       <c r="C417" s="6">
-        <v>14721</v>
+        <v>15121</v>
       </c>
       <c r="D417" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E417" s="3">
         <v>1</v>
@@ -8382,10 +8376,10 @@
     </row>
     <row r="418" spans="3:7">
       <c r="C418" s="6">
-        <v>14722</v>
+        <v>15122</v>
       </c>
       <c r="D418" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8399,10 +8393,10 @@
     </row>
     <row r="419" spans="3:7">
       <c r="C419" s="6">
-        <v>14723</v>
+        <v>15123</v>
       </c>
       <c r="D419" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8416,10 +8410,10 @@
     </row>
     <row r="420" spans="3:7">
       <c r="C420" s="6">
-        <v>14724</v>
+        <v>15124</v>
       </c>
       <c r="D420" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E420" s="5">
         <v>1</v>
@@ -8433,10 +8427,10 @@
     </row>
     <row r="421" spans="3:7">
       <c r="C421" s="6">
-        <v>14725</v>
+        <v>15125</v>
       </c>
       <c r="D421" s="3">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E421" s="3">
         <v>1</v>
@@ -8453,10 +8447,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>15101</v>
+        <v>15501</v>
       </c>
       <c r="D423" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8468,17 +8462,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20415</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>15102</v>
+        <v>15502</v>
       </c>
       <c r="D424" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8490,15 +8484,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20416</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>15103</v>
+        <v>15503</v>
       </c>
       <c r="D425" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8510,15 +8504,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20417</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>15104</v>
+        <v>15504</v>
       </c>
       <c r="D426" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8530,15 +8524,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20418</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>15105</v>
+        <v>15505</v>
       </c>
       <c r="D427" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8552,10 +8546,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>15106</v>
+        <v>15506</v>
       </c>
       <c r="D428" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8569,10 +8563,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>15107</v>
+        <v>15507</v>
       </c>
       <c r="D429" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8586,10 +8580,10 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>15108</v>
+        <v>15508</v>
       </c>
       <c r="D430" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8603,10 +8597,10 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>15109</v>
+        <v>15509</v>
       </c>
       <c r="D431" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8620,10 +8614,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>15110</v>
+        <v>15510</v>
       </c>
       <c r="D432" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8637,10 +8631,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>15111</v>
+        <v>15511</v>
       </c>
       <c r="D433" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8654,10 +8648,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>15112</v>
+        <v>15512</v>
       </c>
       <c r="D434" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8671,10 +8665,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>15113</v>
+        <v>15513</v>
       </c>
       <c r="D435" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8688,10 +8682,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>15114</v>
+        <v>15514</v>
       </c>
       <c r="D436" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8705,10 +8699,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>15115</v>
+        <v>15515</v>
       </c>
       <c r="D437" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8722,10 +8716,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>15116</v>
+        <v>15516</v>
       </c>
       <c r="D438" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8739,10 +8733,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>15117</v>
+        <v>15517</v>
       </c>
       <c r="D439" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8756,10 +8750,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>15118</v>
+        <v>15518</v>
       </c>
       <c r="D440" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8773,10 +8767,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>15119</v>
+        <v>15519</v>
       </c>
       <c r="D441" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8790,10 +8784,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>15120</v>
+        <v>15520</v>
       </c>
       <c r="D442" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8807,10 +8801,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>15121</v>
+        <v>15521</v>
       </c>
       <c r="D443" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8824,10 +8818,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>15122</v>
+        <v>15522</v>
       </c>
       <c r="D444" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8841,10 +8835,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>15123</v>
+        <v>15523</v>
       </c>
       <c r="D445" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8858,10 +8852,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>15124</v>
+        <v>15524</v>
       </c>
       <c r="D446" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8875,10 +8869,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>15125</v>
+        <v>15525</v>
       </c>
       <c r="D447" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8895,10 +8889,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>15501</v>
+        <v>15901</v>
       </c>
       <c r="D449" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8910,17 +8904,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20605</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>15502</v>
+        <v>15902</v>
       </c>
       <c r="D450" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8932,15 +8926,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20606</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>15503</v>
+        <v>15903</v>
       </c>
       <c r="D451" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8952,15 +8946,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20607</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>15504</v>
+        <v>15904</v>
       </c>
       <c r="D452" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8972,15 +8966,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20608</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>15505</v>
+        <v>15905</v>
       </c>
       <c r="D453" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -8994,10 +8988,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>15506</v>
+        <v>15906</v>
       </c>
       <c r="D454" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9011,10 +9005,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>15507</v>
+        <v>15907</v>
       </c>
       <c r="D455" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9028,10 +9022,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>15508</v>
+        <v>15908</v>
       </c>
       <c r="D456" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9045,10 +9039,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>15509</v>
+        <v>15909</v>
       </c>
       <c r="D457" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9062,10 +9056,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>15510</v>
+        <v>15910</v>
       </c>
       <c r="D458" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9079,10 +9073,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>15511</v>
+        <v>15911</v>
       </c>
       <c r="D459" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9096,10 +9090,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>15512</v>
+        <v>15912</v>
       </c>
       <c r="D460" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9113,10 +9107,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>15513</v>
+        <v>15913</v>
       </c>
       <c r="D461" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9130,10 +9124,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>15514</v>
+        <v>15914</v>
       </c>
       <c r="D462" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9147,10 +9141,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>15515</v>
+        <v>15915</v>
       </c>
       <c r="D463" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9164,10 +9158,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>15516</v>
+        <v>15916</v>
       </c>
       <c r="D464" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9181,10 +9175,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>15517</v>
+        <v>15917</v>
       </c>
       <c r="D465" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9198,10 +9192,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>15518</v>
+        <v>15918</v>
       </c>
       <c r="D466" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9215,10 +9209,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>15519</v>
+        <v>15919</v>
       </c>
       <c r="D467" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9232,10 +9226,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>15520</v>
+        <v>15920</v>
       </c>
       <c r="D468" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9249,10 +9243,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>15521</v>
+        <v>15921</v>
       </c>
       <c r="D469" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9266,10 +9260,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>15522</v>
+        <v>15922</v>
       </c>
       <c r="D470" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9283,10 +9277,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>15523</v>
+        <v>15923</v>
       </c>
       <c r="D471" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9300,10 +9294,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>15524</v>
+        <v>15924</v>
       </c>
       <c r="D472" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9317,10 +9311,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>15525</v>
+        <v>15925</v>
       </c>
       <c r="D473" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9337,10 +9331,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>15701</v>
+        <v>16101</v>
       </c>
       <c r="D475" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9352,17 +9346,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20645</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>15702</v>
+        <v>16102</v>
       </c>
       <c r="D476" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9374,15 +9368,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20646</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>15703</v>
+        <v>16103</v>
       </c>
       <c r="D477" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9394,15 +9388,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20647</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>15704</v>
+        <v>16104</v>
       </c>
       <c r="D478" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9414,15 +9408,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20648</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>15705</v>
+        <v>16105</v>
       </c>
       <c r="D479" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9436,10 +9430,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>15706</v>
+        <v>16106</v>
       </c>
       <c r="D480" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9453,10 +9447,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>15707</v>
+        <v>16107</v>
       </c>
       <c r="D481" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9470,10 +9464,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>15708</v>
+        <v>16108</v>
       </c>
       <c r="D482" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9487,10 +9481,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>15709</v>
+        <v>16109</v>
       </c>
       <c r="D483" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9504,10 +9498,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>15710</v>
+        <v>16110</v>
       </c>
       <c r="D484" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9521,10 +9515,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>15711</v>
+        <v>16111</v>
       </c>
       <c r="D485" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9538,10 +9532,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>15712</v>
+        <v>16112</v>
       </c>
       <c r="D486" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9555,10 +9549,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>15713</v>
+        <v>16113</v>
       </c>
       <c r="D487" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9572,10 +9566,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>15714</v>
+        <v>16114</v>
       </c>
       <c r="D488" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9589,10 +9583,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>15715</v>
+        <v>16115</v>
       </c>
       <c r="D489" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9606,10 +9600,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>15716</v>
+        <v>16116</v>
       </c>
       <c r="D490" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9623,10 +9617,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>15717</v>
+        <v>16117</v>
       </c>
       <c r="D491" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9640,10 +9634,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>15718</v>
+        <v>16118</v>
       </c>
       <c r="D492" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9657,10 +9651,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>15719</v>
+        <v>16119</v>
       </c>
       <c r="D493" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9674,10 +9668,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>15720</v>
+        <v>16120</v>
       </c>
       <c r="D494" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9691,10 +9685,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>15721</v>
+        <v>16121</v>
       </c>
       <c r="D495" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9708,10 +9702,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>15722</v>
+        <v>16122</v>
       </c>
       <c r="D496" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9725,10 +9719,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>15723</v>
+        <v>16123</v>
       </c>
       <c r="D497" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9742,10 +9736,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>15724</v>
+        <v>16124</v>
       </c>
       <c r="D498" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9759,10 +9753,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>15725</v>
+        <v>16125</v>
       </c>
       <c r="D499" s="3">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9779,10 +9773,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>15901</v>
+        <v>16301</v>
       </c>
       <c r="D501" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9794,17 +9788,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20405</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>15902</v>
+        <v>16302</v>
       </c>
       <c r="D502" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9816,15 +9810,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20406</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>15903</v>
+        <v>16303</v>
       </c>
       <c r="D503" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9836,15 +9830,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20407</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>15904</v>
+        <v>16304</v>
       </c>
       <c r="D504" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9856,15 +9850,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20408</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>15905</v>
+        <v>16305</v>
       </c>
       <c r="D505" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9878,10 +9872,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>15906</v>
+        <v>16306</v>
       </c>
       <c r="D506" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9895,10 +9889,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>15907</v>
+        <v>16307</v>
       </c>
       <c r="D507" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9912,10 +9906,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>15908</v>
+        <v>16308</v>
       </c>
       <c r="D508" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9929,10 +9923,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>15909</v>
+        <v>16309</v>
       </c>
       <c r="D509" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9946,10 +9940,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>15910</v>
+        <v>16310</v>
       </c>
       <c r="D510" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9963,10 +9957,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>15911</v>
+        <v>16311</v>
       </c>
       <c r="D511" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9980,10 +9974,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>15912</v>
+        <v>16312</v>
       </c>
       <c r="D512" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -9997,10 +9991,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>15913</v>
+        <v>16313</v>
       </c>
       <c r="D513" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10014,10 +10008,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>15914</v>
+        <v>16314</v>
       </c>
       <c r="D514" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10031,10 +10025,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>15915</v>
+        <v>16315</v>
       </c>
       <c r="D515" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10048,10 +10042,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>15916</v>
+        <v>16316</v>
       </c>
       <c r="D516" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10065,10 +10059,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>15917</v>
+        <v>16317</v>
       </c>
       <c r="D517" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10082,10 +10076,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>15918</v>
+        <v>16318</v>
       </c>
       <c r="D518" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10099,10 +10093,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>15919</v>
+        <v>16319</v>
       </c>
       <c r="D519" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10116,10 +10110,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>15920</v>
+        <v>16320</v>
       </c>
       <c r="D520" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10133,10 +10127,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>15921</v>
+        <v>16321</v>
       </c>
       <c r="D521" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10150,10 +10144,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>15922</v>
+        <v>16322</v>
       </c>
       <c r="D522" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10167,10 +10161,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>15923</v>
+        <v>16323</v>
       </c>
       <c r="D523" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10184,10 +10178,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>15924</v>
+        <v>16324</v>
       </c>
       <c r="D524" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10201,10 +10195,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>15925</v>
+        <v>16325</v>
       </c>
       <c r="D525" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10221,10 +10215,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>16101</v>
+        <v>16401</v>
       </c>
       <c r="D527" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10236,17 +10230,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20445</v>
+        <v>20545</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>16102</v>
+        <v>16402</v>
       </c>
       <c r="D528" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10258,15 +10252,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20446</v>
+        <v>20546</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>16103</v>
+        <v>16403</v>
       </c>
       <c r="D529" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10278,15 +10272,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20447</v>
+        <v>20547</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>16104</v>
+        <v>16404</v>
       </c>
       <c r="D530" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10298,15 +10292,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20448</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>16105</v>
+        <v>16405</v>
       </c>
       <c r="D531" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10320,10 +10314,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>16106</v>
+        <v>16406</v>
       </c>
       <c r="D532" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10337,10 +10331,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>16107</v>
+        <v>16407</v>
       </c>
       <c r="D533" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10354,10 +10348,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>16108</v>
+        <v>16408</v>
       </c>
       <c r="D534" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10371,10 +10365,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>16109</v>
+        <v>16409</v>
       </c>
       <c r="D535" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10388,10 +10382,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>16110</v>
+        <v>16410</v>
       </c>
       <c r="D536" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10405,10 +10399,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>16111</v>
+        <v>16411</v>
       </c>
       <c r="D537" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10422,10 +10416,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>16112</v>
+        <v>16412</v>
       </c>
       <c r="D538" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10439,10 +10433,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>16113</v>
+        <v>16413</v>
       </c>
       <c r="D539" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10456,10 +10450,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>16114</v>
+        <v>16414</v>
       </c>
       <c r="D540" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10473,10 +10467,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>16115</v>
+        <v>16415</v>
       </c>
       <c r="D541" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10490,10 +10484,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>16116</v>
+        <v>16416</v>
       </c>
       <c r="D542" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10507,10 +10501,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>16117</v>
+        <v>16417</v>
       </c>
       <c r="D543" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10524,10 +10518,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>16118</v>
+        <v>16418</v>
       </c>
       <c r="D544" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10541,10 +10535,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>16119</v>
+        <v>16419</v>
       </c>
       <c r="D545" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10558,10 +10552,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>16120</v>
+        <v>16420</v>
       </c>
       <c r="D546" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10575,10 +10569,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>16121</v>
+        <v>16421</v>
       </c>
       <c r="D547" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10592,10 +10586,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>16122</v>
+        <v>16422</v>
       </c>
       <c r="D548" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10609,10 +10603,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>16123</v>
+        <v>16423</v>
       </c>
       <c r="D549" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10626,10 +10620,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>16124</v>
+        <v>16424</v>
       </c>
       <c r="D550" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10643,10 +10637,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>16125</v>
+        <v>16425</v>
       </c>
       <c r="D551" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10663,10 +10657,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>16201</v>
+        <v>16501</v>
       </c>
       <c r="D553" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10678,17 +10672,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20505</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>16202</v>
+        <v>16502</v>
       </c>
       <c r="D554" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10700,15 +10694,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20506</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>16203</v>
+        <v>16503</v>
       </c>
       <c r="D555" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10720,15 +10714,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20507</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>16204</v>
+        <v>16504</v>
       </c>
       <c r="D556" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10740,15 +10734,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20508</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>16205</v>
+        <v>16505</v>
       </c>
       <c r="D557" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10762,10 +10756,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>16206</v>
+        <v>16506</v>
       </c>
       <c r="D558" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10779,10 +10773,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>16207</v>
+        <v>16507</v>
       </c>
       <c r="D559" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10796,10 +10790,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>16208</v>
+        <v>16508</v>
       </c>
       <c r="D560" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10813,10 +10807,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>16209</v>
+        <v>16509</v>
       </c>
       <c r="D561" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10830,10 +10824,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>16210</v>
+        <v>16510</v>
       </c>
       <c r="D562" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10847,10 +10841,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>16211</v>
+        <v>16511</v>
       </c>
       <c r="D563" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10864,10 +10858,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>16212</v>
+        <v>16512</v>
       </c>
       <c r="D564" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10881,10 +10875,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>16213</v>
+        <v>16513</v>
       </c>
       <c r="D565" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10898,10 +10892,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>16214</v>
+        <v>16514</v>
       </c>
       <c r="D566" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10915,10 +10909,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>16215</v>
+        <v>16515</v>
       </c>
       <c r="D567" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10932,10 +10926,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>16216</v>
+        <v>16516</v>
       </c>
       <c r="D568" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10949,10 +10943,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>16217</v>
+        <v>16517</v>
       </c>
       <c r="D569" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10966,10 +10960,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>16218</v>
+        <v>16518</v>
       </c>
       <c r="D570" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10983,10 +10977,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>16219</v>
+        <v>16519</v>
       </c>
       <c r="D571" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11000,10 +10994,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>16220</v>
+        <v>16520</v>
       </c>
       <c r="D572" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11017,10 +11011,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>16221</v>
+        <v>16521</v>
       </c>
       <c r="D573" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11034,10 +11028,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>16222</v>
+        <v>16522</v>
       </c>
       <c r="D574" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11051,10 +11045,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>16223</v>
+        <v>16523</v>
       </c>
       <c r="D575" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11068,10 +11062,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>16224</v>
+        <v>16524</v>
       </c>
       <c r="D576" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11085,10 +11079,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>16225</v>
+        <v>16525</v>
       </c>
       <c r="D577" s="3">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11105,10 +11099,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>16301</v>
+        <v>16601</v>
       </c>
       <c r="D579" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11120,17 +11114,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20525</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>16302</v>
+        <v>16602</v>
       </c>
       <c r="D580" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11142,15 +11136,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20526</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>16303</v>
+        <v>16603</v>
       </c>
       <c r="D581" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11162,15 +11156,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20527</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>16304</v>
+        <v>16604</v>
       </c>
       <c r="D582" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11182,15 +11176,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20528</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>16305</v>
+        <v>16605</v>
       </c>
       <c r="D583" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11204,10 +11198,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>16306</v>
+        <v>16606</v>
       </c>
       <c r="D584" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11221,10 +11215,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>16307</v>
+        <v>16607</v>
       </c>
       <c r="D585" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11238,10 +11232,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>16308</v>
+        <v>16608</v>
       </c>
       <c r="D586" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11255,10 +11249,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>16309</v>
+        <v>16609</v>
       </c>
       <c r="D587" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11272,10 +11266,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>16310</v>
+        <v>16610</v>
       </c>
       <c r="D588" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11289,10 +11283,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>16311</v>
+        <v>16611</v>
       </c>
       <c r="D589" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11306,10 +11300,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>16312</v>
+        <v>16612</v>
       </c>
       <c r="D590" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11323,10 +11317,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>16313</v>
+        <v>16613</v>
       </c>
       <c r="D591" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11340,10 +11334,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>16314</v>
+        <v>16614</v>
       </c>
       <c r="D592" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11357,10 +11351,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>16315</v>
+        <v>16615</v>
       </c>
       <c r="D593" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11374,10 +11368,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>16316</v>
+        <v>16616</v>
       </c>
       <c r="D594" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11391,10 +11385,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>16317</v>
+        <v>16617</v>
       </c>
       <c r="D595" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11408,10 +11402,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>16318</v>
+        <v>16618</v>
       </c>
       <c r="D596" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11425,10 +11419,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>16319</v>
+        <v>16619</v>
       </c>
       <c r="D597" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11442,10 +11436,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>16320</v>
+        <v>16620</v>
       </c>
       <c r="D598" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11459,10 +11453,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>16321</v>
+        <v>16621</v>
       </c>
       <c r="D599" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11476,10 +11470,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>16322</v>
+        <v>16622</v>
       </c>
       <c r="D600" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11493,10 +11487,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>16323</v>
+        <v>16623</v>
       </c>
       <c r="D601" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11510,10 +11504,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>16324</v>
+        <v>16624</v>
       </c>
       <c r="D602" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11527,10 +11521,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>16325</v>
+        <v>16625</v>
       </c>
       <c r="D603" s="3">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11547,10 +11541,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>16401</v>
+        <v>16701</v>
       </c>
       <c r="D605" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11562,17 +11556,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20545</v>
+        <v>20555</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>16402</v>
+        <v>16702</v>
       </c>
       <c r="D606" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11584,15 +11578,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20546</v>
+        <v>20556</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>16403</v>
+        <v>16703</v>
       </c>
       <c r="D607" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11604,15 +11598,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20547</v>
+        <v>20557</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>16404</v>
+        <v>16704</v>
       </c>
       <c r="D608" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11624,15 +11618,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20548</v>
+        <v>20558</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>16405</v>
+        <v>16705</v>
       </c>
       <c r="D609" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11646,10 +11640,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>16406</v>
+        <v>16706</v>
       </c>
       <c r="D610" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11663,10 +11657,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>16407</v>
+        <v>16707</v>
       </c>
       <c r="D611" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11680,10 +11674,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>16408</v>
+        <v>16708</v>
       </c>
       <c r="D612" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11697,10 +11691,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>16409</v>
+        <v>16709</v>
       </c>
       <c r="D613" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11714,10 +11708,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>16410</v>
+        <v>16710</v>
       </c>
       <c r="D614" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11731,10 +11725,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>16411</v>
+        <v>16711</v>
       </c>
       <c r="D615" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11748,10 +11742,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>16412</v>
+        <v>16712</v>
       </c>
       <c r="D616" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11765,10 +11759,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>16413</v>
+        <v>16713</v>
       </c>
       <c r="D617" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11782,10 +11776,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>16414</v>
+        <v>16714</v>
       </c>
       <c r="D618" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11799,10 +11793,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>16415</v>
+        <v>16715</v>
       </c>
       <c r="D619" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11816,10 +11810,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>16416</v>
+        <v>16716</v>
       </c>
       <c r="D620" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11833,10 +11827,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>16417</v>
+        <v>16717</v>
       </c>
       <c r="D621" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11850,10 +11844,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>16418</v>
+        <v>16718</v>
       </c>
       <c r="D622" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11867,10 +11861,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>16419</v>
+        <v>16719</v>
       </c>
       <c r="D623" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11884,10 +11878,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>16420</v>
+        <v>16720</v>
       </c>
       <c r="D624" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11901,10 +11895,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>16421</v>
+        <v>16721</v>
       </c>
       <c r="D625" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11918,10 +11912,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>16422</v>
+        <v>16722</v>
       </c>
       <c r="D626" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11935,10 +11929,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>16423</v>
+        <v>16723</v>
       </c>
       <c r="D627" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11952,10 +11946,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>16424</v>
+        <v>16724</v>
       </c>
       <c r="D628" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11969,10 +11963,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>16425</v>
+        <v>16725</v>
       </c>
       <c r="D629" s="3">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11981,890 +11975,6 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8">
-      <c r="A631" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C631" s="6">
-        <v>16501</v>
-      </c>
-      <c r="D631" s="3">
-        <v>165</v>
-      </c>
-      <c r="E631" s="5">
-        <v>1</v>
-      </c>
-      <c r="F631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H631" s="3">
-        <v>20375</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8">
-      <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
-      <c r="C632" s="6">
-        <v>16502</v>
-      </c>
-      <c r="D632" s="3">
-        <v>165</v>
-      </c>
-      <c r="E632" s="5">
-        <v>1</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H632" s="3">
-        <v>20376</v>
-      </c>
-    </row>
-    <row r="633" spans="3:8">
-      <c r="C633" s="6">
-        <v>16503</v>
-      </c>
-      <c r="D633" s="3">
-        <v>165</v>
-      </c>
-      <c r="E633" s="5">
-        <v>1</v>
-      </c>
-      <c r="F633" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G633" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H633" s="3">
-        <v>20377</v>
-      </c>
-    </row>
-    <row r="634" spans="3:8">
-      <c r="C634" s="6">
-        <v>16504</v>
-      </c>
-      <c r="D634" s="3">
-        <v>165</v>
-      </c>
-      <c r="E634" s="5">
-        <v>1</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H634" s="3">
-        <v>20378</v>
-      </c>
-    </row>
-    <row r="635" spans="3:7">
-      <c r="C635" s="6">
-        <v>16505</v>
-      </c>
-      <c r="D635" s="3">
-        <v>165</v>
-      </c>
-      <c r="E635" s="3">
-        <v>1</v>
-      </c>
-      <c r="F635" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G635" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="636" spans="3:7">
-      <c r="C636" s="6">
-        <v>16506</v>
-      </c>
-      <c r="D636" s="3">
-        <v>165</v>
-      </c>
-      <c r="E636" s="5">
-        <v>1</v>
-      </c>
-      <c r="F636" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G636" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="637" spans="3:7">
-      <c r="C637" s="6">
-        <v>16507</v>
-      </c>
-      <c r="D637" s="3">
-        <v>165</v>
-      </c>
-      <c r="E637" s="5">
-        <v>1</v>
-      </c>
-      <c r="F637" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G637" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="638" spans="3:7">
-      <c r="C638" s="6">
-        <v>16508</v>
-      </c>
-      <c r="D638" s="3">
-        <v>165</v>
-      </c>
-      <c r="E638" s="5">
-        <v>1</v>
-      </c>
-      <c r="F638" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G638" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="639" spans="3:7">
-      <c r="C639" s="6">
-        <v>16509</v>
-      </c>
-      <c r="D639" s="3">
-        <v>165</v>
-      </c>
-      <c r="E639" s="3">
-        <v>1</v>
-      </c>
-      <c r="F639" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G639" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="640" spans="3:7">
-      <c r="C640" s="6">
-        <v>16510</v>
-      </c>
-      <c r="D640" s="3">
-        <v>165</v>
-      </c>
-      <c r="E640" s="5">
-        <v>1</v>
-      </c>
-      <c r="F640" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G640" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="641" spans="3:7">
-      <c r="C641" s="6">
-        <v>16511</v>
-      </c>
-      <c r="D641" s="3">
-        <v>165</v>
-      </c>
-      <c r="E641" s="5">
-        <v>1</v>
-      </c>
-      <c r="F641" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G641" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="642" spans="3:7">
-      <c r="C642" s="6">
-        <v>16512</v>
-      </c>
-      <c r="D642" s="3">
-        <v>165</v>
-      </c>
-      <c r="E642" s="5">
-        <v>1</v>
-      </c>
-      <c r="F642" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G642" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="643" spans="3:7">
-      <c r="C643" s="6">
-        <v>16513</v>
-      </c>
-      <c r="D643" s="3">
-        <v>165</v>
-      </c>
-      <c r="E643" s="3">
-        <v>1</v>
-      </c>
-      <c r="F643" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G643" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="644" spans="3:7">
-      <c r="C644" s="6">
-        <v>16514</v>
-      </c>
-      <c r="D644" s="3">
-        <v>165</v>
-      </c>
-      <c r="E644" s="5">
-        <v>1</v>
-      </c>
-      <c r="F644" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G644" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="645" spans="3:7">
-      <c r="C645" s="6">
-        <v>16515</v>
-      </c>
-      <c r="D645" s="3">
-        <v>165</v>
-      </c>
-      <c r="E645" s="5">
-        <v>1</v>
-      </c>
-      <c r="F645" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G645" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="646" spans="3:7">
-      <c r="C646" s="6">
-        <v>16516</v>
-      </c>
-      <c r="D646" s="3">
-        <v>165</v>
-      </c>
-      <c r="E646" s="5">
-        <v>1</v>
-      </c>
-      <c r="F646" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G646" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="647" spans="3:7">
-      <c r="C647" s="6">
-        <v>16517</v>
-      </c>
-      <c r="D647" s="3">
-        <v>165</v>
-      </c>
-      <c r="E647" s="3">
-        <v>1</v>
-      </c>
-      <c r="F647" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G647" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="648" spans="3:7">
-      <c r="C648" s="6">
-        <v>16518</v>
-      </c>
-      <c r="D648" s="3">
-        <v>165</v>
-      </c>
-      <c r="E648" s="5">
-        <v>1</v>
-      </c>
-      <c r="F648" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G648" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="649" spans="3:7">
-      <c r="C649" s="6">
-        <v>16519</v>
-      </c>
-      <c r="D649" s="3">
-        <v>165</v>
-      </c>
-      <c r="E649" s="5">
-        <v>1</v>
-      </c>
-      <c r="F649" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G649" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="650" spans="3:7">
-      <c r="C650" s="6">
-        <v>16520</v>
-      </c>
-      <c r="D650" s="3">
-        <v>165</v>
-      </c>
-      <c r="E650" s="5">
-        <v>1</v>
-      </c>
-      <c r="F650" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G650" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="651" spans="3:7">
-      <c r="C651" s="6">
-        <v>16521</v>
-      </c>
-      <c r="D651" s="3">
-        <v>165</v>
-      </c>
-      <c r="E651" s="3">
-        <v>1</v>
-      </c>
-      <c r="F651" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G651" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="652" spans="3:7">
-      <c r="C652" s="6">
-        <v>16522</v>
-      </c>
-      <c r="D652" s="3">
-        <v>165</v>
-      </c>
-      <c r="E652" s="5">
-        <v>1</v>
-      </c>
-      <c r="F652" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G652" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="653" spans="3:7">
-      <c r="C653" s="6">
-        <v>16523</v>
-      </c>
-      <c r="D653" s="3">
-        <v>165</v>
-      </c>
-      <c r="E653" s="5">
-        <v>1</v>
-      </c>
-      <c r="F653" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G653" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="654" spans="3:7">
-      <c r="C654" s="6">
-        <v>16524</v>
-      </c>
-      <c r="D654" s="3">
-        <v>165</v>
-      </c>
-      <c r="E654" s="5">
-        <v>1</v>
-      </c>
-      <c r="F654" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G654" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="655" spans="3:7">
-      <c r="C655" s="6">
-        <v>16525</v>
-      </c>
-      <c r="D655" s="3">
-        <v>165</v>
-      </c>
-      <c r="E655" s="3">
-        <v>1</v>
-      </c>
-      <c r="F655" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G655" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="657" spans="1:8">
-      <c r="A657" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C657" s="6">
-        <v>16601</v>
-      </c>
-      <c r="D657" s="3">
-        <v>166</v>
-      </c>
-      <c r="E657" s="5">
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H657" s="3">
-        <v>20455</v>
-      </c>
-    </row>
-    <row r="658" spans="1:8">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-      <c r="C658" s="6">
-        <v>16602</v>
-      </c>
-      <c r="D658" s="3">
-        <v>166</v>
-      </c>
-      <c r="E658" s="5">
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H658" s="3">
-        <v>20456</v>
-      </c>
-    </row>
-    <row r="659" spans="3:8">
-      <c r="C659" s="6">
-        <v>16603</v>
-      </c>
-      <c r="D659" s="3">
-        <v>166</v>
-      </c>
-      <c r="E659" s="5">
-        <v>1</v>
-      </c>
-      <c r="F659" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G659" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H659" s="3">
-        <v>20457</v>
-      </c>
-    </row>
-    <row r="660" spans="3:8">
-      <c r="C660" s="6">
-        <v>16604</v>
-      </c>
-      <c r="D660" s="3">
-        <v>166</v>
-      </c>
-      <c r="E660" s="5">
-        <v>1</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H660" s="3">
-        <v>20458</v>
-      </c>
-    </row>
-    <row r="661" spans="3:7">
-      <c r="C661" s="6">
-        <v>16605</v>
-      </c>
-      <c r="D661" s="3">
-        <v>166</v>
-      </c>
-      <c r="E661" s="3">
-        <v>1</v>
-      </c>
-      <c r="F661" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G661" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="662" spans="3:7">
-      <c r="C662" s="6">
-        <v>16606</v>
-      </c>
-      <c r="D662" s="3">
-        <v>166</v>
-      </c>
-      <c r="E662" s="5">
-        <v>1</v>
-      </c>
-      <c r="F662" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G662" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="663" spans="3:7">
-      <c r="C663" s="6">
-        <v>16607</v>
-      </c>
-      <c r="D663" s="3">
-        <v>166</v>
-      </c>
-      <c r="E663" s="5">
-        <v>1</v>
-      </c>
-      <c r="F663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G663" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="664" spans="3:7">
-      <c r="C664" s="6">
-        <v>16608</v>
-      </c>
-      <c r="D664" s="3">
-        <v>166</v>
-      </c>
-      <c r="E664" s="5">
-        <v>1</v>
-      </c>
-      <c r="F664" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G664" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="665" spans="3:7">
-      <c r="C665" s="6">
-        <v>16609</v>
-      </c>
-      <c r="D665" s="3">
-        <v>166</v>
-      </c>
-      <c r="E665" s="3">
-        <v>1</v>
-      </c>
-      <c r="F665" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G665" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="666" spans="3:7">
-      <c r="C666" s="6">
-        <v>16610</v>
-      </c>
-      <c r="D666" s="3">
-        <v>166</v>
-      </c>
-      <c r="E666" s="5">
-        <v>1</v>
-      </c>
-      <c r="F666" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G666" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="667" spans="3:7">
-      <c r="C667" s="6">
-        <v>16611</v>
-      </c>
-      <c r="D667" s="3">
-        <v>166</v>
-      </c>
-      <c r="E667" s="5">
-        <v>1</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G667" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="668" spans="3:7">
-      <c r="C668" s="6">
-        <v>16612</v>
-      </c>
-      <c r="D668" s="3">
-        <v>166</v>
-      </c>
-      <c r="E668" s="5">
-        <v>1</v>
-      </c>
-      <c r="F668" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G668" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="669" spans="3:7">
-      <c r="C669" s="6">
-        <v>16613</v>
-      </c>
-      <c r="D669" s="3">
-        <v>166</v>
-      </c>
-      <c r="E669" s="3">
-        <v>1</v>
-      </c>
-      <c r="F669" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G669" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="670" spans="3:7">
-      <c r="C670" s="6">
-        <v>16614</v>
-      </c>
-      <c r="D670" s="3">
-        <v>166</v>
-      </c>
-      <c r="E670" s="5">
-        <v>1</v>
-      </c>
-      <c r="F670" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G670" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="671" spans="3:7">
-      <c r="C671" s="6">
-        <v>16615</v>
-      </c>
-      <c r="D671" s="3">
-        <v>166</v>
-      </c>
-      <c r="E671" s="5">
-        <v>1</v>
-      </c>
-      <c r="F671" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G671" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="672" spans="3:7">
-      <c r="C672" s="6">
-        <v>16616</v>
-      </c>
-      <c r="D672" s="3">
-        <v>166</v>
-      </c>
-      <c r="E672" s="5">
-        <v>1</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G672" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="673" spans="3:7">
-      <c r="C673" s="6">
-        <v>16617</v>
-      </c>
-      <c r="D673" s="3">
-        <v>166</v>
-      </c>
-      <c r="E673" s="3">
-        <v>1</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G673" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="674" spans="3:7">
-      <c r="C674" s="6">
-        <v>16618</v>
-      </c>
-      <c r="D674" s="3">
-        <v>166</v>
-      </c>
-      <c r="E674" s="5">
-        <v>1</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G674" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="675" spans="3:7">
-      <c r="C675" s="6">
-        <v>16619</v>
-      </c>
-      <c r="D675" s="3">
-        <v>166</v>
-      </c>
-      <c r="E675" s="5">
-        <v>1</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G675" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="676" spans="3:7">
-      <c r="C676" s="6">
-        <v>16620</v>
-      </c>
-      <c r="D676" s="3">
-        <v>166</v>
-      </c>
-      <c r="E676" s="5">
-        <v>1</v>
-      </c>
-      <c r="F676" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G676" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="677" spans="3:7">
-      <c r="C677" s="6">
-        <v>16621</v>
-      </c>
-      <c r="D677" s="3">
-        <v>166</v>
-      </c>
-      <c r="E677" s="3">
-        <v>1</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G677" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="678" spans="3:7">
-      <c r="C678" s="6">
-        <v>16622</v>
-      </c>
-      <c r="D678" s="3">
-        <v>166</v>
-      </c>
-      <c r="E678" s="5">
-        <v>1</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G678" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="679" spans="3:7">
-      <c r="C679" s="6">
-        <v>16623</v>
-      </c>
-      <c r="D679" s="3">
-        <v>166</v>
-      </c>
-      <c r="E679" s="5">
-        <v>1</v>
-      </c>
-      <c r="F679" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G679" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="680" spans="3:7">
-      <c r="C680" s="6">
-        <v>16624</v>
-      </c>
-      <c r="D680" s="3">
-        <v>166</v>
-      </c>
-      <c r="E680" s="5">
-        <v>1</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G680" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="681" spans="3:7">
-      <c r="C681" s="6">
-        <v>16625</v>
-      </c>
-      <c r="D681" s="3">
-        <v>166</v>
-      </c>
-      <c r="E681" s="3">
-        <v>1</v>
-      </c>
-      <c r="F681" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +12095,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +12113,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +12131,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +12149,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +12169,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +12267,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>#先锋167青云之巅</t>
+  </si>
+  <si>
+    <t>#先锋168</t>
   </si>
   <si>
     <t>Center</t>
@@ -1254,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O629"/>
+  <dimension ref="A3:O655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -11975,6 +11978,448 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C631" s="6">
+        <v>16801</v>
+      </c>
+      <c r="D631" s="3">
+        <v>168</v>
+      </c>
+      <c r="E631" s="5">
+        <v>1</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H631" s="3">
+        <v>20505</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="6">
+        <v>16802</v>
+      </c>
+      <c r="D632" s="3">
+        <v>168</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H632" s="3">
+        <v>20506</v>
+      </c>
+    </row>
+    <row r="633" spans="3:8">
+      <c r="C633" s="6">
+        <v>16803</v>
+      </c>
+      <c r="D633" s="3">
+        <v>168</v>
+      </c>
+      <c r="E633" s="5">
+        <v>1</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H633" s="3">
+        <v>20507</v>
+      </c>
+    </row>
+    <row r="634" spans="3:8">
+      <c r="C634" s="6">
+        <v>16804</v>
+      </c>
+      <c r="D634" s="3">
+        <v>168</v>
+      </c>
+      <c r="E634" s="5">
+        <v>1</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H634" s="3">
+        <v>20508</v>
+      </c>
+    </row>
+    <row r="635" spans="3:7">
+      <c r="C635" s="6">
+        <v>16805</v>
+      </c>
+      <c r="D635" s="3">
+        <v>168</v>
+      </c>
+      <c r="E635" s="3">
+        <v>1</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G635" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="636" spans="3:7">
+      <c r="C636" s="6">
+        <v>16806</v>
+      </c>
+      <c r="D636" s="3">
+        <v>168</v>
+      </c>
+      <c r="E636" s="5">
+        <v>1</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="637" spans="3:7">
+      <c r="C637" s="6">
+        <v>16807</v>
+      </c>
+      <c r="D637" s="3">
+        <v>168</v>
+      </c>
+      <c r="E637" s="5">
+        <v>1</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="638" spans="3:7">
+      <c r="C638" s="6">
+        <v>16808</v>
+      </c>
+      <c r="D638" s="3">
+        <v>168</v>
+      </c>
+      <c r="E638" s="5">
+        <v>1</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="639" spans="3:7">
+      <c r="C639" s="6">
+        <v>16809</v>
+      </c>
+      <c r="D639" s="3">
+        <v>168</v>
+      </c>
+      <c r="E639" s="3">
+        <v>1</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="640" spans="3:7">
+      <c r="C640" s="6">
+        <v>16810</v>
+      </c>
+      <c r="D640" s="3">
+        <v>168</v>
+      </c>
+      <c r="E640" s="5">
+        <v>1</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="3:7">
+      <c r="C641" s="6">
+        <v>16811</v>
+      </c>
+      <c r="D641" s="3">
+        <v>168</v>
+      </c>
+      <c r="E641" s="5">
+        <v>1</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="642" spans="3:7">
+      <c r="C642" s="6">
+        <v>16812</v>
+      </c>
+      <c r="D642" s="3">
+        <v>168</v>
+      </c>
+      <c r="E642" s="5">
+        <v>1</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="643" spans="3:7">
+      <c r="C643" s="6">
+        <v>16813</v>
+      </c>
+      <c r="D643" s="3">
+        <v>168</v>
+      </c>
+      <c r="E643" s="3">
+        <v>1</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="644" spans="3:7">
+      <c r="C644" s="6">
+        <v>16814</v>
+      </c>
+      <c r="D644" s="3">
+        <v>168</v>
+      </c>
+      <c r="E644" s="5">
+        <v>1</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G644" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="645" spans="3:7">
+      <c r="C645" s="6">
+        <v>16815</v>
+      </c>
+      <c r="D645" s="3">
+        <v>168</v>
+      </c>
+      <c r="E645" s="5">
+        <v>1</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="646" spans="3:7">
+      <c r="C646" s="6">
+        <v>16816</v>
+      </c>
+      <c r="D646" s="3">
+        <v>168</v>
+      </c>
+      <c r="E646" s="5">
+        <v>1</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="647" spans="3:7">
+      <c r="C647" s="6">
+        <v>16817</v>
+      </c>
+      <c r="D647" s="3">
+        <v>168</v>
+      </c>
+      <c r="E647" s="3">
+        <v>1</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="648" spans="3:7">
+      <c r="C648" s="6">
+        <v>16818</v>
+      </c>
+      <c r="D648" s="3">
+        <v>168</v>
+      </c>
+      <c r="E648" s="5">
+        <v>1</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="649" spans="3:7">
+      <c r="C649" s="6">
+        <v>16819</v>
+      </c>
+      <c r="D649" s="3">
+        <v>168</v>
+      </c>
+      <c r="E649" s="5">
+        <v>1</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="650" spans="3:7">
+      <c r="C650" s="6">
+        <v>16820</v>
+      </c>
+      <c r="D650" s="3">
+        <v>168</v>
+      </c>
+      <c r="E650" s="5">
+        <v>1</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="651" spans="3:7">
+      <c r="C651" s="6">
+        <v>16821</v>
+      </c>
+      <c r="D651" s="3">
+        <v>168</v>
+      </c>
+      <c r="E651" s="3">
+        <v>1</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="652" spans="3:7">
+      <c r="C652" s="6">
+        <v>16822</v>
+      </c>
+      <c r="D652" s="3">
+        <v>168</v>
+      </c>
+      <c r="E652" s="5">
+        <v>1</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="653" spans="3:7">
+      <c r="C653" s="6">
+        <v>16823</v>
+      </c>
+      <c r="D653" s="3">
+        <v>168</v>
+      </c>
+      <c r="E653" s="5">
+        <v>1</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="654" spans="3:7">
+      <c r="C654" s="6">
+        <v>16824</v>
+      </c>
+      <c r="D654" s="3">
+        <v>168</v>
+      </c>
+      <c r="E654" s="5">
+        <v>1</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="655" spans="3:7">
+      <c r="C655" s="6">
+        <v>16825</v>
+      </c>
+      <c r="D655" s="3">
+        <v>168</v>
+      </c>
+      <c r="E655" s="3">
+        <v>1</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G655" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12095,10 +12540,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12113,10 +12558,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12131,10 +12576,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12149,10 +12594,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12169,10 +12614,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12267,10 +12712,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -229,7 +229,7 @@
     <t>#先锋167青云之巅</t>
   </si>
   <si>
-    <t>#先锋168</t>
+    <t>#先锋168时光之歌</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋168时光之歌</t>
+  </si>
+  <si>
+    <t>#先锋169决战之巅</t>
   </si>
   <si>
     <t>Center</t>
@@ -1257,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12420,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>16901</v>
+      </c>
+      <c r="D657" s="3">
+        <v>169</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20515</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>16902</v>
+      </c>
+      <c r="D658" s="3">
+        <v>169</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20516</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>16903</v>
+      </c>
+      <c r="D659" s="3">
+        <v>169</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20517</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>16904</v>
+      </c>
+      <c r="D660" s="3">
+        <v>169</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20518</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>16905</v>
+      </c>
+      <c r="D661" s="3">
+        <v>169</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>16906</v>
+      </c>
+      <c r="D662" s="3">
+        <v>169</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>16907</v>
+      </c>
+      <c r="D663" s="3">
+        <v>169</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>16908</v>
+      </c>
+      <c r="D664" s="3">
+        <v>169</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>16909</v>
+      </c>
+      <c r="D665" s="3">
+        <v>169</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>16910</v>
+      </c>
+      <c r="D666" s="3">
+        <v>169</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>16911</v>
+      </c>
+      <c r="D667" s="3">
+        <v>169</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>16912</v>
+      </c>
+      <c r="D668" s="3">
+        <v>169</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>16913</v>
+      </c>
+      <c r="D669" s="3">
+        <v>169</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>16914</v>
+      </c>
+      <c r="D670" s="3">
+        <v>169</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>16915</v>
+      </c>
+      <c r="D671" s="3">
+        <v>169</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>16916</v>
+      </c>
+      <c r="D672" s="3">
+        <v>169</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>16917</v>
+      </c>
+      <c r="D673" s="3">
+        <v>169</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>16918</v>
+      </c>
+      <c r="D674" s="3">
+        <v>169</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>16919</v>
+      </c>
+      <c r="D675" s="3">
+        <v>169</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>16920</v>
+      </c>
+      <c r="D676" s="3">
+        <v>169</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>16921</v>
+      </c>
+      <c r="D677" s="3">
+        <v>169</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>16922</v>
+      </c>
+      <c r="D678" s="3">
+        <v>169</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>16923</v>
+      </c>
+      <c r="D679" s="3">
+        <v>169</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>16924</v>
+      </c>
+      <c r="D680" s="3">
+        <v>169</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>16925</v>
+      </c>
+      <c r="D681" s="3">
+        <v>169</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12540,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12558,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12576,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12594,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12614,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12712,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋169决战之巅</t>
+  </si>
+  <si>
+    <t>#先锋170迷雾森境</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>17001</v>
+      </c>
+      <c r="D683" s="3">
+        <v>170</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20565</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>17002</v>
+      </c>
+      <c r="D684" s="3">
+        <v>170</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20566</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>17003</v>
+      </c>
+      <c r="D685" s="3">
+        <v>170</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20567</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>17004</v>
+      </c>
+      <c r="D686" s="3">
+        <v>170</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20568</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>17005</v>
+      </c>
+      <c r="D687" s="3">
+        <v>170</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>17006</v>
+      </c>
+      <c r="D688" s="3">
+        <v>170</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>17007</v>
+      </c>
+      <c r="D689" s="3">
+        <v>170</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>17008</v>
+      </c>
+      <c r="D690" s="3">
+        <v>170</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>17009</v>
+      </c>
+      <c r="D691" s="3">
+        <v>170</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>17010</v>
+      </c>
+      <c r="D692" s="3">
+        <v>170</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>17011</v>
+      </c>
+      <c r="D693" s="3">
+        <v>170</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>17012</v>
+      </c>
+      <c r="D694" s="3">
+        <v>170</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>17013</v>
+      </c>
+      <c r="D695" s="3">
+        <v>170</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>17014</v>
+      </c>
+      <c r="D696" s="3">
+        <v>170</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>17015</v>
+      </c>
+      <c r="D697" s="3">
+        <v>170</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>17016</v>
+      </c>
+      <c r="D698" s="3">
+        <v>170</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>17017</v>
+      </c>
+      <c r="D699" s="3">
+        <v>170</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>17018</v>
+      </c>
+      <c r="D700" s="3">
+        <v>170</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>17019</v>
+      </c>
+      <c r="D701" s="3">
+        <v>170</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>17020</v>
+      </c>
+      <c r="D702" s="3">
+        <v>170</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>17021</v>
+      </c>
+      <c r="D703" s="3">
+        <v>170</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>17022</v>
+      </c>
+      <c r="D704" s="3">
+        <v>170</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>17023</v>
+      </c>
+      <c r="D705" s="3">
+        <v>170</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>17024</v>
+      </c>
+      <c r="D706" s="3">
+        <v>170</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>17025</v>
+      </c>
+      <c r="D707" s="3">
+        <v>170</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>#先锋170迷雾森境</t>
+  </si>
+  <si>
+    <t>#先锋171</t>
+  </si>
+  <si>
+    <t>#先锋172</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13310,6 +13316,890 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>17101</v>
+      </c>
+      <c r="D709" s="3">
+        <v>171</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20575</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>17102</v>
+      </c>
+      <c r="D710" s="3">
+        <v>171</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20576</v>
+      </c>
+    </row>
+    <row r="711" spans="3:8">
+      <c r="C711" s="6">
+        <v>17103</v>
+      </c>
+      <c r="D711" s="3">
+        <v>171</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20577</v>
+      </c>
+    </row>
+    <row r="712" spans="3:8">
+      <c r="C712" s="6">
+        <v>17104</v>
+      </c>
+      <c r="D712" s="3">
+        <v>171</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20578</v>
+      </c>
+    </row>
+    <row r="713" spans="3:7">
+      <c r="C713" s="6">
+        <v>17105</v>
+      </c>
+      <c r="D713" s="3">
+        <v>171</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="3:7">
+      <c r="C714" s="6">
+        <v>17106</v>
+      </c>
+      <c r="D714" s="3">
+        <v>171</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="3:7">
+      <c r="C715" s="6">
+        <v>17107</v>
+      </c>
+      <c r="D715" s="3">
+        <v>171</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="3:7">
+      <c r="C716" s="6">
+        <v>17108</v>
+      </c>
+      <c r="D716" s="3">
+        <v>171</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="3:7">
+      <c r="C717" s="6">
+        <v>17109</v>
+      </c>
+      <c r="D717" s="3">
+        <v>171</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="3:7">
+      <c r="C718" s="6">
+        <v>17110</v>
+      </c>
+      <c r="D718" s="3">
+        <v>171</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="3:7">
+      <c r="C719" s="6">
+        <v>17111</v>
+      </c>
+      <c r="D719" s="3">
+        <v>171</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="3:7">
+      <c r="C720" s="6">
+        <v>17112</v>
+      </c>
+      <c r="D720" s="3">
+        <v>171</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>17113</v>
+      </c>
+      <c r="D721" s="3">
+        <v>171</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>17114</v>
+      </c>
+      <c r="D722" s="3">
+        <v>171</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>17115</v>
+      </c>
+      <c r="D723" s="3">
+        <v>171</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>17116</v>
+      </c>
+      <c r="D724" s="3">
+        <v>171</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>17117</v>
+      </c>
+      <c r="D725" s="3">
+        <v>171</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>17118</v>
+      </c>
+      <c r="D726" s="3">
+        <v>171</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>17119</v>
+      </c>
+      <c r="D727" s="3">
+        <v>171</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>17120</v>
+      </c>
+      <c r="D728" s="3">
+        <v>171</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>17121</v>
+      </c>
+      <c r="D729" s="3">
+        <v>171</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>17122</v>
+      </c>
+      <c r="D730" s="3">
+        <v>171</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>17123</v>
+      </c>
+      <c r="D731" s="3">
+        <v>171</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>17124</v>
+      </c>
+      <c r="D732" s="3">
+        <v>171</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>17125</v>
+      </c>
+      <c r="D733" s="3">
+        <v>171</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>17201</v>
+      </c>
+      <c r="D735" s="3">
+        <v>172</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20585</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>17202</v>
+      </c>
+      <c r="D736" s="3">
+        <v>172</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20586</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>17203</v>
+      </c>
+      <c r="D737" s="3">
+        <v>172</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20587</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>17204</v>
+      </c>
+      <c r="D738" s="3">
+        <v>172</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20588</v>
+      </c>
+    </row>
+    <row r="739" spans="3:7">
+      <c r="C739" s="6">
+        <v>17205</v>
+      </c>
+      <c r="D739" s="3">
+        <v>172</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:7">
+      <c r="C740" s="6">
+        <v>17206</v>
+      </c>
+      <c r="D740" s="3">
+        <v>172</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:7">
+      <c r="C741" s="6">
+        <v>17207</v>
+      </c>
+      <c r="D741" s="3">
+        <v>172</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:7">
+      <c r="C742" s="6">
+        <v>17208</v>
+      </c>
+      <c r="D742" s="3">
+        <v>172</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:7">
+      <c r="C743" s="6">
+        <v>17209</v>
+      </c>
+      <c r="D743" s="3">
+        <v>172</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:7">
+      <c r="C744" s="6">
+        <v>17210</v>
+      </c>
+      <c r="D744" s="3">
+        <v>172</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:7">
+      <c r="C745" s="6">
+        <v>17211</v>
+      </c>
+      <c r="D745" s="3">
+        <v>172</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:7">
+      <c r="C746" s="6">
+        <v>17212</v>
+      </c>
+      <c r="D746" s="3">
+        <v>172</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:7">
+      <c r="C747" s="6">
+        <v>17213</v>
+      </c>
+      <c r="D747" s="3">
+        <v>172</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:7">
+      <c r="C748" s="6">
+        <v>17214</v>
+      </c>
+      <c r="D748" s="3">
+        <v>172</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:7">
+      <c r="C749" s="6">
+        <v>17215</v>
+      </c>
+      <c r="D749" s="3">
+        <v>172</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:7">
+      <c r="C750" s="6">
+        <v>17216</v>
+      </c>
+      <c r="D750" s="3">
+        <v>172</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:7">
+      <c r="C751" s="6">
+        <v>17217</v>
+      </c>
+      <c r="D751" s="3">
+        <v>172</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:7">
+      <c r="C752" s="6">
+        <v>17218</v>
+      </c>
+      <c r="D752" s="3">
+        <v>172</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>17219</v>
+      </c>
+      <c r="D753" s="3">
+        <v>172</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>17220</v>
+      </c>
+      <c r="D754" s="3">
+        <v>172</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>17221</v>
+      </c>
+      <c r="D755" s="3">
+        <v>172</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>17222</v>
+      </c>
+      <c r="D756" s="3">
+        <v>172</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>17223</v>
+      </c>
+      <c r="D757" s="3">
+        <v>172</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>17224</v>
+      </c>
+      <c r="D758" s="3">
+        <v>172</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>17225</v>
+      </c>
+      <c r="D759" s="3">
+        <v>172</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -238,7 +238,7 @@
     <t>#先锋170迷雾森境</t>
   </si>
   <si>
-    <t>#先锋171</t>
+    <t>#先锋171ValorArena</t>
   </si>
   <si>
     <t>#先锋172</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -238,10 +238,7 @@
     <t>#先锋170迷雾森境</t>
   </si>
   <si>
-    <t>#先锋171ValorArena</t>
-  </si>
-  <si>
-    <t>#先锋172</t>
+    <t>#先锋172星辰殿堂</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13324,10 +13321,10 @@
         <v>69</v>
       </c>
       <c r="C709" s="6">
-        <v>17101</v>
+        <v>17201</v>
       </c>
       <c r="D709" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E709" s="5">
         <v>1</v>
@@ -13339,17 +13336,17 @@
         <v>15</v>
       </c>
       <c r="H709" s="3">
-        <v>20575</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="710" spans="1:8">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="6">
-        <v>17102</v>
+        <v>17202</v>
       </c>
       <c r="D710" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E710" s="5">
         <v>1</v>
@@ -13361,15 +13358,15 @@
         <v>16</v>
       </c>
       <c r="H710" s="3">
-        <v>20576</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="711" spans="3:8">
       <c r="C711" s="6">
-        <v>17103</v>
+        <v>17203</v>
       </c>
       <c r="D711" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E711" s="5">
         <v>1</v>
@@ -13381,15 +13378,15 @@
         <v>18</v>
       </c>
       <c r="H711" s="3">
-        <v>20577</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="712" spans="3:8">
       <c r="C712" s="6">
-        <v>17104</v>
+        <v>17204</v>
       </c>
       <c r="D712" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E712" s="5">
         <v>1</v>
@@ -13401,15 +13398,15 @@
         <v>19</v>
       </c>
       <c r="H712" s="3">
-        <v>20578</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="713" spans="3:7">
       <c r="C713" s="6">
-        <v>17105</v>
+        <v>17205</v>
       </c>
       <c r="D713" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E713" s="3">
         <v>1</v>
@@ -13423,10 +13420,10 @@
     </row>
     <row r="714" spans="3:7">
       <c r="C714" s="6">
-        <v>17106</v>
+        <v>17206</v>
       </c>
       <c r="D714" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E714" s="5">
         <v>1</v>
@@ -13440,10 +13437,10 @@
     </row>
     <row r="715" spans="3:7">
       <c r="C715" s="6">
-        <v>17107</v>
+        <v>17207</v>
       </c>
       <c r="D715" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E715" s="5">
         <v>1</v>
@@ -13457,10 +13454,10 @@
     </row>
     <row r="716" spans="3:7">
       <c r="C716" s="6">
-        <v>17108</v>
+        <v>17208</v>
       </c>
       <c r="D716" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E716" s="5">
         <v>1</v>
@@ -13474,10 +13471,10 @@
     </row>
     <row r="717" spans="3:7">
       <c r="C717" s="6">
-        <v>17109</v>
+        <v>17209</v>
       </c>
       <c r="D717" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E717" s="3">
         <v>1</v>
@@ -13491,10 +13488,10 @@
     </row>
     <row r="718" spans="3:7">
       <c r="C718" s="6">
-        <v>17110</v>
+        <v>17210</v>
       </c>
       <c r="D718" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E718" s="5">
         <v>1</v>
@@ -13508,10 +13505,10 @@
     </row>
     <row r="719" spans="3:7">
       <c r="C719" s="6">
-        <v>17111</v>
+        <v>17211</v>
       </c>
       <c r="D719" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E719" s="5">
         <v>1</v>
@@ -13525,10 +13522,10 @@
     </row>
     <row r="720" spans="3:7">
       <c r="C720" s="6">
-        <v>17112</v>
+        <v>17212</v>
       </c>
       <c r="D720" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E720" s="5">
         <v>1</v>
@@ -13542,10 +13539,10 @@
     </row>
     <row r="721" spans="3:7">
       <c r="C721" s="6">
-        <v>17113</v>
+        <v>17213</v>
       </c>
       <c r="D721" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E721" s="3">
         <v>1</v>
@@ -13559,10 +13556,10 @@
     </row>
     <row r="722" spans="3:7">
       <c r="C722" s="6">
-        <v>17114</v>
+        <v>17214</v>
       </c>
       <c r="D722" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E722" s="5">
         <v>1</v>
@@ -13576,10 +13573,10 @@
     </row>
     <row r="723" spans="3:7">
       <c r="C723" s="6">
-        <v>17115</v>
+        <v>17215</v>
       </c>
       <c r="D723" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E723" s="5">
         <v>1</v>
@@ -13593,10 +13590,10 @@
     </row>
     <row r="724" spans="3:7">
       <c r="C724" s="6">
-        <v>17116</v>
+        <v>17216</v>
       </c>
       <c r="D724" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E724" s="5">
         <v>1</v>
@@ -13610,10 +13607,10 @@
     </row>
     <row r="725" spans="3:7">
       <c r="C725" s="6">
-        <v>17117</v>
+        <v>17217</v>
       </c>
       <c r="D725" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E725" s="3">
         <v>1</v>
@@ -13627,10 +13624,10 @@
     </row>
     <row r="726" spans="3:7">
       <c r="C726" s="6">
-        <v>17118</v>
+        <v>17218</v>
       </c>
       <c r="D726" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E726" s="5">
         <v>1</v>
@@ -13644,10 +13641,10 @@
     </row>
     <row r="727" spans="3:7">
       <c r="C727" s="6">
-        <v>17119</v>
+        <v>17219</v>
       </c>
       <c r="D727" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E727" s="5">
         <v>1</v>
@@ -13661,10 +13658,10 @@
     </row>
     <row r="728" spans="3:7">
       <c r="C728" s="6">
-        <v>17120</v>
+        <v>17220</v>
       </c>
       <c r="D728" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E728" s="5">
         <v>1</v>
@@ -13678,10 +13675,10 @@
     </row>
     <row r="729" spans="3:7">
       <c r="C729" s="6">
-        <v>17121</v>
+        <v>17221</v>
       </c>
       <c r="D729" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E729" s="3">
         <v>1</v>
@@ -13695,10 +13692,10 @@
     </row>
     <row r="730" spans="3:7">
       <c r="C730" s="6">
-        <v>17122</v>
+        <v>17222</v>
       </c>
       <c r="D730" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E730" s="5">
         <v>1</v>
@@ -13712,10 +13709,10 @@
     </row>
     <row r="731" spans="3:7">
       <c r="C731" s="6">
-        <v>17123</v>
+        <v>17223</v>
       </c>
       <c r="D731" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E731" s="5">
         <v>1</v>
@@ -13729,10 +13726,10 @@
     </row>
     <row r="732" spans="3:7">
       <c r="C732" s="6">
-        <v>17124</v>
+        <v>17224</v>
       </c>
       <c r="D732" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E732" s="5">
         <v>1</v>
@@ -13746,10 +13743,10 @@
     </row>
     <row r="733" spans="3:7">
       <c r="C733" s="6">
-        <v>17125</v>
+        <v>17225</v>
       </c>
       <c r="D733" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E733" s="3">
         <v>1</v>
@@ -13758,448 +13755,6 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>17201</v>
-      </c>
-      <c r="D735" s="3">
-        <v>172</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20585</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>17202</v>
-      </c>
-      <c r="D736" s="3">
-        <v>172</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20586</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>17203</v>
-      </c>
-      <c r="D737" s="3">
-        <v>172</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20587</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>17204</v>
-      </c>
-      <c r="D738" s="3">
-        <v>172</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20588</v>
-      </c>
-    </row>
-    <row r="739" spans="3:7">
-      <c r="C739" s="6">
-        <v>17205</v>
-      </c>
-      <c r="D739" s="3">
-        <v>172</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:7">
-      <c r="C740" s="6">
-        <v>17206</v>
-      </c>
-      <c r="D740" s="3">
-        <v>172</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:7">
-      <c r="C741" s="6">
-        <v>17207</v>
-      </c>
-      <c r="D741" s="3">
-        <v>172</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:7">
-      <c r="C742" s="6">
-        <v>17208</v>
-      </c>
-      <c r="D742" s="3">
-        <v>172</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:7">
-      <c r="C743" s="6">
-        <v>17209</v>
-      </c>
-      <c r="D743" s="3">
-        <v>172</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:7">
-      <c r="C744" s="6">
-        <v>17210</v>
-      </c>
-      <c r="D744" s="3">
-        <v>172</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:7">
-      <c r="C745" s="6">
-        <v>17211</v>
-      </c>
-      <c r="D745" s="3">
-        <v>172</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:7">
-      <c r="C746" s="6">
-        <v>17212</v>
-      </c>
-      <c r="D746" s="3">
-        <v>172</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:7">
-      <c r="C747" s="6">
-        <v>17213</v>
-      </c>
-      <c r="D747" s="3">
-        <v>172</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:7">
-      <c r="C748" s="6">
-        <v>17214</v>
-      </c>
-      <c r="D748" s="3">
-        <v>172</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:7">
-      <c r="C749" s="6">
-        <v>17215</v>
-      </c>
-      <c r="D749" s="3">
-        <v>172</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:7">
-      <c r="C750" s="6">
-        <v>17216</v>
-      </c>
-      <c r="D750" s="3">
-        <v>172</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:7">
-      <c r="C751" s="6">
-        <v>17217</v>
-      </c>
-      <c r="D751" s="3">
-        <v>172</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:7">
-      <c r="C752" s="6">
-        <v>17218</v>
-      </c>
-      <c r="D752" s="3">
-        <v>172</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="3:7">
-      <c r="C753" s="6">
-        <v>17219</v>
-      </c>
-      <c r="D753" s="3">
-        <v>172</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="3:7">
-      <c r="C754" s="6">
-        <v>17220</v>
-      </c>
-      <c r="D754" s="3">
-        <v>172</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="3:7">
-      <c r="C755" s="6">
-        <v>17221</v>
-      </c>
-      <c r="D755" s="3">
-        <v>172</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="3:7">
-      <c r="C756" s="6">
-        <v>17222</v>
-      </c>
-      <c r="D756" s="3">
-        <v>172</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="3:7">
-      <c r="C757" s="6">
-        <v>17223</v>
-      </c>
-      <c r="D757" s="3">
-        <v>172</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="3:7">
-      <c r="C758" s="6">
-        <v>17224</v>
-      </c>
-      <c r="D758" s="3">
-        <v>172</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="3:7">
-      <c r="C759" s="6">
-        <v>17225</v>
-      </c>
-      <c r="D759" s="3">
-        <v>172</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -202,28 +202,16 @@
     <t>#先锋147紫禁之巅</t>
   </si>
   <si>
-    <t>#先锋151龙裔国度</t>
-  </si>
-  <si>
     <t>#先锋155雷霆万钧</t>
   </si>
   <si>
     <t>#先锋159星辰之巅</t>
   </si>
   <si>
-    <t>#先锋161时光镇</t>
-  </si>
-  <si>
     <t>#先锋163破晓战歌</t>
   </si>
   <si>
-    <t>#先锋164翡翠仙境</t>
-  </si>
-  <si>
     <t>#先锋165繁花谷</t>
-  </si>
-  <si>
-    <t>#先锋166萤火森林</t>
   </si>
   <si>
     <t>#先锋167青云之巅</t>
@@ -1266,7 +1254,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O629"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -8017,10 +8005,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>15101</v>
+        <v>15501</v>
       </c>
       <c r="D397" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8032,17 +8020,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20415</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>15102</v>
+        <v>15502</v>
       </c>
       <c r="D398" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8054,15 +8042,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20416</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="399" spans="3:8">
       <c r="C399" s="6">
-        <v>15103</v>
+        <v>15503</v>
       </c>
       <c r="D399" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8074,15 +8062,15 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20417</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="400" spans="3:8">
       <c r="C400" s="6">
-        <v>15104</v>
+        <v>15504</v>
       </c>
       <c r="D400" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E400" s="5">
         <v>1</v>
@@ -8094,15 +8082,15 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20418</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>15105</v>
+        <v>15505</v>
       </c>
       <c r="D401" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E401" s="3">
         <v>1</v>
@@ -8116,10 +8104,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>15106</v>
+        <v>15506</v>
       </c>
       <c r="D402" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8133,10 +8121,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>15107</v>
+        <v>15507</v>
       </c>
       <c r="D403" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8150,10 +8138,10 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>15108</v>
+        <v>15508</v>
       </c>
       <c r="D404" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E404" s="5">
         <v>1</v>
@@ -8167,10 +8155,10 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>15109</v>
+        <v>15509</v>
       </c>
       <c r="D405" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E405" s="3">
         <v>1</v>
@@ -8184,10 +8172,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>15110</v>
+        <v>15510</v>
       </c>
       <c r="D406" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8201,10 +8189,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>15111</v>
+        <v>15511</v>
       </c>
       <c r="D407" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8218,10 +8206,10 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>15112</v>
+        <v>15512</v>
       </c>
       <c r="D408" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E408" s="5">
         <v>1</v>
@@ -8235,10 +8223,10 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>15113</v>
+        <v>15513</v>
       </c>
       <c r="D409" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E409" s="3">
         <v>1</v>
@@ -8252,10 +8240,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>15114</v>
+        <v>15514</v>
       </c>
       <c r="D410" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8269,10 +8257,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>15115</v>
+        <v>15515</v>
       </c>
       <c r="D411" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8286,10 +8274,10 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>15116</v>
+        <v>15516</v>
       </c>
       <c r="D412" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E412" s="5">
         <v>1</v>
@@ -8303,10 +8291,10 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>15117</v>
+        <v>15517</v>
       </c>
       <c r="D413" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E413" s="3">
         <v>1</v>
@@ -8320,10 +8308,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>15118</v>
+        <v>15518</v>
       </c>
       <c r="D414" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8337,10 +8325,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>15119</v>
+        <v>15519</v>
       </c>
       <c r="D415" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8354,10 +8342,10 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>15120</v>
+        <v>15520</v>
       </c>
       <c r="D416" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E416" s="5">
         <v>1</v>
@@ -8371,10 +8359,10 @@
     </row>
     <row r="417" spans="3:7">
       <c r="C417" s="6">
-        <v>15121</v>
+        <v>15521</v>
       </c>
       <c r="D417" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E417" s="3">
         <v>1</v>
@@ -8388,10 +8376,10 @@
     </row>
     <row r="418" spans="3:7">
       <c r="C418" s="6">
-        <v>15122</v>
+        <v>15522</v>
       </c>
       <c r="D418" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8405,10 +8393,10 @@
     </row>
     <row r="419" spans="3:7">
       <c r="C419" s="6">
-        <v>15123</v>
+        <v>15523</v>
       </c>
       <c r="D419" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8422,10 +8410,10 @@
     </row>
     <row r="420" spans="3:7">
       <c r="C420" s="6">
-        <v>15124</v>
+        <v>15524</v>
       </c>
       <c r="D420" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E420" s="5">
         <v>1</v>
@@ -8439,10 +8427,10 @@
     </row>
     <row r="421" spans="3:7">
       <c r="C421" s="6">
-        <v>15125</v>
+        <v>15525</v>
       </c>
       <c r="D421" s="3">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E421" s="3">
         <v>1</v>
@@ -8459,10 +8447,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>15501</v>
+        <v>15901</v>
       </c>
       <c r="D423" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8474,17 +8462,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20605</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>15502</v>
+        <v>15902</v>
       </c>
       <c r="D424" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8496,15 +8484,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20606</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>15503</v>
+        <v>15903</v>
       </c>
       <c r="D425" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8516,15 +8504,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20607</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>15504</v>
+        <v>15904</v>
       </c>
       <c r="D426" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8536,15 +8524,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20608</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>15505</v>
+        <v>15905</v>
       </c>
       <c r="D427" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8558,10 +8546,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>15506</v>
+        <v>15906</v>
       </c>
       <c r="D428" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8575,10 +8563,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>15507</v>
+        <v>15907</v>
       </c>
       <c r="D429" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8592,10 +8580,10 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>15508</v>
+        <v>15908</v>
       </c>
       <c r="D430" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8609,10 +8597,10 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>15509</v>
+        <v>15909</v>
       </c>
       <c r="D431" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8626,10 +8614,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>15510</v>
+        <v>15910</v>
       </c>
       <c r="D432" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8643,10 +8631,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>15511</v>
+        <v>15911</v>
       </c>
       <c r="D433" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8660,10 +8648,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>15512</v>
+        <v>15912</v>
       </c>
       <c r="D434" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8677,10 +8665,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>15513</v>
+        <v>15913</v>
       </c>
       <c r="D435" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8694,10 +8682,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>15514</v>
+        <v>15914</v>
       </c>
       <c r="D436" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8711,10 +8699,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>15515</v>
+        <v>15915</v>
       </c>
       <c r="D437" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8728,10 +8716,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>15516</v>
+        <v>15916</v>
       </c>
       <c r="D438" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8745,10 +8733,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>15517</v>
+        <v>15917</v>
       </c>
       <c r="D439" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8762,10 +8750,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>15518</v>
+        <v>15918</v>
       </c>
       <c r="D440" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8779,10 +8767,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>15519</v>
+        <v>15919</v>
       </c>
       <c r="D441" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8796,10 +8784,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>15520</v>
+        <v>15920</v>
       </c>
       <c r="D442" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8813,10 +8801,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>15521</v>
+        <v>15921</v>
       </c>
       <c r="D443" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8830,10 +8818,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>15522</v>
+        <v>15922</v>
       </c>
       <c r="D444" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8847,10 +8835,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>15523</v>
+        <v>15923</v>
       </c>
       <c r="D445" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8864,10 +8852,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>15524</v>
+        <v>15924</v>
       </c>
       <c r="D446" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8881,10 +8869,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>15525</v>
+        <v>15925</v>
       </c>
       <c r="D447" s="3">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8901,10 +8889,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>15901</v>
+        <v>16301</v>
       </c>
       <c r="D449" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8916,17 +8904,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20405</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>15902</v>
+        <v>16302</v>
       </c>
       <c r="D450" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8938,15 +8926,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20406</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>15903</v>
+        <v>16303</v>
       </c>
       <c r="D451" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8958,15 +8946,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20407</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>15904</v>
+        <v>16304</v>
       </c>
       <c r="D452" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8978,15 +8966,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20408</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>15905</v>
+        <v>16305</v>
       </c>
       <c r="D453" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9000,10 +8988,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>15906</v>
+        <v>16306</v>
       </c>
       <c r="D454" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9017,10 +9005,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>15907</v>
+        <v>16307</v>
       </c>
       <c r="D455" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9034,10 +9022,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>15908</v>
+        <v>16308</v>
       </c>
       <c r="D456" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9051,10 +9039,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>15909</v>
+        <v>16309</v>
       </c>
       <c r="D457" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9068,10 +9056,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>15910</v>
+        <v>16310</v>
       </c>
       <c r="D458" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9085,10 +9073,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>15911</v>
+        <v>16311</v>
       </c>
       <c r="D459" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9102,10 +9090,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>15912</v>
+        <v>16312</v>
       </c>
       <c r="D460" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9119,10 +9107,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>15913</v>
+        <v>16313</v>
       </c>
       <c r="D461" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9136,10 +9124,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>15914</v>
+        <v>16314</v>
       </c>
       <c r="D462" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9153,10 +9141,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>15915</v>
+        <v>16315</v>
       </c>
       <c r="D463" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9170,10 +9158,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>15916</v>
+        <v>16316</v>
       </c>
       <c r="D464" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9187,10 +9175,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>15917</v>
+        <v>16317</v>
       </c>
       <c r="D465" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9204,10 +9192,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>15918</v>
+        <v>16318</v>
       </c>
       <c r="D466" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9221,10 +9209,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>15919</v>
+        <v>16319</v>
       </c>
       <c r="D467" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9238,10 +9226,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>15920</v>
+        <v>16320</v>
       </c>
       <c r="D468" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9255,10 +9243,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>15921</v>
+        <v>16321</v>
       </c>
       <c r="D469" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9272,10 +9260,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>15922</v>
+        <v>16322</v>
       </c>
       <c r="D470" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9289,10 +9277,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>15923</v>
+        <v>16323</v>
       </c>
       <c r="D471" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9306,10 +9294,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>15924</v>
+        <v>16324</v>
       </c>
       <c r="D472" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9323,10 +9311,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>15925</v>
+        <v>16325</v>
       </c>
       <c r="D473" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9343,10 +9331,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>16101</v>
+        <v>16501</v>
       </c>
       <c r="D475" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9358,17 +9346,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20445</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>16102</v>
+        <v>16502</v>
       </c>
       <c r="D476" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9380,15 +9368,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20446</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>16103</v>
+        <v>16503</v>
       </c>
       <c r="D477" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9400,15 +9388,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20447</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>16104</v>
+        <v>16504</v>
       </c>
       <c r="D478" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9420,15 +9408,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20448</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>16105</v>
+        <v>16505</v>
       </c>
       <c r="D479" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9442,10 +9430,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>16106</v>
+        <v>16506</v>
       </c>
       <c r="D480" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9459,10 +9447,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>16107</v>
+        <v>16507</v>
       </c>
       <c r="D481" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9476,10 +9464,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>16108</v>
+        <v>16508</v>
       </c>
       <c r="D482" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9493,10 +9481,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>16109</v>
+        <v>16509</v>
       </c>
       <c r="D483" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9510,10 +9498,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>16110</v>
+        <v>16510</v>
       </c>
       <c r="D484" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9527,10 +9515,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>16111</v>
+        <v>16511</v>
       </c>
       <c r="D485" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9544,10 +9532,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>16112</v>
+        <v>16512</v>
       </c>
       <c r="D486" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9561,10 +9549,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>16113</v>
+        <v>16513</v>
       </c>
       <c r="D487" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9578,10 +9566,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>16114</v>
+        <v>16514</v>
       </c>
       <c r="D488" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9595,10 +9583,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>16115</v>
+        <v>16515</v>
       </c>
       <c r="D489" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9612,10 +9600,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>16116</v>
+        <v>16516</v>
       </c>
       <c r="D490" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9629,10 +9617,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>16117</v>
+        <v>16517</v>
       </c>
       <c r="D491" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9646,10 +9634,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>16118</v>
+        <v>16518</v>
       </c>
       <c r="D492" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9663,10 +9651,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>16119</v>
+        <v>16519</v>
       </c>
       <c r="D493" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9680,10 +9668,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>16120</v>
+        <v>16520</v>
       </c>
       <c r="D494" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9697,10 +9685,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>16121</v>
+        <v>16521</v>
       </c>
       <c r="D495" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9714,10 +9702,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>16122</v>
+        <v>16522</v>
       </c>
       <c r="D496" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9731,10 +9719,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>16123</v>
+        <v>16523</v>
       </c>
       <c r="D497" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9748,10 +9736,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>16124</v>
+        <v>16524</v>
       </c>
       <c r="D498" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9765,10 +9753,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>16125</v>
+        <v>16525</v>
       </c>
       <c r="D499" s="3">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9785,10 +9773,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>16301</v>
+        <v>16701</v>
       </c>
       <c r="D501" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9800,17 +9788,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20525</v>
+        <v>20555</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>16302</v>
+        <v>16702</v>
       </c>
       <c r="D502" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9822,15 +9810,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20526</v>
+        <v>20556</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>16303</v>
+        <v>16703</v>
       </c>
       <c r="D503" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9842,15 +9830,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20527</v>
+        <v>20557</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>16304</v>
+        <v>16704</v>
       </c>
       <c r="D504" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9862,15 +9850,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20528</v>
+        <v>20558</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>16305</v>
+        <v>16705</v>
       </c>
       <c r="D505" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9884,10 +9872,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>16306</v>
+        <v>16706</v>
       </c>
       <c r="D506" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9901,10 +9889,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>16307</v>
+        <v>16707</v>
       </c>
       <c r="D507" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9918,10 +9906,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>16308</v>
+        <v>16708</v>
       </c>
       <c r="D508" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9935,10 +9923,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>16309</v>
+        <v>16709</v>
       </c>
       <c r="D509" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9952,10 +9940,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>16310</v>
+        <v>16710</v>
       </c>
       <c r="D510" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9969,10 +9957,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>16311</v>
+        <v>16711</v>
       </c>
       <c r="D511" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9986,10 +9974,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>16312</v>
+        <v>16712</v>
       </c>
       <c r="D512" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10003,10 +9991,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>16313</v>
+        <v>16713</v>
       </c>
       <c r="D513" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10020,10 +10008,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>16314</v>
+        <v>16714</v>
       </c>
       <c r="D514" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10037,10 +10025,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>16315</v>
+        <v>16715</v>
       </c>
       <c r="D515" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10054,10 +10042,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>16316</v>
+        <v>16716</v>
       </c>
       <c r="D516" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10071,10 +10059,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>16317</v>
+        <v>16717</v>
       </c>
       <c r="D517" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10088,10 +10076,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>16318</v>
+        <v>16718</v>
       </c>
       <c r="D518" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10105,10 +10093,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>16319</v>
+        <v>16719</v>
       </c>
       <c r="D519" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10122,10 +10110,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>16320</v>
+        <v>16720</v>
       </c>
       <c r="D520" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10139,10 +10127,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>16321</v>
+        <v>16721</v>
       </c>
       <c r="D521" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10156,10 +10144,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>16322</v>
+        <v>16722</v>
       </c>
       <c r="D522" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10173,10 +10161,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>16323</v>
+        <v>16723</v>
       </c>
       <c r="D523" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10190,10 +10178,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>16324</v>
+        <v>16724</v>
       </c>
       <c r="D524" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10207,10 +10195,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>16325</v>
+        <v>16725</v>
       </c>
       <c r="D525" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10227,10 +10215,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>16401</v>
+        <v>16801</v>
       </c>
       <c r="D527" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10242,17 +10230,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20545</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>16402</v>
+        <v>16802</v>
       </c>
       <c r="D528" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10264,15 +10252,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20546</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>16403</v>
+        <v>16803</v>
       </c>
       <c r="D529" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10284,15 +10272,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20547</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>16404</v>
+        <v>16804</v>
       </c>
       <c r="D530" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10304,15 +10292,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20548</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>16405</v>
+        <v>16805</v>
       </c>
       <c r="D531" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10326,10 +10314,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>16406</v>
+        <v>16806</v>
       </c>
       <c r="D532" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10343,10 +10331,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>16407</v>
+        <v>16807</v>
       </c>
       <c r="D533" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10360,10 +10348,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>16408</v>
+        <v>16808</v>
       </c>
       <c r="D534" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10377,10 +10365,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>16409</v>
+        <v>16809</v>
       </c>
       <c r="D535" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10394,10 +10382,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>16410</v>
+        <v>16810</v>
       </c>
       <c r="D536" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10411,10 +10399,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>16411</v>
+        <v>16811</v>
       </c>
       <c r="D537" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10428,10 +10416,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>16412</v>
+        <v>16812</v>
       </c>
       <c r="D538" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10445,10 +10433,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>16413</v>
+        <v>16813</v>
       </c>
       <c r="D539" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10462,10 +10450,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>16414</v>
+        <v>16814</v>
       </c>
       <c r="D540" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10479,10 +10467,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>16415</v>
+        <v>16815</v>
       </c>
       <c r="D541" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10496,10 +10484,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>16416</v>
+        <v>16816</v>
       </c>
       <c r="D542" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10513,10 +10501,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>16417</v>
+        <v>16817</v>
       </c>
       <c r="D543" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10530,10 +10518,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>16418</v>
+        <v>16818</v>
       </c>
       <c r="D544" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10547,10 +10535,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>16419</v>
+        <v>16819</v>
       </c>
       <c r="D545" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10564,10 +10552,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>16420</v>
+        <v>16820</v>
       </c>
       <c r="D546" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10581,10 +10569,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>16421</v>
+        <v>16821</v>
       </c>
       <c r="D547" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10598,10 +10586,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>16422</v>
+        <v>16822</v>
       </c>
       <c r="D548" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10615,10 +10603,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>16423</v>
+        <v>16823</v>
       </c>
       <c r="D549" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10632,10 +10620,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>16424</v>
+        <v>16824</v>
       </c>
       <c r="D550" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10649,10 +10637,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>16425</v>
+        <v>16825</v>
       </c>
       <c r="D551" s="3">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10669,10 +10657,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>16501</v>
+        <v>16901</v>
       </c>
       <c r="D553" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10684,17 +10672,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20375</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>16502</v>
+        <v>16902</v>
       </c>
       <c r="D554" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10706,15 +10694,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20376</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>16503</v>
+        <v>16903</v>
       </c>
       <c r="D555" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10726,15 +10714,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20377</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>16504</v>
+        <v>16904</v>
       </c>
       <c r="D556" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10746,15 +10734,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20378</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>16505</v>
+        <v>16905</v>
       </c>
       <c r="D557" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10768,10 +10756,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>16506</v>
+        <v>16906</v>
       </c>
       <c r="D558" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10785,10 +10773,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>16507</v>
+        <v>16907</v>
       </c>
       <c r="D559" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10802,10 +10790,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>16508</v>
+        <v>16908</v>
       </c>
       <c r="D560" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10819,10 +10807,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>16509</v>
+        <v>16909</v>
       </c>
       <c r="D561" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10836,10 +10824,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>16510</v>
+        <v>16910</v>
       </c>
       <c r="D562" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10853,10 +10841,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>16511</v>
+        <v>16911</v>
       </c>
       <c r="D563" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10870,10 +10858,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>16512</v>
+        <v>16912</v>
       </c>
       <c r="D564" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10887,10 +10875,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>16513</v>
+        <v>16913</v>
       </c>
       <c r="D565" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10904,10 +10892,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>16514</v>
+        <v>16914</v>
       </c>
       <c r="D566" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10921,10 +10909,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>16515</v>
+        <v>16915</v>
       </c>
       <c r="D567" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10938,10 +10926,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>16516</v>
+        <v>16916</v>
       </c>
       <c r="D568" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10955,10 +10943,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>16517</v>
+        <v>16917</v>
       </c>
       <c r="D569" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10972,10 +10960,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>16518</v>
+        <v>16918</v>
       </c>
       <c r="D570" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10989,10 +10977,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>16519</v>
+        <v>16919</v>
       </c>
       <c r="D571" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11006,10 +10994,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>16520</v>
+        <v>16920</v>
       </c>
       <c r="D572" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11023,10 +11011,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>16521</v>
+        <v>16921</v>
       </c>
       <c r="D573" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11040,10 +11028,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>16522</v>
+        <v>16922</v>
       </c>
       <c r="D574" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11057,10 +11045,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>16523</v>
+        <v>16923</v>
       </c>
       <c r="D575" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11074,10 +11062,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>16524</v>
+        <v>16924</v>
       </c>
       <c r="D576" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11091,10 +11079,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>16525</v>
+        <v>16925</v>
       </c>
       <c r="D577" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11111,10 +11099,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>16601</v>
+        <v>17001</v>
       </c>
       <c r="D579" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11126,17 +11114,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20455</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>16602</v>
+        <v>17002</v>
       </c>
       <c r="D580" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11148,15 +11136,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20456</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>16603</v>
+        <v>17003</v>
       </c>
       <c r="D581" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11168,15 +11156,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20457</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>16604</v>
+        <v>17004</v>
       </c>
       <c r="D582" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11188,15 +11176,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20458</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>16605</v>
+        <v>17005</v>
       </c>
       <c r="D583" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11210,10 +11198,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>16606</v>
+        <v>17006</v>
       </c>
       <c r="D584" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11227,10 +11215,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>16607</v>
+        <v>17007</v>
       </c>
       <c r="D585" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11244,10 +11232,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>16608</v>
+        <v>17008</v>
       </c>
       <c r="D586" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11261,10 +11249,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>16609</v>
+        <v>17009</v>
       </c>
       <c r="D587" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11278,10 +11266,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>16610</v>
+        <v>17010</v>
       </c>
       <c r="D588" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11295,10 +11283,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>16611</v>
+        <v>17011</v>
       </c>
       <c r="D589" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11312,10 +11300,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>16612</v>
+        <v>17012</v>
       </c>
       <c r="D590" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11329,10 +11317,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>16613</v>
+        <v>17013</v>
       </c>
       <c r="D591" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11346,10 +11334,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>16614</v>
+        <v>17014</v>
       </c>
       <c r="D592" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11363,10 +11351,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>16615</v>
+        <v>17015</v>
       </c>
       <c r="D593" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11380,10 +11368,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>16616</v>
+        <v>17016</v>
       </c>
       <c r="D594" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11397,10 +11385,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>16617</v>
+        <v>17017</v>
       </c>
       <c r="D595" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11414,10 +11402,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>16618</v>
+        <v>17018</v>
       </c>
       <c r="D596" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11431,10 +11419,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>16619</v>
+        <v>17019</v>
       </c>
       <c r="D597" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11448,10 +11436,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>16620</v>
+        <v>17020</v>
       </c>
       <c r="D598" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11465,10 +11453,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>16621</v>
+        <v>17021</v>
       </c>
       <c r="D599" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11482,10 +11470,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>16622</v>
+        <v>17022</v>
       </c>
       <c r="D600" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11499,10 +11487,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>16623</v>
+        <v>17023</v>
       </c>
       <c r="D601" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11516,10 +11504,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>16624</v>
+        <v>17024</v>
       </c>
       <c r="D602" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11533,10 +11521,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>16625</v>
+        <v>17025</v>
       </c>
       <c r="D603" s="3">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11553,10 +11541,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>16701</v>
+        <v>17201</v>
       </c>
       <c r="D605" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11568,17 +11556,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20555</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>16702</v>
+        <v>17202</v>
       </c>
       <c r="D606" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11590,15 +11578,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20556</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>16703</v>
+        <v>17203</v>
       </c>
       <c r="D607" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11610,15 +11598,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20557</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>16704</v>
+        <v>17204</v>
       </c>
       <c r="D608" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11630,15 +11618,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20558</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>16705</v>
+        <v>17205</v>
       </c>
       <c r="D609" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11652,10 +11640,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>16706</v>
+        <v>17206</v>
       </c>
       <c r="D610" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11669,10 +11657,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>16707</v>
+        <v>17207</v>
       </c>
       <c r="D611" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11686,10 +11674,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>16708</v>
+        <v>17208</v>
       </c>
       <c r="D612" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11703,10 +11691,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>16709</v>
+        <v>17209</v>
       </c>
       <c r="D613" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11720,10 +11708,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>16710</v>
+        <v>17210</v>
       </c>
       <c r="D614" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11737,10 +11725,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>16711</v>
+        <v>17211</v>
       </c>
       <c r="D615" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11754,10 +11742,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>16712</v>
+        <v>17212</v>
       </c>
       <c r="D616" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11771,10 +11759,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>16713</v>
+        <v>17213</v>
       </c>
       <c r="D617" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11788,10 +11776,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>16714</v>
+        <v>17214</v>
       </c>
       <c r="D618" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11805,10 +11793,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>16715</v>
+        <v>17215</v>
       </c>
       <c r="D619" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11822,10 +11810,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>16716</v>
+        <v>17216</v>
       </c>
       <c r="D620" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11839,10 +11827,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>16717</v>
+        <v>17217</v>
       </c>
       <c r="D621" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11856,10 +11844,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>16718</v>
+        <v>17218</v>
       </c>
       <c r="D622" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11873,10 +11861,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>16719</v>
+        <v>17219</v>
       </c>
       <c r="D623" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11890,10 +11878,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>16720</v>
+        <v>17220</v>
       </c>
       <c r="D624" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11907,10 +11895,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>16721</v>
+        <v>17221</v>
       </c>
       <c r="D625" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11924,10 +11912,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>16722</v>
+        <v>17222</v>
       </c>
       <c r="D626" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11941,10 +11929,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>16723</v>
+        <v>17223</v>
       </c>
       <c r="D627" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11958,10 +11946,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>16724</v>
+        <v>17224</v>
       </c>
       <c r="D628" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11975,10 +11963,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>16725</v>
+        <v>17225</v>
       </c>
       <c r="D629" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11987,1774 +11975,6 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8">
-      <c r="A631" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C631" s="6">
-        <v>16801</v>
-      </c>
-      <c r="D631" s="3">
-        <v>168</v>
-      </c>
-      <c r="E631" s="5">
-        <v>1</v>
-      </c>
-      <c r="F631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G631" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H631" s="3">
-        <v>20505</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8">
-      <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
-      <c r="C632" s="6">
-        <v>16802</v>
-      </c>
-      <c r="D632" s="3">
-        <v>168</v>
-      </c>
-      <c r="E632" s="5">
-        <v>1</v>
-      </c>
-      <c r="F632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G632" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H632" s="3">
-        <v>20506</v>
-      </c>
-    </row>
-    <row r="633" spans="3:8">
-      <c r="C633" s="6">
-        <v>16803</v>
-      </c>
-      <c r="D633" s="3">
-        <v>168</v>
-      </c>
-      <c r="E633" s="5">
-        <v>1</v>
-      </c>
-      <c r="F633" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G633" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H633" s="3">
-        <v>20507</v>
-      </c>
-    </row>
-    <row r="634" spans="3:8">
-      <c r="C634" s="6">
-        <v>16804</v>
-      </c>
-      <c r="D634" s="3">
-        <v>168</v>
-      </c>
-      <c r="E634" s="5">
-        <v>1</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G634" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H634" s="3">
-        <v>20508</v>
-      </c>
-    </row>
-    <row r="635" spans="3:7">
-      <c r="C635" s="6">
-        <v>16805</v>
-      </c>
-      <c r="D635" s="3">
-        <v>168</v>
-      </c>
-      <c r="E635" s="3">
-        <v>1</v>
-      </c>
-      <c r="F635" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G635" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="636" spans="3:7">
-      <c r="C636" s="6">
-        <v>16806</v>
-      </c>
-      <c r="D636" s="3">
-        <v>168</v>
-      </c>
-      <c r="E636" s="5">
-        <v>1</v>
-      </c>
-      <c r="F636" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G636" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="637" spans="3:7">
-      <c r="C637" s="6">
-        <v>16807</v>
-      </c>
-      <c r="D637" s="3">
-        <v>168</v>
-      </c>
-      <c r="E637" s="5">
-        <v>1</v>
-      </c>
-      <c r="F637" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G637" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="638" spans="3:7">
-      <c r="C638" s="6">
-        <v>16808</v>
-      </c>
-      <c r="D638" s="3">
-        <v>168</v>
-      </c>
-      <c r="E638" s="5">
-        <v>1</v>
-      </c>
-      <c r="F638" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G638" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="639" spans="3:7">
-      <c r="C639" s="6">
-        <v>16809</v>
-      </c>
-      <c r="D639" s="3">
-        <v>168</v>
-      </c>
-      <c r="E639" s="3">
-        <v>1</v>
-      </c>
-      <c r="F639" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G639" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="640" spans="3:7">
-      <c r="C640" s="6">
-        <v>16810</v>
-      </c>
-      <c r="D640" s="3">
-        <v>168</v>
-      </c>
-      <c r="E640" s="5">
-        <v>1</v>
-      </c>
-      <c r="F640" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G640" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="641" spans="3:7">
-      <c r="C641" s="6">
-        <v>16811</v>
-      </c>
-      <c r="D641" s="3">
-        <v>168</v>
-      </c>
-      <c r="E641" s="5">
-        <v>1</v>
-      </c>
-      <c r="F641" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G641" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="642" spans="3:7">
-      <c r="C642" s="6">
-        <v>16812</v>
-      </c>
-      <c r="D642" s="3">
-        <v>168</v>
-      </c>
-      <c r="E642" s="5">
-        <v>1</v>
-      </c>
-      <c r="F642" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G642" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="643" spans="3:7">
-      <c r="C643" s="6">
-        <v>16813</v>
-      </c>
-      <c r="D643" s="3">
-        <v>168</v>
-      </c>
-      <c r="E643" s="3">
-        <v>1</v>
-      </c>
-      <c r="F643" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G643" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="644" spans="3:7">
-      <c r="C644" s="6">
-        <v>16814</v>
-      </c>
-      <c r="D644" s="3">
-        <v>168</v>
-      </c>
-      <c r="E644" s="5">
-        <v>1</v>
-      </c>
-      <c r="F644" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G644" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="645" spans="3:7">
-      <c r="C645" s="6">
-        <v>16815</v>
-      </c>
-      <c r="D645" s="3">
-        <v>168</v>
-      </c>
-      <c r="E645" s="5">
-        <v>1</v>
-      </c>
-      <c r="F645" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G645" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="646" spans="3:7">
-      <c r="C646" s="6">
-        <v>16816</v>
-      </c>
-      <c r="D646" s="3">
-        <v>168</v>
-      </c>
-      <c r="E646" s="5">
-        <v>1</v>
-      </c>
-      <c r="F646" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G646" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="647" spans="3:7">
-      <c r="C647" s="6">
-        <v>16817</v>
-      </c>
-      <c r="D647" s="3">
-        <v>168</v>
-      </c>
-      <c r="E647" s="3">
-        <v>1</v>
-      </c>
-      <c r="F647" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G647" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="648" spans="3:7">
-      <c r="C648" s="6">
-        <v>16818</v>
-      </c>
-      <c r="D648" s="3">
-        <v>168</v>
-      </c>
-      <c r="E648" s="5">
-        <v>1</v>
-      </c>
-      <c r="F648" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G648" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="649" spans="3:7">
-      <c r="C649" s="6">
-        <v>16819</v>
-      </c>
-      <c r="D649" s="3">
-        <v>168</v>
-      </c>
-      <c r="E649" s="5">
-        <v>1</v>
-      </c>
-      <c r="F649" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G649" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="650" spans="3:7">
-      <c r="C650" s="6">
-        <v>16820</v>
-      </c>
-      <c r="D650" s="3">
-        <v>168</v>
-      </c>
-      <c r="E650" s="5">
-        <v>1</v>
-      </c>
-      <c r="F650" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G650" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="651" spans="3:7">
-      <c r="C651" s="6">
-        <v>16821</v>
-      </c>
-      <c r="D651" s="3">
-        <v>168</v>
-      </c>
-      <c r="E651" s="3">
-        <v>1</v>
-      </c>
-      <c r="F651" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G651" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="652" spans="3:7">
-      <c r="C652" s="6">
-        <v>16822</v>
-      </c>
-      <c r="D652" s="3">
-        <v>168</v>
-      </c>
-      <c r="E652" s="5">
-        <v>1</v>
-      </c>
-      <c r="F652" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G652" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="653" spans="3:7">
-      <c r="C653" s="6">
-        <v>16823</v>
-      </c>
-      <c r="D653" s="3">
-        <v>168</v>
-      </c>
-      <c r="E653" s="5">
-        <v>1</v>
-      </c>
-      <c r="F653" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G653" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="654" spans="3:7">
-      <c r="C654" s="6">
-        <v>16824</v>
-      </c>
-      <c r="D654" s="3">
-        <v>168</v>
-      </c>
-      <c r="E654" s="5">
-        <v>1</v>
-      </c>
-      <c r="F654" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G654" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="655" spans="3:7">
-      <c r="C655" s="6">
-        <v>16825</v>
-      </c>
-      <c r="D655" s="3">
-        <v>168</v>
-      </c>
-      <c r="E655" s="3">
-        <v>1</v>
-      </c>
-      <c r="F655" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G655" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="657" spans="1:8">
-      <c r="A657" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C657" s="6">
-        <v>16901</v>
-      </c>
-      <c r="D657" s="3">
-        <v>169</v>
-      </c>
-      <c r="E657" s="5">
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H657" s="3">
-        <v>20515</v>
-      </c>
-    </row>
-    <row r="658" spans="1:8">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-      <c r="C658" s="6">
-        <v>16902</v>
-      </c>
-      <c r="D658" s="3">
-        <v>169</v>
-      </c>
-      <c r="E658" s="5">
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H658" s="3">
-        <v>20516</v>
-      </c>
-    </row>
-    <row r="659" spans="3:8">
-      <c r="C659" s="6">
-        <v>16903</v>
-      </c>
-      <c r="D659" s="3">
-        <v>169</v>
-      </c>
-      <c r="E659" s="5">
-        <v>1</v>
-      </c>
-      <c r="F659" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G659" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H659" s="3">
-        <v>20517</v>
-      </c>
-    </row>
-    <row r="660" spans="3:8">
-      <c r="C660" s="6">
-        <v>16904</v>
-      </c>
-      <c r="D660" s="3">
-        <v>169</v>
-      </c>
-      <c r="E660" s="5">
-        <v>1</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H660" s="3">
-        <v>20518</v>
-      </c>
-    </row>
-    <row r="661" spans="3:7">
-      <c r="C661" s="6">
-        <v>16905</v>
-      </c>
-      <c r="D661" s="3">
-        <v>169</v>
-      </c>
-      <c r="E661" s="3">
-        <v>1</v>
-      </c>
-      <c r="F661" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G661" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="662" spans="3:7">
-      <c r="C662" s="6">
-        <v>16906</v>
-      </c>
-      <c r="D662" s="3">
-        <v>169</v>
-      </c>
-      <c r="E662" s="5">
-        <v>1</v>
-      </c>
-      <c r="F662" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G662" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="663" spans="3:7">
-      <c r="C663" s="6">
-        <v>16907</v>
-      </c>
-      <c r="D663" s="3">
-        <v>169</v>
-      </c>
-      <c r="E663" s="5">
-        <v>1</v>
-      </c>
-      <c r="F663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G663" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="664" spans="3:7">
-      <c r="C664" s="6">
-        <v>16908</v>
-      </c>
-      <c r="D664" s="3">
-        <v>169</v>
-      </c>
-      <c r="E664" s="5">
-        <v>1</v>
-      </c>
-      <c r="F664" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G664" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="665" spans="3:7">
-      <c r="C665" s="6">
-        <v>16909</v>
-      </c>
-      <c r="D665" s="3">
-        <v>169</v>
-      </c>
-      <c r="E665" s="3">
-        <v>1</v>
-      </c>
-      <c r="F665" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G665" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="666" spans="3:7">
-      <c r="C666" s="6">
-        <v>16910</v>
-      </c>
-      <c r="D666" s="3">
-        <v>169</v>
-      </c>
-      <c r="E666" s="5">
-        <v>1</v>
-      </c>
-      <c r="F666" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G666" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="667" spans="3:7">
-      <c r="C667" s="6">
-        <v>16911</v>
-      </c>
-      <c r="D667" s="3">
-        <v>169</v>
-      </c>
-      <c r="E667" s="5">
-        <v>1</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G667" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="668" spans="3:7">
-      <c r="C668" s="6">
-        <v>16912</v>
-      </c>
-      <c r="D668" s="3">
-        <v>169</v>
-      </c>
-      <c r="E668" s="5">
-        <v>1</v>
-      </c>
-      <c r="F668" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G668" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="669" spans="3:7">
-      <c r="C669" s="6">
-        <v>16913</v>
-      </c>
-      <c r="D669" s="3">
-        <v>169</v>
-      </c>
-      <c r="E669" s="3">
-        <v>1</v>
-      </c>
-      <c r="F669" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G669" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="670" spans="3:7">
-      <c r="C670" s="6">
-        <v>16914</v>
-      </c>
-      <c r="D670" s="3">
-        <v>169</v>
-      </c>
-      <c r="E670" s="5">
-        <v>1</v>
-      </c>
-      <c r="F670" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G670" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="671" spans="3:7">
-      <c r="C671" s="6">
-        <v>16915</v>
-      </c>
-      <c r="D671" s="3">
-        <v>169</v>
-      </c>
-      <c r="E671" s="5">
-        <v>1</v>
-      </c>
-      <c r="F671" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G671" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="672" spans="3:7">
-      <c r="C672" s="6">
-        <v>16916</v>
-      </c>
-      <c r="D672" s="3">
-        <v>169</v>
-      </c>
-      <c r="E672" s="5">
-        <v>1</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G672" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="673" spans="3:7">
-      <c r="C673" s="6">
-        <v>16917</v>
-      </c>
-      <c r="D673" s="3">
-        <v>169</v>
-      </c>
-      <c r="E673" s="3">
-        <v>1</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G673" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="674" spans="3:7">
-      <c r="C674" s="6">
-        <v>16918</v>
-      </c>
-      <c r="D674" s="3">
-        <v>169</v>
-      </c>
-      <c r="E674" s="5">
-        <v>1</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G674" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="675" spans="3:7">
-      <c r="C675" s="6">
-        <v>16919</v>
-      </c>
-      <c r="D675" s="3">
-        <v>169</v>
-      </c>
-      <c r="E675" s="5">
-        <v>1</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G675" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="676" spans="3:7">
-      <c r="C676" s="6">
-        <v>16920</v>
-      </c>
-      <c r="D676" s="3">
-        <v>169</v>
-      </c>
-      <c r="E676" s="5">
-        <v>1</v>
-      </c>
-      <c r="F676" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G676" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="677" spans="3:7">
-      <c r="C677" s="6">
-        <v>16921</v>
-      </c>
-      <c r="D677" s="3">
-        <v>169</v>
-      </c>
-      <c r="E677" s="3">
-        <v>1</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G677" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="678" spans="3:7">
-      <c r="C678" s="6">
-        <v>16922</v>
-      </c>
-      <c r="D678" s="3">
-        <v>169</v>
-      </c>
-      <c r="E678" s="5">
-        <v>1</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G678" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="679" spans="3:7">
-      <c r="C679" s="6">
-        <v>16923</v>
-      </c>
-      <c r="D679" s="3">
-        <v>169</v>
-      </c>
-      <c r="E679" s="5">
-        <v>1</v>
-      </c>
-      <c r="F679" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G679" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="680" spans="3:7">
-      <c r="C680" s="6">
-        <v>16924</v>
-      </c>
-      <c r="D680" s="3">
-        <v>169</v>
-      </c>
-      <c r="E680" s="5">
-        <v>1</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G680" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="681" spans="3:7">
-      <c r="C681" s="6">
-        <v>16925</v>
-      </c>
-      <c r="D681" s="3">
-        <v>169</v>
-      </c>
-      <c r="E681" s="3">
-        <v>1</v>
-      </c>
-      <c r="F681" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>17001</v>
-      </c>
-      <c r="D683" s="3">
-        <v>170</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20565</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>17002</v>
-      </c>
-      <c r="D684" s="3">
-        <v>170</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20566</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>17003</v>
-      </c>
-      <c r="D685" s="3">
-        <v>170</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20567</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>17004</v>
-      </c>
-      <c r="D686" s="3">
-        <v>170</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20568</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>17005</v>
-      </c>
-      <c r="D687" s="3">
-        <v>170</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>17006</v>
-      </c>
-      <c r="D688" s="3">
-        <v>170</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>17007</v>
-      </c>
-      <c r="D689" s="3">
-        <v>170</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>17008</v>
-      </c>
-      <c r="D690" s="3">
-        <v>170</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>17009</v>
-      </c>
-      <c r="D691" s="3">
-        <v>170</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>17010</v>
-      </c>
-      <c r="D692" s="3">
-        <v>170</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>17011</v>
-      </c>
-      <c r="D693" s="3">
-        <v>170</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>17012</v>
-      </c>
-      <c r="D694" s="3">
-        <v>170</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>17013</v>
-      </c>
-      <c r="D695" s="3">
-        <v>170</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>17014</v>
-      </c>
-      <c r="D696" s="3">
-        <v>170</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>17015</v>
-      </c>
-      <c r="D697" s="3">
-        <v>170</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>17016</v>
-      </c>
-      <c r="D698" s="3">
-        <v>170</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>17017</v>
-      </c>
-      <c r="D699" s="3">
-        <v>170</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>17018</v>
-      </c>
-      <c r="D700" s="3">
-        <v>170</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>17019</v>
-      </c>
-      <c r="D701" s="3">
-        <v>170</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>17020</v>
-      </c>
-      <c r="D702" s="3">
-        <v>170</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>17021</v>
-      </c>
-      <c r="D703" s="3">
-        <v>170</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>17022</v>
-      </c>
-      <c r="D704" s="3">
-        <v>170</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>17023</v>
-      </c>
-      <c r="D705" s="3">
-        <v>170</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>17024</v>
-      </c>
-      <c r="D706" s="3">
-        <v>170</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>17025</v>
-      </c>
-      <c r="D707" s="3">
-        <v>170</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>17201</v>
-      </c>
-      <c r="D709" s="3">
-        <v>172</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20585</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>17202</v>
-      </c>
-      <c r="D710" s="3">
-        <v>172</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20586</v>
-      </c>
-    </row>
-    <row r="711" spans="3:8">
-      <c r="C711" s="6">
-        <v>17203</v>
-      </c>
-      <c r="D711" s="3">
-        <v>172</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20587</v>
-      </c>
-    </row>
-    <row r="712" spans="3:8">
-      <c r="C712" s="6">
-        <v>17204</v>
-      </c>
-      <c r="D712" s="3">
-        <v>172</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20588</v>
-      </c>
-    </row>
-    <row r="713" spans="3:7">
-      <c r="C713" s="6">
-        <v>17205</v>
-      </c>
-      <c r="D713" s="3">
-        <v>172</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="3:7">
-      <c r="C714" s="6">
-        <v>17206</v>
-      </c>
-      <c r="D714" s="3">
-        <v>172</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="3:7">
-      <c r="C715" s="6">
-        <v>17207</v>
-      </c>
-      <c r="D715" s="3">
-        <v>172</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="3:7">
-      <c r="C716" s="6">
-        <v>17208</v>
-      </c>
-      <c r="D716" s="3">
-        <v>172</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="3:7">
-      <c r="C717" s="6">
-        <v>17209</v>
-      </c>
-      <c r="D717" s="3">
-        <v>172</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="3:7">
-      <c r="C718" s="6">
-        <v>17210</v>
-      </c>
-      <c r="D718" s="3">
-        <v>172</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="3:7">
-      <c r="C719" s="6">
-        <v>17211</v>
-      </c>
-      <c r="D719" s="3">
-        <v>172</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="3:7">
-      <c r="C720" s="6">
-        <v>17212</v>
-      </c>
-      <c r="D720" s="3">
-        <v>172</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="3:7">
-      <c r="C721" s="6">
-        <v>17213</v>
-      </c>
-      <c r="D721" s="3">
-        <v>172</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="3:7">
-      <c r="C722" s="6">
-        <v>17214</v>
-      </c>
-      <c r="D722" s="3">
-        <v>172</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="3:7">
-      <c r="C723" s="6">
-        <v>17215</v>
-      </c>
-      <c r="D723" s="3">
-        <v>172</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="3:7">
-      <c r="C724" s="6">
-        <v>17216</v>
-      </c>
-      <c r="D724" s="3">
-        <v>172</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="3:7">
-      <c r="C725" s="6">
-        <v>17217</v>
-      </c>
-      <c r="D725" s="3">
-        <v>172</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="3:7">
-      <c r="C726" s="6">
-        <v>17218</v>
-      </c>
-      <c r="D726" s="3">
-        <v>172</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="3:7">
-      <c r="C727" s="6">
-        <v>17219</v>
-      </c>
-      <c r="D727" s="3">
-        <v>172</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="3:7">
-      <c r="C728" s="6">
-        <v>17220</v>
-      </c>
-      <c r="D728" s="3">
-        <v>172</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="3:7">
-      <c r="C729" s="6">
-        <v>17221</v>
-      </c>
-      <c r="D729" s="3">
-        <v>172</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="3:7">
-      <c r="C730" s="6">
-        <v>17222</v>
-      </c>
-      <c r="D730" s="3">
-        <v>172</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="3:7">
-      <c r="C731" s="6">
-        <v>17223</v>
-      </c>
-      <c r="D731" s="3">
-        <v>172</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="3:7">
-      <c r="C732" s="6">
-        <v>17224</v>
-      </c>
-      <c r="D732" s="3">
-        <v>172</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="3:7">
-      <c r="C733" s="6">
-        <v>17225</v>
-      </c>
-      <c r="D733" s="3">
-        <v>172</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +12095,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +12113,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +12131,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +12149,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +12169,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +12267,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>#先锋172星辰殿堂</t>
+  </si>
+  <si>
+    <t>#先锋173</t>
   </si>
   <si>
     <t>Center</t>
@@ -1254,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O629"/>
+  <dimension ref="A3:O655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -11975,6 +11978,448 @@
         <v>42</v>
       </c>
       <c r="G629" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8">
+      <c r="A631" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C631" s="6">
+        <v>17301</v>
+      </c>
+      <c r="D631" s="3">
+        <v>173</v>
+      </c>
+      <c r="E631" s="5">
+        <v>1</v>
+      </c>
+      <c r="F631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G631" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H631" s="3">
+        <v>20415</v>
+      </c>
+    </row>
+    <row r="632" spans="1:8">
+      <c r="A632" s="1"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="6">
+        <v>17302</v>
+      </c>
+      <c r="D632" s="3">
+        <v>173</v>
+      </c>
+      <c r="E632" s="5">
+        <v>1</v>
+      </c>
+      <c r="F632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G632" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H632" s="3">
+        <v>20416</v>
+      </c>
+    </row>
+    <row r="633" spans="3:8">
+      <c r="C633" s="6">
+        <v>17303</v>
+      </c>
+      <c r="D633" s="3">
+        <v>173</v>
+      </c>
+      <c r="E633" s="5">
+        <v>1</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G633" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H633" s="3">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="634" spans="3:8">
+      <c r="C634" s="6">
+        <v>17304</v>
+      </c>
+      <c r="D634" s="3">
+        <v>173</v>
+      </c>
+      <c r="E634" s="5">
+        <v>1</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H634" s="3">
+        <v>20418</v>
+      </c>
+    </row>
+    <row r="635" spans="3:7">
+      <c r="C635" s="6">
+        <v>17305</v>
+      </c>
+      <c r="D635" s="3">
+        <v>173</v>
+      </c>
+      <c r="E635" s="3">
+        <v>1</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G635" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="636" spans="3:7">
+      <c r="C636" s="6">
+        <v>17306</v>
+      </c>
+      <c r="D636" s="3">
+        <v>173</v>
+      </c>
+      <c r="E636" s="5">
+        <v>1</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="637" spans="3:7">
+      <c r="C637" s="6">
+        <v>17307</v>
+      </c>
+      <c r="D637" s="3">
+        <v>173</v>
+      </c>
+      <c r="E637" s="5">
+        <v>1</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="638" spans="3:7">
+      <c r="C638" s="6">
+        <v>17308</v>
+      </c>
+      <c r="D638" s="3">
+        <v>173</v>
+      </c>
+      <c r="E638" s="5">
+        <v>1</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="639" spans="3:7">
+      <c r="C639" s="6">
+        <v>17309</v>
+      </c>
+      <c r="D639" s="3">
+        <v>173</v>
+      </c>
+      <c r="E639" s="3">
+        <v>1</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="640" spans="3:7">
+      <c r="C640" s="6">
+        <v>17310</v>
+      </c>
+      <c r="D640" s="3">
+        <v>173</v>
+      </c>
+      <c r="E640" s="5">
+        <v>1</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="3:7">
+      <c r="C641" s="6">
+        <v>17311</v>
+      </c>
+      <c r="D641" s="3">
+        <v>173</v>
+      </c>
+      <c r="E641" s="5">
+        <v>1</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="642" spans="3:7">
+      <c r="C642" s="6">
+        <v>17312</v>
+      </c>
+      <c r="D642" s="3">
+        <v>173</v>
+      </c>
+      <c r="E642" s="5">
+        <v>1</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="643" spans="3:7">
+      <c r="C643" s="6">
+        <v>17313</v>
+      </c>
+      <c r="D643" s="3">
+        <v>173</v>
+      </c>
+      <c r="E643" s="3">
+        <v>1</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="644" spans="3:7">
+      <c r="C644" s="6">
+        <v>17314</v>
+      </c>
+      <c r="D644" s="3">
+        <v>173</v>
+      </c>
+      <c r="E644" s="5">
+        <v>1</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G644" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="645" spans="3:7">
+      <c r="C645" s="6">
+        <v>17315</v>
+      </c>
+      <c r="D645" s="3">
+        <v>173</v>
+      </c>
+      <c r="E645" s="5">
+        <v>1</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="646" spans="3:7">
+      <c r="C646" s="6">
+        <v>17316</v>
+      </c>
+      <c r="D646" s="3">
+        <v>173</v>
+      </c>
+      <c r="E646" s="5">
+        <v>1</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="647" spans="3:7">
+      <c r="C647" s="6">
+        <v>17317</v>
+      </c>
+      <c r="D647" s="3">
+        <v>173</v>
+      </c>
+      <c r="E647" s="3">
+        <v>1</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="648" spans="3:7">
+      <c r="C648" s="6">
+        <v>17318</v>
+      </c>
+      <c r="D648" s="3">
+        <v>173</v>
+      </c>
+      <c r="E648" s="5">
+        <v>1</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="649" spans="3:7">
+      <c r="C649" s="6">
+        <v>17319</v>
+      </c>
+      <c r="D649" s="3">
+        <v>173</v>
+      </c>
+      <c r="E649" s="5">
+        <v>1</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="650" spans="3:7">
+      <c r="C650" s="6">
+        <v>17320</v>
+      </c>
+      <c r="D650" s="3">
+        <v>173</v>
+      </c>
+      <c r="E650" s="5">
+        <v>1</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="651" spans="3:7">
+      <c r="C651" s="6">
+        <v>17321</v>
+      </c>
+      <c r="D651" s="3">
+        <v>173</v>
+      </c>
+      <c r="E651" s="3">
+        <v>1</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="652" spans="3:7">
+      <c r="C652" s="6">
+        <v>17322</v>
+      </c>
+      <c r="D652" s="3">
+        <v>173</v>
+      </c>
+      <c r="E652" s="5">
+        <v>1</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="653" spans="3:7">
+      <c r="C653" s="6">
+        <v>17323</v>
+      </c>
+      <c r="D653" s="3">
+        <v>173</v>
+      </c>
+      <c r="E653" s="5">
+        <v>1</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="654" spans="3:7">
+      <c r="C654" s="6">
+        <v>17324</v>
+      </c>
+      <c r="D654" s="3">
+        <v>173</v>
+      </c>
+      <c r="E654" s="5">
+        <v>1</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="655" spans="3:7">
+      <c r="C655" s="6">
+        <v>17325</v>
+      </c>
+      <c r="D655" s="3">
+        <v>173</v>
+      </c>
+      <c r="E655" s="3">
+        <v>1</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G655" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12095,10 +12540,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12113,10 +12558,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12131,10 +12576,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12149,10 +12594,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12169,10 +12614,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -12267,10 +12712,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -229,7 +229,7 @@
     <t>#先锋172星辰殿堂</t>
   </si>
   <si>
-    <t>#先锋173</t>
+    <t>#先锋173童话森林</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋173童话森林</t>
+  </si>
+  <si>
+    <t>#先锋174</t>
   </si>
   <si>
     <t>Center</t>
@@ -1257,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12420,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>17401</v>
+      </c>
+      <c r="D657" s="3">
+        <v>174</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20445</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>17402</v>
+      </c>
+      <c r="D658" s="3">
+        <v>174</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>17403</v>
+      </c>
+      <c r="D659" s="3">
+        <v>174</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20447</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>17404</v>
+      </c>
+      <c r="D660" s="3">
+        <v>174</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20448</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>17405</v>
+      </c>
+      <c r="D661" s="3">
+        <v>174</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>17406</v>
+      </c>
+      <c r="D662" s="3">
+        <v>174</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>17407</v>
+      </c>
+      <c r="D663" s="3">
+        <v>174</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>17408</v>
+      </c>
+      <c r="D664" s="3">
+        <v>174</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>17409</v>
+      </c>
+      <c r="D665" s="3">
+        <v>174</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>17410</v>
+      </c>
+      <c r="D666" s="3">
+        <v>174</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>17411</v>
+      </c>
+      <c r="D667" s="3">
+        <v>174</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>17412</v>
+      </c>
+      <c r="D668" s="3">
+        <v>174</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>17413</v>
+      </c>
+      <c r="D669" s="3">
+        <v>174</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>17414</v>
+      </c>
+      <c r="D670" s="3">
+        <v>174</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>17415</v>
+      </c>
+      <c r="D671" s="3">
+        <v>174</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>17416</v>
+      </c>
+      <c r="D672" s="3">
+        <v>174</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>17417</v>
+      </c>
+      <c r="D673" s="3">
+        <v>174</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>17418</v>
+      </c>
+      <c r="D674" s="3">
+        <v>174</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>17419</v>
+      </c>
+      <c r="D675" s="3">
+        <v>174</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>17420</v>
+      </c>
+      <c r="D676" s="3">
+        <v>174</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>17421</v>
+      </c>
+      <c r="D677" s="3">
+        <v>174</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>17422</v>
+      </c>
+      <c r="D678" s="3">
+        <v>174</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>17423</v>
+      </c>
+      <c r="D679" s="3">
+        <v>174</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>17424</v>
+      </c>
+      <c r="D680" s="3">
+        <v>174</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>17425</v>
+      </c>
+      <c r="D681" s="3">
+        <v>174</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12540,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12558,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12576,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12594,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12614,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12712,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -232,7 +232,10 @@
     <t>#先锋173童话森林</t>
   </si>
   <si>
-    <t>#先锋174</t>
+    <t>#先锋174龙息之谷</t>
+  </si>
+  <si>
+    <t>#先锋175</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>17501</v>
+      </c>
+      <c r="D683" s="3">
+        <v>175</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>17502</v>
+      </c>
+      <c r="D684" s="3">
+        <v>175</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>17503</v>
+      </c>
+      <c r="D685" s="3">
+        <v>175</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>17504</v>
+      </c>
+      <c r="D686" s="3">
+        <v>175</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>17505</v>
+      </c>
+      <c r="D687" s="3">
+        <v>175</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>17506</v>
+      </c>
+      <c r="D688" s="3">
+        <v>175</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>17507</v>
+      </c>
+      <c r="D689" s="3">
+        <v>175</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>17508</v>
+      </c>
+      <c r="D690" s="3">
+        <v>175</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>17509</v>
+      </c>
+      <c r="D691" s="3">
+        <v>175</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>17510</v>
+      </c>
+      <c r="D692" s="3">
+        <v>175</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>17511</v>
+      </c>
+      <c r="D693" s="3">
+        <v>175</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>17512</v>
+      </c>
+      <c r="D694" s="3">
+        <v>175</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>17513</v>
+      </c>
+      <c r="D695" s="3">
+        <v>175</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>17514</v>
+      </c>
+      <c r="D696" s="3">
+        <v>175</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>17515</v>
+      </c>
+      <c r="D697" s="3">
+        <v>175</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>17516</v>
+      </c>
+      <c r="D698" s="3">
+        <v>175</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>17517</v>
+      </c>
+      <c r="D699" s="3">
+        <v>175</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>17518</v>
+      </c>
+      <c r="D700" s="3">
+        <v>175</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>17519</v>
+      </c>
+      <c r="D701" s="3">
+        <v>175</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>17520</v>
+      </c>
+      <c r="D702" s="3">
+        <v>175</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>17521</v>
+      </c>
+      <c r="D703" s="3">
+        <v>175</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>17522</v>
+      </c>
+      <c r="D704" s="3">
+        <v>175</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>17523</v>
+      </c>
+      <c r="D705" s="3">
+        <v>175</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>17524</v>
+      </c>
+      <c r="D706" s="3">
+        <v>175</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>17525</v>
+      </c>
+      <c r="D707" s="3">
+        <v>175</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -217,13 +217,7 @@
     <t>#先锋167青云之巅</t>
   </si>
   <si>
-    <t>#先锋168时光之歌</t>
-  </si>
-  <si>
     <t>#先锋169决战之巅</t>
-  </si>
-  <si>
-    <t>#先锋170迷雾森境</t>
   </si>
   <si>
     <t>#先锋172星辰殿堂</t>
@@ -235,7 +229,7 @@
     <t>#先锋174龙息之谷</t>
   </si>
   <si>
-    <t>#先锋175</t>
+    <t>#先锋175星界回廊</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1257,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O655"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -10224,10 +10218,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>16801</v>
+        <v>16901</v>
       </c>
       <c r="D527" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10239,17 +10233,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20505</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>16802</v>
+        <v>16902</v>
       </c>
       <c r="D528" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10261,15 +10255,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20506</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>16803</v>
+        <v>16903</v>
       </c>
       <c r="D529" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10281,15 +10275,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20507</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>16804</v>
+        <v>16904</v>
       </c>
       <c r="D530" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10301,15 +10295,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20508</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>16805</v>
+        <v>16905</v>
       </c>
       <c r="D531" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10323,10 +10317,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>16806</v>
+        <v>16906</v>
       </c>
       <c r="D532" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10340,10 +10334,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>16807</v>
+        <v>16907</v>
       </c>
       <c r="D533" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10357,10 +10351,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>16808</v>
+        <v>16908</v>
       </c>
       <c r="D534" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10374,10 +10368,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>16809</v>
+        <v>16909</v>
       </c>
       <c r="D535" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10391,10 +10385,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>16810</v>
+        <v>16910</v>
       </c>
       <c r="D536" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10408,10 +10402,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>16811</v>
+        <v>16911</v>
       </c>
       <c r="D537" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10425,10 +10419,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>16812</v>
+        <v>16912</v>
       </c>
       <c r="D538" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10442,10 +10436,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>16813</v>
+        <v>16913</v>
       </c>
       <c r="D539" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10459,10 +10453,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>16814</v>
+        <v>16914</v>
       </c>
       <c r="D540" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10476,10 +10470,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>16815</v>
+        <v>16915</v>
       </c>
       <c r="D541" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10493,10 +10487,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>16816</v>
+        <v>16916</v>
       </c>
       <c r="D542" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10510,10 +10504,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>16817</v>
+        <v>16917</v>
       </c>
       <c r="D543" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10527,10 +10521,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>16818</v>
+        <v>16918</v>
       </c>
       <c r="D544" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10544,10 +10538,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>16819</v>
+        <v>16919</v>
       </c>
       <c r="D545" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10561,10 +10555,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>16820</v>
+        <v>16920</v>
       </c>
       <c r="D546" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10578,10 +10572,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>16821</v>
+        <v>16921</v>
       </c>
       <c r="D547" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10595,10 +10589,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>16822</v>
+        <v>16922</v>
       </c>
       <c r="D548" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10612,10 +10606,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>16823</v>
+        <v>16923</v>
       </c>
       <c r="D549" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10629,10 +10623,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>16824</v>
+        <v>16924</v>
       </c>
       <c r="D550" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10646,10 +10640,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>16825</v>
+        <v>16925</v>
       </c>
       <c r="D551" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10666,10 +10660,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>16901</v>
+        <v>17201</v>
       </c>
       <c r="D553" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10681,17 +10675,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20515</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>16902</v>
+        <v>17202</v>
       </c>
       <c r="D554" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10703,15 +10697,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20516</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>16903</v>
+        <v>17203</v>
       </c>
       <c r="D555" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10723,15 +10717,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20517</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>16904</v>
+        <v>17204</v>
       </c>
       <c r="D556" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10743,15 +10737,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20518</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>16905</v>
+        <v>17205</v>
       </c>
       <c r="D557" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10765,10 +10759,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>16906</v>
+        <v>17206</v>
       </c>
       <c r="D558" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10782,10 +10776,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>16907</v>
+        <v>17207</v>
       </c>
       <c r="D559" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10799,10 +10793,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>16908</v>
+        <v>17208</v>
       </c>
       <c r="D560" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10816,10 +10810,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>16909</v>
+        <v>17209</v>
       </c>
       <c r="D561" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10833,10 +10827,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>16910</v>
+        <v>17210</v>
       </c>
       <c r="D562" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10850,10 +10844,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>16911</v>
+        <v>17211</v>
       </c>
       <c r="D563" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10867,10 +10861,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>16912</v>
+        <v>17212</v>
       </c>
       <c r="D564" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10884,10 +10878,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>16913</v>
+        <v>17213</v>
       </c>
       <c r="D565" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10901,10 +10895,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>16914</v>
+        <v>17214</v>
       </c>
       <c r="D566" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10918,10 +10912,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>16915</v>
+        <v>17215</v>
       </c>
       <c r="D567" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10935,10 +10929,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>16916</v>
+        <v>17216</v>
       </c>
       <c r="D568" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10952,10 +10946,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>16917</v>
+        <v>17217</v>
       </c>
       <c r="D569" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10969,10 +10963,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>16918</v>
+        <v>17218</v>
       </c>
       <c r="D570" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10986,10 +10980,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>16919</v>
+        <v>17219</v>
       </c>
       <c r="D571" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11003,10 +10997,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>16920</v>
+        <v>17220</v>
       </c>
       <c r="D572" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11020,10 +11014,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>16921</v>
+        <v>17221</v>
       </c>
       <c r="D573" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11037,10 +11031,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>16922</v>
+        <v>17222</v>
       </c>
       <c r="D574" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11054,10 +11048,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>16923</v>
+        <v>17223</v>
       </c>
       <c r="D575" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11071,10 +11065,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>16924</v>
+        <v>17224</v>
       </c>
       <c r="D576" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11088,10 +11082,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>16925</v>
+        <v>17225</v>
       </c>
       <c r="D577" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11108,10 +11102,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>17001</v>
+        <v>17301</v>
       </c>
       <c r="D579" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11123,17 +11117,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20565</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>17002</v>
+        <v>17302</v>
       </c>
       <c r="D580" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11145,15 +11139,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20566</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>17003</v>
+        <v>17303</v>
       </c>
       <c r="D581" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11165,15 +11159,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20567</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>17004</v>
+        <v>17304</v>
       </c>
       <c r="D582" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11185,15 +11179,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20568</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>17005</v>
+        <v>17305</v>
       </c>
       <c r="D583" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11207,10 +11201,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>17006</v>
+        <v>17306</v>
       </c>
       <c r="D584" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11224,10 +11218,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>17007</v>
+        <v>17307</v>
       </c>
       <c r="D585" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11241,10 +11235,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>17008</v>
+        <v>17308</v>
       </c>
       <c r="D586" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11258,10 +11252,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>17009</v>
+        <v>17309</v>
       </c>
       <c r="D587" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11275,10 +11269,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>17010</v>
+        <v>17310</v>
       </c>
       <c r="D588" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11292,10 +11286,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>17011</v>
+        <v>17311</v>
       </c>
       <c r="D589" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11309,10 +11303,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>17012</v>
+        <v>17312</v>
       </c>
       <c r="D590" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11326,10 +11320,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>17013</v>
+        <v>17313</v>
       </c>
       <c r="D591" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11343,10 +11337,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>17014</v>
+        <v>17314</v>
       </c>
       <c r="D592" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11360,10 +11354,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>17015</v>
+        <v>17315</v>
       </c>
       <c r="D593" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11377,10 +11371,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>17016</v>
+        <v>17316</v>
       </c>
       <c r="D594" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11394,10 +11388,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>17017</v>
+        <v>17317</v>
       </c>
       <c r="D595" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11411,10 +11405,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>17018</v>
+        <v>17318</v>
       </c>
       <c r="D596" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11428,10 +11422,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>17019</v>
+        <v>17319</v>
       </c>
       <c r="D597" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11445,10 +11439,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>17020</v>
+        <v>17320</v>
       </c>
       <c r="D598" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11462,10 +11456,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>17021</v>
+        <v>17321</v>
       </c>
       <c r="D599" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11479,10 +11473,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>17022</v>
+        <v>17322</v>
       </c>
       <c r="D600" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11496,10 +11490,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>17023</v>
+        <v>17323</v>
       </c>
       <c r="D601" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11513,10 +11507,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>17024</v>
+        <v>17324</v>
       </c>
       <c r="D602" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11530,10 +11524,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>17025</v>
+        <v>17325</v>
       </c>
       <c r="D603" s="3">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11550,10 +11544,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>17201</v>
+        <v>17401</v>
       </c>
       <c r="D605" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11565,17 +11559,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20585</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>17202</v>
+        <v>17402</v>
       </c>
       <c r="D606" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11587,15 +11581,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20586</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>17203</v>
+        <v>17403</v>
       </c>
       <c r="D607" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11607,15 +11601,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20587</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>17204</v>
+        <v>17404</v>
       </c>
       <c r="D608" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11627,15 +11621,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20588</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>17205</v>
+        <v>17405</v>
       </c>
       <c r="D609" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11649,10 +11643,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>17206</v>
+        <v>17406</v>
       </c>
       <c r="D610" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11666,10 +11660,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>17207</v>
+        <v>17407</v>
       </c>
       <c r="D611" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11683,10 +11677,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>17208</v>
+        <v>17408</v>
       </c>
       <c r="D612" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11700,10 +11694,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>17209</v>
+        <v>17409</v>
       </c>
       <c r="D613" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11717,10 +11711,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>17210</v>
+        <v>17410</v>
       </c>
       <c r="D614" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11734,10 +11728,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>17211</v>
+        <v>17411</v>
       </c>
       <c r="D615" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11751,10 +11745,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>17212</v>
+        <v>17412</v>
       </c>
       <c r="D616" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11768,10 +11762,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>17213</v>
+        <v>17413</v>
       </c>
       <c r="D617" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11785,10 +11779,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>17214</v>
+        <v>17414</v>
       </c>
       <c r="D618" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11802,10 +11796,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>17215</v>
+        <v>17415</v>
       </c>
       <c r="D619" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11819,10 +11813,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>17216</v>
+        <v>17416</v>
       </c>
       <c r="D620" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11836,10 +11830,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>17217</v>
+        <v>17417</v>
       </c>
       <c r="D621" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11853,10 +11847,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>17218</v>
+        <v>17418</v>
       </c>
       <c r="D622" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11870,10 +11864,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>17219</v>
+        <v>17419</v>
       </c>
       <c r="D623" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11887,10 +11881,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>17220</v>
+        <v>17420</v>
       </c>
       <c r="D624" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11904,10 +11898,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>17221</v>
+        <v>17421</v>
       </c>
       <c r="D625" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11921,10 +11915,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>17222</v>
+        <v>17422</v>
       </c>
       <c r="D626" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11938,10 +11932,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>17223</v>
+        <v>17423</v>
       </c>
       <c r="D627" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11955,10 +11949,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>17224</v>
+        <v>17424</v>
       </c>
       <c r="D628" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11972,10 +11966,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>17225</v>
+        <v>17425</v>
       </c>
       <c r="D629" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11992,10 +11986,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>17301</v>
+        <v>17501</v>
       </c>
       <c r="D631" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12007,17 +12001,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20415</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>17302</v>
+        <v>17502</v>
       </c>
       <c r="D632" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12029,15 +12023,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20416</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>17303</v>
+        <v>17503</v>
       </c>
       <c r="D633" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12049,15 +12043,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20417</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>17304</v>
+        <v>17504</v>
       </c>
       <c r="D634" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12069,15 +12063,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20418</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>17305</v>
+        <v>17505</v>
       </c>
       <c r="D635" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12091,10 +12085,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>17306</v>
+        <v>17506</v>
       </c>
       <c r="D636" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12108,10 +12102,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>17307</v>
+        <v>17507</v>
       </c>
       <c r="D637" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12125,10 +12119,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>17308</v>
+        <v>17508</v>
       </c>
       <c r="D638" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12142,10 +12136,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>17309</v>
+        <v>17509</v>
       </c>
       <c r="D639" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12159,10 +12153,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>17310</v>
+        <v>17510</v>
       </c>
       <c r="D640" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12176,10 +12170,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>17311</v>
+        <v>17511</v>
       </c>
       <c r="D641" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12193,10 +12187,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>17312</v>
+        <v>17512</v>
       </c>
       <c r="D642" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12210,10 +12204,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>17313</v>
+        <v>17513</v>
       </c>
       <c r="D643" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12227,10 +12221,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>17314</v>
+        <v>17514</v>
       </c>
       <c r="D644" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12244,10 +12238,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>17315</v>
+        <v>17515</v>
       </c>
       <c r="D645" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12261,10 +12255,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>17316</v>
+        <v>17516</v>
       </c>
       <c r="D646" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12278,10 +12272,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>17317</v>
+        <v>17517</v>
       </c>
       <c r="D647" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12295,10 +12289,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>17318</v>
+        <v>17518</v>
       </c>
       <c r="D648" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12312,10 +12306,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>17319</v>
+        <v>17519</v>
       </c>
       <c r="D649" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12329,10 +12323,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>17320</v>
+        <v>17520</v>
       </c>
       <c r="D650" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12346,10 +12340,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>17321</v>
+        <v>17521</v>
       </c>
       <c r="D651" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12363,10 +12357,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>17322</v>
+        <v>17522</v>
       </c>
       <c r="D652" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12380,10 +12374,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>17323</v>
+        <v>17523</v>
       </c>
       <c r="D653" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12397,10 +12391,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>17324</v>
+        <v>17524</v>
       </c>
       <c r="D654" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12414,10 +12408,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>17325</v>
+        <v>17525</v>
       </c>
       <c r="D655" s="3">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12426,890 +12420,6 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="657" spans="1:8">
-      <c r="A657" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C657" s="6">
-        <v>17401</v>
-      </c>
-      <c r="D657" s="3">
-        <v>174</v>
-      </c>
-      <c r="E657" s="5">
-        <v>1</v>
-      </c>
-      <c r="F657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G657" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H657" s="3">
-        <v>20445</v>
-      </c>
-    </row>
-    <row r="658" spans="1:8">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-      <c r="C658" s="6">
-        <v>17402</v>
-      </c>
-      <c r="D658" s="3">
-        <v>174</v>
-      </c>
-      <c r="E658" s="5">
-        <v>1</v>
-      </c>
-      <c r="F658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G658" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H658" s="3">
-        <v>20446</v>
-      </c>
-    </row>
-    <row r="659" spans="3:8">
-      <c r="C659" s="6">
-        <v>17403</v>
-      </c>
-      <c r="D659" s="3">
-        <v>174</v>
-      </c>
-      <c r="E659" s="5">
-        <v>1</v>
-      </c>
-      <c r="F659" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G659" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H659" s="3">
-        <v>20447</v>
-      </c>
-    </row>
-    <row r="660" spans="3:8">
-      <c r="C660" s="6">
-        <v>17404</v>
-      </c>
-      <c r="D660" s="3">
-        <v>174</v>
-      </c>
-      <c r="E660" s="5">
-        <v>1</v>
-      </c>
-      <c r="F660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G660" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H660" s="3">
-        <v>20448</v>
-      </c>
-    </row>
-    <row r="661" spans="3:7">
-      <c r="C661" s="6">
-        <v>17405</v>
-      </c>
-      <c r="D661" s="3">
-        <v>174</v>
-      </c>
-      <c r="E661" s="3">
-        <v>1</v>
-      </c>
-      <c r="F661" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G661" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="662" spans="3:7">
-      <c r="C662" s="6">
-        <v>17406</v>
-      </c>
-      <c r="D662" s="3">
-        <v>174</v>
-      </c>
-      <c r="E662" s="5">
-        <v>1</v>
-      </c>
-      <c r="F662" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G662" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="663" spans="3:7">
-      <c r="C663" s="6">
-        <v>17407</v>
-      </c>
-      <c r="D663" s="3">
-        <v>174</v>
-      </c>
-      <c r="E663" s="5">
-        <v>1</v>
-      </c>
-      <c r="F663" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G663" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="664" spans="3:7">
-      <c r="C664" s="6">
-        <v>17408</v>
-      </c>
-      <c r="D664" s="3">
-        <v>174</v>
-      </c>
-      <c r="E664" s="5">
-        <v>1</v>
-      </c>
-      <c r="F664" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G664" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="665" spans="3:7">
-      <c r="C665" s="6">
-        <v>17409</v>
-      </c>
-      <c r="D665" s="3">
-        <v>174</v>
-      </c>
-      <c r="E665" s="3">
-        <v>1</v>
-      </c>
-      <c r="F665" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G665" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="666" spans="3:7">
-      <c r="C666" s="6">
-        <v>17410</v>
-      </c>
-      <c r="D666" s="3">
-        <v>174</v>
-      </c>
-      <c r="E666" s="5">
-        <v>1</v>
-      </c>
-      <c r="F666" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G666" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="667" spans="3:7">
-      <c r="C667" s="6">
-        <v>17411</v>
-      </c>
-      <c r="D667" s="3">
-        <v>174</v>
-      </c>
-      <c r="E667" s="5">
-        <v>1</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G667" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="668" spans="3:7">
-      <c r="C668" s="6">
-        <v>17412</v>
-      </c>
-      <c r="D668" s="3">
-        <v>174</v>
-      </c>
-      <c r="E668" s="5">
-        <v>1</v>
-      </c>
-      <c r="F668" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G668" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="669" spans="3:7">
-      <c r="C669" s="6">
-        <v>17413</v>
-      </c>
-      <c r="D669" s="3">
-        <v>174</v>
-      </c>
-      <c r="E669" s="3">
-        <v>1</v>
-      </c>
-      <c r="F669" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G669" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="670" spans="3:7">
-      <c r="C670" s="6">
-        <v>17414</v>
-      </c>
-      <c r="D670" s="3">
-        <v>174</v>
-      </c>
-      <c r="E670" s="5">
-        <v>1</v>
-      </c>
-      <c r="F670" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G670" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="671" spans="3:7">
-      <c r="C671" s="6">
-        <v>17415</v>
-      </c>
-      <c r="D671" s="3">
-        <v>174</v>
-      </c>
-      <c r="E671" s="5">
-        <v>1</v>
-      </c>
-      <c r="F671" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G671" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="672" spans="3:7">
-      <c r="C672" s="6">
-        <v>17416</v>
-      </c>
-      <c r="D672" s="3">
-        <v>174</v>
-      </c>
-      <c r="E672" s="5">
-        <v>1</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G672" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="673" spans="3:7">
-      <c r="C673" s="6">
-        <v>17417</v>
-      </c>
-      <c r="D673" s="3">
-        <v>174</v>
-      </c>
-      <c r="E673" s="3">
-        <v>1</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G673" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="674" spans="3:7">
-      <c r="C674" s="6">
-        <v>17418</v>
-      </c>
-      <c r="D674" s="3">
-        <v>174</v>
-      </c>
-      <c r="E674" s="5">
-        <v>1</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G674" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="675" spans="3:7">
-      <c r="C675" s="6">
-        <v>17419</v>
-      </c>
-      <c r="D675" s="3">
-        <v>174</v>
-      </c>
-      <c r="E675" s="5">
-        <v>1</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G675" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="676" spans="3:7">
-      <c r="C676" s="6">
-        <v>17420</v>
-      </c>
-      <c r="D676" s="3">
-        <v>174</v>
-      </c>
-      <c r="E676" s="5">
-        <v>1</v>
-      </c>
-      <c r="F676" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G676" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="677" spans="3:7">
-      <c r="C677" s="6">
-        <v>17421</v>
-      </c>
-      <c r="D677" s="3">
-        <v>174</v>
-      </c>
-      <c r="E677" s="3">
-        <v>1</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G677" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="678" spans="3:7">
-      <c r="C678" s="6">
-        <v>17422</v>
-      </c>
-      <c r="D678" s="3">
-        <v>174</v>
-      </c>
-      <c r="E678" s="5">
-        <v>1</v>
-      </c>
-      <c r="F678" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G678" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="679" spans="3:7">
-      <c r="C679" s="6">
-        <v>17423</v>
-      </c>
-      <c r="D679" s="3">
-        <v>174</v>
-      </c>
-      <c r="E679" s="5">
-        <v>1</v>
-      </c>
-      <c r="F679" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G679" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="680" spans="3:7">
-      <c r="C680" s="6">
-        <v>17424</v>
-      </c>
-      <c r="D680" s="3">
-        <v>174</v>
-      </c>
-      <c r="E680" s="5">
-        <v>1</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G680" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="681" spans="3:7">
-      <c r="C681" s="6">
-        <v>17425</v>
-      </c>
-      <c r="D681" s="3">
-        <v>174</v>
-      </c>
-      <c r="E681" s="3">
-        <v>1</v>
-      </c>
-      <c r="F681" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>17501</v>
-      </c>
-      <c r="D683" s="3">
-        <v>175</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20455</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>17502</v>
-      </c>
-      <c r="D684" s="3">
-        <v>175</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20456</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>17503</v>
-      </c>
-      <c r="D685" s="3">
-        <v>175</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20457</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>17504</v>
-      </c>
-      <c r="D686" s="3">
-        <v>175</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20458</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>17505</v>
-      </c>
-      <c r="D687" s="3">
-        <v>175</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>17506</v>
-      </c>
-      <c r="D688" s="3">
-        <v>175</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>17507</v>
-      </c>
-      <c r="D689" s="3">
-        <v>175</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>17508</v>
-      </c>
-      <c r="D690" s="3">
-        <v>175</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>17509</v>
-      </c>
-      <c r="D691" s="3">
-        <v>175</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>17510</v>
-      </c>
-      <c r="D692" s="3">
-        <v>175</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>17511</v>
-      </c>
-      <c r="D693" s="3">
-        <v>175</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>17512</v>
-      </c>
-      <c r="D694" s="3">
-        <v>175</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>17513</v>
-      </c>
-      <c r="D695" s="3">
-        <v>175</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>17514</v>
-      </c>
-      <c r="D696" s="3">
-        <v>175</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>17515</v>
-      </c>
-      <c r="D697" s="3">
-        <v>175</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>17516</v>
-      </c>
-      <c r="D698" s="3">
-        <v>175</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>17517</v>
-      </c>
-      <c r="D699" s="3">
-        <v>175</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>17518</v>
-      </c>
-      <c r="D700" s="3">
-        <v>175</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>17519</v>
-      </c>
-      <c r="D701" s="3">
-        <v>175</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>17520</v>
-      </c>
-      <c r="D702" s="3">
-        <v>175</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>17521</v>
-      </c>
-      <c r="D703" s="3">
-        <v>175</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>17522</v>
-      </c>
-      <c r="D704" s="3">
-        <v>175</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>17523</v>
-      </c>
-      <c r="D705" s="3">
-        <v>175</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>17524</v>
-      </c>
-      <c r="D706" s="3">
-        <v>175</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>17525</v>
-      </c>
-      <c r="D707" s="3">
-        <v>175</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +12540,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +12558,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +12576,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +12594,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +12614,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +12712,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>#先锋175星界回廊</t>
+  </si>
+  <si>
+    <t>#先锋176</t>
   </si>
   <si>
     <t>Center</t>
@@ -1257,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O655"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12420,6 +12423,448 @@
         <v>42</v>
       </c>
       <c r="G655" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="657" spans="1:8">
+      <c r="A657" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C657" s="6">
+        <v>17601</v>
+      </c>
+      <c r="D657" s="3">
+        <v>176</v>
+      </c>
+      <c r="E657" s="5">
+        <v>1</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G657" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H657" s="3">
+        <v>20505</v>
+      </c>
+    </row>
+    <row r="658" spans="1:8">
+      <c r="A658" s="1"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="6">
+        <v>17602</v>
+      </c>
+      <c r="D658" s="3">
+        <v>176</v>
+      </c>
+      <c r="E658" s="5">
+        <v>1</v>
+      </c>
+      <c r="F658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G658" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H658" s="3">
+        <v>20506</v>
+      </c>
+    </row>
+    <row r="659" spans="3:8">
+      <c r="C659" s="6">
+        <v>17603</v>
+      </c>
+      <c r="D659" s="3">
+        <v>176</v>
+      </c>
+      <c r="E659" s="5">
+        <v>1</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H659" s="3">
+        <v>20507</v>
+      </c>
+    </row>
+    <row r="660" spans="3:8">
+      <c r="C660" s="6">
+        <v>17604</v>
+      </c>
+      <c r="D660" s="3">
+        <v>176</v>
+      </c>
+      <c r="E660" s="5">
+        <v>1</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H660" s="3">
+        <v>20508</v>
+      </c>
+    </row>
+    <row r="661" spans="3:7">
+      <c r="C661" s="6">
+        <v>17605</v>
+      </c>
+      <c r="D661" s="3">
+        <v>176</v>
+      </c>
+      <c r="E661" s="3">
+        <v>1</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="662" spans="3:7">
+      <c r="C662" s="6">
+        <v>17606</v>
+      </c>
+      <c r="D662" s="3">
+        <v>176</v>
+      </c>
+      <c r="E662" s="5">
+        <v>1</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="663" spans="3:7">
+      <c r="C663" s="6">
+        <v>17607</v>
+      </c>
+      <c r="D663" s="3">
+        <v>176</v>
+      </c>
+      <c r="E663" s="5">
+        <v>1</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="664" spans="3:7">
+      <c r="C664" s="6">
+        <v>17608</v>
+      </c>
+      <c r="D664" s="3">
+        <v>176</v>
+      </c>
+      <c r="E664" s="5">
+        <v>1</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G664" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="3:7">
+      <c r="C665" s="6">
+        <v>17609</v>
+      </c>
+      <c r="D665" s="3">
+        <v>176</v>
+      </c>
+      <c r="E665" s="3">
+        <v>1</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="666" spans="3:7">
+      <c r="C666" s="6">
+        <v>17610</v>
+      </c>
+      <c r="D666" s="3">
+        <v>176</v>
+      </c>
+      <c r="E666" s="5">
+        <v>1</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="3:7">
+      <c r="C667" s="6">
+        <v>17611</v>
+      </c>
+      <c r="D667" s="3">
+        <v>176</v>
+      </c>
+      <c r="E667" s="5">
+        <v>1</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="668" spans="3:7">
+      <c r="C668" s="6">
+        <v>17612</v>
+      </c>
+      <c r="D668" s="3">
+        <v>176</v>
+      </c>
+      <c r="E668" s="5">
+        <v>1</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="669" spans="3:7">
+      <c r="C669" s="6">
+        <v>17613</v>
+      </c>
+      <c r="D669" s="3">
+        <v>176</v>
+      </c>
+      <c r="E669" s="3">
+        <v>1</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="670" spans="3:7">
+      <c r="C670" s="6">
+        <v>17614</v>
+      </c>
+      <c r="D670" s="3">
+        <v>176</v>
+      </c>
+      <c r="E670" s="5">
+        <v>1</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G670" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="671" spans="3:7">
+      <c r="C671" s="6">
+        <v>17615</v>
+      </c>
+      <c r="D671" s="3">
+        <v>176</v>
+      </c>
+      <c r="E671" s="5">
+        <v>1</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="672" spans="3:7">
+      <c r="C672" s="6">
+        <v>17616</v>
+      </c>
+      <c r="D672" s="3">
+        <v>176</v>
+      </c>
+      <c r="E672" s="5">
+        <v>1</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="673" spans="3:7">
+      <c r="C673" s="6">
+        <v>17617</v>
+      </c>
+      <c r="D673" s="3">
+        <v>176</v>
+      </c>
+      <c r="E673" s="3">
+        <v>1</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="674" spans="3:7">
+      <c r="C674" s="6">
+        <v>17618</v>
+      </c>
+      <c r="D674" s="3">
+        <v>176</v>
+      </c>
+      <c r="E674" s="5">
+        <v>1</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="675" spans="3:7">
+      <c r="C675" s="6">
+        <v>17619</v>
+      </c>
+      <c r="D675" s="3">
+        <v>176</v>
+      </c>
+      <c r="E675" s="5">
+        <v>1</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="676" spans="3:7">
+      <c r="C676" s="6">
+        <v>17620</v>
+      </c>
+      <c r="D676" s="3">
+        <v>176</v>
+      </c>
+      <c r="E676" s="5">
+        <v>1</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="677" spans="3:7">
+      <c r="C677" s="6">
+        <v>17621</v>
+      </c>
+      <c r="D677" s="3">
+        <v>176</v>
+      </c>
+      <c r="E677" s="3">
+        <v>1</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="678" spans="3:7">
+      <c r="C678" s="6">
+        <v>17622</v>
+      </c>
+      <c r="D678" s="3">
+        <v>176</v>
+      </c>
+      <c r="E678" s="5">
+        <v>1</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="679" spans="3:7">
+      <c r="C679" s="6">
+        <v>17623</v>
+      </c>
+      <c r="D679" s="3">
+        <v>176</v>
+      </c>
+      <c r="E679" s="5">
+        <v>1</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="680" spans="3:7">
+      <c r="C680" s="6">
+        <v>17624</v>
+      </c>
+      <c r="D680" s="3">
+        <v>176</v>
+      </c>
+      <c r="E680" s="5">
+        <v>1</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G680" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="681" spans="3:7">
+      <c r="C681" s="6">
+        <v>17625</v>
+      </c>
+      <c r="D681" s="3">
+        <v>176</v>
+      </c>
+      <c r="E681" s="3">
+        <v>1</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G681" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12540,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -12558,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -12576,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -12594,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -12614,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12712,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -232,7 +232,10 @@
     <t>#先锋175星界回廊</t>
   </si>
   <si>
-    <t>#先锋176</t>
+    <t>#先锋176普天同庆</t>
+  </si>
+  <si>
+    <t>#先锋177长安旧梦</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>17701</v>
+      </c>
+      <c r="D683" s="3">
+        <v>177</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20545</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>17702</v>
+      </c>
+      <c r="D684" s="3">
+        <v>177</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20546</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>17703</v>
+      </c>
+      <c r="D685" s="3">
+        <v>177</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20547</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>17704</v>
+      </c>
+      <c r="D686" s="3">
+        <v>177</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20548</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>17705</v>
+      </c>
+      <c r="D687" s="3">
+        <v>177</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>17706</v>
+      </c>
+      <c r="D688" s="3">
+        <v>177</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>17707</v>
+      </c>
+      <c r="D689" s="3">
+        <v>177</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>17708</v>
+      </c>
+      <c r="D690" s="3">
+        <v>177</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>17709</v>
+      </c>
+      <c r="D691" s="3">
+        <v>177</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>17710</v>
+      </c>
+      <c r="D692" s="3">
+        <v>177</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>17711</v>
+      </c>
+      <c r="D693" s="3">
+        <v>177</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>17712</v>
+      </c>
+      <c r="D694" s="3">
+        <v>177</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>17713</v>
+      </c>
+      <c r="D695" s="3">
+        <v>177</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>17714</v>
+      </c>
+      <c r="D696" s="3">
+        <v>177</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>17715</v>
+      </c>
+      <c r="D697" s="3">
+        <v>177</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>17716</v>
+      </c>
+      <c r="D698" s="3">
+        <v>177</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>17717</v>
+      </c>
+      <c r="D699" s="3">
+        <v>177</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>17718</v>
+      </c>
+      <c r="D700" s="3">
+        <v>177</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>17719</v>
+      </c>
+      <c r="D701" s="3">
+        <v>177</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>17720</v>
+      </c>
+      <c r="D702" s="3">
+        <v>177</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>17721</v>
+      </c>
+      <c r="D703" s="3">
+        <v>177</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>17722</v>
+      </c>
+      <c r="D704" s="3">
+        <v>177</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>17723</v>
+      </c>
+      <c r="D705" s="3">
+        <v>177</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>17724</v>
+      </c>
+      <c r="D706" s="3">
+        <v>177</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>17725</v>
+      </c>
+      <c r="D707" s="3">
+        <v>177</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋177长安旧梦</t>
+  </si>
+  <si>
+    <t>#先锋178风暴之地</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>17801</v>
+      </c>
+      <c r="D709" s="3">
+        <v>178</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20565</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>17802</v>
+      </c>
+      <c r="D710" s="3">
+        <v>178</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20566</v>
+      </c>
+    </row>
+    <row r="711" spans="3:8">
+      <c r="C711" s="6">
+        <v>17803</v>
+      </c>
+      <c r="D711" s="3">
+        <v>178</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20567</v>
+      </c>
+    </row>
+    <row r="712" spans="3:8">
+      <c r="C712" s="6">
+        <v>17804</v>
+      </c>
+      <c r="D712" s="3">
+        <v>178</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20568</v>
+      </c>
+    </row>
+    <row r="713" spans="3:7">
+      <c r="C713" s="6">
+        <v>17805</v>
+      </c>
+      <c r="D713" s="3">
+        <v>178</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="3:7">
+      <c r="C714" s="6">
+        <v>17806</v>
+      </c>
+      <c r="D714" s="3">
+        <v>178</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="3:7">
+      <c r="C715" s="6">
+        <v>17807</v>
+      </c>
+      <c r="D715" s="3">
+        <v>178</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="3:7">
+      <c r="C716" s="6">
+        <v>17808</v>
+      </c>
+      <c r="D716" s="3">
+        <v>178</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="3:7">
+      <c r="C717" s="6">
+        <v>17809</v>
+      </c>
+      <c r="D717" s="3">
+        <v>178</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="3:7">
+      <c r="C718" s="6">
+        <v>17810</v>
+      </c>
+      <c r="D718" s="3">
+        <v>178</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="3:7">
+      <c r="C719" s="6">
+        <v>17811</v>
+      </c>
+      <c r="D719" s="3">
+        <v>178</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="3:7">
+      <c r="C720" s="6">
+        <v>17812</v>
+      </c>
+      <c r="D720" s="3">
+        <v>178</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>17813</v>
+      </c>
+      <c r="D721" s="3">
+        <v>178</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>17814</v>
+      </c>
+      <c r="D722" s="3">
+        <v>178</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>17815</v>
+      </c>
+      <c r="D723" s="3">
+        <v>178</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>17816</v>
+      </c>
+      <c r="D724" s="3">
+        <v>178</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>17817</v>
+      </c>
+      <c r="D725" s="3">
+        <v>178</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>17818</v>
+      </c>
+      <c r="D726" s="3">
+        <v>178</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>17819</v>
+      </c>
+      <c r="D727" s="3">
+        <v>178</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>17820</v>
+      </c>
+      <c r="D728" s="3">
+        <v>178</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>17821</v>
+      </c>
+      <c r="D729" s="3">
+        <v>178</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>17822</v>
+      </c>
+      <c r="D730" s="3">
+        <v>178</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>17823</v>
+      </c>
+      <c r="D731" s="3">
+        <v>178</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>17824</v>
+      </c>
+      <c r="D732" s="3">
+        <v>178</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>17825</v>
+      </c>
+      <c r="D733" s="3">
+        <v>178</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -205,13 +205,7 @@
     <t>#先锋155雷霆万钧</t>
   </si>
   <si>
-    <t>#先锋159星辰之巅</t>
-  </si>
-  <si>
     <t>#先锋163破晓战歌</t>
-  </si>
-  <si>
-    <t>#先锋165繁花谷</t>
   </si>
   <si>
     <t>#先锋167青云之巅</t>
@@ -221,9 +215,6 @@
   </si>
   <si>
     <t>#先锋172星辰殿堂</t>
-  </si>
-  <si>
-    <t>#先锋173童话森林</t>
   </si>
   <si>
     <t>#先锋174龙息之谷</t>
@@ -239,6 +230,9 @@
   </si>
   <si>
     <t>#先锋178风暴之地</t>
+  </si>
+  <si>
+    <t>#先锋179巨刃降临</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -8459,10 +8453,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>15901</v>
+        <v>16301</v>
       </c>
       <c r="D423" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8474,17 +8468,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20405</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>15902</v>
+        <v>16302</v>
       </c>
       <c r="D424" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8496,15 +8490,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20406</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="425" spans="3:8">
       <c r="C425" s="6">
-        <v>15903</v>
+        <v>16303</v>
       </c>
       <c r="D425" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8516,15 +8510,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20407</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="426" spans="3:8">
       <c r="C426" s="6">
-        <v>15904</v>
+        <v>16304</v>
       </c>
       <c r="D426" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8536,15 +8530,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20408</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="427" spans="3:7">
       <c r="C427" s="6">
-        <v>15905</v>
+        <v>16305</v>
       </c>
       <c r="D427" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8558,10 +8552,10 @@
     </row>
     <row r="428" spans="3:7">
       <c r="C428" s="6">
-        <v>15906</v>
+        <v>16306</v>
       </c>
       <c r="D428" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8575,10 +8569,10 @@
     </row>
     <row r="429" spans="3:7">
       <c r="C429" s="6">
-        <v>15907</v>
+        <v>16307</v>
       </c>
       <c r="D429" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8592,10 +8586,10 @@
     </row>
     <row r="430" spans="3:7">
       <c r="C430" s="6">
-        <v>15908</v>
+        <v>16308</v>
       </c>
       <c r="D430" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8609,10 +8603,10 @@
     </row>
     <row r="431" spans="3:7">
       <c r="C431" s="6">
-        <v>15909</v>
+        <v>16309</v>
       </c>
       <c r="D431" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8626,10 +8620,10 @@
     </row>
     <row r="432" spans="3:7">
       <c r="C432" s="6">
-        <v>15910</v>
+        <v>16310</v>
       </c>
       <c r="D432" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8643,10 +8637,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>15911</v>
+        <v>16311</v>
       </c>
       <c r="D433" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8660,10 +8654,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>15912</v>
+        <v>16312</v>
       </c>
       <c r="D434" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8677,10 +8671,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>15913</v>
+        <v>16313</v>
       </c>
       <c r="D435" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8694,10 +8688,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>15914</v>
+        <v>16314</v>
       </c>
       <c r="D436" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8711,10 +8705,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>15915</v>
+        <v>16315</v>
       </c>
       <c r="D437" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8728,10 +8722,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>15916</v>
+        <v>16316</v>
       </c>
       <c r="D438" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8745,10 +8739,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>15917</v>
+        <v>16317</v>
       </c>
       <c r="D439" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8762,10 +8756,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>15918</v>
+        <v>16318</v>
       </c>
       <c r="D440" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8779,10 +8773,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>15919</v>
+        <v>16319</v>
       </c>
       <c r="D441" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8796,10 +8790,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>15920</v>
+        <v>16320</v>
       </c>
       <c r="D442" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8813,10 +8807,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>15921</v>
+        <v>16321</v>
       </c>
       <c r="D443" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8830,10 +8824,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>15922</v>
+        <v>16322</v>
       </c>
       <c r="D444" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8847,10 +8841,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>15923</v>
+        <v>16323</v>
       </c>
       <c r="D445" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8864,10 +8858,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>15924</v>
+        <v>16324</v>
       </c>
       <c r="D446" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8881,10 +8875,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>15925</v>
+        <v>16325</v>
       </c>
       <c r="D447" s="3">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8901,10 +8895,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>16301</v>
+        <v>16701</v>
       </c>
       <c r="D449" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8916,17 +8910,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20525</v>
+        <v>20555</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>16302</v>
+        <v>16702</v>
       </c>
       <c r="D450" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8938,15 +8932,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20526</v>
+        <v>20556</v>
       </c>
     </row>
     <row r="451" spans="3:8">
       <c r="C451" s="6">
-        <v>16303</v>
+        <v>16703</v>
       </c>
       <c r="D451" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8958,15 +8952,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20527</v>
+        <v>20557</v>
       </c>
     </row>
     <row r="452" spans="3:8">
       <c r="C452" s="6">
-        <v>16304</v>
+        <v>16704</v>
       </c>
       <c r="D452" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8978,15 +8972,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20528</v>
+        <v>20558</v>
       </c>
     </row>
     <row r="453" spans="3:7">
       <c r="C453" s="6">
-        <v>16305</v>
+        <v>16705</v>
       </c>
       <c r="D453" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9000,10 +8994,10 @@
     </row>
     <row r="454" spans="3:7">
       <c r="C454" s="6">
-        <v>16306</v>
+        <v>16706</v>
       </c>
       <c r="D454" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9017,10 +9011,10 @@
     </row>
     <row r="455" spans="3:7">
       <c r="C455" s="6">
-        <v>16307</v>
+        <v>16707</v>
       </c>
       <c r="D455" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9034,10 +9028,10 @@
     </row>
     <row r="456" spans="3:7">
       <c r="C456" s="6">
-        <v>16308</v>
+        <v>16708</v>
       </c>
       <c r="D456" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9051,10 +9045,10 @@
     </row>
     <row r="457" spans="3:7">
       <c r="C457" s="6">
-        <v>16309</v>
+        <v>16709</v>
       </c>
       <c r="D457" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9068,10 +9062,10 @@
     </row>
     <row r="458" spans="3:7">
       <c r="C458" s="6">
-        <v>16310</v>
+        <v>16710</v>
       </c>
       <c r="D458" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9085,10 +9079,10 @@
     </row>
     <row r="459" spans="3:7">
       <c r="C459" s="6">
-        <v>16311</v>
+        <v>16711</v>
       </c>
       <c r="D459" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9102,10 +9096,10 @@
     </row>
     <row r="460" spans="3:7">
       <c r="C460" s="6">
-        <v>16312</v>
+        <v>16712</v>
       </c>
       <c r="D460" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9119,10 +9113,10 @@
     </row>
     <row r="461" spans="3:7">
       <c r="C461" s="6">
-        <v>16313</v>
+        <v>16713</v>
       </c>
       <c r="D461" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9136,10 +9130,10 @@
     </row>
     <row r="462" spans="3:7">
       <c r="C462" s="6">
-        <v>16314</v>
+        <v>16714</v>
       </c>
       <c r="D462" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9153,10 +9147,10 @@
     </row>
     <row r="463" spans="3:7">
       <c r="C463" s="6">
-        <v>16315</v>
+        <v>16715</v>
       </c>
       <c r="D463" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9170,10 +9164,10 @@
     </row>
     <row r="464" spans="3:7">
       <c r="C464" s="6">
-        <v>16316</v>
+        <v>16716</v>
       </c>
       <c r="D464" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9187,10 +9181,10 @@
     </row>
     <row r="465" spans="3:7">
       <c r="C465" s="6">
-        <v>16317</v>
+        <v>16717</v>
       </c>
       <c r="D465" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9204,10 +9198,10 @@
     </row>
     <row r="466" spans="3:7">
       <c r="C466" s="6">
-        <v>16318</v>
+        <v>16718</v>
       </c>
       <c r="D466" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9221,10 +9215,10 @@
     </row>
     <row r="467" spans="3:7">
       <c r="C467" s="6">
-        <v>16319</v>
+        <v>16719</v>
       </c>
       <c r="D467" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9238,10 +9232,10 @@
     </row>
     <row r="468" spans="3:7">
       <c r="C468" s="6">
-        <v>16320</v>
+        <v>16720</v>
       </c>
       <c r="D468" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9255,10 +9249,10 @@
     </row>
     <row r="469" spans="3:7">
       <c r="C469" s="6">
-        <v>16321</v>
+        <v>16721</v>
       </c>
       <c r="D469" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9272,10 +9266,10 @@
     </row>
     <row r="470" spans="3:7">
       <c r="C470" s="6">
-        <v>16322</v>
+        <v>16722</v>
       </c>
       <c r="D470" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9289,10 +9283,10 @@
     </row>
     <row r="471" spans="3:7">
       <c r="C471" s="6">
-        <v>16323</v>
+        <v>16723</v>
       </c>
       <c r="D471" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9306,10 +9300,10 @@
     </row>
     <row r="472" spans="3:7">
       <c r="C472" s="6">
-        <v>16324</v>
+        <v>16724</v>
       </c>
       <c r="D472" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9323,10 +9317,10 @@
     </row>
     <row r="473" spans="3:7">
       <c r="C473" s="6">
-        <v>16325</v>
+        <v>16725</v>
       </c>
       <c r="D473" s="3">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9343,10 +9337,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>16501</v>
+        <v>16901</v>
       </c>
       <c r="D475" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9358,17 +9352,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20375</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>16502</v>
+        <v>16902</v>
       </c>
       <c r="D476" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9380,15 +9374,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20376</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="477" spans="3:8">
       <c r="C477" s="6">
-        <v>16503</v>
+        <v>16903</v>
       </c>
       <c r="D477" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9400,15 +9394,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20377</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="478" spans="3:8">
       <c r="C478" s="6">
-        <v>16504</v>
+        <v>16904</v>
       </c>
       <c r="D478" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9420,15 +9414,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20378</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="479" spans="3:7">
       <c r="C479" s="6">
-        <v>16505</v>
+        <v>16905</v>
       </c>
       <c r="D479" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9442,10 +9436,10 @@
     </row>
     <row r="480" spans="3:7">
       <c r="C480" s="6">
-        <v>16506</v>
+        <v>16906</v>
       </c>
       <c r="D480" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9459,10 +9453,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>16507</v>
+        <v>16907</v>
       </c>
       <c r="D481" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9476,10 +9470,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>16508</v>
+        <v>16908</v>
       </c>
       <c r="D482" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9493,10 +9487,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>16509</v>
+        <v>16909</v>
       </c>
       <c r="D483" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9510,10 +9504,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>16510</v>
+        <v>16910</v>
       </c>
       <c r="D484" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9527,10 +9521,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>16511</v>
+        <v>16911</v>
       </c>
       <c r="D485" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9544,10 +9538,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>16512</v>
+        <v>16912</v>
       </c>
       <c r="D486" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9561,10 +9555,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>16513</v>
+        <v>16913</v>
       </c>
       <c r="D487" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9578,10 +9572,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>16514</v>
+        <v>16914</v>
       </c>
       <c r="D488" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9595,10 +9589,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>16515</v>
+        <v>16915</v>
       </c>
       <c r="D489" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9612,10 +9606,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>16516</v>
+        <v>16916</v>
       </c>
       <c r="D490" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9629,10 +9623,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>16517</v>
+        <v>16917</v>
       </c>
       <c r="D491" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9646,10 +9640,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>16518</v>
+        <v>16918</v>
       </c>
       <c r="D492" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9663,10 +9657,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>16519</v>
+        <v>16919</v>
       </c>
       <c r="D493" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9680,10 +9674,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>16520</v>
+        <v>16920</v>
       </c>
       <c r="D494" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9697,10 +9691,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>16521</v>
+        <v>16921</v>
       </c>
       <c r="D495" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9714,10 +9708,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>16522</v>
+        <v>16922</v>
       </c>
       <c r="D496" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9731,10 +9725,10 @@
     </row>
     <row r="497" spans="3:7">
       <c r="C497" s="6">
-        <v>16523</v>
+        <v>16923</v>
       </c>
       <c r="D497" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9748,10 +9742,10 @@
     </row>
     <row r="498" spans="3:7">
       <c r="C498" s="6">
-        <v>16524</v>
+        <v>16924</v>
       </c>
       <c r="D498" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9765,10 +9759,10 @@
     </row>
     <row r="499" spans="3:7">
       <c r="C499" s="6">
-        <v>16525</v>
+        <v>16925</v>
       </c>
       <c r="D499" s="3">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9785,10 +9779,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>16701</v>
+        <v>17201</v>
       </c>
       <c r="D501" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9800,17 +9794,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20555</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>16702</v>
+        <v>17202</v>
       </c>
       <c r="D502" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9822,15 +9816,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20556</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="503" spans="3:8">
       <c r="C503" s="6">
-        <v>16703</v>
+        <v>17203</v>
       </c>
       <c r="D503" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9842,15 +9836,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20557</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="504" spans="3:8">
       <c r="C504" s="6">
-        <v>16704</v>
+        <v>17204</v>
       </c>
       <c r="D504" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9862,15 +9856,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20558</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="505" spans="3:7">
       <c r="C505" s="6">
-        <v>16705</v>
+        <v>17205</v>
       </c>
       <c r="D505" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9884,10 +9878,10 @@
     </row>
     <row r="506" spans="3:7">
       <c r="C506" s="6">
-        <v>16706</v>
+        <v>17206</v>
       </c>
       <c r="D506" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9901,10 +9895,10 @@
     </row>
     <row r="507" spans="3:7">
       <c r="C507" s="6">
-        <v>16707</v>
+        <v>17207</v>
       </c>
       <c r="D507" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9918,10 +9912,10 @@
     </row>
     <row r="508" spans="3:7">
       <c r="C508" s="6">
-        <v>16708</v>
+        <v>17208</v>
       </c>
       <c r="D508" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9935,10 +9929,10 @@
     </row>
     <row r="509" spans="3:7">
       <c r="C509" s="6">
-        <v>16709</v>
+        <v>17209</v>
       </c>
       <c r="D509" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9952,10 +9946,10 @@
     </row>
     <row r="510" spans="3:7">
       <c r="C510" s="6">
-        <v>16710</v>
+        <v>17210</v>
       </c>
       <c r="D510" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9969,10 +9963,10 @@
     </row>
     <row r="511" spans="3:7">
       <c r="C511" s="6">
-        <v>16711</v>
+        <v>17211</v>
       </c>
       <c r="D511" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9986,10 +9980,10 @@
     </row>
     <row r="512" spans="3:7">
       <c r="C512" s="6">
-        <v>16712</v>
+        <v>17212</v>
       </c>
       <c r="D512" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10003,10 +9997,10 @@
     </row>
     <row r="513" spans="3:7">
       <c r="C513" s="6">
-        <v>16713</v>
+        <v>17213</v>
       </c>
       <c r="D513" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10020,10 +10014,10 @@
     </row>
     <row r="514" spans="3:7">
       <c r="C514" s="6">
-        <v>16714</v>
+        <v>17214</v>
       </c>
       <c r="D514" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10037,10 +10031,10 @@
     </row>
     <row r="515" spans="3:7">
       <c r="C515" s="6">
-        <v>16715</v>
+        <v>17215</v>
       </c>
       <c r="D515" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10054,10 +10048,10 @@
     </row>
     <row r="516" spans="3:7">
       <c r="C516" s="6">
-        <v>16716</v>
+        <v>17216</v>
       </c>
       <c r="D516" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10071,10 +10065,10 @@
     </row>
     <row r="517" spans="3:7">
       <c r="C517" s="6">
-        <v>16717</v>
+        <v>17217</v>
       </c>
       <c r="D517" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10088,10 +10082,10 @@
     </row>
     <row r="518" spans="3:7">
       <c r="C518" s="6">
-        <v>16718</v>
+        <v>17218</v>
       </c>
       <c r="D518" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10105,10 +10099,10 @@
     </row>
     <row r="519" spans="3:7">
       <c r="C519" s="6">
-        <v>16719</v>
+        <v>17219</v>
       </c>
       <c r="D519" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10122,10 +10116,10 @@
     </row>
     <row r="520" spans="3:7">
       <c r="C520" s="6">
-        <v>16720</v>
+        <v>17220</v>
       </c>
       <c r="D520" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10139,10 +10133,10 @@
     </row>
     <row r="521" spans="3:7">
       <c r="C521" s="6">
-        <v>16721</v>
+        <v>17221</v>
       </c>
       <c r="D521" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10156,10 +10150,10 @@
     </row>
     <row r="522" spans="3:7">
       <c r="C522" s="6">
-        <v>16722</v>
+        <v>17222</v>
       </c>
       <c r="D522" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10173,10 +10167,10 @@
     </row>
     <row r="523" spans="3:7">
       <c r="C523" s="6">
-        <v>16723</v>
+        <v>17223</v>
       </c>
       <c r="D523" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10190,10 +10184,10 @@
     </row>
     <row r="524" spans="3:7">
       <c r="C524" s="6">
-        <v>16724</v>
+        <v>17224</v>
       </c>
       <c r="D524" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10207,10 +10201,10 @@
     </row>
     <row r="525" spans="3:7">
       <c r="C525" s="6">
-        <v>16725</v>
+        <v>17225</v>
       </c>
       <c r="D525" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10227,10 +10221,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>16901</v>
+        <v>17401</v>
       </c>
       <c r="D527" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10242,17 +10236,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20515</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>16902</v>
+        <v>17402</v>
       </c>
       <c r="D528" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10264,15 +10258,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20516</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>16903</v>
+        <v>17403</v>
       </c>
       <c r="D529" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10284,15 +10278,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20517</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>16904</v>
+        <v>17404</v>
       </c>
       <c r="D530" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10304,15 +10298,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20518</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="531" spans="3:7">
       <c r="C531" s="6">
-        <v>16905</v>
+        <v>17405</v>
       </c>
       <c r="D531" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10326,10 +10320,10 @@
     </row>
     <row r="532" spans="3:7">
       <c r="C532" s="6">
-        <v>16906</v>
+        <v>17406</v>
       </c>
       <c r="D532" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10343,10 +10337,10 @@
     </row>
     <row r="533" spans="3:7">
       <c r="C533" s="6">
-        <v>16907</v>
+        <v>17407</v>
       </c>
       <c r="D533" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10360,10 +10354,10 @@
     </row>
     <row r="534" spans="3:7">
       <c r="C534" s="6">
-        <v>16908</v>
+        <v>17408</v>
       </c>
       <c r="D534" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10377,10 +10371,10 @@
     </row>
     <row r="535" spans="3:7">
       <c r="C535" s="6">
-        <v>16909</v>
+        <v>17409</v>
       </c>
       <c r="D535" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10394,10 +10388,10 @@
     </row>
     <row r="536" spans="3:7">
       <c r="C536" s="6">
-        <v>16910</v>
+        <v>17410</v>
       </c>
       <c r="D536" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10411,10 +10405,10 @@
     </row>
     <row r="537" spans="3:7">
       <c r="C537" s="6">
-        <v>16911</v>
+        <v>17411</v>
       </c>
       <c r="D537" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10428,10 +10422,10 @@
     </row>
     <row r="538" spans="3:7">
       <c r="C538" s="6">
-        <v>16912</v>
+        <v>17412</v>
       </c>
       <c r="D538" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10445,10 +10439,10 @@
     </row>
     <row r="539" spans="3:7">
       <c r="C539" s="6">
-        <v>16913</v>
+        <v>17413</v>
       </c>
       <c r="D539" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10462,10 +10456,10 @@
     </row>
     <row r="540" spans="3:7">
       <c r="C540" s="6">
-        <v>16914</v>
+        <v>17414</v>
       </c>
       <c r="D540" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10479,10 +10473,10 @@
     </row>
     <row r="541" spans="3:7">
       <c r="C541" s="6">
-        <v>16915</v>
+        <v>17415</v>
       </c>
       <c r="D541" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10496,10 +10490,10 @@
     </row>
     <row r="542" spans="3:7">
       <c r="C542" s="6">
-        <v>16916</v>
+        <v>17416</v>
       </c>
       <c r="D542" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10513,10 +10507,10 @@
     </row>
     <row r="543" spans="3:7">
       <c r="C543" s="6">
-        <v>16917</v>
+        <v>17417</v>
       </c>
       <c r="D543" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10530,10 +10524,10 @@
     </row>
     <row r="544" spans="3:7">
       <c r="C544" s="6">
-        <v>16918</v>
+        <v>17418</v>
       </c>
       <c r="D544" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10547,10 +10541,10 @@
     </row>
     <row r="545" spans="3:7">
       <c r="C545" s="6">
-        <v>16919</v>
+        <v>17419</v>
       </c>
       <c r="D545" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10564,10 +10558,10 @@
     </row>
     <row r="546" spans="3:7">
       <c r="C546" s="6">
-        <v>16920</v>
+        <v>17420</v>
       </c>
       <c r="D546" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10581,10 +10575,10 @@
     </row>
     <row r="547" spans="3:7">
       <c r="C547" s="6">
-        <v>16921</v>
+        <v>17421</v>
       </c>
       <c r="D547" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10598,10 +10592,10 @@
     </row>
     <row r="548" spans="3:7">
       <c r="C548" s="6">
-        <v>16922</v>
+        <v>17422</v>
       </c>
       <c r="D548" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10615,10 +10609,10 @@
     </row>
     <row r="549" spans="3:7">
       <c r="C549" s="6">
-        <v>16923</v>
+        <v>17423</v>
       </c>
       <c r="D549" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10632,10 +10626,10 @@
     </row>
     <row r="550" spans="3:7">
       <c r="C550" s="6">
-        <v>16924</v>
+        <v>17424</v>
       </c>
       <c r="D550" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10649,10 +10643,10 @@
     </row>
     <row r="551" spans="3:7">
       <c r="C551" s="6">
-        <v>16925</v>
+        <v>17425</v>
       </c>
       <c r="D551" s="3">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10669,10 +10663,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>17201</v>
+        <v>17501</v>
       </c>
       <c r="D553" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10684,17 +10678,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20585</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>17202</v>
+        <v>17502</v>
       </c>
       <c r="D554" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10706,15 +10700,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20586</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="555" spans="3:8">
       <c r="C555" s="6">
-        <v>17203</v>
+        <v>17503</v>
       </c>
       <c r="D555" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10726,15 +10720,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20587</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="556" spans="3:8">
       <c r="C556" s="6">
-        <v>17204</v>
+        <v>17504</v>
       </c>
       <c r="D556" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10746,15 +10740,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20588</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="557" spans="3:7">
       <c r="C557" s="6">
-        <v>17205</v>
+        <v>17505</v>
       </c>
       <c r="D557" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10768,10 +10762,10 @@
     </row>
     <row r="558" spans="3:7">
       <c r="C558" s="6">
-        <v>17206</v>
+        <v>17506</v>
       </c>
       <c r="D558" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10785,10 +10779,10 @@
     </row>
     <row r="559" spans="3:7">
       <c r="C559" s="6">
-        <v>17207</v>
+        <v>17507</v>
       </c>
       <c r="D559" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10802,10 +10796,10 @@
     </row>
     <row r="560" spans="3:7">
       <c r="C560" s="6">
-        <v>17208</v>
+        <v>17508</v>
       </c>
       <c r="D560" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10819,10 +10813,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>17209</v>
+        <v>17509</v>
       </c>
       <c r="D561" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10836,10 +10830,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>17210</v>
+        <v>17510</v>
       </c>
       <c r="D562" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10853,10 +10847,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>17211</v>
+        <v>17511</v>
       </c>
       <c r="D563" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10870,10 +10864,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>17212</v>
+        <v>17512</v>
       </c>
       <c r="D564" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10887,10 +10881,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>17213</v>
+        <v>17513</v>
       </c>
       <c r="D565" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10904,10 +10898,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>17214</v>
+        <v>17514</v>
       </c>
       <c r="D566" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10921,10 +10915,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>17215</v>
+        <v>17515</v>
       </c>
       <c r="D567" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10938,10 +10932,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>17216</v>
+        <v>17516</v>
       </c>
       <c r="D568" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10955,10 +10949,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>17217</v>
+        <v>17517</v>
       </c>
       <c r="D569" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10972,10 +10966,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>17218</v>
+        <v>17518</v>
       </c>
       <c r="D570" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10989,10 +10983,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>17219</v>
+        <v>17519</v>
       </c>
       <c r="D571" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11006,10 +11000,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>17220</v>
+        <v>17520</v>
       </c>
       <c r="D572" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11023,10 +11017,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>17221</v>
+        <v>17521</v>
       </c>
       <c r="D573" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11040,10 +11034,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>17222</v>
+        <v>17522</v>
       </c>
       <c r="D574" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11057,10 +11051,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>17223</v>
+        <v>17523</v>
       </c>
       <c r="D575" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11074,10 +11068,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>17224</v>
+        <v>17524</v>
       </c>
       <c r="D576" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11091,10 +11085,10 @@
     </row>
     <row r="577" spans="3:7">
       <c r="C577" s="6">
-        <v>17225</v>
+        <v>17525</v>
       </c>
       <c r="D577" s="3">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11111,10 +11105,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>17301</v>
+        <v>17601</v>
       </c>
       <c r="D579" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11126,17 +11120,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20415</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>17302</v>
+        <v>17602</v>
       </c>
       <c r="D580" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11148,15 +11142,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20416</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="581" spans="3:8">
       <c r="C581" s="6">
-        <v>17303</v>
+        <v>17603</v>
       </c>
       <c r="D581" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11168,15 +11162,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20417</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="582" spans="3:8">
       <c r="C582" s="6">
-        <v>17304</v>
+        <v>17604</v>
       </c>
       <c r="D582" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11188,15 +11182,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20418</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="583" spans="3:7">
       <c r="C583" s="6">
-        <v>17305</v>
+        <v>17605</v>
       </c>
       <c r="D583" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11210,10 +11204,10 @@
     </row>
     <row r="584" spans="3:7">
       <c r="C584" s="6">
-        <v>17306</v>
+        <v>17606</v>
       </c>
       <c r="D584" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11227,10 +11221,10 @@
     </row>
     <row r="585" spans="3:7">
       <c r="C585" s="6">
-        <v>17307</v>
+        <v>17607</v>
       </c>
       <c r="D585" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11244,10 +11238,10 @@
     </row>
     <row r="586" spans="3:7">
       <c r="C586" s="6">
-        <v>17308</v>
+        <v>17608</v>
       </c>
       <c r="D586" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11261,10 +11255,10 @@
     </row>
     <row r="587" spans="3:7">
       <c r="C587" s="6">
-        <v>17309</v>
+        <v>17609</v>
       </c>
       <c r="D587" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11278,10 +11272,10 @@
     </row>
     <row r="588" spans="3:7">
       <c r="C588" s="6">
-        <v>17310</v>
+        <v>17610</v>
       </c>
       <c r="D588" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11295,10 +11289,10 @@
     </row>
     <row r="589" spans="3:7">
       <c r="C589" s="6">
-        <v>17311</v>
+        <v>17611</v>
       </c>
       <c r="D589" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11312,10 +11306,10 @@
     </row>
     <row r="590" spans="3:7">
       <c r="C590" s="6">
-        <v>17312</v>
+        <v>17612</v>
       </c>
       <c r="D590" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11329,10 +11323,10 @@
     </row>
     <row r="591" spans="3:7">
       <c r="C591" s="6">
-        <v>17313</v>
+        <v>17613</v>
       </c>
       <c r="D591" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11346,10 +11340,10 @@
     </row>
     <row r="592" spans="3:7">
       <c r="C592" s="6">
-        <v>17314</v>
+        <v>17614</v>
       </c>
       <c r="D592" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11363,10 +11357,10 @@
     </row>
     <row r="593" spans="3:7">
       <c r="C593" s="6">
-        <v>17315</v>
+        <v>17615</v>
       </c>
       <c r="D593" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11380,10 +11374,10 @@
     </row>
     <row r="594" spans="3:7">
       <c r="C594" s="6">
-        <v>17316</v>
+        <v>17616</v>
       </c>
       <c r="D594" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11397,10 +11391,10 @@
     </row>
     <row r="595" spans="3:7">
       <c r="C595" s="6">
-        <v>17317</v>
+        <v>17617</v>
       </c>
       <c r="D595" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11414,10 +11408,10 @@
     </row>
     <row r="596" spans="3:7">
       <c r="C596" s="6">
-        <v>17318</v>
+        <v>17618</v>
       </c>
       <c r="D596" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11431,10 +11425,10 @@
     </row>
     <row r="597" spans="3:7">
       <c r="C597" s="6">
-        <v>17319</v>
+        <v>17619</v>
       </c>
       <c r="D597" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11448,10 +11442,10 @@
     </row>
     <row r="598" spans="3:7">
       <c r="C598" s="6">
-        <v>17320</v>
+        <v>17620</v>
       </c>
       <c r="D598" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11465,10 +11459,10 @@
     </row>
     <row r="599" spans="3:7">
       <c r="C599" s="6">
-        <v>17321</v>
+        <v>17621</v>
       </c>
       <c r="D599" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11482,10 +11476,10 @@
     </row>
     <row r="600" spans="3:7">
       <c r="C600" s="6">
-        <v>17322</v>
+        <v>17622</v>
       </c>
       <c r="D600" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11499,10 +11493,10 @@
     </row>
     <row r="601" spans="3:7">
       <c r="C601" s="6">
-        <v>17323</v>
+        <v>17623</v>
       </c>
       <c r="D601" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11516,10 +11510,10 @@
     </row>
     <row r="602" spans="3:7">
       <c r="C602" s="6">
-        <v>17324</v>
+        <v>17624</v>
       </c>
       <c r="D602" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11533,10 +11527,10 @@
     </row>
     <row r="603" spans="3:7">
       <c r="C603" s="6">
-        <v>17325</v>
+        <v>17625</v>
       </c>
       <c r="D603" s="3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11553,10 +11547,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>17401</v>
+        <v>17701</v>
       </c>
       <c r="D605" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11568,17 +11562,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20445</v>
+        <v>20545</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>17402</v>
+        <v>17702</v>
       </c>
       <c r="D606" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11590,15 +11584,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20446</v>
+        <v>20546</v>
       </c>
     </row>
     <row r="607" spans="3:8">
       <c r="C607" s="6">
-        <v>17403</v>
+        <v>17703</v>
       </c>
       <c r="D607" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11610,15 +11604,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20447</v>
+        <v>20547</v>
       </c>
     </row>
     <row r="608" spans="3:8">
       <c r="C608" s="6">
-        <v>17404</v>
+        <v>17704</v>
       </c>
       <c r="D608" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11630,15 +11624,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20448</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>17405</v>
+        <v>17705</v>
       </c>
       <c r="D609" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11652,10 +11646,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>17406</v>
+        <v>17706</v>
       </c>
       <c r="D610" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11669,10 +11663,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>17407</v>
+        <v>17707</v>
       </c>
       <c r="D611" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11686,10 +11680,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>17408</v>
+        <v>17708</v>
       </c>
       <c r="D612" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11703,10 +11697,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>17409</v>
+        <v>17709</v>
       </c>
       <c r="D613" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11720,10 +11714,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>17410</v>
+        <v>17710</v>
       </c>
       <c r="D614" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11737,10 +11731,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>17411</v>
+        <v>17711</v>
       </c>
       <c r="D615" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11754,10 +11748,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>17412</v>
+        <v>17712</v>
       </c>
       <c r="D616" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11771,10 +11765,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>17413</v>
+        <v>17713</v>
       </c>
       <c r="D617" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11788,10 +11782,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>17414</v>
+        <v>17714</v>
       </c>
       <c r="D618" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11805,10 +11799,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>17415</v>
+        <v>17715</v>
       </c>
       <c r="D619" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11822,10 +11816,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>17416</v>
+        <v>17716</v>
       </c>
       <c r="D620" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11839,10 +11833,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>17417</v>
+        <v>17717</v>
       </c>
       <c r="D621" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11856,10 +11850,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>17418</v>
+        <v>17718</v>
       </c>
       <c r="D622" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11873,10 +11867,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>17419</v>
+        <v>17719</v>
       </c>
       <c r="D623" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11890,10 +11884,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>17420</v>
+        <v>17720</v>
       </c>
       <c r="D624" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11907,10 +11901,10 @@
     </row>
     <row r="625" spans="3:7">
       <c r="C625" s="6">
-        <v>17421</v>
+        <v>17721</v>
       </c>
       <c r="D625" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11924,10 +11918,10 @@
     </row>
     <row r="626" spans="3:7">
       <c r="C626" s="6">
-        <v>17422</v>
+        <v>17722</v>
       </c>
       <c r="D626" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11941,10 +11935,10 @@
     </row>
     <row r="627" spans="3:7">
       <c r="C627" s="6">
-        <v>17423</v>
+        <v>17723</v>
       </c>
       <c r="D627" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11958,10 +11952,10 @@
     </row>
     <row r="628" spans="3:7">
       <c r="C628" s="6">
-        <v>17424</v>
+        <v>17724</v>
       </c>
       <c r="D628" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11975,10 +11969,10 @@
     </row>
     <row r="629" spans="3:7">
       <c r="C629" s="6">
-        <v>17425</v>
+        <v>17725</v>
       </c>
       <c r="D629" s="3">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11995,10 +11989,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>17501</v>
+        <v>17801</v>
       </c>
       <c r="D631" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12010,17 +12004,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20455</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>17502</v>
+        <v>17802</v>
       </c>
       <c r="D632" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12032,15 +12026,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20456</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="633" spans="3:8">
       <c r="C633" s="6">
-        <v>17503</v>
+        <v>17803</v>
       </c>
       <c r="D633" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12052,15 +12046,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20457</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="634" spans="3:8">
       <c r="C634" s="6">
-        <v>17504</v>
+        <v>17804</v>
       </c>
       <c r="D634" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12072,15 +12066,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20458</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="635" spans="3:7">
       <c r="C635" s="6">
-        <v>17505</v>
+        <v>17805</v>
       </c>
       <c r="D635" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12094,10 +12088,10 @@
     </row>
     <row r="636" spans="3:7">
       <c r="C636" s="6">
-        <v>17506</v>
+        <v>17806</v>
       </c>
       <c r="D636" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12111,10 +12105,10 @@
     </row>
     <row r="637" spans="3:7">
       <c r="C637" s="6">
-        <v>17507</v>
+        <v>17807</v>
       </c>
       <c r="D637" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12128,10 +12122,10 @@
     </row>
     <row r="638" spans="3:7">
       <c r="C638" s="6">
-        <v>17508</v>
+        <v>17808</v>
       </c>
       <c r="D638" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12145,10 +12139,10 @@
     </row>
     <row r="639" spans="3:7">
       <c r="C639" s="6">
-        <v>17509</v>
+        <v>17809</v>
       </c>
       <c r="D639" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12162,10 +12156,10 @@
     </row>
     <row r="640" spans="3:7">
       <c r="C640" s="6">
-        <v>17510</v>
+        <v>17810</v>
       </c>
       <c r="D640" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12179,10 +12173,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>17511</v>
+        <v>17811</v>
       </c>
       <c r="D641" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12196,10 +12190,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>17512</v>
+        <v>17812</v>
       </c>
       <c r="D642" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12213,10 +12207,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>17513</v>
+        <v>17813</v>
       </c>
       <c r="D643" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12230,10 +12224,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>17514</v>
+        <v>17814</v>
       </c>
       <c r="D644" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12247,10 +12241,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>17515</v>
+        <v>17815</v>
       </c>
       <c r="D645" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12264,10 +12258,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>17516</v>
+        <v>17816</v>
       </c>
       <c r="D646" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12281,10 +12275,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>17517</v>
+        <v>17817</v>
       </c>
       <c r="D647" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12298,10 +12292,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>17518</v>
+        <v>17818</v>
       </c>
       <c r="D648" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12315,10 +12309,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>17519</v>
+        <v>17819</v>
       </c>
       <c r="D649" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12332,10 +12326,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>17520</v>
+        <v>17820</v>
       </c>
       <c r="D650" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12349,10 +12343,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>17521</v>
+        <v>17821</v>
       </c>
       <c r="D651" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12366,10 +12360,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>17522</v>
+        <v>17822</v>
       </c>
       <c r="D652" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12383,10 +12377,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>17523</v>
+        <v>17823</v>
       </c>
       <c r="D653" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12400,10 +12394,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>17524</v>
+        <v>17824</v>
       </c>
       <c r="D654" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12417,10 +12411,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>17525</v>
+        <v>17825</v>
       </c>
       <c r="D655" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12437,10 +12431,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>17601</v>
+        <v>17901</v>
       </c>
       <c r="D657" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12452,17 +12446,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20505</v>
+        <v>20595</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>17602</v>
+        <v>17902</v>
       </c>
       <c r="D658" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12474,15 +12468,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20506</v>
+        <v>20596</v>
       </c>
     </row>
     <row r="659" spans="3:8">
       <c r="C659" s="6">
-        <v>17603</v>
+        <v>17903</v>
       </c>
       <c r="D659" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12494,15 +12488,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20507</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="660" spans="3:8">
       <c r="C660" s="6">
-        <v>17604</v>
+        <v>17904</v>
       </c>
       <c r="D660" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12514,15 +12508,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20508</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="661" spans="3:7">
       <c r="C661" s="6">
-        <v>17605</v>
+        <v>17905</v>
       </c>
       <c r="D661" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12536,10 +12530,10 @@
     </row>
     <row r="662" spans="3:7">
       <c r="C662" s="6">
-        <v>17606</v>
+        <v>17906</v>
       </c>
       <c r="D662" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12553,10 +12547,10 @@
     </row>
     <row r="663" spans="3:7">
       <c r="C663" s="6">
-        <v>17607</v>
+        <v>17907</v>
       </c>
       <c r="D663" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12570,10 +12564,10 @@
     </row>
     <row r="664" spans="3:7">
       <c r="C664" s="6">
-        <v>17608</v>
+        <v>17908</v>
       </c>
       <c r="D664" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12587,10 +12581,10 @@
     </row>
     <row r="665" spans="3:7">
       <c r="C665" s="6">
-        <v>17609</v>
+        <v>17909</v>
       </c>
       <c r="D665" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12604,10 +12598,10 @@
     </row>
     <row r="666" spans="3:7">
       <c r="C666" s="6">
-        <v>17610</v>
+        <v>17910</v>
       </c>
       <c r="D666" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12621,10 +12615,10 @@
     </row>
     <row r="667" spans="3:7">
       <c r="C667" s="6">
-        <v>17611</v>
+        <v>17911</v>
       </c>
       <c r="D667" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12638,10 +12632,10 @@
     </row>
     <row r="668" spans="3:7">
       <c r="C668" s="6">
-        <v>17612</v>
+        <v>17912</v>
       </c>
       <c r="D668" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12655,10 +12649,10 @@
     </row>
     <row r="669" spans="3:7">
       <c r="C669" s="6">
-        <v>17613</v>
+        <v>17913</v>
       </c>
       <c r="D669" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12672,10 +12666,10 @@
     </row>
     <row r="670" spans="3:7">
       <c r="C670" s="6">
-        <v>17614</v>
+        <v>17914</v>
       </c>
       <c r="D670" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12689,10 +12683,10 @@
     </row>
     <row r="671" spans="3:7">
       <c r="C671" s="6">
-        <v>17615</v>
+        <v>17915</v>
       </c>
       <c r="D671" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12706,10 +12700,10 @@
     </row>
     <row r="672" spans="3:7">
       <c r="C672" s="6">
-        <v>17616</v>
+        <v>17916</v>
       </c>
       <c r="D672" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12723,10 +12717,10 @@
     </row>
     <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>17617</v>
+        <v>17917</v>
       </c>
       <c r="D673" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12740,10 +12734,10 @@
     </row>
     <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>17618</v>
+        <v>17918</v>
       </c>
       <c r="D674" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12757,10 +12751,10 @@
     </row>
     <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>17619</v>
+        <v>17919</v>
       </c>
       <c r="D675" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12774,10 +12768,10 @@
     </row>
     <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>17620</v>
+        <v>17920</v>
       </c>
       <c r="D676" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12791,10 +12785,10 @@
     </row>
     <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>17621</v>
+        <v>17921</v>
       </c>
       <c r="D677" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12808,10 +12802,10 @@
     </row>
     <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>17622</v>
+        <v>17922</v>
       </c>
       <c r="D678" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12825,10 +12819,10 @@
     </row>
     <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>17623</v>
+        <v>17923</v>
       </c>
       <c r="D679" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12842,10 +12836,10 @@
     </row>
     <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>17624</v>
+        <v>17924</v>
       </c>
       <c r="D680" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12859,10 +12853,10 @@
     </row>
     <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>17625</v>
+        <v>17925</v>
       </c>
       <c r="D681" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12871,890 +12865,6 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>17701</v>
-      </c>
-      <c r="D683" s="3">
-        <v>177</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20545</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>17702</v>
-      </c>
-      <c r="D684" s="3">
-        <v>177</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20546</v>
-      </c>
-    </row>
-    <row r="685" spans="3:8">
-      <c r="C685" s="6">
-        <v>17703</v>
-      </c>
-      <c r="D685" s="3">
-        <v>177</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20547</v>
-      </c>
-    </row>
-    <row r="686" spans="3:8">
-      <c r="C686" s="6">
-        <v>17704</v>
-      </c>
-      <c r="D686" s="3">
-        <v>177</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20548</v>
-      </c>
-    </row>
-    <row r="687" spans="3:7">
-      <c r="C687" s="6">
-        <v>17705</v>
-      </c>
-      <c r="D687" s="3">
-        <v>177</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="3:7">
-      <c r="C688" s="6">
-        <v>17706</v>
-      </c>
-      <c r="D688" s="3">
-        <v>177</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>17707</v>
-      </c>
-      <c r="D689" s="3">
-        <v>177</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>17708</v>
-      </c>
-      <c r="D690" s="3">
-        <v>177</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>17709</v>
-      </c>
-      <c r="D691" s="3">
-        <v>177</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>17710</v>
-      </c>
-      <c r="D692" s="3">
-        <v>177</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>17711</v>
-      </c>
-      <c r="D693" s="3">
-        <v>177</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>17712</v>
-      </c>
-      <c r="D694" s="3">
-        <v>177</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>17713</v>
-      </c>
-      <c r="D695" s="3">
-        <v>177</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>17714</v>
-      </c>
-      <c r="D696" s="3">
-        <v>177</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>17715</v>
-      </c>
-      <c r="D697" s="3">
-        <v>177</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>17716</v>
-      </c>
-      <c r="D698" s="3">
-        <v>177</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>17717</v>
-      </c>
-      <c r="D699" s="3">
-        <v>177</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>17718</v>
-      </c>
-      <c r="D700" s="3">
-        <v>177</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>17719</v>
-      </c>
-      <c r="D701" s="3">
-        <v>177</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>17720</v>
-      </c>
-      <c r="D702" s="3">
-        <v>177</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>17721</v>
-      </c>
-      <c r="D703" s="3">
-        <v>177</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>17722</v>
-      </c>
-      <c r="D704" s="3">
-        <v>177</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="3:7">
-      <c r="C705" s="6">
-        <v>17723</v>
-      </c>
-      <c r="D705" s="3">
-        <v>177</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="3:7">
-      <c r="C706" s="6">
-        <v>17724</v>
-      </c>
-      <c r="D706" s="3">
-        <v>177</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="3:7">
-      <c r="C707" s="6">
-        <v>17725</v>
-      </c>
-      <c r="D707" s="3">
-        <v>177</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>17801</v>
-      </c>
-      <c r="D709" s="3">
-        <v>178</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20565</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>17802</v>
-      </c>
-      <c r="D710" s="3">
-        <v>178</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20566</v>
-      </c>
-    </row>
-    <row r="711" spans="3:8">
-      <c r="C711" s="6">
-        <v>17803</v>
-      </c>
-      <c r="D711" s="3">
-        <v>178</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20567</v>
-      </c>
-    </row>
-    <row r="712" spans="3:8">
-      <c r="C712" s="6">
-        <v>17804</v>
-      </c>
-      <c r="D712" s="3">
-        <v>178</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20568</v>
-      </c>
-    </row>
-    <row r="713" spans="3:7">
-      <c r="C713" s="6">
-        <v>17805</v>
-      </c>
-      <c r="D713" s="3">
-        <v>178</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="3:7">
-      <c r="C714" s="6">
-        <v>17806</v>
-      </c>
-      <c r="D714" s="3">
-        <v>178</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="3:7">
-      <c r="C715" s="6">
-        <v>17807</v>
-      </c>
-      <c r="D715" s="3">
-        <v>178</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="3:7">
-      <c r="C716" s="6">
-        <v>17808</v>
-      </c>
-      <c r="D716" s="3">
-        <v>178</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="3:7">
-      <c r="C717" s="6">
-        <v>17809</v>
-      </c>
-      <c r="D717" s="3">
-        <v>178</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="3:7">
-      <c r="C718" s="6">
-        <v>17810</v>
-      </c>
-      <c r="D718" s="3">
-        <v>178</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="3:7">
-      <c r="C719" s="6">
-        <v>17811</v>
-      </c>
-      <c r="D719" s="3">
-        <v>178</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="3:7">
-      <c r="C720" s="6">
-        <v>17812</v>
-      </c>
-      <c r="D720" s="3">
-        <v>178</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="3:7">
-      <c r="C721" s="6">
-        <v>17813</v>
-      </c>
-      <c r="D721" s="3">
-        <v>178</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="3:7">
-      <c r="C722" s="6">
-        <v>17814</v>
-      </c>
-      <c r="D722" s="3">
-        <v>178</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="3:7">
-      <c r="C723" s="6">
-        <v>17815</v>
-      </c>
-      <c r="D723" s="3">
-        <v>178</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="3:7">
-      <c r="C724" s="6">
-        <v>17816</v>
-      </c>
-      <c r="D724" s="3">
-        <v>178</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="3:7">
-      <c r="C725" s="6">
-        <v>17817</v>
-      </c>
-      <c r="D725" s="3">
-        <v>178</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="3:7">
-      <c r="C726" s="6">
-        <v>17818</v>
-      </c>
-      <c r="D726" s="3">
-        <v>178</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="3:7">
-      <c r="C727" s="6">
-        <v>17819</v>
-      </c>
-      <c r="D727" s="3">
-        <v>178</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="3:7">
-      <c r="C728" s="6">
-        <v>17820</v>
-      </c>
-      <c r="D728" s="3">
-        <v>178</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="3:7">
-      <c r="C729" s="6">
-        <v>17821</v>
-      </c>
-      <c r="D729" s="3">
-        <v>178</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="3:7">
-      <c r="C730" s="6">
-        <v>17822</v>
-      </c>
-      <c r="D730" s="3">
-        <v>178</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="3:7">
-      <c r="C731" s="6">
-        <v>17823</v>
-      </c>
-      <c r="D731" s="3">
-        <v>178</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="3:7">
-      <c r="C732" s="6">
-        <v>17824</v>
-      </c>
-      <c r="D732" s="3">
-        <v>178</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="3:7">
-      <c r="C733" s="6">
-        <v>17825</v>
-      </c>
-      <c r="D733" s="3">
-        <v>178</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋179巨刃降临</t>
+  </si>
+  <si>
+    <t>#先锋180</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>18001</v>
+      </c>
+      <c r="D683" s="3">
+        <v>180</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20375</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>18002</v>
+      </c>
+      <c r="D684" s="3">
+        <v>180</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20376</v>
+      </c>
+    </row>
+    <row r="685" spans="3:8">
+      <c r="C685" s="6">
+        <v>18003</v>
+      </c>
+      <c r="D685" s="3">
+        <v>180</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20377</v>
+      </c>
+    </row>
+    <row r="686" spans="3:8">
+      <c r="C686" s="6">
+        <v>18004</v>
+      </c>
+      <c r="D686" s="3">
+        <v>180</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20378</v>
+      </c>
+    </row>
+    <row r="687" spans="3:7">
+      <c r="C687" s="6">
+        <v>18005</v>
+      </c>
+      <c r="D687" s="3">
+        <v>180</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="3:7">
+      <c r="C688" s="6">
+        <v>18006</v>
+      </c>
+      <c r="D688" s="3">
+        <v>180</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>18007</v>
+      </c>
+      <c r="D689" s="3">
+        <v>180</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>18008</v>
+      </c>
+      <c r="D690" s="3">
+        <v>180</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>18009</v>
+      </c>
+      <c r="D691" s="3">
+        <v>180</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>18010</v>
+      </c>
+      <c r="D692" s="3">
+        <v>180</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>18011</v>
+      </c>
+      <c r="D693" s="3">
+        <v>180</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>18012</v>
+      </c>
+      <c r="D694" s="3">
+        <v>180</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>18013</v>
+      </c>
+      <c r="D695" s="3">
+        <v>180</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>18014</v>
+      </c>
+      <c r="D696" s="3">
+        <v>180</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>18015</v>
+      </c>
+      <c r="D697" s="3">
+        <v>180</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>18016</v>
+      </c>
+      <c r="D698" s="3">
+        <v>180</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>18017</v>
+      </c>
+      <c r="D699" s="3">
+        <v>180</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>18018</v>
+      </c>
+      <c r="D700" s="3">
+        <v>180</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>18019</v>
+      </c>
+      <c r="D701" s="3">
+        <v>180</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>18020</v>
+      </c>
+      <c r="D702" s="3">
+        <v>180</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>18021</v>
+      </c>
+      <c r="D703" s="3">
+        <v>180</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>18022</v>
+      </c>
+      <c r="D704" s="3">
+        <v>180</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>18023</v>
+      </c>
+      <c r="D705" s="3">
+        <v>180</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>18024</v>
+      </c>
+      <c r="D706" s="3">
+        <v>180</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>18025</v>
+      </c>
+      <c r="D707" s="3">
+        <v>180</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -235,7 +235,7 @@
     <t>#先锋179巨刃降临</t>
   </si>
   <si>
-    <t>#先锋180</t>
+    <t>#先锋180生命之树</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋180生命之树</t>
+  </si>
+  <si>
+    <t>#先锋181浮生若梦</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1275,7 +1278,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" spans="1:15">
       <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="3:8">
+    <row r="4" spans="1:15">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" spans="1:15">
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1377,7 +1380,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="3:15">
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="C8" s="8">
         <v>302</v>
       </c>
@@ -1404,7 +1407,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
     </row>
-    <row r="9" spans="3:8">
+    <row r="9" spans="1:15">
       <c r="C9" s="8">
         <v>303</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>20327</v>
       </c>
     </row>
-    <row r="10" spans="3:8">
+    <row r="10" spans="1:15">
       <c r="C10" s="8">
         <v>304</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>20328</v>
       </c>
     </row>
-    <row r="11" spans="3:7">
+    <row r="11" spans="1:15">
       <c r="C11" s="8">
         <v>305</v>
       </c>
@@ -1461,7 +1464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="3:7">
+    <row r="12" spans="1:15">
       <c r="C12" s="8">
         <v>306</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="3:7">
+    <row r="13" spans="1:15">
       <c r="C13" s="8">
         <v>307</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="3:7">
+    <row r="14" spans="1:15">
       <c r="C14" s="8">
         <v>308</v>
       </c>
@@ -1512,7 +1515,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="3:7">
+    <row r="15" spans="1:15">
       <c r="C15" s="8">
         <v>309</v>
       </c>
@@ -1529,7 +1532,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="3:7">
+    <row r="16" spans="1:15">
       <c r="C16" s="8">
         <v>310</v>
       </c>
@@ -1546,7 +1549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:7">
+    <row r="17" spans="3:8">
       <c r="C17" s="8">
         <v>311</v>
       </c>
@@ -1563,7 +1566,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="3:7">
+    <row r="18" spans="3:8">
       <c r="C18" s="8">
         <v>312</v>
       </c>
@@ -1580,7 +1583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="3:7">
+    <row r="19" spans="3:8">
       <c r="C19" s="8">
         <v>313</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="3:7">
+    <row r="20" spans="3:8">
       <c r="C20" s="8">
         <v>314</v>
       </c>
@@ -1614,7 +1617,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="3:7">
+    <row r="21" spans="3:8">
       <c r="C21" s="8">
         <v>315</v>
       </c>
@@ -1631,7 +1634,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:7">
+    <row r="22" spans="3:8">
       <c r="C22" s="8">
         <v>316</v>
       </c>
@@ -1648,7 +1651,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="3:7">
+    <row r="23" spans="3:8">
       <c r="C23" s="8">
         <v>317</v>
       </c>
@@ -1665,7 +1668,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="3:7">
+    <row r="24" spans="3:8">
       <c r="C24" s="8">
         <v>318</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="3:7">
+    <row r="25" spans="3:8">
       <c r="C25" s="8">
         <v>319</v>
       </c>
@@ -1699,7 +1702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="3:7">
+    <row r="26" spans="3:8">
       <c r="C26" s="8">
         <v>320</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="3:7">
+    <row r="27" spans="3:8">
       <c r="C27" s="8">
         <v>321</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="28" spans="3:7">
+    <row r="28" spans="3:8">
       <c r="C28" s="8">
         <v>322</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="3:7">
+    <row r="29" spans="3:8">
       <c r="C29" s="8">
         <v>323</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="3:7">
+    <row r="30" spans="3:8">
       <c r="C30" s="8">
         <v>324</v>
       </c>
@@ -1784,7 +1787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="3:7">
+    <row r="31" spans="3:8">
       <c r="C31" s="8">
         <v>325</v>
       </c>
@@ -1854,7 +1857,7 @@
         <v>20336</v>
       </c>
     </row>
-    <row r="35" spans="3:8">
+    <row r="35" spans="1:8">
       <c r="C35" s="8">
         <v>503</v>
       </c>
@@ -1874,7 +1877,7 @@
         <v>20337</v>
       </c>
     </row>
-    <row r="36" spans="3:8">
+    <row r="36" spans="1:8">
       <c r="C36" s="8">
         <v>504</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>20338</v>
       </c>
     </row>
-    <row r="37" spans="3:7">
+    <row r="37" spans="1:8">
       <c r="C37" s="8">
         <v>505</v>
       </c>
@@ -1911,7 +1914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="3:7">
+    <row r="38" spans="1:8">
       <c r="C38" s="8">
         <v>506</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="3:7">
+    <row r="39" spans="1:8">
       <c r="C39" s="8">
         <v>507</v>
       </c>
@@ -1945,7 +1948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="3:7">
+    <row r="40" spans="1:8">
       <c r="C40" s="8">
         <v>508</v>
       </c>
@@ -1962,7 +1965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="3:7">
+    <row r="41" spans="1:8">
       <c r="C41" s="8">
         <v>509</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="3:7">
+    <row r="42" spans="1:8">
       <c r="C42" s="8">
         <v>510</v>
       </c>
@@ -1996,7 +1999,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="3:7">
+    <row r="43" spans="1:8">
       <c r="C43" s="8">
         <v>511</v>
       </c>
@@ -2013,7 +2016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="3:7">
+    <row r="44" spans="1:8">
       <c r="C44" s="8">
         <v>512</v>
       </c>
@@ -2030,7 +2033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="3:7">
+    <row r="45" spans="1:8">
       <c r="C45" s="8">
         <v>513</v>
       </c>
@@ -2047,7 +2050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="3:7">
+    <row r="46" spans="1:8">
       <c r="C46" s="8">
         <v>514</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="3:7">
+    <row r="47" spans="1:8">
       <c r="C47" s="8">
         <v>515</v>
       </c>
@@ -2081,7 +2084,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="3:7">
+    <row r="48" spans="1:8">
       <c r="C48" s="8">
         <v>516</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="3:7">
+    <row r="49" spans="1:8">
       <c r="C49" s="8">
         <v>517</v>
       </c>
@@ -2115,7 +2118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="3:7">
+    <row r="50" spans="1:8">
       <c r="C50" s="8">
         <v>518</v>
       </c>
@@ -2132,7 +2135,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="3:7">
+    <row r="51" spans="1:8">
       <c r="C51" s="8">
         <v>519</v>
       </c>
@@ -2149,7 +2152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="3:7">
+    <row r="52" spans="1:8">
       <c r="C52" s="8">
         <v>520</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="53" spans="3:7">
+    <row r="53" spans="1:8">
       <c r="C53" s="8">
         <v>521</v>
       </c>
@@ -2183,7 +2186,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="3:7">
+    <row r="54" spans="1:8">
       <c r="C54" s="8">
         <v>522</v>
       </c>
@@ -2200,7 +2203,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="3:7">
+    <row r="55" spans="1:8">
       <c r="C55" s="8">
         <v>523</v>
       </c>
@@ -2217,7 +2220,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="3:7">
+    <row r="56" spans="1:8">
       <c r="C56" s="8">
         <v>524</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="3:7">
+    <row r="57" spans="1:8">
       <c r="C57" s="8">
         <v>525</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="58" ht="13.5" customHeight="1" spans="3:8">
+    <row r="58" ht="13.5" customHeight="1" spans="1:8">
       <c r="C58" s="9"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -2304,7 +2307,7 @@
         <v>20346</v>
       </c>
     </row>
-    <row r="61" spans="3:8">
+    <row r="61" spans="1:8">
       <c r="C61" s="8">
         <v>903</v>
       </c>
@@ -2324,7 +2327,7 @@
         <v>20347</v>
       </c>
     </row>
-    <row r="62" spans="3:8">
+    <row r="62" spans="1:8">
       <c r="C62" s="8">
         <v>904</v>
       </c>
@@ -2344,7 +2347,7 @@
         <v>20348</v>
       </c>
     </row>
-    <row r="63" spans="3:7">
+    <row r="63" spans="1:8">
       <c r="C63" s="8">
         <v>905</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" spans="3:7">
+    <row r="64" spans="1:8">
       <c r="C64" s="8">
         <v>906</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="3:7">
+    <row r="81" spans="1:8">
       <c r="C81" s="8">
         <v>923</v>
       </c>
@@ -2667,7 +2670,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="3:7">
+    <row r="82" spans="1:8">
       <c r="C82" s="8">
         <v>924</v>
       </c>
@@ -2684,7 +2687,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="83" spans="3:7">
+    <row r="83" spans="1:8">
       <c r="C83" s="8">
         <v>925</v>
       </c>
@@ -2701,7 +2704,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="3:5">
+    <row r="84" spans="1:8">
       <c r="C84" s="8"/>
       <c r="E84" s="5"/>
     </row>
@@ -2750,7 +2753,7 @@
         <v>20356</v>
       </c>
     </row>
-    <row r="87" spans="3:8">
+    <row r="87" spans="1:8">
       <c r="C87" s="8">
         <v>1203</v>
       </c>
@@ -2770,7 +2773,7 @@
         <v>20357</v>
       </c>
     </row>
-    <row r="88" spans="3:8">
+    <row r="88" spans="1:8">
       <c r="C88" s="8">
         <v>1204</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>20358</v>
       </c>
     </row>
-    <row r="89" spans="3:7">
+    <row r="89" spans="1:8">
       <c r="C89" s="8">
         <v>1205</v>
       </c>
@@ -2807,7 +2810,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90" spans="3:7">
+    <row r="90" spans="1:8">
       <c r="C90" s="8">
         <v>1206</v>
       </c>
@@ -2824,7 +2827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="3:7">
+    <row r="91" spans="1:8">
       <c r="C91" s="8">
         <v>1207</v>
       </c>
@@ -2841,7 +2844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="3:7">
+    <row r="92" spans="1:8">
       <c r="C92" s="8">
         <v>1208</v>
       </c>
@@ -2858,7 +2861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="3:7">
+    <row r="93" spans="1:8">
       <c r="C93" s="8">
         <v>1209</v>
       </c>
@@ -2875,7 +2878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="3:7">
+    <row r="94" spans="1:8">
       <c r="C94" s="8">
         <v>1210</v>
       </c>
@@ -2892,7 +2895,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="3:7">
+    <row r="95" spans="1:8">
       <c r="C95" s="8">
         <v>1211</v>
       </c>
@@ -2909,7 +2912,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="96" spans="3:7">
+    <row r="96" spans="1:8">
       <c r="C96" s="8">
         <v>1212</v>
       </c>
@@ -2926,7 +2929,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" spans="3:7">
+    <row r="97" spans="1:8">
       <c r="C97" s="8">
         <v>1213</v>
       </c>
@@ -2943,7 +2946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="3:7">
+    <row r="98" spans="1:8">
       <c r="C98" s="8">
         <v>1214</v>
       </c>
@@ -2960,7 +2963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="3:7">
+    <row r="99" spans="1:8">
       <c r="C99" s="8">
         <v>1215</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="3:7">
+    <row r="100" spans="1:8">
       <c r="C100" s="8">
         <v>1216</v>
       </c>
@@ -2994,7 +2997,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" spans="3:7">
+    <row r="101" spans="1:8">
       <c r="C101" s="8">
         <v>1217</v>
       </c>
@@ -3011,7 +3014,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="3:7">
+    <row r="102" spans="1:8">
       <c r="C102" s="8">
         <v>1218</v>
       </c>
@@ -3028,7 +3031,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="3:7">
+    <row r="103" spans="1:8">
       <c r="C103" s="8">
         <v>1219</v>
       </c>
@@ -3045,7 +3048,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="3:7">
+    <row r="104" spans="1:8">
       <c r="C104" s="8">
         <v>1220</v>
       </c>
@@ -3062,7 +3065,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="105" spans="3:7">
+    <row r="105" spans="1:8">
       <c r="C105" s="8">
         <v>1221</v>
       </c>
@@ -3079,7 +3082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="106" spans="3:7">
+    <row r="106" spans="1:8">
       <c r="C106" s="8">
         <v>1222</v>
       </c>
@@ -3096,7 +3099,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="3:7">
+    <row r="107" spans="1:8">
       <c r="C107" s="8">
         <v>1223</v>
       </c>
@@ -3113,7 +3116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="3:7">
+    <row r="108" spans="1:8">
       <c r="C108" s="8">
         <v>1224</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="109" spans="3:7">
+    <row r="109" spans="1:8">
       <c r="C109" s="8">
         <v>1225</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>20388</v>
       </c>
     </row>
-    <row r="115" spans="3:7">
+    <row r="115" spans="3:8">
       <c r="C115" s="6">
         <v>3205</v>
       </c>
@@ -3249,7 +3252,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116" spans="3:7">
+    <row r="116" spans="3:8">
       <c r="C116" s="6">
         <v>3206</v>
       </c>
@@ -3266,7 +3269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="3:7">
+    <row r="117" spans="3:8">
       <c r="C117" s="6">
         <v>3207</v>
       </c>
@@ -3283,7 +3286,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="3:7">
+    <row r="118" spans="3:8">
       <c r="C118" s="6">
         <v>3208</v>
       </c>
@@ -3300,7 +3303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="3:7">
+    <row r="119" spans="3:8">
       <c r="C119" s="6">
         <v>3209</v>
       </c>
@@ -3317,7 +3320,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="120" spans="3:7">
+    <row r="120" spans="3:8">
       <c r="C120" s="6">
         <v>3210</v>
       </c>
@@ -3334,7 +3337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="3:7">
+    <row r="121" spans="3:8">
       <c r="C121" s="6">
         <v>3211</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="3:7">
+    <row r="122" spans="3:8">
       <c r="C122" s="6">
         <v>3212</v>
       </c>
@@ -3368,7 +3371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="123" spans="3:7">
+    <row r="123" spans="3:8">
       <c r="C123" s="6">
         <v>3213</v>
       </c>
@@ -3385,7 +3388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="3:7">
+    <row r="124" spans="3:8">
       <c r="C124" s="6">
         <v>3214</v>
       </c>
@@ -3402,7 +3405,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="3:7">
+    <row r="125" spans="3:8">
       <c r="C125" s="6">
         <v>3215</v>
       </c>
@@ -3419,7 +3422,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="126" spans="3:7">
+    <row r="126" spans="3:8">
       <c r="C126" s="6">
         <v>3216</v>
       </c>
@@ -3436,7 +3439,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="3:7">
+    <row r="127" spans="3:8">
       <c r="C127" s="6">
         <v>3217</v>
       </c>
@@ -3453,7 +3456,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="128" spans="3:7">
+    <row r="128" spans="3:8">
       <c r="C128" s="6">
         <v>3218</v>
       </c>
@@ -3470,7 +3473,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="3:7">
+    <row r="129" spans="1:8">
       <c r="C129" s="6">
         <v>3219</v>
       </c>
@@ -3487,7 +3490,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="3:7">
+    <row r="130" spans="1:8">
       <c r="C130" s="6">
         <v>3220</v>
       </c>
@@ -3504,7 +3507,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="131" spans="3:7">
+    <row r="131" spans="1:8">
       <c r="C131" s="6">
         <v>3221</v>
       </c>
@@ -3521,7 +3524,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="132" spans="3:7">
+    <row r="132" spans="1:8">
       <c r="C132" s="6">
         <v>3222</v>
       </c>
@@ -3538,7 +3541,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="133" spans="3:7">
+    <row r="133" spans="1:8">
       <c r="C133" s="6">
         <v>3223</v>
       </c>
@@ -3555,7 +3558,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="134" spans="3:7">
+    <row r="134" spans="1:8">
       <c r="C134" s="6">
         <v>3224</v>
       </c>
@@ -3572,7 +3575,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="3:7">
+    <row r="135" spans="1:8">
       <c r="C135" s="6">
         <v>3225</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>20366</v>
       </c>
     </row>
-    <row r="139" spans="3:8">
+    <row r="139" spans="1:8">
       <c r="C139" s="6">
         <v>4803</v>
       </c>
@@ -3654,7 +3657,7 @@
         <v>20367</v>
       </c>
     </row>
-    <row r="140" spans="3:8">
+    <row r="140" spans="1:8">
       <c r="C140" s="6">
         <v>4804</v>
       </c>
@@ -3674,7 +3677,7 @@
         <v>20368</v>
       </c>
     </row>
-    <row r="141" spans="3:7">
+    <row r="141" spans="1:8">
       <c r="C141" s="6">
         <v>4805</v>
       </c>
@@ -3691,7 +3694,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142" spans="3:7">
+    <row r="142" spans="1:8">
       <c r="C142" s="6">
         <v>4806</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="3:7">
+    <row r="143" spans="1:8">
       <c r="C143" s="6">
         <v>4807</v>
       </c>
@@ -3725,7 +3728,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="144" spans="3:7">
+    <row r="144" spans="1:8">
       <c r="C144" s="6">
         <v>4808</v>
       </c>
@@ -4014,7 +4017,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="161" spans="3:7">
+    <row r="161" spans="1:8">
       <c r="C161" s="6">
         <v>4825</v>
       </c>
@@ -4076,7 +4079,7 @@
         <v>20486</v>
       </c>
     </row>
-    <row r="165" spans="3:8">
+    <row r="165" spans="1:8">
       <c r="C165" s="6">
         <v>6403</v>
       </c>
@@ -4096,7 +4099,7 @@
         <v>20487</v>
       </c>
     </row>
-    <row r="166" spans="3:8">
+    <row r="166" spans="1:8">
       <c r="C166" s="6">
         <v>6404</v>
       </c>
@@ -4116,7 +4119,7 @@
         <v>20488</v>
       </c>
     </row>
-    <row r="167" spans="3:7">
+    <row r="167" spans="1:8">
       <c r="C167" s="6">
         <v>6405</v>
       </c>
@@ -4133,7 +4136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168" spans="3:7">
+    <row r="168" spans="1:8">
       <c r="C168" s="6">
         <v>6406</v>
       </c>
@@ -4150,7 +4153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="169" spans="3:7">
+    <row r="169" spans="1:8">
       <c r="C169" s="6">
         <v>6407</v>
       </c>
@@ -4167,7 +4170,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="170" spans="3:7">
+    <row r="170" spans="1:8">
       <c r="C170" s="6">
         <v>6408</v>
       </c>
@@ -4184,7 +4187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="3:7">
+    <row r="171" spans="1:8">
       <c r="C171" s="6">
         <v>6409</v>
       </c>
@@ -4201,7 +4204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="172" spans="3:7">
+    <row r="172" spans="1:8">
       <c r="C172" s="6">
         <v>6410</v>
       </c>
@@ -4218,7 +4221,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="173" spans="3:7">
+    <row r="173" spans="1:8">
       <c r="C173" s="6">
         <v>6411</v>
       </c>
@@ -4235,7 +4238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="174" spans="3:7">
+    <row r="174" spans="1:8">
       <c r="C174" s="6">
         <v>6412</v>
       </c>
@@ -4252,7 +4255,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="175" spans="3:7">
+    <row r="175" spans="1:8">
       <c r="C175" s="6">
         <v>6413</v>
       </c>
@@ -4269,7 +4272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="3:7">
+    <row r="176" spans="1:8">
       <c r="C176" s="6">
         <v>6414</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="3:7">
+    <row r="177" spans="1:8">
       <c r="C177" s="6">
         <v>6415</v>
       </c>
@@ -4303,7 +4306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="3:7">
+    <row r="178" spans="1:8">
       <c r="C178" s="6">
         <v>6416</v>
       </c>
@@ -4320,7 +4323,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="3:7">
+    <row r="179" spans="1:8">
       <c r="C179" s="6">
         <v>6417</v>
       </c>
@@ -4337,7 +4340,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="180" spans="3:7">
+    <row r="180" spans="1:8">
       <c r="C180" s="6">
         <v>6418</v>
       </c>
@@ -4354,7 +4357,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="181" spans="3:7">
+    <row r="181" spans="1:8">
       <c r="C181" s="6">
         <v>6419</v>
       </c>
@@ -4371,7 +4374,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="3:7">
+    <row r="182" spans="1:8">
       <c r="C182" s="6">
         <v>6420</v>
       </c>
@@ -4388,7 +4391,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="183" spans="3:7">
+    <row r="183" spans="1:8">
       <c r="C183" s="6">
         <v>6421</v>
       </c>
@@ -4405,7 +4408,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="184" spans="3:7">
+    <row r="184" spans="1:8">
       <c r="C184" s="6">
         <v>6422</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="185" spans="3:7">
+    <row r="185" spans="1:8">
       <c r="C185" s="6">
         <v>6423</v>
       </c>
@@ -4439,7 +4442,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="3:7">
+    <row r="186" spans="1:8">
       <c r="C186" s="6">
         <v>6424</v>
       </c>
@@ -4456,7 +4459,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="187" spans="3:7">
+    <row r="187" spans="1:8">
       <c r="C187" s="6">
         <v>6425</v>
       </c>
@@ -4518,7 +4521,7 @@
         <v>20536</v>
       </c>
     </row>
-    <row r="191" spans="3:8">
+    <row r="191" spans="1:8">
       <c r="C191" s="6">
         <v>8003</v>
       </c>
@@ -4538,7 +4541,7 @@
         <v>20537</v>
       </c>
     </row>
-    <row r="192" spans="3:8">
+    <row r="192" spans="1:8">
       <c r="C192" s="6">
         <v>8004</v>
       </c>
@@ -4830,7 +4833,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="209" spans="3:7">
+    <row r="209" spans="1:8">
       <c r="C209" s="6">
         <v>8021</v>
       </c>
@@ -4847,7 +4850,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="3:7">
+    <row r="210" spans="1:8">
       <c r="C210" s="6">
         <v>8022</v>
       </c>
@@ -4864,7 +4867,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="211" spans="3:7">
+    <row r="211" spans="1:8">
       <c r="C211" s="6">
         <v>8023</v>
       </c>
@@ -4881,7 +4884,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="212" spans="3:7">
+    <row r="212" spans="1:8">
       <c r="C212" s="6">
         <v>8024</v>
       </c>
@@ -4898,7 +4901,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="213" spans="3:7">
+    <row r="213" spans="1:8">
       <c r="C213" s="6">
         <v>8025</v>
       </c>
@@ -4960,7 +4963,7 @@
         <v>20626</v>
       </c>
     </row>
-    <row r="217" spans="3:8">
+    <row r="217" spans="1:8">
       <c r="C217" s="6">
         <v>8403</v>
       </c>
@@ -4980,7 +4983,7 @@
         <v>20627</v>
       </c>
     </row>
-    <row r="218" spans="3:8">
+    <row r="218" spans="1:8">
       <c r="C218" s="6">
         <v>8404</v>
       </c>
@@ -5000,7 +5003,7 @@
         <v>20628</v>
       </c>
     </row>
-    <row r="219" spans="3:7">
+    <row r="219" spans="1:8">
       <c r="C219" s="6">
         <v>8405</v>
       </c>
@@ -5017,7 +5020,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="220" spans="3:7">
+    <row r="220" spans="1:8">
       <c r="C220" s="6">
         <v>8406</v>
       </c>
@@ -5034,7 +5037,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="3:7">
+    <row r="221" spans="1:8">
       <c r="C221" s="6">
         <v>8407</v>
       </c>
@@ -5051,7 +5054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="222" spans="3:7">
+    <row r="222" spans="1:8">
       <c r="C222" s="6">
         <v>8408</v>
       </c>
@@ -5068,7 +5071,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="223" spans="3:7">
+    <row r="223" spans="1:8">
       <c r="C223" s="6">
         <v>8409</v>
       </c>
@@ -5085,7 +5088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="224" spans="3:7">
+    <row r="224" spans="1:8">
       <c r="C224" s="6">
         <v>8410</v>
       </c>
@@ -5402,7 +5405,7 @@
         <v>20436</v>
       </c>
     </row>
-    <row r="243" spans="3:8">
+    <row r="243" spans="1:8">
       <c r="C243" s="6">
         <v>8903</v>
       </c>
@@ -5422,7 +5425,7 @@
         <v>20437</v>
       </c>
     </row>
-    <row r="244" spans="3:8">
+    <row r="244" spans="1:8">
       <c r="C244" s="6">
         <v>8904</v>
       </c>
@@ -5442,7 +5445,7 @@
         <v>20438</v>
       </c>
     </row>
-    <row r="245" spans="3:7">
+    <row r="245" spans="1:8">
       <c r="C245" s="6">
         <v>8905</v>
       </c>
@@ -5459,7 +5462,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="3:7">
+    <row r="246" spans="1:8">
       <c r="C246" s="6">
         <v>8906</v>
       </c>
@@ -5476,7 +5479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="247" spans="3:7">
+    <row r="247" spans="1:8">
       <c r="C247" s="6">
         <v>8907</v>
       </c>
@@ -5493,7 +5496,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="3:7">
+    <row r="248" spans="1:8">
       <c r="C248" s="6">
         <v>8908</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="249" spans="3:7">
+    <row r="249" spans="1:8">
       <c r="C249" s="6">
         <v>8909</v>
       </c>
@@ -5527,7 +5530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="250" spans="3:7">
+    <row r="250" spans="1:8">
       <c r="C250" s="6">
         <v>8910</v>
       </c>
@@ -5544,7 +5547,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="251" spans="3:7">
+    <row r="251" spans="1:8">
       <c r="C251" s="6">
         <v>8911</v>
       </c>
@@ -5561,7 +5564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="252" spans="3:7">
+    <row r="252" spans="1:8">
       <c r="C252" s="6">
         <v>8912</v>
       </c>
@@ -5578,7 +5581,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="3:7">
+    <row r="253" spans="1:8">
       <c r="C253" s="6">
         <v>8913</v>
       </c>
@@ -5595,7 +5598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="3:7">
+    <row r="254" spans="1:8">
       <c r="C254" s="6">
         <v>8914</v>
       </c>
@@ -5612,7 +5615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="255" spans="3:7">
+    <row r="255" spans="1:8">
       <c r="C255" s="6">
         <v>8915</v>
       </c>
@@ -5629,7 +5632,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="256" spans="3:7">
+    <row r="256" spans="1:8">
       <c r="C256" s="6">
         <v>8916</v>
       </c>
@@ -5646,7 +5649,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" spans="3:7">
+    <row r="257" spans="1:8">
       <c r="C257" s="6">
         <v>8917</v>
       </c>
@@ -5663,7 +5666,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="258" spans="3:7">
+    <row r="258" spans="1:8">
       <c r="C258" s="6">
         <v>8918</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="259" spans="3:7">
+    <row r="259" spans="1:8">
       <c r="C259" s="6">
         <v>8919</v>
       </c>
@@ -5697,7 +5700,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="260" spans="3:7">
+    <row r="260" spans="1:8">
       <c r="C260" s="6">
         <v>8920</v>
       </c>
@@ -5714,7 +5717,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="261" spans="3:7">
+    <row r="261" spans="1:8">
       <c r="C261" s="6">
         <v>8921</v>
       </c>
@@ -5731,7 +5734,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="262" spans="3:7">
+    <row r="262" spans="1:8">
       <c r="C262" s="6">
         <v>8922</v>
       </c>
@@ -5748,7 +5751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="263" spans="3:7">
+    <row r="263" spans="1:8">
       <c r="C263" s="6">
         <v>8923</v>
       </c>
@@ -5765,7 +5768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="264" spans="3:7">
+    <row r="264" spans="1:8">
       <c r="C264" s="6">
         <v>8924</v>
       </c>
@@ -5782,7 +5785,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="265" spans="3:7">
+    <row r="265" spans="1:8">
       <c r="C265" s="6">
         <v>8925</v>
       </c>
@@ -5844,7 +5847,7 @@
         <v>20396</v>
       </c>
     </row>
-    <row r="269" spans="3:8">
+    <row r="269" spans="1:8">
       <c r="C269" s="6">
         <v>10503</v>
       </c>
@@ -5864,7 +5867,7 @@
         <v>20397</v>
       </c>
     </row>
-    <row r="270" spans="3:8">
+    <row r="270" spans="1:8">
       <c r="C270" s="6">
         <v>10504</v>
       </c>
@@ -5884,7 +5887,7 @@
         <v>20398</v>
       </c>
     </row>
-    <row r="271" spans="3:7">
+    <row r="271" spans="1:8">
       <c r="C271" s="6">
         <v>10505</v>
       </c>
@@ -5901,7 +5904,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="272" spans="3:7">
+    <row r="272" spans="1:8">
       <c r="C272" s="6">
         <v>10506</v>
       </c>
@@ -6190,7 +6193,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="289" spans="3:7">
+    <row r="289" spans="1:8">
       <c r="C289" s="6">
         <v>10523</v>
       </c>
@@ -6207,7 +6210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="290" spans="3:7">
+    <row r="290" spans="1:8">
       <c r="C290" s="6">
         <v>10524</v>
       </c>
@@ -6224,7 +6227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="291" spans="3:7">
+    <row r="291" spans="1:8">
       <c r="C291" s="6">
         <v>10525</v>
       </c>
@@ -6286,7 +6289,7 @@
         <v>20466</v>
       </c>
     </row>
-    <row r="295" spans="3:8">
+    <row r="295" spans="1:8">
       <c r="C295" s="6">
         <v>12103</v>
       </c>
@@ -6306,7 +6309,7 @@
         <v>20467</v>
       </c>
     </row>
-    <row r="296" spans="3:8">
+    <row r="296" spans="1:8">
       <c r="C296" s="6">
         <v>12104</v>
       </c>
@@ -6326,7 +6329,7 @@
         <v>20468</v>
       </c>
     </row>
-    <row r="297" spans="3:7">
+    <row r="297" spans="1:8">
       <c r="C297" s="6">
         <v>12105</v>
       </c>
@@ -6343,7 +6346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="298" spans="3:7">
+    <row r="298" spans="1:8">
       <c r="C298" s="6">
         <v>12106</v>
       </c>
@@ -6360,7 +6363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="3:7">
+    <row r="299" spans="1:8">
       <c r="C299" s="6">
         <v>12107</v>
       </c>
@@ -6377,7 +6380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="3:7">
+    <row r="300" spans="1:8">
       <c r="C300" s="6">
         <v>12108</v>
       </c>
@@ -6394,7 +6397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="3:7">
+    <row r="301" spans="1:8">
       <c r="C301" s="6">
         <v>12109</v>
       </c>
@@ -6411,7 +6414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="302" spans="3:7">
+    <row r="302" spans="1:8">
       <c r="C302" s="6">
         <v>12110</v>
       </c>
@@ -6428,7 +6431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="3:7">
+    <row r="303" spans="1:8">
       <c r="C303" s="6">
         <v>12111</v>
       </c>
@@ -6445,7 +6448,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="304" spans="3:7">
+    <row r="304" spans="1:8">
       <c r="C304" s="6">
         <v>12112</v>
       </c>
@@ -6462,7 +6465,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="305" spans="3:7">
+    <row r="305" spans="1:8">
       <c r="C305" s="6">
         <v>12113</v>
       </c>
@@ -6479,7 +6482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="3:7">
+    <row r="306" spans="1:8">
       <c r="C306" s="6">
         <v>12114</v>
       </c>
@@ -6496,7 +6499,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="307" spans="3:7">
+    <row r="307" spans="1:8">
       <c r="C307" s="6">
         <v>12115</v>
       </c>
@@ -6513,7 +6516,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="3:7">
+    <row r="308" spans="1:8">
       <c r="C308" s="6">
         <v>12116</v>
       </c>
@@ -6530,7 +6533,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" spans="3:7">
+    <row r="309" spans="1:8">
       <c r="C309" s="6">
         <v>12117</v>
       </c>
@@ -6547,7 +6550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="310" spans="3:7">
+    <row r="310" spans="1:8">
       <c r="C310" s="6">
         <v>12118</v>
       </c>
@@ -6564,7 +6567,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="311" spans="3:7">
+    <row r="311" spans="1:8">
       <c r="C311" s="6">
         <v>12119</v>
       </c>
@@ -6581,7 +6584,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="312" spans="3:7">
+    <row r="312" spans="1:8">
       <c r="C312" s="6">
         <v>12120</v>
       </c>
@@ -6598,7 +6601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="313" spans="3:7">
+    <row r="313" spans="1:8">
       <c r="C313" s="6">
         <v>12121</v>
       </c>
@@ -6615,7 +6618,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="314" spans="3:7">
+    <row r="314" spans="1:8">
       <c r="C314" s="6">
         <v>12122</v>
       </c>
@@ -6632,7 +6635,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="315" spans="3:7">
+    <row r="315" spans="1:8">
       <c r="C315" s="6">
         <v>12123</v>
       </c>
@@ -6649,7 +6652,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="316" spans="3:7">
+    <row r="316" spans="1:8">
       <c r="C316" s="6">
         <v>12124</v>
       </c>
@@ -6666,7 +6669,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="317" spans="3:7">
+    <row r="317" spans="1:8">
       <c r="C317" s="6">
         <v>12125</v>
       </c>
@@ -6768,7 +6771,7 @@
         <v>20428</v>
       </c>
     </row>
-    <row r="323" spans="3:7">
+    <row r="323" spans="3:8">
       <c r="C323" s="6">
         <v>12805</v>
       </c>
@@ -6785,7 +6788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="324" spans="3:7">
+    <row r="324" spans="3:8">
       <c r="C324" s="6">
         <v>12806</v>
       </c>
@@ -6802,7 +6805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="3:7">
+    <row r="325" spans="3:8">
       <c r="C325" s="6">
         <v>12807</v>
       </c>
@@ -6819,7 +6822,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="326" spans="3:7">
+    <row r="326" spans="3:8">
       <c r="C326" s="6">
         <v>12808</v>
       </c>
@@ -6836,7 +6839,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="327" spans="3:7">
+    <row r="327" spans="3:8">
       <c r="C327" s="6">
         <v>12809</v>
       </c>
@@ -6853,7 +6856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="328" spans="3:7">
+    <row r="328" spans="3:8">
       <c r="C328" s="6">
         <v>12810</v>
       </c>
@@ -6870,7 +6873,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="329" spans="3:7">
+    <row r="329" spans="3:8">
       <c r="C329" s="6">
         <v>12811</v>
       </c>
@@ -6887,7 +6890,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="330" spans="3:7">
+    <row r="330" spans="3:8">
       <c r="C330" s="6">
         <v>12812</v>
       </c>
@@ -6904,7 +6907,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="331" spans="3:7">
+    <row r="331" spans="3:8">
       <c r="C331" s="6">
         <v>12813</v>
       </c>
@@ -6921,7 +6924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="332" spans="3:7">
+    <row r="332" spans="3:8">
       <c r="C332" s="6">
         <v>12814</v>
       </c>
@@ -6938,7 +6941,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="333" spans="3:7">
+    <row r="333" spans="3:8">
       <c r="C333" s="6">
         <v>12815</v>
       </c>
@@ -6955,7 +6958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="334" spans="3:7">
+    <row r="334" spans="3:8">
       <c r="C334" s="6">
         <v>12816</v>
       </c>
@@ -6972,7 +6975,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" spans="3:7">
+    <row r="335" spans="3:8">
       <c r="C335" s="6">
         <v>12817</v>
       </c>
@@ -6989,7 +6992,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="336" spans="3:7">
+    <row r="336" spans="3:8">
       <c r="C336" s="6">
         <v>12818</v>
       </c>
@@ -7006,7 +7009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="337" spans="3:7">
+    <row r="337" spans="1:8">
       <c r="C337" s="6">
         <v>12819</v>
       </c>
@@ -7023,7 +7026,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="338" spans="3:7">
+    <row r="338" spans="1:8">
       <c r="C338" s="6">
         <v>12820</v>
       </c>
@@ -7040,7 +7043,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="339" spans="3:7">
+    <row r="339" spans="1:8">
       <c r="C339" s="6">
         <v>12821</v>
       </c>
@@ -7057,7 +7060,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="340" spans="3:7">
+    <row r="340" spans="1:8">
       <c r="C340" s="6">
         <v>12822</v>
       </c>
@@ -7074,7 +7077,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="341" spans="3:7">
+    <row r="341" spans="1:8">
       <c r="C341" s="6">
         <v>12823</v>
       </c>
@@ -7091,7 +7094,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="342" spans="3:7">
+    <row r="342" spans="1:8">
       <c r="C342" s="6">
         <v>12824</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="343" spans="3:7">
+    <row r="343" spans="1:8">
       <c r="C343" s="6">
         <v>12825</v>
       </c>
@@ -7170,7 +7173,7 @@
         <v>20476</v>
       </c>
     </row>
-    <row r="347" spans="3:8">
+    <row r="347" spans="1:8">
       <c r="C347" s="6">
         <v>13903</v>
       </c>
@@ -7190,7 +7193,7 @@
         <v>20477</v>
       </c>
     </row>
-    <row r="348" spans="3:8">
+    <row r="348" spans="1:8">
       <c r="C348" s="6">
         <v>13904</v>
       </c>
@@ -7210,7 +7213,7 @@
         <v>20478</v>
       </c>
     </row>
-    <row r="349" spans="3:7">
+    <row r="349" spans="1:8">
       <c r="C349" s="6">
         <v>13905</v>
       </c>
@@ -7227,7 +7230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="350" spans="3:7">
+    <row r="350" spans="1:8">
       <c r="C350" s="6">
         <v>13906</v>
       </c>
@@ -7244,7 +7247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="3:7">
+    <row r="351" spans="1:8">
       <c r="C351" s="6">
         <v>13907</v>
       </c>
@@ -7261,7 +7264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="352" spans="3:7">
+    <row r="352" spans="1:8">
       <c r="C352" s="6">
         <v>13908</v>
       </c>
@@ -7550,7 +7553,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="369" spans="3:7">
+    <row r="369" spans="1:8">
       <c r="C369" s="6">
         <v>13925</v>
       </c>
@@ -7612,7 +7615,7 @@
         <v>20496</v>
       </c>
     </row>
-    <row r="373" spans="3:8">
+    <row r="373" spans="1:8">
       <c r="C373" s="6">
         <v>14703</v>
       </c>
@@ -7632,7 +7635,7 @@
         <v>20497</v>
       </c>
     </row>
-    <row r="374" spans="3:8">
+    <row r="374" spans="1:8">
       <c r="C374" s="6">
         <v>14704</v>
       </c>
@@ -7652,7 +7655,7 @@
         <v>20498</v>
       </c>
     </row>
-    <row r="375" spans="3:7">
+    <row r="375" spans="1:8">
       <c r="C375" s="6">
         <v>14705</v>
       </c>
@@ -7669,7 +7672,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="376" spans="3:7">
+    <row r="376" spans="1:8">
       <c r="C376" s="6">
         <v>14706</v>
       </c>
@@ -7686,7 +7689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="3:7">
+    <row r="377" spans="1:8">
       <c r="C377" s="6">
         <v>14707</v>
       </c>
@@ -7703,7 +7706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="378" spans="3:7">
+    <row r="378" spans="1:8">
       <c r="C378" s="6">
         <v>14708</v>
       </c>
@@ -7720,7 +7723,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="379" spans="3:7">
+    <row r="379" spans="1:8">
       <c r="C379" s="6">
         <v>14709</v>
       </c>
@@ -7737,7 +7740,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="380" spans="3:7">
+    <row r="380" spans="1:8">
       <c r="C380" s="6">
         <v>14710</v>
       </c>
@@ -7754,7 +7757,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="381" spans="3:7">
+    <row r="381" spans="1:8">
       <c r="C381" s="6">
         <v>14711</v>
       </c>
@@ -7771,7 +7774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="382" spans="3:7">
+    <row r="382" spans="1:8">
       <c r="C382" s="6">
         <v>14712</v>
       </c>
@@ -7788,7 +7791,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="383" spans="3:7">
+    <row r="383" spans="1:8">
       <c r="C383" s="6">
         <v>14713</v>
       </c>
@@ -7805,7 +7808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384" spans="3:7">
+    <row r="384" spans="1:8">
       <c r="C384" s="6">
         <v>14714</v>
       </c>
@@ -7822,7 +7825,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="385" spans="3:7">
+    <row r="385" spans="1:8">
       <c r="C385" s="6">
         <v>14715</v>
       </c>
@@ -7839,7 +7842,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="386" spans="3:7">
+    <row r="386" spans="1:8">
       <c r="C386" s="6">
         <v>14716</v>
       </c>
@@ -7856,7 +7859,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" spans="3:7">
+    <row r="387" spans="1:8">
       <c r="C387" s="6">
         <v>14717</v>
       </c>
@@ -7873,7 +7876,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="388" spans="3:7">
+    <row r="388" spans="1:8">
       <c r="C388" s="6">
         <v>14718</v>
       </c>
@@ -7890,7 +7893,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="389" spans="3:7">
+    <row r="389" spans="1:8">
       <c r="C389" s="6">
         <v>14719</v>
       </c>
@@ -7907,7 +7910,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="390" spans="3:7">
+    <row r="390" spans="1:8">
       <c r="C390" s="6">
         <v>14720</v>
       </c>
@@ -7924,7 +7927,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="391" spans="3:7">
+    <row r="391" spans="1:8">
       <c r="C391" s="6">
         <v>14721</v>
       </c>
@@ -7941,7 +7944,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="392" spans="3:7">
+    <row r="392" spans="1:8">
       <c r="C392" s="6">
         <v>14722</v>
       </c>
@@ -7958,7 +7961,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="393" spans="3:7">
+    <row r="393" spans="1:8">
       <c r="C393" s="6">
         <v>14723</v>
       </c>
@@ -7975,7 +7978,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="394" spans="3:7">
+    <row r="394" spans="1:8">
       <c r="C394" s="6">
         <v>14724</v>
       </c>
@@ -7992,7 +7995,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="395" spans="3:7">
+    <row r="395" spans="1:8">
       <c r="C395" s="6">
         <v>14725</v>
       </c>
@@ -8054,7 +8057,7 @@
         <v>20606</v>
       </c>
     </row>
-    <row r="399" spans="3:8">
+    <row r="399" spans="1:8">
       <c r="C399" s="6">
         <v>15503</v>
       </c>
@@ -8074,7 +8077,7 @@
         <v>20607</v>
       </c>
     </row>
-    <row r="400" spans="3:8">
+    <row r="400" spans="1:8">
       <c r="C400" s="6">
         <v>15504</v>
       </c>
@@ -8366,7 +8369,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="417" spans="3:7">
+    <row r="417" spans="1:8">
       <c r="C417" s="6">
         <v>15521</v>
       </c>
@@ -8383,7 +8386,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="418" spans="3:7">
+    <row r="418" spans="1:8">
       <c r="C418" s="6">
         <v>15522</v>
       </c>
@@ -8400,7 +8403,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="419" spans="3:7">
+    <row r="419" spans="1:8">
       <c r="C419" s="6">
         <v>15523</v>
       </c>
@@ -8417,7 +8420,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="420" spans="3:7">
+    <row r="420" spans="1:8">
       <c r="C420" s="6">
         <v>15524</v>
       </c>
@@ -8434,7 +8437,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="421" spans="3:7">
+    <row r="421" spans="1:8">
       <c r="C421" s="6">
         <v>15525</v>
       </c>
@@ -8496,7 +8499,7 @@
         <v>20526</v>
       </c>
     </row>
-    <row r="425" spans="3:8">
+    <row r="425" spans="1:8">
       <c r="C425" s="6">
         <v>16303</v>
       </c>
@@ -8516,7 +8519,7 @@
         <v>20527</v>
       </c>
     </row>
-    <row r="426" spans="3:8">
+    <row r="426" spans="1:8">
       <c r="C426" s="6">
         <v>16304</v>
       </c>
@@ -8536,7 +8539,7 @@
         <v>20528</v>
       </c>
     </row>
-    <row r="427" spans="3:7">
+    <row r="427" spans="1:8">
       <c r="C427" s="6">
         <v>16305</v>
       </c>
@@ -8553,7 +8556,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="428" spans="3:7">
+    <row r="428" spans="1:8">
       <c r="C428" s="6">
         <v>16306</v>
       </c>
@@ -8570,7 +8573,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="3:7">
+    <row r="429" spans="1:8">
       <c r="C429" s="6">
         <v>16307</v>
       </c>
@@ -8587,7 +8590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="3:7">
+    <row r="430" spans="1:8">
       <c r="C430" s="6">
         <v>16308</v>
       </c>
@@ -8604,7 +8607,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="431" spans="3:7">
+    <row r="431" spans="1:8">
       <c r="C431" s="6">
         <v>16309</v>
       </c>
@@ -8621,7 +8624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="432" spans="3:7">
+    <row r="432" spans="1:8">
       <c r="C432" s="6">
         <v>16310</v>
       </c>
@@ -8938,7 +8941,7 @@
         <v>20556</v>
       </c>
     </row>
-    <row r="451" spans="3:8">
+    <row r="451" spans="1:8">
       <c r="C451" s="6">
         <v>16703</v>
       </c>
@@ -8958,7 +8961,7 @@
         <v>20557</v>
       </c>
     </row>
-    <row r="452" spans="3:8">
+    <row r="452" spans="1:8">
       <c r="C452" s="6">
         <v>16704</v>
       </c>
@@ -8978,7 +8981,7 @@
         <v>20558</v>
       </c>
     </row>
-    <row r="453" spans="3:7">
+    <row r="453" spans="1:8">
       <c r="C453" s="6">
         <v>16705</v>
       </c>
@@ -8995,7 +8998,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="454" spans="3:7">
+    <row r="454" spans="1:8">
       <c r="C454" s="6">
         <v>16706</v>
       </c>
@@ -9012,7 +9015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="3:7">
+    <row r="455" spans="1:8">
       <c r="C455" s="6">
         <v>16707</v>
       </c>
@@ -9029,7 +9032,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="456" spans="3:7">
+    <row r="456" spans="1:8">
       <c r="C456" s="6">
         <v>16708</v>
       </c>
@@ -9046,7 +9049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="457" spans="3:7">
+    <row r="457" spans="1:8">
       <c r="C457" s="6">
         <v>16709</v>
       </c>
@@ -9063,7 +9066,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="458" spans="3:7">
+    <row r="458" spans="1:8">
       <c r="C458" s="6">
         <v>16710</v>
       </c>
@@ -9080,7 +9083,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="459" spans="3:7">
+    <row r="459" spans="1:8">
       <c r="C459" s="6">
         <v>16711</v>
       </c>
@@ -9097,7 +9100,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="460" spans="3:7">
+    <row r="460" spans="1:8">
       <c r="C460" s="6">
         <v>16712</v>
       </c>
@@ -9114,7 +9117,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="461" spans="3:7">
+    <row r="461" spans="1:8">
       <c r="C461" s="6">
         <v>16713</v>
       </c>
@@ -9131,7 +9134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="462" spans="3:7">
+    <row r="462" spans="1:8">
       <c r="C462" s="6">
         <v>16714</v>
       </c>
@@ -9148,7 +9151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="463" spans="3:7">
+    <row r="463" spans="1:8">
       <c r="C463" s="6">
         <v>16715</v>
       </c>
@@ -9165,7 +9168,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="464" spans="3:7">
+    <row r="464" spans="1:8">
       <c r="C464" s="6">
         <v>16716</v>
       </c>
@@ -9182,7 +9185,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="465" spans="3:7">
+    <row r="465" spans="1:8">
       <c r="C465" s="6">
         <v>16717</v>
       </c>
@@ -9199,7 +9202,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="466" spans="3:7">
+    <row r="466" spans="1:8">
       <c r="C466" s="6">
         <v>16718</v>
       </c>
@@ -9216,7 +9219,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="467" spans="3:7">
+    <row r="467" spans="1:8">
       <c r="C467" s="6">
         <v>16719</v>
       </c>
@@ -9233,7 +9236,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="468" spans="3:7">
+    <row r="468" spans="1:8">
       <c r="C468" s="6">
         <v>16720</v>
       </c>
@@ -9250,7 +9253,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="469" spans="3:7">
+    <row r="469" spans="1:8">
       <c r="C469" s="6">
         <v>16721</v>
       </c>
@@ -9267,7 +9270,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="470" spans="3:7">
+    <row r="470" spans="1:8">
       <c r="C470" s="6">
         <v>16722</v>
       </c>
@@ -9284,7 +9287,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="471" spans="3:7">
+    <row r="471" spans="1:8">
       <c r="C471" s="6">
         <v>16723</v>
       </c>
@@ -9301,7 +9304,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="472" spans="3:7">
+    <row r="472" spans="1:8">
       <c r="C472" s="6">
         <v>16724</v>
       </c>
@@ -9318,7 +9321,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="473" spans="3:7">
+    <row r="473" spans="1:8">
       <c r="C473" s="6">
         <v>16725</v>
       </c>
@@ -9380,7 +9383,7 @@
         <v>20516</v>
       </c>
     </row>
-    <row r="477" spans="3:8">
+    <row r="477" spans="1:8">
       <c r="C477" s="6">
         <v>16903</v>
       </c>
@@ -9400,7 +9403,7 @@
         <v>20517</v>
       </c>
     </row>
-    <row r="478" spans="3:8">
+    <row r="478" spans="1:8">
       <c r="C478" s="6">
         <v>16904</v>
       </c>
@@ -9420,7 +9423,7 @@
         <v>20518</v>
       </c>
     </row>
-    <row r="479" spans="3:7">
+    <row r="479" spans="1:8">
       <c r="C479" s="6">
         <v>16905</v>
       </c>
@@ -9437,7 +9440,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="480" spans="3:7">
+    <row r="480" spans="1:8">
       <c r="C480" s="6">
         <v>16906</v>
       </c>
@@ -9726,7 +9729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="497" spans="3:7">
+    <row r="497" spans="1:8">
       <c r="C497" s="6">
         <v>16923</v>
       </c>
@@ -9743,7 +9746,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="498" spans="3:7">
+    <row r="498" spans="1:8">
       <c r="C498" s="6">
         <v>16924</v>
       </c>
@@ -9760,7 +9763,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="499" spans="3:7">
+    <row r="499" spans="1:8">
       <c r="C499" s="6">
         <v>16925</v>
       </c>
@@ -9822,7 +9825,7 @@
         <v>20586</v>
       </c>
     </row>
-    <row r="503" spans="3:8">
+    <row r="503" spans="1:8">
       <c r="C503" s="6">
         <v>17203</v>
       </c>
@@ -9842,7 +9845,7 @@
         <v>20587</v>
       </c>
     </row>
-    <row r="504" spans="3:8">
+    <row r="504" spans="1:8">
       <c r="C504" s="6">
         <v>17204</v>
       </c>
@@ -9862,7 +9865,7 @@
         <v>20588</v>
       </c>
     </row>
-    <row r="505" spans="3:7">
+    <row r="505" spans="1:8">
       <c r="C505" s="6">
         <v>17205</v>
       </c>
@@ -9879,7 +9882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="506" spans="3:7">
+    <row r="506" spans="1:8">
       <c r="C506" s="6">
         <v>17206</v>
       </c>
@@ -9896,7 +9899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="507" spans="3:7">
+    <row r="507" spans="1:8">
       <c r="C507" s="6">
         <v>17207</v>
       </c>
@@ -9913,7 +9916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="508" spans="3:7">
+    <row r="508" spans="1:8">
       <c r="C508" s="6">
         <v>17208</v>
       </c>
@@ -9930,7 +9933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="509" spans="3:7">
+    <row r="509" spans="1:8">
       <c r="C509" s="6">
         <v>17209</v>
       </c>
@@ -9947,7 +9950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="510" spans="3:7">
+    <row r="510" spans="1:8">
       <c r="C510" s="6">
         <v>17210</v>
       </c>
@@ -9964,7 +9967,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="511" spans="3:7">
+    <row r="511" spans="1:8">
       <c r="C511" s="6">
         <v>17211</v>
       </c>
@@ -9981,7 +9984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="512" spans="3:7">
+    <row r="512" spans="1:8">
       <c r="C512" s="6">
         <v>17212</v>
       </c>
@@ -9998,7 +10001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="513" spans="3:7">
+    <row r="513" spans="1:8">
       <c r="C513" s="6">
         <v>17213</v>
       </c>
@@ -10015,7 +10018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="514" spans="3:7">
+    <row r="514" spans="1:8">
       <c r="C514" s="6">
         <v>17214</v>
       </c>
@@ -10032,7 +10035,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="515" spans="3:7">
+    <row r="515" spans="1:8">
       <c r="C515" s="6">
         <v>17215</v>
       </c>
@@ -10049,7 +10052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="516" spans="3:7">
+    <row r="516" spans="1:8">
       <c r="C516" s="6">
         <v>17216</v>
       </c>
@@ -10066,7 +10069,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="517" spans="3:7">
+    <row r="517" spans="1:8">
       <c r="C517" s="6">
         <v>17217</v>
       </c>
@@ -10083,7 +10086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="518" spans="3:7">
+    <row r="518" spans="1:8">
       <c r="C518" s="6">
         <v>17218</v>
       </c>
@@ -10100,7 +10103,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="519" spans="3:7">
+    <row r="519" spans="1:8">
       <c r="C519" s="6">
         <v>17219</v>
       </c>
@@ -10117,7 +10120,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="520" spans="3:7">
+    <row r="520" spans="1:8">
       <c r="C520" s="6">
         <v>17220</v>
       </c>
@@ -10134,7 +10137,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="521" spans="3:7">
+    <row r="521" spans="1:8">
       <c r="C521" s="6">
         <v>17221</v>
       </c>
@@ -10151,7 +10154,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="522" spans="3:7">
+    <row r="522" spans="1:8">
       <c r="C522" s="6">
         <v>17222</v>
       </c>
@@ -10168,7 +10171,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="523" spans="3:7">
+    <row r="523" spans="1:8">
       <c r="C523" s="6">
         <v>17223</v>
       </c>
@@ -10185,7 +10188,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="524" spans="3:7">
+    <row r="524" spans="1:8">
       <c r="C524" s="6">
         <v>17224</v>
       </c>
@@ -10202,7 +10205,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="525" spans="3:7">
+    <row r="525" spans="1:8">
       <c r="C525" s="6">
         <v>17225</v>
       </c>
@@ -10304,7 +10307,7 @@
         <v>20448</v>
       </c>
     </row>
-    <row r="531" spans="3:7">
+    <row r="531" spans="3:8">
       <c r="C531" s="6">
         <v>17405</v>
       </c>
@@ -10321,7 +10324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="532" spans="3:7">
+    <row r="532" spans="3:8">
       <c r="C532" s="6">
         <v>17406</v>
       </c>
@@ -10338,7 +10341,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="533" spans="3:7">
+    <row r="533" spans="3:8">
       <c r="C533" s="6">
         <v>17407</v>
       </c>
@@ -10355,7 +10358,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="534" spans="3:7">
+    <row r="534" spans="3:8">
       <c r="C534" s="6">
         <v>17408</v>
       </c>
@@ -10372,7 +10375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="535" spans="3:7">
+    <row r="535" spans="3:8">
       <c r="C535" s="6">
         <v>17409</v>
       </c>
@@ -10389,7 +10392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="536" spans="3:7">
+    <row r="536" spans="3:8">
       <c r="C536" s="6">
         <v>17410</v>
       </c>
@@ -10406,7 +10409,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="537" spans="3:7">
+    <row r="537" spans="3:8">
       <c r="C537" s="6">
         <v>17411</v>
       </c>
@@ -10423,7 +10426,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="538" spans="3:7">
+    <row r="538" spans="3:8">
       <c r="C538" s="6">
         <v>17412</v>
       </c>
@@ -10440,7 +10443,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="539" spans="3:7">
+    <row r="539" spans="3:8">
       <c r="C539" s="6">
         <v>17413</v>
       </c>
@@ -10457,7 +10460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="540" spans="3:7">
+    <row r="540" spans="3:8">
       <c r="C540" s="6">
         <v>17414</v>
       </c>
@@ -10474,7 +10477,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="541" spans="3:7">
+    <row r="541" spans="3:8">
       <c r="C541" s="6">
         <v>17415</v>
       </c>
@@ -10491,7 +10494,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="542" spans="3:7">
+    <row r="542" spans="3:8">
       <c r="C542" s="6">
         <v>17416</v>
       </c>
@@ -10508,7 +10511,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="543" spans="3:7">
+    <row r="543" spans="3:8">
       <c r="C543" s="6">
         <v>17417</v>
       </c>
@@ -10525,7 +10528,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="544" spans="3:7">
+    <row r="544" spans="3:8">
       <c r="C544" s="6">
         <v>17418</v>
       </c>
@@ -10542,7 +10545,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="545" spans="3:7">
+    <row r="545" spans="1:8">
       <c r="C545" s="6">
         <v>17419</v>
       </c>
@@ -10559,7 +10562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="546" spans="3:7">
+    <row r="546" spans="1:8">
       <c r="C546" s="6">
         <v>17420</v>
       </c>
@@ -10576,7 +10579,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="547" spans="3:7">
+    <row r="547" spans="1:8">
       <c r="C547" s="6">
         <v>17421</v>
       </c>
@@ -10593,7 +10596,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="548" spans="3:7">
+    <row r="548" spans="1:8">
       <c r="C548" s="6">
         <v>17422</v>
       </c>
@@ -10610,7 +10613,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="549" spans="3:7">
+    <row r="549" spans="1:8">
       <c r="C549" s="6">
         <v>17423</v>
       </c>
@@ -10627,7 +10630,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="550" spans="3:7">
+    <row r="550" spans="1:8">
       <c r="C550" s="6">
         <v>17424</v>
       </c>
@@ -10644,7 +10647,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="551" spans="3:7">
+    <row r="551" spans="1:8">
       <c r="C551" s="6">
         <v>17425</v>
       </c>
@@ -10706,7 +10709,7 @@
         <v>20456</v>
       </c>
     </row>
-    <row r="555" spans="3:8">
+    <row r="555" spans="1:8">
       <c r="C555" s="6">
         <v>17503</v>
       </c>
@@ -10726,7 +10729,7 @@
         <v>20457</v>
       </c>
     </row>
-    <row r="556" spans="3:8">
+    <row r="556" spans="1:8">
       <c r="C556" s="6">
         <v>17504</v>
       </c>
@@ -10746,7 +10749,7 @@
         <v>20458</v>
       </c>
     </row>
-    <row r="557" spans="3:7">
+    <row r="557" spans="1:8">
       <c r="C557" s="6">
         <v>17505</v>
       </c>
@@ -10763,7 +10766,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="558" spans="3:7">
+    <row r="558" spans="1:8">
       <c r="C558" s="6">
         <v>17506</v>
       </c>
@@ -10780,7 +10783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="3:7">
+    <row r="559" spans="1:8">
       <c r="C559" s="6">
         <v>17507</v>
       </c>
@@ -10797,7 +10800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="560" spans="3:7">
+    <row r="560" spans="1:8">
       <c r="C560" s="6">
         <v>17508</v>
       </c>
@@ -11086,7 +11089,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="577" spans="3:7">
+    <row r="577" spans="1:8">
       <c r="C577" s="6">
         <v>17525</v>
       </c>
@@ -11148,7 +11151,7 @@
         <v>20506</v>
       </c>
     </row>
-    <row r="581" spans="3:8">
+    <row r="581" spans="1:8">
       <c r="C581" s="6">
         <v>17603</v>
       </c>
@@ -11168,7 +11171,7 @@
         <v>20507</v>
       </c>
     </row>
-    <row r="582" spans="3:8">
+    <row r="582" spans="1:8">
       <c r="C582" s="6">
         <v>17604</v>
       </c>
@@ -11188,7 +11191,7 @@
         <v>20508</v>
       </c>
     </row>
-    <row r="583" spans="3:7">
+    <row r="583" spans="1:8">
       <c r="C583" s="6">
         <v>17605</v>
       </c>
@@ -11205,7 +11208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="584" spans="3:7">
+    <row r="584" spans="1:8">
       <c r="C584" s="6">
         <v>17606</v>
       </c>
@@ -11222,7 +11225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="585" spans="3:7">
+    <row r="585" spans="1:8">
       <c r="C585" s="6">
         <v>17607</v>
       </c>
@@ -11239,7 +11242,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="586" spans="3:7">
+    <row r="586" spans="1:8">
       <c r="C586" s="6">
         <v>17608</v>
       </c>
@@ -11256,7 +11259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="587" spans="3:7">
+    <row r="587" spans="1:8">
       <c r="C587" s="6">
         <v>17609</v>
       </c>
@@ -11273,7 +11276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="588" spans="3:7">
+    <row r="588" spans="1:8">
       <c r="C588" s="6">
         <v>17610</v>
       </c>
@@ -11290,7 +11293,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="589" spans="3:7">
+    <row r="589" spans="1:8">
       <c r="C589" s="6">
         <v>17611</v>
       </c>
@@ -11307,7 +11310,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="590" spans="3:7">
+    <row r="590" spans="1:8">
       <c r="C590" s="6">
         <v>17612</v>
       </c>
@@ -11324,7 +11327,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="591" spans="3:7">
+    <row r="591" spans="1:8">
       <c r="C591" s="6">
         <v>17613</v>
       </c>
@@ -11341,7 +11344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="592" spans="3:7">
+    <row r="592" spans="1:8">
       <c r="C592" s="6">
         <v>17614</v>
       </c>
@@ -11358,7 +11361,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="593" spans="3:7">
+    <row r="593" spans="1:8">
       <c r="C593" s="6">
         <v>17615</v>
       </c>
@@ -11375,7 +11378,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="594" spans="3:7">
+    <row r="594" spans="1:8">
       <c r="C594" s="6">
         <v>17616</v>
       </c>
@@ -11392,7 +11395,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="595" spans="3:7">
+    <row r="595" spans="1:8">
       <c r="C595" s="6">
         <v>17617</v>
       </c>
@@ -11409,7 +11412,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="596" spans="3:7">
+    <row r="596" spans="1:8">
       <c r="C596" s="6">
         <v>17618</v>
       </c>
@@ -11426,7 +11429,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="597" spans="3:7">
+    <row r="597" spans="1:8">
       <c r="C597" s="6">
         <v>17619</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="598" spans="3:7">
+    <row r="598" spans="1:8">
       <c r="C598" s="6">
         <v>17620</v>
       </c>
@@ -11460,7 +11463,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="599" spans="3:7">
+    <row r="599" spans="1:8">
       <c r="C599" s="6">
         <v>17621</v>
       </c>
@@ -11477,7 +11480,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="600" spans="3:7">
+    <row r="600" spans="1:8">
       <c r="C600" s="6">
         <v>17622</v>
       </c>
@@ -11494,7 +11497,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="601" spans="3:7">
+    <row r="601" spans="1:8">
       <c r="C601" s="6">
         <v>17623</v>
       </c>
@@ -11511,7 +11514,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="602" spans="3:7">
+    <row r="602" spans="1:8">
       <c r="C602" s="6">
         <v>17624</v>
       </c>
@@ -11528,7 +11531,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="603" spans="3:7">
+    <row r="603" spans="1:8">
       <c r="C603" s="6">
         <v>17625</v>
       </c>
@@ -11590,7 +11593,7 @@
         <v>20546</v>
       </c>
     </row>
-    <row r="607" spans="3:8">
+    <row r="607" spans="1:8">
       <c r="C607" s="6">
         <v>17703</v>
       </c>
@@ -11610,7 +11613,7 @@
         <v>20547</v>
       </c>
     </row>
-    <row r="608" spans="3:8">
+    <row r="608" spans="1:8">
       <c r="C608" s="6">
         <v>17704</v>
       </c>
@@ -11902,7 +11905,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="625" spans="3:7">
+    <row r="625" spans="1:8">
       <c r="C625" s="6">
         <v>17721</v>
       </c>
@@ -11919,7 +11922,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="626" spans="3:7">
+    <row r="626" spans="1:8">
       <c r="C626" s="6">
         <v>17722</v>
       </c>
@@ -11936,7 +11939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="627" spans="3:7">
+    <row r="627" spans="1:8">
       <c r="C627" s="6">
         <v>17723</v>
       </c>
@@ -11953,7 +11956,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="628" spans="3:7">
+    <row r="628" spans="1:8">
       <c r="C628" s="6">
         <v>17724</v>
       </c>
@@ -11970,7 +11973,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="629" spans="3:7">
+    <row r="629" spans="1:8">
       <c r="C629" s="6">
         <v>17725</v>
       </c>
@@ -12032,7 +12035,7 @@
         <v>20566</v>
       </c>
     </row>
-    <row r="633" spans="3:8">
+    <row r="633" spans="1:8">
       <c r="C633" s="6">
         <v>17803</v>
       </c>
@@ -12052,7 +12055,7 @@
         <v>20567</v>
       </c>
     </row>
-    <row r="634" spans="3:8">
+    <row r="634" spans="1:8">
       <c r="C634" s="6">
         <v>17804</v>
       </c>
@@ -12072,7 +12075,7 @@
         <v>20568</v>
       </c>
     </row>
-    <row r="635" spans="3:7">
+    <row r="635" spans="1:8">
       <c r="C635" s="6">
         <v>17805</v>
       </c>
@@ -12089,7 +12092,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="636" spans="3:7">
+    <row r="636" spans="1:8">
       <c r="C636" s="6">
         <v>17806</v>
       </c>
@@ -12106,7 +12109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="3:7">
+    <row r="637" spans="1:8">
       <c r="C637" s="6">
         <v>17807</v>
       </c>
@@ -12123,7 +12126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="638" spans="3:7">
+    <row r="638" spans="1:8">
       <c r="C638" s="6">
         <v>17808</v>
       </c>
@@ -12140,7 +12143,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="639" spans="3:7">
+    <row r="639" spans="1:8">
       <c r="C639" s="6">
         <v>17809</v>
       </c>
@@ -12157,7 +12160,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="640" spans="3:7">
+    <row r="640" spans="1:8">
       <c r="C640" s="6">
         <v>17810</v>
       </c>
@@ -12474,7 +12477,7 @@
         <v>20596</v>
       </c>
     </row>
-    <row r="659" spans="3:8">
+    <row r="659" spans="1:8">
       <c r="C659" s="6">
         <v>17903</v>
       </c>
@@ -12494,7 +12497,7 @@
         <v>20597</v>
       </c>
     </row>
-    <row r="660" spans="3:8">
+    <row r="660" spans="1:8">
       <c r="C660" s="6">
         <v>17904</v>
       </c>
@@ -12514,7 +12517,7 @@
         <v>20598</v>
       </c>
     </row>
-    <row r="661" spans="3:7">
+    <row r="661" spans="1:8">
       <c r="C661" s="6">
         <v>17905</v>
       </c>
@@ -12531,7 +12534,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="662" spans="3:7">
+    <row r="662" spans="1:8">
       <c r="C662" s="6">
         <v>17906</v>
       </c>
@@ -12548,7 +12551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="663" spans="3:7">
+    <row r="663" spans="1:8">
       <c r="C663" s="6">
         <v>17907</v>
       </c>
@@ -12565,7 +12568,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="664" spans="3:7">
+    <row r="664" spans="1:8">
       <c r="C664" s="6">
         <v>17908</v>
       </c>
@@ -12582,7 +12585,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="665" spans="3:7">
+    <row r="665" spans="1:8">
       <c r="C665" s="6">
         <v>17909</v>
       </c>
@@ -12599,7 +12602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="666" spans="3:7">
+    <row r="666" spans="1:8">
       <c r="C666" s="6">
         <v>17910</v>
       </c>
@@ -12616,7 +12619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="667" spans="3:7">
+    <row r="667" spans="1:8">
       <c r="C667" s="6">
         <v>17911</v>
       </c>
@@ -12633,7 +12636,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="668" spans="3:7">
+    <row r="668" spans="1:8">
       <c r="C668" s="6">
         <v>17912</v>
       </c>
@@ -12650,7 +12653,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="669" spans="3:7">
+    <row r="669" spans="1:8">
       <c r="C669" s="6">
         <v>17913</v>
       </c>
@@ -12667,7 +12670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="670" spans="3:7">
+    <row r="670" spans="1:8">
       <c r="C670" s="6">
         <v>17914</v>
       </c>
@@ -12684,7 +12687,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="671" spans="3:7">
+    <row r="671" spans="1:8">
       <c r="C671" s="6">
         <v>17915</v>
       </c>
@@ -12701,7 +12704,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="672" spans="3:7">
+    <row r="672" spans="1:8">
       <c r="C672" s="6">
         <v>17916</v>
       </c>
@@ -12718,7 +12721,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="673" spans="3:7">
+    <row r="673" spans="1:8">
       <c r="C673" s="6">
         <v>17917</v>
       </c>
@@ -12735,7 +12738,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="674" spans="3:7">
+    <row r="674" spans="1:8">
       <c r="C674" s="6">
         <v>17918</v>
       </c>
@@ -12752,7 +12755,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="675" spans="3:7">
+    <row r="675" spans="1:8">
       <c r="C675" s="6">
         <v>17919</v>
       </c>
@@ -12769,7 +12772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="676" spans="3:7">
+    <row r="676" spans="1:8">
       <c r="C676" s="6">
         <v>17920</v>
       </c>
@@ -12786,7 +12789,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="677" spans="3:7">
+    <row r="677" spans="1:8">
       <c r="C677" s="6">
         <v>17921</v>
       </c>
@@ -12803,7 +12806,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="678" spans="3:7">
+    <row r="678" spans="1:8">
       <c r="C678" s="6">
         <v>17922</v>
       </c>
@@ -12820,7 +12823,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="679" spans="3:7">
+    <row r="679" spans="1:8">
       <c r="C679" s="6">
         <v>17923</v>
       </c>
@@ -12837,7 +12840,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="680" spans="3:7">
+    <row r="680" spans="1:8">
       <c r="C680" s="6">
         <v>17924</v>
       </c>
@@ -12854,7 +12857,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="681" spans="3:7">
+    <row r="681" spans="1:8">
       <c r="C681" s="6">
         <v>17925</v>
       </c>
@@ -12916,7 +12919,7 @@
         <v>20376</v>
       </c>
     </row>
-    <row r="685" spans="3:8">
+    <row r="685" spans="1:8">
       <c r="C685" s="6">
         <v>18003</v>
       </c>
@@ -12936,7 +12939,7 @@
         <v>20377</v>
       </c>
     </row>
-    <row r="686" spans="3:8">
+    <row r="686" spans="1:8">
       <c r="C686" s="6">
         <v>18004</v>
       </c>
@@ -12956,7 +12959,7 @@
         <v>20378</v>
       </c>
     </row>
-    <row r="687" spans="3:7">
+    <row r="687" spans="1:8">
       <c r="C687" s="6">
         <v>18005</v>
       </c>
@@ -12973,7 +12976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="688" spans="3:7">
+    <row r="688" spans="1:8">
       <c r="C688" s="6">
         <v>18006</v>
       </c>
@@ -13262,7 +13265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="3:7">
+    <row r="705" spans="1:8">
       <c r="C705" s="6">
         <v>18023</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="3:7">
+    <row r="706" spans="1:8">
       <c r="C706" s="6">
         <v>18024</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="3:7">
+    <row r="707" spans="1:8">
       <c r="C707" s="6">
         <v>18025</v>
       </c>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>18101</v>
+      </c>
+      <c r="D709" s="3">
+        <v>181</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20405</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>18102</v>
+      </c>
+      <c r="D710" s="3">
+        <v>181</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20406</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="C711" s="6">
+        <v>18103</v>
+      </c>
+      <c r="D711" s="3">
+        <v>181</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20407</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="C712" s="6">
+        <v>18104</v>
+      </c>
+      <c r="D712" s="3">
+        <v>181</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20408</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="C713" s="6">
+        <v>18105</v>
+      </c>
+      <c r="D713" s="3">
+        <v>181</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="C714" s="6">
+        <v>18106</v>
+      </c>
+      <c r="D714" s="3">
+        <v>181</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="C715" s="6">
+        <v>18107</v>
+      </c>
+      <c r="D715" s="3">
+        <v>181</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="C716" s="6">
+        <v>18108</v>
+      </c>
+      <c r="D716" s="3">
+        <v>181</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="C717" s="6">
+        <v>18109</v>
+      </c>
+      <c r="D717" s="3">
+        <v>181</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="C718" s="6">
+        <v>18110</v>
+      </c>
+      <c r="D718" s="3">
+        <v>181</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="C719" s="6">
+        <v>18111</v>
+      </c>
+      <c r="D719" s="3">
+        <v>181</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="C720" s="6">
+        <v>18112</v>
+      </c>
+      <c r="D720" s="3">
+        <v>181</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>18113</v>
+      </c>
+      <c r="D721" s="3">
+        <v>181</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>18114</v>
+      </c>
+      <c r="D722" s="3">
+        <v>181</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>18115</v>
+      </c>
+      <c r="D723" s="3">
+        <v>181</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>18116</v>
+      </c>
+      <c r="D724" s="3">
+        <v>181</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>18117</v>
+      </c>
+      <c r="D725" s="3">
+        <v>181</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>18118</v>
+      </c>
+      <c r="D726" s="3">
+        <v>181</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>18119</v>
+      </c>
+      <c r="D727" s="3">
+        <v>181</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>18120</v>
+      </c>
+      <c r="D728" s="3">
+        <v>181</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>18121</v>
+      </c>
+      <c r="D729" s="3">
+        <v>181</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>18122</v>
+      </c>
+      <c r="D730" s="3">
+        <v>181</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>18123</v>
+      </c>
+      <c r="D731" s="3">
+        <v>181</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>18124</v>
+      </c>
+      <c r="D732" s="3">
+        <v>181</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>18125</v>
+      </c>
+      <c r="D733" s="3">
+        <v>181</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,14 +13875,14 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" s="1" customFormat="1" ht="14.25" spans="3:8">
+    <row r="7" s="1" customFormat="1" ht="14.25" spans="1:8">
       <c r="C7" s="5">
         <v>20202</v>
       </c>
@@ -13448,14 +13893,14 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="14.25" spans="3:8">
+    <row r="8" s="2" customFormat="1" ht="14.25" spans="1:8">
       <c r="C8" s="5">
         <v>20203</v>
       </c>
@@ -13466,14 +13911,14 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" ht="14.25" spans="3:8">
+    <row r="9" ht="14.25" spans="1:8">
       <c r="C9" s="5">
         <v>20204</v>
       </c>
@@ -13484,16 +13929,16 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="3:7">
+    <row r="10" ht="14.25" spans="1:8">
       <c r="C10" s="5">
         <v>20205</v>
       </c>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,14 +14047,14 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>
-    <row r="8" spans="7:7">
+    <row r="8" spans="3:8">
       <c r="G8" s="1"/>
     </row>
   </sheetData>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋181浮生若梦</t>
+  </si>
+  <si>
+    <t>#先锋182</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13537,7 +13540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="721" spans="3:7">
+    <row r="721" spans="1:8">
       <c r="C721" s="6">
         <v>18113</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="3:7">
+    <row r="722" spans="1:8">
       <c r="C722" s="6">
         <v>18114</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="723" spans="3:7">
+    <row r="723" spans="1:8">
       <c r="C723" s="6">
         <v>18115</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="724" spans="3:7">
+    <row r="724" spans="1:8">
       <c r="C724" s="6">
         <v>18116</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="725" spans="3:7">
+    <row r="725" spans="1:8">
       <c r="C725" s="6">
         <v>18117</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="3:7">
+    <row r="726" spans="1:8">
       <c r="C726" s="6">
         <v>18118</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="727" spans="3:7">
+    <row r="727" spans="1:8">
       <c r="C727" s="6">
         <v>18119</v>
       </c>
@@ -13656,7 +13659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="728" spans="3:7">
+    <row r="728" spans="1:8">
       <c r="C728" s="6">
         <v>18120</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="729" spans="3:7">
+    <row r="729" spans="1:8">
       <c r="C729" s="6">
         <v>18121</v>
       </c>
@@ -13690,7 +13693,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="730" spans="3:7">
+    <row r="730" spans="1:8">
       <c r="C730" s="6">
         <v>18122</v>
       </c>
@@ -13707,7 +13710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="731" spans="3:7">
+    <row r="731" spans="1:8">
       <c r="C731" s="6">
         <v>18123</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="732" spans="3:7">
+    <row r="732" spans="1:8">
       <c r="C732" s="6">
         <v>18124</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="733" spans="3:7">
+    <row r="733" spans="1:8">
       <c r="C733" s="6">
         <v>18125</v>
       </c>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>18201</v>
+      </c>
+      <c r="D735" s="3">
+        <v>182</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20415</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>18202</v>
+      </c>
+      <c r="D736" s="3">
+        <v>182</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20416</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>18203</v>
+      </c>
+      <c r="D737" s="3">
+        <v>182</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20417</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>18204</v>
+      </c>
+      <c r="D738" s="3">
+        <v>182</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20418</v>
+      </c>
+    </row>
+    <row r="739" spans="3:8">
+      <c r="C739" s="6">
+        <v>18205</v>
+      </c>
+      <c r="D739" s="3">
+        <v>182</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:8">
+      <c r="C740" s="6">
+        <v>18206</v>
+      </c>
+      <c r="D740" s="3">
+        <v>182</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:8">
+      <c r="C741" s="6">
+        <v>18207</v>
+      </c>
+      <c r="D741" s="3">
+        <v>182</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:8">
+      <c r="C742" s="6">
+        <v>18208</v>
+      </c>
+      <c r="D742" s="3">
+        <v>182</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:8">
+      <c r="C743" s="6">
+        <v>18209</v>
+      </c>
+      <c r="D743" s="3">
+        <v>182</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:8">
+      <c r="C744" s="6">
+        <v>18210</v>
+      </c>
+      <c r="D744" s="3">
+        <v>182</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:8">
+      <c r="C745" s="6">
+        <v>18211</v>
+      </c>
+      <c r="D745" s="3">
+        <v>182</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:8">
+      <c r="C746" s="6">
+        <v>18212</v>
+      </c>
+      <c r="D746" s="3">
+        <v>182</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:8">
+      <c r="C747" s="6">
+        <v>18213</v>
+      </c>
+      <c r="D747" s="3">
+        <v>182</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:8">
+      <c r="C748" s="6">
+        <v>18214</v>
+      </c>
+      <c r="D748" s="3">
+        <v>182</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:8">
+      <c r="C749" s="6">
+        <v>18215</v>
+      </c>
+      <c r="D749" s="3">
+        <v>182</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:8">
+      <c r="C750" s="6">
+        <v>18216</v>
+      </c>
+      <c r="D750" s="3">
+        <v>182</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:8">
+      <c r="C751" s="6">
+        <v>18217</v>
+      </c>
+      <c r="D751" s="3">
+        <v>182</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:8">
+      <c r="C752" s="6">
+        <v>18218</v>
+      </c>
+      <c r="D752" s="3">
+        <v>182</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>18219</v>
+      </c>
+      <c r="D753" s="3">
+        <v>182</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>18220</v>
+      </c>
+      <c r="D754" s="3">
+        <v>182</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>18221</v>
+      </c>
+      <c r="D755" s="3">
+        <v>182</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>18222</v>
+      </c>
+      <c r="D756" s="3">
+        <v>182</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>18223</v>
+      </c>
+      <c r="D757" s="3">
+        <v>182</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>18224</v>
+      </c>
+      <c r="D758" s="3">
+        <v>182</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>18225</v>
+      </c>
+      <c r="D759" s="3">
+        <v>182</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
   <si>
     <t>Id</t>
   </si>
@@ -211,22 +211,13 @@
     <t>#先锋167青云之巅</t>
   </si>
   <si>
-    <t>#先锋169决战之巅</t>
-  </si>
-  <si>
     <t>#先锋172星辰殿堂</t>
   </si>
   <si>
     <t>#先锋174龙息之谷</t>
   </si>
   <si>
-    <t>#先锋175星界回廊</t>
-  </si>
-  <si>
     <t>#先锋176普天同庆</t>
-  </si>
-  <si>
-    <t>#先锋177长安旧梦</t>
   </si>
   <si>
     <t>#先锋178风暴之地</t>
@@ -241,7 +232,7 @@
     <t>#先锋181浮生若梦</t>
   </si>
   <si>
-    <t>#先锋182</t>
+    <t>#先锋182泰坦之锤</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O681"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -9346,10 +9337,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>16901</v>
+        <v>17201</v>
       </c>
       <c r="D475" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9361,17 +9352,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20515</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>16902</v>
+        <v>17202</v>
       </c>
       <c r="D476" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9383,15 +9374,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20516</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="477" spans="1:8">
       <c r="C477" s="6">
-        <v>16903</v>
+        <v>17203</v>
       </c>
       <c r="D477" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9403,15 +9394,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20517</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="478" spans="1:8">
       <c r="C478" s="6">
-        <v>16904</v>
+        <v>17204</v>
       </c>
       <c r="D478" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9423,15 +9414,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20518</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="479" spans="1:8">
       <c r="C479" s="6">
-        <v>16905</v>
+        <v>17205</v>
       </c>
       <c r="D479" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9445,10 +9436,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="C480" s="6">
-        <v>16906</v>
+        <v>17206</v>
       </c>
       <c r="D480" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9462,10 +9453,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>16907</v>
+        <v>17207</v>
       </c>
       <c r="D481" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9479,10 +9470,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>16908</v>
+        <v>17208</v>
       </c>
       <c r="D482" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9496,10 +9487,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>16909</v>
+        <v>17209</v>
       </c>
       <c r="D483" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9513,10 +9504,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>16910</v>
+        <v>17210</v>
       </c>
       <c r="D484" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9530,10 +9521,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>16911</v>
+        <v>17211</v>
       </c>
       <c r="D485" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9547,10 +9538,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>16912</v>
+        <v>17212</v>
       </c>
       <c r="D486" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9564,10 +9555,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>16913</v>
+        <v>17213</v>
       </c>
       <c r="D487" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9581,10 +9572,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>16914</v>
+        <v>17214</v>
       </c>
       <c r="D488" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9598,10 +9589,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>16915</v>
+        <v>17215</v>
       </c>
       <c r="D489" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9615,10 +9606,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>16916</v>
+        <v>17216</v>
       </c>
       <c r="D490" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9632,10 +9623,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>16917</v>
+        <v>17217</v>
       </c>
       <c r="D491" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9649,10 +9640,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>16918</v>
+        <v>17218</v>
       </c>
       <c r="D492" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9666,10 +9657,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>16919</v>
+        <v>17219</v>
       </c>
       <c r="D493" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9683,10 +9674,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>16920</v>
+        <v>17220</v>
       </c>
       <c r="D494" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9700,10 +9691,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>16921</v>
+        <v>17221</v>
       </c>
       <c r="D495" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9717,10 +9708,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>16922</v>
+        <v>17222</v>
       </c>
       <c r="D496" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9734,10 +9725,10 @@
     </row>
     <row r="497" spans="1:8">
       <c r="C497" s="6">
-        <v>16923</v>
+        <v>17223</v>
       </c>
       <c r="D497" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9751,10 +9742,10 @@
     </row>
     <row r="498" spans="1:8">
       <c r="C498" s="6">
-        <v>16924</v>
+        <v>17224</v>
       </c>
       <c r="D498" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9768,10 +9759,10 @@
     </row>
     <row r="499" spans="1:8">
       <c r="C499" s="6">
-        <v>16925</v>
+        <v>17225</v>
       </c>
       <c r="D499" s="3">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9788,10 +9779,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>17201</v>
+        <v>17401</v>
       </c>
       <c r="D501" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9803,17 +9794,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20585</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>17202</v>
+        <v>17402</v>
       </c>
       <c r="D502" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9825,15 +9816,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20586</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="503" spans="1:8">
       <c r="C503" s="6">
-        <v>17203</v>
+        <v>17403</v>
       </c>
       <c r="D503" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9845,15 +9836,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20587</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="504" spans="1:8">
       <c r="C504" s="6">
-        <v>17204</v>
+        <v>17404</v>
       </c>
       <c r="D504" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9865,15 +9856,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20588</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="C505" s="6">
-        <v>17205</v>
+        <v>17405</v>
       </c>
       <c r="D505" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9887,10 +9878,10 @@
     </row>
     <row r="506" spans="1:8">
       <c r="C506" s="6">
-        <v>17206</v>
+        <v>17406</v>
       </c>
       <c r="D506" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9904,10 +9895,10 @@
     </row>
     <row r="507" spans="1:8">
       <c r="C507" s="6">
-        <v>17207</v>
+        <v>17407</v>
       </c>
       <c r="D507" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9921,10 +9912,10 @@
     </row>
     <row r="508" spans="1:8">
       <c r="C508" s="6">
-        <v>17208</v>
+        <v>17408</v>
       </c>
       <c r="D508" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9938,10 +9929,10 @@
     </row>
     <row r="509" spans="1:8">
       <c r="C509" s="6">
-        <v>17209</v>
+        <v>17409</v>
       </c>
       <c r="D509" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9955,10 +9946,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="C510" s="6">
-        <v>17210</v>
+        <v>17410</v>
       </c>
       <c r="D510" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9972,10 +9963,10 @@
     </row>
     <row r="511" spans="1:8">
       <c r="C511" s="6">
-        <v>17211</v>
+        <v>17411</v>
       </c>
       <c r="D511" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9989,10 +9980,10 @@
     </row>
     <row r="512" spans="1:8">
       <c r="C512" s="6">
-        <v>17212</v>
+        <v>17412</v>
       </c>
       <c r="D512" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10006,10 +9997,10 @@
     </row>
     <row r="513" spans="1:8">
       <c r="C513" s="6">
-        <v>17213</v>
+        <v>17413</v>
       </c>
       <c r="D513" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10023,10 +10014,10 @@
     </row>
     <row r="514" spans="1:8">
       <c r="C514" s="6">
-        <v>17214</v>
+        <v>17414</v>
       </c>
       <c r="D514" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10040,10 +10031,10 @@
     </row>
     <row r="515" spans="1:8">
       <c r="C515" s="6">
-        <v>17215</v>
+        <v>17415</v>
       </c>
       <c r="D515" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10057,10 +10048,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="C516" s="6">
-        <v>17216</v>
+        <v>17416</v>
       </c>
       <c r="D516" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10074,10 +10065,10 @@
     </row>
     <row r="517" spans="1:8">
       <c r="C517" s="6">
-        <v>17217</v>
+        <v>17417</v>
       </c>
       <c r="D517" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10091,10 +10082,10 @@
     </row>
     <row r="518" spans="1:8">
       <c r="C518" s="6">
-        <v>17218</v>
+        <v>17418</v>
       </c>
       <c r="D518" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10108,10 +10099,10 @@
     </row>
     <row r="519" spans="1:8">
       <c r="C519" s="6">
-        <v>17219</v>
+        <v>17419</v>
       </c>
       <c r="D519" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10125,10 +10116,10 @@
     </row>
     <row r="520" spans="1:8">
       <c r="C520" s="6">
-        <v>17220</v>
+        <v>17420</v>
       </c>
       <c r="D520" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10142,10 +10133,10 @@
     </row>
     <row r="521" spans="1:8">
       <c r="C521" s="6">
-        <v>17221</v>
+        <v>17421</v>
       </c>
       <c r="D521" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10159,10 +10150,10 @@
     </row>
     <row r="522" spans="1:8">
       <c r="C522" s="6">
-        <v>17222</v>
+        <v>17422</v>
       </c>
       <c r="D522" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10176,10 +10167,10 @@
     </row>
     <row r="523" spans="1:8">
       <c r="C523" s="6">
-        <v>17223</v>
+        <v>17423</v>
       </c>
       <c r="D523" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10193,10 +10184,10 @@
     </row>
     <row r="524" spans="1:8">
       <c r="C524" s="6">
-        <v>17224</v>
+        <v>17424</v>
       </c>
       <c r="D524" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10210,10 +10201,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="C525" s="6">
-        <v>17225</v>
+        <v>17425</v>
       </c>
       <c r="D525" s="3">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10230,10 +10221,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>17401</v>
+        <v>17601</v>
       </c>
       <c r="D527" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10245,17 +10236,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20445</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>17402</v>
+        <v>17602</v>
       </c>
       <c r="D528" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10267,15 +10258,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20446</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>17403</v>
+        <v>17603</v>
       </c>
       <c r="D529" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10287,15 +10278,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20447</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>17404</v>
+        <v>17604</v>
       </c>
       <c r="D530" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10307,15 +10298,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20448</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="531" spans="3:8">
       <c r="C531" s="6">
-        <v>17405</v>
+        <v>17605</v>
       </c>
       <c r="D531" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10329,10 +10320,10 @@
     </row>
     <row r="532" spans="3:8">
       <c r="C532" s="6">
-        <v>17406</v>
+        <v>17606</v>
       </c>
       <c r="D532" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10346,10 +10337,10 @@
     </row>
     <row r="533" spans="3:8">
       <c r="C533" s="6">
-        <v>17407</v>
+        <v>17607</v>
       </c>
       <c r="D533" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10363,10 +10354,10 @@
     </row>
     <row r="534" spans="3:8">
       <c r="C534" s="6">
-        <v>17408</v>
+        <v>17608</v>
       </c>
       <c r="D534" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10380,10 +10371,10 @@
     </row>
     <row r="535" spans="3:8">
       <c r="C535" s="6">
-        <v>17409</v>
+        <v>17609</v>
       </c>
       <c r="D535" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10397,10 +10388,10 @@
     </row>
     <row r="536" spans="3:8">
       <c r="C536" s="6">
-        <v>17410</v>
+        <v>17610</v>
       </c>
       <c r="D536" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10414,10 +10405,10 @@
     </row>
     <row r="537" spans="3:8">
       <c r="C537" s="6">
-        <v>17411</v>
+        <v>17611</v>
       </c>
       <c r="D537" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10431,10 +10422,10 @@
     </row>
     <row r="538" spans="3:8">
       <c r="C538" s="6">
-        <v>17412</v>
+        <v>17612</v>
       </c>
       <c r="D538" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10448,10 +10439,10 @@
     </row>
     <row r="539" spans="3:8">
       <c r="C539" s="6">
-        <v>17413</v>
+        <v>17613</v>
       </c>
       <c r="D539" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10465,10 +10456,10 @@
     </row>
     <row r="540" spans="3:8">
       <c r="C540" s="6">
-        <v>17414</v>
+        <v>17614</v>
       </c>
       <c r="D540" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10482,10 +10473,10 @@
     </row>
     <row r="541" spans="3:8">
       <c r="C541" s="6">
-        <v>17415</v>
+        <v>17615</v>
       </c>
       <c r="D541" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10499,10 +10490,10 @@
     </row>
     <row r="542" spans="3:8">
       <c r="C542" s="6">
-        <v>17416</v>
+        <v>17616</v>
       </c>
       <c r="D542" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10516,10 +10507,10 @@
     </row>
     <row r="543" spans="3:8">
       <c r="C543" s="6">
-        <v>17417</v>
+        <v>17617</v>
       </c>
       <c r="D543" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10533,10 +10524,10 @@
     </row>
     <row r="544" spans="3:8">
       <c r="C544" s="6">
-        <v>17418</v>
+        <v>17618</v>
       </c>
       <c r="D544" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10550,10 +10541,10 @@
     </row>
     <row r="545" spans="1:8">
       <c r="C545" s="6">
-        <v>17419</v>
+        <v>17619</v>
       </c>
       <c r="D545" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10567,10 +10558,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="C546" s="6">
-        <v>17420</v>
+        <v>17620</v>
       </c>
       <c r="D546" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10584,10 +10575,10 @@
     </row>
     <row r="547" spans="1:8">
       <c r="C547" s="6">
-        <v>17421</v>
+        <v>17621</v>
       </c>
       <c r="D547" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10601,10 +10592,10 @@
     </row>
     <row r="548" spans="1:8">
       <c r="C548" s="6">
-        <v>17422</v>
+        <v>17622</v>
       </c>
       <c r="D548" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10618,10 +10609,10 @@
     </row>
     <row r="549" spans="1:8">
       <c r="C549" s="6">
-        <v>17423</v>
+        <v>17623</v>
       </c>
       <c r="D549" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10635,10 +10626,10 @@
     </row>
     <row r="550" spans="1:8">
       <c r="C550" s="6">
-        <v>17424</v>
+        <v>17624</v>
       </c>
       <c r="D550" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10652,10 +10643,10 @@
     </row>
     <row r="551" spans="1:8">
       <c r="C551" s="6">
-        <v>17425</v>
+        <v>17625</v>
       </c>
       <c r="D551" s="3">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10672,10 +10663,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>17501</v>
+        <v>17801</v>
       </c>
       <c r="D553" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10687,17 +10678,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20455</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>17502</v>
+        <v>17802</v>
       </c>
       <c r="D554" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10709,15 +10700,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20456</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="555" spans="1:8">
       <c r="C555" s="6">
-        <v>17503</v>
+        <v>17803</v>
       </c>
       <c r="D555" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10729,15 +10720,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20457</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="556" spans="1:8">
       <c r="C556" s="6">
-        <v>17504</v>
+        <v>17804</v>
       </c>
       <c r="D556" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10749,15 +10740,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20458</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="557" spans="1:8">
       <c r="C557" s="6">
-        <v>17505</v>
+        <v>17805</v>
       </c>
       <c r="D557" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10771,10 +10762,10 @@
     </row>
     <row r="558" spans="1:8">
       <c r="C558" s="6">
-        <v>17506</v>
+        <v>17806</v>
       </c>
       <c r="D558" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10788,10 +10779,10 @@
     </row>
     <row r="559" spans="1:8">
       <c r="C559" s="6">
-        <v>17507</v>
+        <v>17807</v>
       </c>
       <c r="D559" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10805,10 +10796,10 @@
     </row>
     <row r="560" spans="1:8">
       <c r="C560" s="6">
-        <v>17508</v>
+        <v>17808</v>
       </c>
       <c r="D560" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10822,10 +10813,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>17509</v>
+        <v>17809</v>
       </c>
       <c r="D561" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10839,10 +10830,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>17510</v>
+        <v>17810</v>
       </c>
       <c r="D562" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10856,10 +10847,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>17511</v>
+        <v>17811</v>
       </c>
       <c r="D563" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10873,10 +10864,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>17512</v>
+        <v>17812</v>
       </c>
       <c r="D564" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10890,10 +10881,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>17513</v>
+        <v>17813</v>
       </c>
       <c r="D565" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10907,10 +10898,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>17514</v>
+        <v>17814</v>
       </c>
       <c r="D566" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10924,10 +10915,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>17515</v>
+        <v>17815</v>
       </c>
       <c r="D567" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10941,10 +10932,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>17516</v>
+        <v>17816</v>
       </c>
       <c r="D568" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10958,10 +10949,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>17517</v>
+        <v>17817</v>
       </c>
       <c r="D569" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10975,10 +10966,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>17518</v>
+        <v>17818</v>
       </c>
       <c r="D570" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10992,10 +10983,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>17519</v>
+        <v>17819</v>
       </c>
       <c r="D571" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11009,10 +11000,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>17520</v>
+        <v>17820</v>
       </c>
       <c r="D572" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11026,10 +11017,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>17521</v>
+        <v>17821</v>
       </c>
       <c r="D573" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11043,10 +11034,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>17522</v>
+        <v>17822</v>
       </c>
       <c r="D574" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11060,10 +11051,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>17523</v>
+        <v>17823</v>
       </c>
       <c r="D575" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11077,10 +11068,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>17524</v>
+        <v>17824</v>
       </c>
       <c r="D576" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11094,10 +11085,10 @@
     </row>
     <row r="577" spans="1:8">
       <c r="C577" s="6">
-        <v>17525</v>
+        <v>17825</v>
       </c>
       <c r="D577" s="3">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11114,10 +11105,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>17601</v>
+        <v>17901</v>
       </c>
       <c r="D579" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11129,17 +11120,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20505</v>
+        <v>20595</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>17602</v>
+        <v>17902</v>
       </c>
       <c r="D580" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11151,15 +11142,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20506</v>
+        <v>20596</v>
       </c>
     </row>
     <row r="581" spans="1:8">
       <c r="C581" s="6">
-        <v>17603</v>
+        <v>17903</v>
       </c>
       <c r="D581" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11171,15 +11162,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20507</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="582" spans="1:8">
       <c r="C582" s="6">
-        <v>17604</v>
+        <v>17904</v>
       </c>
       <c r="D582" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11191,15 +11182,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20508</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="583" spans="1:8">
       <c r="C583" s="6">
-        <v>17605</v>
+        <v>17905</v>
       </c>
       <c r="D583" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11213,10 +11204,10 @@
     </row>
     <row r="584" spans="1:8">
       <c r="C584" s="6">
-        <v>17606</v>
+        <v>17906</v>
       </c>
       <c r="D584" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11230,10 +11221,10 @@
     </row>
     <row r="585" spans="1:8">
       <c r="C585" s="6">
-        <v>17607</v>
+        <v>17907</v>
       </c>
       <c r="D585" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11247,10 +11238,10 @@
     </row>
     <row r="586" spans="1:8">
       <c r="C586" s="6">
-        <v>17608</v>
+        <v>17908</v>
       </c>
       <c r="D586" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11264,10 +11255,10 @@
     </row>
     <row r="587" spans="1:8">
       <c r="C587" s="6">
-        <v>17609</v>
+        <v>17909</v>
       </c>
       <c r="D587" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11281,10 +11272,10 @@
     </row>
     <row r="588" spans="1:8">
       <c r="C588" s="6">
-        <v>17610</v>
+        <v>17910</v>
       </c>
       <c r="D588" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11298,10 +11289,10 @@
     </row>
     <row r="589" spans="1:8">
       <c r="C589" s="6">
-        <v>17611</v>
+        <v>17911</v>
       </c>
       <c r="D589" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11315,10 +11306,10 @@
     </row>
     <row r="590" spans="1:8">
       <c r="C590" s="6">
-        <v>17612</v>
+        <v>17912</v>
       </c>
       <c r="D590" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11332,10 +11323,10 @@
     </row>
     <row r="591" spans="1:8">
       <c r="C591" s="6">
-        <v>17613</v>
+        <v>17913</v>
       </c>
       <c r="D591" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11349,10 +11340,10 @@
     </row>
     <row r="592" spans="1:8">
       <c r="C592" s="6">
-        <v>17614</v>
+        <v>17914</v>
       </c>
       <c r="D592" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11366,10 +11357,10 @@
     </row>
     <row r="593" spans="1:8">
       <c r="C593" s="6">
-        <v>17615</v>
+        <v>17915</v>
       </c>
       <c r="D593" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11383,10 +11374,10 @@
     </row>
     <row r="594" spans="1:8">
       <c r="C594" s="6">
-        <v>17616</v>
+        <v>17916</v>
       </c>
       <c r="D594" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11400,10 +11391,10 @@
     </row>
     <row r="595" spans="1:8">
       <c r="C595" s="6">
-        <v>17617</v>
+        <v>17917</v>
       </c>
       <c r="D595" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11417,10 +11408,10 @@
     </row>
     <row r="596" spans="1:8">
       <c r="C596" s="6">
-        <v>17618</v>
+        <v>17918</v>
       </c>
       <c r="D596" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11434,10 +11425,10 @@
     </row>
     <row r="597" spans="1:8">
       <c r="C597" s="6">
-        <v>17619</v>
+        <v>17919</v>
       </c>
       <c r="D597" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11451,10 +11442,10 @@
     </row>
     <row r="598" spans="1:8">
       <c r="C598" s="6">
-        <v>17620</v>
+        <v>17920</v>
       </c>
       <c r="D598" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11468,10 +11459,10 @@
     </row>
     <row r="599" spans="1:8">
       <c r="C599" s="6">
-        <v>17621</v>
+        <v>17921</v>
       </c>
       <c r="D599" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11485,10 +11476,10 @@
     </row>
     <row r="600" spans="1:8">
       <c r="C600" s="6">
-        <v>17622</v>
+        <v>17922</v>
       </c>
       <c r="D600" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11502,10 +11493,10 @@
     </row>
     <row r="601" spans="1:8">
       <c r="C601" s="6">
-        <v>17623</v>
+        <v>17923</v>
       </c>
       <c r="D601" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11519,10 +11510,10 @@
     </row>
     <row r="602" spans="1:8">
       <c r="C602" s="6">
-        <v>17624</v>
+        <v>17924</v>
       </c>
       <c r="D602" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11536,10 +11527,10 @@
     </row>
     <row r="603" spans="1:8">
       <c r="C603" s="6">
-        <v>17625</v>
+        <v>17925</v>
       </c>
       <c r="D603" s="3">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11556,10 +11547,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>17701</v>
+        <v>18001</v>
       </c>
       <c r="D605" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11571,17 +11562,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20545</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>17702</v>
+        <v>18002</v>
       </c>
       <c r="D606" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11593,15 +11584,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20546</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="607" spans="1:8">
       <c r="C607" s="6">
-        <v>17703</v>
+        <v>18003</v>
       </c>
       <c r="D607" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11613,15 +11604,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20547</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="608" spans="1:8">
       <c r="C608" s="6">
-        <v>17704</v>
+        <v>18004</v>
       </c>
       <c r="D608" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11633,15 +11624,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20548</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>17705</v>
+        <v>18005</v>
       </c>
       <c r="D609" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11655,10 +11646,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>17706</v>
+        <v>18006</v>
       </c>
       <c r="D610" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11672,10 +11663,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>17707</v>
+        <v>18007</v>
       </c>
       <c r="D611" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11689,10 +11680,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>17708</v>
+        <v>18008</v>
       </c>
       <c r="D612" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11706,10 +11697,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>17709</v>
+        <v>18009</v>
       </c>
       <c r="D613" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11723,10 +11714,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>17710</v>
+        <v>18010</v>
       </c>
       <c r="D614" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11740,10 +11731,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>17711</v>
+        <v>18011</v>
       </c>
       <c r="D615" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11757,10 +11748,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>17712</v>
+        <v>18012</v>
       </c>
       <c r="D616" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11774,10 +11765,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>17713</v>
+        <v>18013</v>
       </c>
       <c r="D617" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11791,10 +11782,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>17714</v>
+        <v>18014</v>
       </c>
       <c r="D618" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11808,10 +11799,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>17715</v>
+        <v>18015</v>
       </c>
       <c r="D619" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11825,10 +11816,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>17716</v>
+        <v>18016</v>
       </c>
       <c r="D620" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11842,10 +11833,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>17717</v>
+        <v>18017</v>
       </c>
       <c r="D621" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11859,10 +11850,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>17718</v>
+        <v>18018</v>
       </c>
       <c r="D622" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11876,10 +11867,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>17719</v>
+        <v>18019</v>
       </c>
       <c r="D623" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11893,10 +11884,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>17720</v>
+        <v>18020</v>
       </c>
       <c r="D624" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11910,10 +11901,10 @@
     </row>
     <row r="625" spans="1:8">
       <c r="C625" s="6">
-        <v>17721</v>
+        <v>18021</v>
       </c>
       <c r="D625" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11927,10 +11918,10 @@
     </row>
     <row r="626" spans="1:8">
       <c r="C626" s="6">
-        <v>17722</v>
+        <v>18022</v>
       </c>
       <c r="D626" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11944,10 +11935,10 @@
     </row>
     <row r="627" spans="1:8">
       <c r="C627" s="6">
-        <v>17723</v>
+        <v>18023</v>
       </c>
       <c r="D627" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11961,10 +11952,10 @@
     </row>
     <row r="628" spans="1:8">
       <c r="C628" s="6">
-        <v>17724</v>
+        <v>18024</v>
       </c>
       <c r="D628" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11978,10 +11969,10 @@
     </row>
     <row r="629" spans="1:8">
       <c r="C629" s="6">
-        <v>17725</v>
+        <v>18025</v>
       </c>
       <c r="D629" s="3">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -11998,10 +11989,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>17801</v>
+        <v>18101</v>
       </c>
       <c r="D631" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12013,17 +12004,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20565</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>17802</v>
+        <v>18102</v>
       </c>
       <c r="D632" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12035,15 +12026,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20566</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="633" spans="1:8">
       <c r="C633" s="6">
-        <v>17803</v>
+        <v>18103</v>
       </c>
       <c r="D633" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12055,15 +12046,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20567</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="634" spans="1:8">
       <c r="C634" s="6">
-        <v>17804</v>
+        <v>18104</v>
       </c>
       <c r="D634" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12075,15 +12066,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20568</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="635" spans="1:8">
       <c r="C635" s="6">
-        <v>17805</v>
+        <v>18105</v>
       </c>
       <c r="D635" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12097,10 +12088,10 @@
     </row>
     <row r="636" spans="1:8">
       <c r="C636" s="6">
-        <v>17806</v>
+        <v>18106</v>
       </c>
       <c r="D636" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12114,10 +12105,10 @@
     </row>
     <row r="637" spans="1:8">
       <c r="C637" s="6">
-        <v>17807</v>
+        <v>18107</v>
       </c>
       <c r="D637" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12131,10 +12122,10 @@
     </row>
     <row r="638" spans="1:8">
       <c r="C638" s="6">
-        <v>17808</v>
+        <v>18108</v>
       </c>
       <c r="D638" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12148,10 +12139,10 @@
     </row>
     <row r="639" spans="1:8">
       <c r="C639" s="6">
-        <v>17809</v>
+        <v>18109</v>
       </c>
       <c r="D639" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12165,10 +12156,10 @@
     </row>
     <row r="640" spans="1:8">
       <c r="C640" s="6">
-        <v>17810</v>
+        <v>18110</v>
       </c>
       <c r="D640" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12182,10 +12173,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>17811</v>
+        <v>18111</v>
       </c>
       <c r="D641" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12199,10 +12190,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>17812</v>
+        <v>18112</v>
       </c>
       <c r="D642" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12216,10 +12207,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>17813</v>
+        <v>18113</v>
       </c>
       <c r="D643" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12233,10 +12224,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>17814</v>
+        <v>18114</v>
       </c>
       <c r="D644" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12250,10 +12241,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>17815</v>
+        <v>18115</v>
       </c>
       <c r="D645" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12267,10 +12258,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>17816</v>
+        <v>18116</v>
       </c>
       <c r="D646" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12284,10 +12275,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>17817</v>
+        <v>18117</v>
       </c>
       <c r="D647" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12301,10 +12292,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>17818</v>
+        <v>18118</v>
       </c>
       <c r="D648" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12318,10 +12309,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>17819</v>
+        <v>18119</v>
       </c>
       <c r="D649" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12335,10 +12326,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>17820</v>
+        <v>18120</v>
       </c>
       <c r="D650" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12352,10 +12343,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>17821</v>
+        <v>18121</v>
       </c>
       <c r="D651" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12369,10 +12360,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>17822</v>
+        <v>18122</v>
       </c>
       <c r="D652" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12386,10 +12377,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>17823</v>
+        <v>18123</v>
       </c>
       <c r="D653" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12403,10 +12394,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>17824</v>
+        <v>18124</v>
       </c>
       <c r="D654" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12420,10 +12411,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>17825</v>
+        <v>18125</v>
       </c>
       <c r="D655" s="3">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12440,10 +12431,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>17901</v>
+        <v>18201</v>
       </c>
       <c r="D657" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12455,17 +12446,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20595</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>17902</v>
+        <v>18202</v>
       </c>
       <c r="D658" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12477,15 +12468,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20596</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="659" spans="1:8">
       <c r="C659" s="6">
-        <v>17903</v>
+        <v>18203</v>
       </c>
       <c r="D659" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12497,15 +12488,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20597</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="660" spans="1:8">
       <c r="C660" s="6">
-        <v>17904</v>
+        <v>18204</v>
       </c>
       <c r="D660" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12517,15 +12508,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20598</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="661" spans="1:8">
       <c r="C661" s="6">
-        <v>17905</v>
+        <v>18205</v>
       </c>
       <c r="D661" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12539,10 +12530,10 @@
     </row>
     <row r="662" spans="1:8">
       <c r="C662" s="6">
-        <v>17906</v>
+        <v>18206</v>
       </c>
       <c r="D662" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12556,10 +12547,10 @@
     </row>
     <row r="663" spans="1:8">
       <c r="C663" s="6">
-        <v>17907</v>
+        <v>18207</v>
       </c>
       <c r="D663" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12573,10 +12564,10 @@
     </row>
     <row r="664" spans="1:8">
       <c r="C664" s="6">
-        <v>17908</v>
+        <v>18208</v>
       </c>
       <c r="D664" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12590,10 +12581,10 @@
     </row>
     <row r="665" spans="1:8">
       <c r="C665" s="6">
-        <v>17909</v>
+        <v>18209</v>
       </c>
       <c r="D665" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12607,10 +12598,10 @@
     </row>
     <row r="666" spans="1:8">
       <c r="C666" s="6">
-        <v>17910</v>
+        <v>18210</v>
       </c>
       <c r="D666" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12624,10 +12615,10 @@
     </row>
     <row r="667" spans="1:8">
       <c r="C667" s="6">
-        <v>17911</v>
+        <v>18211</v>
       </c>
       <c r="D667" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12641,10 +12632,10 @@
     </row>
     <row r="668" spans="1:8">
       <c r="C668" s="6">
-        <v>17912</v>
+        <v>18212</v>
       </c>
       <c r="D668" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12658,10 +12649,10 @@
     </row>
     <row r="669" spans="1:8">
       <c r="C669" s="6">
-        <v>17913</v>
+        <v>18213</v>
       </c>
       <c r="D669" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12675,10 +12666,10 @@
     </row>
     <row r="670" spans="1:8">
       <c r="C670" s="6">
-        <v>17914</v>
+        <v>18214</v>
       </c>
       <c r="D670" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12692,10 +12683,10 @@
     </row>
     <row r="671" spans="1:8">
       <c r="C671" s="6">
-        <v>17915</v>
+        <v>18215</v>
       </c>
       <c r="D671" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12709,10 +12700,10 @@
     </row>
     <row r="672" spans="1:8">
       <c r="C672" s="6">
-        <v>17916</v>
+        <v>18216</v>
       </c>
       <c r="D672" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12724,12 +12715,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="673" spans="1:8">
+    <row r="673" spans="3:7">
       <c r="C673" s="6">
-        <v>17917</v>
+        <v>18217</v>
       </c>
       <c r="D673" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12741,12 +12732,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="674" spans="1:8">
+    <row r="674" spans="3:7">
       <c r="C674" s="6">
-        <v>17918</v>
+        <v>18218</v>
       </c>
       <c r="D674" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12758,12 +12749,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="675" spans="1:8">
+    <row r="675" spans="3:7">
       <c r="C675" s="6">
-        <v>17919</v>
+        <v>18219</v>
       </c>
       <c r="D675" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12775,12 +12766,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="676" spans="1:8">
+    <row r="676" spans="3:7">
       <c r="C676" s="6">
-        <v>17920</v>
+        <v>18220</v>
       </c>
       <c r="D676" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12792,12 +12783,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="677" spans="1:8">
+    <row r="677" spans="3:7">
       <c r="C677" s="6">
-        <v>17921</v>
+        <v>18221</v>
       </c>
       <c r="D677" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12809,12 +12800,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="678" spans="1:8">
+    <row r="678" spans="3:7">
       <c r="C678" s="6">
-        <v>17922</v>
+        <v>18222</v>
       </c>
       <c r="D678" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12826,12 +12817,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="679" spans="1:8">
+    <row r="679" spans="3:7">
       <c r="C679" s="6">
-        <v>17923</v>
+        <v>18223</v>
       </c>
       <c r="D679" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12843,12 +12834,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="680" spans="1:8">
+    <row r="680" spans="3:7">
       <c r="C680" s="6">
-        <v>17924</v>
+        <v>18224</v>
       </c>
       <c r="D680" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12860,12 +12851,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="681" spans="1:8">
+    <row r="681" spans="3:7">
       <c r="C681" s="6">
-        <v>17925</v>
+        <v>18225</v>
       </c>
       <c r="D681" s="3">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12874,1332 +12865,6 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="683" spans="1:8">
-      <c r="A683" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C683" s="6">
-        <v>18001</v>
-      </c>
-      <c r="D683" s="3">
-        <v>180</v>
-      </c>
-      <c r="E683" s="5">
-        <v>1</v>
-      </c>
-      <c r="F683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G683" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H683" s="3">
-        <v>20375</v>
-      </c>
-    </row>
-    <row r="684" spans="1:8">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-      <c r="C684" s="6">
-        <v>18002</v>
-      </c>
-      <c r="D684" s="3">
-        <v>180</v>
-      </c>
-      <c r="E684" s="5">
-        <v>1</v>
-      </c>
-      <c r="F684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G684" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H684" s="3">
-        <v>20376</v>
-      </c>
-    </row>
-    <row r="685" spans="1:8">
-      <c r="C685" s="6">
-        <v>18003</v>
-      </c>
-      <c r="D685" s="3">
-        <v>180</v>
-      </c>
-      <c r="E685" s="5">
-        <v>1</v>
-      </c>
-      <c r="F685" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G685" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H685" s="3">
-        <v>20377</v>
-      </c>
-    </row>
-    <row r="686" spans="1:8">
-      <c r="C686" s="6">
-        <v>18004</v>
-      </c>
-      <c r="D686" s="3">
-        <v>180</v>
-      </c>
-      <c r="E686" s="5">
-        <v>1</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G686" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H686" s="3">
-        <v>20378</v>
-      </c>
-    </row>
-    <row r="687" spans="1:8">
-      <c r="C687" s="6">
-        <v>18005</v>
-      </c>
-      <c r="D687" s="3">
-        <v>180</v>
-      </c>
-      <c r="E687" s="3">
-        <v>1</v>
-      </c>
-      <c r="F687" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G687" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="688" spans="1:8">
-      <c r="C688" s="6">
-        <v>18006</v>
-      </c>
-      <c r="D688" s="3">
-        <v>180</v>
-      </c>
-      <c r="E688" s="5">
-        <v>1</v>
-      </c>
-      <c r="F688" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G688" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="689" spans="3:7">
-      <c r="C689" s="6">
-        <v>18007</v>
-      </c>
-      <c r="D689" s="3">
-        <v>180</v>
-      </c>
-      <c r="E689" s="5">
-        <v>1</v>
-      </c>
-      <c r="F689" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G689" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="690" spans="3:7">
-      <c r="C690" s="6">
-        <v>18008</v>
-      </c>
-      <c r="D690" s="3">
-        <v>180</v>
-      </c>
-      <c r="E690" s="5">
-        <v>1</v>
-      </c>
-      <c r="F690" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G690" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="691" spans="3:7">
-      <c r="C691" s="6">
-        <v>18009</v>
-      </c>
-      <c r="D691" s="3">
-        <v>180</v>
-      </c>
-      <c r="E691" s="3">
-        <v>1</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G691" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="692" spans="3:7">
-      <c r="C692" s="6">
-        <v>18010</v>
-      </c>
-      <c r="D692" s="3">
-        <v>180</v>
-      </c>
-      <c r="E692" s="5">
-        <v>1</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G692" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="693" spans="3:7">
-      <c r="C693" s="6">
-        <v>18011</v>
-      </c>
-      <c r="D693" s="3">
-        <v>180</v>
-      </c>
-      <c r="E693" s="5">
-        <v>1</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G693" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="694" spans="3:7">
-      <c r="C694" s="6">
-        <v>18012</v>
-      </c>
-      <c r="D694" s="3">
-        <v>180</v>
-      </c>
-      <c r="E694" s="5">
-        <v>1</v>
-      </c>
-      <c r="F694" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G694" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="695" spans="3:7">
-      <c r="C695" s="6">
-        <v>18013</v>
-      </c>
-      <c r="D695" s="3">
-        <v>180</v>
-      </c>
-      <c r="E695" s="3">
-        <v>1</v>
-      </c>
-      <c r="F695" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G695" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="696" spans="3:7">
-      <c r="C696" s="6">
-        <v>18014</v>
-      </c>
-      <c r="D696" s="3">
-        <v>180</v>
-      </c>
-      <c r="E696" s="5">
-        <v>1</v>
-      </c>
-      <c r="F696" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G696" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="697" spans="3:7">
-      <c r="C697" s="6">
-        <v>18015</v>
-      </c>
-      <c r="D697" s="3">
-        <v>180</v>
-      </c>
-      <c r="E697" s="5">
-        <v>1</v>
-      </c>
-      <c r="F697" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G697" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="698" spans="3:7">
-      <c r="C698" s="6">
-        <v>18016</v>
-      </c>
-      <c r="D698" s="3">
-        <v>180</v>
-      </c>
-      <c r="E698" s="5">
-        <v>1</v>
-      </c>
-      <c r="F698" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G698" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="699" spans="3:7">
-      <c r="C699" s="6">
-        <v>18017</v>
-      </c>
-      <c r="D699" s="3">
-        <v>180</v>
-      </c>
-      <c r="E699" s="3">
-        <v>1</v>
-      </c>
-      <c r="F699" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G699" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="700" spans="3:7">
-      <c r="C700" s="6">
-        <v>18018</v>
-      </c>
-      <c r="D700" s="3">
-        <v>180</v>
-      </c>
-      <c r="E700" s="5">
-        <v>1</v>
-      </c>
-      <c r="F700" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G700" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="701" spans="3:7">
-      <c r="C701" s="6">
-        <v>18019</v>
-      </c>
-      <c r="D701" s="3">
-        <v>180</v>
-      </c>
-      <c r="E701" s="5">
-        <v>1</v>
-      </c>
-      <c r="F701" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G701" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="702" spans="3:7">
-      <c r="C702" s="6">
-        <v>18020</v>
-      </c>
-      <c r="D702" s="3">
-        <v>180</v>
-      </c>
-      <c r="E702" s="5">
-        <v>1</v>
-      </c>
-      <c r="F702" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G702" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="703" spans="3:7">
-      <c r="C703" s="6">
-        <v>18021</v>
-      </c>
-      <c r="D703" s="3">
-        <v>180</v>
-      </c>
-      <c r="E703" s="3">
-        <v>1</v>
-      </c>
-      <c r="F703" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G703" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="704" spans="3:7">
-      <c r="C704" s="6">
-        <v>18022</v>
-      </c>
-      <c r="D704" s="3">
-        <v>180</v>
-      </c>
-      <c r="E704" s="5">
-        <v>1</v>
-      </c>
-      <c r="F704" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G704" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="705" spans="1:8">
-      <c r="C705" s="6">
-        <v>18023</v>
-      </c>
-      <c r="D705" s="3">
-        <v>180</v>
-      </c>
-      <c r="E705" s="5">
-        <v>1</v>
-      </c>
-      <c r="F705" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G705" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="706" spans="1:8">
-      <c r="C706" s="6">
-        <v>18024</v>
-      </c>
-      <c r="D706" s="3">
-        <v>180</v>
-      </c>
-      <c r="E706" s="5">
-        <v>1</v>
-      </c>
-      <c r="F706" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G706" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="707" spans="1:8">
-      <c r="C707" s="6">
-        <v>18025</v>
-      </c>
-      <c r="D707" s="3">
-        <v>180</v>
-      </c>
-      <c r="E707" s="3">
-        <v>1</v>
-      </c>
-      <c r="F707" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>18101</v>
-      </c>
-      <c r="D709" s="3">
-        <v>181</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20405</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>18102</v>
-      </c>
-      <c r="D710" s="3">
-        <v>181</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20406</v>
-      </c>
-    </row>
-    <row r="711" spans="1:8">
-      <c r="C711" s="6">
-        <v>18103</v>
-      </c>
-      <c r="D711" s="3">
-        <v>181</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20407</v>
-      </c>
-    </row>
-    <row r="712" spans="1:8">
-      <c r="C712" s="6">
-        <v>18104</v>
-      </c>
-      <c r="D712" s="3">
-        <v>181</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20408</v>
-      </c>
-    </row>
-    <row r="713" spans="1:8">
-      <c r="C713" s="6">
-        <v>18105</v>
-      </c>
-      <c r="D713" s="3">
-        <v>181</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="1:8">
-      <c r="C714" s="6">
-        <v>18106</v>
-      </c>
-      <c r="D714" s="3">
-        <v>181</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="1:8">
-      <c r="C715" s="6">
-        <v>18107</v>
-      </c>
-      <c r="D715" s="3">
-        <v>181</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="1:8">
-      <c r="C716" s="6">
-        <v>18108</v>
-      </c>
-      <c r="D716" s="3">
-        <v>181</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="1:8">
-      <c r="C717" s="6">
-        <v>18109</v>
-      </c>
-      <c r="D717" s="3">
-        <v>181</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="1:8">
-      <c r="C718" s="6">
-        <v>18110</v>
-      </c>
-      <c r="D718" s="3">
-        <v>181</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="1:8">
-      <c r="C719" s="6">
-        <v>18111</v>
-      </c>
-      <c r="D719" s="3">
-        <v>181</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="1:8">
-      <c r="C720" s="6">
-        <v>18112</v>
-      </c>
-      <c r="D720" s="3">
-        <v>181</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="1:8">
-      <c r="C721" s="6">
-        <v>18113</v>
-      </c>
-      <c r="D721" s="3">
-        <v>181</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="1:8">
-      <c r="C722" s="6">
-        <v>18114</v>
-      </c>
-      <c r="D722" s="3">
-        <v>181</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="1:8">
-      <c r="C723" s="6">
-        <v>18115</v>
-      </c>
-      <c r="D723" s="3">
-        <v>181</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="1:8">
-      <c r="C724" s="6">
-        <v>18116</v>
-      </c>
-      <c r="D724" s="3">
-        <v>181</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="1:8">
-      <c r="C725" s="6">
-        <v>18117</v>
-      </c>
-      <c r="D725" s="3">
-        <v>181</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="1:8">
-      <c r="C726" s="6">
-        <v>18118</v>
-      </c>
-      <c r="D726" s="3">
-        <v>181</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="1:8">
-      <c r="C727" s="6">
-        <v>18119</v>
-      </c>
-      <c r="D727" s="3">
-        <v>181</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="1:8">
-      <c r="C728" s="6">
-        <v>18120</v>
-      </c>
-      <c r="D728" s="3">
-        <v>181</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="1:8">
-      <c r="C729" s="6">
-        <v>18121</v>
-      </c>
-      <c r="D729" s="3">
-        <v>181</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="1:8">
-      <c r="C730" s="6">
-        <v>18122</v>
-      </c>
-      <c r="D730" s="3">
-        <v>181</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="1:8">
-      <c r="C731" s="6">
-        <v>18123</v>
-      </c>
-      <c r="D731" s="3">
-        <v>181</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="1:8">
-      <c r="C732" s="6">
-        <v>18124</v>
-      </c>
-      <c r="D732" s="3">
-        <v>181</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="1:8">
-      <c r="C733" s="6">
-        <v>18125</v>
-      </c>
-      <c r="D733" s="3">
-        <v>181</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>18201</v>
-      </c>
-      <c r="D735" s="3">
-        <v>182</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20415</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>18202</v>
-      </c>
-      <c r="D736" s="3">
-        <v>182</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20416</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>18203</v>
-      </c>
-      <c r="D737" s="3">
-        <v>182</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20417</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>18204</v>
-      </c>
-      <c r="D738" s="3">
-        <v>182</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20418</v>
-      </c>
-    </row>
-    <row r="739" spans="3:8">
-      <c r="C739" s="6">
-        <v>18205</v>
-      </c>
-      <c r="D739" s="3">
-        <v>182</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:8">
-      <c r="C740" s="6">
-        <v>18206</v>
-      </c>
-      <c r="D740" s="3">
-        <v>182</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:8">
-      <c r="C741" s="6">
-        <v>18207</v>
-      </c>
-      <c r="D741" s="3">
-        <v>182</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:8">
-      <c r="C742" s="6">
-        <v>18208</v>
-      </c>
-      <c r="D742" s="3">
-        <v>182</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:8">
-      <c r="C743" s="6">
-        <v>18209</v>
-      </c>
-      <c r="D743" s="3">
-        <v>182</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:8">
-      <c r="C744" s="6">
-        <v>18210</v>
-      </c>
-      <c r="D744" s="3">
-        <v>182</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:8">
-      <c r="C745" s="6">
-        <v>18211</v>
-      </c>
-      <c r="D745" s="3">
-        <v>182</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:8">
-      <c r="C746" s="6">
-        <v>18212</v>
-      </c>
-      <c r="D746" s="3">
-        <v>182</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:8">
-      <c r="C747" s="6">
-        <v>18213</v>
-      </c>
-      <c r="D747" s="3">
-        <v>182</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:8">
-      <c r="C748" s="6">
-        <v>18214</v>
-      </c>
-      <c r="D748" s="3">
-        <v>182</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:8">
-      <c r="C749" s="6">
-        <v>18215</v>
-      </c>
-      <c r="D749" s="3">
-        <v>182</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:8">
-      <c r="C750" s="6">
-        <v>18216</v>
-      </c>
-      <c r="D750" s="3">
-        <v>182</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:8">
-      <c r="C751" s="6">
-        <v>18217</v>
-      </c>
-      <c r="D751" s="3">
-        <v>182</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:8">
-      <c r="C752" s="6">
-        <v>18218</v>
-      </c>
-      <c r="D752" s="3">
-        <v>182</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="3:7">
-      <c r="C753" s="6">
-        <v>18219</v>
-      </c>
-      <c r="D753" s="3">
-        <v>182</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="3:7">
-      <c r="C754" s="6">
-        <v>18220</v>
-      </c>
-      <c r="D754" s="3">
-        <v>182</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="3:7">
-      <c r="C755" s="6">
-        <v>18221</v>
-      </c>
-      <c r="D755" s="3">
-        <v>182</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="3:7">
-      <c r="C756" s="6">
-        <v>18222</v>
-      </c>
-      <c r="D756" s="3">
-        <v>182</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="3:7">
-      <c r="C757" s="6">
-        <v>18223</v>
-      </c>
-      <c r="D757" s="3">
-        <v>182</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="3:7">
-      <c r="C758" s="6">
-        <v>18224</v>
-      </c>
-      <c r="D758" s="3">
-        <v>182</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="3:7">
-      <c r="C759" s="6">
-        <v>18225</v>
-      </c>
-      <c r="D759" s="3">
-        <v>182</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +12985,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +13003,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +13021,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +13039,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +13059,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +13157,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>#先锋182泰坦之锤</t>
+  </si>
+  <si>
+    <t>#先锋183</t>
   </si>
   <si>
     <t>Center</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O681"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -12715,7 +12718,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="673" spans="3:7">
+    <row r="673" spans="1:8">
       <c r="C673" s="6">
         <v>18217</v>
       </c>
@@ -12732,7 +12735,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="674" spans="3:7">
+    <row r="674" spans="1:8">
       <c r="C674" s="6">
         <v>18218</v>
       </c>
@@ -12749,7 +12752,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="675" spans="3:7">
+    <row r="675" spans="1:8">
       <c r="C675" s="6">
         <v>18219</v>
       </c>
@@ -12766,7 +12769,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="676" spans="3:7">
+    <row r="676" spans="1:8">
       <c r="C676" s="6">
         <v>18220</v>
       </c>
@@ -12783,7 +12786,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="677" spans="3:7">
+    <row r="677" spans="1:8">
       <c r="C677" s="6">
         <v>18221</v>
       </c>
@@ -12800,7 +12803,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="678" spans="3:7">
+    <row r="678" spans="1:8">
       <c r="C678" s="6">
         <v>18222</v>
       </c>
@@ -12817,7 +12820,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="679" spans="3:7">
+    <row r="679" spans="1:8">
       <c r="C679" s="6">
         <v>18223</v>
       </c>
@@ -12834,7 +12837,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="680" spans="3:7">
+    <row r="680" spans="1:8">
       <c r="C680" s="6">
         <v>18224</v>
       </c>
@@ -12851,7 +12854,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="681" spans="3:7">
+    <row r="681" spans="1:8">
       <c r="C681" s="6">
         <v>18225</v>
       </c>
@@ -12865,6 +12868,448 @@
         <v>42</v>
       </c>
       <c r="G681" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8">
+      <c r="A683" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C683" s="6">
+        <v>18301</v>
+      </c>
+      <c r="D683" s="3">
+        <v>183</v>
+      </c>
+      <c r="E683" s="5">
+        <v>1</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G683" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H683" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8">
+      <c r="A684" s="1"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="6">
+        <v>18302</v>
+      </c>
+      <c r="D684" s="3">
+        <v>183</v>
+      </c>
+      <c r="E684" s="5">
+        <v>1</v>
+      </c>
+      <c r="F684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G684" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H684" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8">
+      <c r="C685" s="6">
+        <v>18303</v>
+      </c>
+      <c r="D685" s="3">
+        <v>183</v>
+      </c>
+      <c r="E685" s="5">
+        <v>1</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H685" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8">
+      <c r="C686" s="6">
+        <v>18304</v>
+      </c>
+      <c r="D686" s="3">
+        <v>183</v>
+      </c>
+      <c r="E686" s="5">
+        <v>1</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G686" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H686" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8">
+      <c r="C687" s="6">
+        <v>18305</v>
+      </c>
+      <c r="D687" s="3">
+        <v>183</v>
+      </c>
+      <c r="E687" s="3">
+        <v>1</v>
+      </c>
+      <c r="F687" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G687" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8">
+      <c r="C688" s="6">
+        <v>18306</v>
+      </c>
+      <c r="D688" s="3">
+        <v>183</v>
+      </c>
+      <c r="E688" s="5">
+        <v>1</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G688" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="689" spans="3:7">
+      <c r="C689" s="6">
+        <v>18307</v>
+      </c>
+      <c r="D689" s="3">
+        <v>183</v>
+      </c>
+      <c r="E689" s="5">
+        <v>1</v>
+      </c>
+      <c r="F689" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G689" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="690" spans="3:7">
+      <c r="C690" s="6">
+        <v>18308</v>
+      </c>
+      <c r="D690" s="3">
+        <v>183</v>
+      </c>
+      <c r="E690" s="5">
+        <v>1</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G690" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="3:7">
+      <c r="C691" s="6">
+        <v>18309</v>
+      </c>
+      <c r="D691" s="3">
+        <v>183</v>
+      </c>
+      <c r="E691" s="3">
+        <v>1</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G691" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="692" spans="3:7">
+      <c r="C692" s="6">
+        <v>18310</v>
+      </c>
+      <c r="D692" s="3">
+        <v>183</v>
+      </c>
+      <c r="E692" s="5">
+        <v>1</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G692" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="3:7">
+      <c r="C693" s="6">
+        <v>18311</v>
+      </c>
+      <c r="D693" s="3">
+        <v>183</v>
+      </c>
+      <c r="E693" s="5">
+        <v>1</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G693" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="694" spans="3:7">
+      <c r="C694" s="6">
+        <v>18312</v>
+      </c>
+      <c r="D694" s="3">
+        <v>183</v>
+      </c>
+      <c r="E694" s="5">
+        <v>1</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G694" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="695" spans="3:7">
+      <c r="C695" s="6">
+        <v>18313</v>
+      </c>
+      <c r="D695" s="3">
+        <v>183</v>
+      </c>
+      <c r="E695" s="3">
+        <v>1</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G695" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="696" spans="3:7">
+      <c r="C696" s="6">
+        <v>18314</v>
+      </c>
+      <c r="D696" s="3">
+        <v>183</v>
+      </c>
+      <c r="E696" s="5">
+        <v>1</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G696" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="697" spans="3:7">
+      <c r="C697" s="6">
+        <v>18315</v>
+      </c>
+      <c r="D697" s="3">
+        <v>183</v>
+      </c>
+      <c r="E697" s="5">
+        <v>1</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G697" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="698" spans="3:7">
+      <c r="C698" s="6">
+        <v>18316</v>
+      </c>
+      <c r="D698" s="3">
+        <v>183</v>
+      </c>
+      <c r="E698" s="5">
+        <v>1</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G698" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="699" spans="3:7">
+      <c r="C699" s="6">
+        <v>18317</v>
+      </c>
+      <c r="D699" s="3">
+        <v>183</v>
+      </c>
+      <c r="E699" s="3">
+        <v>1</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G699" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="700" spans="3:7">
+      <c r="C700" s="6">
+        <v>18318</v>
+      </c>
+      <c r="D700" s="3">
+        <v>183</v>
+      </c>
+      <c r="E700" s="5">
+        <v>1</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G700" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="701" spans="3:7">
+      <c r="C701" s="6">
+        <v>18319</v>
+      </c>
+      <c r="D701" s="3">
+        <v>183</v>
+      </c>
+      <c r="E701" s="5">
+        <v>1</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G701" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="702" spans="3:7">
+      <c r="C702" s="6">
+        <v>18320</v>
+      </c>
+      <c r="D702" s="3">
+        <v>183</v>
+      </c>
+      <c r="E702" s="5">
+        <v>1</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G702" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="703" spans="3:7">
+      <c r="C703" s="6">
+        <v>18321</v>
+      </c>
+      <c r="D703" s="3">
+        <v>183</v>
+      </c>
+      <c r="E703" s="3">
+        <v>1</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G703" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="3:7">
+      <c r="C704" s="6">
+        <v>18322</v>
+      </c>
+      <c r="D704" s="3">
+        <v>183</v>
+      </c>
+      <c r="E704" s="5">
+        <v>1</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G704" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="705" spans="3:7">
+      <c r="C705" s="6">
+        <v>18323</v>
+      </c>
+      <c r="D705" s="3">
+        <v>183</v>
+      </c>
+      <c r="E705" s="5">
+        <v>1</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G705" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="706" spans="3:7">
+      <c r="C706" s="6">
+        <v>18324</v>
+      </c>
+      <c r="D706" s="3">
+        <v>183</v>
+      </c>
+      <c r="E706" s="5">
+        <v>1</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G706" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="707" spans="3:7">
+      <c r="C707" s="6">
+        <v>18325</v>
+      </c>
+      <c r="D707" s="3">
+        <v>183</v>
+      </c>
+      <c r="E707" s="3">
+        <v>1</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G707" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -12985,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13003,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13021,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13039,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13059,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -13157,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -235,7 +235,7 @@
     <t>#先锋182泰坦之锤</t>
   </si>
   <si>
-    <t>#先锋183</t>
+    <t>#先锋183圣光神域</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋183圣光神域</t>
+  </si>
+  <si>
+    <t>#先锋184</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13262,7 +13265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="3:7">
+    <row r="705" spans="1:8">
       <c r="C705" s="6">
         <v>18323</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="3:7">
+    <row r="706" spans="1:8">
       <c r="C706" s="6">
         <v>18324</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="3:7">
+    <row r="707" spans="1:8">
       <c r="C707" s="6">
         <v>18325</v>
       </c>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>18401</v>
+      </c>
+      <c r="D709" s="3">
+        <v>184</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20515</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>18402</v>
+      </c>
+      <c r="D710" s="3">
+        <v>184</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20516</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="C711" s="6">
+        <v>18403</v>
+      </c>
+      <c r="D711" s="3">
+        <v>184</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20517</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="C712" s="6">
+        <v>18404</v>
+      </c>
+      <c r="D712" s="3">
+        <v>184</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20518</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="C713" s="6">
+        <v>18405</v>
+      </c>
+      <c r="D713" s="3">
+        <v>184</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="C714" s="6">
+        <v>18406</v>
+      </c>
+      <c r="D714" s="3">
+        <v>184</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="C715" s="6">
+        <v>18407</v>
+      </c>
+      <c r="D715" s="3">
+        <v>184</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="C716" s="6">
+        <v>18408</v>
+      </c>
+      <c r="D716" s="3">
+        <v>184</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="C717" s="6">
+        <v>18409</v>
+      </c>
+      <c r="D717" s="3">
+        <v>184</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="C718" s="6">
+        <v>18410</v>
+      </c>
+      <c r="D718" s="3">
+        <v>184</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="C719" s="6">
+        <v>18411</v>
+      </c>
+      <c r="D719" s="3">
+        <v>184</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="C720" s="6">
+        <v>18412</v>
+      </c>
+      <c r="D720" s="3">
+        <v>184</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>18413</v>
+      </c>
+      <c r="D721" s="3">
+        <v>184</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>18414</v>
+      </c>
+      <c r="D722" s="3">
+        <v>184</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>18415</v>
+      </c>
+      <c r="D723" s="3">
+        <v>184</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>18416</v>
+      </c>
+      <c r="D724" s="3">
+        <v>184</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>18417</v>
+      </c>
+      <c r="D725" s="3">
+        <v>184</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>18418</v>
+      </c>
+      <c r="D726" s="3">
+        <v>184</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>18419</v>
+      </c>
+      <c r="D727" s="3">
+        <v>184</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>18420</v>
+      </c>
+      <c r="D728" s="3">
+        <v>184</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>18421</v>
+      </c>
+      <c r="D729" s="3">
+        <v>184</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>18422</v>
+      </c>
+      <c r="D730" s="3">
+        <v>184</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>18423</v>
+      </c>
+      <c r="D731" s="3">
+        <v>184</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>18424</v>
+      </c>
+      <c r="D732" s="3">
+        <v>184</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>18425</v>
+      </c>
+      <c r="D733" s="3">
+        <v>184</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -238,7 +238,7 @@
     <t>#先锋183圣光神域</t>
   </si>
   <si>
-    <t>#先锋184</t>
+    <t>#先锋184炽焰神殿</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋184炽焰神殿</t>
+  </si>
+  <si>
+    <t>#先锋185</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13537,7 +13540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="721" spans="3:7">
+    <row r="721" spans="1:8">
       <c r="C721" s="6">
         <v>18413</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="3:7">
+    <row r="722" spans="1:8">
       <c r="C722" s="6">
         <v>18414</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="723" spans="3:7">
+    <row r="723" spans="1:8">
       <c r="C723" s="6">
         <v>18415</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="724" spans="3:7">
+    <row r="724" spans="1:8">
       <c r="C724" s="6">
         <v>18416</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="725" spans="3:7">
+    <row r="725" spans="1:8">
       <c r="C725" s="6">
         <v>18417</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="3:7">
+    <row r="726" spans="1:8">
       <c r="C726" s="6">
         <v>18418</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="727" spans="3:7">
+    <row r="727" spans="1:8">
       <c r="C727" s="6">
         <v>18419</v>
       </c>
@@ -13656,7 +13659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="728" spans="3:7">
+    <row r="728" spans="1:8">
       <c r="C728" s="6">
         <v>18420</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="729" spans="3:7">
+    <row r="729" spans="1:8">
       <c r="C729" s="6">
         <v>18421</v>
       </c>
@@ -13690,7 +13693,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="730" spans="3:7">
+    <row r="730" spans="1:8">
       <c r="C730" s="6">
         <v>18422</v>
       </c>
@@ -13707,7 +13710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="731" spans="3:7">
+    <row r="731" spans="1:8">
       <c r="C731" s="6">
         <v>18423</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="732" spans="3:7">
+    <row r="732" spans="1:8">
       <c r="C732" s="6">
         <v>18424</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="733" spans="3:7">
+    <row r="733" spans="1:8">
       <c r="C733" s="6">
         <v>18425</v>
       </c>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>18501</v>
+      </c>
+      <c r="D735" s="3">
+        <v>185</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20545</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>18502</v>
+      </c>
+      <c r="D736" s="3">
+        <v>185</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20546</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>18503</v>
+      </c>
+      <c r="D737" s="3">
+        <v>185</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20547</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>18504</v>
+      </c>
+      <c r="D738" s="3">
+        <v>185</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20548</v>
+      </c>
+    </row>
+    <row r="739" spans="3:8">
+      <c r="C739" s="6">
+        <v>18505</v>
+      </c>
+      <c r="D739" s="3">
+        <v>185</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:8">
+      <c r="C740" s="6">
+        <v>18506</v>
+      </c>
+      <c r="D740" s="3">
+        <v>185</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:8">
+      <c r="C741" s="6">
+        <v>18507</v>
+      </c>
+      <c r="D741" s="3">
+        <v>185</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:8">
+      <c r="C742" s="6">
+        <v>18508</v>
+      </c>
+      <c r="D742" s="3">
+        <v>185</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:8">
+      <c r="C743" s="6">
+        <v>18509</v>
+      </c>
+      <c r="D743" s="3">
+        <v>185</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:8">
+      <c r="C744" s="6">
+        <v>18510</v>
+      </c>
+      <c r="D744" s="3">
+        <v>185</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:8">
+      <c r="C745" s="6">
+        <v>18511</v>
+      </c>
+      <c r="D745" s="3">
+        <v>185</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:8">
+      <c r="C746" s="6">
+        <v>18512</v>
+      </c>
+      <c r="D746" s="3">
+        <v>185</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:8">
+      <c r="C747" s="6">
+        <v>18513</v>
+      </c>
+      <c r="D747" s="3">
+        <v>185</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:8">
+      <c r="C748" s="6">
+        <v>18514</v>
+      </c>
+      <c r="D748" s="3">
+        <v>185</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:8">
+      <c r="C749" s="6">
+        <v>18515</v>
+      </c>
+      <c r="D749" s="3">
+        <v>185</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:8">
+      <c r="C750" s="6">
+        <v>18516</v>
+      </c>
+      <c r="D750" s="3">
+        <v>185</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:8">
+      <c r="C751" s="6">
+        <v>18517</v>
+      </c>
+      <c r="D751" s="3">
+        <v>185</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:8">
+      <c r="C752" s="6">
+        <v>18518</v>
+      </c>
+      <c r="D752" s="3">
+        <v>185</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>18519</v>
+      </c>
+      <c r="D753" s="3">
+        <v>185</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>18520</v>
+      </c>
+      <c r="D754" s="3">
+        <v>185</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>18521</v>
+      </c>
+      <c r="D755" s="3">
+        <v>185</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>18522</v>
+      </c>
+      <c r="D756" s="3">
+        <v>185</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>18523</v>
+      </c>
+      <c r="D757" s="3">
+        <v>185</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>18524</v>
+      </c>
+      <c r="D758" s="3">
+        <v>185</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>18525</v>
+      </c>
+      <c r="D759" s="3">
+        <v>185</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -241,7 +241,10 @@
     <t>#先锋184炽焰神殿</t>
   </si>
   <si>
-    <t>#先锋185</t>
+    <t>#先锋185山河万里</t>
+  </si>
+  <si>
+    <t>#先锋186</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O785"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14084,7 +14087,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="753" spans="3:7">
+    <row r="753" spans="1:8">
       <c r="C753" s="6">
         <v>18519</v>
       </c>
@@ -14101,7 +14104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="754" spans="3:7">
+    <row r="754" spans="1:8">
       <c r="C754" s="6">
         <v>18520</v>
       </c>
@@ -14118,7 +14121,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="755" spans="3:7">
+    <row r="755" spans="1:8">
       <c r="C755" s="6">
         <v>18521</v>
       </c>
@@ -14135,7 +14138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="756" spans="3:7">
+    <row r="756" spans="1:8">
       <c r="C756" s="6">
         <v>18522</v>
       </c>
@@ -14152,7 +14155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="757" spans="3:7">
+    <row r="757" spans="1:8">
       <c r="C757" s="6">
         <v>18523</v>
       </c>
@@ -14169,7 +14172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="758" spans="3:7">
+    <row r="758" spans="1:8">
       <c r="C758" s="6">
         <v>18524</v>
       </c>
@@ -14186,7 +14189,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="759" spans="3:7">
+    <row r="759" spans="1:8">
       <c r="C759" s="6">
         <v>18525</v>
       </c>
@@ -14200,6 +14203,448 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C761" s="6">
+        <v>18601</v>
+      </c>
+      <c r="D761" s="3">
+        <v>186</v>
+      </c>
+      <c r="E761" s="5">
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H761" s="3">
+        <v>20615</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="6">
+        <v>18602</v>
+      </c>
+      <c r="D762" s="3">
+        <v>186</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20616</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8">
+      <c r="C763" s="6">
+        <v>18603</v>
+      </c>
+      <c r="D763" s="3">
+        <v>186</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20617</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8">
+      <c r="C764" s="6">
+        <v>18604</v>
+      </c>
+      <c r="D764" s="3">
+        <v>186</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20618</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8">
+      <c r="C765" s="6">
+        <v>18605</v>
+      </c>
+      <c r="D765" s="3">
+        <v>186</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8">
+      <c r="C766" s="6">
+        <v>18606</v>
+      </c>
+      <c r="D766" s="3">
+        <v>186</v>
+      </c>
+      <c r="E766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8">
+      <c r="C767" s="6">
+        <v>18607</v>
+      </c>
+      <c r="D767" s="3">
+        <v>186</v>
+      </c>
+      <c r="E767" s="5">
+        <v>1</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8">
+      <c r="C768" s="6">
+        <v>18608</v>
+      </c>
+      <c r="D768" s="3">
+        <v>186</v>
+      </c>
+      <c r="E768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>18609</v>
+      </c>
+      <c r="D769" s="3">
+        <v>186</v>
+      </c>
+      <c r="E769" s="3">
+        <v>1</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>18610</v>
+      </c>
+      <c r="D770" s="3">
+        <v>186</v>
+      </c>
+      <c r="E770" s="5">
+        <v>1</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>18611</v>
+      </c>
+      <c r="D771" s="3">
+        <v>186</v>
+      </c>
+      <c r="E771" s="5">
+        <v>1</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>18612</v>
+      </c>
+      <c r="D772" s="3">
+        <v>186</v>
+      </c>
+      <c r="E772" s="5">
+        <v>1</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>18613</v>
+      </c>
+      <c r="D773" s="3">
+        <v>186</v>
+      </c>
+      <c r="E773" s="3">
+        <v>1</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>18614</v>
+      </c>
+      <c r="D774" s="3">
+        <v>186</v>
+      </c>
+      <c r="E774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>18615</v>
+      </c>
+      <c r="D775" s="3">
+        <v>186</v>
+      </c>
+      <c r="E775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>18616</v>
+      </c>
+      <c r="D776" s="3">
+        <v>186</v>
+      </c>
+      <c r="E776" s="5">
+        <v>1</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>18617</v>
+      </c>
+      <c r="D777" s="3">
+        <v>186</v>
+      </c>
+      <c r="E777" s="3">
+        <v>1</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>18618</v>
+      </c>
+      <c r="D778" s="3">
+        <v>186</v>
+      </c>
+      <c r="E778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>18619</v>
+      </c>
+      <c r="D779" s="3">
+        <v>186</v>
+      </c>
+      <c r="E779" s="5">
+        <v>1</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>18620</v>
+      </c>
+      <c r="D780" s="3">
+        <v>186</v>
+      </c>
+      <c r="E780" s="5">
+        <v>1</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>18621</v>
+      </c>
+      <c r="D781" s="3">
+        <v>186</v>
+      </c>
+      <c r="E781" s="3">
+        <v>1</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>18622</v>
+      </c>
+      <c r="D782" s="3">
+        <v>186</v>
+      </c>
+      <c r="E782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>18623</v>
+      </c>
+      <c r="D783" s="3">
+        <v>186</v>
+      </c>
+      <c r="E783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>18624</v>
+      </c>
+      <c r="D784" s="3">
+        <v>186</v>
+      </c>
+      <c r="E784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>18625</v>
+      </c>
+      <c r="D785" s="3">
+        <v>186</v>
+      </c>
+      <c r="E785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +14765,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +14783,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +14801,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +14819,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +14839,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14937,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -244,7 +244,7 @@
     <t>#先锋185山河万里</t>
   </si>
   <si>
-    <t>#先锋186</t>
+    <t>#先锋186忘川彼岸</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -208,13 +208,7 @@
     <t>#先锋163破晓战歌</t>
   </si>
   <si>
-    <t>#先锋167青云之巅</t>
-  </si>
-  <si>
     <t>#先锋172星辰殿堂</t>
-  </si>
-  <si>
-    <t>#先锋174龙息之谷</t>
   </si>
   <si>
     <t>#先锋176普天同庆</t>
@@ -223,13 +217,7 @@
     <t>#先锋178风暴之地</t>
   </si>
   <si>
-    <t>#先锋179巨刃降临</t>
-  </si>
-  <si>
     <t>#先锋180生命之树</t>
-  </si>
-  <si>
-    <t>#先锋181浮生若梦</t>
   </si>
   <si>
     <t>#先锋182泰坦之锤</t>
@@ -245,6 +233,9 @@
   </si>
   <si>
     <t>#先锋186忘川彼岸</t>
+  </si>
+  <si>
+    <t>#先锋187花涧语</t>
   </si>
   <si>
     <t>Center</t>
@@ -1272,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O785"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -8907,10 +8898,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>16701</v>
+        <v>17201</v>
       </c>
       <c r="D449" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8922,17 +8913,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20555</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>16702</v>
+        <v>17202</v>
       </c>
       <c r="D450" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8944,15 +8935,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20556</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="451" spans="1:8">
       <c r="C451" s="6">
-        <v>16703</v>
+        <v>17203</v>
       </c>
       <c r="D451" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8964,15 +8955,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20557</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="452" spans="1:8">
       <c r="C452" s="6">
-        <v>16704</v>
+        <v>17204</v>
       </c>
       <c r="D452" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8984,15 +8975,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20558</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="453" spans="1:8">
       <c r="C453" s="6">
-        <v>16705</v>
+        <v>17205</v>
       </c>
       <c r="D453" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9006,10 +8997,10 @@
     </row>
     <row r="454" spans="1:8">
       <c r="C454" s="6">
-        <v>16706</v>
+        <v>17206</v>
       </c>
       <c r="D454" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9023,10 +9014,10 @@
     </row>
     <row r="455" spans="1:8">
       <c r="C455" s="6">
-        <v>16707</v>
+        <v>17207</v>
       </c>
       <c r="D455" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9040,10 +9031,10 @@
     </row>
     <row r="456" spans="1:8">
       <c r="C456" s="6">
-        <v>16708</v>
+        <v>17208</v>
       </c>
       <c r="D456" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9057,10 +9048,10 @@
     </row>
     <row r="457" spans="1:8">
       <c r="C457" s="6">
-        <v>16709</v>
+        <v>17209</v>
       </c>
       <c r="D457" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9074,10 +9065,10 @@
     </row>
     <row r="458" spans="1:8">
       <c r="C458" s="6">
-        <v>16710</v>
+        <v>17210</v>
       </c>
       <c r="D458" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9091,10 +9082,10 @@
     </row>
     <row r="459" spans="1:8">
       <c r="C459" s="6">
-        <v>16711</v>
+        <v>17211</v>
       </c>
       <c r="D459" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9108,10 +9099,10 @@
     </row>
     <row r="460" spans="1:8">
       <c r="C460" s="6">
-        <v>16712</v>
+        <v>17212</v>
       </c>
       <c r="D460" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9125,10 +9116,10 @@
     </row>
     <row r="461" spans="1:8">
       <c r="C461" s="6">
-        <v>16713</v>
+        <v>17213</v>
       </c>
       <c r="D461" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9142,10 +9133,10 @@
     </row>
     <row r="462" spans="1:8">
       <c r="C462" s="6">
-        <v>16714</v>
+        <v>17214</v>
       </c>
       <c r="D462" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9159,10 +9150,10 @@
     </row>
     <row r="463" spans="1:8">
       <c r="C463" s="6">
-        <v>16715</v>
+        <v>17215</v>
       </c>
       <c r="D463" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9176,10 +9167,10 @@
     </row>
     <row r="464" spans="1:8">
       <c r="C464" s="6">
-        <v>16716</v>
+        <v>17216</v>
       </c>
       <c r="D464" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9193,10 +9184,10 @@
     </row>
     <row r="465" spans="1:8">
       <c r="C465" s="6">
-        <v>16717</v>
+        <v>17217</v>
       </c>
       <c r="D465" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9210,10 +9201,10 @@
     </row>
     <row r="466" spans="1:8">
       <c r="C466" s="6">
-        <v>16718</v>
+        <v>17218</v>
       </c>
       <c r="D466" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9227,10 +9218,10 @@
     </row>
     <row r="467" spans="1:8">
       <c r="C467" s="6">
-        <v>16719</v>
+        <v>17219</v>
       </c>
       <c r="D467" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9244,10 +9235,10 @@
     </row>
     <row r="468" spans="1:8">
       <c r="C468" s="6">
-        <v>16720</v>
+        <v>17220</v>
       </c>
       <c r="D468" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9261,10 +9252,10 @@
     </row>
     <row r="469" spans="1:8">
       <c r="C469" s="6">
-        <v>16721</v>
+        <v>17221</v>
       </c>
       <c r="D469" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9278,10 +9269,10 @@
     </row>
     <row r="470" spans="1:8">
       <c r="C470" s="6">
-        <v>16722</v>
+        <v>17222</v>
       </c>
       <c r="D470" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9295,10 +9286,10 @@
     </row>
     <row r="471" spans="1:8">
       <c r="C471" s="6">
-        <v>16723</v>
+        <v>17223</v>
       </c>
       <c r="D471" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9312,10 +9303,10 @@
     </row>
     <row r="472" spans="1:8">
       <c r="C472" s="6">
-        <v>16724</v>
+        <v>17224</v>
       </c>
       <c r="D472" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9329,10 +9320,10 @@
     </row>
     <row r="473" spans="1:8">
       <c r="C473" s="6">
-        <v>16725</v>
+        <v>17225</v>
       </c>
       <c r="D473" s="3">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9349,10 +9340,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>17201</v>
+        <v>17601</v>
       </c>
       <c r="D475" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9364,17 +9355,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20585</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>17202</v>
+        <v>17602</v>
       </c>
       <c r="D476" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9386,15 +9377,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20586</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="477" spans="1:8">
       <c r="C477" s="6">
-        <v>17203</v>
+        <v>17603</v>
       </c>
       <c r="D477" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9406,15 +9397,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20587</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="478" spans="1:8">
       <c r="C478" s="6">
-        <v>17204</v>
+        <v>17604</v>
       </c>
       <c r="D478" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9426,15 +9417,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20588</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="479" spans="1:8">
       <c r="C479" s="6">
-        <v>17205</v>
+        <v>17605</v>
       </c>
       <c r="D479" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9448,10 +9439,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="C480" s="6">
-        <v>17206</v>
+        <v>17606</v>
       </c>
       <c r="D480" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9465,10 +9456,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>17207</v>
+        <v>17607</v>
       </c>
       <c r="D481" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9482,10 +9473,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>17208</v>
+        <v>17608</v>
       </c>
       <c r="D482" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9499,10 +9490,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>17209</v>
+        <v>17609</v>
       </c>
       <c r="D483" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9516,10 +9507,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>17210</v>
+        <v>17610</v>
       </c>
       <c r="D484" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9533,10 +9524,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>17211</v>
+        <v>17611</v>
       </c>
       <c r="D485" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9550,10 +9541,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>17212</v>
+        <v>17612</v>
       </c>
       <c r="D486" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9567,10 +9558,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>17213</v>
+        <v>17613</v>
       </c>
       <c r="D487" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9584,10 +9575,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>17214</v>
+        <v>17614</v>
       </c>
       <c r="D488" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9601,10 +9592,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>17215</v>
+        <v>17615</v>
       </c>
       <c r="D489" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9618,10 +9609,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>17216</v>
+        <v>17616</v>
       </c>
       <c r="D490" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9635,10 +9626,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>17217</v>
+        <v>17617</v>
       </c>
       <c r="D491" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9652,10 +9643,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>17218</v>
+        <v>17618</v>
       </c>
       <c r="D492" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9669,10 +9660,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>17219</v>
+        <v>17619</v>
       </c>
       <c r="D493" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9686,10 +9677,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>17220</v>
+        <v>17620</v>
       </c>
       <c r="D494" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9703,10 +9694,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>17221</v>
+        <v>17621</v>
       </c>
       <c r="D495" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9720,10 +9711,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>17222</v>
+        <v>17622</v>
       </c>
       <c r="D496" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9737,10 +9728,10 @@
     </row>
     <row r="497" spans="1:8">
       <c r="C497" s="6">
-        <v>17223</v>
+        <v>17623</v>
       </c>
       <c r="D497" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9754,10 +9745,10 @@
     </row>
     <row r="498" spans="1:8">
       <c r="C498" s="6">
-        <v>17224</v>
+        <v>17624</v>
       </c>
       <c r="D498" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9771,10 +9762,10 @@
     </row>
     <row r="499" spans="1:8">
       <c r="C499" s="6">
-        <v>17225</v>
+        <v>17625</v>
       </c>
       <c r="D499" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9791,10 +9782,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>17401</v>
+        <v>17801</v>
       </c>
       <c r="D501" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9806,17 +9797,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20445</v>
+        <v>20565</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>17402</v>
+        <v>17802</v>
       </c>
       <c r="D502" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9828,15 +9819,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20446</v>
+        <v>20566</v>
       </c>
     </row>
     <row r="503" spans="1:8">
       <c r="C503" s="6">
-        <v>17403</v>
+        <v>17803</v>
       </c>
       <c r="D503" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9848,15 +9839,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20447</v>
+        <v>20567</v>
       </c>
     </row>
     <row r="504" spans="1:8">
       <c r="C504" s="6">
-        <v>17404</v>
+        <v>17804</v>
       </c>
       <c r="D504" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9868,15 +9859,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20448</v>
+        <v>20568</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="C505" s="6">
-        <v>17405</v>
+        <v>17805</v>
       </c>
       <c r="D505" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9890,10 +9881,10 @@
     </row>
     <row r="506" spans="1:8">
       <c r="C506" s="6">
-        <v>17406</v>
+        <v>17806</v>
       </c>
       <c r="D506" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9907,10 +9898,10 @@
     </row>
     <row r="507" spans="1:8">
       <c r="C507" s="6">
-        <v>17407</v>
+        <v>17807</v>
       </c>
       <c r="D507" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9924,10 +9915,10 @@
     </row>
     <row r="508" spans="1:8">
       <c r="C508" s="6">
-        <v>17408</v>
+        <v>17808</v>
       </c>
       <c r="D508" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9941,10 +9932,10 @@
     </row>
     <row r="509" spans="1:8">
       <c r="C509" s="6">
-        <v>17409</v>
+        <v>17809</v>
       </c>
       <c r="D509" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9958,10 +9949,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="C510" s="6">
-        <v>17410</v>
+        <v>17810</v>
       </c>
       <c r="D510" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9975,10 +9966,10 @@
     </row>
     <row r="511" spans="1:8">
       <c r="C511" s="6">
-        <v>17411</v>
+        <v>17811</v>
       </c>
       <c r="D511" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9992,10 +9983,10 @@
     </row>
     <row r="512" spans="1:8">
       <c r="C512" s="6">
-        <v>17412</v>
+        <v>17812</v>
       </c>
       <c r="D512" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10009,10 +10000,10 @@
     </row>
     <row r="513" spans="1:8">
       <c r="C513" s="6">
-        <v>17413</v>
+        <v>17813</v>
       </c>
       <c r="D513" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10026,10 +10017,10 @@
     </row>
     <row r="514" spans="1:8">
       <c r="C514" s="6">
-        <v>17414</v>
+        <v>17814</v>
       </c>
       <c r="D514" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10043,10 +10034,10 @@
     </row>
     <row r="515" spans="1:8">
       <c r="C515" s="6">
-        <v>17415</v>
+        <v>17815</v>
       </c>
       <c r="D515" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10060,10 +10051,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="C516" s="6">
-        <v>17416</v>
+        <v>17816</v>
       </c>
       <c r="D516" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10077,10 +10068,10 @@
     </row>
     <row r="517" spans="1:8">
       <c r="C517" s="6">
-        <v>17417</v>
+        <v>17817</v>
       </c>
       <c r="D517" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10094,10 +10085,10 @@
     </row>
     <row r="518" spans="1:8">
       <c r="C518" s="6">
-        <v>17418</v>
+        <v>17818</v>
       </c>
       <c r="D518" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10111,10 +10102,10 @@
     </row>
     <row r="519" spans="1:8">
       <c r="C519" s="6">
-        <v>17419</v>
+        <v>17819</v>
       </c>
       <c r="D519" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10128,10 +10119,10 @@
     </row>
     <row r="520" spans="1:8">
       <c r="C520" s="6">
-        <v>17420</v>
+        <v>17820</v>
       </c>
       <c r="D520" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10145,10 +10136,10 @@
     </row>
     <row r="521" spans="1:8">
       <c r="C521" s="6">
-        <v>17421</v>
+        <v>17821</v>
       </c>
       <c r="D521" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10162,10 +10153,10 @@
     </row>
     <row r="522" spans="1:8">
       <c r="C522" s="6">
-        <v>17422</v>
+        <v>17822</v>
       </c>
       <c r="D522" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10179,10 +10170,10 @@
     </row>
     <row r="523" spans="1:8">
       <c r="C523" s="6">
-        <v>17423</v>
+        <v>17823</v>
       </c>
       <c r="D523" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10196,10 +10187,10 @@
     </row>
     <row r="524" spans="1:8">
       <c r="C524" s="6">
-        <v>17424</v>
+        <v>17824</v>
       </c>
       <c r="D524" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10213,10 +10204,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="C525" s="6">
-        <v>17425</v>
+        <v>17825</v>
       </c>
       <c r="D525" s="3">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10233,10 +10224,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>17601</v>
+        <v>18001</v>
       </c>
       <c r="D527" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10248,17 +10239,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20505</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>17602</v>
+        <v>18002</v>
       </c>
       <c r="D528" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10270,15 +10261,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20506</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>17603</v>
+        <v>18003</v>
       </c>
       <c r="D529" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10290,15 +10281,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20507</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>17604</v>
+        <v>18004</v>
       </c>
       <c r="D530" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10310,15 +10301,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20508</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="531" spans="3:8">
       <c r="C531" s="6">
-        <v>17605</v>
+        <v>18005</v>
       </c>
       <c r="D531" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10332,10 +10323,10 @@
     </row>
     <row r="532" spans="3:8">
       <c r="C532" s="6">
-        <v>17606</v>
+        <v>18006</v>
       </c>
       <c r="D532" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10349,10 +10340,10 @@
     </row>
     <row r="533" spans="3:8">
       <c r="C533" s="6">
-        <v>17607</v>
+        <v>18007</v>
       </c>
       <c r="D533" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10366,10 +10357,10 @@
     </row>
     <row r="534" spans="3:8">
       <c r="C534" s="6">
-        <v>17608</v>
+        <v>18008</v>
       </c>
       <c r="D534" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10383,10 +10374,10 @@
     </row>
     <row r="535" spans="3:8">
       <c r="C535" s="6">
-        <v>17609</v>
+        <v>18009</v>
       </c>
       <c r="D535" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10400,10 +10391,10 @@
     </row>
     <row r="536" spans="3:8">
       <c r="C536" s="6">
-        <v>17610</v>
+        <v>18010</v>
       </c>
       <c r="D536" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10417,10 +10408,10 @@
     </row>
     <row r="537" spans="3:8">
       <c r="C537" s="6">
-        <v>17611</v>
+        <v>18011</v>
       </c>
       <c r="D537" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10434,10 +10425,10 @@
     </row>
     <row r="538" spans="3:8">
       <c r="C538" s="6">
-        <v>17612</v>
+        <v>18012</v>
       </c>
       <c r="D538" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10451,10 +10442,10 @@
     </row>
     <row r="539" spans="3:8">
       <c r="C539" s="6">
-        <v>17613</v>
+        <v>18013</v>
       </c>
       <c r="D539" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10468,10 +10459,10 @@
     </row>
     <row r="540" spans="3:8">
       <c r="C540" s="6">
-        <v>17614</v>
+        <v>18014</v>
       </c>
       <c r="D540" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10485,10 +10476,10 @@
     </row>
     <row r="541" spans="3:8">
       <c r="C541" s="6">
-        <v>17615</v>
+        <v>18015</v>
       </c>
       <c r="D541" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10502,10 +10493,10 @@
     </row>
     <row r="542" spans="3:8">
       <c r="C542" s="6">
-        <v>17616</v>
+        <v>18016</v>
       </c>
       <c r="D542" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10519,10 +10510,10 @@
     </row>
     <row r="543" spans="3:8">
       <c r="C543" s="6">
-        <v>17617</v>
+        <v>18017</v>
       </c>
       <c r="D543" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10536,10 +10527,10 @@
     </row>
     <row r="544" spans="3:8">
       <c r="C544" s="6">
-        <v>17618</v>
+        <v>18018</v>
       </c>
       <c r="D544" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10553,10 +10544,10 @@
     </row>
     <row r="545" spans="1:8">
       <c r="C545" s="6">
-        <v>17619</v>
+        <v>18019</v>
       </c>
       <c r="D545" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10570,10 +10561,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="C546" s="6">
-        <v>17620</v>
+        <v>18020</v>
       </c>
       <c r="D546" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10587,10 +10578,10 @@
     </row>
     <row r="547" spans="1:8">
       <c r="C547" s="6">
-        <v>17621</v>
+        <v>18021</v>
       </c>
       <c r="D547" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10604,10 +10595,10 @@
     </row>
     <row r="548" spans="1:8">
       <c r="C548" s="6">
-        <v>17622</v>
+        <v>18022</v>
       </c>
       <c r="D548" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10621,10 +10612,10 @@
     </row>
     <row r="549" spans="1:8">
       <c r="C549" s="6">
-        <v>17623</v>
+        <v>18023</v>
       </c>
       <c r="D549" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10638,10 +10629,10 @@
     </row>
     <row r="550" spans="1:8">
       <c r="C550" s="6">
-        <v>17624</v>
+        <v>18024</v>
       </c>
       <c r="D550" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10655,10 +10646,10 @@
     </row>
     <row r="551" spans="1:8">
       <c r="C551" s="6">
-        <v>17625</v>
+        <v>18025</v>
       </c>
       <c r="D551" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10675,10 +10666,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>17801</v>
+        <v>18201</v>
       </c>
       <c r="D553" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10690,17 +10681,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20565</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>17802</v>
+        <v>18202</v>
       </c>
       <c r="D554" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10712,15 +10703,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20566</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="555" spans="1:8">
       <c r="C555" s="6">
-        <v>17803</v>
+        <v>18203</v>
       </c>
       <c r="D555" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10732,15 +10723,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20567</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="556" spans="1:8">
       <c r="C556" s="6">
-        <v>17804</v>
+        <v>18204</v>
       </c>
       <c r="D556" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10752,15 +10743,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20568</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="557" spans="1:8">
       <c r="C557" s="6">
-        <v>17805</v>
+        <v>18205</v>
       </c>
       <c r="D557" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10774,10 +10765,10 @@
     </row>
     <row r="558" spans="1:8">
       <c r="C558" s="6">
-        <v>17806</v>
+        <v>18206</v>
       </c>
       <c r="D558" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10791,10 +10782,10 @@
     </row>
     <row r="559" spans="1:8">
       <c r="C559" s="6">
-        <v>17807</v>
+        <v>18207</v>
       </c>
       <c r="D559" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10808,10 +10799,10 @@
     </row>
     <row r="560" spans="1:8">
       <c r="C560" s="6">
-        <v>17808</v>
+        <v>18208</v>
       </c>
       <c r="D560" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10825,10 +10816,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>17809</v>
+        <v>18209</v>
       </c>
       <c r="D561" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10842,10 +10833,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>17810</v>
+        <v>18210</v>
       </c>
       <c r="D562" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10859,10 +10850,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>17811</v>
+        <v>18211</v>
       </c>
       <c r="D563" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10876,10 +10867,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>17812</v>
+        <v>18212</v>
       </c>
       <c r="D564" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10893,10 +10884,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>17813</v>
+        <v>18213</v>
       </c>
       <c r="D565" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10910,10 +10901,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>17814</v>
+        <v>18214</v>
       </c>
       <c r="D566" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10927,10 +10918,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>17815</v>
+        <v>18215</v>
       </c>
       <c r="D567" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10944,10 +10935,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>17816</v>
+        <v>18216</v>
       </c>
       <c r="D568" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10961,10 +10952,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>17817</v>
+        <v>18217</v>
       </c>
       <c r="D569" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10978,10 +10969,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>17818</v>
+        <v>18218</v>
       </c>
       <c r="D570" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10995,10 +10986,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>17819</v>
+        <v>18219</v>
       </c>
       <c r="D571" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11012,10 +11003,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>17820</v>
+        <v>18220</v>
       </c>
       <c r="D572" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11029,10 +11020,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>17821</v>
+        <v>18221</v>
       </c>
       <c r="D573" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11046,10 +11037,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>17822</v>
+        <v>18222</v>
       </c>
       <c r="D574" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11063,10 +11054,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>17823</v>
+        <v>18223</v>
       </c>
       <c r="D575" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11080,10 +11071,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>17824</v>
+        <v>18224</v>
       </c>
       <c r="D576" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11097,10 +11088,10 @@
     </row>
     <row r="577" spans="1:8">
       <c r="C577" s="6">
-        <v>17825</v>
+        <v>18225</v>
       </c>
       <c r="D577" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11117,10 +11108,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>17901</v>
+        <v>18301</v>
       </c>
       <c r="D579" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11132,17 +11123,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20595</v>
+        <v>20455</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>17902</v>
+        <v>18302</v>
       </c>
       <c r="D580" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11154,15 +11145,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20596</v>
+        <v>20456</v>
       </c>
     </row>
     <row r="581" spans="1:8">
       <c r="C581" s="6">
-        <v>17903</v>
+        <v>18303</v>
       </c>
       <c r="D581" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11174,15 +11165,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20597</v>
+        <v>20457</v>
       </c>
     </row>
     <row r="582" spans="1:8">
       <c r="C582" s="6">
-        <v>17904</v>
+        <v>18304</v>
       </c>
       <c r="D582" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11194,15 +11185,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20598</v>
+        <v>20458</v>
       </c>
     </row>
     <row r="583" spans="1:8">
       <c r="C583" s="6">
-        <v>17905</v>
+        <v>18305</v>
       </c>
       <c r="D583" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11216,10 +11207,10 @@
     </row>
     <row r="584" spans="1:8">
       <c r="C584" s="6">
-        <v>17906</v>
+        <v>18306</v>
       </c>
       <c r="D584" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11233,10 +11224,10 @@
     </row>
     <row r="585" spans="1:8">
       <c r="C585" s="6">
-        <v>17907</v>
+        <v>18307</v>
       </c>
       <c r="D585" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11250,10 +11241,10 @@
     </row>
     <row r="586" spans="1:8">
       <c r="C586" s="6">
-        <v>17908</v>
+        <v>18308</v>
       </c>
       <c r="D586" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11267,10 +11258,10 @@
     </row>
     <row r="587" spans="1:8">
       <c r="C587" s="6">
-        <v>17909</v>
+        <v>18309</v>
       </c>
       <c r="D587" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11284,10 +11275,10 @@
     </row>
     <row r="588" spans="1:8">
       <c r="C588" s="6">
-        <v>17910</v>
+        <v>18310</v>
       </c>
       <c r="D588" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11301,10 +11292,10 @@
     </row>
     <row r="589" spans="1:8">
       <c r="C589" s="6">
-        <v>17911</v>
+        <v>18311</v>
       </c>
       <c r="D589" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11318,10 +11309,10 @@
     </row>
     <row r="590" spans="1:8">
       <c r="C590" s="6">
-        <v>17912</v>
+        <v>18312</v>
       </c>
       <c r="D590" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11335,10 +11326,10 @@
     </row>
     <row r="591" spans="1:8">
       <c r="C591" s="6">
-        <v>17913</v>
+        <v>18313</v>
       </c>
       <c r="D591" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11352,10 +11343,10 @@
     </row>
     <row r="592" spans="1:8">
       <c r="C592" s="6">
-        <v>17914</v>
+        <v>18314</v>
       </c>
       <c r="D592" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11369,10 +11360,10 @@
     </row>
     <row r="593" spans="1:8">
       <c r="C593" s="6">
-        <v>17915</v>
+        <v>18315</v>
       </c>
       <c r="D593" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11386,10 +11377,10 @@
     </row>
     <row r="594" spans="1:8">
       <c r="C594" s="6">
-        <v>17916</v>
+        <v>18316</v>
       </c>
       <c r="D594" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11403,10 +11394,10 @@
     </row>
     <row r="595" spans="1:8">
       <c r="C595" s="6">
-        <v>17917</v>
+        <v>18317</v>
       </c>
       <c r="D595" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11420,10 +11411,10 @@
     </row>
     <row r="596" spans="1:8">
       <c r="C596" s="6">
-        <v>17918</v>
+        <v>18318</v>
       </c>
       <c r="D596" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11437,10 +11428,10 @@
     </row>
     <row r="597" spans="1:8">
       <c r="C597" s="6">
-        <v>17919</v>
+        <v>18319</v>
       </c>
       <c r="D597" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11454,10 +11445,10 @@
     </row>
     <row r="598" spans="1:8">
       <c r="C598" s="6">
-        <v>17920</v>
+        <v>18320</v>
       </c>
       <c r="D598" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11471,10 +11462,10 @@
     </row>
     <row r="599" spans="1:8">
       <c r="C599" s="6">
-        <v>17921</v>
+        <v>18321</v>
       </c>
       <c r="D599" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11488,10 +11479,10 @@
     </row>
     <row r="600" spans="1:8">
       <c r="C600" s="6">
-        <v>17922</v>
+        <v>18322</v>
       </c>
       <c r="D600" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11505,10 +11496,10 @@
     </row>
     <row r="601" spans="1:8">
       <c r="C601" s="6">
-        <v>17923</v>
+        <v>18323</v>
       </c>
       <c r="D601" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11522,10 +11513,10 @@
     </row>
     <row r="602" spans="1:8">
       <c r="C602" s="6">
-        <v>17924</v>
+        <v>18324</v>
       </c>
       <c r="D602" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11539,10 +11530,10 @@
     </row>
     <row r="603" spans="1:8">
       <c r="C603" s="6">
-        <v>17925</v>
+        <v>18325</v>
       </c>
       <c r="D603" s="3">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11559,10 +11550,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>18001</v>
+        <v>18401</v>
       </c>
       <c r="D605" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11574,17 +11565,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20375</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>18002</v>
+        <v>18402</v>
       </c>
       <c r="D606" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11596,15 +11587,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20376</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="607" spans="1:8">
       <c r="C607" s="6">
-        <v>18003</v>
+        <v>18403</v>
       </c>
       <c r="D607" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11616,15 +11607,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20377</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="608" spans="1:8">
       <c r="C608" s="6">
-        <v>18004</v>
+        <v>18404</v>
       </c>
       <c r="D608" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11636,15 +11627,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20378</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>18005</v>
+        <v>18405</v>
       </c>
       <c r="D609" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11658,10 +11649,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>18006</v>
+        <v>18406</v>
       </c>
       <c r="D610" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11675,10 +11666,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>18007</v>
+        <v>18407</v>
       </c>
       <c r="D611" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11692,10 +11683,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>18008</v>
+        <v>18408</v>
       </c>
       <c r="D612" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11709,10 +11700,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>18009</v>
+        <v>18409</v>
       </c>
       <c r="D613" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11726,10 +11717,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>18010</v>
+        <v>18410</v>
       </c>
       <c r="D614" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11743,10 +11734,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>18011</v>
+        <v>18411</v>
       </c>
       <c r="D615" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11760,10 +11751,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>18012</v>
+        <v>18412</v>
       </c>
       <c r="D616" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11777,10 +11768,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>18013</v>
+        <v>18413</v>
       </c>
       <c r="D617" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11794,10 +11785,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>18014</v>
+        <v>18414</v>
       </c>
       <c r="D618" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11811,10 +11802,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>18015</v>
+        <v>18415</v>
       </c>
       <c r="D619" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11828,10 +11819,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>18016</v>
+        <v>18416</v>
       </c>
       <c r="D620" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11845,10 +11836,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>18017</v>
+        <v>18417</v>
       </c>
       <c r="D621" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11862,10 +11853,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>18018</v>
+        <v>18418</v>
       </c>
       <c r="D622" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11879,10 +11870,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>18019</v>
+        <v>18419</v>
       </c>
       <c r="D623" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11896,10 +11887,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>18020</v>
+        <v>18420</v>
       </c>
       <c r="D624" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11913,10 +11904,10 @@
     </row>
     <row r="625" spans="1:8">
       <c r="C625" s="6">
-        <v>18021</v>
+        <v>18421</v>
       </c>
       <c r="D625" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11930,10 +11921,10 @@
     </row>
     <row r="626" spans="1:8">
       <c r="C626" s="6">
-        <v>18022</v>
+        <v>18422</v>
       </c>
       <c r="D626" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11947,10 +11938,10 @@
     </row>
     <row r="627" spans="1:8">
       <c r="C627" s="6">
-        <v>18023</v>
+        <v>18423</v>
       </c>
       <c r="D627" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11964,10 +11955,10 @@
     </row>
     <row r="628" spans="1:8">
       <c r="C628" s="6">
-        <v>18024</v>
+        <v>18424</v>
       </c>
       <c r="D628" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11981,10 +11972,10 @@
     </row>
     <row r="629" spans="1:8">
       <c r="C629" s="6">
-        <v>18025</v>
+        <v>18425</v>
       </c>
       <c r="D629" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -12001,10 +11992,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>18101</v>
+        <v>18501</v>
       </c>
       <c r="D631" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12016,17 +12007,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20405</v>
+        <v>20545</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>18102</v>
+        <v>18502</v>
       </c>
       <c r="D632" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12038,15 +12029,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20406</v>
+        <v>20546</v>
       </c>
     </row>
     <row r="633" spans="1:8">
       <c r="C633" s="6">
-        <v>18103</v>
+        <v>18503</v>
       </c>
       <c r="D633" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12058,15 +12049,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20407</v>
+        <v>20547</v>
       </c>
     </row>
     <row r="634" spans="1:8">
       <c r="C634" s="6">
-        <v>18104</v>
+        <v>18504</v>
       </c>
       <c r="D634" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12078,15 +12069,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20408</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="635" spans="1:8">
       <c r="C635" s="6">
-        <v>18105</v>
+        <v>18505</v>
       </c>
       <c r="D635" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12100,10 +12091,10 @@
     </row>
     <row r="636" spans="1:8">
       <c r="C636" s="6">
-        <v>18106</v>
+        <v>18506</v>
       </c>
       <c r="D636" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12117,10 +12108,10 @@
     </row>
     <row r="637" spans="1:8">
       <c r="C637" s="6">
-        <v>18107</v>
+        <v>18507</v>
       </c>
       <c r="D637" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12134,10 +12125,10 @@
     </row>
     <row r="638" spans="1:8">
       <c r="C638" s="6">
-        <v>18108</v>
+        <v>18508</v>
       </c>
       <c r="D638" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12151,10 +12142,10 @@
     </row>
     <row r="639" spans="1:8">
       <c r="C639" s="6">
-        <v>18109</v>
+        <v>18509</v>
       </c>
       <c r="D639" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12168,10 +12159,10 @@
     </row>
     <row r="640" spans="1:8">
       <c r="C640" s="6">
-        <v>18110</v>
+        <v>18510</v>
       </c>
       <c r="D640" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12185,10 +12176,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>18111</v>
+        <v>18511</v>
       </c>
       <c r="D641" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12202,10 +12193,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>18112</v>
+        <v>18512</v>
       </c>
       <c r="D642" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12219,10 +12210,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>18113</v>
+        <v>18513</v>
       </c>
       <c r="D643" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12236,10 +12227,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>18114</v>
+        <v>18514</v>
       </c>
       <c r="D644" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12253,10 +12244,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>18115</v>
+        <v>18515</v>
       </c>
       <c r="D645" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12270,10 +12261,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>18116</v>
+        <v>18516</v>
       </c>
       <c r="D646" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12287,10 +12278,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>18117</v>
+        <v>18517</v>
       </c>
       <c r="D647" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12304,10 +12295,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>18118</v>
+        <v>18518</v>
       </c>
       <c r="D648" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12321,10 +12312,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>18119</v>
+        <v>18519</v>
       </c>
       <c r="D649" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12338,10 +12329,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>18120</v>
+        <v>18520</v>
       </c>
       <c r="D650" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12355,10 +12346,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>18121</v>
+        <v>18521</v>
       </c>
       <c r="D651" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12372,10 +12363,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>18122</v>
+        <v>18522</v>
       </c>
       <c r="D652" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12389,10 +12380,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>18123</v>
+        <v>18523</v>
       </c>
       <c r="D653" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12406,10 +12397,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>18124</v>
+        <v>18524</v>
       </c>
       <c r="D654" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12423,10 +12414,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>18125</v>
+        <v>18525</v>
       </c>
       <c r="D655" s="3">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12443,10 +12434,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>18201</v>
+        <v>18601</v>
       </c>
       <c r="D657" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12458,17 +12449,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20415</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>18202</v>
+        <v>18602</v>
       </c>
       <c r="D658" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12480,15 +12471,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20416</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="659" spans="1:8">
       <c r="C659" s="6">
-        <v>18203</v>
+        <v>18603</v>
       </c>
       <c r="D659" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12500,15 +12491,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20417</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="660" spans="1:8">
       <c r="C660" s="6">
-        <v>18204</v>
+        <v>18604</v>
       </c>
       <c r="D660" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12520,15 +12511,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20418</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="661" spans="1:8">
       <c r="C661" s="6">
-        <v>18205</v>
+        <v>18605</v>
       </c>
       <c r="D661" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12542,10 +12533,10 @@
     </row>
     <row r="662" spans="1:8">
       <c r="C662" s="6">
-        <v>18206</v>
+        <v>18606</v>
       </c>
       <c r="D662" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12559,10 +12550,10 @@
     </row>
     <row r="663" spans="1:8">
       <c r="C663" s="6">
-        <v>18207</v>
+        <v>18607</v>
       </c>
       <c r="D663" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12576,10 +12567,10 @@
     </row>
     <row r="664" spans="1:8">
       <c r="C664" s="6">
-        <v>18208</v>
+        <v>18608</v>
       </c>
       <c r="D664" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12593,10 +12584,10 @@
     </row>
     <row r="665" spans="1:8">
       <c r="C665" s="6">
-        <v>18209</v>
+        <v>18609</v>
       </c>
       <c r="D665" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12610,10 +12601,10 @@
     </row>
     <row r="666" spans="1:8">
       <c r="C666" s="6">
-        <v>18210</v>
+        <v>18610</v>
       </c>
       <c r="D666" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12627,10 +12618,10 @@
     </row>
     <row r="667" spans="1:8">
       <c r="C667" s="6">
-        <v>18211</v>
+        <v>18611</v>
       </c>
       <c r="D667" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12644,10 +12635,10 @@
     </row>
     <row r="668" spans="1:8">
       <c r="C668" s="6">
-        <v>18212</v>
+        <v>18612</v>
       </c>
       <c r="D668" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12661,10 +12652,10 @@
     </row>
     <row r="669" spans="1:8">
       <c r="C669" s="6">
-        <v>18213</v>
+        <v>18613</v>
       </c>
       <c r="D669" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12678,10 +12669,10 @@
     </row>
     <row r="670" spans="1:8">
       <c r="C670" s="6">
-        <v>18214</v>
+        <v>18614</v>
       </c>
       <c r="D670" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12695,10 +12686,10 @@
     </row>
     <row r="671" spans="1:8">
       <c r="C671" s="6">
-        <v>18215</v>
+        <v>18615</v>
       </c>
       <c r="D671" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12712,10 +12703,10 @@
     </row>
     <row r="672" spans="1:8">
       <c r="C672" s="6">
-        <v>18216</v>
+        <v>18616</v>
       </c>
       <c r="D672" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12729,10 +12720,10 @@
     </row>
     <row r="673" spans="1:8">
       <c r="C673" s="6">
-        <v>18217</v>
+        <v>18617</v>
       </c>
       <c r="D673" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12746,10 +12737,10 @@
     </row>
     <row r="674" spans="1:8">
       <c r="C674" s="6">
-        <v>18218</v>
+        <v>18618</v>
       </c>
       <c r="D674" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12763,10 +12754,10 @@
     </row>
     <row r="675" spans="1:8">
       <c r="C675" s="6">
-        <v>18219</v>
+        <v>18619</v>
       </c>
       <c r="D675" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12780,10 +12771,10 @@
     </row>
     <row r="676" spans="1:8">
       <c r="C676" s="6">
-        <v>18220</v>
+        <v>18620</v>
       </c>
       <c r="D676" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12797,10 +12788,10 @@
     </row>
     <row r="677" spans="1:8">
       <c r="C677" s="6">
-        <v>18221</v>
+        <v>18621</v>
       </c>
       <c r="D677" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12814,10 +12805,10 @@
     </row>
     <row r="678" spans="1:8">
       <c r="C678" s="6">
-        <v>18222</v>
+        <v>18622</v>
       </c>
       <c r="D678" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12831,10 +12822,10 @@
     </row>
     <row r="679" spans="1:8">
       <c r="C679" s="6">
-        <v>18223</v>
+        <v>18623</v>
       </c>
       <c r="D679" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12848,10 +12839,10 @@
     </row>
     <row r="680" spans="1:8">
       <c r="C680" s="6">
-        <v>18224</v>
+        <v>18624</v>
       </c>
       <c r="D680" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12865,10 +12856,10 @@
     </row>
     <row r="681" spans="1:8">
       <c r="C681" s="6">
-        <v>18225</v>
+        <v>18625</v>
       </c>
       <c r="D681" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12885,10 +12876,10 @@
         <v>68</v>
       </c>
       <c r="C683" s="6">
-        <v>18301</v>
+        <v>18701</v>
       </c>
       <c r="D683" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E683" s="5">
         <v>1</v>
@@ -12900,17 +12891,17 @@
         <v>15</v>
       </c>
       <c r="H683" s="3">
-        <v>20455</v>
+        <v>20635</v>
       </c>
     </row>
     <row r="684" spans="1:8">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="6">
-        <v>18302</v>
+        <v>18702</v>
       </c>
       <c r="D684" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E684" s="5">
         <v>1</v>
@@ -12922,15 +12913,15 @@
         <v>16</v>
       </c>
       <c r="H684" s="3">
-        <v>20456</v>
+        <v>20636</v>
       </c>
     </row>
     <row r="685" spans="1:8">
       <c r="C685" s="6">
-        <v>18303</v>
+        <v>18703</v>
       </c>
       <c r="D685" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E685" s="5">
         <v>1</v>
@@ -12942,15 +12933,15 @@
         <v>18</v>
       </c>
       <c r="H685" s="3">
-        <v>20457</v>
+        <v>20637</v>
       </c>
     </row>
     <row r="686" spans="1:8">
       <c r="C686" s="6">
-        <v>18304</v>
+        <v>18704</v>
       </c>
       <c r="D686" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E686" s="5">
         <v>1</v>
@@ -12962,15 +12953,15 @@
         <v>19</v>
       </c>
       <c r="H686" s="3">
-        <v>20458</v>
+        <v>20638</v>
       </c>
     </row>
     <row r="687" spans="1:8">
       <c r="C687" s="6">
-        <v>18305</v>
+        <v>18705</v>
       </c>
       <c r="D687" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E687" s="3">
         <v>1</v>
@@ -12984,10 +12975,10 @@
     </row>
     <row r="688" spans="1:8">
       <c r="C688" s="6">
-        <v>18306</v>
+        <v>18706</v>
       </c>
       <c r="D688" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E688" s="5">
         <v>1</v>
@@ -13001,10 +12992,10 @@
     </row>
     <row r="689" spans="3:7">
       <c r="C689" s="6">
-        <v>18307</v>
+        <v>18707</v>
       </c>
       <c r="D689" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E689" s="5">
         <v>1</v>
@@ -13018,10 +13009,10 @@
     </row>
     <row r="690" spans="3:7">
       <c r="C690" s="6">
-        <v>18308</v>
+        <v>18708</v>
       </c>
       <c r="D690" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E690" s="5">
         <v>1</v>
@@ -13035,10 +13026,10 @@
     </row>
     <row r="691" spans="3:7">
       <c r="C691" s="6">
-        <v>18309</v>
+        <v>18709</v>
       </c>
       <c r="D691" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E691" s="3">
         <v>1</v>
@@ -13052,10 +13043,10 @@
     </row>
     <row r="692" spans="3:7">
       <c r="C692" s="6">
-        <v>18310</v>
+        <v>18710</v>
       </c>
       <c r="D692" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E692" s="5">
         <v>1</v>
@@ -13069,10 +13060,10 @@
     </row>
     <row r="693" spans="3:7">
       <c r="C693" s="6">
-        <v>18311</v>
+        <v>18711</v>
       </c>
       <c r="D693" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E693" s="5">
         <v>1</v>
@@ -13086,10 +13077,10 @@
     </row>
     <row r="694" spans="3:7">
       <c r="C694" s="6">
-        <v>18312</v>
+        <v>18712</v>
       </c>
       <c r="D694" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E694" s="5">
         <v>1</v>
@@ -13103,10 +13094,10 @@
     </row>
     <row r="695" spans="3:7">
       <c r="C695" s="6">
-        <v>18313</v>
+        <v>18713</v>
       </c>
       <c r="D695" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E695" s="3">
         <v>1</v>
@@ -13120,10 +13111,10 @@
     </row>
     <row r="696" spans="3:7">
       <c r="C696" s="6">
-        <v>18314</v>
+        <v>18714</v>
       </c>
       <c r="D696" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E696" s="5">
         <v>1</v>
@@ -13137,10 +13128,10 @@
     </row>
     <row r="697" spans="3:7">
       <c r="C697" s="6">
-        <v>18315</v>
+        <v>18715</v>
       </c>
       <c r="D697" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E697" s="5">
         <v>1</v>
@@ -13154,10 +13145,10 @@
     </row>
     <row r="698" spans="3:7">
       <c r="C698" s="6">
-        <v>18316</v>
+        <v>18716</v>
       </c>
       <c r="D698" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E698" s="5">
         <v>1</v>
@@ -13171,10 +13162,10 @@
     </row>
     <row r="699" spans="3:7">
       <c r="C699" s="6">
-        <v>18317</v>
+        <v>18717</v>
       </c>
       <c r="D699" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E699" s="3">
         <v>1</v>
@@ -13188,10 +13179,10 @@
     </row>
     <row r="700" spans="3:7">
       <c r="C700" s="6">
-        <v>18318</v>
+        <v>18718</v>
       </c>
       <c r="D700" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E700" s="5">
         <v>1</v>
@@ -13205,10 +13196,10 @@
     </row>
     <row r="701" spans="3:7">
       <c r="C701" s="6">
-        <v>18319</v>
+        <v>18719</v>
       </c>
       <c r="D701" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E701" s="5">
         <v>1</v>
@@ -13222,10 +13213,10 @@
     </row>
     <row r="702" spans="3:7">
       <c r="C702" s="6">
-        <v>18320</v>
+        <v>18720</v>
       </c>
       <c r="D702" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E702" s="5">
         <v>1</v>
@@ -13239,10 +13230,10 @@
     </row>
     <row r="703" spans="3:7">
       <c r="C703" s="6">
-        <v>18321</v>
+        <v>18721</v>
       </c>
       <c r="D703" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E703" s="3">
         <v>1</v>
@@ -13256,10 +13247,10 @@
     </row>
     <row r="704" spans="3:7">
       <c r="C704" s="6">
-        <v>18322</v>
+        <v>18722</v>
       </c>
       <c r="D704" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E704" s="5">
         <v>1</v>
@@ -13271,12 +13262,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" spans="3:7">
       <c r="C705" s="6">
-        <v>18323</v>
+        <v>18723</v>
       </c>
       <c r="D705" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E705" s="5">
         <v>1</v>
@@ -13288,12 +13279,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" spans="3:7">
       <c r="C706" s="6">
-        <v>18324</v>
+        <v>18724</v>
       </c>
       <c r="D706" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E706" s="5">
         <v>1</v>
@@ -13305,12 +13296,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="1:8">
+    <row r="707" spans="3:7">
       <c r="C707" s="6">
-        <v>18325</v>
+        <v>18725</v>
       </c>
       <c r="D707" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E707" s="3">
         <v>1</v>
@@ -13319,1332 +13310,6 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>18401</v>
-      </c>
-      <c r="D709" s="3">
-        <v>184</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20515</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>18402</v>
-      </c>
-      <c r="D710" s="3">
-        <v>184</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20516</v>
-      </c>
-    </row>
-    <row r="711" spans="1:8">
-      <c r="C711" s="6">
-        <v>18403</v>
-      </c>
-      <c r="D711" s="3">
-        <v>184</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20517</v>
-      </c>
-    </row>
-    <row r="712" spans="1:8">
-      <c r="C712" s="6">
-        <v>18404</v>
-      </c>
-      <c r="D712" s="3">
-        <v>184</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20518</v>
-      </c>
-    </row>
-    <row r="713" spans="1:8">
-      <c r="C713" s="6">
-        <v>18405</v>
-      </c>
-      <c r="D713" s="3">
-        <v>184</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="1:8">
-      <c r="C714" s="6">
-        <v>18406</v>
-      </c>
-      <c r="D714" s="3">
-        <v>184</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="1:8">
-      <c r="C715" s="6">
-        <v>18407</v>
-      </c>
-      <c r="D715" s="3">
-        <v>184</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="1:8">
-      <c r="C716" s="6">
-        <v>18408</v>
-      </c>
-      <c r="D716" s="3">
-        <v>184</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="1:8">
-      <c r="C717" s="6">
-        <v>18409</v>
-      </c>
-      <c r="D717" s="3">
-        <v>184</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="1:8">
-      <c r="C718" s="6">
-        <v>18410</v>
-      </c>
-      <c r="D718" s="3">
-        <v>184</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="1:8">
-      <c r="C719" s="6">
-        <v>18411</v>
-      </c>
-      <c r="D719" s="3">
-        <v>184</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="1:8">
-      <c r="C720" s="6">
-        <v>18412</v>
-      </c>
-      <c r="D720" s="3">
-        <v>184</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="1:8">
-      <c r="C721" s="6">
-        <v>18413</v>
-      </c>
-      <c r="D721" s="3">
-        <v>184</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="1:8">
-      <c r="C722" s="6">
-        <v>18414</v>
-      </c>
-      <c r="D722" s="3">
-        <v>184</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="1:8">
-      <c r="C723" s="6">
-        <v>18415</v>
-      </c>
-      <c r="D723" s="3">
-        <v>184</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="1:8">
-      <c r="C724" s="6">
-        <v>18416</v>
-      </c>
-      <c r="D724" s="3">
-        <v>184</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="1:8">
-      <c r="C725" s="6">
-        <v>18417</v>
-      </c>
-      <c r="D725" s="3">
-        <v>184</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="1:8">
-      <c r="C726" s="6">
-        <v>18418</v>
-      </c>
-      <c r="D726" s="3">
-        <v>184</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="1:8">
-      <c r="C727" s="6">
-        <v>18419</v>
-      </c>
-      <c r="D727" s="3">
-        <v>184</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="1:8">
-      <c r="C728" s="6">
-        <v>18420</v>
-      </c>
-      <c r="D728" s="3">
-        <v>184</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="1:8">
-      <c r="C729" s="6">
-        <v>18421</v>
-      </c>
-      <c r="D729" s="3">
-        <v>184</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="1:8">
-      <c r="C730" s="6">
-        <v>18422</v>
-      </c>
-      <c r="D730" s="3">
-        <v>184</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="1:8">
-      <c r="C731" s="6">
-        <v>18423</v>
-      </c>
-      <c r="D731" s="3">
-        <v>184</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="1:8">
-      <c r="C732" s="6">
-        <v>18424</v>
-      </c>
-      <c r="D732" s="3">
-        <v>184</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="1:8">
-      <c r="C733" s="6">
-        <v>18425</v>
-      </c>
-      <c r="D733" s="3">
-        <v>184</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>18501</v>
-      </c>
-      <c r="D735" s="3">
-        <v>185</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20545</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>18502</v>
-      </c>
-      <c r="D736" s="3">
-        <v>185</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20546</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>18503</v>
-      </c>
-      <c r="D737" s="3">
-        <v>185</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20547</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>18504</v>
-      </c>
-      <c r="D738" s="3">
-        <v>185</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20548</v>
-      </c>
-    </row>
-    <row r="739" spans="3:8">
-      <c r="C739" s="6">
-        <v>18505</v>
-      </c>
-      <c r="D739" s="3">
-        <v>185</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:8">
-      <c r="C740" s="6">
-        <v>18506</v>
-      </c>
-      <c r="D740" s="3">
-        <v>185</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:8">
-      <c r="C741" s="6">
-        <v>18507</v>
-      </c>
-      <c r="D741" s="3">
-        <v>185</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:8">
-      <c r="C742" s="6">
-        <v>18508</v>
-      </c>
-      <c r="D742" s="3">
-        <v>185</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:8">
-      <c r="C743" s="6">
-        <v>18509</v>
-      </c>
-      <c r="D743" s="3">
-        <v>185</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:8">
-      <c r="C744" s="6">
-        <v>18510</v>
-      </c>
-      <c r="D744" s="3">
-        <v>185</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:8">
-      <c r="C745" s="6">
-        <v>18511</v>
-      </c>
-      <c r="D745" s="3">
-        <v>185</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:8">
-      <c r="C746" s="6">
-        <v>18512</v>
-      </c>
-      <c r="D746" s="3">
-        <v>185</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:8">
-      <c r="C747" s="6">
-        <v>18513</v>
-      </c>
-      <c r="D747" s="3">
-        <v>185</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:8">
-      <c r="C748" s="6">
-        <v>18514</v>
-      </c>
-      <c r="D748" s="3">
-        <v>185</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:8">
-      <c r="C749" s="6">
-        <v>18515</v>
-      </c>
-      <c r="D749" s="3">
-        <v>185</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:8">
-      <c r="C750" s="6">
-        <v>18516</v>
-      </c>
-      <c r="D750" s="3">
-        <v>185</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:8">
-      <c r="C751" s="6">
-        <v>18517</v>
-      </c>
-      <c r="D751" s="3">
-        <v>185</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:8">
-      <c r="C752" s="6">
-        <v>18518</v>
-      </c>
-      <c r="D752" s="3">
-        <v>185</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="1:8">
-      <c r="C753" s="6">
-        <v>18519</v>
-      </c>
-      <c r="D753" s="3">
-        <v>185</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="1:8">
-      <c r="C754" s="6">
-        <v>18520</v>
-      </c>
-      <c r="D754" s="3">
-        <v>185</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="1:8">
-      <c r="C755" s="6">
-        <v>18521</v>
-      </c>
-      <c r="D755" s="3">
-        <v>185</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="1:8">
-      <c r="C756" s="6">
-        <v>18522</v>
-      </c>
-      <c r="D756" s="3">
-        <v>185</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="1:8">
-      <c r="C757" s="6">
-        <v>18523</v>
-      </c>
-      <c r="D757" s="3">
-        <v>185</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="1:8">
-      <c r="C758" s="6">
-        <v>18524</v>
-      </c>
-      <c r="D758" s="3">
-        <v>185</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="1:8">
-      <c r="C759" s="6">
-        <v>18525</v>
-      </c>
-      <c r="D759" s="3">
-        <v>185</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="761" spans="1:8">
-      <c r="A761" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C761" s="6">
-        <v>18601</v>
-      </c>
-      <c r="D761" s="3">
-        <v>186</v>
-      </c>
-      <c r="E761" s="5">
-        <v>1</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H761" s="3">
-        <v>20615</v>
-      </c>
-    </row>
-    <row r="762" spans="1:8">
-      <c r="A762" s="1"/>
-      <c r="B762" s="1"/>
-      <c r="C762" s="6">
-        <v>18602</v>
-      </c>
-      <c r="D762" s="3">
-        <v>186</v>
-      </c>
-      <c r="E762" s="5">
-        <v>1</v>
-      </c>
-      <c r="F762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H762" s="3">
-        <v>20616</v>
-      </c>
-    </row>
-    <row r="763" spans="1:8">
-      <c r="C763" s="6">
-        <v>18603</v>
-      </c>
-      <c r="D763" s="3">
-        <v>186</v>
-      </c>
-      <c r="E763" s="5">
-        <v>1</v>
-      </c>
-      <c r="F763" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G763" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H763" s="3">
-        <v>20617</v>
-      </c>
-    </row>
-    <row r="764" spans="1:8">
-      <c r="C764" s="6">
-        <v>18604</v>
-      </c>
-      <c r="D764" s="3">
-        <v>186</v>
-      </c>
-      <c r="E764" s="5">
-        <v>1</v>
-      </c>
-      <c r="F764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H764" s="3">
-        <v>20618</v>
-      </c>
-    </row>
-    <row r="765" spans="1:8">
-      <c r="C765" s="6">
-        <v>18605</v>
-      </c>
-      <c r="D765" s="3">
-        <v>186</v>
-      </c>
-      <c r="E765" s="3">
-        <v>1</v>
-      </c>
-      <c r="F765" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G765" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="766" spans="1:8">
-      <c r="C766" s="6">
-        <v>18606</v>
-      </c>
-      <c r="D766" s="3">
-        <v>186</v>
-      </c>
-      <c r="E766" s="5">
-        <v>1</v>
-      </c>
-      <c r="F766" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G766" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="767" spans="1:8">
-      <c r="C767" s="6">
-        <v>18607</v>
-      </c>
-      <c r="D767" s="3">
-        <v>186</v>
-      </c>
-      <c r="E767" s="5">
-        <v>1</v>
-      </c>
-      <c r="F767" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G767" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="768" spans="1:8">
-      <c r="C768" s="6">
-        <v>18608</v>
-      </c>
-      <c r="D768" s="3">
-        <v>186</v>
-      </c>
-      <c r="E768" s="5">
-        <v>1</v>
-      </c>
-      <c r="F768" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G768" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="769" spans="3:7">
-      <c r="C769" s="6">
-        <v>18609</v>
-      </c>
-      <c r="D769" s="3">
-        <v>186</v>
-      </c>
-      <c r="E769" s="3">
-        <v>1</v>
-      </c>
-      <c r="F769" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G769" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="770" spans="3:7">
-      <c r="C770" s="6">
-        <v>18610</v>
-      </c>
-      <c r="D770" s="3">
-        <v>186</v>
-      </c>
-      <c r="E770" s="5">
-        <v>1</v>
-      </c>
-      <c r="F770" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G770" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="771" spans="3:7">
-      <c r="C771" s="6">
-        <v>18611</v>
-      </c>
-      <c r="D771" s="3">
-        <v>186</v>
-      </c>
-      <c r="E771" s="5">
-        <v>1</v>
-      </c>
-      <c r="F771" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G771" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="772" spans="3:7">
-      <c r="C772" s="6">
-        <v>18612</v>
-      </c>
-      <c r="D772" s="3">
-        <v>186</v>
-      </c>
-      <c r="E772" s="5">
-        <v>1</v>
-      </c>
-      <c r="F772" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G772" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="773" spans="3:7">
-      <c r="C773" s="6">
-        <v>18613</v>
-      </c>
-      <c r="D773" s="3">
-        <v>186</v>
-      </c>
-      <c r="E773" s="3">
-        <v>1</v>
-      </c>
-      <c r="F773" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G773" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="774" spans="3:7">
-      <c r="C774" s="6">
-        <v>18614</v>
-      </c>
-      <c r="D774" s="3">
-        <v>186</v>
-      </c>
-      <c r="E774" s="5">
-        <v>1</v>
-      </c>
-      <c r="F774" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G774" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="775" spans="3:7">
-      <c r="C775" s="6">
-        <v>18615</v>
-      </c>
-      <c r="D775" s="3">
-        <v>186</v>
-      </c>
-      <c r="E775" s="5">
-        <v>1</v>
-      </c>
-      <c r="F775" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G775" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="776" spans="3:7">
-      <c r="C776" s="6">
-        <v>18616</v>
-      </c>
-      <c r="D776" s="3">
-        <v>186</v>
-      </c>
-      <c r="E776" s="5">
-        <v>1</v>
-      </c>
-      <c r="F776" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G776" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="777" spans="3:7">
-      <c r="C777" s="6">
-        <v>18617</v>
-      </c>
-      <c r="D777" s="3">
-        <v>186</v>
-      </c>
-      <c r="E777" s="3">
-        <v>1</v>
-      </c>
-      <c r="F777" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G777" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="778" spans="3:7">
-      <c r="C778" s="6">
-        <v>18618</v>
-      </c>
-      <c r="D778" s="3">
-        <v>186</v>
-      </c>
-      <c r="E778" s="5">
-        <v>1</v>
-      </c>
-      <c r="F778" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G778" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="779" spans="3:7">
-      <c r="C779" s="6">
-        <v>18619</v>
-      </c>
-      <c r="D779" s="3">
-        <v>186</v>
-      </c>
-      <c r="E779" s="5">
-        <v>1</v>
-      </c>
-      <c r="F779" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G779" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="780" spans="3:7">
-      <c r="C780" s="6">
-        <v>18620</v>
-      </c>
-      <c r="D780" s="3">
-        <v>186</v>
-      </c>
-      <c r="E780" s="5">
-        <v>1</v>
-      </c>
-      <c r="F780" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G780" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="781" spans="3:7">
-      <c r="C781" s="6">
-        <v>18621</v>
-      </c>
-      <c r="D781" s="3">
-        <v>186</v>
-      </c>
-      <c r="E781" s="3">
-        <v>1</v>
-      </c>
-      <c r="F781" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G781" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="782" spans="3:7">
-      <c r="C782" s="6">
-        <v>18622</v>
-      </c>
-      <c r="D782" s="3">
-        <v>186</v>
-      </c>
-      <c r="E782" s="5">
-        <v>1</v>
-      </c>
-      <c r="F782" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G782" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="783" spans="3:7">
-      <c r="C783" s="6">
-        <v>18623</v>
-      </c>
-      <c r="D783" s="3">
-        <v>186</v>
-      </c>
-      <c r="E783" s="5">
-        <v>1</v>
-      </c>
-      <c r="F783" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G783" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="784" spans="3:7">
-      <c r="C784" s="6">
-        <v>18624</v>
-      </c>
-      <c r="D784" s="3">
-        <v>186</v>
-      </c>
-      <c r="E784" s="5">
-        <v>1</v>
-      </c>
-      <c r="F784" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G784" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="785" spans="3:7">
-      <c r="C785" s="6">
-        <v>18625</v>
-      </c>
-      <c r="D785" s="3">
-        <v>186</v>
-      </c>
-      <c r="E785" s="3">
-        <v>1</v>
-      </c>
-      <c r="F785" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14765,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14783,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14801,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14819,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14839,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -14937,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋187花涧语</t>
+  </si>
+  <si>
+    <t>#先锋188九天境</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13262,7 +13265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="3:7">
+    <row r="705" spans="1:8">
       <c r="C705" s="6">
         <v>18723</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="3:7">
+    <row r="706" spans="1:8">
       <c r="C706" s="6">
         <v>18724</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="3:7">
+    <row r="707" spans="1:8">
       <c r="C707" s="6">
         <v>18725</v>
       </c>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>18801</v>
+      </c>
+      <c r="D709" s="3">
+        <v>188</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20405</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>18802</v>
+      </c>
+      <c r="D710" s="3">
+        <v>188</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20406</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="C711" s="6">
+        <v>18803</v>
+      </c>
+      <c r="D711" s="3">
+        <v>188</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20407</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="C712" s="6">
+        <v>18804</v>
+      </c>
+      <c r="D712" s="3">
+        <v>188</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20408</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="C713" s="6">
+        <v>18805</v>
+      </c>
+      <c r="D713" s="3">
+        <v>188</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="C714" s="6">
+        <v>18806</v>
+      </c>
+      <c r="D714" s="3">
+        <v>188</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="C715" s="6">
+        <v>18807</v>
+      </c>
+      <c r="D715" s="3">
+        <v>188</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="C716" s="6">
+        <v>18808</v>
+      </c>
+      <c r="D716" s="3">
+        <v>188</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="C717" s="6">
+        <v>18809</v>
+      </c>
+      <c r="D717" s="3">
+        <v>188</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="C718" s="6">
+        <v>18810</v>
+      </c>
+      <c r="D718" s="3">
+        <v>188</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="C719" s="6">
+        <v>18811</v>
+      </c>
+      <c r="D719" s="3">
+        <v>188</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="C720" s="6">
+        <v>18812</v>
+      </c>
+      <c r="D720" s="3">
+        <v>188</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>18813</v>
+      </c>
+      <c r="D721" s="3">
+        <v>188</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>18814</v>
+      </c>
+      <c r="D722" s="3">
+        <v>188</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>18815</v>
+      </c>
+      <c r="D723" s="3">
+        <v>188</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>18816</v>
+      </c>
+      <c r="D724" s="3">
+        <v>188</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>18817</v>
+      </c>
+      <c r="D725" s="3">
+        <v>188</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>18818</v>
+      </c>
+      <c r="D726" s="3">
+        <v>188</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>18819</v>
+      </c>
+      <c r="D727" s="3">
+        <v>188</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>18820</v>
+      </c>
+      <c r="D728" s="3">
+        <v>188</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>18821</v>
+      </c>
+      <c r="D729" s="3">
+        <v>188</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>18822</v>
+      </c>
+      <c r="D730" s="3">
+        <v>188</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>18823</v>
+      </c>
+      <c r="D731" s="3">
+        <v>188</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>18824</v>
+      </c>
+      <c r="D732" s="3">
+        <v>188</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>18825</v>
+      </c>
+      <c r="D733" s="3">
+        <v>188</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋188九天境</t>
+  </si>
+  <si>
+    <t>#先锋189</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13537,7 +13540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="721" spans="3:7">
+    <row r="721" spans="1:8">
       <c r="C721" s="6">
         <v>18813</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="3:7">
+    <row r="722" spans="1:8">
       <c r="C722" s="6">
         <v>18814</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="723" spans="3:7">
+    <row r="723" spans="1:8">
       <c r="C723" s="6">
         <v>18815</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="724" spans="3:7">
+    <row r="724" spans="1:8">
       <c r="C724" s="6">
         <v>18816</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="725" spans="3:7">
+    <row r="725" spans="1:8">
       <c r="C725" s="6">
         <v>18817</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="3:7">
+    <row r="726" spans="1:8">
       <c r="C726" s="6">
         <v>18818</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="727" spans="3:7">
+    <row r="727" spans="1:8">
       <c r="C727" s="6">
         <v>18819</v>
       </c>
@@ -13656,7 +13659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="728" spans="3:7">
+    <row r="728" spans="1:8">
       <c r="C728" s="6">
         <v>18820</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="729" spans="3:7">
+    <row r="729" spans="1:8">
       <c r="C729" s="6">
         <v>18821</v>
       </c>
@@ -13690,7 +13693,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="730" spans="3:7">
+    <row r="730" spans="1:8">
       <c r="C730" s="6">
         <v>18822</v>
       </c>
@@ -13707,7 +13710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="731" spans="3:7">
+    <row r="731" spans="1:8">
       <c r="C731" s="6">
         <v>18823</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="732" spans="3:7">
+    <row r="732" spans="1:8">
       <c r="C732" s="6">
         <v>18824</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="733" spans="3:7">
+    <row r="733" spans="1:8">
       <c r="C733" s="6">
         <v>18825</v>
       </c>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>18901</v>
+      </c>
+      <c r="D735" s="3">
+        <v>189</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20445</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>18902</v>
+      </c>
+      <c r="D736" s="3">
+        <v>189</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20446</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>18903</v>
+      </c>
+      <c r="D737" s="3">
+        <v>189</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20447</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>18904</v>
+      </c>
+      <c r="D738" s="3">
+        <v>189</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20448</v>
+      </c>
+    </row>
+    <row r="739" spans="3:8">
+      <c r="C739" s="6">
+        <v>18905</v>
+      </c>
+      <c r="D739" s="3">
+        <v>189</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:8">
+      <c r="C740" s="6">
+        <v>18906</v>
+      </c>
+      <c r="D740" s="3">
+        <v>189</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:8">
+      <c r="C741" s="6">
+        <v>18907</v>
+      </c>
+      <c r="D741" s="3">
+        <v>189</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:8">
+      <c r="C742" s="6">
+        <v>18908</v>
+      </c>
+      <c r="D742" s="3">
+        <v>189</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:8">
+      <c r="C743" s="6">
+        <v>18909</v>
+      </c>
+      <c r="D743" s="3">
+        <v>189</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:8">
+      <c r="C744" s="6">
+        <v>18910</v>
+      </c>
+      <c r="D744" s="3">
+        <v>189</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:8">
+      <c r="C745" s="6">
+        <v>18911</v>
+      </c>
+      <c r="D745" s="3">
+        <v>189</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:8">
+      <c r="C746" s="6">
+        <v>18912</v>
+      </c>
+      <c r="D746" s="3">
+        <v>189</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:8">
+      <c r="C747" s="6">
+        <v>18913</v>
+      </c>
+      <c r="D747" s="3">
+        <v>189</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:8">
+      <c r="C748" s="6">
+        <v>18914</v>
+      </c>
+      <c r="D748" s="3">
+        <v>189</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:8">
+      <c r="C749" s="6">
+        <v>18915</v>
+      </c>
+      <c r="D749" s="3">
+        <v>189</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:8">
+      <c r="C750" s="6">
+        <v>18916</v>
+      </c>
+      <c r="D750" s="3">
+        <v>189</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:8">
+      <c r="C751" s="6">
+        <v>18917</v>
+      </c>
+      <c r="D751" s="3">
+        <v>189</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:8">
+      <c r="C752" s="6">
+        <v>18918</v>
+      </c>
+      <c r="D752" s="3">
+        <v>189</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>18919</v>
+      </c>
+      <c r="D753" s="3">
+        <v>189</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>18920</v>
+      </c>
+      <c r="D754" s="3">
+        <v>189</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>18921</v>
+      </c>
+      <c r="D755" s="3">
+        <v>189</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>18922</v>
+      </c>
+      <c r="D756" s="3">
+        <v>189</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>18923</v>
+      </c>
+      <c r="D757" s="3">
+        <v>189</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>18924</v>
+      </c>
+      <c r="D758" s="3">
+        <v>189</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>18925</v>
+      </c>
+      <c r="D759" s="3">
+        <v>189</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>#先锋189</t>
+  </si>
+  <si>
+    <t>#先锋190</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O785"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14084,7 +14087,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="753" spans="3:7">
+    <row r="753" spans="1:8">
       <c r="C753" s="6">
         <v>18919</v>
       </c>
@@ -14101,7 +14104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="754" spans="3:7">
+    <row r="754" spans="1:8">
       <c r="C754" s="6">
         <v>18920</v>
       </c>
@@ -14118,7 +14121,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="755" spans="3:7">
+    <row r="755" spans="1:8">
       <c r="C755" s="6">
         <v>18921</v>
       </c>
@@ -14135,7 +14138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="756" spans="3:7">
+    <row r="756" spans="1:8">
       <c r="C756" s="6">
         <v>18922</v>
       </c>
@@ -14152,7 +14155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="757" spans="3:7">
+    <row r="757" spans="1:8">
       <c r="C757" s="6">
         <v>18923</v>
       </c>
@@ -14169,7 +14172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="758" spans="3:7">
+    <row r="758" spans="1:8">
       <c r="C758" s="6">
         <v>18924</v>
       </c>
@@ -14186,7 +14189,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="759" spans="3:7">
+    <row r="759" spans="1:8">
       <c r="C759" s="6">
         <v>18925</v>
       </c>
@@ -14200,6 +14203,448 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C761" s="6">
+        <v>19001</v>
+      </c>
+      <c r="D761" s="3">
+        <v>190</v>
+      </c>
+      <c r="E761" s="5">
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H761" s="3">
+        <v>20555</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="6">
+        <v>19002</v>
+      </c>
+      <c r="D762" s="3">
+        <v>190</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20556</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8">
+      <c r="C763" s="6">
+        <v>19003</v>
+      </c>
+      <c r="D763" s="3">
+        <v>190</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20557</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8">
+      <c r="C764" s="6">
+        <v>19004</v>
+      </c>
+      <c r="D764" s="3">
+        <v>190</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20558</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8">
+      <c r="C765" s="6">
+        <v>19005</v>
+      </c>
+      <c r="D765" s="3">
+        <v>190</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8">
+      <c r="C766" s="6">
+        <v>19006</v>
+      </c>
+      <c r="D766" s="3">
+        <v>190</v>
+      </c>
+      <c r="E766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8">
+      <c r="C767" s="6">
+        <v>19007</v>
+      </c>
+      <c r="D767" s="3">
+        <v>190</v>
+      </c>
+      <c r="E767" s="5">
+        <v>1</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8">
+      <c r="C768" s="6">
+        <v>19008</v>
+      </c>
+      <c r="D768" s="3">
+        <v>190</v>
+      </c>
+      <c r="E768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>19009</v>
+      </c>
+      <c r="D769" s="3">
+        <v>190</v>
+      </c>
+      <c r="E769" s="3">
+        <v>1</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>19010</v>
+      </c>
+      <c r="D770" s="3">
+        <v>190</v>
+      </c>
+      <c r="E770" s="5">
+        <v>1</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>19011</v>
+      </c>
+      <c r="D771" s="3">
+        <v>190</v>
+      </c>
+      <c r="E771" s="5">
+        <v>1</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>19012</v>
+      </c>
+      <c r="D772" s="3">
+        <v>190</v>
+      </c>
+      <c r="E772" s="5">
+        <v>1</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>19013</v>
+      </c>
+      <c r="D773" s="3">
+        <v>190</v>
+      </c>
+      <c r="E773" s="3">
+        <v>1</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>19014</v>
+      </c>
+      <c r="D774" s="3">
+        <v>190</v>
+      </c>
+      <c r="E774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>19015</v>
+      </c>
+      <c r="D775" s="3">
+        <v>190</v>
+      </c>
+      <c r="E775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>19016</v>
+      </c>
+      <c r="D776" s="3">
+        <v>190</v>
+      </c>
+      <c r="E776" s="5">
+        <v>1</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>19017</v>
+      </c>
+      <c r="D777" s="3">
+        <v>190</v>
+      </c>
+      <c r="E777" s="3">
+        <v>1</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>19018</v>
+      </c>
+      <c r="D778" s="3">
+        <v>190</v>
+      </c>
+      <c r="E778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>19019</v>
+      </c>
+      <c r="D779" s="3">
+        <v>190</v>
+      </c>
+      <c r="E779" s="5">
+        <v>1</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>19020</v>
+      </c>
+      <c r="D780" s="3">
+        <v>190</v>
+      </c>
+      <c r="E780" s="5">
+        <v>1</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>19021</v>
+      </c>
+      <c r="D781" s="3">
+        <v>190</v>
+      </c>
+      <c r="E781" s="3">
+        <v>1</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>19022</v>
+      </c>
+      <c r="D782" s="3">
+        <v>190</v>
+      </c>
+      <c r="E782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>19023</v>
+      </c>
+      <c r="D783" s="3">
+        <v>190</v>
+      </c>
+      <c r="E783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>19024</v>
+      </c>
+      <c r="D784" s="3">
+        <v>190</v>
+      </c>
+      <c r="E784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>19025</v>
+      </c>
+      <c r="D785" s="3">
+        <v>190</v>
+      </c>
+      <c r="E785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +14765,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +14783,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +14801,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +14819,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +14839,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14937,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -244,7 +244,10 @@
     <t>#先锋189</t>
   </si>
   <si>
-    <t>#先锋190</t>
+    <t>#先锋190逐月谷</t>
+  </si>
+  <si>
+    <t>#先锋191</t>
   </si>
   <si>
     <t>Center</t>
@@ -1272,7 +1275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O785"/>
+  <dimension ref="A3:O811"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14631,7 +14634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="785" spans="3:7">
+    <row r="785" spans="1:8">
       <c r="C785" s="6">
         <v>19025</v>
       </c>
@@ -14645,6 +14648,448 @@
         <v>42</v>
       </c>
       <c r="G785" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8">
+      <c r="A787" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C787" s="6">
+        <v>19101</v>
+      </c>
+      <c r="D787" s="3">
+        <v>191</v>
+      </c>
+      <c r="E787" s="5">
+        <v>1</v>
+      </c>
+      <c r="F787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H787" s="3">
+        <v>20595</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8">
+      <c r="A788" s="1"/>
+      <c r="B788" s="1"/>
+      <c r="C788" s="6">
+        <v>19102</v>
+      </c>
+      <c r="D788" s="3">
+        <v>191</v>
+      </c>
+      <c r="E788" s="5">
+        <v>1</v>
+      </c>
+      <c r="F788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H788" s="3">
+        <v>20596</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8">
+      <c r="C789" s="6">
+        <v>19103</v>
+      </c>
+      <c r="D789" s="3">
+        <v>191</v>
+      </c>
+      <c r="E789" s="5">
+        <v>1</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H789" s="3">
+        <v>20597</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8">
+      <c r="C790" s="6">
+        <v>19104</v>
+      </c>
+      <c r="D790" s="3">
+        <v>191</v>
+      </c>
+      <c r="E790" s="5">
+        <v>1</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H790" s="3">
+        <v>20598</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8">
+      <c r="C791" s="6">
+        <v>19105</v>
+      </c>
+      <c r="D791" s="3">
+        <v>191</v>
+      </c>
+      <c r="E791" s="3">
+        <v>1</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8">
+      <c r="C792" s="6">
+        <v>19106</v>
+      </c>
+      <c r="D792" s="3">
+        <v>191</v>
+      </c>
+      <c r="E792" s="5">
+        <v>1</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8">
+      <c r="C793" s="6">
+        <v>19107</v>
+      </c>
+      <c r="D793" s="3">
+        <v>191</v>
+      </c>
+      <c r="E793" s="5">
+        <v>1</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8">
+      <c r="C794" s="6">
+        <v>19108</v>
+      </c>
+      <c r="D794" s="3">
+        <v>191</v>
+      </c>
+      <c r="E794" s="5">
+        <v>1</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8">
+      <c r="C795" s="6">
+        <v>19109</v>
+      </c>
+      <c r="D795" s="3">
+        <v>191</v>
+      </c>
+      <c r="E795" s="3">
+        <v>1</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8">
+      <c r="C796" s="6">
+        <v>19110</v>
+      </c>
+      <c r="D796" s="3">
+        <v>191</v>
+      </c>
+      <c r="E796" s="5">
+        <v>1</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8">
+      <c r="C797" s="6">
+        <v>19111</v>
+      </c>
+      <c r="D797" s="3">
+        <v>191</v>
+      </c>
+      <c r="E797" s="5">
+        <v>1</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8">
+      <c r="C798" s="6">
+        <v>19112</v>
+      </c>
+      <c r="D798" s="3">
+        <v>191</v>
+      </c>
+      <c r="E798" s="5">
+        <v>1</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8">
+      <c r="C799" s="6">
+        <v>19113</v>
+      </c>
+      <c r="D799" s="3">
+        <v>191</v>
+      </c>
+      <c r="E799" s="3">
+        <v>1</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8">
+      <c r="C800" s="6">
+        <v>19114</v>
+      </c>
+      <c r="D800" s="3">
+        <v>191</v>
+      </c>
+      <c r="E800" s="5">
+        <v>1</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="801" spans="3:7">
+      <c r="C801" s="6">
+        <v>19115</v>
+      </c>
+      <c r="D801" s="3">
+        <v>191</v>
+      </c>
+      <c r="E801" s="5">
+        <v>1</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="802" spans="3:7">
+      <c r="C802" s="6">
+        <v>19116</v>
+      </c>
+      <c r="D802" s="3">
+        <v>191</v>
+      </c>
+      <c r="E802" s="5">
+        <v>1</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="803" spans="3:7">
+      <c r="C803" s="6">
+        <v>19117</v>
+      </c>
+      <c r="D803" s="3">
+        <v>191</v>
+      </c>
+      <c r="E803" s="3">
+        <v>1</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="804" spans="3:7">
+      <c r="C804" s="6">
+        <v>19118</v>
+      </c>
+      <c r="D804" s="3">
+        <v>191</v>
+      </c>
+      <c r="E804" s="5">
+        <v>1</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="805" spans="3:7">
+      <c r="C805" s="6">
+        <v>19119</v>
+      </c>
+      <c r="D805" s="3">
+        <v>191</v>
+      </c>
+      <c r="E805" s="5">
+        <v>1</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="806" spans="3:7">
+      <c r="C806" s="6">
+        <v>19120</v>
+      </c>
+      <c r="D806" s="3">
+        <v>191</v>
+      </c>
+      <c r="E806" s="5">
+        <v>1</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="807" spans="3:7">
+      <c r="C807" s="6">
+        <v>19121</v>
+      </c>
+      <c r="D807" s="3">
+        <v>191</v>
+      </c>
+      <c r="E807" s="3">
+        <v>1</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="808" spans="3:7">
+      <c r="C808" s="6">
+        <v>19122</v>
+      </c>
+      <c r="D808" s="3">
+        <v>191</v>
+      </c>
+      <c r="E808" s="5">
+        <v>1</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="809" spans="3:7">
+      <c r="C809" s="6">
+        <v>19123</v>
+      </c>
+      <c r="D809" s="3">
+        <v>191</v>
+      </c>
+      <c r="E809" s="5">
+        <v>1</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="810" spans="3:7">
+      <c r="C810" s="6">
+        <v>19124</v>
+      </c>
+      <c r="D810" s="3">
+        <v>191</v>
+      </c>
+      <c r="E810" s="5">
+        <v>1</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="811" spans="3:7">
+      <c r="C811" s="6">
+        <v>19125</v>
+      </c>
+      <c r="D811" s="3">
+        <v>191</v>
+      </c>
+      <c r="E811" s="3">
+        <v>1</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G811" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14765,10 +15210,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14783,10 +15228,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14801,10 +15246,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14819,10 +15264,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14839,10 +15284,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14937,10 +15382,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -199,9 +199,6 @@
     <t>#先锋139吉祥如意</t>
   </si>
   <si>
-    <t>#先锋147紫禁之巅</t>
-  </si>
-  <si>
     <t>#先锋155雷霆万钧</t>
   </si>
   <si>
@@ -214,22 +211,13 @@
     <t>#先锋176普天同庆</t>
   </si>
   <si>
-    <t>#先锋178风暴之地</t>
-  </si>
-  <si>
     <t>#先锋180生命之树</t>
   </si>
   <si>
     <t>#先锋182泰坦之锤</t>
   </si>
   <si>
-    <t>#先锋183圣光神域</t>
-  </si>
-  <si>
     <t>#先锋184炽焰神殿</t>
-  </si>
-  <si>
-    <t>#先锋185山河万里</t>
   </si>
   <si>
     <t>#先锋186忘川彼岸</t>
@@ -247,7 +235,7 @@
     <t>#先锋190逐月谷</t>
   </si>
   <si>
-    <t>#先锋191</t>
+    <t>#先锋191沧澜神域</t>
   </si>
   <si>
     <t>Center</t>
@@ -1275,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O811"/>
+  <dimension ref="A3:O707"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -7584,10 +7572,10 @@
         <v>56</v>
       </c>
       <c r="C371" s="6">
-        <v>14701</v>
+        <v>15501</v>
       </c>
       <c r="D371" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E371" s="5">
         <v>1</v>
@@ -7599,17 +7587,17 @@
         <v>15</v>
       </c>
       <c r="H371" s="3">
-        <v>20495</v>
+        <v>20605</v>
       </c>
     </row>
     <row r="372" spans="1:8">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="6">
-        <v>14702</v>
+        <v>15502</v>
       </c>
       <c r="D372" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E372" s="5">
         <v>1</v>
@@ -7621,15 +7609,15 @@
         <v>16</v>
       </c>
       <c r="H372" s="3">
-        <v>20496</v>
+        <v>20606</v>
       </c>
     </row>
     <row r="373" spans="1:8">
       <c r="C373" s="6">
-        <v>14703</v>
+        <v>15503</v>
       </c>
       <c r="D373" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E373" s="5">
         <v>1</v>
@@ -7641,15 +7629,15 @@
         <v>18</v>
       </c>
       <c r="H373" s="3">
-        <v>20497</v>
+        <v>20607</v>
       </c>
     </row>
     <row r="374" spans="1:8">
       <c r="C374" s="6">
-        <v>14704</v>
+        <v>15504</v>
       </c>
       <c r="D374" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E374" s="5">
         <v>1</v>
@@ -7661,15 +7649,15 @@
         <v>19</v>
       </c>
       <c r="H374" s="3">
-        <v>20498</v>
+        <v>20608</v>
       </c>
     </row>
     <row r="375" spans="1:8">
       <c r="C375" s="6">
-        <v>14705</v>
+        <v>15505</v>
       </c>
       <c r="D375" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E375" s="3">
         <v>1</v>
@@ -7683,10 +7671,10 @@
     </row>
     <row r="376" spans="1:8">
       <c r="C376" s="6">
-        <v>14706</v>
+        <v>15506</v>
       </c>
       <c r="D376" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E376" s="5">
         <v>1</v>
@@ -7700,10 +7688,10 @@
     </row>
     <row r="377" spans="1:8">
       <c r="C377" s="6">
-        <v>14707</v>
+        <v>15507</v>
       </c>
       <c r="D377" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E377" s="5">
         <v>1</v>
@@ -7717,10 +7705,10 @@
     </row>
     <row r="378" spans="1:8">
       <c r="C378" s="6">
-        <v>14708</v>
+        <v>15508</v>
       </c>
       <c r="D378" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E378" s="5">
         <v>1</v>
@@ -7734,10 +7722,10 @@
     </row>
     <row r="379" spans="1:8">
       <c r="C379" s="6">
-        <v>14709</v>
+        <v>15509</v>
       </c>
       <c r="D379" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E379" s="3">
         <v>1</v>
@@ -7751,10 +7739,10 @@
     </row>
     <row r="380" spans="1:8">
       <c r="C380" s="6">
-        <v>14710</v>
+        <v>15510</v>
       </c>
       <c r="D380" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E380" s="5">
         <v>1</v>
@@ -7768,10 +7756,10 @@
     </row>
     <row r="381" spans="1:8">
       <c r="C381" s="6">
-        <v>14711</v>
+        <v>15511</v>
       </c>
       <c r="D381" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E381" s="5">
         <v>1</v>
@@ -7785,10 +7773,10 @@
     </row>
     <row r="382" spans="1:8">
       <c r="C382" s="6">
-        <v>14712</v>
+        <v>15512</v>
       </c>
       <c r="D382" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E382" s="5">
         <v>1</v>
@@ -7802,10 +7790,10 @@
     </row>
     <row r="383" spans="1:8">
       <c r="C383" s="6">
-        <v>14713</v>
+        <v>15513</v>
       </c>
       <c r="D383" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E383" s="3">
         <v>1</v>
@@ -7819,10 +7807,10 @@
     </row>
     <row r="384" spans="1:8">
       <c r="C384" s="6">
-        <v>14714</v>
+        <v>15514</v>
       </c>
       <c r="D384" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E384" s="5">
         <v>1</v>
@@ -7836,10 +7824,10 @@
     </row>
     <row r="385" spans="1:8">
       <c r="C385" s="6">
-        <v>14715</v>
+        <v>15515</v>
       </c>
       <c r="D385" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E385" s="5">
         <v>1</v>
@@ -7853,10 +7841,10 @@
     </row>
     <row r="386" spans="1:8">
       <c r="C386" s="6">
-        <v>14716</v>
+        <v>15516</v>
       </c>
       <c r="D386" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E386" s="5">
         <v>1</v>
@@ -7870,10 +7858,10 @@
     </row>
     <row r="387" spans="1:8">
       <c r="C387" s="6">
-        <v>14717</v>
+        <v>15517</v>
       </c>
       <c r="D387" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E387" s="3">
         <v>1</v>
@@ -7887,10 +7875,10 @@
     </row>
     <row r="388" spans="1:8">
       <c r="C388" s="6">
-        <v>14718</v>
+        <v>15518</v>
       </c>
       <c r="D388" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E388" s="5">
         <v>1</v>
@@ -7904,10 +7892,10 @@
     </row>
     <row r="389" spans="1:8">
       <c r="C389" s="6">
-        <v>14719</v>
+        <v>15519</v>
       </c>
       <c r="D389" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E389" s="5">
         <v>1</v>
@@ -7921,10 +7909,10 @@
     </row>
     <row r="390" spans="1:8">
       <c r="C390" s="6">
-        <v>14720</v>
+        <v>15520</v>
       </c>
       <c r="D390" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E390" s="5">
         <v>1</v>
@@ -7938,10 +7926,10 @@
     </row>
     <row r="391" spans="1:8">
       <c r="C391" s="6">
-        <v>14721</v>
+        <v>15521</v>
       </c>
       <c r="D391" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E391" s="3">
         <v>1</v>
@@ -7955,10 +7943,10 @@
     </row>
     <row r="392" spans="1:8">
       <c r="C392" s="6">
-        <v>14722</v>
+        <v>15522</v>
       </c>
       <c r="D392" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E392" s="5">
         <v>1</v>
@@ -7972,10 +7960,10 @@
     </row>
     <row r="393" spans="1:8">
       <c r="C393" s="6">
-        <v>14723</v>
+        <v>15523</v>
       </c>
       <c r="D393" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E393" s="5">
         <v>1</v>
@@ -7989,10 +7977,10 @@
     </row>
     <row r="394" spans="1:8">
       <c r="C394" s="6">
-        <v>14724</v>
+        <v>15524</v>
       </c>
       <c r="D394" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E394" s="5">
         <v>1</v>
@@ -8006,10 +7994,10 @@
     </row>
     <row r="395" spans="1:8">
       <c r="C395" s="6">
-        <v>14725</v>
+        <v>15525</v>
       </c>
       <c r="D395" s="3">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E395" s="3">
         <v>1</v>
@@ -8026,10 +8014,10 @@
         <v>57</v>
       </c>
       <c r="C397" s="6">
-        <v>15501</v>
+        <v>16301</v>
       </c>
       <c r="D397" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E397" s="5">
         <v>1</v>
@@ -8041,17 +8029,17 @@
         <v>15</v>
       </c>
       <c r="H397" s="3">
-        <v>20605</v>
+        <v>20525</v>
       </c>
     </row>
     <row r="398" spans="1:8">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="6">
-        <v>15502</v>
+        <v>16302</v>
       </c>
       <c r="D398" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E398" s="5">
         <v>1</v>
@@ -8063,15 +8051,15 @@
         <v>16</v>
       </c>
       <c r="H398" s="3">
-        <v>20606</v>
+        <v>20526</v>
       </c>
     </row>
     <row r="399" spans="1:8">
       <c r="C399" s="6">
-        <v>15503</v>
+        <v>16303</v>
       </c>
       <c r="D399" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E399" s="5">
         <v>1</v>
@@ -8083,15 +8071,15 @@
         <v>18</v>
       </c>
       <c r="H399" s="3">
-        <v>20607</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="400" spans="1:8">
       <c r="C400" s="6">
-        <v>15504</v>
+        <v>16304</v>
       </c>
       <c r="D400" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E400" s="5">
         <v>1</v>
@@ -8103,15 +8091,15 @@
         <v>19</v>
       </c>
       <c r="H400" s="3">
-        <v>20608</v>
+        <v>20528</v>
       </c>
     </row>
     <row r="401" spans="3:7">
       <c r="C401" s="6">
-        <v>15505</v>
+        <v>16305</v>
       </c>
       <c r="D401" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E401" s="3">
         <v>1</v>
@@ -8125,10 +8113,10 @@
     </row>
     <row r="402" spans="3:7">
       <c r="C402" s="6">
-        <v>15506</v>
+        <v>16306</v>
       </c>
       <c r="D402" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E402" s="5">
         <v>1</v>
@@ -8142,10 +8130,10 @@
     </row>
     <row r="403" spans="3:7">
       <c r="C403" s="6">
-        <v>15507</v>
+        <v>16307</v>
       </c>
       <c r="D403" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E403" s="5">
         <v>1</v>
@@ -8159,10 +8147,10 @@
     </row>
     <row r="404" spans="3:7">
       <c r="C404" s="6">
-        <v>15508</v>
+        <v>16308</v>
       </c>
       <c r="D404" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E404" s="5">
         <v>1</v>
@@ -8176,10 +8164,10 @@
     </row>
     <row r="405" spans="3:7">
       <c r="C405" s="6">
-        <v>15509</v>
+        <v>16309</v>
       </c>
       <c r="D405" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E405" s="3">
         <v>1</v>
@@ -8193,10 +8181,10 @@
     </row>
     <row r="406" spans="3:7">
       <c r="C406" s="6">
-        <v>15510</v>
+        <v>16310</v>
       </c>
       <c r="D406" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E406" s="5">
         <v>1</v>
@@ -8210,10 +8198,10 @@
     </row>
     <row r="407" spans="3:7">
       <c r="C407" s="6">
-        <v>15511</v>
+        <v>16311</v>
       </c>
       <c r="D407" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E407" s="5">
         <v>1</v>
@@ -8227,10 +8215,10 @@
     </row>
     <row r="408" spans="3:7">
       <c r="C408" s="6">
-        <v>15512</v>
+        <v>16312</v>
       </c>
       <c r="D408" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E408" s="5">
         <v>1</v>
@@ -8244,10 +8232,10 @@
     </row>
     <row r="409" spans="3:7">
       <c r="C409" s="6">
-        <v>15513</v>
+        <v>16313</v>
       </c>
       <c r="D409" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E409" s="3">
         <v>1</v>
@@ -8261,10 +8249,10 @@
     </row>
     <row r="410" spans="3:7">
       <c r="C410" s="6">
-        <v>15514</v>
+        <v>16314</v>
       </c>
       <c r="D410" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E410" s="5">
         <v>1</v>
@@ -8278,10 +8266,10 @@
     </row>
     <row r="411" spans="3:7">
       <c r="C411" s="6">
-        <v>15515</v>
+        <v>16315</v>
       </c>
       <c r="D411" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E411" s="5">
         <v>1</v>
@@ -8295,10 +8283,10 @@
     </row>
     <row r="412" spans="3:7">
       <c r="C412" s="6">
-        <v>15516</v>
+        <v>16316</v>
       </c>
       <c r="D412" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E412" s="5">
         <v>1</v>
@@ -8312,10 +8300,10 @@
     </row>
     <row r="413" spans="3:7">
       <c r="C413" s="6">
-        <v>15517</v>
+        <v>16317</v>
       </c>
       <c r="D413" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E413" s="3">
         <v>1</v>
@@ -8329,10 +8317,10 @@
     </row>
     <row r="414" spans="3:7">
       <c r="C414" s="6">
-        <v>15518</v>
+        <v>16318</v>
       </c>
       <c r="D414" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E414" s="5">
         <v>1</v>
@@ -8346,10 +8334,10 @@
     </row>
     <row r="415" spans="3:7">
       <c r="C415" s="6">
-        <v>15519</v>
+        <v>16319</v>
       </c>
       <c r="D415" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E415" s="5">
         <v>1</v>
@@ -8363,10 +8351,10 @@
     </row>
     <row r="416" spans="3:7">
       <c r="C416" s="6">
-        <v>15520</v>
+        <v>16320</v>
       </c>
       <c r="D416" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E416" s="5">
         <v>1</v>
@@ -8380,10 +8368,10 @@
     </row>
     <row r="417" spans="1:8">
       <c r="C417" s="6">
-        <v>15521</v>
+        <v>16321</v>
       </c>
       <c r="D417" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E417" s="3">
         <v>1</v>
@@ -8397,10 +8385,10 @@
     </row>
     <row r="418" spans="1:8">
       <c r="C418" s="6">
-        <v>15522</v>
+        <v>16322</v>
       </c>
       <c r="D418" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E418" s="5">
         <v>1</v>
@@ -8414,10 +8402,10 @@
     </row>
     <row r="419" spans="1:8">
       <c r="C419" s="6">
-        <v>15523</v>
+        <v>16323</v>
       </c>
       <c r="D419" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E419" s="5">
         <v>1</v>
@@ -8431,10 +8419,10 @@
     </row>
     <row r="420" spans="1:8">
       <c r="C420" s="6">
-        <v>15524</v>
+        <v>16324</v>
       </c>
       <c r="D420" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E420" s="5">
         <v>1</v>
@@ -8448,10 +8436,10 @@
     </row>
     <row r="421" spans="1:8">
       <c r="C421" s="6">
-        <v>15525</v>
+        <v>16325</v>
       </c>
       <c r="D421" s="3">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E421" s="3">
         <v>1</v>
@@ -8468,10 +8456,10 @@
         <v>58</v>
       </c>
       <c r="C423" s="6">
-        <v>16301</v>
+        <v>17201</v>
       </c>
       <c r="D423" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E423" s="5">
         <v>1</v>
@@ -8483,17 +8471,17 @@
         <v>15</v>
       </c>
       <c r="H423" s="3">
-        <v>20525</v>
+        <v>20585</v>
       </c>
     </row>
     <row r="424" spans="1:8">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="6">
-        <v>16302</v>
+        <v>17202</v>
       </c>
       <c r="D424" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E424" s="5">
         <v>1</v>
@@ -8505,15 +8493,15 @@
         <v>16</v>
       </c>
       <c r="H424" s="3">
-        <v>20526</v>
+        <v>20586</v>
       </c>
     </row>
     <row r="425" spans="1:8">
       <c r="C425" s="6">
-        <v>16303</v>
+        <v>17203</v>
       </c>
       <c r="D425" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E425" s="5">
         <v>1</v>
@@ -8525,15 +8513,15 @@
         <v>18</v>
       </c>
       <c r="H425" s="3">
-        <v>20527</v>
+        <v>20587</v>
       </c>
     </row>
     <row r="426" spans="1:8">
       <c r="C426" s="6">
-        <v>16304</v>
+        <v>17204</v>
       </c>
       <c r="D426" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E426" s="5">
         <v>1</v>
@@ -8545,15 +8533,15 @@
         <v>19</v>
       </c>
       <c r="H426" s="3">
-        <v>20528</v>
+        <v>20588</v>
       </c>
     </row>
     <row r="427" spans="1:8">
       <c r="C427" s="6">
-        <v>16305</v>
+        <v>17205</v>
       </c>
       <c r="D427" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E427" s="3">
         <v>1</v>
@@ -8567,10 +8555,10 @@
     </row>
     <row r="428" spans="1:8">
       <c r="C428" s="6">
-        <v>16306</v>
+        <v>17206</v>
       </c>
       <c r="D428" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E428" s="5">
         <v>1</v>
@@ -8584,10 +8572,10 @@
     </row>
     <row r="429" spans="1:8">
       <c r="C429" s="6">
-        <v>16307</v>
+        <v>17207</v>
       </c>
       <c r="D429" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E429" s="5">
         <v>1</v>
@@ -8601,10 +8589,10 @@
     </row>
     <row r="430" spans="1:8">
       <c r="C430" s="6">
-        <v>16308</v>
+        <v>17208</v>
       </c>
       <c r="D430" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E430" s="5">
         <v>1</v>
@@ -8618,10 +8606,10 @@
     </row>
     <row r="431" spans="1:8">
       <c r="C431" s="6">
-        <v>16309</v>
+        <v>17209</v>
       </c>
       <c r="D431" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E431" s="3">
         <v>1</v>
@@ -8635,10 +8623,10 @@
     </row>
     <row r="432" spans="1:8">
       <c r="C432" s="6">
-        <v>16310</v>
+        <v>17210</v>
       </c>
       <c r="D432" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E432" s="5">
         <v>1</v>
@@ -8652,10 +8640,10 @@
     </row>
     <row r="433" spans="3:7">
       <c r="C433" s="6">
-        <v>16311</v>
+        <v>17211</v>
       </c>
       <c r="D433" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E433" s="5">
         <v>1</v>
@@ -8669,10 +8657,10 @@
     </row>
     <row r="434" spans="3:7">
       <c r="C434" s="6">
-        <v>16312</v>
+        <v>17212</v>
       </c>
       <c r="D434" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E434" s="5">
         <v>1</v>
@@ -8686,10 +8674,10 @@
     </row>
     <row r="435" spans="3:7">
       <c r="C435" s="6">
-        <v>16313</v>
+        <v>17213</v>
       </c>
       <c r="D435" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E435" s="3">
         <v>1</v>
@@ -8703,10 +8691,10 @@
     </row>
     <row r="436" spans="3:7">
       <c r="C436" s="6">
-        <v>16314</v>
+        <v>17214</v>
       </c>
       <c r="D436" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E436" s="5">
         <v>1</v>
@@ -8720,10 +8708,10 @@
     </row>
     <row r="437" spans="3:7">
       <c r="C437" s="6">
-        <v>16315</v>
+        <v>17215</v>
       </c>
       <c r="D437" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E437" s="5">
         <v>1</v>
@@ -8737,10 +8725,10 @@
     </row>
     <row r="438" spans="3:7">
       <c r="C438" s="6">
-        <v>16316</v>
+        <v>17216</v>
       </c>
       <c r="D438" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E438" s="5">
         <v>1</v>
@@ -8754,10 +8742,10 @@
     </row>
     <row r="439" spans="3:7">
       <c r="C439" s="6">
-        <v>16317</v>
+        <v>17217</v>
       </c>
       <c r="D439" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E439" s="3">
         <v>1</v>
@@ -8771,10 +8759,10 @@
     </row>
     <row r="440" spans="3:7">
       <c r="C440" s="6">
-        <v>16318</v>
+        <v>17218</v>
       </c>
       <c r="D440" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E440" s="5">
         <v>1</v>
@@ -8788,10 +8776,10 @@
     </row>
     <row r="441" spans="3:7">
       <c r="C441" s="6">
-        <v>16319</v>
+        <v>17219</v>
       </c>
       <c r="D441" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E441" s="5">
         <v>1</v>
@@ -8805,10 +8793,10 @@
     </row>
     <row r="442" spans="3:7">
       <c r="C442" s="6">
-        <v>16320</v>
+        <v>17220</v>
       </c>
       <c r="D442" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E442" s="5">
         <v>1</v>
@@ -8822,10 +8810,10 @@
     </row>
     <row r="443" spans="3:7">
       <c r="C443" s="6">
-        <v>16321</v>
+        <v>17221</v>
       </c>
       <c r="D443" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E443" s="3">
         <v>1</v>
@@ -8839,10 +8827,10 @@
     </row>
     <row r="444" spans="3:7">
       <c r="C444" s="6">
-        <v>16322</v>
+        <v>17222</v>
       </c>
       <c r="D444" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E444" s="5">
         <v>1</v>
@@ -8856,10 +8844,10 @@
     </row>
     <row r="445" spans="3:7">
       <c r="C445" s="6">
-        <v>16323</v>
+        <v>17223</v>
       </c>
       <c r="D445" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E445" s="5">
         <v>1</v>
@@ -8873,10 +8861,10 @@
     </row>
     <row r="446" spans="3:7">
       <c r="C446" s="6">
-        <v>16324</v>
+        <v>17224</v>
       </c>
       <c r="D446" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E446" s="5">
         <v>1</v>
@@ -8890,10 +8878,10 @@
     </row>
     <row r="447" spans="3:7">
       <c r="C447" s="6">
-        <v>16325</v>
+        <v>17225</v>
       </c>
       <c r="D447" s="3">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E447" s="3">
         <v>1</v>
@@ -8910,10 +8898,10 @@
         <v>59</v>
       </c>
       <c r="C449" s="6">
-        <v>17201</v>
+        <v>17601</v>
       </c>
       <c r="D449" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E449" s="5">
         <v>1</v>
@@ -8925,17 +8913,17 @@
         <v>15</v>
       </c>
       <c r="H449" s="3">
-        <v>20585</v>
+        <v>20505</v>
       </c>
     </row>
     <row r="450" spans="1:8">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="6">
-        <v>17202</v>
+        <v>17602</v>
       </c>
       <c r="D450" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E450" s="5">
         <v>1</v>
@@ -8947,15 +8935,15 @@
         <v>16</v>
       </c>
       <c r="H450" s="3">
-        <v>20586</v>
+        <v>20506</v>
       </c>
     </row>
     <row r="451" spans="1:8">
       <c r="C451" s="6">
-        <v>17203</v>
+        <v>17603</v>
       </c>
       <c r="D451" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E451" s="5">
         <v>1</v>
@@ -8967,15 +8955,15 @@
         <v>18</v>
       </c>
       <c r="H451" s="3">
-        <v>20587</v>
+        <v>20507</v>
       </c>
     </row>
     <row r="452" spans="1:8">
       <c r="C452" s="6">
-        <v>17204</v>
+        <v>17604</v>
       </c>
       <c r="D452" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E452" s="5">
         <v>1</v>
@@ -8987,15 +8975,15 @@
         <v>19</v>
       </c>
       <c r="H452" s="3">
-        <v>20588</v>
+        <v>20508</v>
       </c>
     </row>
     <row r="453" spans="1:8">
       <c r="C453" s="6">
-        <v>17205</v>
+        <v>17605</v>
       </c>
       <c r="D453" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E453" s="3">
         <v>1</v>
@@ -9009,10 +8997,10 @@
     </row>
     <row r="454" spans="1:8">
       <c r="C454" s="6">
-        <v>17206</v>
+        <v>17606</v>
       </c>
       <c r="D454" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E454" s="5">
         <v>1</v>
@@ -9026,10 +9014,10 @@
     </row>
     <row r="455" spans="1:8">
       <c r="C455" s="6">
-        <v>17207</v>
+        <v>17607</v>
       </c>
       <c r="D455" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E455" s="5">
         <v>1</v>
@@ -9043,10 +9031,10 @@
     </row>
     <row r="456" spans="1:8">
       <c r="C456" s="6">
-        <v>17208</v>
+        <v>17608</v>
       </c>
       <c r="D456" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E456" s="5">
         <v>1</v>
@@ -9060,10 +9048,10 @@
     </row>
     <row r="457" spans="1:8">
       <c r="C457" s="6">
-        <v>17209</v>
+        <v>17609</v>
       </c>
       <c r="D457" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E457" s="3">
         <v>1</v>
@@ -9077,10 +9065,10 @@
     </row>
     <row r="458" spans="1:8">
       <c r="C458" s="6">
-        <v>17210</v>
+        <v>17610</v>
       </c>
       <c r="D458" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E458" s="5">
         <v>1</v>
@@ -9094,10 +9082,10 @@
     </row>
     <row r="459" spans="1:8">
       <c r="C459" s="6">
-        <v>17211</v>
+        <v>17611</v>
       </c>
       <c r="D459" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E459" s="5">
         <v>1</v>
@@ -9111,10 +9099,10 @@
     </row>
     <row r="460" spans="1:8">
       <c r="C460" s="6">
-        <v>17212</v>
+        <v>17612</v>
       </c>
       <c r="D460" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E460" s="5">
         <v>1</v>
@@ -9128,10 +9116,10 @@
     </row>
     <row r="461" spans="1:8">
       <c r="C461" s="6">
-        <v>17213</v>
+        <v>17613</v>
       </c>
       <c r="D461" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E461" s="3">
         <v>1</v>
@@ -9145,10 +9133,10 @@
     </row>
     <row r="462" spans="1:8">
       <c r="C462" s="6">
-        <v>17214</v>
+        <v>17614</v>
       </c>
       <c r="D462" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E462" s="5">
         <v>1</v>
@@ -9162,10 +9150,10 @@
     </row>
     <row r="463" spans="1:8">
       <c r="C463" s="6">
-        <v>17215</v>
+        <v>17615</v>
       </c>
       <c r="D463" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E463" s="5">
         <v>1</v>
@@ -9179,10 +9167,10 @@
     </row>
     <row r="464" spans="1:8">
       <c r="C464" s="6">
-        <v>17216</v>
+        <v>17616</v>
       </c>
       <c r="D464" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E464" s="5">
         <v>1</v>
@@ -9196,10 +9184,10 @@
     </row>
     <row r="465" spans="1:8">
       <c r="C465" s="6">
-        <v>17217</v>
+        <v>17617</v>
       </c>
       <c r="D465" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E465" s="3">
         <v>1</v>
@@ -9213,10 +9201,10 @@
     </row>
     <row r="466" spans="1:8">
       <c r="C466" s="6">
-        <v>17218</v>
+        <v>17618</v>
       </c>
       <c r="D466" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E466" s="5">
         <v>1</v>
@@ -9230,10 +9218,10 @@
     </row>
     <row r="467" spans="1:8">
       <c r="C467" s="6">
-        <v>17219</v>
+        <v>17619</v>
       </c>
       <c r="D467" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E467" s="5">
         <v>1</v>
@@ -9247,10 +9235,10 @@
     </row>
     <row r="468" spans="1:8">
       <c r="C468" s="6">
-        <v>17220</v>
+        <v>17620</v>
       </c>
       <c r="D468" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E468" s="5">
         <v>1</v>
@@ -9264,10 +9252,10 @@
     </row>
     <row r="469" spans="1:8">
       <c r="C469" s="6">
-        <v>17221</v>
+        <v>17621</v>
       </c>
       <c r="D469" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E469" s="3">
         <v>1</v>
@@ -9281,10 +9269,10 @@
     </row>
     <row r="470" spans="1:8">
       <c r="C470" s="6">
-        <v>17222</v>
+        <v>17622</v>
       </c>
       <c r="D470" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E470" s="5">
         <v>1</v>
@@ -9298,10 +9286,10 @@
     </row>
     <row r="471" spans="1:8">
       <c r="C471" s="6">
-        <v>17223</v>
+        <v>17623</v>
       </c>
       <c r="D471" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E471" s="5">
         <v>1</v>
@@ -9315,10 +9303,10 @@
     </row>
     <row r="472" spans="1:8">
       <c r="C472" s="6">
-        <v>17224</v>
+        <v>17624</v>
       </c>
       <c r="D472" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E472" s="5">
         <v>1</v>
@@ -9332,10 +9320,10 @@
     </row>
     <row r="473" spans="1:8">
       <c r="C473" s="6">
-        <v>17225</v>
+        <v>17625</v>
       </c>
       <c r="D473" s="3">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E473" s="3">
         <v>1</v>
@@ -9352,10 +9340,10 @@
         <v>60</v>
       </c>
       <c r="C475" s="6">
-        <v>17601</v>
+        <v>18001</v>
       </c>
       <c r="D475" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E475" s="5">
         <v>1</v>
@@ -9367,17 +9355,17 @@
         <v>15</v>
       </c>
       <c r="H475" s="3">
-        <v>20505</v>
+        <v>20375</v>
       </c>
     </row>
     <row r="476" spans="1:8">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="6">
-        <v>17602</v>
+        <v>18002</v>
       </c>
       <c r="D476" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E476" s="5">
         <v>1</v>
@@ -9389,15 +9377,15 @@
         <v>16</v>
       </c>
       <c r="H476" s="3">
-        <v>20506</v>
+        <v>20376</v>
       </c>
     </row>
     <row r="477" spans="1:8">
       <c r="C477" s="6">
-        <v>17603</v>
+        <v>18003</v>
       </c>
       <c r="D477" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E477" s="5">
         <v>1</v>
@@ -9409,15 +9397,15 @@
         <v>18</v>
       </c>
       <c r="H477" s="3">
-        <v>20507</v>
+        <v>20377</v>
       </c>
     </row>
     <row r="478" spans="1:8">
       <c r="C478" s="6">
-        <v>17604</v>
+        <v>18004</v>
       </c>
       <c r="D478" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E478" s="5">
         <v>1</v>
@@ -9429,15 +9417,15 @@
         <v>19</v>
       </c>
       <c r="H478" s="3">
-        <v>20508</v>
+        <v>20378</v>
       </c>
     </row>
     <row r="479" spans="1:8">
       <c r="C479" s="6">
-        <v>17605</v>
+        <v>18005</v>
       </c>
       <c r="D479" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E479" s="3">
         <v>1</v>
@@ -9451,10 +9439,10 @@
     </row>
     <row r="480" spans="1:8">
       <c r="C480" s="6">
-        <v>17606</v>
+        <v>18006</v>
       </c>
       <c r="D480" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E480" s="5">
         <v>1</v>
@@ -9468,10 +9456,10 @@
     </row>
     <row r="481" spans="3:7">
       <c r="C481" s="6">
-        <v>17607</v>
+        <v>18007</v>
       </c>
       <c r="D481" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E481" s="5">
         <v>1</v>
@@ -9485,10 +9473,10 @@
     </row>
     <row r="482" spans="3:7">
       <c r="C482" s="6">
-        <v>17608</v>
+        <v>18008</v>
       </c>
       <c r="D482" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E482" s="5">
         <v>1</v>
@@ -9502,10 +9490,10 @@
     </row>
     <row r="483" spans="3:7">
       <c r="C483" s="6">
-        <v>17609</v>
+        <v>18009</v>
       </c>
       <c r="D483" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E483" s="3">
         <v>1</v>
@@ -9519,10 +9507,10 @@
     </row>
     <row r="484" spans="3:7">
       <c r="C484" s="6">
-        <v>17610</v>
+        <v>18010</v>
       </c>
       <c r="D484" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E484" s="5">
         <v>1</v>
@@ -9536,10 +9524,10 @@
     </row>
     <row r="485" spans="3:7">
       <c r="C485" s="6">
-        <v>17611</v>
+        <v>18011</v>
       </c>
       <c r="D485" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E485" s="5">
         <v>1</v>
@@ -9553,10 +9541,10 @@
     </row>
     <row r="486" spans="3:7">
       <c r="C486" s="6">
-        <v>17612</v>
+        <v>18012</v>
       </c>
       <c r="D486" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E486" s="5">
         <v>1</v>
@@ -9570,10 +9558,10 @@
     </row>
     <row r="487" spans="3:7">
       <c r="C487" s="6">
-        <v>17613</v>
+        <v>18013</v>
       </c>
       <c r="D487" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E487" s="3">
         <v>1</v>
@@ -9587,10 +9575,10 @@
     </row>
     <row r="488" spans="3:7">
       <c r="C488" s="6">
-        <v>17614</v>
+        <v>18014</v>
       </c>
       <c r="D488" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E488" s="5">
         <v>1</v>
@@ -9604,10 +9592,10 @@
     </row>
     <row r="489" spans="3:7">
       <c r="C489" s="6">
-        <v>17615</v>
+        <v>18015</v>
       </c>
       <c r="D489" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E489" s="5">
         <v>1</v>
@@ -9621,10 +9609,10 @@
     </row>
     <row r="490" spans="3:7">
       <c r="C490" s="6">
-        <v>17616</v>
+        <v>18016</v>
       </c>
       <c r="D490" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E490" s="5">
         <v>1</v>
@@ -9638,10 +9626,10 @@
     </row>
     <row r="491" spans="3:7">
       <c r="C491" s="6">
-        <v>17617</v>
+        <v>18017</v>
       </c>
       <c r="D491" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E491" s="3">
         <v>1</v>
@@ -9655,10 +9643,10 @@
     </row>
     <row r="492" spans="3:7">
       <c r="C492" s="6">
-        <v>17618</v>
+        <v>18018</v>
       </c>
       <c r="D492" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E492" s="5">
         <v>1</v>
@@ -9672,10 +9660,10 @@
     </row>
     <row r="493" spans="3:7">
       <c r="C493" s="6">
-        <v>17619</v>
+        <v>18019</v>
       </c>
       <c r="D493" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E493" s="5">
         <v>1</v>
@@ -9689,10 +9677,10 @@
     </row>
     <row r="494" spans="3:7">
       <c r="C494" s="6">
-        <v>17620</v>
+        <v>18020</v>
       </c>
       <c r="D494" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E494" s="5">
         <v>1</v>
@@ -9706,10 +9694,10 @@
     </row>
     <row r="495" spans="3:7">
       <c r="C495" s="6">
-        <v>17621</v>
+        <v>18021</v>
       </c>
       <c r="D495" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E495" s="3">
         <v>1</v>
@@ -9723,10 +9711,10 @@
     </row>
     <row r="496" spans="3:7">
       <c r="C496" s="6">
-        <v>17622</v>
+        <v>18022</v>
       </c>
       <c r="D496" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E496" s="5">
         <v>1</v>
@@ -9740,10 +9728,10 @@
     </row>
     <row r="497" spans="1:8">
       <c r="C497" s="6">
-        <v>17623</v>
+        <v>18023</v>
       </c>
       <c r="D497" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E497" s="5">
         <v>1</v>
@@ -9757,10 +9745,10 @@
     </row>
     <row r="498" spans="1:8">
       <c r="C498" s="6">
-        <v>17624</v>
+        <v>18024</v>
       </c>
       <c r="D498" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E498" s="5">
         <v>1</v>
@@ -9774,10 +9762,10 @@
     </row>
     <row r="499" spans="1:8">
       <c r="C499" s="6">
-        <v>17625</v>
+        <v>18025</v>
       </c>
       <c r="D499" s="3">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E499" s="3">
         <v>1</v>
@@ -9794,10 +9782,10 @@
         <v>61</v>
       </c>
       <c r="C501" s="6">
-        <v>17801</v>
+        <v>18201</v>
       </c>
       <c r="D501" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E501" s="5">
         <v>1</v>
@@ -9809,17 +9797,17 @@
         <v>15</v>
       </c>
       <c r="H501" s="3">
-        <v>20565</v>
+        <v>20415</v>
       </c>
     </row>
     <row r="502" spans="1:8">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="6">
-        <v>17802</v>
+        <v>18202</v>
       </c>
       <c r="D502" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E502" s="5">
         <v>1</v>
@@ -9831,15 +9819,15 @@
         <v>16</v>
       </c>
       <c r="H502" s="3">
-        <v>20566</v>
+        <v>20416</v>
       </c>
     </row>
     <row r="503" spans="1:8">
       <c r="C503" s="6">
-        <v>17803</v>
+        <v>18203</v>
       </c>
       <c r="D503" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E503" s="5">
         <v>1</v>
@@ -9851,15 +9839,15 @@
         <v>18</v>
       </c>
       <c r="H503" s="3">
-        <v>20567</v>
+        <v>20417</v>
       </c>
     </row>
     <row r="504" spans="1:8">
       <c r="C504" s="6">
-        <v>17804</v>
+        <v>18204</v>
       </c>
       <c r="D504" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E504" s="5">
         <v>1</v>
@@ -9871,15 +9859,15 @@
         <v>19</v>
       </c>
       <c r="H504" s="3">
-        <v>20568</v>
+        <v>20418</v>
       </c>
     </row>
     <row r="505" spans="1:8">
       <c r="C505" s="6">
-        <v>17805</v>
+        <v>18205</v>
       </c>
       <c r="D505" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E505" s="3">
         <v>1</v>
@@ -9893,10 +9881,10 @@
     </row>
     <row r="506" spans="1:8">
       <c r="C506" s="6">
-        <v>17806</v>
+        <v>18206</v>
       </c>
       <c r="D506" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E506" s="5">
         <v>1</v>
@@ -9910,10 +9898,10 @@
     </row>
     <row r="507" spans="1:8">
       <c r="C507" s="6">
-        <v>17807</v>
+        <v>18207</v>
       </c>
       <c r="D507" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E507" s="5">
         <v>1</v>
@@ -9927,10 +9915,10 @@
     </row>
     <row r="508" spans="1:8">
       <c r="C508" s="6">
-        <v>17808</v>
+        <v>18208</v>
       </c>
       <c r="D508" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E508" s="5">
         <v>1</v>
@@ -9944,10 +9932,10 @@
     </row>
     <row r="509" spans="1:8">
       <c r="C509" s="6">
-        <v>17809</v>
+        <v>18209</v>
       </c>
       <c r="D509" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E509" s="3">
         <v>1</v>
@@ -9961,10 +9949,10 @@
     </row>
     <row r="510" spans="1:8">
       <c r="C510" s="6">
-        <v>17810</v>
+        <v>18210</v>
       </c>
       <c r="D510" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E510" s="5">
         <v>1</v>
@@ -9978,10 +9966,10 @@
     </row>
     <row r="511" spans="1:8">
       <c r="C511" s="6">
-        <v>17811</v>
+        <v>18211</v>
       </c>
       <c r="D511" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E511" s="5">
         <v>1</v>
@@ -9995,10 +9983,10 @@
     </row>
     <row r="512" spans="1:8">
       <c r="C512" s="6">
-        <v>17812</v>
+        <v>18212</v>
       </c>
       <c r="D512" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E512" s="5">
         <v>1</v>
@@ -10012,10 +10000,10 @@
     </row>
     <row r="513" spans="1:8">
       <c r="C513" s="6">
-        <v>17813</v>
+        <v>18213</v>
       </c>
       <c r="D513" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E513" s="3">
         <v>1</v>
@@ -10029,10 +10017,10 @@
     </row>
     <row r="514" spans="1:8">
       <c r="C514" s="6">
-        <v>17814</v>
+        <v>18214</v>
       </c>
       <c r="D514" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E514" s="5">
         <v>1</v>
@@ -10046,10 +10034,10 @@
     </row>
     <row r="515" spans="1:8">
       <c r="C515" s="6">
-        <v>17815</v>
+        <v>18215</v>
       </c>
       <c r="D515" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E515" s="5">
         <v>1</v>
@@ -10063,10 +10051,10 @@
     </row>
     <row r="516" spans="1:8">
       <c r="C516" s="6">
-        <v>17816</v>
+        <v>18216</v>
       </c>
       <c r="D516" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E516" s="5">
         <v>1</v>
@@ -10080,10 +10068,10 @@
     </row>
     <row r="517" spans="1:8">
       <c r="C517" s="6">
-        <v>17817</v>
+        <v>18217</v>
       </c>
       <c r="D517" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E517" s="3">
         <v>1</v>
@@ -10097,10 +10085,10 @@
     </row>
     <row r="518" spans="1:8">
       <c r="C518" s="6">
-        <v>17818</v>
+        <v>18218</v>
       </c>
       <c r="D518" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E518" s="5">
         <v>1</v>
@@ -10114,10 +10102,10 @@
     </row>
     <row r="519" spans="1:8">
       <c r="C519" s="6">
-        <v>17819</v>
+        <v>18219</v>
       </c>
       <c r="D519" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E519" s="5">
         <v>1</v>
@@ -10131,10 +10119,10 @@
     </row>
     <row r="520" spans="1:8">
       <c r="C520" s="6">
-        <v>17820</v>
+        <v>18220</v>
       </c>
       <c r="D520" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E520" s="5">
         <v>1</v>
@@ -10148,10 +10136,10 @@
     </row>
     <row r="521" spans="1:8">
       <c r="C521" s="6">
-        <v>17821</v>
+        <v>18221</v>
       </c>
       <c r="D521" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E521" s="3">
         <v>1</v>
@@ -10165,10 +10153,10 @@
     </row>
     <row r="522" spans="1:8">
       <c r="C522" s="6">
-        <v>17822</v>
+        <v>18222</v>
       </c>
       <c r="D522" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E522" s="5">
         <v>1</v>
@@ -10182,10 +10170,10 @@
     </row>
     <row r="523" spans="1:8">
       <c r="C523" s="6">
-        <v>17823</v>
+        <v>18223</v>
       </c>
       <c r="D523" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E523" s="5">
         <v>1</v>
@@ -10199,10 +10187,10 @@
     </row>
     <row r="524" spans="1:8">
       <c r="C524" s="6">
-        <v>17824</v>
+        <v>18224</v>
       </c>
       <c r="D524" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E524" s="5">
         <v>1</v>
@@ -10216,10 +10204,10 @@
     </row>
     <row r="525" spans="1:8">
       <c r="C525" s="6">
-        <v>17825</v>
+        <v>18225</v>
       </c>
       <c r="D525" s="3">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E525" s="3">
         <v>1</v>
@@ -10236,10 +10224,10 @@
         <v>62</v>
       </c>
       <c r="C527" s="6">
-        <v>18001</v>
+        <v>18401</v>
       </c>
       <c r="D527" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E527" s="5">
         <v>1</v>
@@ -10251,17 +10239,17 @@
         <v>15</v>
       </c>
       <c r="H527" s="3">
-        <v>20375</v>
+        <v>20515</v>
       </c>
     </row>
     <row r="528" spans="1:8">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="6">
-        <v>18002</v>
+        <v>18402</v>
       </c>
       <c r="D528" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E528" s="5">
         <v>1</v>
@@ -10273,15 +10261,15 @@
         <v>16</v>
       </c>
       <c r="H528" s="3">
-        <v>20376</v>
+        <v>20516</v>
       </c>
     </row>
     <row r="529" spans="3:8">
       <c r="C529" s="6">
-        <v>18003</v>
+        <v>18403</v>
       </c>
       <c r="D529" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E529" s="5">
         <v>1</v>
@@ -10293,15 +10281,15 @@
         <v>18</v>
       </c>
       <c r="H529" s="3">
-        <v>20377</v>
+        <v>20517</v>
       </c>
     </row>
     <row r="530" spans="3:8">
       <c r="C530" s="6">
-        <v>18004</v>
+        <v>18404</v>
       </c>
       <c r="D530" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E530" s="5">
         <v>1</v>
@@ -10313,15 +10301,15 @@
         <v>19</v>
       </c>
       <c r="H530" s="3">
-        <v>20378</v>
+        <v>20518</v>
       </c>
     </row>
     <row r="531" spans="3:8">
       <c r="C531" s="6">
-        <v>18005</v>
+        <v>18405</v>
       </c>
       <c r="D531" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E531" s="3">
         <v>1</v>
@@ -10335,10 +10323,10 @@
     </row>
     <row r="532" spans="3:8">
       <c r="C532" s="6">
-        <v>18006</v>
+        <v>18406</v>
       </c>
       <c r="D532" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E532" s="5">
         <v>1</v>
@@ -10352,10 +10340,10 @@
     </row>
     <row r="533" spans="3:8">
       <c r="C533" s="6">
-        <v>18007</v>
+        <v>18407</v>
       </c>
       <c r="D533" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E533" s="5">
         <v>1</v>
@@ -10369,10 +10357,10 @@
     </row>
     <row r="534" spans="3:8">
       <c r="C534" s="6">
-        <v>18008</v>
+        <v>18408</v>
       </c>
       <c r="D534" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E534" s="5">
         <v>1</v>
@@ -10386,10 +10374,10 @@
     </row>
     <row r="535" spans="3:8">
       <c r="C535" s="6">
-        <v>18009</v>
+        <v>18409</v>
       </c>
       <c r="D535" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E535" s="3">
         <v>1</v>
@@ -10403,10 +10391,10 @@
     </row>
     <row r="536" spans="3:8">
       <c r="C536" s="6">
-        <v>18010</v>
+        <v>18410</v>
       </c>
       <c r="D536" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E536" s="5">
         <v>1</v>
@@ -10420,10 +10408,10 @@
     </row>
     <row r="537" spans="3:8">
       <c r="C537" s="6">
-        <v>18011</v>
+        <v>18411</v>
       </c>
       <c r="D537" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E537" s="5">
         <v>1</v>
@@ -10437,10 +10425,10 @@
     </row>
     <row r="538" spans="3:8">
       <c r="C538" s="6">
-        <v>18012</v>
+        <v>18412</v>
       </c>
       <c r="D538" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E538" s="5">
         <v>1</v>
@@ -10454,10 +10442,10 @@
     </row>
     <row r="539" spans="3:8">
       <c r="C539" s="6">
-        <v>18013</v>
+        <v>18413</v>
       </c>
       <c r="D539" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E539" s="3">
         <v>1</v>
@@ -10471,10 +10459,10 @@
     </row>
     <row r="540" spans="3:8">
       <c r="C540" s="6">
-        <v>18014</v>
+        <v>18414</v>
       </c>
       <c r="D540" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E540" s="5">
         <v>1</v>
@@ -10488,10 +10476,10 @@
     </row>
     <row r="541" spans="3:8">
       <c r="C541" s="6">
-        <v>18015</v>
+        <v>18415</v>
       </c>
       <c r="D541" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E541" s="5">
         <v>1</v>
@@ -10505,10 +10493,10 @@
     </row>
     <row r="542" spans="3:8">
       <c r="C542" s="6">
-        <v>18016</v>
+        <v>18416</v>
       </c>
       <c r="D542" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E542" s="5">
         <v>1</v>
@@ -10522,10 +10510,10 @@
     </row>
     <row r="543" spans="3:8">
       <c r="C543" s="6">
-        <v>18017</v>
+        <v>18417</v>
       </c>
       <c r="D543" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E543" s="3">
         <v>1</v>
@@ -10539,10 +10527,10 @@
     </row>
     <row r="544" spans="3:8">
       <c r="C544" s="6">
-        <v>18018</v>
+        <v>18418</v>
       </c>
       <c r="D544" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E544" s="5">
         <v>1</v>
@@ -10556,10 +10544,10 @@
     </row>
     <row r="545" spans="1:8">
       <c r="C545" s="6">
-        <v>18019</v>
+        <v>18419</v>
       </c>
       <c r="D545" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E545" s="5">
         <v>1</v>
@@ -10573,10 +10561,10 @@
     </row>
     <row r="546" spans="1:8">
       <c r="C546" s="6">
-        <v>18020</v>
+        <v>18420</v>
       </c>
       <c r="D546" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E546" s="5">
         <v>1</v>
@@ -10590,10 +10578,10 @@
     </row>
     <row r="547" spans="1:8">
       <c r="C547" s="6">
-        <v>18021</v>
+        <v>18421</v>
       </c>
       <c r="D547" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E547" s="3">
         <v>1</v>
@@ -10607,10 +10595,10 @@
     </row>
     <row r="548" spans="1:8">
       <c r="C548" s="6">
-        <v>18022</v>
+        <v>18422</v>
       </c>
       <c r="D548" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E548" s="5">
         <v>1</v>
@@ -10624,10 +10612,10 @@
     </row>
     <row r="549" spans="1:8">
       <c r="C549" s="6">
-        <v>18023</v>
+        <v>18423</v>
       </c>
       <c r="D549" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E549" s="5">
         <v>1</v>
@@ -10641,10 +10629,10 @@
     </row>
     <row r="550" spans="1:8">
       <c r="C550" s="6">
-        <v>18024</v>
+        <v>18424</v>
       </c>
       <c r="D550" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E550" s="5">
         <v>1</v>
@@ -10658,10 +10646,10 @@
     </row>
     <row r="551" spans="1:8">
       <c r="C551" s="6">
-        <v>18025</v>
+        <v>18425</v>
       </c>
       <c r="D551" s="3">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E551" s="3">
         <v>1</v>
@@ -10678,10 +10666,10 @@
         <v>63</v>
       </c>
       <c r="C553" s="6">
-        <v>18201</v>
+        <v>18601</v>
       </c>
       <c r="D553" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E553" s="5">
         <v>1</v>
@@ -10693,17 +10681,17 @@
         <v>15</v>
       </c>
       <c r="H553" s="3">
-        <v>20415</v>
+        <v>20615</v>
       </c>
     </row>
     <row r="554" spans="1:8">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="6">
-        <v>18202</v>
+        <v>18602</v>
       </c>
       <c r="D554" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E554" s="5">
         <v>1</v>
@@ -10715,15 +10703,15 @@
         <v>16</v>
       </c>
       <c r="H554" s="3">
-        <v>20416</v>
+        <v>20616</v>
       </c>
     </row>
     <row r="555" spans="1:8">
       <c r="C555" s="6">
-        <v>18203</v>
+        <v>18603</v>
       </c>
       <c r="D555" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E555" s="5">
         <v>1</v>
@@ -10735,15 +10723,15 @@
         <v>18</v>
       </c>
       <c r="H555" s="3">
-        <v>20417</v>
+        <v>20617</v>
       </c>
     </row>
     <row r="556" spans="1:8">
       <c r="C556" s="6">
-        <v>18204</v>
+        <v>18604</v>
       </c>
       <c r="D556" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E556" s="5">
         <v>1</v>
@@ -10755,15 +10743,15 @@
         <v>19</v>
       </c>
       <c r="H556" s="3">
-        <v>20418</v>
+        <v>20618</v>
       </c>
     </row>
     <row r="557" spans="1:8">
       <c r="C557" s="6">
-        <v>18205</v>
+        <v>18605</v>
       </c>
       <c r="D557" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E557" s="3">
         <v>1</v>
@@ -10777,10 +10765,10 @@
     </row>
     <row r="558" spans="1:8">
       <c r="C558" s="6">
-        <v>18206</v>
+        <v>18606</v>
       </c>
       <c r="D558" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E558" s="5">
         <v>1</v>
@@ -10794,10 +10782,10 @@
     </row>
     <row r="559" spans="1:8">
       <c r="C559" s="6">
-        <v>18207</v>
+        <v>18607</v>
       </c>
       <c r="D559" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E559" s="5">
         <v>1</v>
@@ -10811,10 +10799,10 @@
     </row>
     <row r="560" spans="1:8">
       <c r="C560" s="6">
-        <v>18208</v>
+        <v>18608</v>
       </c>
       <c r="D560" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E560" s="5">
         <v>1</v>
@@ -10828,10 +10816,10 @@
     </row>
     <row r="561" spans="3:7">
       <c r="C561" s="6">
-        <v>18209</v>
+        <v>18609</v>
       </c>
       <c r="D561" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E561" s="3">
         <v>1</v>
@@ -10845,10 +10833,10 @@
     </row>
     <row r="562" spans="3:7">
       <c r="C562" s="6">
-        <v>18210</v>
+        <v>18610</v>
       </c>
       <c r="D562" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E562" s="5">
         <v>1</v>
@@ -10862,10 +10850,10 @@
     </row>
     <row r="563" spans="3:7">
       <c r="C563" s="6">
-        <v>18211</v>
+        <v>18611</v>
       </c>
       <c r="D563" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E563" s="5">
         <v>1</v>
@@ -10879,10 +10867,10 @@
     </row>
     <row r="564" spans="3:7">
       <c r="C564" s="6">
-        <v>18212</v>
+        <v>18612</v>
       </c>
       <c r="D564" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E564" s="5">
         <v>1</v>
@@ -10896,10 +10884,10 @@
     </row>
     <row r="565" spans="3:7">
       <c r="C565" s="6">
-        <v>18213</v>
+        <v>18613</v>
       </c>
       <c r="D565" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E565" s="3">
         <v>1</v>
@@ -10913,10 +10901,10 @@
     </row>
     <row r="566" spans="3:7">
       <c r="C566" s="6">
-        <v>18214</v>
+        <v>18614</v>
       </c>
       <c r="D566" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E566" s="5">
         <v>1</v>
@@ -10930,10 +10918,10 @@
     </row>
     <row r="567" spans="3:7">
       <c r="C567" s="6">
-        <v>18215</v>
+        <v>18615</v>
       </c>
       <c r="D567" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E567" s="5">
         <v>1</v>
@@ -10947,10 +10935,10 @@
     </row>
     <row r="568" spans="3:7">
       <c r="C568" s="6">
-        <v>18216</v>
+        <v>18616</v>
       </c>
       <c r="D568" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E568" s="5">
         <v>1</v>
@@ -10964,10 +10952,10 @@
     </row>
     <row r="569" spans="3:7">
       <c r="C569" s="6">
-        <v>18217</v>
+        <v>18617</v>
       </c>
       <c r="D569" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E569" s="3">
         <v>1</v>
@@ -10981,10 +10969,10 @@
     </row>
     <row r="570" spans="3:7">
       <c r="C570" s="6">
-        <v>18218</v>
+        <v>18618</v>
       </c>
       <c r="D570" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E570" s="5">
         <v>1</v>
@@ -10998,10 +10986,10 @@
     </row>
     <row r="571" spans="3:7">
       <c r="C571" s="6">
-        <v>18219</v>
+        <v>18619</v>
       </c>
       <c r="D571" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E571" s="5">
         <v>1</v>
@@ -11015,10 +11003,10 @@
     </row>
     <row r="572" spans="3:7">
       <c r="C572" s="6">
-        <v>18220</v>
+        <v>18620</v>
       </c>
       <c r="D572" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E572" s="5">
         <v>1</v>
@@ -11032,10 +11020,10 @@
     </row>
     <row r="573" spans="3:7">
       <c r="C573" s="6">
-        <v>18221</v>
+        <v>18621</v>
       </c>
       <c r="D573" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E573" s="3">
         <v>1</v>
@@ -11049,10 +11037,10 @@
     </row>
     <row r="574" spans="3:7">
       <c r="C574" s="6">
-        <v>18222</v>
+        <v>18622</v>
       </c>
       <c r="D574" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E574" s="5">
         <v>1</v>
@@ -11066,10 +11054,10 @@
     </row>
     <row r="575" spans="3:7">
       <c r="C575" s="6">
-        <v>18223</v>
+        <v>18623</v>
       </c>
       <c r="D575" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E575" s="5">
         <v>1</v>
@@ -11083,10 +11071,10 @@
     </row>
     <row r="576" spans="3:7">
       <c r="C576" s="6">
-        <v>18224</v>
+        <v>18624</v>
       </c>
       <c r="D576" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E576" s="5">
         <v>1</v>
@@ -11100,10 +11088,10 @@
     </row>
     <row r="577" spans="1:8">
       <c r="C577" s="6">
-        <v>18225</v>
+        <v>18625</v>
       </c>
       <c r="D577" s="3">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E577" s="3">
         <v>1</v>
@@ -11120,10 +11108,10 @@
         <v>64</v>
       </c>
       <c r="C579" s="6">
-        <v>18301</v>
+        <v>18701</v>
       </c>
       <c r="D579" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E579" s="5">
         <v>1</v>
@@ -11135,17 +11123,17 @@
         <v>15</v>
       </c>
       <c r="H579" s="3">
-        <v>20455</v>
+        <v>20635</v>
       </c>
     </row>
     <row r="580" spans="1:8">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="6">
-        <v>18302</v>
+        <v>18702</v>
       </c>
       <c r="D580" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E580" s="5">
         <v>1</v>
@@ -11157,15 +11145,15 @@
         <v>16</v>
       </c>
       <c r="H580" s="3">
-        <v>20456</v>
+        <v>20636</v>
       </c>
     </row>
     <row r="581" spans="1:8">
       <c r="C581" s="6">
-        <v>18303</v>
+        <v>18703</v>
       </c>
       <c r="D581" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E581" s="5">
         <v>1</v>
@@ -11177,15 +11165,15 @@
         <v>18</v>
       </c>
       <c r="H581" s="3">
-        <v>20457</v>
+        <v>20637</v>
       </c>
     </row>
     <row r="582" spans="1:8">
       <c r="C582" s="6">
-        <v>18304</v>
+        <v>18704</v>
       </c>
       <c r="D582" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E582" s="5">
         <v>1</v>
@@ -11197,15 +11185,15 @@
         <v>19</v>
       </c>
       <c r="H582" s="3">
-        <v>20458</v>
+        <v>20638</v>
       </c>
     </row>
     <row r="583" spans="1:8">
       <c r="C583" s="6">
-        <v>18305</v>
+        <v>18705</v>
       </c>
       <c r="D583" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E583" s="3">
         <v>1</v>
@@ -11219,10 +11207,10 @@
     </row>
     <row r="584" spans="1:8">
       <c r="C584" s="6">
-        <v>18306</v>
+        <v>18706</v>
       </c>
       <c r="D584" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E584" s="5">
         <v>1</v>
@@ -11236,10 +11224,10 @@
     </row>
     <row r="585" spans="1:8">
       <c r="C585" s="6">
-        <v>18307</v>
+        <v>18707</v>
       </c>
       <c r="D585" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E585" s="5">
         <v>1</v>
@@ -11253,10 +11241,10 @@
     </row>
     <row r="586" spans="1:8">
       <c r="C586" s="6">
-        <v>18308</v>
+        <v>18708</v>
       </c>
       <c r="D586" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E586" s="5">
         <v>1</v>
@@ -11270,10 +11258,10 @@
     </row>
     <row r="587" spans="1:8">
       <c r="C587" s="6">
-        <v>18309</v>
+        <v>18709</v>
       </c>
       <c r="D587" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E587" s="3">
         <v>1</v>
@@ -11287,10 +11275,10 @@
     </row>
     <row r="588" spans="1:8">
       <c r="C588" s="6">
-        <v>18310</v>
+        <v>18710</v>
       </c>
       <c r="D588" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E588" s="5">
         <v>1</v>
@@ -11304,10 +11292,10 @@
     </row>
     <row r="589" spans="1:8">
       <c r="C589" s="6">
-        <v>18311</v>
+        <v>18711</v>
       </c>
       <c r="D589" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E589" s="5">
         <v>1</v>
@@ -11321,10 +11309,10 @@
     </row>
     <row r="590" spans="1:8">
       <c r="C590" s="6">
-        <v>18312</v>
+        <v>18712</v>
       </c>
       <c r="D590" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E590" s="5">
         <v>1</v>
@@ -11338,10 +11326,10 @@
     </row>
     <row r="591" spans="1:8">
       <c r="C591" s="6">
-        <v>18313</v>
+        <v>18713</v>
       </c>
       <c r="D591" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E591" s="3">
         <v>1</v>
@@ -11355,10 +11343,10 @@
     </row>
     <row r="592" spans="1:8">
       <c r="C592" s="6">
-        <v>18314</v>
+        <v>18714</v>
       </c>
       <c r="D592" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E592" s="5">
         <v>1</v>
@@ -11372,10 +11360,10 @@
     </row>
     <row r="593" spans="1:8">
       <c r="C593" s="6">
-        <v>18315</v>
+        <v>18715</v>
       </c>
       <c r="D593" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E593" s="5">
         <v>1</v>
@@ -11389,10 +11377,10 @@
     </row>
     <row r="594" spans="1:8">
       <c r="C594" s="6">
-        <v>18316</v>
+        <v>18716</v>
       </c>
       <c r="D594" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E594" s="5">
         <v>1</v>
@@ -11406,10 +11394,10 @@
     </row>
     <row r="595" spans="1:8">
       <c r="C595" s="6">
-        <v>18317</v>
+        <v>18717</v>
       </c>
       <c r="D595" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E595" s="3">
         <v>1</v>
@@ -11423,10 +11411,10 @@
     </row>
     <row r="596" spans="1:8">
       <c r="C596" s="6">
-        <v>18318</v>
+        <v>18718</v>
       </c>
       <c r="D596" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E596" s="5">
         <v>1</v>
@@ -11440,10 +11428,10 @@
     </row>
     <row r="597" spans="1:8">
       <c r="C597" s="6">
-        <v>18319</v>
+        <v>18719</v>
       </c>
       <c r="D597" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E597" s="5">
         <v>1</v>
@@ -11457,10 +11445,10 @@
     </row>
     <row r="598" spans="1:8">
       <c r="C598" s="6">
-        <v>18320</v>
+        <v>18720</v>
       </c>
       <c r="D598" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E598" s="5">
         <v>1</v>
@@ -11474,10 +11462,10 @@
     </row>
     <row r="599" spans="1:8">
       <c r="C599" s="6">
-        <v>18321</v>
+        <v>18721</v>
       </c>
       <c r="D599" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E599" s="3">
         <v>1</v>
@@ -11491,10 +11479,10 @@
     </row>
     <row r="600" spans="1:8">
       <c r="C600" s="6">
-        <v>18322</v>
+        <v>18722</v>
       </c>
       <c r="D600" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E600" s="5">
         <v>1</v>
@@ -11508,10 +11496,10 @@
     </row>
     <row r="601" spans="1:8">
       <c r="C601" s="6">
-        <v>18323</v>
+        <v>18723</v>
       </c>
       <c r="D601" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E601" s="5">
         <v>1</v>
@@ -11525,10 +11513,10 @@
     </row>
     <row r="602" spans="1:8">
       <c r="C602" s="6">
-        <v>18324</v>
+        <v>18724</v>
       </c>
       <c r="D602" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E602" s="5">
         <v>1</v>
@@ -11542,10 +11530,10 @@
     </row>
     <row r="603" spans="1:8">
       <c r="C603" s="6">
-        <v>18325</v>
+        <v>18725</v>
       </c>
       <c r="D603" s="3">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E603" s="3">
         <v>1</v>
@@ -11562,10 +11550,10 @@
         <v>65</v>
       </c>
       <c r="C605" s="6">
-        <v>18401</v>
+        <v>18801</v>
       </c>
       <c r="D605" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E605" s="5">
         <v>1</v>
@@ -11577,17 +11565,17 @@
         <v>15</v>
       </c>
       <c r="H605" s="3">
-        <v>20515</v>
+        <v>20405</v>
       </c>
     </row>
     <row r="606" spans="1:8">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="6">
-        <v>18402</v>
+        <v>18802</v>
       </c>
       <c r="D606" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E606" s="5">
         <v>1</v>
@@ -11599,15 +11587,15 @@
         <v>16</v>
       </c>
       <c r="H606" s="3">
-        <v>20516</v>
+        <v>20406</v>
       </c>
     </row>
     <row r="607" spans="1:8">
       <c r="C607" s="6">
-        <v>18403</v>
+        <v>18803</v>
       </c>
       <c r="D607" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E607" s="5">
         <v>1</v>
@@ -11619,15 +11607,15 @@
         <v>18</v>
       </c>
       <c r="H607" s="3">
-        <v>20517</v>
+        <v>20407</v>
       </c>
     </row>
     <row r="608" spans="1:8">
       <c r="C608" s="6">
-        <v>18404</v>
+        <v>18804</v>
       </c>
       <c r="D608" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E608" s="5">
         <v>1</v>
@@ -11639,15 +11627,15 @@
         <v>19</v>
       </c>
       <c r="H608" s="3">
-        <v>20518</v>
+        <v>20408</v>
       </c>
     </row>
     <row r="609" spans="3:7">
       <c r="C609" s="6">
-        <v>18405</v>
+        <v>18805</v>
       </c>
       <c r="D609" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E609" s="3">
         <v>1</v>
@@ -11661,10 +11649,10 @@
     </row>
     <row r="610" spans="3:7">
       <c r="C610" s="6">
-        <v>18406</v>
+        <v>18806</v>
       </c>
       <c r="D610" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E610" s="5">
         <v>1</v>
@@ -11678,10 +11666,10 @@
     </row>
     <row r="611" spans="3:7">
       <c r="C611" s="6">
-        <v>18407</v>
+        <v>18807</v>
       </c>
       <c r="D611" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E611" s="5">
         <v>1</v>
@@ -11695,10 +11683,10 @@
     </row>
     <row r="612" spans="3:7">
       <c r="C612" s="6">
-        <v>18408</v>
+        <v>18808</v>
       </c>
       <c r="D612" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E612" s="5">
         <v>1</v>
@@ -11712,10 +11700,10 @@
     </row>
     <row r="613" spans="3:7">
       <c r="C613" s="6">
-        <v>18409</v>
+        <v>18809</v>
       </c>
       <c r="D613" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E613" s="3">
         <v>1</v>
@@ -11729,10 +11717,10 @@
     </row>
     <row r="614" spans="3:7">
       <c r="C614" s="6">
-        <v>18410</v>
+        <v>18810</v>
       </c>
       <c r="D614" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E614" s="5">
         <v>1</v>
@@ -11746,10 +11734,10 @@
     </row>
     <row r="615" spans="3:7">
       <c r="C615" s="6">
-        <v>18411</v>
+        <v>18811</v>
       </c>
       <c r="D615" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E615" s="5">
         <v>1</v>
@@ -11763,10 +11751,10 @@
     </row>
     <row r="616" spans="3:7">
       <c r="C616" s="6">
-        <v>18412</v>
+        <v>18812</v>
       </c>
       <c r="D616" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E616" s="5">
         <v>1</v>
@@ -11780,10 +11768,10 @@
     </row>
     <row r="617" spans="3:7">
       <c r="C617" s="6">
-        <v>18413</v>
+        <v>18813</v>
       </c>
       <c r="D617" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E617" s="3">
         <v>1</v>
@@ -11797,10 +11785,10 @@
     </row>
     <row r="618" spans="3:7">
       <c r="C618" s="6">
-        <v>18414</v>
+        <v>18814</v>
       </c>
       <c r="D618" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E618" s="5">
         <v>1</v>
@@ -11814,10 +11802,10 @@
     </row>
     <row r="619" spans="3:7">
       <c r="C619" s="6">
-        <v>18415</v>
+        <v>18815</v>
       </c>
       <c r="D619" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E619" s="5">
         <v>1</v>
@@ -11831,10 +11819,10 @@
     </row>
     <row r="620" spans="3:7">
       <c r="C620" s="6">
-        <v>18416</v>
+        <v>18816</v>
       </c>
       <c r="D620" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E620" s="5">
         <v>1</v>
@@ -11848,10 +11836,10 @@
     </row>
     <row r="621" spans="3:7">
       <c r="C621" s="6">
-        <v>18417</v>
+        <v>18817</v>
       </c>
       <c r="D621" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E621" s="3">
         <v>1</v>
@@ -11865,10 +11853,10 @@
     </row>
     <row r="622" spans="3:7">
       <c r="C622" s="6">
-        <v>18418</v>
+        <v>18818</v>
       </c>
       <c r="D622" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E622" s="5">
         <v>1</v>
@@ -11882,10 +11870,10 @@
     </row>
     <row r="623" spans="3:7">
       <c r="C623" s="6">
-        <v>18419</v>
+        <v>18819</v>
       </c>
       <c r="D623" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E623" s="5">
         <v>1</v>
@@ -11899,10 +11887,10 @@
     </row>
     <row r="624" spans="3:7">
       <c r="C624" s="6">
-        <v>18420</v>
+        <v>18820</v>
       </c>
       <c r="D624" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E624" s="5">
         <v>1</v>
@@ -11916,10 +11904,10 @@
     </row>
     <row r="625" spans="1:8">
       <c r="C625" s="6">
-        <v>18421</v>
+        <v>18821</v>
       </c>
       <c r="D625" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E625" s="3">
         <v>1</v>
@@ -11933,10 +11921,10 @@
     </row>
     <row r="626" spans="1:8">
       <c r="C626" s="6">
-        <v>18422</v>
+        <v>18822</v>
       </c>
       <c r="D626" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E626" s="5">
         <v>1</v>
@@ -11950,10 +11938,10 @@
     </row>
     <row r="627" spans="1:8">
       <c r="C627" s="6">
-        <v>18423</v>
+        <v>18823</v>
       </c>
       <c r="D627" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E627" s="5">
         <v>1</v>
@@ -11967,10 +11955,10 @@
     </row>
     <row r="628" spans="1:8">
       <c r="C628" s="6">
-        <v>18424</v>
+        <v>18824</v>
       </c>
       <c r="D628" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E628" s="5">
         <v>1</v>
@@ -11984,10 +11972,10 @@
     </row>
     <row r="629" spans="1:8">
       <c r="C629" s="6">
-        <v>18425</v>
+        <v>18825</v>
       </c>
       <c r="D629" s="3">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E629" s="3">
         <v>1</v>
@@ -12004,10 +11992,10 @@
         <v>66</v>
       </c>
       <c r="C631" s="6">
-        <v>18501</v>
+        <v>18901</v>
       </c>
       <c r="D631" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E631" s="5">
         <v>1</v>
@@ -12019,17 +12007,17 @@
         <v>15</v>
       </c>
       <c r="H631" s="3">
-        <v>20545</v>
+        <v>20445</v>
       </c>
     </row>
     <row r="632" spans="1:8">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="6">
-        <v>18502</v>
+        <v>18902</v>
       </c>
       <c r="D632" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E632" s="5">
         <v>1</v>
@@ -12041,15 +12029,15 @@
         <v>16</v>
       </c>
       <c r="H632" s="3">
-        <v>20546</v>
+        <v>20446</v>
       </c>
     </row>
     <row r="633" spans="1:8">
       <c r="C633" s="6">
-        <v>18503</v>
+        <v>18903</v>
       </c>
       <c r="D633" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E633" s="5">
         <v>1</v>
@@ -12061,15 +12049,15 @@
         <v>18</v>
       </c>
       <c r="H633" s="3">
-        <v>20547</v>
+        <v>20447</v>
       </c>
     </row>
     <row r="634" spans="1:8">
       <c r="C634" s="6">
-        <v>18504</v>
+        <v>18904</v>
       </c>
       <c r="D634" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E634" s="5">
         <v>1</v>
@@ -12081,15 +12069,15 @@
         <v>19</v>
       </c>
       <c r="H634" s="3">
-        <v>20548</v>
+        <v>20448</v>
       </c>
     </row>
     <row r="635" spans="1:8">
       <c r="C635" s="6">
-        <v>18505</v>
+        <v>18905</v>
       </c>
       <c r="D635" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E635" s="3">
         <v>1</v>
@@ -12103,10 +12091,10 @@
     </row>
     <row r="636" spans="1:8">
       <c r="C636" s="6">
-        <v>18506</v>
+        <v>18906</v>
       </c>
       <c r="D636" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E636" s="5">
         <v>1</v>
@@ -12120,10 +12108,10 @@
     </row>
     <row r="637" spans="1:8">
       <c r="C637" s="6">
-        <v>18507</v>
+        <v>18907</v>
       </c>
       <c r="D637" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E637" s="5">
         <v>1</v>
@@ -12137,10 +12125,10 @@
     </row>
     <row r="638" spans="1:8">
       <c r="C638" s="6">
-        <v>18508</v>
+        <v>18908</v>
       </c>
       <c r="D638" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E638" s="5">
         <v>1</v>
@@ -12154,10 +12142,10 @@
     </row>
     <row r="639" spans="1:8">
       <c r="C639" s="6">
-        <v>18509</v>
+        <v>18909</v>
       </c>
       <c r="D639" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E639" s="3">
         <v>1</v>
@@ -12171,10 +12159,10 @@
     </row>
     <row r="640" spans="1:8">
       <c r="C640" s="6">
-        <v>18510</v>
+        <v>18910</v>
       </c>
       <c r="D640" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E640" s="5">
         <v>1</v>
@@ -12188,10 +12176,10 @@
     </row>
     <row r="641" spans="3:7">
       <c r="C641" s="6">
-        <v>18511</v>
+        <v>18911</v>
       </c>
       <c r="D641" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E641" s="5">
         <v>1</v>
@@ -12205,10 +12193,10 @@
     </row>
     <row r="642" spans="3:7">
       <c r="C642" s="6">
-        <v>18512</v>
+        <v>18912</v>
       </c>
       <c r="D642" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E642" s="5">
         <v>1</v>
@@ -12222,10 +12210,10 @@
     </row>
     <row r="643" spans="3:7">
       <c r="C643" s="6">
-        <v>18513</v>
+        <v>18913</v>
       </c>
       <c r="D643" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E643" s="3">
         <v>1</v>
@@ -12239,10 +12227,10 @@
     </row>
     <row r="644" spans="3:7">
       <c r="C644" s="6">
-        <v>18514</v>
+        <v>18914</v>
       </c>
       <c r="D644" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E644" s="5">
         <v>1</v>
@@ -12256,10 +12244,10 @@
     </row>
     <row r="645" spans="3:7">
       <c r="C645" s="6">
-        <v>18515</v>
+        <v>18915</v>
       </c>
       <c r="D645" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E645" s="5">
         <v>1</v>
@@ -12273,10 +12261,10 @@
     </row>
     <row r="646" spans="3:7">
       <c r="C646" s="6">
-        <v>18516</v>
+        <v>18916</v>
       </c>
       <c r="D646" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E646" s="5">
         <v>1</v>
@@ -12290,10 +12278,10 @@
     </row>
     <row r="647" spans="3:7">
       <c r="C647" s="6">
-        <v>18517</v>
+        <v>18917</v>
       </c>
       <c r="D647" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E647" s="3">
         <v>1</v>
@@ -12307,10 +12295,10 @@
     </row>
     <row r="648" spans="3:7">
       <c r="C648" s="6">
-        <v>18518</v>
+        <v>18918</v>
       </c>
       <c r="D648" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E648" s="5">
         <v>1</v>
@@ -12324,10 +12312,10 @@
     </row>
     <row r="649" spans="3:7">
       <c r="C649" s="6">
-        <v>18519</v>
+        <v>18919</v>
       </c>
       <c r="D649" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E649" s="5">
         <v>1</v>
@@ -12341,10 +12329,10 @@
     </row>
     <row r="650" spans="3:7">
       <c r="C650" s="6">
-        <v>18520</v>
+        <v>18920</v>
       </c>
       <c r="D650" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E650" s="5">
         <v>1</v>
@@ -12358,10 +12346,10 @@
     </row>
     <row r="651" spans="3:7">
       <c r="C651" s="6">
-        <v>18521</v>
+        <v>18921</v>
       </c>
       <c r="D651" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E651" s="3">
         <v>1</v>
@@ -12375,10 +12363,10 @@
     </row>
     <row r="652" spans="3:7">
       <c r="C652" s="6">
-        <v>18522</v>
+        <v>18922</v>
       </c>
       <c r="D652" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E652" s="5">
         <v>1</v>
@@ -12392,10 +12380,10 @@
     </row>
     <row r="653" spans="3:7">
       <c r="C653" s="6">
-        <v>18523</v>
+        <v>18923</v>
       </c>
       <c r="D653" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E653" s="5">
         <v>1</v>
@@ -12409,10 +12397,10 @@
     </row>
     <row r="654" spans="3:7">
       <c r="C654" s="6">
-        <v>18524</v>
+        <v>18924</v>
       </c>
       <c r="D654" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E654" s="5">
         <v>1</v>
@@ -12426,10 +12414,10 @@
     </row>
     <row r="655" spans="3:7">
       <c r="C655" s="6">
-        <v>18525</v>
+        <v>18925</v>
       </c>
       <c r="D655" s="3">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E655" s="3">
         <v>1</v>
@@ -12446,10 +12434,10 @@
         <v>67</v>
       </c>
       <c r="C657" s="6">
-        <v>18601</v>
+        <v>19001</v>
       </c>
       <c r="D657" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E657" s="5">
         <v>1</v>
@@ -12461,17 +12449,17 @@
         <v>15</v>
       </c>
       <c r="H657" s="3">
-        <v>20615</v>
+        <v>20555</v>
       </c>
     </row>
     <row r="658" spans="1:8">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="6">
-        <v>18602</v>
+        <v>19002</v>
       </c>
       <c r="D658" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E658" s="5">
         <v>1</v>
@@ -12483,15 +12471,15 @@
         <v>16</v>
       </c>
       <c r="H658" s="3">
-        <v>20616</v>
+        <v>20556</v>
       </c>
     </row>
     <row r="659" spans="1:8">
       <c r="C659" s="6">
-        <v>18603</v>
+        <v>19003</v>
       </c>
       <c r="D659" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E659" s="5">
         <v>1</v>
@@ -12503,15 +12491,15 @@
         <v>18</v>
       </c>
       <c r="H659" s="3">
-        <v>20617</v>
+        <v>20557</v>
       </c>
     </row>
     <row r="660" spans="1:8">
       <c r="C660" s="6">
-        <v>18604</v>
+        <v>19004</v>
       </c>
       <c r="D660" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E660" s="5">
         <v>1</v>
@@ -12523,15 +12511,15 @@
         <v>19</v>
       </c>
       <c r="H660" s="3">
-        <v>20618</v>
+        <v>20558</v>
       </c>
     </row>
     <row r="661" spans="1:8">
       <c r="C661" s="6">
-        <v>18605</v>
+        <v>19005</v>
       </c>
       <c r="D661" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E661" s="3">
         <v>1</v>
@@ -12545,10 +12533,10 @@
     </row>
     <row r="662" spans="1:8">
       <c r="C662" s="6">
-        <v>18606</v>
+        <v>19006</v>
       </c>
       <c r="D662" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E662" s="5">
         <v>1</v>
@@ -12562,10 +12550,10 @@
     </row>
     <row r="663" spans="1:8">
       <c r="C663" s="6">
-        <v>18607</v>
+        <v>19007</v>
       </c>
       <c r="D663" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E663" s="5">
         <v>1</v>
@@ -12579,10 +12567,10 @@
     </row>
     <row r="664" spans="1:8">
       <c r="C664" s="6">
-        <v>18608</v>
+        <v>19008</v>
       </c>
       <c r="D664" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E664" s="5">
         <v>1</v>
@@ -12596,10 +12584,10 @@
     </row>
     <row r="665" spans="1:8">
       <c r="C665" s="6">
-        <v>18609</v>
+        <v>19009</v>
       </c>
       <c r="D665" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E665" s="3">
         <v>1</v>
@@ -12613,10 +12601,10 @@
     </row>
     <row r="666" spans="1:8">
       <c r="C666" s="6">
-        <v>18610</v>
+        <v>19010</v>
       </c>
       <c r="D666" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E666" s="5">
         <v>1</v>
@@ -12630,10 +12618,10 @@
     </row>
     <row r="667" spans="1:8">
       <c r="C667" s="6">
-        <v>18611</v>
+        <v>19011</v>
       </c>
       <c r="D667" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E667" s="5">
         <v>1</v>
@@ -12647,10 +12635,10 @@
     </row>
     <row r="668" spans="1:8">
       <c r="C668" s="6">
-        <v>18612</v>
+        <v>19012</v>
       </c>
       <c r="D668" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E668" s="5">
         <v>1</v>
@@ -12664,10 +12652,10 @@
     </row>
     <row r="669" spans="1:8">
       <c r="C669" s="6">
-        <v>18613</v>
+        <v>19013</v>
       </c>
       <c r="D669" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E669" s="3">
         <v>1</v>
@@ -12681,10 +12669,10 @@
     </row>
     <row r="670" spans="1:8">
       <c r="C670" s="6">
-        <v>18614</v>
+        <v>19014</v>
       </c>
       <c r="D670" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E670" s="5">
         <v>1</v>
@@ -12698,10 +12686,10 @@
     </row>
     <row r="671" spans="1:8">
       <c r="C671" s="6">
-        <v>18615</v>
+        <v>19015</v>
       </c>
       <c r="D671" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E671" s="5">
         <v>1</v>
@@ -12715,10 +12703,10 @@
     </row>
     <row r="672" spans="1:8">
       <c r="C672" s="6">
-        <v>18616</v>
+        <v>19016</v>
       </c>
       <c r="D672" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E672" s="5">
         <v>1</v>
@@ -12732,10 +12720,10 @@
     </row>
     <row r="673" spans="1:8">
       <c r="C673" s="6">
-        <v>18617</v>
+        <v>19017</v>
       </c>
       <c r="D673" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E673" s="3">
         <v>1</v>
@@ -12749,10 +12737,10 @@
     </row>
     <row r="674" spans="1:8">
       <c r="C674" s="6">
-        <v>18618</v>
+        <v>19018</v>
       </c>
       <c r="D674" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E674" s="5">
         <v>1</v>
@@ -12766,10 +12754,10 @@
     </row>
     <row r="675" spans="1:8">
       <c r="C675" s="6">
-        <v>18619</v>
+        <v>19019</v>
       </c>
       <c r="D675" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E675" s="5">
         <v>1</v>
@@ -12783,10 +12771,10 @@
     </row>
     <row r="676" spans="1:8">
       <c r="C676" s="6">
-        <v>18620</v>
+        <v>19020</v>
       </c>
       <c r="D676" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E676" s="5">
         <v>1</v>
@@ -12800,10 +12788,10 @@
     </row>
     <row r="677" spans="1:8">
       <c r="C677" s="6">
-        <v>18621</v>
+        <v>19021</v>
       </c>
       <c r="D677" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E677" s="3">
         <v>1</v>
@@ -12817,10 +12805,10 @@
     </row>
     <row r="678" spans="1:8">
       <c r="C678" s="6">
-        <v>18622</v>
+        <v>19022</v>
       </c>
       <c r="D678" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E678" s="5">
         <v>1</v>
@@ -12834,10 +12822,10 @@
     </row>
     <row r="679" spans="1:8">
       <c r="C679" s="6">
-        <v>18623</v>
+        <v>19023</v>
       </c>
       <c r="D679" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E679" s="5">
         <v>1</v>
@@ -12851,10 +12839,10 @@
     </row>
     <row r="680" spans="1:8">
       <c r="C680" s="6">
-        <v>18624</v>
+        <v>19024</v>
       </c>
       <c r="D680" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E680" s="5">
         <v>1</v>
@@ -12868,10 +12856,10 @@
     </row>
     <row r="681" spans="1:8">
       <c r="C681" s="6">
-        <v>18625</v>
+        <v>19025</v>
       </c>
       <c r="D681" s="3">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E681" s="3">
         <v>1</v>
@@ -12888,10 +12876,10 @@
         <v>68</v>
       </c>
       <c r="C683" s="6">
-        <v>18701</v>
+        <v>19101</v>
       </c>
       <c r="D683" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E683" s="5">
         <v>1</v>
@@ -12903,17 +12891,17 @@
         <v>15</v>
       </c>
       <c r="H683" s="3">
-        <v>20635</v>
+        <v>20595</v>
       </c>
     </row>
     <row r="684" spans="1:8">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="6">
-        <v>18702</v>
+        <v>19102</v>
       </c>
       <c r="D684" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E684" s="5">
         <v>1</v>
@@ -12925,15 +12913,15 @@
         <v>16</v>
       </c>
       <c r="H684" s="3">
-        <v>20636</v>
+        <v>20596</v>
       </c>
     </row>
     <row r="685" spans="1:8">
       <c r="C685" s="6">
-        <v>18703</v>
+        <v>19103</v>
       </c>
       <c r="D685" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E685" s="5">
         <v>1</v>
@@ -12945,15 +12933,15 @@
         <v>18</v>
       </c>
       <c r="H685" s="3">
-        <v>20637</v>
+        <v>20597</v>
       </c>
     </row>
     <row r="686" spans="1:8">
       <c r="C686" s="6">
-        <v>18704</v>
+        <v>19104</v>
       </c>
       <c r="D686" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E686" s="5">
         <v>1</v>
@@ -12965,15 +12953,15 @@
         <v>19</v>
       </c>
       <c r="H686" s="3">
-        <v>20638</v>
+        <v>20598</v>
       </c>
     </row>
     <row r="687" spans="1:8">
       <c r="C687" s="6">
-        <v>18705</v>
+        <v>19105</v>
       </c>
       <c r="D687" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E687" s="3">
         <v>1</v>
@@ -12987,10 +12975,10 @@
     </row>
     <row r="688" spans="1:8">
       <c r="C688" s="6">
-        <v>18706</v>
+        <v>19106</v>
       </c>
       <c r="D688" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E688" s="5">
         <v>1</v>
@@ -13004,10 +12992,10 @@
     </row>
     <row r="689" spans="3:7">
       <c r="C689" s="6">
-        <v>18707</v>
+        <v>19107</v>
       </c>
       <c r="D689" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E689" s="5">
         <v>1</v>
@@ -13021,10 +13009,10 @@
     </row>
     <row r="690" spans="3:7">
       <c r="C690" s="6">
-        <v>18708</v>
+        <v>19108</v>
       </c>
       <c r="D690" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E690" s="5">
         <v>1</v>
@@ -13038,10 +13026,10 @@
     </row>
     <row r="691" spans="3:7">
       <c r="C691" s="6">
-        <v>18709</v>
+        <v>19109</v>
       </c>
       <c r="D691" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E691" s="3">
         <v>1</v>
@@ -13055,10 +13043,10 @@
     </row>
     <row r="692" spans="3:7">
       <c r="C692" s="6">
-        <v>18710</v>
+        <v>19110</v>
       </c>
       <c r="D692" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E692" s="5">
         <v>1</v>
@@ -13072,10 +13060,10 @@
     </row>
     <row r="693" spans="3:7">
       <c r="C693" s="6">
-        <v>18711</v>
+        <v>19111</v>
       </c>
       <c r="D693" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E693" s="5">
         <v>1</v>
@@ -13089,10 +13077,10 @@
     </row>
     <row r="694" spans="3:7">
       <c r="C694" s="6">
-        <v>18712</v>
+        <v>19112</v>
       </c>
       <c r="D694" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E694" s="5">
         <v>1</v>
@@ -13106,10 +13094,10 @@
     </row>
     <row r="695" spans="3:7">
       <c r="C695" s="6">
-        <v>18713</v>
+        <v>19113</v>
       </c>
       <c r="D695" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E695" s="3">
         <v>1</v>
@@ -13123,10 +13111,10 @@
     </row>
     <row r="696" spans="3:7">
       <c r="C696" s="6">
-        <v>18714</v>
+        <v>19114</v>
       </c>
       <c r="D696" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E696" s="5">
         <v>1</v>
@@ -13140,10 +13128,10 @@
     </row>
     <row r="697" spans="3:7">
       <c r="C697" s="6">
-        <v>18715</v>
+        <v>19115</v>
       </c>
       <c r="D697" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E697" s="5">
         <v>1</v>
@@ -13157,10 +13145,10 @@
     </row>
     <row r="698" spans="3:7">
       <c r="C698" s="6">
-        <v>18716</v>
+        <v>19116</v>
       </c>
       <c r="D698" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E698" s="5">
         <v>1</v>
@@ -13174,10 +13162,10 @@
     </row>
     <row r="699" spans="3:7">
       <c r="C699" s="6">
-        <v>18717</v>
+        <v>19117</v>
       </c>
       <c r="D699" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E699" s="3">
         <v>1</v>
@@ -13191,10 +13179,10 @@
     </row>
     <row r="700" spans="3:7">
       <c r="C700" s="6">
-        <v>18718</v>
+        <v>19118</v>
       </c>
       <c r="D700" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E700" s="5">
         <v>1</v>
@@ -13208,10 +13196,10 @@
     </row>
     <row r="701" spans="3:7">
       <c r="C701" s="6">
-        <v>18719</v>
+        <v>19119</v>
       </c>
       <c r="D701" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E701" s="5">
         <v>1</v>
@@ -13225,10 +13213,10 @@
     </row>
     <row r="702" spans="3:7">
       <c r="C702" s="6">
-        <v>18720</v>
+        <v>19120</v>
       </c>
       <c r="D702" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E702" s="5">
         <v>1</v>
@@ -13242,10 +13230,10 @@
     </row>
     <row r="703" spans="3:7">
       <c r="C703" s="6">
-        <v>18721</v>
+        <v>19121</v>
       </c>
       <c r="D703" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E703" s="3">
         <v>1</v>
@@ -13259,10 +13247,10 @@
     </row>
     <row r="704" spans="3:7">
       <c r="C704" s="6">
-        <v>18722</v>
+        <v>19122</v>
       </c>
       <c r="D704" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E704" s="5">
         <v>1</v>
@@ -13274,12 +13262,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="1:8">
+    <row r="705" spans="3:7">
       <c r="C705" s="6">
-        <v>18723</v>
+        <v>19123</v>
       </c>
       <c r="D705" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E705" s="5">
         <v>1</v>
@@ -13291,12 +13279,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="1:8">
+    <row r="706" spans="3:7">
       <c r="C706" s="6">
-        <v>18724</v>
+        <v>19124</v>
       </c>
       <c r="D706" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E706" s="5">
         <v>1</v>
@@ -13308,12 +13296,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="1:8">
+    <row r="707" spans="3:7">
       <c r="C707" s="6">
-        <v>18725</v>
+        <v>19125</v>
       </c>
       <c r="D707" s="3">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E707" s="3">
         <v>1</v>
@@ -13322,1774 +13310,6 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="709" spans="1:8">
-      <c r="A709" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C709" s="6">
-        <v>18801</v>
-      </c>
-      <c r="D709" s="3">
-        <v>188</v>
-      </c>
-      <c r="E709" s="5">
-        <v>1</v>
-      </c>
-      <c r="F709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G709" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H709" s="3">
-        <v>20405</v>
-      </c>
-    </row>
-    <row r="710" spans="1:8">
-      <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
-      <c r="C710" s="6">
-        <v>18802</v>
-      </c>
-      <c r="D710" s="3">
-        <v>188</v>
-      </c>
-      <c r="E710" s="5">
-        <v>1</v>
-      </c>
-      <c r="F710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G710" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H710" s="3">
-        <v>20406</v>
-      </c>
-    </row>
-    <row r="711" spans="1:8">
-      <c r="C711" s="6">
-        <v>18803</v>
-      </c>
-      <c r="D711" s="3">
-        <v>188</v>
-      </c>
-      <c r="E711" s="5">
-        <v>1</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G711" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H711" s="3">
-        <v>20407</v>
-      </c>
-    </row>
-    <row r="712" spans="1:8">
-      <c r="C712" s="6">
-        <v>18804</v>
-      </c>
-      <c r="D712" s="3">
-        <v>188</v>
-      </c>
-      <c r="E712" s="5">
-        <v>1</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G712" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H712" s="3">
-        <v>20408</v>
-      </c>
-    </row>
-    <row r="713" spans="1:8">
-      <c r="C713" s="6">
-        <v>18805</v>
-      </c>
-      <c r="D713" s="3">
-        <v>188</v>
-      </c>
-      <c r="E713" s="3">
-        <v>1</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G713" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="714" spans="1:8">
-      <c r="C714" s="6">
-        <v>18806</v>
-      </c>
-      <c r="D714" s="3">
-        <v>188</v>
-      </c>
-      <c r="E714" s="5">
-        <v>1</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G714" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="715" spans="1:8">
-      <c r="C715" s="6">
-        <v>18807</v>
-      </c>
-      <c r="D715" s="3">
-        <v>188</v>
-      </c>
-      <c r="E715" s="5">
-        <v>1</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G715" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="716" spans="1:8">
-      <c r="C716" s="6">
-        <v>18808</v>
-      </c>
-      <c r="D716" s="3">
-        <v>188</v>
-      </c>
-      <c r="E716" s="5">
-        <v>1</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G716" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="717" spans="1:8">
-      <c r="C717" s="6">
-        <v>18809</v>
-      </c>
-      <c r="D717" s="3">
-        <v>188</v>
-      </c>
-      <c r="E717" s="3">
-        <v>1</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G717" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="718" spans="1:8">
-      <c r="C718" s="6">
-        <v>18810</v>
-      </c>
-      <c r="D718" s="3">
-        <v>188</v>
-      </c>
-      <c r="E718" s="5">
-        <v>1</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G718" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="719" spans="1:8">
-      <c r="C719" s="6">
-        <v>18811</v>
-      </c>
-      <c r="D719" s="3">
-        <v>188</v>
-      </c>
-      <c r="E719" s="5">
-        <v>1</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G719" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="720" spans="1:8">
-      <c r="C720" s="6">
-        <v>18812</v>
-      </c>
-      <c r="D720" s="3">
-        <v>188</v>
-      </c>
-      <c r="E720" s="5">
-        <v>1</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G720" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="721" spans="1:8">
-      <c r="C721" s="6">
-        <v>18813</v>
-      </c>
-      <c r="D721" s="3">
-        <v>188</v>
-      </c>
-      <c r="E721" s="3">
-        <v>1</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G721" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="722" spans="1:8">
-      <c r="C722" s="6">
-        <v>18814</v>
-      </c>
-      <c r="D722" s="3">
-        <v>188</v>
-      </c>
-      <c r="E722" s="5">
-        <v>1</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G722" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="723" spans="1:8">
-      <c r="C723" s="6">
-        <v>18815</v>
-      </c>
-      <c r="D723" s="3">
-        <v>188</v>
-      </c>
-      <c r="E723" s="5">
-        <v>1</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G723" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="724" spans="1:8">
-      <c r="C724" s="6">
-        <v>18816</v>
-      </c>
-      <c r="D724" s="3">
-        <v>188</v>
-      </c>
-      <c r="E724" s="5">
-        <v>1</v>
-      </c>
-      <c r="F724" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G724" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="725" spans="1:8">
-      <c r="C725" s="6">
-        <v>18817</v>
-      </c>
-      <c r="D725" s="3">
-        <v>188</v>
-      </c>
-      <c r="E725" s="3">
-        <v>1</v>
-      </c>
-      <c r="F725" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G725" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="726" spans="1:8">
-      <c r="C726" s="6">
-        <v>18818</v>
-      </c>
-      <c r="D726" s="3">
-        <v>188</v>
-      </c>
-      <c r="E726" s="5">
-        <v>1</v>
-      </c>
-      <c r="F726" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G726" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="727" spans="1:8">
-      <c r="C727" s="6">
-        <v>18819</v>
-      </c>
-      <c r="D727" s="3">
-        <v>188</v>
-      </c>
-      <c r="E727" s="5">
-        <v>1</v>
-      </c>
-      <c r="F727" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G727" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="728" spans="1:8">
-      <c r="C728" s="6">
-        <v>18820</v>
-      </c>
-      <c r="D728" s="3">
-        <v>188</v>
-      </c>
-      <c r="E728" s="5">
-        <v>1</v>
-      </c>
-      <c r="F728" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G728" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="729" spans="1:8">
-      <c r="C729" s="6">
-        <v>18821</v>
-      </c>
-      <c r="D729" s="3">
-        <v>188</v>
-      </c>
-      <c r="E729" s="3">
-        <v>1</v>
-      </c>
-      <c r="F729" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G729" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="730" spans="1:8">
-      <c r="C730" s="6">
-        <v>18822</v>
-      </c>
-      <c r="D730" s="3">
-        <v>188</v>
-      </c>
-      <c r="E730" s="5">
-        <v>1</v>
-      </c>
-      <c r="F730" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G730" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="731" spans="1:8">
-      <c r="C731" s="6">
-        <v>18823</v>
-      </c>
-      <c r="D731" s="3">
-        <v>188</v>
-      </c>
-      <c r="E731" s="5">
-        <v>1</v>
-      </c>
-      <c r="F731" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G731" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="732" spans="1:8">
-      <c r="C732" s="6">
-        <v>18824</v>
-      </c>
-      <c r="D732" s="3">
-        <v>188</v>
-      </c>
-      <c r="E732" s="5">
-        <v>1</v>
-      </c>
-      <c r="F732" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G732" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="733" spans="1:8">
-      <c r="C733" s="6">
-        <v>18825</v>
-      </c>
-      <c r="D733" s="3">
-        <v>188</v>
-      </c>
-      <c r="E733" s="3">
-        <v>1</v>
-      </c>
-      <c r="F733" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G733" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="735" spans="1:8">
-      <c r="A735" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C735" s="6">
-        <v>18901</v>
-      </c>
-      <c r="D735" s="3">
-        <v>189</v>
-      </c>
-      <c r="E735" s="5">
-        <v>1</v>
-      </c>
-      <c r="F735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G735" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H735" s="3">
-        <v>20445</v>
-      </c>
-    </row>
-    <row r="736" spans="1:8">
-      <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
-      <c r="C736" s="6">
-        <v>18902</v>
-      </c>
-      <c r="D736" s="3">
-        <v>189</v>
-      </c>
-      <c r="E736" s="5">
-        <v>1</v>
-      </c>
-      <c r="F736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G736" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H736" s="3">
-        <v>20446</v>
-      </c>
-    </row>
-    <row r="737" spans="3:8">
-      <c r="C737" s="6">
-        <v>18903</v>
-      </c>
-      <c r="D737" s="3">
-        <v>189</v>
-      </c>
-      <c r="E737" s="5">
-        <v>1</v>
-      </c>
-      <c r="F737" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G737" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H737" s="3">
-        <v>20447</v>
-      </c>
-    </row>
-    <row r="738" spans="3:8">
-      <c r="C738" s="6">
-        <v>18904</v>
-      </c>
-      <c r="D738" s="3">
-        <v>189</v>
-      </c>
-      <c r="E738" s="5">
-        <v>1</v>
-      </c>
-      <c r="F738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G738" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H738" s="3">
-        <v>20448</v>
-      </c>
-    </row>
-    <row r="739" spans="3:8">
-      <c r="C739" s="6">
-        <v>18905</v>
-      </c>
-      <c r="D739" s="3">
-        <v>189</v>
-      </c>
-      <c r="E739" s="3">
-        <v>1</v>
-      </c>
-      <c r="F739" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G739" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="740" spans="3:8">
-      <c r="C740" s="6">
-        <v>18906</v>
-      </c>
-      <c r="D740" s="3">
-        <v>189</v>
-      </c>
-      <c r="E740" s="5">
-        <v>1</v>
-      </c>
-      <c r="F740" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G740" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="741" spans="3:8">
-      <c r="C741" s="6">
-        <v>18907</v>
-      </c>
-      <c r="D741" s="3">
-        <v>189</v>
-      </c>
-      <c r="E741" s="5">
-        <v>1</v>
-      </c>
-      <c r="F741" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G741" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="742" spans="3:8">
-      <c r="C742" s="6">
-        <v>18908</v>
-      </c>
-      <c r="D742" s="3">
-        <v>189</v>
-      </c>
-      <c r="E742" s="5">
-        <v>1</v>
-      </c>
-      <c r="F742" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G742" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="743" spans="3:8">
-      <c r="C743" s="6">
-        <v>18909</v>
-      </c>
-      <c r="D743" s="3">
-        <v>189</v>
-      </c>
-      <c r="E743" s="3">
-        <v>1</v>
-      </c>
-      <c r="F743" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G743" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="744" spans="3:8">
-      <c r="C744" s="6">
-        <v>18910</v>
-      </c>
-      <c r="D744" s="3">
-        <v>189</v>
-      </c>
-      <c r="E744" s="5">
-        <v>1</v>
-      </c>
-      <c r="F744" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G744" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="745" spans="3:8">
-      <c r="C745" s="6">
-        <v>18911</v>
-      </c>
-      <c r="D745" s="3">
-        <v>189</v>
-      </c>
-      <c r="E745" s="5">
-        <v>1</v>
-      </c>
-      <c r="F745" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G745" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="746" spans="3:8">
-      <c r="C746" s="6">
-        <v>18912</v>
-      </c>
-      <c r="D746" s="3">
-        <v>189</v>
-      </c>
-      <c r="E746" s="5">
-        <v>1</v>
-      </c>
-      <c r="F746" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G746" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="747" spans="3:8">
-      <c r="C747" s="6">
-        <v>18913</v>
-      </c>
-      <c r="D747" s="3">
-        <v>189</v>
-      </c>
-      <c r="E747" s="3">
-        <v>1</v>
-      </c>
-      <c r="F747" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G747" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="748" spans="3:8">
-      <c r="C748" s="6">
-        <v>18914</v>
-      </c>
-      <c r="D748" s="3">
-        <v>189</v>
-      </c>
-      <c r="E748" s="5">
-        <v>1</v>
-      </c>
-      <c r="F748" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G748" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="749" spans="3:8">
-      <c r="C749" s="6">
-        <v>18915</v>
-      </c>
-      <c r="D749" s="3">
-        <v>189</v>
-      </c>
-      <c r="E749" s="5">
-        <v>1</v>
-      </c>
-      <c r="F749" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G749" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="750" spans="3:8">
-      <c r="C750" s="6">
-        <v>18916</v>
-      </c>
-      <c r="D750" s="3">
-        <v>189</v>
-      </c>
-      <c r="E750" s="5">
-        <v>1</v>
-      </c>
-      <c r="F750" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G750" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="751" spans="3:8">
-      <c r="C751" s="6">
-        <v>18917</v>
-      </c>
-      <c r="D751" s="3">
-        <v>189</v>
-      </c>
-      <c r="E751" s="3">
-        <v>1</v>
-      </c>
-      <c r="F751" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G751" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="752" spans="3:8">
-      <c r="C752" s="6">
-        <v>18918</v>
-      </c>
-      <c r="D752" s="3">
-        <v>189</v>
-      </c>
-      <c r="E752" s="5">
-        <v>1</v>
-      </c>
-      <c r="F752" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G752" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="753" spans="1:8">
-      <c r="C753" s="6">
-        <v>18919</v>
-      </c>
-      <c r="D753" s="3">
-        <v>189</v>
-      </c>
-      <c r="E753" s="5">
-        <v>1</v>
-      </c>
-      <c r="F753" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G753" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="754" spans="1:8">
-      <c r="C754" s="6">
-        <v>18920</v>
-      </c>
-      <c r="D754" s="3">
-        <v>189</v>
-      </c>
-      <c r="E754" s="5">
-        <v>1</v>
-      </c>
-      <c r="F754" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G754" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="755" spans="1:8">
-      <c r="C755" s="6">
-        <v>18921</v>
-      </c>
-      <c r="D755" s="3">
-        <v>189</v>
-      </c>
-      <c r="E755" s="3">
-        <v>1</v>
-      </c>
-      <c r="F755" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G755" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="756" spans="1:8">
-      <c r="C756" s="6">
-        <v>18922</v>
-      </c>
-      <c r="D756" s="3">
-        <v>189</v>
-      </c>
-      <c r="E756" s="5">
-        <v>1</v>
-      </c>
-      <c r="F756" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G756" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="757" spans="1:8">
-      <c r="C757" s="6">
-        <v>18923</v>
-      </c>
-      <c r="D757" s="3">
-        <v>189</v>
-      </c>
-      <c r="E757" s="5">
-        <v>1</v>
-      </c>
-      <c r="F757" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G757" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="758" spans="1:8">
-      <c r="C758" s="6">
-        <v>18924</v>
-      </c>
-      <c r="D758" s="3">
-        <v>189</v>
-      </c>
-      <c r="E758" s="5">
-        <v>1</v>
-      </c>
-      <c r="F758" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G758" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="759" spans="1:8">
-      <c r="C759" s="6">
-        <v>18925</v>
-      </c>
-      <c r="D759" s="3">
-        <v>189</v>
-      </c>
-      <c r="E759" s="3">
-        <v>1</v>
-      </c>
-      <c r="F759" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G759" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="761" spans="1:8">
-      <c r="A761" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C761" s="6">
-        <v>19001</v>
-      </c>
-      <c r="D761" s="3">
-        <v>190</v>
-      </c>
-      <c r="E761" s="5">
-        <v>1</v>
-      </c>
-      <c r="F761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G761" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H761" s="3">
-        <v>20555</v>
-      </c>
-    </row>
-    <row r="762" spans="1:8">
-      <c r="A762" s="1"/>
-      <c r="B762" s="1"/>
-      <c r="C762" s="6">
-        <v>19002</v>
-      </c>
-      <c r="D762" s="3">
-        <v>190</v>
-      </c>
-      <c r="E762" s="5">
-        <v>1</v>
-      </c>
-      <c r="F762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G762" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H762" s="3">
-        <v>20556</v>
-      </c>
-    </row>
-    <row r="763" spans="1:8">
-      <c r="C763" s="6">
-        <v>19003</v>
-      </c>
-      <c r="D763" s="3">
-        <v>190</v>
-      </c>
-      <c r="E763" s="5">
-        <v>1</v>
-      </c>
-      <c r="F763" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G763" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H763" s="3">
-        <v>20557</v>
-      </c>
-    </row>
-    <row r="764" spans="1:8">
-      <c r="C764" s="6">
-        <v>19004</v>
-      </c>
-      <c r="D764" s="3">
-        <v>190</v>
-      </c>
-      <c r="E764" s="5">
-        <v>1</v>
-      </c>
-      <c r="F764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G764" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H764" s="3">
-        <v>20558</v>
-      </c>
-    </row>
-    <row r="765" spans="1:8">
-      <c r="C765" s="6">
-        <v>19005</v>
-      </c>
-      <c r="D765" s="3">
-        <v>190</v>
-      </c>
-      <c r="E765" s="3">
-        <v>1</v>
-      </c>
-      <c r="F765" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G765" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="766" spans="1:8">
-      <c r="C766" s="6">
-        <v>19006</v>
-      </c>
-      <c r="D766" s="3">
-        <v>190</v>
-      </c>
-      <c r="E766" s="5">
-        <v>1</v>
-      </c>
-      <c r="F766" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G766" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="767" spans="1:8">
-      <c r="C767" s="6">
-        <v>19007</v>
-      </c>
-      <c r="D767" s="3">
-        <v>190</v>
-      </c>
-      <c r="E767" s="5">
-        <v>1</v>
-      </c>
-      <c r="F767" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G767" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="768" spans="1:8">
-      <c r="C768" s="6">
-        <v>19008</v>
-      </c>
-      <c r="D768" s="3">
-        <v>190</v>
-      </c>
-      <c r="E768" s="5">
-        <v>1</v>
-      </c>
-      <c r="F768" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G768" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="769" spans="3:7">
-      <c r="C769" s="6">
-        <v>19009</v>
-      </c>
-      <c r="D769" s="3">
-        <v>190</v>
-      </c>
-      <c r="E769" s="3">
-        <v>1</v>
-      </c>
-      <c r="F769" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G769" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="770" spans="3:7">
-      <c r="C770" s="6">
-        <v>19010</v>
-      </c>
-      <c r="D770" s="3">
-        <v>190</v>
-      </c>
-      <c r="E770" s="5">
-        <v>1</v>
-      </c>
-      <c r="F770" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G770" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="771" spans="3:7">
-      <c r="C771" s="6">
-        <v>19011</v>
-      </c>
-      <c r="D771" s="3">
-        <v>190</v>
-      </c>
-      <c r="E771" s="5">
-        <v>1</v>
-      </c>
-      <c r="F771" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G771" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="772" spans="3:7">
-      <c r="C772" s="6">
-        <v>19012</v>
-      </c>
-      <c r="D772" s="3">
-        <v>190</v>
-      </c>
-      <c r="E772" s="5">
-        <v>1</v>
-      </c>
-      <c r="F772" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G772" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="773" spans="3:7">
-      <c r="C773" s="6">
-        <v>19013</v>
-      </c>
-      <c r="D773" s="3">
-        <v>190</v>
-      </c>
-      <c r="E773" s="3">
-        <v>1</v>
-      </c>
-      <c r="F773" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G773" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="774" spans="3:7">
-      <c r="C774" s="6">
-        <v>19014</v>
-      </c>
-      <c r="D774" s="3">
-        <v>190</v>
-      </c>
-      <c r="E774" s="5">
-        <v>1</v>
-      </c>
-      <c r="F774" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G774" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="775" spans="3:7">
-      <c r="C775" s="6">
-        <v>19015</v>
-      </c>
-      <c r="D775" s="3">
-        <v>190</v>
-      </c>
-      <c r="E775" s="5">
-        <v>1</v>
-      </c>
-      <c r="F775" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G775" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="776" spans="3:7">
-      <c r="C776" s="6">
-        <v>19016</v>
-      </c>
-      <c r="D776" s="3">
-        <v>190</v>
-      </c>
-      <c r="E776" s="5">
-        <v>1</v>
-      </c>
-      <c r="F776" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G776" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="777" spans="3:7">
-      <c r="C777" s="6">
-        <v>19017</v>
-      </c>
-      <c r="D777" s="3">
-        <v>190</v>
-      </c>
-      <c r="E777" s="3">
-        <v>1</v>
-      </c>
-      <c r="F777" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G777" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="778" spans="3:7">
-      <c r="C778" s="6">
-        <v>19018</v>
-      </c>
-      <c r="D778" s="3">
-        <v>190</v>
-      </c>
-      <c r="E778" s="5">
-        <v>1</v>
-      </c>
-      <c r="F778" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G778" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="779" spans="3:7">
-      <c r="C779" s="6">
-        <v>19019</v>
-      </c>
-      <c r="D779" s="3">
-        <v>190</v>
-      </c>
-      <c r="E779" s="5">
-        <v>1</v>
-      </c>
-      <c r="F779" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G779" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="780" spans="3:7">
-      <c r="C780" s="6">
-        <v>19020</v>
-      </c>
-      <c r="D780" s="3">
-        <v>190</v>
-      </c>
-      <c r="E780" s="5">
-        <v>1</v>
-      </c>
-      <c r="F780" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G780" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="781" spans="3:7">
-      <c r="C781" s="6">
-        <v>19021</v>
-      </c>
-      <c r="D781" s="3">
-        <v>190</v>
-      </c>
-      <c r="E781" s="3">
-        <v>1</v>
-      </c>
-      <c r="F781" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G781" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="782" spans="3:7">
-      <c r="C782" s="6">
-        <v>19022</v>
-      </c>
-      <c r="D782" s="3">
-        <v>190</v>
-      </c>
-      <c r="E782" s="5">
-        <v>1</v>
-      </c>
-      <c r="F782" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G782" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="783" spans="3:7">
-      <c r="C783" s="6">
-        <v>19023</v>
-      </c>
-      <c r="D783" s="3">
-        <v>190</v>
-      </c>
-      <c r="E783" s="5">
-        <v>1</v>
-      </c>
-      <c r="F783" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G783" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="784" spans="3:7">
-      <c r="C784" s="6">
-        <v>19024</v>
-      </c>
-      <c r="D784" s="3">
-        <v>190</v>
-      </c>
-      <c r="E784" s="5">
-        <v>1</v>
-      </c>
-      <c r="F784" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G784" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="785" spans="1:8">
-      <c r="C785" s="6">
-        <v>19025</v>
-      </c>
-      <c r="D785" s="3">
-        <v>190</v>
-      </c>
-      <c r="E785" s="3">
-        <v>1</v>
-      </c>
-      <c r="F785" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G785" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="787" spans="1:8">
-      <c r="A787" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C787" s="6">
-        <v>19101</v>
-      </c>
-      <c r="D787" s="3">
-        <v>191</v>
-      </c>
-      <c r="E787" s="5">
-        <v>1</v>
-      </c>
-      <c r="F787" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G787" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H787" s="3">
-        <v>20595</v>
-      </c>
-    </row>
-    <row r="788" spans="1:8">
-      <c r="A788" s="1"/>
-      <c r="B788" s="1"/>
-      <c r="C788" s="6">
-        <v>19102</v>
-      </c>
-      <c r="D788" s="3">
-        <v>191</v>
-      </c>
-      <c r="E788" s="5">
-        <v>1</v>
-      </c>
-      <c r="F788" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G788" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H788" s="3">
-        <v>20596</v>
-      </c>
-    </row>
-    <row r="789" spans="1:8">
-      <c r="C789" s="6">
-        <v>19103</v>
-      </c>
-      <c r="D789" s="3">
-        <v>191</v>
-      </c>
-      <c r="E789" s="5">
-        <v>1</v>
-      </c>
-      <c r="F789" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G789" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H789" s="3">
-        <v>20597</v>
-      </c>
-    </row>
-    <row r="790" spans="1:8">
-      <c r="C790" s="6">
-        <v>19104</v>
-      </c>
-      <c r="D790" s="3">
-        <v>191</v>
-      </c>
-      <c r="E790" s="5">
-        <v>1</v>
-      </c>
-      <c r="F790" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G790" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H790" s="3">
-        <v>20598</v>
-      </c>
-    </row>
-    <row r="791" spans="1:8">
-      <c r="C791" s="6">
-        <v>19105</v>
-      </c>
-      <c r="D791" s="3">
-        <v>191</v>
-      </c>
-      <c r="E791" s="3">
-        <v>1</v>
-      </c>
-      <c r="F791" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G791" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="792" spans="1:8">
-      <c r="C792" s="6">
-        <v>19106</v>
-      </c>
-      <c r="D792" s="3">
-        <v>191</v>
-      </c>
-      <c r="E792" s="5">
-        <v>1</v>
-      </c>
-      <c r="F792" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G792" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="793" spans="1:8">
-      <c r="C793" s="6">
-        <v>19107</v>
-      </c>
-      <c r="D793" s="3">
-        <v>191</v>
-      </c>
-      <c r="E793" s="5">
-        <v>1</v>
-      </c>
-      <c r="F793" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G793" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="794" spans="1:8">
-      <c r="C794" s="6">
-        <v>19108</v>
-      </c>
-      <c r="D794" s="3">
-        <v>191</v>
-      </c>
-      <c r="E794" s="5">
-        <v>1</v>
-      </c>
-      <c r="F794" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G794" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="795" spans="1:8">
-      <c r="C795" s="6">
-        <v>19109</v>
-      </c>
-      <c r="D795" s="3">
-        <v>191</v>
-      </c>
-      <c r="E795" s="3">
-        <v>1</v>
-      </c>
-      <c r="F795" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G795" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="796" spans="1:8">
-      <c r="C796" s="6">
-        <v>19110</v>
-      </c>
-      <c r="D796" s="3">
-        <v>191</v>
-      </c>
-      <c r="E796" s="5">
-        <v>1</v>
-      </c>
-      <c r="F796" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G796" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="797" spans="1:8">
-      <c r="C797" s="6">
-        <v>19111</v>
-      </c>
-      <c r="D797" s="3">
-        <v>191</v>
-      </c>
-      <c r="E797" s="5">
-        <v>1</v>
-      </c>
-      <c r="F797" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G797" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="798" spans="1:8">
-      <c r="C798" s="6">
-        <v>19112</v>
-      </c>
-      <c r="D798" s="3">
-        <v>191</v>
-      </c>
-      <c r="E798" s="5">
-        <v>1</v>
-      </c>
-      <c r="F798" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G798" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="799" spans="1:8">
-      <c r="C799" s="6">
-        <v>19113</v>
-      </c>
-      <c r="D799" s="3">
-        <v>191</v>
-      </c>
-      <c r="E799" s="3">
-        <v>1</v>
-      </c>
-      <c r="F799" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G799" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="800" spans="1:8">
-      <c r="C800" s="6">
-        <v>19114</v>
-      </c>
-      <c r="D800" s="3">
-        <v>191</v>
-      </c>
-      <c r="E800" s="5">
-        <v>1</v>
-      </c>
-      <c r="F800" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G800" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="801" spans="3:7">
-      <c r="C801" s="6">
-        <v>19115</v>
-      </c>
-      <c r="D801" s="3">
-        <v>191</v>
-      </c>
-      <c r="E801" s="5">
-        <v>1</v>
-      </c>
-      <c r="F801" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G801" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="802" spans="3:7">
-      <c r="C802" s="6">
-        <v>19116</v>
-      </c>
-      <c r="D802" s="3">
-        <v>191</v>
-      </c>
-      <c r="E802" s="5">
-        <v>1</v>
-      </c>
-      <c r="F802" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G802" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="803" spans="3:7">
-      <c r="C803" s="6">
-        <v>19117</v>
-      </c>
-      <c r="D803" s="3">
-        <v>191</v>
-      </c>
-      <c r="E803" s="3">
-        <v>1</v>
-      </c>
-      <c r="F803" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G803" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="804" spans="3:7">
-      <c r="C804" s="6">
-        <v>19118</v>
-      </c>
-      <c r="D804" s="3">
-        <v>191</v>
-      </c>
-      <c r="E804" s="5">
-        <v>1</v>
-      </c>
-      <c r="F804" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G804" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="805" spans="3:7">
-      <c r="C805" s="6">
-        <v>19119</v>
-      </c>
-      <c r="D805" s="3">
-        <v>191</v>
-      </c>
-      <c r="E805" s="5">
-        <v>1</v>
-      </c>
-      <c r="F805" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G805" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="806" spans="3:7">
-      <c r="C806" s="6">
-        <v>19120</v>
-      </c>
-      <c r="D806" s="3">
-        <v>191</v>
-      </c>
-      <c r="E806" s="5">
-        <v>1</v>
-      </c>
-      <c r="F806" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G806" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="807" spans="3:7">
-      <c r="C807" s="6">
-        <v>19121</v>
-      </c>
-      <c r="D807" s="3">
-        <v>191</v>
-      </c>
-      <c r="E807" s="3">
-        <v>1</v>
-      </c>
-      <c r="F807" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G807" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="808" spans="3:7">
-      <c r="C808" s="6">
-        <v>19122</v>
-      </c>
-      <c r="D808" s="3">
-        <v>191</v>
-      </c>
-      <c r="E808" s="5">
-        <v>1</v>
-      </c>
-      <c r="F808" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G808" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="809" spans="3:7">
-      <c r="C809" s="6">
-        <v>19123</v>
-      </c>
-      <c r="D809" s="3">
-        <v>191</v>
-      </c>
-      <c r="E809" s="5">
-        <v>1</v>
-      </c>
-      <c r="F809" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G809" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="810" spans="3:7">
-      <c r="C810" s="6">
-        <v>19124</v>
-      </c>
-      <c r="D810" s="3">
-        <v>191</v>
-      </c>
-      <c r="E810" s="5">
-        <v>1</v>
-      </c>
-      <c r="F810" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G810" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="811" spans="3:7">
-      <c r="C811" s="6">
-        <v>19125</v>
-      </c>
-      <c r="D811" s="3">
-        <v>191</v>
-      </c>
-      <c r="E811" s="3">
-        <v>1</v>
-      </c>
-      <c r="F811" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G811" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15210,10 +13430,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -15228,10 +13448,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -15246,10 +13466,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -15264,10 +13484,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -15284,10 +13504,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -15382,10 +13602,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
   <si>
     <t>Id</t>
   </si>
@@ -236,6 +236,9 @@
   </si>
   <si>
     <t>#先锋191沧澜神域</t>
+  </si>
+  <si>
+    <t>#先锋192剑啸山河</t>
   </si>
   <si>
     <t>Center</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O707"/>
+  <dimension ref="A3:O733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13262,7 +13265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="705" spans="3:7">
+    <row r="705" spans="1:8">
       <c r="C705" s="6">
         <v>19123</v>
       </c>
@@ -13279,7 +13282,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="706" spans="3:7">
+    <row r="706" spans="1:8">
       <c r="C706" s="6">
         <v>19124</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="707" spans="3:7">
+    <row r="707" spans="1:8">
       <c r="C707" s="6">
         <v>19125</v>
       </c>
@@ -13310,6 +13313,448 @@
         <v>42</v>
       </c>
       <c r="G707" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="709" spans="1:8">
+      <c r="A709" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C709" s="6">
+        <v>19201</v>
+      </c>
+      <c r="D709" s="3">
+        <v>192</v>
+      </c>
+      <c r="E709" s="5">
+        <v>1</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G709" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H709" s="3">
+        <v>20455</v>
+      </c>
+    </row>
+    <row r="710" spans="1:8">
+      <c r="A710" s="1"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="6">
+        <v>19202</v>
+      </c>
+      <c r="D710" s="3">
+        <v>192</v>
+      </c>
+      <c r="E710" s="5">
+        <v>1</v>
+      </c>
+      <c r="F710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G710" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H710" s="3">
+        <v>20456</v>
+      </c>
+    </row>
+    <row r="711" spans="1:8">
+      <c r="C711" s="6">
+        <v>19203</v>
+      </c>
+      <c r="D711" s="3">
+        <v>192</v>
+      </c>
+      <c r="E711" s="5">
+        <v>1</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G711" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H711" s="3">
+        <v>20457</v>
+      </c>
+    </row>
+    <row r="712" spans="1:8">
+      <c r="C712" s="6">
+        <v>19204</v>
+      </c>
+      <c r="D712" s="3">
+        <v>192</v>
+      </c>
+      <c r="E712" s="5">
+        <v>1</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G712" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H712" s="3">
+        <v>20458</v>
+      </c>
+    </row>
+    <row r="713" spans="1:8">
+      <c r="C713" s="6">
+        <v>19205</v>
+      </c>
+      <c r="D713" s="3">
+        <v>192</v>
+      </c>
+      <c r="E713" s="3">
+        <v>1</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G713" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="714" spans="1:8">
+      <c r="C714" s="6">
+        <v>19206</v>
+      </c>
+      <c r="D714" s="3">
+        <v>192</v>
+      </c>
+      <c r="E714" s="5">
+        <v>1</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G714" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="715" spans="1:8">
+      <c r="C715" s="6">
+        <v>19207</v>
+      </c>
+      <c r="D715" s="3">
+        <v>192</v>
+      </c>
+      <c r="E715" s="5">
+        <v>1</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G715" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="716" spans="1:8">
+      <c r="C716" s="6">
+        <v>19208</v>
+      </c>
+      <c r="D716" s="3">
+        <v>192</v>
+      </c>
+      <c r="E716" s="5">
+        <v>1</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G716" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="1:8">
+      <c r="C717" s="6">
+        <v>19209</v>
+      </c>
+      <c r="D717" s="3">
+        <v>192</v>
+      </c>
+      <c r="E717" s="3">
+        <v>1</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G717" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="718" spans="1:8">
+      <c r="C718" s="6">
+        <v>19210</v>
+      </c>
+      <c r="D718" s="3">
+        <v>192</v>
+      </c>
+      <c r="E718" s="5">
+        <v>1</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G718" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="719" spans="1:8">
+      <c r="C719" s="6">
+        <v>19211</v>
+      </c>
+      <c r="D719" s="3">
+        <v>192</v>
+      </c>
+      <c r="E719" s="5">
+        <v>1</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G719" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="720" spans="1:8">
+      <c r="C720" s="6">
+        <v>19212</v>
+      </c>
+      <c r="D720" s="3">
+        <v>192</v>
+      </c>
+      <c r="E720" s="5">
+        <v>1</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G720" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="721" spans="3:7">
+      <c r="C721" s="6">
+        <v>19213</v>
+      </c>
+      <c r="D721" s="3">
+        <v>192</v>
+      </c>
+      <c r="E721" s="3">
+        <v>1</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G721" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="722" spans="3:7">
+      <c r="C722" s="6">
+        <v>19214</v>
+      </c>
+      <c r="D722" s="3">
+        <v>192</v>
+      </c>
+      <c r="E722" s="5">
+        <v>1</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G722" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="723" spans="3:7">
+      <c r="C723" s="6">
+        <v>19215</v>
+      </c>
+      <c r="D723" s="3">
+        <v>192</v>
+      </c>
+      <c r="E723" s="5">
+        <v>1</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G723" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="724" spans="3:7">
+      <c r="C724" s="6">
+        <v>19216</v>
+      </c>
+      <c r="D724" s="3">
+        <v>192</v>
+      </c>
+      <c r="E724" s="5">
+        <v>1</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G724" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="725" spans="3:7">
+      <c r="C725" s="6">
+        <v>19217</v>
+      </c>
+      <c r="D725" s="3">
+        <v>192</v>
+      </c>
+      <c r="E725" s="3">
+        <v>1</v>
+      </c>
+      <c r="F725" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G725" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="726" spans="3:7">
+      <c r="C726" s="6">
+        <v>19218</v>
+      </c>
+      <c r="D726" s="3">
+        <v>192</v>
+      </c>
+      <c r="E726" s="5">
+        <v>1</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G726" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="727" spans="3:7">
+      <c r="C727" s="6">
+        <v>19219</v>
+      </c>
+      <c r="D727" s="3">
+        <v>192</v>
+      </c>
+      <c r="E727" s="5">
+        <v>1</v>
+      </c>
+      <c r="F727" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G727" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="728" spans="3:7">
+      <c r="C728" s="6">
+        <v>19220</v>
+      </c>
+      <c r="D728" s="3">
+        <v>192</v>
+      </c>
+      <c r="E728" s="5">
+        <v>1</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G728" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="729" spans="3:7">
+      <c r="C729" s="6">
+        <v>19221</v>
+      </c>
+      <c r="D729" s="3">
+        <v>192</v>
+      </c>
+      <c r="E729" s="3">
+        <v>1</v>
+      </c>
+      <c r="F729" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G729" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="730" spans="3:7">
+      <c r="C730" s="6">
+        <v>19222</v>
+      </c>
+      <c r="D730" s="3">
+        <v>192</v>
+      </c>
+      <c r="E730" s="5">
+        <v>1</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G730" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="731" spans="3:7">
+      <c r="C731" s="6">
+        <v>19223</v>
+      </c>
+      <c r="D731" s="3">
+        <v>192</v>
+      </c>
+      <c r="E731" s="5">
+        <v>1</v>
+      </c>
+      <c r="F731" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G731" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="732" spans="3:7">
+      <c r="C732" s="6">
+        <v>19224</v>
+      </c>
+      <c r="D732" s="3">
+        <v>192</v>
+      </c>
+      <c r="E732" s="5">
+        <v>1</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G732" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="733" spans="3:7">
+      <c r="C733" s="6">
+        <v>19225</v>
+      </c>
+      <c r="D733" s="3">
+        <v>192</v>
+      </c>
+      <c r="E733" s="3">
+        <v>1</v>
+      </c>
+      <c r="F733" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G733" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13430,10 +13875,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13448,10 +13893,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13466,10 +13911,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13484,10 +13929,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13504,10 +13949,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +14047,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
   <si>
     <t>Id</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>#先锋192剑啸山河</t>
+  </si>
+  <si>
+    <t>#先锋193精灵之森</t>
   </si>
   <si>
     <t>Center</t>
@@ -1266,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O733"/>
+  <dimension ref="A3:O759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -13537,7 +13540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="721" spans="3:7">
+    <row r="721" spans="1:8">
       <c r="C721" s="6">
         <v>19213</v>
       </c>
@@ -13554,7 +13557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="722" spans="3:7">
+    <row r="722" spans="1:8">
       <c r="C722" s="6">
         <v>19214</v>
       </c>
@@ -13571,7 +13574,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="723" spans="3:7">
+    <row r="723" spans="1:8">
       <c r="C723" s="6">
         <v>19215</v>
       </c>
@@ -13588,7 +13591,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="724" spans="3:7">
+    <row r="724" spans="1:8">
       <c r="C724" s="6">
         <v>19216</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="725" spans="3:7">
+    <row r="725" spans="1:8">
       <c r="C725" s="6">
         <v>19217</v>
       </c>
@@ -13622,7 +13625,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="726" spans="3:7">
+    <row r="726" spans="1:8">
       <c r="C726" s="6">
         <v>19218</v>
       </c>
@@ -13639,7 +13642,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="727" spans="3:7">
+    <row r="727" spans="1:8">
       <c r="C727" s="6">
         <v>19219</v>
       </c>
@@ -13656,7 +13659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="728" spans="3:7">
+    <row r="728" spans="1:8">
       <c r="C728" s="6">
         <v>19220</v>
       </c>
@@ -13673,7 +13676,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="729" spans="3:7">
+    <row r="729" spans="1:8">
       <c r="C729" s="6">
         <v>19221</v>
       </c>
@@ -13690,7 +13693,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="730" spans="3:7">
+    <row r="730" spans="1:8">
       <c r="C730" s="6">
         <v>19222</v>
       </c>
@@ -13707,7 +13710,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="731" spans="3:7">
+    <row r="731" spans="1:8">
       <c r="C731" s="6">
         <v>19223</v>
       </c>
@@ -13724,7 +13727,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="732" spans="3:7">
+    <row r="732" spans="1:8">
       <c r="C732" s="6">
         <v>19224</v>
       </c>
@@ -13741,7 +13744,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="733" spans="3:7">
+    <row r="733" spans="1:8">
       <c r="C733" s="6">
         <v>19225</v>
       </c>
@@ -13755,6 +13758,448 @@
         <v>42</v>
       </c>
       <c r="G733" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="735" spans="1:8">
+      <c r="A735" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C735" s="6">
+        <v>19301</v>
+      </c>
+      <c r="D735" s="3">
+        <v>193</v>
+      </c>
+      <c r="E735" s="5">
+        <v>1</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G735" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H735" s="3">
+        <v>20495</v>
+      </c>
+    </row>
+    <row r="736" spans="1:8">
+      <c r="A736" s="1"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="6">
+        <v>19302</v>
+      </c>
+      <c r="D736" s="3">
+        <v>193</v>
+      </c>
+      <c r="E736" s="5">
+        <v>1</v>
+      </c>
+      <c r="F736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G736" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H736" s="3">
+        <v>20496</v>
+      </c>
+    </row>
+    <row r="737" spans="3:8">
+      <c r="C737" s="6">
+        <v>19303</v>
+      </c>
+      <c r="D737" s="3">
+        <v>193</v>
+      </c>
+      <c r="E737" s="5">
+        <v>1</v>
+      </c>
+      <c r="F737" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G737" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H737" s="3">
+        <v>20497</v>
+      </c>
+    </row>
+    <row r="738" spans="3:8">
+      <c r="C738" s="6">
+        <v>19304</v>
+      </c>
+      <c r="D738" s="3">
+        <v>193</v>
+      </c>
+      <c r="E738" s="5">
+        <v>1</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G738" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H738" s="3">
+        <v>20498</v>
+      </c>
+    </row>
+    <row r="739" spans="3:8">
+      <c r="C739" s="6">
+        <v>19305</v>
+      </c>
+      <c r="D739" s="3">
+        <v>193</v>
+      </c>
+      <c r="E739" s="3">
+        <v>1</v>
+      </c>
+      <c r="F739" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G739" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="740" spans="3:8">
+      <c r="C740" s="6">
+        <v>19306</v>
+      </c>
+      <c r="D740" s="3">
+        <v>193</v>
+      </c>
+      <c r="E740" s="5">
+        <v>1</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G740" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="741" spans="3:8">
+      <c r="C741" s="6">
+        <v>19307</v>
+      </c>
+      <c r="D741" s="3">
+        <v>193</v>
+      </c>
+      <c r="E741" s="5">
+        <v>1</v>
+      </c>
+      <c r="F741" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G741" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="742" spans="3:8">
+      <c r="C742" s="6">
+        <v>19308</v>
+      </c>
+      <c r="D742" s="3">
+        <v>193</v>
+      </c>
+      <c r="E742" s="5">
+        <v>1</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G742" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="743" spans="3:8">
+      <c r="C743" s="6">
+        <v>19309</v>
+      </c>
+      <c r="D743" s="3">
+        <v>193</v>
+      </c>
+      <c r="E743" s="3">
+        <v>1</v>
+      </c>
+      <c r="F743" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G743" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="744" spans="3:8">
+      <c r="C744" s="6">
+        <v>19310</v>
+      </c>
+      <c r="D744" s="3">
+        <v>193</v>
+      </c>
+      <c r="E744" s="5">
+        <v>1</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G744" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="745" spans="3:8">
+      <c r="C745" s="6">
+        <v>19311</v>
+      </c>
+      <c r="D745" s="3">
+        <v>193</v>
+      </c>
+      <c r="E745" s="5">
+        <v>1</v>
+      </c>
+      <c r="F745" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G745" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="746" spans="3:8">
+      <c r="C746" s="6">
+        <v>19312</v>
+      </c>
+      <c r="D746" s="3">
+        <v>193</v>
+      </c>
+      <c r="E746" s="5">
+        <v>1</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G746" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="747" spans="3:8">
+      <c r="C747" s="6">
+        <v>19313</v>
+      </c>
+      <c r="D747" s="3">
+        <v>193</v>
+      </c>
+      <c r="E747" s="3">
+        <v>1</v>
+      </c>
+      <c r="F747" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G747" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="748" spans="3:8">
+      <c r="C748" s="6">
+        <v>19314</v>
+      </c>
+      <c r="D748" s="3">
+        <v>193</v>
+      </c>
+      <c r="E748" s="5">
+        <v>1</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G748" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="749" spans="3:8">
+      <c r="C749" s="6">
+        <v>19315</v>
+      </c>
+      <c r="D749" s="3">
+        <v>193</v>
+      </c>
+      <c r="E749" s="5">
+        <v>1</v>
+      </c>
+      <c r="F749" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G749" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="750" spans="3:8">
+      <c r="C750" s="6">
+        <v>19316</v>
+      </c>
+      <c r="D750" s="3">
+        <v>193</v>
+      </c>
+      <c r="E750" s="5">
+        <v>1</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G750" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="751" spans="3:8">
+      <c r="C751" s="6">
+        <v>19317</v>
+      </c>
+      <c r="D751" s="3">
+        <v>193</v>
+      </c>
+      <c r="E751" s="3">
+        <v>1</v>
+      </c>
+      <c r="F751" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G751" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="752" spans="3:8">
+      <c r="C752" s="6">
+        <v>19318</v>
+      </c>
+      <c r="D752" s="3">
+        <v>193</v>
+      </c>
+      <c r="E752" s="5">
+        <v>1</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G752" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="753" spans="3:7">
+      <c r="C753" s="6">
+        <v>19319</v>
+      </c>
+      <c r="D753" s="3">
+        <v>193</v>
+      </c>
+      <c r="E753" s="5">
+        <v>1</v>
+      </c>
+      <c r="F753" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G753" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="754" spans="3:7">
+      <c r="C754" s="6">
+        <v>19320</v>
+      </c>
+      <c r="D754" s="3">
+        <v>193</v>
+      </c>
+      <c r="E754" s="5">
+        <v>1</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G754" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="755" spans="3:7">
+      <c r="C755" s="6">
+        <v>19321</v>
+      </c>
+      <c r="D755" s="3">
+        <v>193</v>
+      </c>
+      <c r="E755" s="3">
+        <v>1</v>
+      </c>
+      <c r="F755" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G755" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="756" spans="3:7">
+      <c r="C756" s="6">
+        <v>19322</v>
+      </c>
+      <c r="D756" s="3">
+        <v>193</v>
+      </c>
+      <c r="E756" s="5">
+        <v>1</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G756" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="757" spans="3:7">
+      <c r="C757" s="6">
+        <v>19323</v>
+      </c>
+      <c r="D757" s="3">
+        <v>193</v>
+      </c>
+      <c r="E757" s="5">
+        <v>1</v>
+      </c>
+      <c r="F757" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G757" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="758" spans="3:7">
+      <c r="C758" s="6">
+        <v>19324</v>
+      </c>
+      <c r="D758" s="3">
+        <v>193</v>
+      </c>
+      <c r="E758" s="5">
+        <v>1</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G758" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="759" spans="3:7">
+      <c r="C759" s="6">
+        <v>19325</v>
+      </c>
+      <c r="D759" s="3">
+        <v>193</v>
+      </c>
+      <c r="E759" s="3">
+        <v>1</v>
+      </c>
+      <c r="F759" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G759" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13875,10 +14320,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -13893,10 +14338,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -13911,10 +14356,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -13929,10 +14374,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -13949,10 +14394,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -14047,10 +14492,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>#先锋193精灵之森</t>
+  </si>
+  <si>
+    <t>#先锋194</t>
   </si>
   <si>
     <t>Center</t>
@@ -1269,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O759"/>
+  <dimension ref="A3:O785"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14084,7 +14087,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="753" spans="3:7">
+    <row r="753" spans="1:8">
       <c r="C753" s="6">
         <v>19319</v>
       </c>
@@ -14101,7 +14104,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="754" spans="3:7">
+    <row r="754" spans="1:8">
       <c r="C754" s="6">
         <v>19320</v>
       </c>
@@ -14118,7 +14121,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="755" spans="3:7">
+    <row r="755" spans="1:8">
       <c r="C755" s="6">
         <v>19321</v>
       </c>
@@ -14135,7 +14138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="756" spans="3:7">
+    <row r="756" spans="1:8">
       <c r="C756" s="6">
         <v>19322</v>
       </c>
@@ -14152,7 +14155,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="757" spans="3:7">
+    <row r="757" spans="1:8">
       <c r="C757" s="6">
         <v>19323</v>
       </c>
@@ -14169,7 +14172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="758" spans="3:7">
+    <row r="758" spans="1:8">
       <c r="C758" s="6">
         <v>19324</v>
       </c>
@@ -14186,7 +14189,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="759" spans="3:7">
+    <row r="759" spans="1:8">
       <c r="C759" s="6">
         <v>19325</v>
       </c>
@@ -14200,6 +14203,448 @@
         <v>42</v>
       </c>
       <c r="G759" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="761" spans="1:8">
+      <c r="A761" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C761" s="6">
+        <v>19401</v>
+      </c>
+      <c r="D761" s="3">
+        <v>194</v>
+      </c>
+      <c r="E761" s="5">
+        <v>1</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G761" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H761" s="3">
+        <v>20545</v>
+      </c>
+    </row>
+    <row r="762" spans="1:8">
+      <c r="A762" s="1"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="6">
+        <v>19402</v>
+      </c>
+      <c r="D762" s="3">
+        <v>194</v>
+      </c>
+      <c r="E762" s="5">
+        <v>1</v>
+      </c>
+      <c r="F762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G762" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H762" s="3">
+        <v>20546</v>
+      </c>
+    </row>
+    <row r="763" spans="1:8">
+      <c r="C763" s="6">
+        <v>19403</v>
+      </c>
+      <c r="D763" s="3">
+        <v>194</v>
+      </c>
+      <c r="E763" s="5">
+        <v>1</v>
+      </c>
+      <c r="F763" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G763" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H763" s="3">
+        <v>20547</v>
+      </c>
+    </row>
+    <row r="764" spans="1:8">
+      <c r="C764" s="6">
+        <v>19404</v>
+      </c>
+      <c r="D764" s="3">
+        <v>194</v>
+      </c>
+      <c r="E764" s="5">
+        <v>1</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G764" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H764" s="3">
+        <v>20548</v>
+      </c>
+    </row>
+    <row r="765" spans="1:8">
+      <c r="C765" s="6">
+        <v>19405</v>
+      </c>
+      <c r="D765" s="3">
+        <v>194</v>
+      </c>
+      <c r="E765" s="3">
+        <v>1</v>
+      </c>
+      <c r="F765" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G765" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="766" spans="1:8">
+      <c r="C766" s="6">
+        <v>19406</v>
+      </c>
+      <c r="D766" s="3">
+        <v>194</v>
+      </c>
+      <c r="E766" s="5">
+        <v>1</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G766" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="767" spans="1:8">
+      <c r="C767" s="6">
+        <v>19407</v>
+      </c>
+      <c r="D767" s="3">
+        <v>194</v>
+      </c>
+      <c r="E767" s="5">
+        <v>1</v>
+      </c>
+      <c r="F767" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G767" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="768" spans="1:8">
+      <c r="C768" s="6">
+        <v>19408</v>
+      </c>
+      <c r="D768" s="3">
+        <v>194</v>
+      </c>
+      <c r="E768" s="5">
+        <v>1</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G768" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="769" spans="3:7">
+      <c r="C769" s="6">
+        <v>19409</v>
+      </c>
+      <c r="D769" s="3">
+        <v>194</v>
+      </c>
+      <c r="E769" s="3">
+        <v>1</v>
+      </c>
+      <c r="F769" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G769" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="770" spans="3:7">
+      <c r="C770" s="6">
+        <v>19410</v>
+      </c>
+      <c r="D770" s="3">
+        <v>194</v>
+      </c>
+      <c r="E770" s="5">
+        <v>1</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G770" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="771" spans="3:7">
+      <c r="C771" s="6">
+        <v>19411</v>
+      </c>
+      <c r="D771" s="3">
+        <v>194</v>
+      </c>
+      <c r="E771" s="5">
+        <v>1</v>
+      </c>
+      <c r="F771" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G771" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="772" spans="3:7">
+      <c r="C772" s="6">
+        <v>19412</v>
+      </c>
+      <c r="D772" s="3">
+        <v>194</v>
+      </c>
+      <c r="E772" s="5">
+        <v>1</v>
+      </c>
+      <c r="F772" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G772" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="773" spans="3:7">
+      <c r="C773" s="6">
+        <v>19413</v>
+      </c>
+      <c r="D773" s="3">
+        <v>194</v>
+      </c>
+      <c r="E773" s="3">
+        <v>1</v>
+      </c>
+      <c r="F773" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G773" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="774" spans="3:7">
+      <c r="C774" s="6">
+        <v>19414</v>
+      </c>
+      <c r="D774" s="3">
+        <v>194</v>
+      </c>
+      <c r="E774" s="5">
+        <v>1</v>
+      </c>
+      <c r="F774" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G774" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="775" spans="3:7">
+      <c r="C775" s="6">
+        <v>19415</v>
+      </c>
+      <c r="D775" s="3">
+        <v>194</v>
+      </c>
+      <c r="E775" s="5">
+        <v>1</v>
+      </c>
+      <c r="F775" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G775" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="776" spans="3:7">
+      <c r="C776" s="6">
+        <v>19416</v>
+      </c>
+      <c r="D776" s="3">
+        <v>194</v>
+      </c>
+      <c r="E776" s="5">
+        <v>1</v>
+      </c>
+      <c r="F776" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G776" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="777" spans="3:7">
+      <c r="C777" s="6">
+        <v>19417</v>
+      </c>
+      <c r="D777" s="3">
+        <v>194</v>
+      </c>
+      <c r="E777" s="3">
+        <v>1</v>
+      </c>
+      <c r="F777" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G777" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="778" spans="3:7">
+      <c r="C778" s="6">
+        <v>19418</v>
+      </c>
+      <c r="D778" s="3">
+        <v>194</v>
+      </c>
+      <c r="E778" s="5">
+        <v>1</v>
+      </c>
+      <c r="F778" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G778" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="779" spans="3:7">
+      <c r="C779" s="6">
+        <v>19419</v>
+      </c>
+      <c r="D779" s="3">
+        <v>194</v>
+      </c>
+      <c r="E779" s="5">
+        <v>1</v>
+      </c>
+      <c r="F779" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G779" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="780" spans="3:7">
+      <c r="C780" s="6">
+        <v>19420</v>
+      </c>
+      <c r="D780" s="3">
+        <v>194</v>
+      </c>
+      <c r="E780" s="5">
+        <v>1</v>
+      </c>
+      <c r="F780" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G780" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="781" spans="3:7">
+      <c r="C781" s="6">
+        <v>19421</v>
+      </c>
+      <c r="D781" s="3">
+        <v>194</v>
+      </c>
+      <c r="E781" s="3">
+        <v>1</v>
+      </c>
+      <c r="F781" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G781" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="782" spans="3:7">
+      <c r="C782" s="6">
+        <v>19422</v>
+      </c>
+      <c r="D782" s="3">
+        <v>194</v>
+      </c>
+      <c r="E782" s="5">
+        <v>1</v>
+      </c>
+      <c r="F782" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G782" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="783" spans="3:7">
+      <c r="C783" s="6">
+        <v>19423</v>
+      </c>
+      <c r="D783" s="3">
+        <v>194</v>
+      </c>
+      <c r="E783" s="5">
+        <v>1</v>
+      </c>
+      <c r="F783" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G783" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="784" spans="3:7">
+      <c r="C784" s="6">
+        <v>19424</v>
+      </c>
+      <c r="D784" s="3">
+        <v>194</v>
+      </c>
+      <c r="E784" s="5">
+        <v>1</v>
+      </c>
+      <c r="F784" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G784" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="785" spans="3:7">
+      <c r="C785" s="6">
+        <v>19425</v>
+      </c>
+      <c r="D785" s="3">
+        <v>194</v>
+      </c>
+      <c r="E785" s="3">
+        <v>1</v>
+      </c>
+      <c r="F785" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G785" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14320,10 +14765,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14338,10 +14783,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14356,10 +14801,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14374,10 +14819,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14394,10 +14839,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14492,10 +14937,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -244,7 +244,7 @@
     <t>#先锋193精灵之森</t>
   </si>
   <si>
-    <t>#先锋194</t>
+    <t>#先锋194龙焰王座</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
   <si>
     <t>Id</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>#先锋194龙焰王座</t>
+  </si>
+  <si>
+    <t>#先锋195</t>
   </si>
   <si>
     <t>Center</t>
@@ -1272,7 +1275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O785"/>
+  <dimension ref="A3:O811"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14631,7 +14634,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="785" spans="3:7">
+    <row r="785" spans="1:8">
       <c r="C785" s="6">
         <v>19425</v>
       </c>
@@ -14645,6 +14648,448 @@
         <v>42</v>
       </c>
       <c r="G785" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="787" spans="1:8">
+      <c r="A787" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C787" s="6">
+        <v>19501</v>
+      </c>
+      <c r="D787" s="3">
+        <v>195</v>
+      </c>
+      <c r="E787" s="5">
+        <v>1</v>
+      </c>
+      <c r="F787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G787" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H787" s="3">
+        <v>20565</v>
+      </c>
+    </row>
+    <row r="788" spans="1:8">
+      <c r="A788" s="1"/>
+      <c r="B788" s="1"/>
+      <c r="C788" s="6">
+        <v>19502</v>
+      </c>
+      <c r="D788" s="3">
+        <v>195</v>
+      </c>
+      <c r="E788" s="5">
+        <v>1</v>
+      </c>
+      <c r="F788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G788" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H788" s="3">
+        <v>20566</v>
+      </c>
+    </row>
+    <row r="789" spans="1:8">
+      <c r="C789" s="6">
+        <v>19503</v>
+      </c>
+      <c r="D789" s="3">
+        <v>195</v>
+      </c>
+      <c r="E789" s="5">
+        <v>1</v>
+      </c>
+      <c r="F789" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G789" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H789" s="3">
+        <v>20567</v>
+      </c>
+    </row>
+    <row r="790" spans="1:8">
+      <c r="C790" s="6">
+        <v>19504</v>
+      </c>
+      <c r="D790" s="3">
+        <v>195</v>
+      </c>
+      <c r="E790" s="5">
+        <v>1</v>
+      </c>
+      <c r="F790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G790" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H790" s="3">
+        <v>20568</v>
+      </c>
+    </row>
+    <row r="791" spans="1:8">
+      <c r="C791" s="6">
+        <v>19505</v>
+      </c>
+      <c r="D791" s="3">
+        <v>195</v>
+      </c>
+      <c r="E791" s="3">
+        <v>1</v>
+      </c>
+      <c r="F791" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G791" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="1:8">
+      <c r="C792" s="6">
+        <v>19506</v>
+      </c>
+      <c r="D792" s="3">
+        <v>195</v>
+      </c>
+      <c r="E792" s="5">
+        <v>1</v>
+      </c>
+      <c r="F792" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G792" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="793" spans="1:8">
+      <c r="C793" s="6">
+        <v>19507</v>
+      </c>
+      <c r="D793" s="3">
+        <v>195</v>
+      </c>
+      <c r="E793" s="5">
+        <v>1</v>
+      </c>
+      <c r="F793" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G793" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="794" spans="1:8">
+      <c r="C794" s="6">
+        <v>19508</v>
+      </c>
+      <c r="D794" s="3">
+        <v>195</v>
+      </c>
+      <c r="E794" s="5">
+        <v>1</v>
+      </c>
+      <c r="F794" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G794" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="795" spans="1:8">
+      <c r="C795" s="6">
+        <v>19509</v>
+      </c>
+      <c r="D795" s="3">
+        <v>195</v>
+      </c>
+      <c r="E795" s="3">
+        <v>1</v>
+      </c>
+      <c r="F795" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G795" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="796" spans="1:8">
+      <c r="C796" s="6">
+        <v>19510</v>
+      </c>
+      <c r="D796" s="3">
+        <v>195</v>
+      </c>
+      <c r="E796" s="5">
+        <v>1</v>
+      </c>
+      <c r="F796" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G796" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="797" spans="1:8">
+      <c r="C797" s="6">
+        <v>19511</v>
+      </c>
+      <c r="D797" s="3">
+        <v>195</v>
+      </c>
+      <c r="E797" s="5">
+        <v>1</v>
+      </c>
+      <c r="F797" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G797" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="798" spans="1:8">
+      <c r="C798" s="6">
+        <v>19512</v>
+      </c>
+      <c r="D798" s="3">
+        <v>195</v>
+      </c>
+      <c r="E798" s="5">
+        <v>1</v>
+      </c>
+      <c r="F798" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G798" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="799" spans="1:8">
+      <c r="C799" s="6">
+        <v>19513</v>
+      </c>
+      <c r="D799" s="3">
+        <v>195</v>
+      </c>
+      <c r="E799" s="3">
+        <v>1</v>
+      </c>
+      <c r="F799" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G799" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="800" spans="1:8">
+      <c r="C800" s="6">
+        <v>19514</v>
+      </c>
+      <c r="D800" s="3">
+        <v>195</v>
+      </c>
+      <c r="E800" s="5">
+        <v>1</v>
+      </c>
+      <c r="F800" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G800" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="801" spans="3:7">
+      <c r="C801" s="6">
+        <v>19515</v>
+      </c>
+      <c r="D801" s="3">
+        <v>195</v>
+      </c>
+      <c r="E801" s="5">
+        <v>1</v>
+      </c>
+      <c r="F801" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G801" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="802" spans="3:7">
+      <c r="C802" s="6">
+        <v>19516</v>
+      </c>
+      <c r="D802" s="3">
+        <v>195</v>
+      </c>
+      <c r="E802" s="5">
+        <v>1</v>
+      </c>
+      <c r="F802" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G802" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="803" spans="3:7">
+      <c r="C803" s="6">
+        <v>19517</v>
+      </c>
+      <c r="D803" s="3">
+        <v>195</v>
+      </c>
+      <c r="E803" s="3">
+        <v>1</v>
+      </c>
+      <c r="F803" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G803" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="804" spans="3:7">
+      <c r="C804" s="6">
+        <v>19518</v>
+      </c>
+      <c r="D804" s="3">
+        <v>195</v>
+      </c>
+      <c r="E804" s="5">
+        <v>1</v>
+      </c>
+      <c r="F804" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G804" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="805" spans="3:7">
+      <c r="C805" s="6">
+        <v>19519</v>
+      </c>
+      <c r="D805" s="3">
+        <v>195</v>
+      </c>
+      <c r="E805" s="5">
+        <v>1</v>
+      </c>
+      <c r="F805" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G805" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="806" spans="3:7">
+      <c r="C806" s="6">
+        <v>19520</v>
+      </c>
+      <c r="D806" s="3">
+        <v>195</v>
+      </c>
+      <c r="E806" s="5">
+        <v>1</v>
+      </c>
+      <c r="F806" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G806" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="807" spans="3:7">
+      <c r="C807" s="6">
+        <v>19521</v>
+      </c>
+      <c r="D807" s="3">
+        <v>195</v>
+      </c>
+      <c r="E807" s="3">
+        <v>1</v>
+      </c>
+      <c r="F807" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G807" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="808" spans="3:7">
+      <c r="C808" s="6">
+        <v>19522</v>
+      </c>
+      <c r="D808" s="3">
+        <v>195</v>
+      </c>
+      <c r="E808" s="5">
+        <v>1</v>
+      </c>
+      <c r="F808" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G808" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="809" spans="3:7">
+      <c r="C809" s="6">
+        <v>19523</v>
+      </c>
+      <c r="D809" s="3">
+        <v>195</v>
+      </c>
+      <c r="E809" s="5">
+        <v>1</v>
+      </c>
+      <c r="F809" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G809" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="810" spans="3:7">
+      <c r="C810" s="6">
+        <v>19524</v>
+      </c>
+      <c r="D810" s="3">
+        <v>195</v>
+      </c>
+      <c r="E810" s="5">
+        <v>1</v>
+      </c>
+      <c r="F810" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G810" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="811" spans="3:7">
+      <c r="C811" s="6">
+        <v>19525</v>
+      </c>
+      <c r="D811" s="3">
+        <v>195</v>
+      </c>
+      <c r="E811" s="3">
+        <v>1</v>
+      </c>
+      <c r="F811" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G811" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -14765,10 +15210,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -14783,10 +15228,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -14801,10 +15246,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -14819,10 +15264,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -14839,10 +15284,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -14937,10 +15382,10 @@
         <v>203</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H6" s="5"/>
     </row>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="16785" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
     <t>#先锋194龙焰王座</t>
   </si>
   <si>
-    <t>#先锋195</t>
+    <t>#先锋195逐鹿天下</t>
   </si>
   <si>
     <t>Center</t>

--- a/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
+++ b/Excel/StartConfig/Localhost/StartSceneConfig@s.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16785" windowHeight="4560"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="81">
   <si>
     <t>Id</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>#先锋195逐鹿天下</t>
+  </si>
+  <si>
+    <t>#先锋196</t>
   </si>
   <si>
     <t>Center</t>
@@ -1275,7 +1278,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:O811"/>
+  <dimension ref="A3:O837"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -14906,7 +14909,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="801" spans="3:7">
+    <row r="801" spans="1:8">
       <c r="C801" s="6">
         <v>19515</v>
       </c>
@@ -14923,7 +14926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="802" spans="3:7">
+    <row r="802" spans="1:8">
       <c r="C802" s="6">
         <v>19516</v>
       </c>
@@ -14940,7 +14943,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="803" spans="3:7">
+    <row r="803" spans="1:8">
       <c r="C803" s="6">
         <v>19517</v>
       </c>
@@ -14957,7 +14960,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="804" spans="3:7">
+    <row r="804" spans="1:8">
       <c r="C804" s="6">
         <v>19518</v>
       </c>
@@ -14974,7 +14977,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="805" spans="3:7">
+    <row r="805" spans="1:8">
       <c r="C805" s="6">
         <v>19519</v>
       </c>
@@ -14991,7 +14994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="806" spans="3:7">
+    <row r="806" spans="1:8">
       <c r="C806" s="6">
         <v>19520</v>
       </c>
@@ -15008,7 +15011,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="807" spans="3:7">
+    <row r="807" spans="1:8">
       <c r="C807" s="6">
         <v>19521</v>
       </c>
@@ -15025,7 +15028,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="808" spans="3:7">
+    <row r="808" spans="1:8">
       <c r="C808" s="6">
         <v>19522</v>
       </c>
@@ -15042,7 +15045,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="809" spans="3:7">
+    <row r="809" spans="1:8">
       <c r="C809" s="6">
         <v>19523</v>
       </c>
@@ -15059,7 +15062,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="810" spans="3:7">
+    <row r="810" spans="1:8">
       <c r="C810" s="6">
         <v>19524</v>
       </c>
@@ -15076,7 +15079,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="811" spans="3:7">
+    <row r="811" spans="1:8">
       <c r="C811" s="6">
         <v>19525</v>
       </c>
@@ -15090,6 +15093,448 @@
         <v>42</v>
       </c>
       <c r="G811" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="813" spans="1:8">
+      <c r="A813" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C813" s="6">
+        <v>19601</v>
+      </c>
+      <c r="D813" s="3">
+        <v>196</v>
+      </c>
+      <c r="E813" s="5">
+        <v>1</v>
+      </c>
+      <c r="F813" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G813" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H813" s="3">
+        <v>20645</v>
+      </c>
+    </row>
+    <row r="814" spans="1:8">
+      <c r="A814" s="1"/>
+      <c r="B814" s="1"/>
+      <c r="C814" s="6">
+        <v>19602</v>
+      </c>
+      <c r="D814" s="3">
+        <v>196</v>
+      </c>
+      <c r="E814" s="5">
+        <v>1</v>
+      </c>
+      <c r="F814" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G814" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H814" s="3">
+        <v>20646</v>
+      </c>
+    </row>
+    <row r="815" spans="1:8">
+      <c r="C815" s="6">
+        <v>19603</v>
+      </c>
+      <c r="D815" s="3">
+        <v>196</v>
+      </c>
+      <c r="E815" s="5">
+        <v>1</v>
+      </c>
+      <c r="F815" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G815" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H815" s="3">
+        <v>20647</v>
+      </c>
+    </row>
+    <row r="816" spans="1:8">
+      <c r="C816" s="6">
+        <v>19604</v>
+      </c>
+      <c r="D816" s="3">
+        <v>196</v>
+      </c>
+      <c r="E816" s="5">
+        <v>1</v>
+      </c>
+      <c r="F816" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G816" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H816" s="3">
+        <v>20648</v>
+      </c>
+    </row>
+    <row r="817" spans="3:7">
+      <c r="C817" s="6">
+        <v>19605</v>
+      </c>
+      <c r="D817" s="3">
+        <v>196</v>
+      </c>
+      <c r="E817" s="3">
+        <v>1</v>
+      </c>
+      <c r="F817" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G817" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="818" spans="3:7">
+      <c r="C818" s="6">
+        <v>19606</v>
+      </c>
+      <c r="D818" s="3">
+        <v>196</v>
+      </c>
+      <c r="E818" s="5">
+        <v>1</v>
+      </c>
+      <c r="F818" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G818" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="819" spans="3:7">
+      <c r="C819" s="6">
+        <v>19607</v>
+      </c>
+      <c r="D819" s="3">
+        <v>196</v>
+      </c>
+      <c r="E819" s="5">
+        <v>1</v>
+      </c>
+      <c r="F819" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G819" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="820" spans="3:7">
+      <c r="C820" s="6">
+        <v>19608</v>
+      </c>
+      <c r="D820" s="3">
+        <v>196</v>
+      </c>
+      <c r="E820" s="5">
+        <v>1</v>
+      </c>
+      <c r="F820" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G820" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="821" spans="3:7">
+      <c r="C821" s="6">
+        <v>19609</v>
+      </c>
+      <c r="D821" s="3">
+        <v>196</v>
+      </c>
+      <c r="E821" s="3">
+        <v>1</v>
+      </c>
+      <c r="F821" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G821" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="822" spans="3:7">
+      <c r="C822" s="6">
+        <v>19610</v>
+      </c>
+      <c r="D822" s="3">
+        <v>196</v>
+      </c>
+      <c r="E822" s="5">
+        <v>1</v>
+      </c>
+      <c r="F822" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G822" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="823" spans="3:7">
+      <c r="C823" s="6">
+        <v>19611</v>
+      </c>
+      <c r="D823" s="3">
+        <v>196</v>
+      </c>
+      <c r="E823" s="5">
+        <v>1</v>
+      </c>
+      <c r="F823" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G823" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="824" spans="3:7">
+      <c r="C824" s="6">
+        <v>19612</v>
+      </c>
+      <c r="D824" s="3">
+        <v>196</v>
+      </c>
+      <c r="E824" s="5">
+        <v>1</v>
+      </c>
+      <c r="F824" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G824" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="825" spans="3:7">
+      <c r="C825" s="6">
+        <v>19613</v>
+      </c>
+      <c r="D825" s="3">
+        <v>196</v>
+      </c>
+      <c r="E825" s="3">
+        <v>1</v>
+      </c>
+      <c r="F825" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G825" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="826" spans="3:7">
+      <c r="C826" s="6">
+        <v>19614</v>
+      </c>
+      <c r="D826" s="3">
+        <v>196</v>
+      </c>
+      <c r="E826" s="5">
+        <v>1</v>
+      </c>
+      <c r="F826" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G826" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="827" spans="3:7">
+      <c r="C827" s="6">
+        <v>19615</v>
+      </c>
+      <c r="D827" s="3">
+        <v>196</v>
+      </c>
+      <c r="E827" s="5">
+        <v>1</v>
+      </c>
+      <c r="F827" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G827" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="828" spans="3:7">
+      <c r="C828" s="6">
+        <v>19616</v>
+      </c>
+      <c r="D828" s="3">
+        <v>196</v>
+      </c>
+      <c r="E828" s="5">
+        <v>1</v>
+      </c>
+      <c r="F828" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G828" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="829" spans="3:7">
+      <c r="C829" s="6">
+        <v>19617</v>
+      </c>
+      <c r="D829" s="3">
+        <v>196</v>
+      </c>
+      <c r="E829" s="3">
+        <v>1</v>
+      </c>
+      <c r="F829" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G829" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="830" spans="3:7">
+      <c r="C830" s="6">
+        <v>19618</v>
+      </c>
+      <c r="D830" s="3">
+        <v>196</v>
+      </c>
+      <c r="E830" s="5">
+        <v>1</v>
+      </c>
+      <c r="F830" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G830" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="831" spans="3:7">
+      <c r="C831" s="6">
+        <v>19619</v>
+      </c>
+      <c r="D831" s="3">
+        <v>196</v>
+      </c>
+      <c r="E831" s="5">
+        <v>1</v>
+      </c>
+      <c r="F831" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G831" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="832" spans="3:7">
+      <c r="C832" s="6">
+        <v>19620</v>
+      </c>
+      <c r="D832" s="3">
+        <v>196</v>
+      </c>
+      <c r="E832" s="5">
+        <v>1</v>
+      </c>
+      <c r="F832" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G832" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="833" spans="3:7">
+      <c r="C833" s="6">
+        <v>19621</v>
+      </c>
+      <c r="D833" s="3">
+        <v>196</v>
+      </c>
+      <c r="E833" s="3">
+        <v>1</v>
+      </c>
+      <c r="F833" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G833" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="834" spans="3:7">
+      <c r="C834" s="6">
+        <v>19622</v>
+      </c>
+      <c r="D834" s="3">
+        <v>196</v>
+      </c>
+      <c r="E834" s="5">
+        <v>1</v>
+      </c>
+      <c r="F834" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G834" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="835" spans="3:7">
+      <c r="C835" s="6">
+        <v>19623</v>
+      </c>
+      <c r="D835" s="3">
+        <v>196</v>
+      </c>
+      <c r="E835" s="5">
+        <v>1</v>
+      </c>
+      <c r="F835" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G835" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="836" spans="3:7">
+      <c r="C836" s="6">
+        <v>19624</v>
+      </c>
+      <c r="D836" s="3">
+        <v>196</v>
+      </c>
+      <c r="E836" s="5">
+        <v>1</v>
+      </c>
+      <c r="F836" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G836" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="837" spans="3:7">
+      <c r="C837" s="6">
+        <v>19625</v>
+      </c>
+      <c r="D837" s="3">
+        <v>196</v>
+      </c>
+      <c r="E837" s="3">
+        <v>1</v>
+      </c>
+      <c r="F837" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G837" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -15210,10 +15655,10 @@
         <v>202</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H6" s="5"/>
     </row>
@@ -15228,10 +15673,10 @@
         <v>202</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="5"/>
     </row>
@@ -15246,10 +15691,10 @@
         <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -15264,10 +15709,10 @@
         <v>202</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="5">
         <v>20304</v>
@@ -15284,10 +15729,10 @@
         <v>202</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
 